--- a/results_(stress_test)_baselines/summary.xlsx
+++ b/results_(stress_test)_baselines/summary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usouu\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\RnD_Repo\Research_Engineering\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_baselines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D12ABF4A-4C64-4610-8346-7C79EEA49A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F9999C-AD3F-485B-813B-5685C4E104FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="639" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-210" windowWidth="29040" windowHeight="16440" tabRatio="639" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="partialdata_20260429_spt_idx" sheetId="6" r:id="rId1"/>
@@ -620,16 +620,61 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -638,75 +683,30 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1048,10 +1048,10 @@
       <c r="R1" s="12"/>
     </row>
     <row r="2" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="92" t="s">
+      <c r="A2" s="107" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="93"/>
+      <c r="B2" s="108"/>
       <c r="C2">
         <v>92.97270449283009</v>
       </c>
@@ -1079,10 +1079,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:G2)&amp;","</f>
         <v xml:space="preserve">    92.9727044928301, 92.6568511261632, 90.6124851137697, 76.8900480684666, 57.4311571322704,</v>
       </c>
-      <c r="K2" s="92" t="s">
+      <c r="K2" s="107" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="93"/>
+      <c r="L2" s="108"/>
       <c r="M2">
         <v>3.6723191410127392</v>
       </c>
@@ -1104,10 +1104,10 @@
       </c>
     </row>
     <row r="3" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="107" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="93"/>
+      <c r="B3" s="108"/>
       <c r="C3">
         <v>93.550650668835075</v>
       </c>
@@ -1135,10 +1135,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:G3)&amp;","</f>
         <v xml:space="preserve">    93.5506506688351, 92.2822198577266, 90.5016796569751, 72.8058085854261, 54.0640662981514,</v>
       </c>
-      <c r="K3" s="92" t="s">
+      <c r="K3" s="107" t="s">
         <v>6</v>
       </c>
-      <c r="L3" s="93"/>
+      <c r="L3" s="108"/>
       <c r="M3">
         <v>3.5444962758226279</v>
       </c>
@@ -1160,10 +1160,10 @@
       </c>
     </row>
     <row r="4" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="92" t="s">
+      <c r="A4" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="93"/>
+      <c r="B4" s="108"/>
       <c r="C4">
         <v>88.646029233240199</v>
       </c>
@@ -1191,10 +1191,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C4:G4)&amp;","</f>
         <v xml:space="preserve">    88.6460292332402, 87.5880039331367, 87.1022730877141, 74.8267141872623, 50.0552455759421,</v>
       </c>
-      <c r="K4" s="92" t="s">
+      <c r="K4" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="93"/>
+      <c r="L4" s="108"/>
       <c r="M4">
         <v>3.1531095164540388</v>
       </c>
@@ -1216,27 +1216,27 @@
       </c>
     </row>
     <row r="5" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="98"/>
-      <c r="C5" s="98"/>
-      <c r="D5" s="98"/>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
+      <c r="B5" s="109"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="109"/>
+      <c r="E5" s="109"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="109"/>
       <c r="H5" s="34"/>
       <c r="I5" s="34"/>
       <c r="J5" s="12"/>
-      <c r="K5" s="92" t="s">
+      <c r="K5" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="98"/>
-      <c r="M5" s="98"/>
-      <c r="N5" s="98"/>
-      <c r="O5" s="98"/>
-      <c r="P5" s="98"/>
-      <c r="Q5" s="98"/>
+      <c r="L5" s="109"/>
+      <c r="M5" s="109"/>
+      <c r="N5" s="109"/>
+      <c r="O5" s="109"/>
+      <c r="P5" s="109"/>
+      <c r="Q5" s="109"/>
       <c r="R5" s="12"/>
     </row>
     <row r="6" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -1306,22 +1306,32 @@
       <c r="B7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="51"/>
-      <c r="D7" s="52"/>
-      <c r="E7" s="52"/>
-      <c r="F7" s="52"/>
-      <c r="G7" s="52"/>
+      <c r="C7">
+        <v>92.744346116027529</v>
+      </c>
+      <c r="D7">
+        <v>92.328416912487711</v>
+      </c>
+      <c r="E7">
+        <v>91.156108616856514</v>
+      </c>
+      <c r="F7">
+        <v>82.307782362592519</v>
+      </c>
+      <c r="G7">
+        <v>57.694504277718679</v>
+      </c>
       <c r="H7" s="34" cm="1">
         <f t="array" ref="H7">-SUMPRODUCT((D1:F1-C1:E1)*(C7:E7+D7:F7)/2)</f>
-        <v>0</v>
+        <v>80.045249634512402</v>
       </c>
       <c r="I7" s="34" cm="1">
         <f t="array" ref="I7">-SUMPRODUCT((D1:G1-C1:F1)*(C7:F7+D7:G7)/2)</f>
-        <v>0</v>
+        <v>84.420321092022121</v>
       </c>
       <c r="J7" s="12" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C7:G7)&amp;","</f>
-        <v xml:space="preserve">    ,</v>
+        <v xml:space="preserve">    92.7443461160275, 92.3284169124877, 91.1561086168565, 82.3077823625925, 57.6945042777187,</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>11</v>
@@ -1340,34 +1350,34 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="92" t="s">
+      <c r="A8" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="98"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="104"/>
-      <c r="E8" s="104"/>
-      <c r="F8" s="104"/>
-      <c r="G8" s="104"/>
+      <c r="B8" s="109"/>
+      <c r="C8" s="113"/>
+      <c r="D8" s="113"/>
+      <c r="E8" s="113"/>
+      <c r="F8" s="113"/>
+      <c r="G8" s="113"/>
       <c r="H8" s="34"/>
       <c r="I8" s="34"/>
       <c r="J8" s="12"/>
-      <c r="K8" s="92" t="s">
+      <c r="K8" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="L8" s="98"/>
-      <c r="M8" s="104"/>
-      <c r="N8" s="104"/>
-      <c r="O8" s="104"/>
-      <c r="P8" s="104"/>
-      <c r="Q8" s="104"/>
+      <c r="L8" s="109"/>
+      <c r="M8" s="113"/>
+      <c r="N8" s="113"/>
+      <c r="O8" s="113"/>
+      <c r="P8" s="113"/>
+      <c r="Q8" s="113"/>
       <c r="R8" s="12"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="92" t="s">
+      <c r="A9" s="107" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="93"/>
+      <c r="B9" s="108"/>
       <c r="C9">
         <v>93.207752662220258</v>
       </c>
@@ -1395,10 +1405,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C9:G9)&amp;","</f>
         <v xml:space="preserve">    93.2077526622203, 92.7830344553153, 90.5658843646283, 73.0768864782567, 58.5569944376681,</v>
       </c>
-      <c r="K9" s="92" t="s">
+      <c r="K9" s="107" t="s">
         <v>7</v>
       </c>
-      <c r="L9" s="93"/>
+      <c r="L9" s="108"/>
       <c r="M9">
         <v>4.081079160307894</v>
       </c>
@@ -1420,10 +1430,10 @@
       </c>
     </row>
     <row r="10" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="96" t="s">
+      <c r="A10" s="111" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="97"/>
+      <c r="B10" s="112"/>
       <c r="C10">
         <v>93.534975792754821</v>
       </c>
@@ -1451,10 +1461,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C10:G10)&amp;","</f>
         <v xml:space="preserve">    93.5349757927548, 92.3364677318431, 88.5935201284902, 71.0452945094681, 53.4670628638656,</v>
       </c>
-      <c r="K10" s="92" t="s">
+      <c r="K10" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="L10" s="93"/>
+      <c r="L10" s="108"/>
       <c r="M10">
         <v>3.8494978151380188</v>
       </c>
@@ -1476,10 +1486,10 @@
       </c>
     </row>
     <row r="11" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="92" t="s">
+      <c r="A11" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="93"/>
+      <c r="B11" s="108"/>
       <c r="C11">
         <v>93.005297046975599</v>
       </c>
@@ -1507,10 +1517,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C11:G11)&amp;","</f>
         <v xml:space="preserve">    93.0052970469756, 91.9024443694726, 89.1162783991788, 72.2588142342639, 53.8436289817963,</v>
       </c>
-      <c r="K11" s="92" t="s">
+      <c r="K11" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="L11" s="93"/>
+      <c r="L11" s="108"/>
       <c r="M11">
         <v>3.458803648865628</v>
       </c>
@@ -1532,10 +1542,10 @@
       </c>
     </row>
     <row r="12" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="92" t="s">
+      <c r="A12" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="93"/>
+      <c r="B12" s="108"/>
       <c r="C12" s="35"/>
       <c r="D12" s="36"/>
       <c r="E12" s="36"/>
@@ -1553,10 +1563,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C12:G12)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="K12" s="92" t="s">
+      <c r="K12" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="L12" s="93"/>
+      <c r="L12" s="108"/>
       <c r="M12" s="35"/>
       <c r="N12" s="36"/>
       <c r="O12" s="36"/>
@@ -1568,34 +1578,34 @@
       </c>
     </row>
     <row r="13" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="92" t="s">
+      <c r="A13" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="98"/>
-      <c r="C13" s="99"/>
-      <c r="D13" s="99"/>
-      <c r="E13" s="99"/>
-      <c r="F13" s="99"/>
-      <c r="G13" s="99"/>
+      <c r="B13" s="109"/>
+      <c r="C13" s="110"/>
+      <c r="D13" s="110"/>
+      <c r="E13" s="110"/>
+      <c r="F13" s="110"/>
+      <c r="G13" s="110"/>
       <c r="H13" s="34"/>
       <c r="I13" s="34"/>
       <c r="J13" s="12"/>
-      <c r="K13" s="92" t="s">
+      <c r="K13" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="L13" s="98"/>
-      <c r="M13" s="99"/>
-      <c r="N13" s="99"/>
-      <c r="O13" s="99"/>
-      <c r="P13" s="99"/>
-      <c r="Q13" s="99"/>
+      <c r="L13" s="109"/>
+      <c r="M13" s="110"/>
+      <c r="N13" s="110"/>
+      <c r="O13" s="110"/>
+      <c r="P13" s="110"/>
+      <c r="Q13" s="110"/>
       <c r="R13" s="12"/>
     </row>
     <row r="14" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="92" t="s">
+      <c r="A14" s="107" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="93"/>
+      <c r="B14" s="108"/>
       <c r="C14">
         <v>93.204569243678591</v>
       </c>
@@ -1623,10 +1633,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C14:G14)&amp;","</f>
         <v xml:space="preserve">    93.2045692436786, 92.7189364383198, 91.0101961666335, 77.7756122457807, 55.9218563021018,</v>
       </c>
-      <c r="K14" s="92" t="s">
+      <c r="K14" s="107" t="s">
         <v>7</v>
       </c>
-      <c r="L14" s="93"/>
+      <c r="L14" s="108"/>
       <c r="M14">
         <v>3.5338969773137729</v>
       </c>
@@ -1648,10 +1658,10 @@
       </c>
     </row>
     <row r="15" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="96" t="s">
+      <c r="A15" s="111" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="97"/>
+      <c r="B15" s="112"/>
       <c r="C15">
         <v>91.935155148400952</v>
       </c>
@@ -1679,10 +1689,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C15:G15)&amp;","</f>
         <v xml:space="preserve">    91.935155148401, 91.6922551233142, 89.8476486244114, 79.4007474113098, 53.2536440626649,</v>
       </c>
-      <c r="K15" s="92" t="s">
+      <c r="K15" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="L15" s="93"/>
+      <c r="L15" s="108"/>
       <c r="M15">
         <v>3.0404967647063641</v>
       </c>
@@ -1704,10 +1714,10 @@
       </c>
     </row>
     <row r="16" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="92" t="s">
+      <c r="A16" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="93"/>
+      <c r="B16" s="108"/>
       <c r="C16">
         <v>93.32960781090955</v>
       </c>
@@ -1735,10 +1745,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C16:G16)&amp;","</f>
         <v xml:space="preserve">    93.3296078109096, 92.6274333399655, 90.919543710009, 77.7434003177651, 58.3910702803081,</v>
       </c>
-      <c r="K16" s="92" t="s">
+      <c r="K16" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="L16" s="93"/>
+      <c r="L16" s="108"/>
       <c r="M16">
         <v>3.3471189071482028</v>
       </c>
@@ -1760,10 +1770,10 @@
       </c>
     </row>
     <row r="17" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="92" t="s">
+      <c r="A17" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="93"/>
+      <c r="B17" s="108"/>
       <c r="C17" s="35"/>
       <c r="D17" s="36"/>
       <c r="E17" s="36"/>
@@ -1781,10 +1791,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C17:G17)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="K17" s="92" t="s">
+      <c r="K17" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="L17" s="93"/>
+      <c r="L17" s="108"/>
       <c r="M17" s="35"/>
       <c r="N17" s="36"/>
       <c r="O17" s="36"/>
@@ -1862,10 +1872,10 @@
       <c r="R19" s="1"/>
     </row>
     <row r="20" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="94" t="s">
+      <c r="A20" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="95"/>
+      <c r="B20" s="101"/>
       <c r="C20">
         <v>92.485449200300948</v>
       </c>
@@ -1887,10 +1897,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C20:G20)&amp;","</f>
         <v xml:space="preserve">    92.4854492003009, 92.1853579700095, 90.0493612740203, 76.4241798948027, 55.8171663737853,</v>
       </c>
-      <c r="K20" s="94" t="s">
+      <c r="K20" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="L20" s="95"/>
+      <c r="L20" s="101"/>
       <c r="M20">
         <v>4.0542209595909764</v>
       </c>
@@ -1912,10 +1922,10 @@
       </c>
     </row>
     <row r="21" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="94" t="s">
+      <c r="A21" s="100" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="95"/>
+      <c r="B21" s="101"/>
       <c r="C21">
         <v>93.221737995090834</v>
       </c>
@@ -1937,10 +1947,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:G21)&amp;","</f>
         <v xml:space="preserve">    93.2217379950908, 91.8880330056846, 90.0239389840154, 72.2904200814482, 51.8413052641743,</v>
       </c>
-      <c r="K21" s="94" t="s">
+      <c r="K21" s="100" t="s">
         <v>6</v>
       </c>
-      <c r="L21" s="95"/>
+      <c r="L21" s="101"/>
       <c r="M21">
         <v>3.877808098377264</v>
       </c>
@@ -1962,10 +1972,10 @@
       </c>
     </row>
     <row r="22" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="94" t="s">
+      <c r="A22" s="100" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="95"/>
+      <c r="B22" s="101"/>
       <c r="C22">
         <v>88.242190127710941</v>
       </c>
@@ -1987,10 +1997,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C22:G22)&amp;","</f>
         <v xml:space="preserve">    88.2421901277109, 87.2356592457238, 86.8403563631381, 74.5410000823158, 48.9795299923061,</v>
       </c>
-      <c r="K22" s="94" t="s">
+      <c r="K22" s="100" t="s">
         <v>10</v>
       </c>
-      <c r="L22" s="95"/>
+      <c r="L22" s="101"/>
       <c r="M22">
         <v>3.345739818904093</v>
       </c>
@@ -2012,27 +2022,27 @@
       </c>
     </row>
     <row r="23" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="94" t="s">
+      <c r="A23" s="100" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="101"/>
-      <c r="C23" s="101"/>
-      <c r="D23" s="101"/>
-      <c r="E23" s="101"/>
-      <c r="F23" s="101"/>
-      <c r="G23" s="101"/>
+      <c r="B23" s="104"/>
+      <c r="C23" s="104"/>
+      <c r="D23" s="104"/>
+      <c r="E23" s="104"/>
+      <c r="F23" s="104"/>
+      <c r="G23" s="104"/>
       <c r="H23" s="40"/>
       <c r="I23" s="40"/>
       <c r="J23" s="1"/>
-      <c r="K23" s="94" t="s">
+      <c r="K23" s="100" t="s">
         <v>12</v>
       </c>
-      <c r="L23" s="101"/>
-      <c r="M23" s="101"/>
-      <c r="N23" s="101"/>
-      <c r="O23" s="101"/>
-      <c r="P23" s="101"/>
-      <c r="Q23" s="101"/>
+      <c r="L23" s="104"/>
+      <c r="M23" s="104"/>
+      <c r="N23" s="104"/>
+      <c r="O23" s="104"/>
+      <c r="P23" s="104"/>
+      <c r="Q23" s="104"/>
       <c r="R23" s="1"/>
     </row>
     <row r="24" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -2124,34 +2134,34 @@
       </c>
     </row>
     <row r="26" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="94" t="s">
+      <c r="A26" s="100" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="101"/>
-      <c r="C26" s="111"/>
-      <c r="D26" s="111"/>
-      <c r="E26" s="111"/>
-      <c r="F26" s="111"/>
-      <c r="G26" s="111"/>
+      <c r="B26" s="104"/>
+      <c r="C26" s="106"/>
+      <c r="D26" s="106"/>
+      <c r="E26" s="106"/>
+      <c r="F26" s="106"/>
+      <c r="G26" s="106"/>
       <c r="H26" s="40"/>
       <c r="I26" s="40"/>
       <c r="J26" s="1"/>
-      <c r="K26" s="94" t="s">
+      <c r="K26" s="100" t="s">
         <v>20</v>
       </c>
-      <c r="L26" s="101"/>
-      <c r="M26" s="111"/>
-      <c r="N26" s="111"/>
-      <c r="O26" s="111"/>
-      <c r="P26" s="111"/>
-      <c r="Q26" s="111"/>
+      <c r="L26" s="104"/>
+      <c r="M26" s="106"/>
+      <c r="N26" s="106"/>
+      <c r="O26" s="106"/>
+      <c r="P26" s="106"/>
+      <c r="Q26" s="106"/>
       <c r="R26" s="1"/>
     </row>
     <row r="27" spans="1:18" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="94" t="s">
+      <c r="A27" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="B27" s="95"/>
+      <c r="B27" s="101"/>
       <c r="C27">
         <v>92.781043798288394</v>
       </c>
@@ -2173,10 +2183,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C27:G27)&amp;","</f>
         <v xml:space="preserve">    92.7810437982884, 92.3938056553932, 90.0090839662476, 72.4981719652037, 56.6748529979919,</v>
       </c>
-      <c r="K27" s="94" t="s">
+      <c r="K27" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="L27" s="95"/>
+      <c r="L27" s="101"/>
       <c r="M27">
         <v>4.5014366094349993</v>
       </c>
@@ -2198,10 +2208,10 @@
       </c>
     </row>
     <row r="28" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="94" t="s">
+      <c r="A28" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="95"/>
+      <c r="B28" s="101"/>
       <c r="C28">
         <v>93.113144022293241</v>
       </c>
@@ -2223,10 +2233,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C28:G28)&amp;","</f>
         <v xml:space="preserve">    93.1131440222932, 91.9496041120699, 88.043149271791, 70.4378143831585, 50.0271657882747,</v>
       </c>
-      <c r="K28" s="94" t="s">
+      <c r="K28" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="L28" s="95"/>
+      <c r="L28" s="101"/>
       <c r="M28">
         <v>4.249709534316878</v>
       </c>
@@ -2248,10 +2258,10 @@
       </c>
     </row>
     <row r="29" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="94" t="s">
+      <c r="A29" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="95"/>
+      <c r="B29" s="101"/>
       <c r="C29">
         <v>92.587964837227005</v>
       </c>
@@ -2273,10 +2283,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C29:G29)&amp;","</f>
         <v xml:space="preserve">    92.587964837227, 91.4235824416001, 88.5454649294227, 71.6598005950386, 50.2664690265607,</v>
       </c>
-      <c r="K29" s="94" t="s">
+      <c r="K29" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="L29" s="95"/>
+      <c r="L29" s="101"/>
       <c r="M29">
         <v>3.7645606938355249</v>
       </c>
@@ -2298,10 +2308,10 @@
       </c>
     </row>
     <row r="30" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="94" t="s">
+      <c r="A30" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="95"/>
+      <c r="B30" s="101"/>
       <c r="C30" s="41"/>
       <c r="D30" s="42"/>
       <c r="E30" s="42"/>
@@ -2313,10 +2323,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C30:G30)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="K30" s="94" t="s">
+      <c r="K30" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="L30" s="95"/>
+      <c r="L30" s="101"/>
       <c r="M30" s="41"/>
       <c r="N30" s="42"/>
       <c r="O30" s="42"/>
@@ -2328,34 +2338,34 @@
       </c>
     </row>
     <row r="31" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="94" t="s">
+      <c r="A31" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="B31" s="101"/>
-      <c r="C31" s="102"/>
-      <c r="D31" s="102"/>
-      <c r="E31" s="102"/>
-      <c r="F31" s="102"/>
-      <c r="G31" s="102"/>
+      <c r="B31" s="104"/>
+      <c r="C31" s="105"/>
+      <c r="D31" s="105"/>
+      <c r="E31" s="105"/>
+      <c r="F31" s="105"/>
+      <c r="G31" s="105"/>
       <c r="H31" s="40"/>
       <c r="I31" s="40"/>
       <c r="J31" s="1"/>
-      <c r="K31" s="94" t="s">
+      <c r="K31" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="L31" s="101"/>
-      <c r="M31" s="102"/>
-      <c r="N31" s="102"/>
-      <c r="O31" s="102"/>
-      <c r="P31" s="102"/>
-      <c r="Q31" s="102"/>
+      <c r="L31" s="104"/>
+      <c r="M31" s="105"/>
+      <c r="N31" s="105"/>
+      <c r="O31" s="105"/>
+      <c r="P31" s="105"/>
+      <c r="Q31" s="105"/>
       <c r="R31" s="1"/>
     </row>
     <row r="32" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="94" t="s">
+      <c r="A32" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="B32" s="95"/>
+      <c r="B32" s="101"/>
       <c r="C32">
         <v>92.779242983398433</v>
       </c>
@@ -2377,10 +2387,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C32:G32)&amp;","</f>
         <v xml:space="preserve">    92.7792429833984, 92.2402701949049, 90.5523014335592, 77.4468153062754, 54.049481297537,</v>
       </c>
-      <c r="K32" s="94" t="s">
+      <c r="K32" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="L32" s="95"/>
+      <c r="L32" s="101"/>
       <c r="M32">
         <v>3.8708284466838099</v>
       </c>
@@ -2402,10 +2412,10 @@
       </c>
     </row>
     <row r="33" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="105" t="s">
+      <c r="A33" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="106"/>
+      <c r="B33" s="103"/>
       <c r="C33">
         <v>91.529115829853595</v>
       </c>
@@ -2427,10 +2437,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C33:G33)&amp;","</f>
         <v xml:space="preserve">    91.5291158298536, 91.3506434233222, 89.3417609327998, 79.0450519987888, 52.3197117316979,</v>
       </c>
-      <c r="K33" s="94" t="s">
+      <c r="K33" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="L33" s="95"/>
+      <c r="L33" s="101"/>
       <c r="M33">
         <v>3.326792742141544</v>
       </c>
@@ -2452,10 +2462,10 @@
       </c>
     </row>
     <row r="34" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="94" t="s">
+      <c r="A34" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="B34" s="95"/>
+      <c r="B34" s="101"/>
       <c r="C34">
         <v>92.904210456970588</v>
       </c>
@@ -2477,10 +2487,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C34:G34)&amp;","</f>
         <v xml:space="preserve">    92.9042104569706, 92.1891124359732, 90.4960366989424, 77.336951327755, 56.2225359371609,</v>
       </c>
-      <c r="K34" s="94" t="s">
+      <c r="K34" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="L34" s="95"/>
+      <c r="L34" s="101"/>
       <c r="M34">
         <v>3.6016716439248402</v>
       </c>
@@ -2502,10 +2512,10 @@
       </c>
     </row>
     <row r="35" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="94" t="s">
+      <c r="A35" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="B35" s="95"/>
+      <c r="B35" s="101"/>
       <c r="C35" s="41"/>
       <c r="D35" s="42"/>
       <c r="E35" s="42"/>
@@ -2517,10 +2527,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C35:G35)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="K35" s="94" t="s">
+      <c r="K35" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="L35" s="95"/>
+      <c r="L35" s="101"/>
       <c r="M35" s="41"/>
       <c r="N35" s="42"/>
       <c r="O35" s="42"/>
@@ -2601,6 +2611,54 @@
     </row>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="K5:Q5"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="K8:Q8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="K13:Q13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="K23:Q23"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="K26:Q26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="K31:Q31"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="K35:L35"/>
     <mergeCell ref="A32:B32"/>
@@ -2609,56 +2667,314 @@
     <mergeCell ref="K33:L33"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="K34:L34"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="K31:Q31"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="K26:Q26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="K23:Q23"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="K13:Q13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="K5:Q5"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="K8:Q8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="K4:L4"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="C2:G4 C6:G7 C9:G12 C14:G17">
+    <cfRule type="colorScale" priority="294">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:G4 H2:I17">
+    <cfRule type="colorScale" priority="277">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:G4">
+    <cfRule type="colorScale" priority="298">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="299">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="300">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3:G4 H3:I5">
+    <cfRule type="colorScale" priority="280">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="281">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="282">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="283">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="284">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="285">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C6:G6">
+    <cfRule type="colorScale" priority="301">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="302">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C7:G7">
+    <cfRule type="colorScale" priority="303">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="304">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9:G11 C14:G16">
+    <cfRule type="colorScale" priority="305">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9:G11">
+    <cfRule type="colorScale" priority="307">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="308">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="309">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9:G12 C14:G17 C6:G7 C2:G4">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C9:G12 C14:G17">
+    <cfRule type="colorScale" priority="310">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14:G16">
+    <cfRule type="colorScale" priority="312">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="313">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="314">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H17">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H31:H35">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="I2:I17">
     <cfRule type="colorScale" priority="2">
       <colorScale>
@@ -2682,82 +2998,6 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:G4 H2:I17">
-    <cfRule type="colorScale" priority="277">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C3:G4 H3:I5">
-    <cfRule type="colorScale" priority="280">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="281">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="282">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="283">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="284">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="285">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I31:I35">
     <cfRule type="colorScale" priority="292">
       <colorScale>
         <cfvo type="min"/>
@@ -2769,240 +3009,6 @@
       </colorScale>
     </cfRule>
     <cfRule type="colorScale" priority="293">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:G4 C6:G7 C9:G12 C14:G17">
-    <cfRule type="colorScale" priority="294">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:G4">
-    <cfRule type="colorScale" priority="298">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="299">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="300">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C6:G6">
-    <cfRule type="colorScale" priority="301">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="302">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C7:G7">
-    <cfRule type="colorScale" priority="303">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="304">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C9:G11 C14:G16">
-    <cfRule type="colorScale" priority="305">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C9:G11">
-    <cfRule type="colorScale" priority="307">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="308">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="309">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C9:G12 C14:G17">
-    <cfRule type="colorScale" priority="310">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C14:G16">
-    <cfRule type="colorScale" priority="312">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="313">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="314">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C9:G12 C14:G17 C6:G7 C2:G4">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H17">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H31:H35">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H31:H35">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3096,10 +3102,10 @@
       <c r="V1" s="12"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="92" t="s">
+      <c r="A2" s="107" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="93"/>
+      <c r="B2" s="108"/>
       <c r="C2" s="20"/>
       <c r="D2" s="21"/>
       <c r="E2" s="21"/>
@@ -3119,10 +3125,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:I2)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M2" s="92" t="s">
+      <c r="M2" s="107" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="93"/>
+      <c r="N2" s="108"/>
       <c r="O2" s="31"/>
       <c r="P2" s="32"/>
       <c r="Q2" s="32"/>
@@ -3136,10 +3142,10 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="92" t="s">
+      <c r="A3" s="107" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="93"/>
+      <c r="B3" s="108"/>
       <c r="C3" s="31"/>
       <c r="D3" s="32"/>
       <c r="E3" s="32"/>
@@ -3159,10 +3165,10 @@
         <f t="shared" ref="L3:L18" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M3" s="92" t="s">
+      <c r="M3" s="107" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="93"/>
+      <c r="N3" s="108"/>
       <c r="O3" s="31"/>
       <c r="P3" s="32"/>
       <c r="Q3" s="32"/>
@@ -3176,10 +3182,10 @@
       </c>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="92" t="s">
+      <c r="A4" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="93"/>
+      <c r="B4" s="108"/>
       <c r="C4" s="24"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
@@ -3199,10 +3205,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M4" s="92" t="s">
+      <c r="M4" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="93"/>
+      <c r="N4" s="108"/>
       <c r="O4" s="43"/>
       <c r="P4" s="26"/>
       <c r="Q4" s="26"/>
@@ -3216,35 +3222,35 @@
       </c>
     </row>
     <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="92" t="s">
+      <c r="A5" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="98"/>
-      <c r="C5" s="98"/>
-      <c r="D5" s="98"/>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="93"/>
+      <c r="B5" s="109"/>
+      <c r="C5" s="109"/>
+      <c r="D5" s="109"/>
+      <c r="E5" s="109"/>
+      <c r="F5" s="109"/>
+      <c r="G5" s="109"/>
+      <c r="H5" s="109"/>
+      <c r="I5" s="108"/>
       <c r="J5" s="34"/>
       <c r="K5" s="34"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="92" t="s">
+      <c r="M5" s="107" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="98"/>
-      <c r="O5" s="98"/>
-      <c r="P5" s="98"/>
-      <c r="Q5" s="98"/>
-      <c r="R5" s="98"/>
-      <c r="S5" s="98"/>
-      <c r="T5" s="98"/>
-      <c r="U5" s="93"/>
+      <c r="N5" s="109"/>
+      <c r="O5" s="109"/>
+      <c r="P5" s="109"/>
+      <c r="Q5" s="109"/>
+      <c r="R5" s="109"/>
+      <c r="S5" s="109"/>
+      <c r="T5" s="109"/>
+      <c r="U5" s="108"/>
       <c r="V5" s="12"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="96" t="s">
+      <c r="A6" s="111" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -3269,7 +3275,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M6" s="96" t="s">
+      <c r="M6" s="111" t="s">
         <v>11</v>
       </c>
       <c r="N6" s="8" t="s">
@@ -3288,7 +3294,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="107"/>
+      <c r="A7" s="114"/>
       <c r="B7" s="8" t="s">
         <v>14</v>
       </c>
@@ -3311,7 +3317,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M7" s="107"/>
+      <c r="M7" s="114"/>
       <c r="N7" s="8" t="s">
         <v>14</v>
       </c>
@@ -3328,7 +3334,7 @@
       </c>
     </row>
     <row r="8" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="107"/>
+      <c r="A8" s="114"/>
       <c r="B8" s="8" t="s">
         <v>17</v>
       </c>
@@ -3351,7 +3357,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M8" s="107"/>
+      <c r="M8" s="114"/>
       <c r="N8" s="8" t="s">
         <v>17</v>
       </c>
@@ -3365,7 +3371,7 @@
       <c r="V8" s="12"/>
     </row>
     <row r="9" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="107"/>
+      <c r="A9" s="114"/>
       <c r="B9" s="8" t="s">
         <v>18</v>
       </c>
@@ -3388,7 +3394,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M9" s="107"/>
+      <c r="M9" s="114"/>
       <c r="N9" s="8" t="s">
         <v>18</v>
       </c>
@@ -3402,7 +3408,7 @@
       <c r="V9" s="12"/>
     </row>
     <row r="10" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="107"/>
+      <c r="A10" s="114"/>
       <c r="B10" s="8" t="s">
         <v>15</v>
       </c>
@@ -3425,7 +3431,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M10" s="107"/>
+      <c r="M10" s="114"/>
       <c r="N10" s="8" t="s">
         <v>15</v>
       </c>
@@ -3439,7 +3445,7 @@
       <c r="V10" s="12"/>
     </row>
     <row r="11" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="107"/>
+      <c r="A11" s="114"/>
       <c r="B11" s="8" t="s">
         <v>25</v>
       </c>
@@ -3462,7 +3468,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M11" s="107"/>
+      <c r="M11" s="114"/>
       <c r="N11" s="8" t="s">
         <v>25</v>
       </c>
@@ -3476,7 +3482,7 @@
       <c r="V11" s="12"/>
     </row>
     <row r="12" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="107"/>
+      <c r="A12" s="114"/>
       <c r="B12" s="8" t="s">
         <v>19</v>
       </c>
@@ -3499,7 +3505,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M12" s="107"/>
+      <c r="M12" s="114"/>
       <c r="N12" s="8" t="s">
         <v>19</v>
       </c>
@@ -3513,7 +3519,7 @@
       <c r="V12" s="12"/>
     </row>
     <row r="13" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="107"/>
+      <c r="A13" s="114"/>
       <c r="B13" s="8" t="s">
         <v>16</v>
       </c>
@@ -3536,7 +3542,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M13" s="107"/>
+      <c r="M13" s="114"/>
       <c r="N13" s="8" t="s">
         <v>16</v>
       </c>
@@ -3550,7 +3556,7 @@
       <c r="V13" s="12"/>
     </row>
     <row r="14" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="108"/>
+      <c r="A14" s="115"/>
       <c r="B14" s="8" t="s">
         <v>26</v>
       </c>
@@ -3573,7 +3579,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M14" s="108"/>
+      <c r="M14" s="115"/>
       <c r="N14" s="8" t="s">
         <v>26</v>
       </c>
@@ -3587,38 +3593,38 @@
       <c r="V14" s="12"/>
     </row>
     <row r="15" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="92" t="s">
+      <c r="A15" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="98"/>
-      <c r="C15" s="99"/>
-      <c r="D15" s="99"/>
-      <c r="E15" s="99"/>
-      <c r="F15" s="99"/>
-      <c r="G15" s="99"/>
-      <c r="H15" s="99"/>
-      <c r="I15" s="100"/>
+      <c r="B15" s="109"/>
+      <c r="C15" s="110"/>
+      <c r="D15" s="110"/>
+      <c r="E15" s="110"/>
+      <c r="F15" s="110"/>
+      <c r="G15" s="110"/>
+      <c r="H15" s="110"/>
+      <c r="I15" s="119"/>
       <c r="J15" s="34"/>
       <c r="K15" s="34"/>
       <c r="L15" s="12"/>
-      <c r="M15" s="92" t="s">
+      <c r="M15" s="107" t="s">
         <v>20</v>
       </c>
-      <c r="N15" s="98"/>
-      <c r="O15" s="104"/>
-      <c r="P15" s="104"/>
-      <c r="Q15" s="104"/>
-      <c r="R15" s="104"/>
-      <c r="S15" s="104"/>
-      <c r="T15" s="104"/>
-      <c r="U15" s="97"/>
+      <c r="N15" s="109"/>
+      <c r="O15" s="113"/>
+      <c r="P15" s="113"/>
+      <c r="Q15" s="113"/>
+      <c r="R15" s="113"/>
+      <c r="S15" s="113"/>
+      <c r="T15" s="113"/>
+      <c r="U15" s="112"/>
       <c r="V15" s="12"/>
     </row>
     <row r="16" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="92" t="s">
+      <c r="A16" s="107" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="93"/>
+      <c r="B16" s="108"/>
       <c r="C16" s="46"/>
       <c r="D16" s="47"/>
       <c r="E16" s="47"/>
@@ -3638,10 +3644,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M16" s="92" t="s">
+      <c r="M16" s="107" t="s">
         <v>7</v>
       </c>
-      <c r="N16" s="93"/>
+      <c r="N16" s="108"/>
       <c r="O16" s="46"/>
       <c r="P16" s="47"/>
       <c r="Q16" s="47"/>
@@ -3655,10 +3661,10 @@
       </c>
     </row>
     <row r="17" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="96" t="s">
+      <c r="A17" s="111" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="97"/>
+      <c r="B17" s="112"/>
       <c r="C17" s="49"/>
       <c r="D17" s="12"/>
       <c r="E17" s="12"/>
@@ -3678,10 +3684,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M17" s="92" t="s">
+      <c r="M17" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="N17" s="93"/>
+      <c r="N17" s="108"/>
       <c r="O17" s="49"/>
       <c r="P17" s="12"/>
       <c r="Q17" s="12"/>
@@ -3695,10 +3701,10 @@
       </c>
     </row>
     <row r="18" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="92" t="s">
+      <c r="A18" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="93"/>
+      <c r="B18" s="108"/>
       <c r="C18" s="49"/>
       <c r="D18" s="12"/>
       <c r="E18" s="12"/>
@@ -3718,10 +3724,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M18" s="92" t="s">
+      <c r="M18" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="N18" s="93"/>
+      <c r="N18" s="108"/>
       <c r="O18" s="49"/>
       <c r="P18" s="12"/>
       <c r="Q18" s="12"/>
@@ -3735,10 +3741,10 @@
       </c>
     </row>
     <row r="19" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="92" t="s">
+      <c r="A19" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="93"/>
+      <c r="B19" s="108"/>
       <c r="C19" s="51"/>
       <c r="D19" s="52"/>
       <c r="E19" s="52"/>
@@ -3755,10 +3761,10 @@
         <v>0</v>
       </c>
       <c r="L19" s="12"/>
-      <c r="M19" s="92" t="s">
+      <c r="M19" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="N19" s="93"/>
+      <c r="N19" s="108"/>
       <c r="O19" s="51"/>
       <c r="P19" s="52"/>
       <c r="Q19" s="52"/>
@@ -3769,38 +3775,38 @@
       <c r="V19" s="12"/>
     </row>
     <row r="20" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="92" t="s">
+      <c r="A20" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="98"/>
-      <c r="C20" s="99"/>
-      <c r="D20" s="99"/>
-      <c r="E20" s="99"/>
-      <c r="F20" s="99"/>
-      <c r="G20" s="99"/>
-      <c r="H20" s="99"/>
-      <c r="I20" s="100"/>
+      <c r="B20" s="109"/>
+      <c r="C20" s="110"/>
+      <c r="D20" s="110"/>
+      <c r="E20" s="110"/>
+      <c r="F20" s="110"/>
+      <c r="G20" s="110"/>
+      <c r="H20" s="110"/>
+      <c r="I20" s="119"/>
       <c r="J20" s="34"/>
       <c r="K20" s="34"/>
       <c r="L20" s="12"/>
-      <c r="M20" s="92" t="s">
+      <c r="M20" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="N20" s="98"/>
-      <c r="O20" s="99"/>
-      <c r="P20" s="99"/>
-      <c r="Q20" s="99"/>
-      <c r="R20" s="99"/>
-      <c r="S20" s="99"/>
-      <c r="T20" s="99"/>
-      <c r="U20" s="100"/>
+      <c r="N20" s="109"/>
+      <c r="O20" s="110"/>
+      <c r="P20" s="110"/>
+      <c r="Q20" s="110"/>
+      <c r="R20" s="110"/>
+      <c r="S20" s="110"/>
+      <c r="T20" s="110"/>
+      <c r="U20" s="119"/>
       <c r="V20" s="12"/>
     </row>
     <row r="21" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="92" t="s">
+      <c r="A21" s="107" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="93"/>
+      <c r="B21" s="108"/>
       <c r="C21" s="46"/>
       <c r="D21" s="47"/>
       <c r="E21" s="47"/>
@@ -3820,10 +3826,10 @@
         <f t="shared" ref="L21:L23" si="2">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:I21)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M21" s="92" t="s">
+      <c r="M21" s="107" t="s">
         <v>7</v>
       </c>
-      <c r="N21" s="93"/>
+      <c r="N21" s="108"/>
       <c r="O21" s="46"/>
       <c r="P21" s="47"/>
       <c r="Q21" s="47"/>
@@ -3837,10 +3843,10 @@
       </c>
     </row>
     <row r="22" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="96" t="s">
+      <c r="A22" s="111" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="97"/>
+      <c r="B22" s="112"/>
       <c r="C22" s="49"/>
       <c r="D22" s="12"/>
       <c r="E22" s="12"/>
@@ -3860,10 +3866,10 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M22" s="92" t="s">
+      <c r="M22" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="N22" s="93"/>
+      <c r="N22" s="108"/>
       <c r="O22" s="49"/>
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
@@ -3877,10 +3883,10 @@
       </c>
     </row>
     <row r="23" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="92" t="s">
+      <c r="A23" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="93"/>
+      <c r="B23" s="108"/>
       <c r="C23" s="49"/>
       <c r="D23" s="12"/>
       <c r="E23" s="12"/>
@@ -3900,10 +3906,10 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M23" s="92" t="s">
+      <c r="M23" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="N23" s="93"/>
+      <c r="N23" s="108"/>
       <c r="O23" s="49"/>
       <c r="P23" s="12"/>
       <c r="Q23" s="12"/>
@@ -3917,10 +3923,10 @@
       </c>
     </row>
     <row r="24" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="92" t="s">
+      <c r="A24" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="93"/>
+      <c r="B24" s="108"/>
       <c r="C24" s="51"/>
       <c r="D24" s="52"/>
       <c r="E24" s="52"/>
@@ -3937,10 +3943,10 @@
         <v>0</v>
       </c>
       <c r="L24" s="12"/>
-      <c r="M24" s="92" t="s">
+      <c r="M24" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="N24" s="93"/>
+      <c r="N24" s="108"/>
       <c r="O24" s="51"/>
       <c r="P24" s="52"/>
       <c r="Q24" s="52"/>
@@ -3951,38 +3957,38 @@
       <c r="V24" s="12"/>
     </row>
     <row r="25" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="92" t="s">
+      <c r="A25" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="98"/>
-      <c r="C25" s="99"/>
-      <c r="D25" s="99"/>
-      <c r="E25" s="99"/>
-      <c r="F25" s="99"/>
-      <c r="G25" s="99"/>
-      <c r="H25" s="99"/>
-      <c r="I25" s="100"/>
+      <c r="B25" s="109"/>
+      <c r="C25" s="110"/>
+      <c r="D25" s="110"/>
+      <c r="E25" s="110"/>
+      <c r="F25" s="110"/>
+      <c r="G25" s="110"/>
+      <c r="H25" s="110"/>
+      <c r="I25" s="119"/>
       <c r="J25" s="34"/>
       <c r="K25" s="34"/>
       <c r="L25" s="12"/>
-      <c r="M25" s="92" t="s">
+      <c r="M25" s="107" t="s">
         <v>23</v>
       </c>
-      <c r="N25" s="98"/>
-      <c r="O25" s="99"/>
-      <c r="P25" s="99"/>
-      <c r="Q25" s="99"/>
-      <c r="R25" s="99"/>
-      <c r="S25" s="99"/>
-      <c r="T25" s="99"/>
-      <c r="U25" s="100"/>
+      <c r="N25" s="109"/>
+      <c r="O25" s="110"/>
+      <c r="P25" s="110"/>
+      <c r="Q25" s="110"/>
+      <c r="R25" s="110"/>
+      <c r="S25" s="110"/>
+      <c r="T25" s="110"/>
+      <c r="U25" s="119"/>
       <c r="V25" s="12"/>
     </row>
     <row r="26" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="92" t="s">
+      <c r="A26" s="107" t="s">
         <v>7</v>
       </c>
-      <c r="B26" s="93"/>
+      <c r="B26" s="108"/>
       <c r="C26"/>
       <c r="D26"/>
       <c r="E26"/>
@@ -4002,10 +4008,10 @@
         <f t="shared" ref="L26:L28" si="4">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C26:I26)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M26" s="92" t="s">
+      <c r="M26" s="107" t="s">
         <v>7</v>
       </c>
-      <c r="N26" s="93"/>
+      <c r="N26" s="108"/>
       <c r="O26"/>
       <c r="P26"/>
       <c r="Q26"/>
@@ -4019,10 +4025,10 @@
       </c>
     </row>
     <row r="27" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="96" t="s">
+      <c r="A27" s="111" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="97"/>
+      <c r="B27" s="112"/>
       <c r="C27"/>
       <c r="D27"/>
       <c r="E27"/>
@@ -4042,10 +4048,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M27" s="92" t="s">
+      <c r="M27" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="N27" s="93"/>
+      <c r="N27" s="108"/>
       <c r="O27"/>
       <c r="P27"/>
       <c r="Q27"/>
@@ -4059,10 +4065,10 @@
       </c>
     </row>
     <row r="28" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="92" t="s">
+      <c r="A28" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="93"/>
+      <c r="B28" s="108"/>
       <c r="C28"/>
       <c r="D28"/>
       <c r="E28"/>
@@ -4082,10 +4088,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M28" s="92" t="s">
+      <c r="M28" s="107" t="s">
         <v>21</v>
       </c>
-      <c r="N28" s="93"/>
+      <c r="N28" s="108"/>
       <c r="O28"/>
       <c r="P28"/>
       <c r="Q28"/>
@@ -4099,10 +4105,10 @@
       </c>
     </row>
     <row r="29" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="92" t="s">
+      <c r="A29" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="B29" s="93"/>
+      <c r="B29" s="108"/>
       <c r="C29"/>
       <c r="D29"/>
       <c r="E29"/>
@@ -4119,10 +4125,10 @@
         <v>0</v>
       </c>
       <c r="L29" s="12"/>
-      <c r="M29" s="92" t="s">
+      <c r="M29" s="107" t="s">
         <v>22</v>
       </c>
-      <c r="N29" s="93"/>
+      <c r="N29" s="108"/>
       <c r="O29" s="89"/>
       <c r="P29" s="90"/>
       <c r="Q29" s="90"/>
@@ -4215,10 +4221,10 @@
       <c r="V31" s="1"/>
     </row>
     <row r="32" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="94" t="s">
+      <c r="A32" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="B32" s="95"/>
+      <c r="B32" s="101"/>
       <c r="C32" s="38"/>
       <c r="D32" s="38"/>
       <c r="E32" s="38"/>
@@ -4232,10 +4238,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C32:I32)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M32" s="94" t="s">
+      <c r="M32" s="100" t="s">
         <v>5</v>
       </c>
-      <c r="N32" s="95"/>
+      <c r="N32" s="101"/>
       <c r="O32" s="37"/>
       <c r="P32" s="38"/>
       <c r="Q32" s="38"/>
@@ -4249,10 +4255,10 @@
       </c>
     </row>
     <row r="33" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="94" t="s">
+      <c r="A33" s="100" t="s">
         <v>6</v>
       </c>
-      <c r="B33" s="95"/>
+      <c r="B33" s="101"/>
       <c r="C33" s="38"/>
       <c r="D33" s="38"/>
       <c r="E33" s="38"/>
@@ -4266,10 +4272,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C33:I33)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M33" s="94" t="s">
+      <c r="M33" s="100" t="s">
         <v>6</v>
       </c>
-      <c r="N33" s="95"/>
+      <c r="N33" s="101"/>
       <c r="O33" s="38"/>
       <c r="P33" s="38"/>
       <c r="Q33" s="38"/>
@@ -4283,10 +4289,10 @@
       </c>
     </row>
     <row r="34" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="94" t="s">
+      <c r="A34" s="100" t="s">
         <v>10</v>
       </c>
-      <c r="B34" s="95"/>
+      <c r="B34" s="101"/>
       <c r="C34" s="28"/>
       <c r="D34" s="29"/>
       <c r="E34" s="29"/>
@@ -4300,10 +4306,10 @@
         <f t="shared" ref="L34:L43" si="7">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C34:I34)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M34" s="94" t="s">
+      <c r="M34" s="100" t="s">
         <v>10</v>
       </c>
-      <c r="N34" s="95"/>
+      <c r="N34" s="101"/>
       <c r="O34" s="28"/>
       <c r="P34" s="29"/>
       <c r="Q34" s="29"/>
@@ -4317,35 +4323,35 @@
       </c>
     </row>
     <row r="35" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="94" t="s">
+      <c r="A35" s="100" t="s">
         <v>12</v>
       </c>
-      <c r="B35" s="101"/>
-      <c r="C35" s="101"/>
-      <c r="D35" s="101"/>
-      <c r="E35" s="101"/>
-      <c r="F35" s="101"/>
-      <c r="G35" s="101"/>
-      <c r="H35" s="101"/>
-      <c r="I35" s="95"/>
+      <c r="B35" s="104"/>
+      <c r="C35" s="104"/>
+      <c r="D35" s="104"/>
+      <c r="E35" s="104"/>
+      <c r="F35" s="104"/>
+      <c r="G35" s="104"/>
+      <c r="H35" s="104"/>
+      <c r="I35" s="101"/>
       <c r="J35" s="40"/>
       <c r="K35" s="40"/>
       <c r="L35" s="1"/>
-      <c r="M35" s="94" t="s">
+      <c r="M35" s="100" t="s">
         <v>12</v>
       </c>
-      <c r="N35" s="101"/>
-      <c r="O35" s="101"/>
-      <c r="P35" s="101"/>
-      <c r="Q35" s="101"/>
-      <c r="R35" s="101"/>
-      <c r="S35" s="101"/>
-      <c r="T35" s="101"/>
-      <c r="U35" s="95"/>
+      <c r="N35" s="104"/>
+      <c r="O35" s="104"/>
+      <c r="P35" s="104"/>
+      <c r="Q35" s="104"/>
+      <c r="R35" s="104"/>
+      <c r="S35" s="104"/>
+      <c r="T35" s="104"/>
+      <c r="U35" s="101"/>
       <c r="V35" s="1"/>
     </row>
     <row r="36" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="105" t="s">
+      <c r="A36" s="102" t="s">
         <v>11</v>
       </c>
       <c r="B36" s="9" t="s">
@@ -4364,7 +4370,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M36" s="105" t="s">
+      <c r="M36" s="102" t="s">
         <v>11</v>
       </c>
       <c r="N36" s="9" t="s">
@@ -4383,7 +4389,7 @@
       </c>
     </row>
     <row r="37" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="109"/>
+      <c r="A37" s="116"/>
       <c r="B37" s="9" t="s">
         <v>14</v>
       </c>
@@ -4400,7 +4406,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M37" s="109"/>
+      <c r="M37" s="116"/>
       <c r="N37" s="9" t="s">
         <v>14</v>
       </c>
@@ -4417,7 +4423,7 @@
       </c>
     </row>
     <row r="38" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="109"/>
+      <c r="A38" s="116"/>
       <c r="B38" s="9" t="s">
         <v>17</v>
       </c>
@@ -4431,7 +4437,7 @@
       <c r="J38" s="40"/>
       <c r="K38" s="40"/>
       <c r="L38" s="1"/>
-      <c r="M38" s="109"/>
+      <c r="M38" s="116"/>
       <c r="N38" s="9" t="s">
         <v>17</v>
       </c>
@@ -4445,7 +4451,7 @@
       <c r="V38" s="1"/>
     </row>
     <row r="39" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="109"/>
+      <c r="A39" s="116"/>
       <c r="B39" s="9" t="s">
         <v>18</v>
       </c>
@@ -4459,7 +4465,7 @@
       <c r="J39" s="40"/>
       <c r="K39" s="40"/>
       <c r="L39" s="1"/>
-      <c r="M39" s="109"/>
+      <c r="M39" s="116"/>
       <c r="N39" s="9" t="s">
         <v>18</v>
       </c>
@@ -4473,7 +4479,7 @@
       <c r="V39" s="1"/>
     </row>
     <row r="40" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="109"/>
+      <c r="A40" s="116"/>
       <c r="B40" s="9" t="s">
         <v>15</v>
       </c>
@@ -4490,7 +4496,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M40" s="109"/>
+      <c r="M40" s="116"/>
       <c r="N40" s="9" t="s">
         <v>15</v>
       </c>
@@ -4504,7 +4510,7 @@
       <c r="V40" s="1"/>
     </row>
     <row r="41" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="109"/>
+      <c r="A41" s="116"/>
       <c r="B41" s="9" t="s">
         <v>25</v>
       </c>
@@ -4518,7 +4524,7 @@
       <c r="J41" s="40"/>
       <c r="K41" s="40"/>
       <c r="L41" s="1"/>
-      <c r="M41" s="109"/>
+      <c r="M41" s="116"/>
       <c r="N41" s="9" t="s">
         <v>25</v>
       </c>
@@ -4532,7 +4538,7 @@
       <c r="V41" s="1"/>
     </row>
     <row r="42" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="109"/>
+      <c r="A42" s="116"/>
       <c r="B42" s="9" t="s">
         <v>19</v>
       </c>
@@ -4546,7 +4552,7 @@
       <c r="J42" s="40"/>
       <c r="K42" s="40"/>
       <c r="L42" s="1"/>
-      <c r="M42" s="109"/>
+      <c r="M42" s="116"/>
       <c r="N42" s="9" t="s">
         <v>19</v>
       </c>
@@ -4560,7 +4566,7 @@
       <c r="V42" s="1"/>
     </row>
     <row r="43" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="109"/>
+      <c r="A43" s="116"/>
       <c r="B43" s="9" t="s">
         <v>16</v>
       </c>
@@ -4577,7 +4583,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M43" s="109"/>
+      <c r="M43" s="116"/>
       <c r="N43" s="9" t="s">
         <v>16</v>
       </c>
@@ -4591,7 +4597,7 @@
       <c r="V43" s="1"/>
     </row>
     <row r="44" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="110"/>
+      <c r="A44" s="117"/>
       <c r="B44" s="9" t="s">
         <v>26</v>
       </c>
@@ -4605,7 +4611,7 @@
       <c r="J44" s="40"/>
       <c r="K44" s="40"/>
       <c r="L44" s="1"/>
-      <c r="M44" s="110"/>
+      <c r="M44" s="117"/>
       <c r="N44" s="9" t="s">
         <v>26</v>
       </c>
@@ -4619,38 +4625,38 @@
       <c r="V44" s="1"/>
     </row>
     <row r="45" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="94" t="s">
+      <c r="A45" s="100" t="s">
         <v>20</v>
       </c>
-      <c r="B45" s="101"/>
-      <c r="C45" s="102"/>
-      <c r="D45" s="102"/>
-      <c r="E45" s="102"/>
-      <c r="F45" s="102"/>
-      <c r="G45" s="102"/>
-      <c r="H45" s="102"/>
-      <c r="I45" s="103"/>
+      <c r="B45" s="104"/>
+      <c r="C45" s="105"/>
+      <c r="D45" s="105"/>
+      <c r="E45" s="105"/>
+      <c r="F45" s="105"/>
+      <c r="G45" s="105"/>
+      <c r="H45" s="105"/>
+      <c r="I45" s="118"/>
       <c r="J45" s="40"/>
       <c r="K45" s="40"/>
       <c r="L45" s="1"/>
-      <c r="M45" s="94" t="s">
+      <c r="M45" s="100" t="s">
         <v>20</v>
       </c>
-      <c r="N45" s="101"/>
-      <c r="O45" s="102"/>
-      <c r="P45" s="102"/>
-      <c r="Q45" s="102"/>
-      <c r="R45" s="102"/>
-      <c r="S45" s="102"/>
-      <c r="T45" s="102"/>
-      <c r="U45" s="103"/>
+      <c r="N45" s="104"/>
+      <c r="O45" s="105"/>
+      <c r="P45" s="105"/>
+      <c r="Q45" s="105"/>
+      <c r="R45" s="105"/>
+      <c r="S45" s="105"/>
+      <c r="T45" s="105"/>
+      <c r="U45" s="118"/>
       <c r="V45" s="1"/>
     </row>
     <row r="46" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="94" t="s">
+      <c r="A46" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="B46" s="95"/>
+      <c r="B46" s="101"/>
       <c r="C46" s="54"/>
       <c r="D46" s="55"/>
       <c r="E46" s="55"/>
@@ -4664,10 +4670,10 @@
         <f t="shared" ref="L46:L48" si="8">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C46:I46)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M46" s="94" t="s">
+      <c r="M46" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="N46" s="95"/>
+      <c r="N46" s="101"/>
       <c r="O46" s="54"/>
       <c r="P46" s="55"/>
       <c r="Q46" s="55"/>
@@ -4681,10 +4687,10 @@
       </c>
     </row>
     <row r="47" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="94" t="s">
+      <c r="A47" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="B47" s="95"/>
+      <c r="B47" s="101"/>
       <c r="C47" s="57"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -4698,10 +4704,10 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M47" s="94" t="s">
+      <c r="M47" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="95"/>
+      <c r="N47" s="101"/>
       <c r="O47" s="57"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
@@ -4715,10 +4721,10 @@
       </c>
     </row>
     <row r="48" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="94" t="s">
+      <c r="A48" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="B48" s="95"/>
+      <c r="B48" s="101"/>
       <c r="C48" s="57"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -4732,10 +4738,10 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M48" s="94" t="s">
+      <c r="M48" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="N48" s="95"/>
+      <c r="N48" s="101"/>
       <c r="O48" s="57"/>
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
@@ -4749,10 +4755,10 @@
       </c>
     </row>
     <row r="49" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="94" t="s">
+      <c r="A49" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="B49" s="95"/>
+      <c r="B49" s="101"/>
       <c r="C49" s="59"/>
       <c r="D49" s="60"/>
       <c r="E49" s="60"/>
@@ -4763,10 +4769,10 @@
       <c r="J49" s="45"/>
       <c r="K49" s="45"/>
       <c r="L49" s="44"/>
-      <c r="M49" s="94" t="s">
+      <c r="M49" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="N49" s="95"/>
+      <c r="N49" s="101"/>
       <c r="O49" s="59"/>
       <c r="P49" s="60"/>
       <c r="Q49" s="60"/>
@@ -4777,38 +4783,38 @@
       <c r="V49" s="1"/>
     </row>
     <row r="50" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="94" t="s">
+      <c r="A50" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="B50" s="101"/>
-      <c r="C50" s="102"/>
-      <c r="D50" s="102"/>
-      <c r="E50" s="102"/>
-      <c r="F50" s="102"/>
-      <c r="G50" s="102"/>
-      <c r="H50" s="102"/>
-      <c r="I50" s="103"/>
+      <c r="B50" s="104"/>
+      <c r="C50" s="105"/>
+      <c r="D50" s="105"/>
+      <c r="E50" s="105"/>
+      <c r="F50" s="105"/>
+      <c r="G50" s="105"/>
+      <c r="H50" s="105"/>
+      <c r="I50" s="118"/>
       <c r="J50" s="40"/>
       <c r="K50" s="40"/>
       <c r="L50" s="1"/>
-      <c r="M50" s="94" t="s">
+      <c r="M50" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="N50" s="101"/>
-      <c r="O50" s="102"/>
-      <c r="P50" s="102"/>
-      <c r="Q50" s="102"/>
-      <c r="R50" s="102"/>
-      <c r="S50" s="102"/>
-      <c r="T50" s="102"/>
-      <c r="U50" s="103"/>
+      <c r="N50" s="104"/>
+      <c r="O50" s="105"/>
+      <c r="P50" s="105"/>
+      <c r="Q50" s="105"/>
+      <c r="R50" s="105"/>
+      <c r="S50" s="105"/>
+      <c r="T50" s="105"/>
+      <c r="U50" s="118"/>
       <c r="V50" s="1"/>
     </row>
     <row r="51" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="94" t="s">
+      <c r="A51" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="B51" s="95"/>
+      <c r="B51" s="101"/>
       <c r="C51" s="54"/>
       <c r="D51" s="55"/>
       <c r="E51" s="55"/>
@@ -4822,10 +4828,10 @@
         <f t="shared" ref="L51:L53" si="9">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C51:I51)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M51" s="94" t="s">
+      <c r="M51" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="N51" s="95"/>
+      <c r="N51" s="101"/>
       <c r="O51" s="54"/>
       <c r="P51" s="55"/>
       <c r="Q51" s="55"/>
@@ -4839,10 +4845,10 @@
       </c>
     </row>
     <row r="52" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="105" t="s">
+      <c r="A52" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="B52" s="106"/>
+      <c r="B52" s="103"/>
       <c r="C52" s="57"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -4856,10 +4862,10 @@
         <f t="shared" si="9"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M52" s="94" t="s">
+      <c r="M52" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="N52" s="95"/>
+      <c r="N52" s="101"/>
       <c r="O52" s="57"/>
       <c r="P52" s="1"/>
       <c r="Q52" s="1"/>
@@ -4873,10 +4879,10 @@
       </c>
     </row>
     <row r="53" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="94" t="s">
+      <c r="A53" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="B53" s="95"/>
+      <c r="B53" s="101"/>
       <c r="C53" s="57"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -4890,10 +4896,10 @@
         <f t="shared" si="9"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M53" s="94" t="s">
+      <c r="M53" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="N53" s="95"/>
+      <c r="N53" s="101"/>
       <c r="O53" s="57"/>
       <c r="P53" s="1"/>
       <c r="Q53" s="1"/>
@@ -4907,10 +4913,10 @@
       </c>
     </row>
     <row r="54" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="94" t="s">
+      <c r="A54" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="B54" s="95"/>
+      <c r="B54" s="101"/>
       <c r="C54" s="59"/>
       <c r="D54" s="60"/>
       <c r="E54" s="60"/>
@@ -4921,10 +4927,10 @@
       <c r="J54" s="40"/>
       <c r="K54" s="40"/>
       <c r="L54" s="1"/>
-      <c r="M54" s="94" t="s">
+      <c r="M54" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="N54" s="95"/>
+      <c r="N54" s="101"/>
       <c r="O54" s="59"/>
       <c r="P54" s="60"/>
       <c r="Q54" s="60"/>
@@ -4935,38 +4941,38 @@
       <c r="V54" s="1"/>
     </row>
     <row r="55" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="94" t="s">
+      <c r="A55" s="100" t="s">
         <v>24</v>
       </c>
-      <c r="B55" s="101"/>
-      <c r="C55" s="102"/>
-      <c r="D55" s="102"/>
-      <c r="E55" s="102"/>
-      <c r="F55" s="102"/>
-      <c r="G55" s="102"/>
-      <c r="H55" s="102"/>
-      <c r="I55" s="103"/>
+      <c r="B55" s="104"/>
+      <c r="C55" s="105"/>
+      <c r="D55" s="105"/>
+      <c r="E55" s="105"/>
+      <c r="F55" s="105"/>
+      <c r="G55" s="105"/>
+      <c r="H55" s="105"/>
+      <c r="I55" s="118"/>
       <c r="J55" s="40"/>
       <c r="K55" s="40"/>
       <c r="L55" s="1"/>
-      <c r="M55" s="94" t="s">
+      <c r="M55" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="N55" s="101"/>
-      <c r="O55" s="102"/>
-      <c r="P55" s="102"/>
-      <c r="Q55" s="102"/>
-      <c r="R55" s="102"/>
-      <c r="S55" s="102"/>
-      <c r="T55" s="102"/>
-      <c r="U55" s="103"/>
+      <c r="N55" s="104"/>
+      <c r="O55" s="105"/>
+      <c r="P55" s="105"/>
+      <c r="Q55" s="105"/>
+      <c r="R55" s="105"/>
+      <c r="S55" s="105"/>
+      <c r="T55" s="105"/>
+      <c r="U55" s="118"/>
       <c r="V55" s="1"/>
     </row>
     <row r="56" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="94" t="s">
+      <c r="A56" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="B56" s="95"/>
+      <c r="B56" s="101"/>
       <c r="C56"/>
       <c r="D56"/>
       <c r="E56"/>
@@ -4980,10 +4986,10 @@
         <f t="shared" ref="L56:L58" si="11">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C56:I56)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M56" s="94" t="s">
+      <c r="M56" s="100" t="s">
         <v>7</v>
       </c>
-      <c r="N56" s="95"/>
+      <c r="N56" s="101"/>
       <c r="O56"/>
       <c r="P56"/>
       <c r="Q56"/>
@@ -4997,10 +5003,10 @@
       </c>
     </row>
     <row r="57" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="105" t="s">
+      <c r="A57" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="B57" s="106"/>
+      <c r="B57" s="103"/>
       <c r="C57"/>
       <c r="D57"/>
       <c r="E57"/>
@@ -5014,10 +5020,10 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M57" s="94" t="s">
+      <c r="M57" s="100" t="s">
         <v>8</v>
       </c>
-      <c r="N57" s="95"/>
+      <c r="N57" s="101"/>
       <c r="O57"/>
       <c r="P57"/>
       <c r="Q57"/>
@@ -5031,10 +5037,10 @@
       </c>
     </row>
     <row r="58" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="94" t="s">
+      <c r="A58" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="B58" s="95"/>
+      <c r="B58" s="101"/>
       <c r="C58"/>
       <c r="D58"/>
       <c r="E58"/>
@@ -5048,10 +5054,10 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M58" s="94" t="s">
+      <c r="M58" s="100" t="s">
         <v>21</v>
       </c>
-      <c r="N58" s="95"/>
+      <c r="N58" s="101"/>
       <c r="O58"/>
       <c r="P58"/>
       <c r="Q58"/>
@@ -5065,10 +5071,10 @@
       </c>
     </row>
     <row r="59" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="94" t="s">
+      <c r="A59" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="B59" s="95"/>
+      <c r="B59" s="101"/>
       <c r="C59" s="86"/>
       <c r="D59" s="87"/>
       <c r="E59" s="87"/>
@@ -5079,10 +5085,10 @@
       <c r="J59" s="40"/>
       <c r="K59" s="40"/>
       <c r="L59" s="1"/>
-      <c r="M59" s="94" t="s">
+      <c r="M59" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="N59" s="95"/>
+      <c r="N59" s="101"/>
       <c r="O59" s="86"/>
       <c r="P59" s="87"/>
       <c r="Q59" s="87"/>
@@ -5108,14 +5114,62 @@
     </row>
   </sheetData>
   <mergeCells count="80">
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="M59:N59"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="M56:N56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="M57:N57"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="M58:N58"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="M5:U5"/>
+    <mergeCell ref="M20:U20"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="M48:N48"/>
+    <mergeCell ref="M49:N49"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="M46:N46"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="M15:U15"/>
+    <mergeCell ref="M45:U45"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="M35:U35"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="M54:N54"/>
+    <mergeCell ref="A50:I50"/>
+    <mergeCell ref="M50:U50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="M51:N51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="M52:N52"/>
     <mergeCell ref="A6:A14"/>
     <mergeCell ref="M6:M14"/>
     <mergeCell ref="A36:A44"/>
@@ -5132,62 +5186,14 @@
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="A53:B53"/>
     <mergeCell ref="M53:N53"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="M54:N54"/>
-    <mergeCell ref="A50:I50"/>
-    <mergeCell ref="M50:U50"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="M51:N51"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="M52:N52"/>
-    <mergeCell ref="A45:I45"/>
-    <mergeCell ref="M15:U15"/>
-    <mergeCell ref="M45:U45"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="M35:U35"/>
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="M48:N48"/>
-    <mergeCell ref="M49:N49"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="M46:N46"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="M5:U5"/>
-    <mergeCell ref="M20:U20"/>
-    <mergeCell ref="A15:I15"/>
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="M59:N59"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="M56:N56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="M57:N57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="M58:N58"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C2:I4 C6:I14 C16:I19 C21:I24 C26:I29">
@@ -5649,20 +5655,20 @@
   <sheetData>
     <row r="1" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="92" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="118"/>
-      <c r="D2" s="115" t="s">
+      <c r="C2" s="98"/>
+      <c r="D2" s="95" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="117"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="97"/>
     </row>
     <row r="3" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="114"/>
-      <c r="C3" s="119"/>
+      <c r="B3" s="94"/>
+      <c r="C3" s="99"/>
       <c r="D3" s="77" t="s">
         <v>27</v>
       </c>
@@ -5715,20 +5721,20 @@
       <c r="G7" s="25"/>
     </row>
     <row r="8" spans="2:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="B8" s="112" t="s">
+      <c r="B8" s="92" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="118"/>
-      <c r="D8" s="115" t="s">
+      <c r="C8" s="98"/>
+      <c r="D8" s="95" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="116"/>
-      <c r="F8" s="116"/>
-      <c r="G8" s="117"/>
+      <c r="E8" s="96"/>
+      <c r="F8" s="96"/>
+      <c r="G8" s="97"/>
     </row>
     <row r="9" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="114"/>
-      <c r="C9" s="119"/>
+      <c r="B9" s="94"/>
+      <c r="C9" s="99"/>
       <c r="D9" s="77" t="s">
         <v>27</v>
       </c>
@@ -5743,7 +5749,7 @@
       </c>
     </row>
     <row r="10" spans="2:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="B10" s="112" t="s">
+      <c r="B10" s="92" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="70" t="s">
@@ -5755,7 +5761,7 @@
       <c r="G10" s="81"/>
     </row>
     <row r="11" spans="2:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="B11" s="113"/>
+      <c r="B11" s="93"/>
       <c r="C11" s="72" t="s">
         <v>28</v>
       </c>
@@ -5765,7 +5771,7 @@
       <c r="G11" s="73"/>
     </row>
     <row r="12" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="114"/>
+      <c r="B12" s="94"/>
       <c r="C12" s="83" t="s">
         <v>29</v>
       </c>

--- a/results_(stress_test)_baselines/summary.xlsx
+++ b/results_(stress_test)_baselines/summary.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\RnD_Repo\Research_Engineering\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_baselines\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RnD_Repo\Research_Engineeirng\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_baselines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F9999C-AD3F-485B-813B-5685C4E104FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D28307-8715-4E58-907A-13F1E5B3B399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-210" windowWidth="29040" windowHeight="16440" tabRatio="639" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="639" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="partialdata_20260429_spt_idx" sheetId="6" r:id="rId1"/>
-    <sheet name="fullldata_20260524_spt_idx" sheetId="5" r:id="rId2"/>
-    <sheet name="confusion_mtx" sheetId="7" r:id="rId3"/>
+    <sheet name="partialdata_20260429_unf_idx" sheetId="6" r:id="rId1"/>
+    <sheet name="figure" sheetId="8" r:id="rId2"/>
+    <sheet name="fullldata_20260524_spt_idx" sheetId="5" r:id="rId3"/>
+    <sheet name="confusion_mtx" sheetId="7" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -620,6 +621,66 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -644,69 +705,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1048,10 +1049,10 @@
       <c r="R1" s="12"/>
     </row>
     <row r="2" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="107" t="s">
+      <c r="A2" s="99" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="108"/>
+      <c r="B2" s="100"/>
       <c r="C2">
         <v>92.97270449283009</v>
       </c>
@@ -1079,10 +1080,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:G2)&amp;","</f>
         <v xml:space="preserve">    92.9727044928301, 92.6568511261632, 90.6124851137697, 76.8900480684666, 57.4311571322704,</v>
       </c>
-      <c r="K2" s="107" t="s">
+      <c r="K2" s="99" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="108"/>
+      <c r="L2" s="100"/>
       <c r="M2">
         <v>3.6723191410127392</v>
       </c>
@@ -1104,10 +1105,10 @@
       </c>
     </row>
     <row r="3" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="107" t="s">
+      <c r="A3" s="99" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="108"/>
+      <c r="B3" s="100"/>
       <c r="C3">
         <v>93.550650668835075</v>
       </c>
@@ -1135,10 +1136,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:G3)&amp;","</f>
         <v xml:space="preserve">    93.5506506688351, 92.2822198577266, 90.5016796569751, 72.8058085854261, 54.0640662981514,</v>
       </c>
-      <c r="K3" s="107" t="s">
+      <c r="K3" s="99" t="s">
         <v>6</v>
       </c>
-      <c r="L3" s="108"/>
+      <c r="L3" s="100"/>
       <c r="M3">
         <v>3.5444962758226279</v>
       </c>
@@ -1160,10 +1161,10 @@
       </c>
     </row>
     <row r="4" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="107" t="s">
+      <c r="A4" s="99" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="108"/>
+      <c r="B4" s="100"/>
       <c r="C4">
         <v>88.646029233240199</v>
       </c>
@@ -1191,10 +1192,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C4:G4)&amp;","</f>
         <v xml:space="preserve">    88.6460292332402, 87.5880039331367, 87.1022730877141, 74.8267141872623, 50.0552455759421,</v>
       </c>
-      <c r="K4" s="107" t="s">
+      <c r="K4" s="99" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="108"/>
+      <c r="L4" s="100"/>
       <c r="M4">
         <v>3.1531095164540388</v>
       </c>
@@ -1216,27 +1217,27 @@
       </c>
     </row>
     <row r="5" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="107" t="s">
+      <c r="A5" s="99" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="109"/>
-      <c r="C5" s="109"/>
-      <c r="D5" s="109"/>
-      <c r="E5" s="109"/>
-      <c r="F5" s="109"/>
-      <c r="G5" s="109"/>
+      <c r="B5" s="101"/>
+      <c r="C5" s="101"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="101"/>
+      <c r="F5" s="101"/>
+      <c r="G5" s="101"/>
       <c r="H5" s="34"/>
       <c r="I5" s="34"/>
       <c r="J5" s="12"/>
-      <c r="K5" s="107" t="s">
+      <c r="K5" s="99" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="109"/>
-      <c r="M5" s="109"/>
-      <c r="N5" s="109"/>
-      <c r="O5" s="109"/>
-      <c r="P5" s="109"/>
-      <c r="Q5" s="109"/>
+      <c r="L5" s="101"/>
+      <c r="M5" s="101"/>
+      <c r="N5" s="101"/>
+      <c r="O5" s="101"/>
+      <c r="P5" s="101"/>
+      <c r="Q5" s="101"/>
       <c r="R5" s="12"/>
     </row>
     <row r="6" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -1350,34 +1351,34 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="107" t="s">
+      <c r="A8" s="99" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="109"/>
-      <c r="C8" s="113"/>
-      <c r="D8" s="113"/>
-      <c r="E8" s="113"/>
-      <c r="F8" s="113"/>
-      <c r="G8" s="113"/>
+      <c r="B8" s="101"/>
+      <c r="C8" s="105"/>
+      <c r="D8" s="105"/>
+      <c r="E8" s="105"/>
+      <c r="F8" s="105"/>
+      <c r="G8" s="105"/>
       <c r="H8" s="34"/>
       <c r="I8" s="34"/>
       <c r="J8" s="12"/>
-      <c r="K8" s="107" t="s">
+      <c r="K8" s="99" t="s">
         <v>20</v>
       </c>
-      <c r="L8" s="109"/>
-      <c r="M8" s="113"/>
-      <c r="N8" s="113"/>
-      <c r="O8" s="113"/>
-      <c r="P8" s="113"/>
-      <c r="Q8" s="113"/>
+      <c r="L8" s="101"/>
+      <c r="M8" s="105"/>
+      <c r="N8" s="105"/>
+      <c r="O8" s="105"/>
+      <c r="P8" s="105"/>
+      <c r="Q8" s="105"/>
       <c r="R8" s="12"/>
     </row>
     <row r="9" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="107" t="s">
+      <c r="A9" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="108"/>
+      <c r="B9" s="100"/>
       <c r="C9">
         <v>93.207752662220258</v>
       </c>
@@ -1405,10 +1406,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C9:G9)&amp;","</f>
         <v xml:space="preserve">    93.2077526622203, 92.7830344553153, 90.5658843646283, 73.0768864782567, 58.5569944376681,</v>
       </c>
-      <c r="K9" s="107" t="s">
+      <c r="K9" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="L9" s="108"/>
+      <c r="L9" s="100"/>
       <c r="M9">
         <v>4.081079160307894</v>
       </c>
@@ -1430,10 +1431,10 @@
       </c>
     </row>
     <row r="10" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="111" t="s">
+      <c r="A10" s="103" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="112"/>
+      <c r="B10" s="104"/>
       <c r="C10">
         <v>93.534975792754821</v>
       </c>
@@ -1461,10 +1462,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C10:G10)&amp;","</f>
         <v xml:space="preserve">    93.5349757927548, 92.3364677318431, 88.5935201284902, 71.0452945094681, 53.4670628638656,</v>
       </c>
-      <c r="K10" s="107" t="s">
+      <c r="K10" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="L10" s="108"/>
+      <c r="L10" s="100"/>
       <c r="M10">
         <v>3.8494978151380188</v>
       </c>
@@ -1486,10 +1487,10 @@
       </c>
     </row>
     <row r="11" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="107" t="s">
+      <c r="A11" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="108"/>
+      <c r="B11" s="100"/>
       <c r="C11">
         <v>93.005297046975599</v>
       </c>
@@ -1517,10 +1518,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C11:G11)&amp;","</f>
         <v xml:space="preserve">    93.0052970469756, 91.9024443694726, 89.1162783991788, 72.2588142342639, 53.8436289817963,</v>
       </c>
-      <c r="K11" s="107" t="s">
+      <c r="K11" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="L11" s="108"/>
+      <c r="L11" s="100"/>
       <c r="M11">
         <v>3.458803648865628</v>
       </c>
@@ -1542,10 +1543,10 @@
       </c>
     </row>
     <row r="12" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="107" t="s">
+      <c r="A12" s="99" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="108"/>
+      <c r="B12" s="100"/>
       <c r="C12" s="35"/>
       <c r="D12" s="36"/>
       <c r="E12" s="36"/>
@@ -1563,10 +1564,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C12:G12)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="K12" s="107" t="s">
+      <c r="K12" s="99" t="s">
         <v>22</v>
       </c>
-      <c r="L12" s="108"/>
+      <c r="L12" s="100"/>
       <c r="M12" s="35"/>
       <c r="N12" s="36"/>
       <c r="O12" s="36"/>
@@ -1578,34 +1579,34 @@
       </c>
     </row>
     <row r="13" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="107" t="s">
+      <c r="A13" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="109"/>
-      <c r="C13" s="110"/>
-      <c r="D13" s="110"/>
-      <c r="E13" s="110"/>
-      <c r="F13" s="110"/>
-      <c r="G13" s="110"/>
+      <c r="B13" s="101"/>
+      <c r="C13" s="102"/>
+      <c r="D13" s="102"/>
+      <c r="E13" s="102"/>
+      <c r="F13" s="102"/>
+      <c r="G13" s="102"/>
       <c r="H13" s="34"/>
       <c r="I13" s="34"/>
       <c r="J13" s="12"/>
-      <c r="K13" s="107" t="s">
+      <c r="K13" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="L13" s="109"/>
-      <c r="M13" s="110"/>
-      <c r="N13" s="110"/>
-      <c r="O13" s="110"/>
-      <c r="P13" s="110"/>
-      <c r="Q13" s="110"/>
+      <c r="L13" s="101"/>
+      <c r="M13" s="102"/>
+      <c r="N13" s="102"/>
+      <c r="O13" s="102"/>
+      <c r="P13" s="102"/>
+      <c r="Q13" s="102"/>
       <c r="R13" s="12"/>
     </row>
     <row r="14" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="107" t="s">
+      <c r="A14" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="108"/>
+      <c r="B14" s="100"/>
       <c r="C14">
         <v>93.204569243678591</v>
       </c>
@@ -1633,10 +1634,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C14:G14)&amp;","</f>
         <v xml:space="preserve">    93.2045692436786, 92.7189364383198, 91.0101961666335, 77.7756122457807, 55.9218563021018,</v>
       </c>
-      <c r="K14" s="107" t="s">
+      <c r="K14" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="L14" s="108"/>
+      <c r="L14" s="100"/>
       <c r="M14">
         <v>3.5338969773137729</v>
       </c>
@@ -1658,10 +1659,10 @@
       </c>
     </row>
     <row r="15" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="111" t="s">
+      <c r="A15" s="103" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="112"/>
+      <c r="B15" s="104"/>
       <c r="C15">
         <v>91.935155148400952</v>
       </c>
@@ -1689,10 +1690,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C15:G15)&amp;","</f>
         <v xml:space="preserve">    91.935155148401, 91.6922551233142, 89.8476486244114, 79.4007474113098, 53.2536440626649,</v>
       </c>
-      <c r="K15" s="107" t="s">
+      <c r="K15" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="L15" s="108"/>
+      <c r="L15" s="100"/>
       <c r="M15">
         <v>3.0404967647063641</v>
       </c>
@@ -1714,10 +1715,10 @@
       </c>
     </row>
     <row r="16" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="107" t="s">
+      <c r="A16" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="B16" s="108"/>
+      <c r="B16" s="100"/>
       <c r="C16">
         <v>93.32960781090955</v>
       </c>
@@ -1745,10 +1746,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C16:G16)&amp;","</f>
         <v xml:space="preserve">    93.3296078109096, 92.6274333399655, 90.919543710009, 77.7434003177651, 58.3910702803081,</v>
       </c>
-      <c r="K16" s="107" t="s">
+      <c r="K16" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="L16" s="108"/>
+      <c r="L16" s="100"/>
       <c r="M16">
         <v>3.3471189071482028</v>
       </c>
@@ -1770,10 +1771,10 @@
       </c>
     </row>
     <row r="17" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="107" t="s">
+      <c r="A17" s="99" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="108"/>
+      <c r="B17" s="100"/>
       <c r="C17" s="35"/>
       <c r="D17" s="36"/>
       <c r="E17" s="36"/>
@@ -1791,10 +1792,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C17:G17)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="K17" s="107" t="s">
+      <c r="K17" s="99" t="s">
         <v>22</v>
       </c>
-      <c r="L17" s="108"/>
+      <c r="L17" s="100"/>
       <c r="M17" s="35"/>
       <c r="N17" s="36"/>
       <c r="O17" s="36"/>
@@ -1872,10 +1873,10 @@
       <c r="R19" s="1"/>
     </row>
     <row r="20" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="100" t="s">
+      <c r="A20" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="101"/>
+      <c r="B20" s="93"/>
       <c r="C20">
         <v>92.485449200300948</v>
       </c>
@@ -1897,10 +1898,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C20:G20)&amp;","</f>
         <v xml:space="preserve">    92.4854492003009, 92.1853579700095, 90.0493612740203, 76.4241798948027, 55.8171663737853,</v>
       </c>
-      <c r="K20" s="100" t="s">
+      <c r="K20" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="L20" s="101"/>
+      <c r="L20" s="93"/>
       <c r="M20">
         <v>4.0542209595909764</v>
       </c>
@@ -1922,10 +1923,10 @@
       </c>
     </row>
     <row r="21" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="100" t="s">
+      <c r="A21" s="92" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="101"/>
+      <c r="B21" s="93"/>
       <c r="C21">
         <v>93.221737995090834</v>
       </c>
@@ -1947,10 +1948,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:G21)&amp;","</f>
         <v xml:space="preserve">    93.2217379950908, 91.8880330056846, 90.0239389840154, 72.2904200814482, 51.8413052641743,</v>
       </c>
-      <c r="K21" s="100" t="s">
+      <c r="K21" s="92" t="s">
         <v>6</v>
       </c>
-      <c r="L21" s="101"/>
+      <c r="L21" s="93"/>
       <c r="M21">
         <v>3.877808098377264</v>
       </c>
@@ -1972,10 +1973,10 @@
       </c>
     </row>
     <row r="22" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="100" t="s">
+      <c r="A22" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="B22" s="101"/>
+      <c r="B22" s="93"/>
       <c r="C22">
         <v>88.242190127710941</v>
       </c>
@@ -1997,10 +1998,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C22:G22)&amp;","</f>
         <v xml:space="preserve">    88.2421901277109, 87.2356592457238, 86.8403563631381, 74.5410000823158, 48.9795299923061,</v>
       </c>
-      <c r="K22" s="100" t="s">
+      <c r="K22" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="L22" s="101"/>
+      <c r="L22" s="93"/>
       <c r="M22">
         <v>3.345739818904093</v>
       </c>
@@ -2022,27 +2023,27 @@
       </c>
     </row>
     <row r="23" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="100" t="s">
+      <c r="A23" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="104"/>
-      <c r="C23" s="104"/>
-      <c r="D23" s="104"/>
-      <c r="E23" s="104"/>
-      <c r="F23" s="104"/>
-      <c r="G23" s="104"/>
+      <c r="B23" s="96"/>
+      <c r="C23" s="96"/>
+      <c r="D23" s="96"/>
+      <c r="E23" s="96"/>
+      <c r="F23" s="96"/>
+      <c r="G23" s="96"/>
       <c r="H23" s="40"/>
       <c r="I23" s="40"/>
       <c r="J23" s="1"/>
-      <c r="K23" s="100" t="s">
+      <c r="K23" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="L23" s="104"/>
-      <c r="M23" s="104"/>
-      <c r="N23" s="104"/>
-      <c r="O23" s="104"/>
-      <c r="P23" s="104"/>
-      <c r="Q23" s="104"/>
+      <c r="L23" s="96"/>
+      <c r="M23" s="96"/>
+      <c r="N23" s="96"/>
+      <c r="O23" s="96"/>
+      <c r="P23" s="96"/>
+      <c r="Q23" s="96"/>
       <c r="R23" s="1"/>
     </row>
     <row r="24" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -2134,34 +2135,34 @@
       </c>
     </row>
     <row r="26" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="100" t="s">
+      <c r="A26" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="B26" s="104"/>
-      <c r="C26" s="106"/>
-      <c r="D26" s="106"/>
-      <c r="E26" s="106"/>
-      <c r="F26" s="106"/>
-      <c r="G26" s="106"/>
+      <c r="B26" s="96"/>
+      <c r="C26" s="98"/>
+      <c r="D26" s="98"/>
+      <c r="E26" s="98"/>
+      <c r="F26" s="98"/>
+      <c r="G26" s="98"/>
       <c r="H26" s="40"/>
       <c r="I26" s="40"/>
       <c r="J26" s="1"/>
-      <c r="K26" s="100" t="s">
+      <c r="K26" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="L26" s="104"/>
-      <c r="M26" s="106"/>
-      <c r="N26" s="106"/>
-      <c r="O26" s="106"/>
-      <c r="P26" s="106"/>
-      <c r="Q26" s="106"/>
+      <c r="L26" s="96"/>
+      <c r="M26" s="98"/>
+      <c r="N26" s="98"/>
+      <c r="O26" s="98"/>
+      <c r="P26" s="98"/>
+      <c r="Q26" s="98"/>
       <c r="R26" s="1"/>
     </row>
     <row r="27" spans="1:18" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="100" t="s">
+      <c r="A27" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="B27" s="101"/>
+      <c r="B27" s="93"/>
       <c r="C27">
         <v>92.781043798288394</v>
       </c>
@@ -2183,10 +2184,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C27:G27)&amp;","</f>
         <v xml:space="preserve">    92.7810437982884, 92.3938056553932, 90.0090839662476, 72.4981719652037, 56.6748529979919,</v>
       </c>
-      <c r="K27" s="100" t="s">
+      <c r="K27" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="L27" s="101"/>
+      <c r="L27" s="93"/>
       <c r="M27">
         <v>4.5014366094349993</v>
       </c>
@@ -2208,10 +2209,10 @@
       </c>
     </row>
     <row r="28" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="100" t="s">
+      <c r="A28" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="B28" s="101"/>
+      <c r="B28" s="93"/>
       <c r="C28">
         <v>93.113144022293241</v>
       </c>
@@ -2233,10 +2234,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C28:G28)&amp;","</f>
         <v xml:space="preserve">    93.1131440222932, 91.9496041120699, 88.043149271791, 70.4378143831585, 50.0271657882747,</v>
       </c>
-      <c r="K28" s="100" t="s">
+      <c r="K28" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="L28" s="101"/>
+      <c r="L28" s="93"/>
       <c r="M28">
         <v>4.249709534316878</v>
       </c>
@@ -2258,10 +2259,10 @@
       </c>
     </row>
     <row r="29" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="100" t="s">
+      <c r="A29" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="B29" s="101"/>
+      <c r="B29" s="93"/>
       <c r="C29">
         <v>92.587964837227005</v>
       </c>
@@ -2283,10 +2284,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C29:G29)&amp;","</f>
         <v xml:space="preserve">    92.587964837227, 91.4235824416001, 88.5454649294227, 71.6598005950386, 50.2664690265607,</v>
       </c>
-      <c r="K29" s="100" t="s">
+      <c r="K29" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="L29" s="101"/>
+      <c r="L29" s="93"/>
       <c r="M29">
         <v>3.7645606938355249</v>
       </c>
@@ -2308,10 +2309,10 @@
       </c>
     </row>
     <row r="30" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="100" t="s">
+      <c r="A30" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="B30" s="101"/>
+      <c r="B30" s="93"/>
       <c r="C30" s="41"/>
       <c r="D30" s="42"/>
       <c r="E30" s="42"/>
@@ -2323,10 +2324,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C30:G30)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="K30" s="100" t="s">
+      <c r="K30" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="L30" s="101"/>
+      <c r="L30" s="93"/>
       <c r="M30" s="41"/>
       <c r="N30" s="42"/>
       <c r="O30" s="42"/>
@@ -2338,34 +2339,34 @@
       </c>
     </row>
     <row r="31" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="100" t="s">
+      <c r="A31" s="92" t="s">
         <v>23</v>
       </c>
-      <c r="B31" s="104"/>
-      <c r="C31" s="105"/>
-      <c r="D31" s="105"/>
-      <c r="E31" s="105"/>
-      <c r="F31" s="105"/>
-      <c r="G31" s="105"/>
+      <c r="B31" s="96"/>
+      <c r="C31" s="97"/>
+      <c r="D31" s="97"/>
+      <c r="E31" s="97"/>
+      <c r="F31" s="97"/>
+      <c r="G31" s="97"/>
       <c r="H31" s="40"/>
       <c r="I31" s="40"/>
       <c r="J31" s="1"/>
-      <c r="K31" s="100" t="s">
+      <c r="K31" s="92" t="s">
         <v>23</v>
       </c>
-      <c r="L31" s="104"/>
-      <c r="M31" s="105"/>
-      <c r="N31" s="105"/>
-      <c r="O31" s="105"/>
-      <c r="P31" s="105"/>
-      <c r="Q31" s="105"/>
+      <c r="L31" s="96"/>
+      <c r="M31" s="97"/>
+      <c r="N31" s="97"/>
+      <c r="O31" s="97"/>
+      <c r="P31" s="97"/>
+      <c r="Q31" s="97"/>
       <c r="R31" s="1"/>
     </row>
     <row r="32" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="100" t="s">
+      <c r="A32" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="B32" s="101"/>
+      <c r="B32" s="93"/>
       <c r="C32">
         <v>92.779242983398433</v>
       </c>
@@ -2387,10 +2388,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C32:G32)&amp;","</f>
         <v xml:space="preserve">    92.7792429833984, 92.2402701949049, 90.5523014335592, 77.4468153062754, 54.049481297537,</v>
       </c>
-      <c r="K32" s="100" t="s">
+      <c r="K32" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="L32" s="101"/>
+      <c r="L32" s="93"/>
       <c r="M32">
         <v>3.8708284466838099</v>
       </c>
@@ -2412,10 +2413,10 @@
       </c>
     </row>
     <row r="33" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="102" t="s">
+      <c r="A33" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="103"/>
+      <c r="B33" s="95"/>
       <c r="C33">
         <v>91.529115829853595</v>
       </c>
@@ -2437,10 +2438,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C33:G33)&amp;","</f>
         <v xml:space="preserve">    91.5291158298536, 91.3506434233222, 89.3417609327998, 79.0450519987888, 52.3197117316979,</v>
       </c>
-      <c r="K33" s="100" t="s">
+      <c r="K33" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="L33" s="101"/>
+      <c r="L33" s="93"/>
       <c r="M33">
         <v>3.326792742141544</v>
       </c>
@@ -2462,10 +2463,10 @@
       </c>
     </row>
     <row r="34" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="100" t="s">
+      <c r="A34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="B34" s="101"/>
+      <c r="B34" s="93"/>
       <c r="C34">
         <v>92.904210456970588</v>
       </c>
@@ -2487,10 +2488,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C34:G34)&amp;","</f>
         <v xml:space="preserve">    92.9042104569706, 92.1891124359732, 90.4960366989424, 77.336951327755, 56.2225359371609,</v>
       </c>
-      <c r="K34" s="100" t="s">
+      <c r="K34" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="L34" s="101"/>
+      <c r="L34" s="93"/>
       <c r="M34">
         <v>3.6016716439248402</v>
       </c>
@@ -2512,10 +2513,10 @@
       </c>
     </row>
     <row r="35" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="100" t="s">
+      <c r="A35" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="B35" s="101"/>
+      <c r="B35" s="93"/>
       <c r="C35" s="41"/>
       <c r="D35" s="42"/>
       <c r="E35" s="42"/>
@@ -2527,10 +2528,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C35:G35)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="K35" s="100" t="s">
+      <c r="K35" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="L35" s="101"/>
+      <c r="L35" s="93"/>
       <c r="M35" s="41"/>
       <c r="N35" s="42"/>
       <c r="O35" s="42"/>
@@ -3025,6 +3026,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FD1D2A5-B6AE-49D4-BC83-17C47B77B66C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData/>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61C29D5C-8639-4163-9432-7C70C26E1499}">
   <dimension ref="A1:V60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -3102,10 +3113,10 @@
       <c r="V1" s="12"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="107" t="s">
+      <c r="A2" s="99" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="108"/>
+      <c r="B2" s="100"/>
       <c r="C2" s="20"/>
       <c r="D2" s="21"/>
       <c r="E2" s="21"/>
@@ -3125,10 +3136,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:I2)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M2" s="107" t="s">
+      <c r="M2" s="99" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="108"/>
+      <c r="N2" s="100"/>
       <c r="O2" s="31"/>
       <c r="P2" s="32"/>
       <c r="Q2" s="32"/>
@@ -3142,10 +3153,10 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="107" t="s">
+      <c r="A3" s="99" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="108"/>
+      <c r="B3" s="100"/>
       <c r="C3" s="31"/>
       <c r="D3" s="32"/>
       <c r="E3" s="32"/>
@@ -3165,10 +3176,10 @@
         <f t="shared" ref="L3:L18" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M3" s="107" t="s">
+      <c r="M3" s="99" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="108"/>
+      <c r="N3" s="100"/>
       <c r="O3" s="31"/>
       <c r="P3" s="32"/>
       <c r="Q3" s="32"/>
@@ -3182,10 +3193,10 @@
       </c>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="107" t="s">
+      <c r="A4" s="99" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="108"/>
+      <c r="B4" s="100"/>
       <c r="C4" s="24"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
@@ -3205,10 +3216,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M4" s="107" t="s">
+      <c r="M4" s="99" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="108"/>
+      <c r="N4" s="100"/>
       <c r="O4" s="43"/>
       <c r="P4" s="26"/>
       <c r="Q4" s="26"/>
@@ -3222,35 +3233,35 @@
       </c>
     </row>
     <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="107" t="s">
+      <c r="A5" s="99" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="109"/>
-      <c r="C5" s="109"/>
-      <c r="D5" s="109"/>
-      <c r="E5" s="109"/>
-      <c r="F5" s="109"/>
-      <c r="G5" s="109"/>
-      <c r="H5" s="109"/>
-      <c r="I5" s="108"/>
+      <c r="B5" s="101"/>
+      <c r="C5" s="101"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="101"/>
+      <c r="F5" s="101"/>
+      <c r="G5" s="101"/>
+      <c r="H5" s="101"/>
+      <c r="I5" s="100"/>
       <c r="J5" s="34"/>
       <c r="K5" s="34"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="107" t="s">
+      <c r="M5" s="99" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="109"/>
-      <c r="O5" s="109"/>
-      <c r="P5" s="109"/>
-      <c r="Q5" s="109"/>
-      <c r="R5" s="109"/>
-      <c r="S5" s="109"/>
-      <c r="T5" s="109"/>
-      <c r="U5" s="108"/>
+      <c r="N5" s="101"/>
+      <c r="O5" s="101"/>
+      <c r="P5" s="101"/>
+      <c r="Q5" s="101"/>
+      <c r="R5" s="101"/>
+      <c r="S5" s="101"/>
+      <c r="T5" s="101"/>
+      <c r="U5" s="100"/>
       <c r="V5" s="12"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="111" t="s">
+      <c r="A6" s="103" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -3275,7 +3286,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M6" s="111" t="s">
+      <c r="M6" s="103" t="s">
         <v>11</v>
       </c>
       <c r="N6" s="8" t="s">
@@ -3294,7 +3305,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="114"/>
+      <c r="A7" s="106"/>
       <c r="B7" s="8" t="s">
         <v>14</v>
       </c>
@@ -3317,7 +3328,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M7" s="114"/>
+      <c r="M7" s="106"/>
       <c r="N7" s="8" t="s">
         <v>14</v>
       </c>
@@ -3334,7 +3345,7 @@
       </c>
     </row>
     <row r="8" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="114"/>
+      <c r="A8" s="106"/>
       <c r="B8" s="8" t="s">
         <v>17</v>
       </c>
@@ -3357,7 +3368,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M8" s="114"/>
+      <c r="M8" s="106"/>
       <c r="N8" s="8" t="s">
         <v>17</v>
       </c>
@@ -3371,7 +3382,7 @@
       <c r="V8" s="12"/>
     </row>
     <row r="9" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="114"/>
+      <c r="A9" s="106"/>
       <c r="B9" s="8" t="s">
         <v>18</v>
       </c>
@@ -3394,7 +3405,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M9" s="114"/>
+      <c r="M9" s="106"/>
       <c r="N9" s="8" t="s">
         <v>18</v>
       </c>
@@ -3408,7 +3419,7 @@
       <c r="V9" s="12"/>
     </row>
     <row r="10" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="114"/>
+      <c r="A10" s="106"/>
       <c r="B10" s="8" t="s">
         <v>15</v>
       </c>
@@ -3431,7 +3442,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M10" s="114"/>
+      <c r="M10" s="106"/>
       <c r="N10" s="8" t="s">
         <v>15</v>
       </c>
@@ -3445,7 +3456,7 @@
       <c r="V10" s="12"/>
     </row>
     <row r="11" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="114"/>
+      <c r="A11" s="106"/>
       <c r="B11" s="8" t="s">
         <v>25</v>
       </c>
@@ -3468,7 +3479,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M11" s="114"/>
+      <c r="M11" s="106"/>
       <c r="N11" s="8" t="s">
         <v>25</v>
       </c>
@@ -3482,7 +3493,7 @@
       <c r="V11" s="12"/>
     </row>
     <row r="12" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="114"/>
+      <c r="A12" s="106"/>
       <c r="B12" s="8" t="s">
         <v>19</v>
       </c>
@@ -3505,7 +3516,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M12" s="114"/>
+      <c r="M12" s="106"/>
       <c r="N12" s="8" t="s">
         <v>19</v>
       </c>
@@ -3519,7 +3530,7 @@
       <c r="V12" s="12"/>
     </row>
     <row r="13" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="114"/>
+      <c r="A13" s="106"/>
       <c r="B13" s="8" t="s">
         <v>16</v>
       </c>
@@ -3542,7 +3553,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M13" s="114"/>
+      <c r="M13" s="106"/>
       <c r="N13" s="8" t="s">
         <v>16</v>
       </c>
@@ -3556,7 +3567,7 @@
       <c r="V13" s="12"/>
     </row>
     <row r="14" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="115"/>
+      <c r="A14" s="107"/>
       <c r="B14" s="8" t="s">
         <v>26</v>
       </c>
@@ -3579,7 +3590,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M14" s="115"/>
+      <c r="M14" s="107"/>
       <c r="N14" s="8" t="s">
         <v>26</v>
       </c>
@@ -3593,38 +3604,38 @@
       <c r="V14" s="12"/>
     </row>
     <row r="15" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="107" t="s">
+      <c r="A15" s="99" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="109"/>
-      <c r="C15" s="110"/>
-      <c r="D15" s="110"/>
-      <c r="E15" s="110"/>
-      <c r="F15" s="110"/>
-      <c r="G15" s="110"/>
-      <c r="H15" s="110"/>
-      <c r="I15" s="119"/>
+      <c r="B15" s="101"/>
+      <c r="C15" s="102"/>
+      <c r="D15" s="102"/>
+      <c r="E15" s="102"/>
+      <c r="F15" s="102"/>
+      <c r="G15" s="102"/>
+      <c r="H15" s="102"/>
+      <c r="I15" s="111"/>
       <c r="J15" s="34"/>
       <c r="K15" s="34"/>
       <c r="L15" s="12"/>
-      <c r="M15" s="107" t="s">
+      <c r="M15" s="99" t="s">
         <v>20</v>
       </c>
-      <c r="N15" s="109"/>
-      <c r="O15" s="113"/>
-      <c r="P15" s="113"/>
-      <c r="Q15" s="113"/>
-      <c r="R15" s="113"/>
-      <c r="S15" s="113"/>
-      <c r="T15" s="113"/>
-      <c r="U15" s="112"/>
+      <c r="N15" s="101"/>
+      <c r="O15" s="105"/>
+      <c r="P15" s="105"/>
+      <c r="Q15" s="105"/>
+      <c r="R15" s="105"/>
+      <c r="S15" s="105"/>
+      <c r="T15" s="105"/>
+      <c r="U15" s="104"/>
       <c r="V15" s="12"/>
     </row>
     <row r="16" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="107" t="s">
+      <c r="A16" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="108"/>
+      <c r="B16" s="100"/>
       <c r="C16" s="46"/>
       <c r="D16" s="47"/>
       <c r="E16" s="47"/>
@@ -3644,10 +3655,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M16" s="107" t="s">
+      <c r="M16" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="N16" s="108"/>
+      <c r="N16" s="100"/>
       <c r="O16" s="46"/>
       <c r="P16" s="47"/>
       <c r="Q16" s="47"/>
@@ -3661,10 +3672,10 @@
       </c>
     </row>
     <row r="17" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="111" t="s">
+      <c r="A17" s="103" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="112"/>
+      <c r="B17" s="104"/>
       <c r="C17" s="49"/>
       <c r="D17" s="12"/>
       <c r="E17" s="12"/>
@@ -3684,10 +3695,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M17" s="107" t="s">
+      <c r="M17" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="N17" s="108"/>
+      <c r="N17" s="100"/>
       <c r="O17" s="49"/>
       <c r="P17" s="12"/>
       <c r="Q17" s="12"/>
@@ -3701,10 +3712,10 @@
       </c>
     </row>
     <row r="18" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="107" t="s">
+      <c r="A18" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="108"/>
+      <c r="B18" s="100"/>
       <c r="C18" s="49"/>
       <c r="D18" s="12"/>
       <c r="E18" s="12"/>
@@ -3724,10 +3735,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M18" s="107" t="s">
+      <c r="M18" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="N18" s="108"/>
+      <c r="N18" s="100"/>
       <c r="O18" s="49"/>
       <c r="P18" s="12"/>
       <c r="Q18" s="12"/>
@@ -3741,10 +3752,10 @@
       </c>
     </row>
     <row r="19" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="107" t="s">
+      <c r="A19" s="99" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="108"/>
+      <c r="B19" s="100"/>
       <c r="C19" s="51"/>
       <c r="D19" s="52"/>
       <c r="E19" s="52"/>
@@ -3761,10 +3772,10 @@
         <v>0</v>
       </c>
       <c r="L19" s="12"/>
-      <c r="M19" s="107" t="s">
+      <c r="M19" s="99" t="s">
         <v>22</v>
       </c>
-      <c r="N19" s="108"/>
+      <c r="N19" s="100"/>
       <c r="O19" s="51"/>
       <c r="P19" s="52"/>
       <c r="Q19" s="52"/>
@@ -3775,38 +3786,38 @@
       <c r="V19" s="12"/>
     </row>
     <row r="20" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="107" t="s">
+      <c r="A20" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="109"/>
-      <c r="C20" s="110"/>
-      <c r="D20" s="110"/>
-      <c r="E20" s="110"/>
-      <c r="F20" s="110"/>
-      <c r="G20" s="110"/>
-      <c r="H20" s="110"/>
-      <c r="I20" s="119"/>
+      <c r="B20" s="101"/>
+      <c r="C20" s="102"/>
+      <c r="D20" s="102"/>
+      <c r="E20" s="102"/>
+      <c r="F20" s="102"/>
+      <c r="G20" s="102"/>
+      <c r="H20" s="102"/>
+      <c r="I20" s="111"/>
       <c r="J20" s="34"/>
       <c r="K20" s="34"/>
       <c r="L20" s="12"/>
-      <c r="M20" s="107" t="s">
+      <c r="M20" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="N20" s="109"/>
-      <c r="O20" s="110"/>
-      <c r="P20" s="110"/>
-      <c r="Q20" s="110"/>
-      <c r="R20" s="110"/>
-      <c r="S20" s="110"/>
-      <c r="T20" s="110"/>
-      <c r="U20" s="119"/>
+      <c r="N20" s="101"/>
+      <c r="O20" s="102"/>
+      <c r="P20" s="102"/>
+      <c r="Q20" s="102"/>
+      <c r="R20" s="102"/>
+      <c r="S20" s="102"/>
+      <c r="T20" s="102"/>
+      <c r="U20" s="111"/>
       <c r="V20" s="12"/>
     </row>
     <row r="21" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="107" t="s">
+      <c r="A21" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="108"/>
+      <c r="B21" s="100"/>
       <c r="C21" s="46"/>
       <c r="D21" s="47"/>
       <c r="E21" s="47"/>
@@ -3826,10 +3837,10 @@
         <f t="shared" ref="L21:L23" si="2">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:I21)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M21" s="107" t="s">
+      <c r="M21" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="N21" s="108"/>
+      <c r="N21" s="100"/>
       <c r="O21" s="46"/>
       <c r="P21" s="47"/>
       <c r="Q21" s="47"/>
@@ -3843,10 +3854,10 @@
       </c>
     </row>
     <row r="22" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="111" t="s">
+      <c r="A22" s="103" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="112"/>
+      <c r="B22" s="104"/>
       <c r="C22" s="49"/>
       <c r="D22" s="12"/>
       <c r="E22" s="12"/>
@@ -3866,10 +3877,10 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M22" s="107" t="s">
+      <c r="M22" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="N22" s="108"/>
+      <c r="N22" s="100"/>
       <c r="O22" s="49"/>
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
@@ -3883,10 +3894,10 @@
       </c>
     </row>
     <row r="23" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="107" t="s">
+      <c r="A23" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="108"/>
+      <c r="B23" s="100"/>
       <c r="C23" s="49"/>
       <c r="D23" s="12"/>
       <c r="E23" s="12"/>
@@ -3906,10 +3917,10 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M23" s="107" t="s">
+      <c r="M23" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="N23" s="108"/>
+      <c r="N23" s="100"/>
       <c r="O23" s="49"/>
       <c r="P23" s="12"/>
       <c r="Q23" s="12"/>
@@ -3923,10 +3934,10 @@
       </c>
     </row>
     <row r="24" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="107" t="s">
+      <c r="A24" s="99" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="108"/>
+      <c r="B24" s="100"/>
       <c r="C24" s="51"/>
       <c r="D24" s="52"/>
       <c r="E24" s="52"/>
@@ -3943,10 +3954,10 @@
         <v>0</v>
       </c>
       <c r="L24" s="12"/>
-      <c r="M24" s="107" t="s">
+      <c r="M24" s="99" t="s">
         <v>22</v>
       </c>
-      <c r="N24" s="108"/>
+      <c r="N24" s="100"/>
       <c r="O24" s="51"/>
       <c r="P24" s="52"/>
       <c r="Q24" s="52"/>
@@ -3957,38 +3968,38 @@
       <c r="V24" s="12"/>
     </row>
     <row r="25" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="107" t="s">
+      <c r="A25" s="99" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="109"/>
-      <c r="C25" s="110"/>
-      <c r="D25" s="110"/>
-      <c r="E25" s="110"/>
-      <c r="F25" s="110"/>
-      <c r="G25" s="110"/>
-      <c r="H25" s="110"/>
-      <c r="I25" s="119"/>
+      <c r="B25" s="101"/>
+      <c r="C25" s="102"/>
+      <c r="D25" s="102"/>
+      <c r="E25" s="102"/>
+      <c r="F25" s="102"/>
+      <c r="G25" s="102"/>
+      <c r="H25" s="102"/>
+      <c r="I25" s="111"/>
       <c r="J25" s="34"/>
       <c r="K25" s="34"/>
       <c r="L25" s="12"/>
-      <c r="M25" s="107" t="s">
+      <c r="M25" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="N25" s="109"/>
-      <c r="O25" s="110"/>
-      <c r="P25" s="110"/>
-      <c r="Q25" s="110"/>
-      <c r="R25" s="110"/>
-      <c r="S25" s="110"/>
-      <c r="T25" s="110"/>
-      <c r="U25" s="119"/>
+      <c r="N25" s="101"/>
+      <c r="O25" s="102"/>
+      <c r="P25" s="102"/>
+      <c r="Q25" s="102"/>
+      <c r="R25" s="102"/>
+      <c r="S25" s="102"/>
+      <c r="T25" s="102"/>
+      <c r="U25" s="111"/>
       <c r="V25" s="12"/>
     </row>
     <row r="26" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="107" t="s">
+      <c r="A26" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="B26" s="108"/>
+      <c r="B26" s="100"/>
       <c r="C26"/>
       <c r="D26"/>
       <c r="E26"/>
@@ -4008,10 +4019,10 @@
         <f t="shared" ref="L26:L28" si="4">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C26:I26)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M26" s="107" t="s">
+      <c r="M26" s="99" t="s">
         <v>7</v>
       </c>
-      <c r="N26" s="108"/>
+      <c r="N26" s="100"/>
       <c r="O26"/>
       <c r="P26"/>
       <c r="Q26"/>
@@ -4025,10 +4036,10 @@
       </c>
     </row>
     <row r="27" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="111" t="s">
+      <c r="A27" s="103" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="112"/>
+      <c r="B27" s="104"/>
       <c r="C27"/>
       <c r="D27"/>
       <c r="E27"/>
@@ -4048,10 +4059,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M27" s="107" t="s">
+      <c r="M27" s="99" t="s">
         <v>8</v>
       </c>
-      <c r="N27" s="108"/>
+      <c r="N27" s="100"/>
       <c r="O27"/>
       <c r="P27"/>
       <c r="Q27"/>
@@ -4065,10 +4076,10 @@
       </c>
     </row>
     <row r="28" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="107" t="s">
+      <c r="A28" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="108"/>
+      <c r="B28" s="100"/>
       <c r="C28"/>
       <c r="D28"/>
       <c r="E28"/>
@@ -4088,10 +4099,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M28" s="107" t="s">
+      <c r="M28" s="99" t="s">
         <v>21</v>
       </c>
-      <c r="N28" s="108"/>
+      <c r="N28" s="100"/>
       <c r="O28"/>
       <c r="P28"/>
       <c r="Q28"/>
@@ -4105,10 +4116,10 @@
       </c>
     </row>
     <row r="29" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="107" t="s">
+      <c r="A29" s="99" t="s">
         <v>22</v>
       </c>
-      <c r="B29" s="108"/>
+      <c r="B29" s="100"/>
       <c r="C29"/>
       <c r="D29"/>
       <c r="E29"/>
@@ -4125,10 +4136,10 @@
         <v>0</v>
       </c>
       <c r="L29" s="12"/>
-      <c r="M29" s="107" t="s">
+      <c r="M29" s="99" t="s">
         <v>22</v>
       </c>
-      <c r="N29" s="108"/>
+      <c r="N29" s="100"/>
       <c r="O29" s="89"/>
       <c r="P29" s="90"/>
       <c r="Q29" s="90"/>
@@ -4221,10 +4232,10 @@
       <c r="V31" s="1"/>
     </row>
     <row r="32" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="100" t="s">
+      <c r="A32" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="B32" s="101"/>
+      <c r="B32" s="93"/>
       <c r="C32" s="38"/>
       <c r="D32" s="38"/>
       <c r="E32" s="38"/>
@@ -4238,10 +4249,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C32:I32)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M32" s="100" t="s">
+      <c r="M32" s="92" t="s">
         <v>5</v>
       </c>
-      <c r="N32" s="101"/>
+      <c r="N32" s="93"/>
       <c r="O32" s="37"/>
       <c r="P32" s="38"/>
       <c r="Q32" s="38"/>
@@ -4255,10 +4266,10 @@
       </c>
     </row>
     <row r="33" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="100" t="s">
+      <c r="A33" s="92" t="s">
         <v>6</v>
       </c>
-      <c r="B33" s="101"/>
+      <c r="B33" s="93"/>
       <c r="C33" s="38"/>
       <c r="D33" s="38"/>
       <c r="E33" s="38"/>
@@ -4272,10 +4283,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C33:I33)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M33" s="100" t="s">
+      <c r="M33" s="92" t="s">
         <v>6</v>
       </c>
-      <c r="N33" s="101"/>
+      <c r="N33" s="93"/>
       <c r="O33" s="38"/>
       <c r="P33" s="38"/>
       <c r="Q33" s="38"/>
@@ -4289,10 +4300,10 @@
       </c>
     </row>
     <row r="34" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="100" t="s">
+      <c r="A34" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="B34" s="101"/>
+      <c r="B34" s="93"/>
       <c r="C34" s="28"/>
       <c r="D34" s="29"/>
       <c r="E34" s="29"/>
@@ -4306,10 +4317,10 @@
         <f t="shared" ref="L34:L43" si="7">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C34:I34)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M34" s="100" t="s">
+      <c r="M34" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="N34" s="101"/>
+      <c r="N34" s="93"/>
       <c r="O34" s="28"/>
       <c r="P34" s="29"/>
       <c r="Q34" s="29"/>
@@ -4323,35 +4334,35 @@
       </c>
     </row>
     <row r="35" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="100" t="s">
+      <c r="A35" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="B35" s="104"/>
-      <c r="C35" s="104"/>
-      <c r="D35" s="104"/>
-      <c r="E35" s="104"/>
-      <c r="F35" s="104"/>
-      <c r="G35" s="104"/>
-      <c r="H35" s="104"/>
-      <c r="I35" s="101"/>
+      <c r="B35" s="96"/>
+      <c r="C35" s="96"/>
+      <c r="D35" s="96"/>
+      <c r="E35" s="96"/>
+      <c r="F35" s="96"/>
+      <c r="G35" s="96"/>
+      <c r="H35" s="96"/>
+      <c r="I35" s="93"/>
       <c r="J35" s="40"/>
       <c r="K35" s="40"/>
       <c r="L35" s="1"/>
-      <c r="M35" s="100" t="s">
+      <c r="M35" s="92" t="s">
         <v>12</v>
       </c>
-      <c r="N35" s="104"/>
-      <c r="O35" s="104"/>
-      <c r="P35" s="104"/>
-      <c r="Q35" s="104"/>
-      <c r="R35" s="104"/>
-      <c r="S35" s="104"/>
-      <c r="T35" s="104"/>
-      <c r="U35" s="101"/>
+      <c r="N35" s="96"/>
+      <c r="O35" s="96"/>
+      <c r="P35" s="96"/>
+      <c r="Q35" s="96"/>
+      <c r="R35" s="96"/>
+      <c r="S35" s="96"/>
+      <c r="T35" s="96"/>
+      <c r="U35" s="93"/>
       <c r="V35" s="1"/>
     </row>
     <row r="36" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="102" t="s">
+      <c r="A36" s="94" t="s">
         <v>11</v>
       </c>
       <c r="B36" s="9" t="s">
@@ -4370,7 +4381,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M36" s="102" t="s">
+      <c r="M36" s="94" t="s">
         <v>11</v>
       </c>
       <c r="N36" s="9" t="s">
@@ -4389,7 +4400,7 @@
       </c>
     </row>
     <row r="37" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="116"/>
+      <c r="A37" s="108"/>
       <c r="B37" s="9" t="s">
         <v>14</v>
       </c>
@@ -4406,7 +4417,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M37" s="116"/>
+      <c r="M37" s="108"/>
       <c r="N37" s="9" t="s">
         <v>14</v>
       </c>
@@ -4423,7 +4434,7 @@
       </c>
     </row>
     <row r="38" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="116"/>
+      <c r="A38" s="108"/>
       <c r="B38" s="9" t="s">
         <v>17</v>
       </c>
@@ -4437,7 +4448,7 @@
       <c r="J38" s="40"/>
       <c r="K38" s="40"/>
       <c r="L38" s="1"/>
-      <c r="M38" s="116"/>
+      <c r="M38" s="108"/>
       <c r="N38" s="9" t="s">
         <v>17</v>
       </c>
@@ -4451,7 +4462,7 @@
       <c r="V38" s="1"/>
     </row>
     <row r="39" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="116"/>
+      <c r="A39" s="108"/>
       <c r="B39" s="9" t="s">
         <v>18</v>
       </c>
@@ -4465,7 +4476,7 @@
       <c r="J39" s="40"/>
       <c r="K39" s="40"/>
       <c r="L39" s="1"/>
-      <c r="M39" s="116"/>
+      <c r="M39" s="108"/>
       <c r="N39" s="9" t="s">
         <v>18</v>
       </c>
@@ -4479,7 +4490,7 @@
       <c r="V39" s="1"/>
     </row>
     <row r="40" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="116"/>
+      <c r="A40" s="108"/>
       <c r="B40" s="9" t="s">
         <v>15</v>
       </c>
@@ -4496,7 +4507,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M40" s="116"/>
+      <c r="M40" s="108"/>
       <c r="N40" s="9" t="s">
         <v>15</v>
       </c>
@@ -4510,7 +4521,7 @@
       <c r="V40" s="1"/>
     </row>
     <row r="41" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="116"/>
+      <c r="A41" s="108"/>
       <c r="B41" s="9" t="s">
         <v>25</v>
       </c>
@@ -4524,7 +4535,7 @@
       <c r="J41" s="40"/>
       <c r="K41" s="40"/>
       <c r="L41" s="1"/>
-      <c r="M41" s="116"/>
+      <c r="M41" s="108"/>
       <c r="N41" s="9" t="s">
         <v>25</v>
       </c>
@@ -4538,7 +4549,7 @@
       <c r="V41" s="1"/>
     </row>
     <row r="42" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="116"/>
+      <c r="A42" s="108"/>
       <c r="B42" s="9" t="s">
         <v>19</v>
       </c>
@@ -4552,7 +4563,7 @@
       <c r="J42" s="40"/>
       <c r="K42" s="40"/>
       <c r="L42" s="1"/>
-      <c r="M42" s="116"/>
+      <c r="M42" s="108"/>
       <c r="N42" s="9" t="s">
         <v>19</v>
       </c>
@@ -4566,7 +4577,7 @@
       <c r="V42" s="1"/>
     </row>
     <row r="43" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="116"/>
+      <c r="A43" s="108"/>
       <c r="B43" s="9" t="s">
         <v>16</v>
       </c>
@@ -4583,7 +4594,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M43" s="116"/>
+      <c r="M43" s="108"/>
       <c r="N43" s="9" t="s">
         <v>16</v>
       </c>
@@ -4597,7 +4608,7 @@
       <c r="V43" s="1"/>
     </row>
     <row r="44" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="117"/>
+      <c r="A44" s="109"/>
       <c r="B44" s="9" t="s">
         <v>26</v>
       </c>
@@ -4611,7 +4622,7 @@
       <c r="J44" s="40"/>
       <c r="K44" s="40"/>
       <c r="L44" s="1"/>
-      <c r="M44" s="117"/>
+      <c r="M44" s="109"/>
       <c r="N44" s="9" t="s">
         <v>26</v>
       </c>
@@ -4625,38 +4636,38 @@
       <c r="V44" s="1"/>
     </row>
     <row r="45" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="100" t="s">
+      <c r="A45" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="B45" s="104"/>
-      <c r="C45" s="105"/>
-      <c r="D45" s="105"/>
-      <c r="E45" s="105"/>
-      <c r="F45" s="105"/>
-      <c r="G45" s="105"/>
-      <c r="H45" s="105"/>
-      <c r="I45" s="118"/>
+      <c r="B45" s="96"/>
+      <c r="C45" s="97"/>
+      <c r="D45" s="97"/>
+      <c r="E45" s="97"/>
+      <c r="F45" s="97"/>
+      <c r="G45" s="97"/>
+      <c r="H45" s="97"/>
+      <c r="I45" s="110"/>
       <c r="J45" s="40"/>
       <c r="K45" s="40"/>
       <c r="L45" s="1"/>
-      <c r="M45" s="100" t="s">
+      <c r="M45" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="N45" s="104"/>
-      <c r="O45" s="105"/>
-      <c r="P45" s="105"/>
-      <c r="Q45" s="105"/>
-      <c r="R45" s="105"/>
-      <c r="S45" s="105"/>
-      <c r="T45" s="105"/>
-      <c r="U45" s="118"/>
+      <c r="N45" s="96"/>
+      <c r="O45" s="97"/>
+      <c r="P45" s="97"/>
+      <c r="Q45" s="97"/>
+      <c r="R45" s="97"/>
+      <c r="S45" s="97"/>
+      <c r="T45" s="97"/>
+      <c r="U45" s="110"/>
       <c r="V45" s="1"/>
     </row>
     <row r="46" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="100" t="s">
+      <c r="A46" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="B46" s="101"/>
+      <c r="B46" s="93"/>
       <c r="C46" s="54"/>
       <c r="D46" s="55"/>
       <c r="E46" s="55"/>
@@ -4670,10 +4681,10 @@
         <f t="shared" ref="L46:L48" si="8">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C46:I46)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M46" s="100" t="s">
+      <c r="M46" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="N46" s="101"/>
+      <c r="N46" s="93"/>
       <c r="O46" s="54"/>
       <c r="P46" s="55"/>
       <c r="Q46" s="55"/>
@@ -4687,10 +4698,10 @@
       </c>
     </row>
     <row r="47" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="100" t="s">
+      <c r="A47" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="B47" s="101"/>
+      <c r="B47" s="93"/>
       <c r="C47" s="57"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -4704,10 +4715,10 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M47" s="100" t="s">
+      <c r="M47" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="101"/>
+      <c r="N47" s="93"/>
       <c r="O47" s="57"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
@@ -4721,10 +4732,10 @@
       </c>
     </row>
     <row r="48" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="100" t="s">
+      <c r="A48" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="B48" s="101"/>
+      <c r="B48" s="93"/>
       <c r="C48" s="57"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -4738,10 +4749,10 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M48" s="100" t="s">
+      <c r="M48" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="N48" s="101"/>
+      <c r="N48" s="93"/>
       <c r="O48" s="57"/>
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
@@ -4755,10 +4766,10 @@
       </c>
     </row>
     <row r="49" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="100" t="s">
+      <c r="A49" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="B49" s="101"/>
+      <c r="B49" s="93"/>
       <c r="C49" s="59"/>
       <c r="D49" s="60"/>
       <c r="E49" s="60"/>
@@ -4769,10 +4780,10 @@
       <c r="J49" s="45"/>
       <c r="K49" s="45"/>
       <c r="L49" s="44"/>
-      <c r="M49" s="100" t="s">
+      <c r="M49" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="N49" s="101"/>
+      <c r="N49" s="93"/>
       <c r="O49" s="59"/>
       <c r="P49" s="60"/>
       <c r="Q49" s="60"/>
@@ -4783,38 +4794,38 @@
       <c r="V49" s="1"/>
     </row>
     <row r="50" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="100" t="s">
+      <c r="A50" s="92" t="s">
         <v>23</v>
       </c>
-      <c r="B50" s="104"/>
-      <c r="C50" s="105"/>
-      <c r="D50" s="105"/>
-      <c r="E50" s="105"/>
-      <c r="F50" s="105"/>
-      <c r="G50" s="105"/>
-      <c r="H50" s="105"/>
-      <c r="I50" s="118"/>
+      <c r="B50" s="96"/>
+      <c r="C50" s="97"/>
+      <c r="D50" s="97"/>
+      <c r="E50" s="97"/>
+      <c r="F50" s="97"/>
+      <c r="G50" s="97"/>
+      <c r="H50" s="97"/>
+      <c r="I50" s="110"/>
       <c r="J50" s="40"/>
       <c r="K50" s="40"/>
       <c r="L50" s="1"/>
-      <c r="M50" s="100" t="s">
+      <c r="M50" s="92" t="s">
         <v>23</v>
       </c>
-      <c r="N50" s="104"/>
-      <c r="O50" s="105"/>
-      <c r="P50" s="105"/>
-      <c r="Q50" s="105"/>
-      <c r="R50" s="105"/>
-      <c r="S50" s="105"/>
-      <c r="T50" s="105"/>
-      <c r="U50" s="118"/>
+      <c r="N50" s="96"/>
+      <c r="O50" s="97"/>
+      <c r="P50" s="97"/>
+      <c r="Q50" s="97"/>
+      <c r="R50" s="97"/>
+      <c r="S50" s="97"/>
+      <c r="T50" s="97"/>
+      <c r="U50" s="110"/>
       <c r="V50" s="1"/>
     </row>
     <row r="51" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="100" t="s">
+      <c r="A51" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="B51" s="101"/>
+      <c r="B51" s="93"/>
       <c r="C51" s="54"/>
       <c r="D51" s="55"/>
       <c r="E51" s="55"/>
@@ -4828,10 +4839,10 @@
         <f t="shared" ref="L51:L53" si="9">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C51:I51)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M51" s="100" t="s">
+      <c r="M51" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="N51" s="101"/>
+      <c r="N51" s="93"/>
       <c r="O51" s="54"/>
       <c r="P51" s="55"/>
       <c r="Q51" s="55"/>
@@ -4845,10 +4856,10 @@
       </c>
     </row>
     <row r="52" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="102" t="s">
+      <c r="A52" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="B52" s="103"/>
+      <c r="B52" s="95"/>
       <c r="C52" s="57"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -4862,10 +4873,10 @@
         <f t="shared" si="9"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M52" s="100" t="s">
+      <c r="M52" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="N52" s="101"/>
+      <c r="N52" s="93"/>
       <c r="O52" s="57"/>
       <c r="P52" s="1"/>
       <c r="Q52" s="1"/>
@@ -4879,10 +4890,10 @@
       </c>
     </row>
     <row r="53" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="100" t="s">
+      <c r="A53" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="B53" s="101"/>
+      <c r="B53" s="93"/>
       <c r="C53" s="57"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -4896,10 +4907,10 @@
         <f t="shared" si="9"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M53" s="100" t="s">
+      <c r="M53" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="N53" s="101"/>
+      <c r="N53" s="93"/>
       <c r="O53" s="57"/>
       <c r="P53" s="1"/>
       <c r="Q53" s="1"/>
@@ -4913,10 +4924,10 @@
       </c>
     </row>
     <row r="54" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="100" t="s">
+      <c r="A54" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="B54" s="101"/>
+      <c r="B54" s="93"/>
       <c r="C54" s="59"/>
       <c r="D54" s="60"/>
       <c r="E54" s="60"/>
@@ -4927,10 +4938,10 @@
       <c r="J54" s="40"/>
       <c r="K54" s="40"/>
       <c r="L54" s="1"/>
-      <c r="M54" s="100" t="s">
+      <c r="M54" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="N54" s="101"/>
+      <c r="N54" s="93"/>
       <c r="O54" s="59"/>
       <c r="P54" s="60"/>
       <c r="Q54" s="60"/>
@@ -4941,38 +4952,38 @@
       <c r="V54" s="1"/>
     </row>
     <row r="55" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="100" t="s">
+      <c r="A55" s="92" t="s">
         <v>24</v>
       </c>
-      <c r="B55" s="104"/>
-      <c r="C55" s="105"/>
-      <c r="D55" s="105"/>
-      <c r="E55" s="105"/>
-      <c r="F55" s="105"/>
-      <c r="G55" s="105"/>
-      <c r="H55" s="105"/>
-      <c r="I55" s="118"/>
+      <c r="B55" s="96"/>
+      <c r="C55" s="97"/>
+      <c r="D55" s="97"/>
+      <c r="E55" s="97"/>
+      <c r="F55" s="97"/>
+      <c r="G55" s="97"/>
+      <c r="H55" s="97"/>
+      <c r="I55" s="110"/>
       <c r="J55" s="40"/>
       <c r="K55" s="40"/>
       <c r="L55" s="1"/>
-      <c r="M55" s="100" t="s">
+      <c r="M55" s="92" t="s">
         <v>23</v>
       </c>
-      <c r="N55" s="104"/>
-      <c r="O55" s="105"/>
-      <c r="P55" s="105"/>
-      <c r="Q55" s="105"/>
-      <c r="R55" s="105"/>
-      <c r="S55" s="105"/>
-      <c r="T55" s="105"/>
-      <c r="U55" s="118"/>
+      <c r="N55" s="96"/>
+      <c r="O55" s="97"/>
+      <c r="P55" s="97"/>
+      <c r="Q55" s="97"/>
+      <c r="R55" s="97"/>
+      <c r="S55" s="97"/>
+      <c r="T55" s="97"/>
+      <c r="U55" s="110"/>
       <c r="V55" s="1"/>
     </row>
     <row r="56" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="100" t="s">
+      <c r="A56" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="B56" s="101"/>
+      <c r="B56" s="93"/>
       <c r="C56"/>
       <c r="D56"/>
       <c r="E56"/>
@@ -4986,10 +4997,10 @@
         <f t="shared" ref="L56:L58" si="11">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C56:I56)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M56" s="100" t="s">
+      <c r="M56" s="92" t="s">
         <v>7</v>
       </c>
-      <c r="N56" s="101"/>
+      <c r="N56" s="93"/>
       <c r="O56"/>
       <c r="P56"/>
       <c r="Q56"/>
@@ -5003,10 +5014,10 @@
       </c>
     </row>
     <row r="57" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="102" t="s">
+      <c r="A57" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="B57" s="103"/>
+      <c r="B57" s="95"/>
       <c r="C57"/>
       <c r="D57"/>
       <c r="E57"/>
@@ -5020,10 +5031,10 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M57" s="100" t="s">
+      <c r="M57" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="N57" s="101"/>
+      <c r="N57" s="93"/>
       <c r="O57"/>
       <c r="P57"/>
       <c r="Q57"/>
@@ -5037,10 +5048,10 @@
       </c>
     </row>
     <row r="58" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="100" t="s">
+      <c r="A58" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="B58" s="101"/>
+      <c r="B58" s="93"/>
       <c r="C58"/>
       <c r="D58"/>
       <c r="E58"/>
@@ -5054,10 +5065,10 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M58" s="100" t="s">
+      <c r="M58" s="92" t="s">
         <v>21</v>
       </c>
-      <c r="N58" s="101"/>
+      <c r="N58" s="93"/>
       <c r="O58"/>
       <c r="P58"/>
       <c r="Q58"/>
@@ -5071,10 +5082,10 @@
       </c>
     </row>
     <row r="59" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="100" t="s">
+      <c r="A59" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="B59" s="101"/>
+      <c r="B59" s="93"/>
       <c r="C59" s="86"/>
       <c r="D59" s="87"/>
       <c r="E59" s="87"/>
@@ -5085,10 +5096,10 @@
       <c r="J59" s="40"/>
       <c r="K59" s="40"/>
       <c r="L59" s="1"/>
-      <c r="M59" s="100" t="s">
+      <c r="M59" s="92" t="s">
         <v>22</v>
       </c>
-      <c r="N59" s="101"/>
+      <c r="N59" s="93"/>
       <c r="O59" s="86"/>
       <c r="P59" s="87"/>
       <c r="Q59" s="87"/>
@@ -5265,17 +5276,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9:I9">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="23">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="24">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5309,17 +5320,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12:I12">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="25">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="26">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5645,7 +5656,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A38A25A9-7BAB-4662-AC2A-B7F2DABCCE29}">
   <dimension ref="B1:G12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
@@ -5655,20 +5666,20 @@
   <sheetData>
     <row r="1" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="B2" s="92" t="s">
+      <c r="B2" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="98"/>
-      <c r="D2" s="95" t="s">
+      <c r="C2" s="118"/>
+      <c r="D2" s="115" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="96"/>
-      <c r="F2" s="96"/>
-      <c r="G2" s="97"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="117"/>
     </row>
     <row r="3" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="94"/>
-      <c r="C3" s="99"/>
+      <c r="B3" s="114"/>
+      <c r="C3" s="119"/>
       <c r="D3" s="77" t="s">
         <v>27</v>
       </c>
@@ -5721,20 +5732,20 @@
       <c r="G7" s="25"/>
     </row>
     <row r="8" spans="2:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="B8" s="92" t="s">
+      <c r="B8" s="112" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="98"/>
-      <c r="D8" s="95" t="s">
+      <c r="C8" s="118"/>
+      <c r="D8" s="115" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="96"/>
-      <c r="F8" s="96"/>
-      <c r="G8" s="97"/>
+      <c r="E8" s="116"/>
+      <c r="F8" s="116"/>
+      <c r="G8" s="117"/>
     </row>
     <row r="9" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="94"/>
-      <c r="C9" s="99"/>
+      <c r="B9" s="114"/>
+      <c r="C9" s="119"/>
       <c r="D9" s="77" t="s">
         <v>27</v>
       </c>
@@ -5749,7 +5760,7 @@
       </c>
     </row>
     <row r="10" spans="2:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="B10" s="92" t="s">
+      <c r="B10" s="112" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="70" t="s">
@@ -5761,7 +5772,7 @@
       <c r="G10" s="81"/>
     </row>
     <row r="11" spans="2:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="B11" s="93"/>
+      <c r="B11" s="113"/>
       <c r="C11" s="72" t="s">
         <v>28</v>
       </c>
@@ -5771,7 +5782,7 @@
       <c r="G11" s="73"/>
     </row>
     <row r="12" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="94"/>
+      <c r="B12" s="114"/>
       <c r="C12" s="83" t="s">
         <v>29</v>
       </c>

--- a/results_(stress_test)_baselines/summary.xlsx
+++ b/results_(stress_test)_baselines/summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RnD_Repo\Research_Engineeirng\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_baselines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D28307-8715-4E58-907A-13F1E5B3B399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0BD73A1-3C2C-41D5-84E5-5EAED4D67950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="639" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="639" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="partialdata_20260429_unf_idx" sheetId="6" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="36">
   <si>
     <t>Accuracy</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -264,7 +264,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -404,11 +404,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -621,46 +647,58 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -675,12 +713,6 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -704,6 +736,60 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -985,7 +1071,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4687D530-62F3-45D6-8CBF-3B0602E24BE5}">
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:R45"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25" style="10" customWidth="1"/>
@@ -1049,23 +1135,23 @@
       <c r="R1" s="12"/>
     </row>
     <row r="2" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="99" t="s">
+      <c r="A2" s="94" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="100"/>
-      <c r="C2">
+      <c r="B2" s="95"/>
+      <c r="C2" s="125">
         <v>92.97270449283009</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="126">
         <v>92.656851126163161</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="126">
         <v>90.612485113769722</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="126">
         <v>76.890048068466555</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="127">
         <v>57.431157132270449</v>
       </c>
       <c r="H2" s="23" cm="1">
@@ -1080,23 +1166,23 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:G2)&amp;","</f>
         <v xml:space="preserve">    92.9727044928301, 92.6568511261632, 90.6124851137697, 76.8900480684666, 57.4311571322704,</v>
       </c>
-      <c r="K2" s="99" t="s">
+      <c r="K2" s="94" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="100"/>
-      <c r="M2">
+      <c r="L2" s="95"/>
+      <c r="M2" s="125">
         <v>3.6723191410127392</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="126">
         <v>3.8557140126956959</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="126">
         <v>4.1717853309388913</v>
       </c>
-      <c r="P2">
+      <c r="P2" s="126">
         <v>8.1206319222896362</v>
       </c>
-      <c r="Q2">
+      <c r="Q2" s="127">
         <v>8.7326493747450371</v>
       </c>
       <c r="R2" s="12" t="str">
@@ -1105,23 +1191,23 @@
       </c>
     </row>
     <row r="3" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="99" t="s">
+      <c r="A3" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="100"/>
-      <c r="C3">
+      <c r="B3" s="95"/>
+      <c r="C3" s="128">
         <v>93.550650668835075</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="124">
         <v>92.282219857726602</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="124">
         <v>90.501679656975099</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="124">
         <v>72.805808585426078</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="129">
         <v>54.064066298151367</v>
       </c>
       <c r="H3" s="23" cm="1">
@@ -1136,23 +1222,23 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:G3)&amp;","</f>
         <v xml:space="preserve">    93.5506506688351, 92.2822198577266, 90.5016796569751, 72.8058085854261, 54.0640662981514,</v>
       </c>
-      <c r="K3" s="99" t="s">
+      <c r="K3" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="L3" s="100"/>
-      <c r="M3">
+      <c r="L3" s="95"/>
+      <c r="M3" s="128">
         <v>3.5444962758226279</v>
       </c>
-      <c r="N3">
+      <c r="N3" s="124">
         <v>3.640571601682856</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="124">
         <v>3.5241233819887818</v>
       </c>
-      <c r="P3">
+      <c r="P3" s="124">
         <v>9.1245390051568016</v>
       </c>
-      <c r="Q3">
+      <c r="Q3" s="129">
         <v>7.5991148630492704</v>
       </c>
       <c r="R3" s="12" t="str">
@@ -1161,23 +1247,23 @@
       </c>
     </row>
     <row r="4" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="99" t="s">
+      <c r="A4" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="100"/>
-      <c r="C4">
+      <c r="B4" s="99"/>
+      <c r="C4" s="128">
         <v>88.646029233240199</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="124">
         <v>87.588003933136662</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="124">
         <v>87.102273087714138</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="124">
         <v>74.826714187262283</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="129">
         <v>50.055245575942109</v>
       </c>
       <c r="H4" s="34" cm="1">
@@ -1192,23 +1278,23 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C4:G4)&amp;","</f>
         <v xml:space="preserve">    88.6460292332402, 87.5880039331367, 87.1022730877141, 74.8267141872623, 50.0552455759421,</v>
       </c>
-      <c r="K4" s="99" t="s">
+      <c r="K4" s="98" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="100"/>
-      <c r="M4">
+      <c r="L4" s="99"/>
+      <c r="M4" s="128">
         <v>3.1531095164540388</v>
       </c>
-      <c r="N4">
+      <c r="N4" s="124">
         <v>2.2977524920825498</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="124">
         <v>1.6498123709550609</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="124">
         <v>2.8561346399896621</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="129">
         <v>1.6635727988470741</v>
       </c>
       <c r="R4" s="12" t="str">
@@ -1217,49 +1303,49 @@
       </c>
     </row>
     <row r="5" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="99" t="s">
+      <c r="A5" s="94" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="101"/>
-      <c r="C5" s="101"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="101"/>
-      <c r="G5" s="101"/>
+      <c r="B5" s="96"/>
+      <c r="C5" s="96"/>
+      <c r="D5" s="96"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="96"/>
+      <c r="G5" s="95"/>
       <c r="H5" s="34"/>
       <c r="I5" s="34"/>
       <c r="J5" s="12"/>
-      <c r="K5" s="99" t="s">
+      <c r="K5" s="94" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="101"/>
-      <c r="M5" s="101"/>
-      <c r="N5" s="101"/>
-      <c r="O5" s="101"/>
-      <c r="P5" s="101"/>
-      <c r="Q5" s="101"/>
+      <c r="L5" s="96"/>
+      <c r="M5" s="96"/>
+      <c r="N5" s="96"/>
+      <c r="O5" s="96"/>
+      <c r="P5" s="96"/>
+      <c r="Q5" s="95"/>
       <c r="R5" s="12"/>
     </row>
     <row r="6" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="92" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="144" t="s">
         <v>13</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="128">
         <v>93.358985227669237</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="124">
         <v>92.785690187631374</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="124">
         <v>91.279001836809442</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="124">
         <v>77.243569004345488</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="129">
         <v>56.641689518652129</v>
       </c>
       <c r="H6" s="34" cm="1">
@@ -1274,25 +1360,25 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C6:G6)&amp;","</f>
         <v xml:space="preserve">    93.3589852276692, 92.7856901876314, 91.2790018368094, 77.2435690043455, 56.6416895186521,</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="K6" s="92" t="s">
         <v>11</v>
       </c>
-      <c r="L6" s="8" t="s">
+      <c r="L6" s="144" t="s">
         <v>13</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="128">
         <v>3.5292136776947389</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="124">
         <v>3.7787197360632829</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="124">
         <v>3.589155414302748</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="124">
         <v>7.7490040503559836</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="129">
         <v>8.6647795337348459</v>
       </c>
       <c r="R6" s="12" t="str">
@@ -1307,19 +1393,19 @@
       <c r="B7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="128">
         <v>92.744346116027529</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="124">
         <v>92.328416912487711</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="124">
         <v>91.156108616856514</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="124">
         <v>82.307782362592519</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="129">
         <v>57.694504277718679</v>
       </c>
       <c r="H7" s="34" cm="1">
@@ -1340,1255 +1426,1449 @@
       <c r="L7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="M7" s="51"/>
-      <c r="N7" s="52"/>
-      <c r="O7" s="52"/>
-      <c r="P7" s="52"/>
-      <c r="Q7" s="52"/>
+      <c r="M7" s="128">
+        <v>3.3427481085122568</v>
+      </c>
+      <c r="N7" s="124">
+        <v>3.376440347285802</v>
+      </c>
+      <c r="O7" s="124">
+        <v>3.0132050938587081</v>
+      </c>
+      <c r="P7" s="124">
+        <v>4.6775599948055158</v>
+      </c>
+      <c r="Q7" s="129">
+        <v>6.3264357320363649</v>
+      </c>
       <c r="R7" s="12" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M7:Q7)&amp;","</f>
-        <v xml:space="preserve">    ,</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="99" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="101"/>
-      <c r="C8" s="105"/>
-      <c r="D8" s="105"/>
-      <c r="E8" s="105"/>
-      <c r="F8" s="105"/>
-      <c r="G8" s="105"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="34"/>
+        <v xml:space="preserve">    3.34274810851226, 3.3764403472858, 3.01320509385871, 4.67755999480552, 6.32643573203636,</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="128">
+        <v>93.578171091445412</v>
+      </c>
+      <c r="D8" s="124">
+        <v>92.721736347200235</v>
+      </c>
+      <c r="E8" s="124">
+        <v>90.919630215947663</v>
+      </c>
+      <c r="F8" s="124">
+        <v>73.42964039481312</v>
+      </c>
+      <c r="G8" s="129">
+        <v>56.559615567608724</v>
+      </c>
+      <c r="H8" s="34" cm="1">
+        <f t="array" ref="H8">-SUMPRODUCT((D1:F1-C1:E1)*(C8:E8+D8:F8)/2)</f>
+        <v>79.80197709322745</v>
+      </c>
+      <c r="I8" s="34" cm="1">
+        <f t="array" ref="I8">-SUMPRODUCT((D1:G1-C1:F1)*(C8:F8+D8:G8)/2)</f>
+        <v>83.864141342053131</v>
+      </c>
       <c r="J8" s="12"/>
-      <c r="K8" s="99" t="s">
-        <v>20</v>
-      </c>
-      <c r="L8" s="101"/>
-      <c r="M8" s="105"/>
-      <c r="N8" s="105"/>
-      <c r="O8" s="105"/>
-      <c r="P8" s="105"/>
-      <c r="Q8" s="105"/>
-      <c r="R8" s="12"/>
+      <c r="K8" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M8" s="128">
+        <v>3.4211604643278899</v>
+      </c>
+      <c r="N8" s="124">
+        <v>3.758697386182225</v>
+      </c>
+      <c r="O8" s="124">
+        <v>3.9384751732193859</v>
+      </c>
+      <c r="P8" s="124">
+        <v>8.9824743171696255</v>
+      </c>
+      <c r="Q8" s="129">
+        <v>8.2082515511175735</v>
+      </c>
+      <c r="R8" s="12" t="str">
+        <f t="shared" ref="R8:R9" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M8:Q8)&amp;","</f>
+        <v xml:space="preserve">    3.42116046432789, 3.75869738618223, 3.93847517321939, 8.98247431716963, 8.20825155111757,</v>
+      </c>
     </row>
     <row r="9" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="99" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="100"/>
-      <c r="C9">
-        <v>93.207752662220258</v>
-      </c>
-      <c r="D9">
-        <v>92.783034455315345</v>
-      </c>
-      <c r="E9">
-        <v>90.565884364628303</v>
-      </c>
-      <c r="F9">
-        <v>73.076886478256739</v>
-      </c>
-      <c r="G9">
-        <v>58.556994437668138</v>
+      <c r="A9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="140" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="128">
+        <v>90.553588987217324</v>
+      </c>
+      <c r="D9" s="124">
+        <v>90.325467059980355</v>
+      </c>
+      <c r="E9" s="124">
+        <v>89.668636118536241</v>
+      </c>
+      <c r="F9" s="124">
+        <v>78.678561233228677</v>
+      </c>
+      <c r="G9" s="129">
+        <v>53.098925307889047</v>
       </c>
       <c r="H9" s="34" cm="1">
         <f t="array" ref="H9">-SUMPRODUCT((D1:F1-C1:E1)*(C9:E9+D9:F9)/2)</f>
-        <v>79.643984809557168</v>
+        <v>78.240726743599296</v>
       </c>
       <c r="I9" s="34" cm="1">
         <f t="array" ref="I9">-SUMPRODUCT((D1:G1-C1:F1)*(C9:F9+D9:G9)/2)</f>
-        <v>83.757543588179814</v>
-      </c>
-      <c r="J9" s="12" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C9:G9)&amp;","</f>
-        <v xml:space="preserve">    93.2077526622203, 92.7830344553153, 90.5658843646283, 73.0768864782567, 58.5569944376681,</v>
-      </c>
-      <c r="K9" s="99" t="s">
+        <v>82.358773198009231</v>
+      </c>
+      <c r="J9" s="12"/>
+      <c r="K9" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="L9" s="140" t="s">
+        <v>19</v>
+      </c>
+      <c r="M9" s="128">
+        <v>2.5990157411770438</v>
+      </c>
+      <c r="N9" s="124">
+        <v>2.3843919339500612</v>
+      </c>
+      <c r="O9" s="124">
+        <v>2.4318730481068318</v>
+      </c>
+      <c r="P9" s="124">
+        <v>3.814135483602267</v>
+      </c>
+      <c r="Q9" s="129">
+        <v>3.5742222382122981</v>
+      </c>
+      <c r="R9" s="12" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">    2.59901574117704, 2.38439193395006, 2.43187304810683, 3.81413548360227, 3.5742222382123,</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="94" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="96"/>
+      <c r="C10" s="96"/>
+      <c r="D10" s="96"/>
+      <c r="E10" s="96"/>
+      <c r="F10" s="96"/>
+      <c r="G10" s="95"/>
+      <c r="H10" s="34"/>
+      <c r="I10" s="34"/>
+      <c r="J10" s="12"/>
+      <c r="K10" s="94" t="s">
+        <v>20</v>
+      </c>
+      <c r="L10" s="96"/>
+      <c r="M10" s="96"/>
+      <c r="N10" s="96"/>
+      <c r="O10" s="96"/>
+      <c r="P10" s="96"/>
+      <c r="Q10" s="95"/>
+      <c r="R10" s="12"/>
+    </row>
+    <row r="11" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="111" t="s">
         <v>7</v>
       </c>
-      <c r="L9" s="100"/>
-      <c r="M9">
-        <v>4.081079160307894</v>
-      </c>
-      <c r="N9">
-        <v>3.9215668791224498</v>
-      </c>
-      <c r="O9">
-        <v>3.873470124738835</v>
-      </c>
-      <c r="P9">
-        <v>9.0889689998586825</v>
-      </c>
-      <c r="Q9">
-        <v>9.0192886420696112</v>
-      </c>
-      <c r="R9" s="12" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M9:Q9)&amp;","</f>
-        <v xml:space="preserve">    4.08107916030789, 3.92156687912245, 3.87347012473884, 9.08896899985868, 9.01928864206961,</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="103" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="104"/>
-      <c r="C10">
-        <v>93.534975792754821</v>
-      </c>
-      <c r="D10">
-        <v>92.336467731843129</v>
-      </c>
-      <c r="E10">
-        <v>88.593520128490155</v>
-      </c>
-      <c r="F10">
-        <v>71.045294509468079</v>
-      </c>
-      <c r="G10">
-        <v>53.467062863865607</v>
-      </c>
-      <c r="H10" s="34" cm="1">
-        <f t="array" ref="H10">-SUMPRODUCT((D1:F1-C1:E1)*(C10:E10+D10:F10)/2)</f>
-        <v>79.061535278563539</v>
-      </c>
-      <c r="I10" s="34" cm="1">
-        <f t="array" ref="I10">-SUMPRODUCT((D1:G1-C1:F1)*(C10:F10+D10:G10)/2)</f>
-        <v>82.952546446480213</v>
-      </c>
-      <c r="J10" s="12" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C10:G10)&amp;","</f>
-        <v xml:space="preserve">    93.5349757927548, 92.3364677318431, 88.5935201284902, 71.0452945094681, 53.4670628638656,</v>
-      </c>
-      <c r="K10" s="99" t="s">
-        <v>8</v>
-      </c>
-      <c r="L10" s="100"/>
-      <c r="M10">
-        <v>3.8494978151380188</v>
-      </c>
-      <c r="N10">
-        <v>3.7468317792042942</v>
-      </c>
-      <c r="O10">
-        <v>4.6420078579248552</v>
-      </c>
-      <c r="P10">
-        <v>10.247976510425289</v>
-      </c>
-      <c r="Q10">
-        <v>9.5145399413620808</v>
-      </c>
-      <c r="R10" s="12" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M10:Q10)&amp;","</f>
-        <v xml:space="preserve">    3.84949781513802, 3.74683177920429, 4.64200785792486, 10.2479765104253, 9.51453994136208,</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="99" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="100"/>
-      <c r="C11">
-        <v>93.005297046975599</v>
-      </c>
-      <c r="D11">
-        <v>91.902444369472647</v>
-      </c>
-      <c r="E11">
-        <v>89.116278399178753</v>
-      </c>
-      <c r="F11">
-        <v>72.258814234263852</v>
-      </c>
-      <c r="G11">
-        <v>53.843628981796257</v>
+      <c r="B11" s="143"/>
+      <c r="C11" s="128">
+        <v>93.207752662220258</v>
+      </c>
+      <c r="D11" s="124">
+        <v>92.783034455315345</v>
+      </c>
+      <c r="E11" s="124">
+        <v>90.565884364628303</v>
+      </c>
+      <c r="F11" s="124">
+        <v>73.076886478256739</v>
+      </c>
+      <c r="G11" s="129">
+        <v>58.556994437668138</v>
       </c>
       <c r="H11" s="34" cm="1">
         <f t="array" ref="H11">-SUMPRODUCT((D1:F1-C1:E1)*(C11:E11+D11:F11)/2)</f>
-        <v>78.940218989783645</v>
+        <v>79.643984809557168</v>
       </c>
       <c r="I11" s="34" cm="1">
         <f t="array" ref="I11">-SUMPRODUCT((D1:G1-C1:F1)*(C11:F11+D11:G11)/2)</f>
-        <v>82.880920340285527</v>
+        <v>83.757543588179814</v>
       </c>
       <c r="J11" s="12" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C11:G11)&amp;","</f>
-        <v xml:space="preserve">    93.0052970469756, 91.9024443694726, 89.1162783991788, 72.2588142342639, 53.8436289817963,</v>
-      </c>
-      <c r="K11" s="99" t="s">
-        <v>21</v>
-      </c>
-      <c r="L11" s="100"/>
-      <c r="M11">
-        <v>3.458803648865628</v>
-      </c>
-      <c r="N11">
-        <v>4.1139178681351494</v>
-      </c>
-      <c r="O11">
-        <v>4.3674865362294497</v>
-      </c>
-      <c r="P11">
-        <v>10.1810612930344</v>
-      </c>
-      <c r="Q11">
-        <v>8.6745540222164905</v>
+        <v xml:space="preserve">    93.2077526622203, 92.7830344553153, 90.5658843646283, 73.0768864782567, 58.5569944376681,</v>
+      </c>
+      <c r="K11" s="111" t="s">
+        <v>7</v>
+      </c>
+      <c r="L11" s="143"/>
+      <c r="M11" s="128">
+        <v>4.081079160307894</v>
+      </c>
+      <c r="N11" s="124">
+        <v>3.9215668791224498</v>
+      </c>
+      <c r="O11" s="124">
+        <v>3.873470124738835</v>
+      </c>
+      <c r="P11" s="124">
+        <v>9.0889689998586825</v>
+      </c>
+      <c r="Q11" s="129">
+        <v>9.0192886420696112</v>
       </c>
       <c r="R11" s="12" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M11:Q11)&amp;","</f>
-        <v xml:space="preserve">    3.45880364886563, 4.11391786813515, 4.36748653622945, 10.1810612930344, 8.67455402221649,</v>
+        <v xml:space="preserve">    4.08107916030789, 3.92156687912245, 3.87347012473884, 9.08896899985868, 9.01928864206961,</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="99" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="100"/>
-      <c r="C12" s="35"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
+      <c r="A12" s="98" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="99"/>
+      <c r="C12" s="128">
+        <v>93.534975792754821</v>
+      </c>
+      <c r="D12" s="124">
+        <v>92.336467731843129</v>
+      </c>
+      <c r="E12" s="124">
+        <v>88.593520128490155</v>
+      </c>
+      <c r="F12" s="124">
+        <v>71.045294509468079</v>
+      </c>
+      <c r="G12" s="129">
+        <v>53.467062863865607</v>
+      </c>
       <c r="H12" s="34" cm="1">
         <f t="array" ref="H12">-SUMPRODUCT((D1:F1-C1:E1)*(C12:E12+D12:F12)/2)</f>
-        <v>0</v>
+        <v>79.061535278563539</v>
       </c>
       <c r="I12" s="34" cm="1">
         <f t="array" ref="I12">-SUMPRODUCT((D1:G1-C1:F1)*(C12:F12+D12:G12)/2)</f>
-        <v>0</v>
+        <v>82.952546446480213</v>
       </c>
       <c r="J12" s="12" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C12:G12)&amp;","</f>
-        <v xml:space="preserve">    ,</v>
-      </c>
-      <c r="K12" s="99" t="s">
-        <v>22</v>
-      </c>
-      <c r="L12" s="100"/>
-      <c r="M12" s="35"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="36"/>
+        <v xml:space="preserve">    93.5349757927548, 92.3364677318431, 88.5935201284902, 71.0452945094681, 53.4670628638656,</v>
+      </c>
+      <c r="K12" s="94" t="s">
+        <v>8</v>
+      </c>
+      <c r="L12" s="95"/>
+      <c r="M12" s="128">
+        <v>3.8494978151380188</v>
+      </c>
+      <c r="N12" s="124">
+        <v>3.7468317792042942</v>
+      </c>
+      <c r="O12" s="124">
+        <v>4.6420078579248552</v>
+      </c>
+      <c r="P12" s="124">
+        <v>10.247976510425289</v>
+      </c>
+      <c r="Q12" s="129">
+        <v>9.5145399413620808</v>
+      </c>
       <c r="R12" s="12" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M12:Q12)&amp;","</f>
-        <v xml:space="preserve">    ,</v>
+        <v xml:space="preserve">    3.84949781513802, 3.74683177920429, 4.64200785792486, 10.2479765104253, 9.51453994136208,</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="99" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="101"/>
-      <c r="C13" s="102"/>
-      <c r="D13" s="102"/>
-      <c r="E13" s="102"/>
-      <c r="F13" s="102"/>
-      <c r="G13" s="102"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="99" t="s">
-        <v>23</v>
-      </c>
-      <c r="L13" s="101"/>
-      <c r="M13" s="102"/>
-      <c r="N13" s="102"/>
-      <c r="O13" s="102"/>
-      <c r="P13" s="102"/>
-      <c r="Q13" s="102"/>
-      <c r="R13" s="12"/>
+      <c r="A13" s="94" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="95"/>
+      <c r="C13" s="128">
+        <v>93.005297046975599</v>
+      </c>
+      <c r="D13" s="124">
+        <v>91.902444369472647</v>
+      </c>
+      <c r="E13" s="124">
+        <v>89.116278399178753</v>
+      </c>
+      <c r="F13" s="124">
+        <v>72.258814234263852</v>
+      </c>
+      <c r="G13" s="129">
+        <v>53.843628981796257</v>
+      </c>
+      <c r="H13" s="34" cm="1">
+        <f t="array" ref="H13">-SUMPRODUCT((D1:F1-C1:E1)*(C13:E13+D13:F13)/2)</f>
+        <v>78.940218989783645</v>
+      </c>
+      <c r="I13" s="34" cm="1">
+        <f t="array" ref="I13">-SUMPRODUCT((D1:G1-C1:F1)*(C13:F13+D13:G13)/2)</f>
+        <v>82.880920340285527</v>
+      </c>
+      <c r="J13" s="12" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C13:G13)&amp;","</f>
+        <v xml:space="preserve">    93.0052970469756, 91.9024443694726, 89.1162783991788, 72.2588142342639, 53.8436289817963,</v>
+      </c>
+      <c r="K13" s="94" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="95"/>
+      <c r="M13" s="128">
+        <v>3.458803648865628</v>
+      </c>
+      <c r="N13" s="124">
+        <v>4.1139178681351494</v>
+      </c>
+      <c r="O13" s="124">
+        <v>4.3674865362294497</v>
+      </c>
+      <c r="P13" s="124">
+        <v>10.1810612930344</v>
+      </c>
+      <c r="Q13" s="129">
+        <v>8.6745540222164905</v>
+      </c>
+      <c r="R13" s="12" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M13:Q13)&amp;","</f>
+        <v xml:space="preserve">    3.45880364886563, 4.11391786813515, 4.36748653622945, 10.1810612930344, 8.67455402221649,</v>
+      </c>
     </row>
     <row r="14" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="99" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="100"/>
-      <c r="C14">
-        <v>93.204569243678591</v>
-      </c>
-      <c r="D14">
-        <v>92.71893643831983</v>
-      </c>
-      <c r="E14">
-        <v>91.010196166633492</v>
-      </c>
-      <c r="F14">
-        <v>77.775612245780678</v>
-      </c>
-      <c r="G14">
-        <v>55.921856302101808</v>
-      </c>
+      <c r="A14" s="98" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="99"/>
+      <c r="C14" s="137"/>
+      <c r="D14" s="138"/>
+      <c r="E14" s="138"/>
+      <c r="F14" s="138"/>
+      <c r="G14" s="139"/>
       <c r="H14" s="34" cm="1">
         <f t="array" ref="H14">-SUMPRODUCT((D1:F1-C1:E1)*(C14:E14+D14:F14)/2)</f>
-        <v>79.996131021894655</v>
+        <v>0</v>
       </c>
       <c r="I14" s="34" cm="1">
         <f t="array" ref="I14">-SUMPRODUCT((D1:G1-C1:F1)*(C14:F14+D14:G14)/2)</f>
-        <v>84.174176914015987</v>
+        <v>0</v>
       </c>
       <c r="J14" s="12" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C14:G14)&amp;","</f>
-        <v xml:space="preserve">    93.2045692436786, 92.7189364383198, 91.0101961666335, 77.7756122457807, 55.9218563021018,</v>
-      </c>
-      <c r="K14" s="99" t="s">
-        <v>7</v>
-      </c>
-      <c r="L14" s="100"/>
-      <c r="M14">
-        <v>3.5338969773137729</v>
-      </c>
-      <c r="N14">
-        <v>3.7216965755259852</v>
-      </c>
-      <c r="O14">
-        <v>3.7478593835578962</v>
-      </c>
-      <c r="P14">
-        <v>6.7863547394302319</v>
-      </c>
-      <c r="Q14">
-        <v>8.2097242202983072</v>
-      </c>
+        <v xml:space="preserve">    ,</v>
+      </c>
+      <c r="K14" s="98" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" s="99"/>
+      <c r="M14" s="137"/>
+      <c r="N14" s="138"/>
+      <c r="O14" s="138"/>
+      <c r="P14" s="138"/>
+      <c r="Q14" s="139"/>
       <c r="R14" s="12" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M14:Q14)&amp;","</f>
-        <v xml:space="preserve">    3.53389697731377, 3.72169657552599, 3.7478593835579, 6.78635473943023, 8.20972422029831,</v>
+        <v xml:space="preserve">    ,</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="103" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="104"/>
-      <c r="C15">
-        <v>91.935155148400952</v>
-      </c>
-      <c r="D15">
-        <v>91.692255123314226</v>
-      </c>
-      <c r="E15">
-        <v>89.847648624411406</v>
-      </c>
-      <c r="F15">
-        <v>79.400747411309794</v>
-      </c>
-      <c r="G15">
-        <v>53.25364406266489</v>
-      </c>
-      <c r="H15" s="34" cm="1">
-        <f t="array" ref="H15">-SUMPRODUCT((D1:F1-C1:E1)*(C15:E15+D15:F15)/2)</f>
-        <v>79.177365288627072</v>
-      </c>
-      <c r="I15" s="34" cm="1">
-        <f t="array" ref="I15">-SUMPRODUCT((D1:G1-C1:F1)*(C15:F15+D15:G15)/2)</f>
-        <v>83.322815022188777</v>
-      </c>
-      <c r="J15" s="12" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C15:G15)&amp;","</f>
-        <v xml:space="preserve">    91.935155148401, 91.6922551233142, 89.8476486244114, 79.4007474113098, 53.2536440626649,</v>
-      </c>
-      <c r="K15" s="99" t="s">
-        <v>8</v>
-      </c>
-      <c r="L15" s="100"/>
-      <c r="M15">
-        <v>3.0404967647063641</v>
-      </c>
-      <c r="N15">
-        <v>3.2195663824364602</v>
-      </c>
-      <c r="O15">
-        <v>5.1059080333021827</v>
-      </c>
-      <c r="P15">
-        <v>3.323723681934811</v>
-      </c>
-      <c r="Q15">
-        <v>4.2607284397566696</v>
-      </c>
-      <c r="R15" s="12" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M15:Q15)&amp;","</f>
-        <v xml:space="preserve">    3.04049676470636, 3.21956638243646, 5.10590803330218, 3.32372368193481, 4.26072843975667,</v>
-      </c>
+      <c r="A15" s="94" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="96"/>
+      <c r="C15" s="96"/>
+      <c r="D15" s="96"/>
+      <c r="E15" s="96"/>
+      <c r="F15" s="96"/>
+      <c r="G15" s="95"/>
+      <c r="H15" s="34"/>
+      <c r="I15" s="34"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="94" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" s="96"/>
+      <c r="M15" s="96"/>
+      <c r="N15" s="96"/>
+      <c r="O15" s="96"/>
+      <c r="P15" s="96"/>
+      <c r="Q15" s="95"/>
+      <c r="R15" s="12"/>
     </row>
     <row r="16" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="99" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="100"/>
-      <c r="C16">
-        <v>93.32960781090955</v>
-      </c>
-      <c r="D16">
-        <v>92.627433339965464</v>
-      </c>
-      <c r="E16">
-        <v>90.919543710009009</v>
-      </c>
-      <c r="F16">
-        <v>77.743400317765136</v>
-      </c>
-      <c r="G16">
-        <v>58.391070280308071</v>
+      <c r="A16" s="111" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="143"/>
+      <c r="C16" s="128">
+        <v>93.204569243678591</v>
+      </c>
+      <c r="D16" s="124">
+        <v>92.71893643831983</v>
+      </c>
+      <c r="E16" s="124">
+        <v>91.010196166633492</v>
+      </c>
+      <c r="F16" s="124">
+        <v>77.775612245780678</v>
+      </c>
+      <c r="G16" s="129">
+        <v>55.921856302101808</v>
       </c>
       <c r="H16" s="34" cm="1">
         <f t="array" ref="H16">-SUMPRODUCT((D1:F1-C1:E1)*(C16:E16+D16:F16)/2)</f>
-        <v>79.974066420701448</v>
+        <v>79.996131021894655</v>
       </c>
       <c r="I16" s="34" cm="1">
         <f t="array" ref="I16">-SUMPRODUCT((D1:G1-C1:F1)*(C16:F16+D16:G16)/2)</f>
-        <v>84.228268626891236</v>
+        <v>84.174176914015987</v>
       </c>
       <c r="J16" s="12" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C16:G16)&amp;","</f>
-        <v xml:space="preserve">    93.3296078109096, 92.6274333399655, 90.919543710009, 77.7434003177651, 58.3910702803081,</v>
-      </c>
-      <c r="K16" s="99" t="s">
-        <v>21</v>
-      </c>
-      <c r="L16" s="100"/>
-      <c r="M16">
-        <v>3.3471189071482028</v>
-      </c>
-      <c r="N16">
-        <v>3.632082464261972</v>
-      </c>
-      <c r="O16">
-        <v>3.8019445786359811</v>
-      </c>
-      <c r="P16">
-        <v>7.5417080235248886</v>
-      </c>
-      <c r="Q16">
-        <v>8.4137702230121008</v>
+        <v xml:space="preserve">    93.2045692436786, 92.7189364383198, 91.0101961666335, 77.7756122457807, 55.9218563021018,</v>
+      </c>
+      <c r="K16" s="111" t="s">
+        <v>7</v>
+      </c>
+      <c r="L16" s="143"/>
+      <c r="M16" s="128">
+        <v>3.5338969773137729</v>
+      </c>
+      <c r="N16" s="124">
+        <v>3.7216965755259852</v>
+      </c>
+      <c r="O16" s="124">
+        <v>3.7478593835578962</v>
+      </c>
+      <c r="P16" s="124">
+        <v>6.7863547394302319</v>
+      </c>
+      <c r="Q16" s="129">
+        <v>8.2097242202983072</v>
       </c>
       <c r="R16" s="12" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M16:Q16)&amp;","</f>
-        <v xml:space="preserve">    3.3471189071482, 3.63208246426197, 3.80194457863598, 7.54170802352489, 8.4137702230121,</v>
+        <v xml:space="preserve">    3.53389697731377, 3.72169657552599, 3.7478593835579, 6.78635473943023, 8.20972422029831,</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="99" t="s">
-        <v>22</v>
-      </c>
-      <c r="B17" s="100"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="36"/>
+      <c r="A17" s="98" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="99"/>
+      <c r="C17" s="128">
+        <v>91.935155148400952</v>
+      </c>
+      <c r="D17" s="124">
+        <v>91.692255123314226</v>
+      </c>
+      <c r="E17" s="124">
+        <v>89.847648624411406</v>
+      </c>
+      <c r="F17" s="124">
+        <v>79.400747411309794</v>
+      </c>
+      <c r="G17" s="129">
+        <v>53.25364406266489</v>
+      </c>
       <c r="H17" s="34" cm="1">
         <f t="array" ref="H17">-SUMPRODUCT((D1:F1-C1:E1)*(C17:E17+D17:F17)/2)</f>
-        <v>0</v>
+        <v>79.177365288627072</v>
       </c>
       <c r="I17" s="34" cm="1">
         <f t="array" ref="I17">-SUMPRODUCT((D1:G1-C1:F1)*(C17:F17+D17:G17)/2)</f>
-        <v>0</v>
+        <v>83.322815022188777</v>
       </c>
       <c r="J17" s="12" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C17:G17)&amp;","</f>
-        <v xml:space="preserve">    ,</v>
-      </c>
-      <c r="K17" s="99" t="s">
-        <v>22</v>
-      </c>
-      <c r="L17" s="100"/>
-      <c r="M17" s="35"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="36"/>
-      <c r="P17" s="36"/>
-      <c r="Q17" s="36"/>
+        <v xml:space="preserve">    91.935155148401, 91.6922551233142, 89.8476486244114, 79.4007474113098, 53.2536440626649,</v>
+      </c>
+      <c r="K17" s="94" t="s">
+        <v>8</v>
+      </c>
+      <c r="L17" s="95"/>
+      <c r="M17" s="128">
+        <v>3.0404967647063641</v>
+      </c>
+      <c r="N17" s="124">
+        <v>3.2195663824364602</v>
+      </c>
+      <c r="O17" s="124">
+        <v>5.1059080333021827</v>
+      </c>
+      <c r="P17" s="124">
+        <v>3.323723681934811</v>
+      </c>
+      <c r="Q17" s="129">
+        <v>4.2607284397566696</v>
+      </c>
       <c r="R17" s="12" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M17:Q17)&amp;","</f>
-        <v xml:space="preserve">    ,</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="25"/>
-      <c r="B18" s="25"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="25"/>
-      <c r="H18" s="25"/>
-      <c r="I18" s="25"/>
-      <c r="K18" s="25"/>
-      <c r="L18" s="25"/>
-      <c r="M18" s="25"/>
-      <c r="N18" s="25"/>
-      <c r="O18" s="25"/>
-      <c r="P18" s="25"/>
-      <c r="Q18" s="25"/>
-    </row>
-    <row r="19" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+        <v xml:space="preserve">    3.04049676470636, 3.21956638243646, 5.10590803330218, 3.32372368193481, 4.26072843975667,</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="94" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="95"/>
+      <c r="C18" s="128">
+        <v>93.32960781090955</v>
+      </c>
+      <c r="D18" s="124">
+        <v>92.627433339965464</v>
+      </c>
+      <c r="E18" s="124">
+        <v>90.919543710009009</v>
+      </c>
+      <c r="F18" s="124">
+        <v>77.743400317765136</v>
+      </c>
+      <c r="G18" s="129">
+        <v>58.391070280308071</v>
+      </c>
+      <c r="H18" s="34" cm="1">
+        <f t="array" ref="H18">-SUMPRODUCT((D1:F1-C1:E1)*(C18:E18+D18:F18)/2)</f>
+        <v>79.974066420701448</v>
+      </c>
+      <c r="I18" s="34" cm="1">
+        <f t="array" ref="I18">-SUMPRODUCT((D1:G1-C1:F1)*(C18:F18+D18:G18)/2)</f>
+        <v>84.228268626891236</v>
+      </c>
+      <c r="J18" s="12" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C18:G18)&amp;","</f>
+        <v xml:space="preserve">    93.3296078109096, 92.6274333399655, 90.919543710009, 77.7434003177651, 58.3910702803081,</v>
+      </c>
+      <c r="K18" s="94" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="95"/>
+      <c r="M18" s="128">
+        <v>3.3471189071482028</v>
+      </c>
+      <c r="N18" s="124">
+        <v>3.632082464261972</v>
+      </c>
+      <c r="O18" s="124">
+        <v>3.8019445786359811</v>
+      </c>
+      <c r="P18" s="124">
+        <v>7.5417080235248886</v>
+      </c>
+      <c r="Q18" s="129">
+        <v>8.4137702230121008</v>
+      </c>
+      <c r="R18" s="12" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M18:Q18)&amp;","</f>
+        <v xml:space="preserve">    3.3471189071482, 3.63208246426197, 3.80194457863598, 7.54170802352489, 8.4137702230121,</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="94" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="95"/>
+      <c r="C19" s="35"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="133"/>
+      <c r="H19" s="34" cm="1">
+        <f t="array" ref="H19">-SUMPRODUCT((D1:F1-C1:E1)*(C19:E19+D19:F19)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="34" cm="1">
+        <f t="array" ref="I19">-SUMPRODUCT((D1:G1-C1:F1)*(C19:F19+D19:G19)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="12" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C19:G19)&amp;","</f>
+        <v xml:space="preserve">    ,</v>
+      </c>
+      <c r="K19" s="94" t="s">
+        <v>22</v>
+      </c>
+      <c r="L19" s="95"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="133"/>
+      <c r="R19" s="12" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M19:Q19)&amp;","</f>
+        <v xml:space="preserve">    ,</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="25"/>
+      <c r="B20" s="25"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
+      <c r="M20" s="25"/>
+      <c r="N20" s="25"/>
+      <c r="O20" s="25"/>
+      <c r="P20" s="25"/>
+      <c r="Q20" s="25"/>
+    </row>
+    <row r="21" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B21" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C21" s="14">
         <v>1</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D21" s="16">
         <v>0.5</v>
       </c>
-      <c r="E19" s="15">
+      <c r="E21" s="16">
         <v>0.25</v>
       </c>
-      <c r="F19" s="15">
+      <c r="F21" s="16">
         <v>0.125</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G21" s="2">
         <v>6.25E-2</v>
       </c>
-      <c r="H19" s="19"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="4" t="s">
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L19" s="5" t="s">
+      <c r="L21" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="M19" s="4">
+      <c r="M21" s="14">
         <v>1</v>
       </c>
-      <c r="N19" s="15">
+      <c r="N21" s="16">
         <v>0.5</v>
       </c>
-      <c r="O19" s="15">
+      <c r="O21" s="16">
         <v>0.25</v>
       </c>
-      <c r="P19" s="15">
+      <c r="P21" s="16">
         <v>0.125</v>
       </c>
-      <c r="Q19" s="5">
+      <c r="Q21" s="2">
         <v>6.25E-2</v>
       </c>
-      <c r="R19" s="1"/>
-    </row>
-    <row r="20" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="92" t="s">
+      <c r="R21" s="1"/>
+    </row>
+    <row r="22" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="93"/>
-      <c r="C20">
+      <c r="B22" s="103"/>
+      <c r="C22" s="125">
         <v>92.485449200300948</v>
       </c>
-      <c r="D20">
+      <c r="D22" s="126">
         <v>92.185357970009463</v>
       </c>
-      <c r="E20">
+      <c r="E22" s="126">
         <v>90.049361274020285</v>
       </c>
-      <c r="F20">
+      <c r="F22" s="126">
         <v>76.424179894802663</v>
       </c>
-      <c r="G20">
+      <c r="G22" s="127">
         <v>55.817166373785298</v>
-      </c>
-      <c r="H20" s="40"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C20:G20)&amp;","</f>
-        <v xml:space="preserve">    92.4854492003009, 92.1853579700095, 90.0493612740203, 76.4241798948027, 55.8171663737853,</v>
-      </c>
-      <c r="K20" s="92" t="s">
-        <v>5</v>
-      </c>
-      <c r="L20" s="93"/>
-      <c r="M20">
-        <v>4.0542209595909764</v>
-      </c>
-      <c r="N20">
-        <v>4.1862833242412467</v>
-      </c>
-      <c r="O20">
-        <v>4.5232246954320994</v>
-      </c>
-      <c r="P20">
-        <v>8.3692490038067824</v>
-      </c>
-      <c r="Q20">
-        <v>9.4522568492704835</v>
-      </c>
-      <c r="R20" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M20:Q20)&amp;","</f>
-        <v xml:space="preserve">    4.05422095959098, 4.18628332424125, 4.5232246954321, 8.36924900380678, 9.45225684927048,</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="92" t="s">
-        <v>6</v>
-      </c>
-      <c r="B21" s="93"/>
-      <c r="C21">
-        <v>93.221737995090834</v>
-      </c>
-      <c r="D21">
-        <v>91.888033005684576</v>
-      </c>
-      <c r="E21">
-        <v>90.02393898401543</v>
-      </c>
-      <c r="F21">
-        <v>72.290420081448175</v>
-      </c>
-      <c r="G21">
-        <v>51.841305264174281</v>
-      </c>
-      <c r="H21" s="40"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:G21)&amp;","</f>
-        <v xml:space="preserve">    93.2217379950908, 91.8880330056846, 90.0239389840154, 72.2904200814482, 51.8413052641743,</v>
-      </c>
-      <c r="K21" s="92" t="s">
-        <v>6</v>
-      </c>
-      <c r="L21" s="93"/>
-      <c r="M21">
-        <v>3.877808098377264</v>
-      </c>
-      <c r="N21">
-        <v>3.9588226549458381</v>
-      </c>
-      <c r="O21">
-        <v>3.8583306594917439</v>
-      </c>
-      <c r="P21">
-        <v>9.3469718907111154</v>
-      </c>
-      <c r="Q21">
-        <v>8.4900588367667034</v>
-      </c>
-      <c r="R21" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M21:Q21)&amp;","</f>
-        <v xml:space="preserve">    3.87780809837726, 3.95882265494584, 3.85833065949174, 9.34697189071112, 8.4900588367667,</v>
-      </c>
-    </row>
-    <row r="22" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="92" t="s">
-        <v>10</v>
-      </c>
-      <c r="B22" s="93"/>
-      <c r="C22">
-        <v>88.242190127710941</v>
-      </c>
-      <c r="D22">
-        <v>87.235659245723795</v>
-      </c>
-      <c r="E22">
-        <v>86.840356363138071</v>
-      </c>
-      <c r="F22">
-        <v>74.54100008231579</v>
-      </c>
-      <c r="G22">
-        <v>48.979529992306112</v>
       </c>
       <c r="H22" s="40"/>
       <c r="I22" s="40"/>
       <c r="J22" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C22:G22)&amp;","</f>
-        <v xml:space="preserve">    88.2421901277109, 87.2356592457238, 86.8403563631381, 74.5410000823158, 48.9795299923061,</v>
-      </c>
-      <c r="K22" s="92" t="s">
-        <v>10</v>
-      </c>
-      <c r="L22" s="93"/>
-      <c r="M22">
-        <v>3.345739818904093</v>
-      </c>
-      <c r="N22">
-        <v>2.427737239251389</v>
-      </c>
-      <c r="O22">
-        <v>1.707344435820553</v>
-      </c>
-      <c r="P22">
-        <v>2.910710341880129</v>
-      </c>
-      <c r="Q22">
-        <v>2.034771708486713</v>
+        <v xml:space="preserve">    92.4854492003009, 92.1853579700095, 90.0493612740203, 76.4241798948027, 55.8171663737853,</v>
+      </c>
+      <c r="K22" s="101" t="s">
+        <v>5</v>
+      </c>
+      <c r="L22" s="103"/>
+      <c r="M22" s="125">
+        <v>4.0542209595909764</v>
+      </c>
+      <c r="N22" s="126">
+        <v>4.1862833242412467</v>
+      </c>
+      <c r="O22" s="126">
+        <v>4.5232246954320994</v>
+      </c>
+      <c r="P22" s="126">
+        <v>8.3692490038067824</v>
+      </c>
+      <c r="Q22" s="127">
+        <v>9.4522568492704835</v>
       </c>
       <c r="R22" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M22:Q22)&amp;","</f>
-        <v xml:space="preserve">    3.34573981890409, 2.42773723925139, 1.70734443582055, 2.91071034188013, 2.03477170848671,</v>
+        <v xml:space="preserve">    4.05422095959098, 4.18628332424125, 4.5232246954321, 8.36924900380678, 9.45225684927048,</v>
       </c>
     </row>
     <row r="23" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="92" t="s">
-        <v>12</v>
-      </c>
-      <c r="B23" s="96"/>
-      <c r="C23" s="96"/>
-      <c r="D23" s="96"/>
-      <c r="E23" s="96"/>
-      <c r="F23" s="96"/>
-      <c r="G23" s="96"/>
+      <c r="A23" s="101" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="103"/>
+      <c r="C23" s="128">
+        <v>93.221737995090834</v>
+      </c>
+      <c r="D23" s="124">
+        <v>91.888033005684576</v>
+      </c>
+      <c r="E23" s="124">
+        <v>90.02393898401543</v>
+      </c>
+      <c r="F23" s="124">
+        <v>72.290420081448175</v>
+      </c>
+      <c r="G23" s="129">
+        <v>51.841305264174281</v>
+      </c>
       <c r="H23" s="40"/>
       <c r="I23" s="40"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="92" t="s">
-        <v>12</v>
-      </c>
-      <c r="L23" s="96"/>
-      <c r="M23" s="96"/>
-      <c r="N23" s="96"/>
-      <c r="O23" s="96"/>
-      <c r="P23" s="96"/>
-      <c r="Q23" s="96"/>
-      <c r="R23" s="1"/>
+      <c r="J23" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C23:G23)&amp;","</f>
+        <v xml:space="preserve">    93.2217379950908, 91.8880330056846, 90.0239389840154, 72.2904200814482, 51.8413052641743,</v>
+      </c>
+      <c r="K23" s="101" t="s">
+        <v>6</v>
+      </c>
+      <c r="L23" s="103"/>
+      <c r="M23" s="128">
+        <v>3.877808098377264</v>
+      </c>
+      <c r="N23" s="124">
+        <v>3.9588226549458381</v>
+      </c>
+      <c r="O23" s="124">
+        <v>3.8583306594917439</v>
+      </c>
+      <c r="P23" s="124">
+        <v>9.3469718907111154</v>
+      </c>
+      <c r="Q23" s="129">
+        <v>8.4900588367667034</v>
+      </c>
+      <c r="R23" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M23:Q23)&amp;","</f>
+        <v xml:space="preserve">    3.87780809837726, 3.95882265494584, 3.85833065949174, 9.34697189071112, 8.4900588367667,</v>
+      </c>
     </row>
     <row r="24" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="C24">
-        <v>92.884757186814937</v>
-      </c>
-      <c r="D24">
-        <v>92.335436215459112</v>
-      </c>
-      <c r="E24">
-        <v>90.9231205519105</v>
-      </c>
-      <c r="F24">
-        <v>76.864790806262661</v>
-      </c>
-      <c r="G24">
-        <v>54.700390036572337</v>
+      <c r="A24" s="106" t="s">
+        <v>10</v>
+      </c>
+      <c r="B24" s="104"/>
+      <c r="C24" s="130">
+        <v>88.242190127710941</v>
+      </c>
+      <c r="D24" s="131">
+        <v>87.235659245723795</v>
+      </c>
+      <c r="E24" s="131">
+        <v>86.840356363138071</v>
+      </c>
+      <c r="F24" s="131">
+        <v>74.54100008231579</v>
+      </c>
+      <c r="G24" s="132">
+        <v>48.979529992306112</v>
       </c>
       <c r="H24" s="40"/>
       <c r="I24" s="40"/>
       <c r="J24" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C24:G24)&amp;","</f>
-        <v xml:space="preserve">    92.8847571868149, 92.3354362154591, 90.9231205519105, 76.8647908062627, 54.7003900365723,</v>
-      </c>
-      <c r="K24" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="L24" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="M24">
-        <v>3.9275095693540201</v>
-      </c>
-      <c r="N24">
-        <v>4.1004926648702904</v>
-      </c>
-      <c r="O24">
-        <v>3.731232057084795</v>
-      </c>
-      <c r="P24">
-        <v>7.9334375921235116</v>
-      </c>
-      <c r="Q24">
-        <v>9.3194201516218254</v>
+        <v xml:space="preserve">    88.2421901277109, 87.2356592457238, 86.8403563631381, 74.5410000823158, 48.9795299923061,</v>
+      </c>
+      <c r="K24" s="106" t="s">
+        <v>10</v>
+      </c>
+      <c r="L24" s="104"/>
+      <c r="M24" s="130">
+        <v>3.345739818904093</v>
+      </c>
+      <c r="N24" s="131">
+        <v>2.427737239251389</v>
+      </c>
+      <c r="O24" s="131">
+        <v>1.707344435820553</v>
+      </c>
+      <c r="P24" s="131">
+        <v>2.910710341880129</v>
+      </c>
+      <c r="Q24" s="132">
+        <v>2.034771708486713</v>
       </c>
       <c r="R24" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M24:Q24)&amp;","</f>
-        <v xml:space="preserve">    3.92750956935402, 4.10049266487029, 3.73123205708479, 7.93343759212351, 9.31942015162183,</v>
+        <v xml:space="preserve">    3.34573981890409, 2.42773723925139, 1.70734443582055, 2.91071034188013, 2.03477170848671,</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="59"/>
-      <c r="D25" s="60"/>
-      <c r="E25" s="60"/>
-      <c r="F25" s="60"/>
-      <c r="G25" s="60"/>
+      <c r="A25" s="101" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="103"/>
+      <c r="C25" s="103"/>
+      <c r="D25" s="103"/>
+      <c r="E25" s="103"/>
+      <c r="F25" s="103"/>
+      <c r="G25" s="102"/>
       <c r="H25" s="40"/>
       <c r="I25" s="40"/>
-      <c r="J25" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C25:G25)&amp;","</f>
-        <v xml:space="preserve">    ,</v>
-      </c>
-      <c r="K25" s="14" t="s">
+      <c r="J25" s="1"/>
+      <c r="K25" s="101" t="s">
+        <v>12</v>
+      </c>
+      <c r="L25" s="103"/>
+      <c r="M25" s="103"/>
+      <c r="N25" s="103"/>
+      <c r="O25" s="103"/>
+      <c r="P25" s="103"/>
+      <c r="Q25" s="102"/>
+      <c r="R25" s="1"/>
+    </row>
+    <row r="26" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="93" t="s">
         <v>11</v>
       </c>
-      <c r="L25" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="M25" s="59"/>
-      <c r="N25" s="60"/>
-      <c r="O25" s="60"/>
-      <c r="P25" s="60"/>
-      <c r="Q25" s="60"/>
-      <c r="R25" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M25:Q25)&amp;","</f>
-        <v xml:space="preserve">    ,</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="92" t="s">
-        <v>20</v>
-      </c>
-      <c r="B26" s="96"/>
-      <c r="C26" s="98"/>
-      <c r="D26" s="98"/>
-      <c r="E26" s="98"/>
-      <c r="F26" s="98"/>
-      <c r="G26" s="98"/>
+      <c r="B26" s="142" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="125">
+        <v>92.884757186814937</v>
+      </c>
+      <c r="D26" s="126">
+        <v>92.335436215459112</v>
+      </c>
+      <c r="E26" s="126">
+        <v>90.9231205519105</v>
+      </c>
+      <c r="F26" s="126">
+        <v>76.864790806262661</v>
+      </c>
+      <c r="G26" s="127">
+        <v>54.700390036572337</v>
+      </c>
       <c r="H26" s="40"/>
       <c r="I26" s="40"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="92" t="s">
-        <v>20</v>
-      </c>
-      <c r="L26" s="96"/>
-      <c r="M26" s="98"/>
-      <c r="N26" s="98"/>
-      <c r="O26" s="98"/>
-      <c r="P26" s="98"/>
-      <c r="Q26" s="98"/>
-      <c r="R26" s="1"/>
-    </row>
-    <row r="27" spans="1:18" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="92" t="s">
-        <v>7</v>
-      </c>
-      <c r="B27" s="93"/>
-      <c r="C27">
-        <v>92.781043798288394</v>
-      </c>
-      <c r="D27">
-        <v>92.393805655393209</v>
-      </c>
-      <c r="E27">
-        <v>90.00908396624763</v>
-      </c>
-      <c r="F27">
-        <v>72.498171965203667</v>
-      </c>
-      <c r="G27">
-        <v>56.674852997991948</v>
+      <c r="J26" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C26:G26)&amp;","</f>
+        <v xml:space="preserve">    92.8847571868149, 92.3354362154591, 90.9231205519105, 76.8647908062627, 54.7003900365723,</v>
+      </c>
+      <c r="K26" s="93" t="s">
+        <v>11</v>
+      </c>
+      <c r="L26" s="142" t="s">
+        <v>13</v>
+      </c>
+      <c r="M26" s="125">
+        <v>3.9275095693540201</v>
+      </c>
+      <c r="N26" s="126">
+        <v>4.1004926648702904</v>
+      </c>
+      <c r="O26" s="126">
+        <v>3.731232057084795</v>
+      </c>
+      <c r="P26" s="126">
+        <v>7.9334375921235116</v>
+      </c>
+      <c r="Q26" s="127">
+        <v>9.3194201516218254</v>
+      </c>
+      <c r="R26" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M26:Q26)&amp;","</f>
+        <v xml:space="preserve">    3.92750956935402, 4.10049266487029, 3.73123205708479, 7.93343759212351, 9.31942015162183,</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27" s="122" t="s">
+        <v>14</v>
+      </c>
+      <c r="C27" s="128">
+        <v>92.328683900261311</v>
+      </c>
+      <c r="D27" s="124">
+        <v>92.052039116791605</v>
+      </c>
+      <c r="E27" s="124">
+        <v>90.722946775710213</v>
+      </c>
+      <c r="F27" s="124">
+        <v>81.998727124399025</v>
+      </c>
+      <c r="G27" s="129">
+        <v>56.932651064742558</v>
       </c>
       <c r="H27" s="40"/>
       <c r="I27" s="40"/>
       <c r="J27" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C27:G27)&amp;","</f>
-        <v xml:space="preserve">    92.7810437982884, 92.3938056553932, 90.0090839662476, 72.4981719652037, 56.6748529979919,</v>
-      </c>
-      <c r="K27" s="92" t="s">
-        <v>7</v>
-      </c>
-      <c r="L27" s="93"/>
-      <c r="M27">
-        <v>4.5014366094349993</v>
-      </c>
-      <c r="N27">
-        <v>4.2660991290099446</v>
-      </c>
-      <c r="O27">
-        <v>4.2894182874628113</v>
-      </c>
-      <c r="P27">
-        <v>9.3344724861133059</v>
-      </c>
-      <c r="Q27">
-        <v>9.7546209717543917</v>
+        <v xml:space="preserve">    92.3286839002613, 92.0520391167916, 90.7229467757102, 81.998727124399, 56.9326510647426,</v>
+      </c>
+      <c r="K27" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="L27" s="122" t="s">
+        <v>14</v>
+      </c>
+      <c r="M27" s="128">
+        <v>3.6425445085490389</v>
+      </c>
+      <c r="N27" s="124">
+        <v>3.5031960343483388</v>
+      </c>
+      <c r="O27" s="124">
+        <v>3.28867394504752</v>
+      </c>
+      <c r="P27" s="124">
+        <v>4.6860855472410874</v>
+      </c>
+      <c r="Q27" s="129">
+        <v>6.5118967468904154</v>
       </c>
       <c r="R27" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M27:Q27)&amp;","</f>
-        <v xml:space="preserve">    4.501436609435, 4.26609912900994, 4.28941828746281, 9.33447248611331, 9.75462097175439,</v>
+        <v xml:space="preserve">    3.64254450854904, 3.50319603434834, 3.28867394504752, 4.68608554724109, 6.51189674689042,</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="92" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" s="93"/>
-      <c r="C28">
-        <v>93.113144022293241</v>
-      </c>
-      <c r="D28">
-        <v>91.949604112069864</v>
-      </c>
-      <c r="E28">
-        <v>88.043149271791009</v>
-      </c>
-      <c r="F28">
-        <v>70.437814383158539</v>
-      </c>
-      <c r="G28">
-        <v>50.027165788274679</v>
+      <c r="A28" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="122" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="128">
+        <v>93.17956577363725</v>
+      </c>
+      <c r="D28" s="124">
+        <v>92.311564351892216</v>
+      </c>
+      <c r="E28" s="124">
+        <v>90.442696954145944</v>
+      </c>
+      <c r="F28" s="124">
+        <v>73.029683164461161</v>
+      </c>
+      <c r="G28" s="129">
+        <v>54.393186167944343</v>
       </c>
       <c r="H28" s="40"/>
       <c r="I28" s="40"/>
-      <c r="J28" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C28:G28)&amp;","</f>
-        <v xml:space="preserve">    93.1131440222932, 91.9496041120699, 88.043149271791, 70.4378143831585, 50.0271657882747,</v>
-      </c>
-      <c r="K28" s="92" t="s">
-        <v>8</v>
-      </c>
-      <c r="L28" s="93"/>
-      <c r="M28">
-        <v>4.249709534316878</v>
-      </c>
-      <c r="N28">
-        <v>4.0308606644498308</v>
-      </c>
-      <c r="O28">
-        <v>4.9865974054077986</v>
-      </c>
-      <c r="P28">
-        <v>10.497443911766959</v>
-      </c>
-      <c r="Q28">
-        <v>10.803449952087821</v>
-      </c>
-      <c r="R28" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M28:Q28)&amp;","</f>
-        <v xml:space="preserve">    4.24970953431688, 4.03086066444983, 4.9865974054078, 10.497443911767, 10.8034499520878,</v>
-      </c>
+      <c r="J28" s="1"/>
+      <c r="K28" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="L28" s="122" t="s">
+        <v>18</v>
+      </c>
+      <c r="M28" s="128">
+        <v>3.743131605295734</v>
+      </c>
+      <c r="N28" s="124">
+        <v>4.0679999153192643</v>
+      </c>
+      <c r="O28" s="124">
+        <v>4.2835813429220631</v>
+      </c>
+      <c r="P28" s="124">
+        <v>9.1240722898599991</v>
+      </c>
+      <c r="Q28" s="129">
+        <v>8.7084512165137298</v>
+      </c>
+      <c r="R28" s="1"/>
     </row>
     <row r="29" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="92" t="s">
-        <v>21</v>
-      </c>
-      <c r="B29" s="93"/>
-      <c r="C29">
-        <v>92.587964837227005</v>
-      </c>
-      <c r="D29">
-        <v>91.423582441600061</v>
-      </c>
-      <c r="E29">
-        <v>88.545464929422721</v>
-      </c>
-      <c r="F29">
-        <v>71.659800595038618</v>
-      </c>
-      <c r="G29">
-        <v>50.266469026560699</v>
+      <c r="A29" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" s="122" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" s="130">
+        <v>90.264167794210408</v>
+      </c>
+      <c r="D29" s="131">
+        <v>89.992256751037203</v>
+      </c>
+      <c r="E29" s="131">
+        <v>89.343495694119156</v>
+      </c>
+      <c r="F29" s="131">
+        <v>78.329165755951735</v>
+      </c>
+      <c r="G29" s="132">
+        <v>52.215737786802968</v>
       </c>
       <c r="H29" s="40"/>
       <c r="I29" s="40"/>
-      <c r="J29" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C29:G29)&amp;","</f>
-        <v xml:space="preserve">    92.587964837227, 91.4235824416001, 88.5454649294227, 71.6598005950386, 50.2664690265607,</v>
-      </c>
-      <c r="K29" s="92" t="s">
-        <v>21</v>
-      </c>
-      <c r="L29" s="93"/>
-      <c r="M29">
-        <v>3.7645606938355249</v>
-      </c>
-      <c r="N29">
-        <v>4.4885904163036674</v>
-      </c>
-      <c r="O29">
-        <v>4.6842035667864703</v>
-      </c>
-      <c r="P29">
-        <v>10.46873255591585</v>
-      </c>
-      <c r="Q29">
-        <v>9.9892548989807413</v>
-      </c>
-      <c r="R29" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M29:Q29)&amp;","</f>
-        <v xml:space="preserve">    3.76456069383552, 4.48859041630367, 4.68420356678647, 10.4687325559158, 9.98925489898074,</v>
-      </c>
+      <c r="J29" s="1"/>
+      <c r="K29" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="L29" s="136" t="s">
+        <v>19</v>
+      </c>
+      <c r="M29" s="130">
+        <v>2.813777787794177</v>
+      </c>
+      <c r="N29" s="131">
+        <v>2.515073286885404</v>
+      </c>
+      <c r="O29" s="131">
+        <v>2.61246052058309</v>
+      </c>
+      <c r="P29" s="131">
+        <v>3.988565827203912</v>
+      </c>
+      <c r="Q29" s="132">
+        <v>3.7859616126423878</v>
+      </c>
+      <c r="R29" s="1"/>
     </row>
     <row r="30" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="92" t="s">
-        <v>22</v>
-      </c>
-      <c r="B30" s="93"/>
-      <c r="C30" s="41"/>
-      <c r="D30" s="42"/>
-      <c r="E30" s="42"/>
-      <c r="F30" s="42"/>
-      <c r="G30" s="42"/>
-      <c r="H30" s="45"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C30:G30)&amp;","</f>
-        <v xml:space="preserve">    ,</v>
-      </c>
-      <c r="K30" s="92" t="s">
-        <v>22</v>
-      </c>
-      <c r="L30" s="93"/>
-      <c r="M30" s="41"/>
-      <c r="N30" s="42"/>
-      <c r="O30" s="42"/>
-      <c r="P30" s="42"/>
-      <c r="Q30" s="42"/>
-      <c r="R30" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M30:Q30)&amp;","</f>
-        <v xml:space="preserve">    ,</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="92" t="s">
-        <v>23</v>
-      </c>
-      <c r="B31" s="96"/>
-      <c r="C31" s="97"/>
-      <c r="D31" s="97"/>
-      <c r="E31" s="97"/>
-      <c r="F31" s="97"/>
-      <c r="G31" s="97"/>
+      <c r="A30" s="101" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30" s="103"/>
+      <c r="C30" s="123"/>
+      <c r="D30" s="123"/>
+      <c r="E30" s="123"/>
+      <c r="F30" s="123"/>
+      <c r="G30" s="123"/>
+      <c r="H30" s="40"/>
+      <c r="I30" s="40"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="101" t="s">
+        <v>20</v>
+      </c>
+      <c r="L30" s="103"/>
+      <c r="M30" s="103"/>
+      <c r="N30" s="103"/>
+      <c r="O30" s="103"/>
+      <c r="P30" s="103"/>
+      <c r="Q30" s="102"/>
+      <c r="R30" s="1"/>
+    </row>
+    <row r="31" spans="1:18" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="101" t="s">
+        <v>7</v>
+      </c>
+      <c r="B31" s="103"/>
+      <c r="C31" s="125">
+        <v>92.781043798288394</v>
+      </c>
+      <c r="D31" s="126">
+        <v>92.393805655393209</v>
+      </c>
+      <c r="E31" s="126">
+        <v>90.00908396624763</v>
+      </c>
+      <c r="F31" s="126">
+        <v>72.498171965203667</v>
+      </c>
+      <c r="G31" s="127">
+        <v>56.674852997991948</v>
+      </c>
       <c r="H31" s="40"/>
       <c r="I31" s="40"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="92" t="s">
-        <v>23</v>
-      </c>
-      <c r="L31" s="96"/>
-      <c r="M31" s="97"/>
-      <c r="N31" s="97"/>
-      <c r="O31" s="97"/>
-      <c r="P31" s="97"/>
-      <c r="Q31" s="97"/>
-      <c r="R31" s="1"/>
-    </row>
-    <row r="32" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="92" t="s">
+      <c r="J31" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C31:G31)&amp;","</f>
+        <v xml:space="preserve">    92.7810437982884, 92.3938056553932, 90.0090839662476, 72.4981719652037, 56.6748529979919,</v>
+      </c>
+      <c r="K31" s="113" t="s">
         <v>7</v>
       </c>
-      <c r="B32" s="93"/>
-      <c r="C32">
-        <v>92.779242983398433</v>
-      </c>
-      <c r="D32">
-        <v>92.240270194904923</v>
-      </c>
-      <c r="E32">
-        <v>90.552301433559194</v>
-      </c>
-      <c r="F32">
-        <v>77.44681530627544</v>
-      </c>
-      <c r="G32">
-        <v>54.049481297537007</v>
+      <c r="L31" s="141"/>
+      <c r="M31" s="125">
+        <v>4.5014366094349993</v>
+      </c>
+      <c r="N31" s="126">
+        <v>4.2660991290099446</v>
+      </c>
+      <c r="O31" s="126">
+        <v>4.2894182874628113</v>
+      </c>
+      <c r="P31" s="126">
+        <v>9.3344724861133059</v>
+      </c>
+      <c r="Q31" s="127">
+        <v>9.7546209717543917</v>
+      </c>
+      <c r="R31" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M31:Q31)&amp;","</f>
+        <v xml:space="preserve">    4.501436609435, 4.26609912900994, 4.28941828746281, 9.33447248611331, 9.75462097175439,</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="101" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" s="103"/>
+      <c r="C32" s="128">
+        <v>93.113144022293241</v>
+      </c>
+      <c r="D32" s="124">
+        <v>91.949604112069864</v>
+      </c>
+      <c r="E32" s="124">
+        <v>88.043149271791009</v>
+      </c>
+      <c r="F32" s="124">
+        <v>70.437814383158539</v>
+      </c>
+      <c r="G32" s="129">
+        <v>50.027165788274679</v>
       </c>
       <c r="H32" s="40"/>
       <c r="I32" s="40"/>
       <c r="J32" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C32:G32)&amp;","</f>
-        <v xml:space="preserve">    92.7792429833984, 92.2402701949049, 90.5523014335592, 77.4468153062754, 54.049481297537,</v>
-      </c>
-      <c r="K32" s="92" t="s">
-        <v>7</v>
-      </c>
-      <c r="L32" s="93"/>
-      <c r="M32">
-        <v>3.8708284466838099</v>
-      </c>
-      <c r="N32">
-        <v>4.1159624538095514</v>
-      </c>
-      <c r="O32">
-        <v>4.0917292690559766</v>
-      </c>
-      <c r="P32">
-        <v>6.9723184162377478</v>
-      </c>
-      <c r="Q32">
-        <v>8.876523191689154</v>
+        <v xml:space="preserve">    93.1131440222932, 91.9496041120699, 88.043149271791, 70.4378143831585, 50.0271657882747,</v>
+      </c>
+      <c r="K32" s="101" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="103"/>
+      <c r="M32" s="128">
+        <v>4.249709534316878</v>
+      </c>
+      <c r="N32" s="124">
+        <v>4.0308606644498308</v>
+      </c>
+      <c r="O32" s="124">
+        <v>4.9865974054077986</v>
+      </c>
+      <c r="P32" s="124">
+        <v>10.497443911766959</v>
+      </c>
+      <c r="Q32" s="129">
+        <v>10.803449952087821</v>
       </c>
       <c r="R32" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M32:Q32)&amp;","</f>
-        <v xml:space="preserve">    3.87082844668381, 4.11596245380955, 4.09172926905598, 6.97231841623775, 8.87652319168915,</v>
-      </c>
-    </row>
-    <row r="33" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="94" t="s">
-        <v>8</v>
-      </c>
-      <c r="B33" s="95"/>
-      <c r="C33">
-        <v>91.529115829853595</v>
-      </c>
-      <c r="D33">
-        <v>91.350643423322225</v>
-      </c>
-      <c r="E33">
-        <v>89.341760932799787</v>
-      </c>
-      <c r="F33">
-        <v>79.045051998788765</v>
-      </c>
-      <c r="G33">
-        <v>52.319711731697872</v>
+        <v xml:space="preserve">    4.24970953431688, 4.03086066444983, 4.9865974054078, 10.497443911767, 10.8034499520878,</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="101" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33" s="103"/>
+      <c r="C33" s="130">
+        <v>92.587964837227005</v>
+      </c>
+      <c r="D33" s="131">
+        <v>91.423582441600061</v>
+      </c>
+      <c r="E33" s="131">
+        <v>88.545464929422721</v>
+      </c>
+      <c r="F33" s="131">
+        <v>71.659800595038618</v>
+      </c>
+      <c r="G33" s="132">
+        <v>50.266469026560699</v>
       </c>
       <c r="H33" s="40"/>
       <c r="I33" s="40"/>
       <c r="J33" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C33:G33)&amp;","</f>
-        <v xml:space="preserve">    91.5291158298536, 91.3506434233222, 89.3417609327998, 79.0450519987888, 52.3197117316979,</v>
-      </c>
-      <c r="K33" s="92" t="s">
-        <v>8</v>
-      </c>
-      <c r="L33" s="93"/>
-      <c r="M33">
-        <v>3.326792742141544</v>
-      </c>
-      <c r="N33">
-        <v>3.370578982220036</v>
-      </c>
-      <c r="O33">
-        <v>5.5895882093977454</v>
-      </c>
-      <c r="P33">
-        <v>3.3906236766273481</v>
-      </c>
-      <c r="Q33">
-        <v>4.5139463885317248</v>
+        <v xml:space="preserve">    92.587964837227, 91.4235824416001, 88.5454649294227, 71.6598005950386, 50.2664690265607,</v>
+      </c>
+      <c r="K33" s="101" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" s="103"/>
+      <c r="M33" s="128">
+        <v>3.7645606938355249</v>
+      </c>
+      <c r="N33" s="124">
+        <v>4.4885904163036674</v>
+      </c>
+      <c r="O33" s="124">
+        <v>4.6842035667864703</v>
+      </c>
+      <c r="P33" s="124">
+        <v>10.46873255591585</v>
+      </c>
+      <c r="Q33" s="129">
+        <v>9.9892548989807413</v>
       </c>
       <c r="R33" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M33:Q33)&amp;","</f>
-        <v xml:space="preserve">    3.32679274214154, 3.37057898222004, 5.58958820939775, 3.39062367662735, 4.51394638853172,</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="92" t="s">
-        <v>21</v>
-      </c>
-      <c r="B34" s="93"/>
-      <c r="C34">
-        <v>92.904210456970588</v>
-      </c>
-      <c r="D34">
-        <v>92.1891124359732</v>
-      </c>
-      <c r="E34">
-        <v>90.496036698942376</v>
-      </c>
-      <c r="F34">
-        <v>77.336951327754974</v>
-      </c>
-      <c r="G34">
-        <v>56.222535937160863</v>
-      </c>
-      <c r="H34" s="40"/>
-      <c r="I34" s="40"/>
+        <v xml:space="preserve">    3.76456069383552, 4.48859041630367, 4.68420356678647, 10.4687325559158, 9.98925489898074,</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="106" t="s">
+        <v>22</v>
+      </c>
+      <c r="B34" s="107"/>
+      <c r="C34" s="134"/>
+      <c r="D34" s="135"/>
+      <c r="E34" s="135"/>
+      <c r="F34" s="135"/>
+      <c r="G34" s="135"/>
+      <c r="H34" s="45"/>
+      <c r="I34" s="45"/>
       <c r="J34" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C34:G34)&amp;","</f>
-        <v xml:space="preserve">    92.9042104569706, 92.1891124359732, 90.4960366989424, 77.336951327755, 56.2225359371609,</v>
-      </c>
-      <c r="K34" s="92" t="s">
-        <v>21</v>
-      </c>
-      <c r="L34" s="93"/>
-      <c r="M34">
-        <v>3.6016716439248402</v>
-      </c>
-      <c r="N34">
-        <v>3.9740552459554821</v>
-      </c>
-      <c r="O34">
-        <v>4.0466560589706821</v>
-      </c>
-      <c r="P34">
-        <v>7.6607457787732498</v>
-      </c>
-      <c r="Q34">
-        <v>9.1988486675501449</v>
-      </c>
+        <v xml:space="preserve">    ,</v>
+      </c>
+      <c r="K34" s="106" t="s">
+        <v>22</v>
+      </c>
+      <c r="L34" s="104"/>
+      <c r="M34" s="41"/>
+      <c r="N34" s="42"/>
+      <c r="O34" s="42"/>
+      <c r="P34" s="42"/>
+      <c r="Q34" s="145"/>
       <c r="R34" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M34:Q34)&amp;","</f>
-        <v xml:space="preserve">    3.60167164392484, 3.97405524595548, 4.04665605897068, 7.66074577877325, 9.19884866755014,</v>
+        <v xml:space="preserve">    ,</v>
       </c>
     </row>
     <row r="35" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="92" t="s">
-        <v>22</v>
-      </c>
-      <c r="B35" s="93"/>
-      <c r="C35" s="41"/>
-      <c r="D35" s="42"/>
-      <c r="E35" s="42"/>
-      <c r="F35" s="42"/>
-      <c r="G35" s="42"/>
+      <c r="A35" s="101" t="s">
+        <v>23</v>
+      </c>
+      <c r="B35" s="103"/>
+      <c r="C35" s="103"/>
+      <c r="D35" s="103"/>
+      <c r="E35" s="103"/>
+      <c r="F35" s="103"/>
+      <c r="G35" s="102"/>
       <c r="H35" s="40"/>
       <c r="I35" s="40"/>
-      <c r="J35" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C35:G35)&amp;","</f>
-        <v xml:space="preserve">    ,</v>
-      </c>
-      <c r="K35" s="92" t="s">
+      <c r="J35" s="1"/>
+      <c r="K35" s="101" t="s">
+        <v>23</v>
+      </c>
+      <c r="L35" s="103"/>
+      <c r="M35" s="103"/>
+      <c r="N35" s="103"/>
+      <c r="O35" s="103"/>
+      <c r="P35" s="103"/>
+      <c r="Q35" s="102"/>
+      <c r="R35" s="1"/>
+    </row>
+    <row r="36" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="113" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="141"/>
+      <c r="C36" s="125">
+        <v>92.779242983398433</v>
+      </c>
+      <c r="D36" s="126">
+        <v>92.240270194904923</v>
+      </c>
+      <c r="E36" s="126">
+        <v>90.552301433559194</v>
+      </c>
+      <c r="F36" s="126">
+        <v>77.44681530627544</v>
+      </c>
+      <c r="G36" s="127">
+        <v>54.049481297537007</v>
+      </c>
+      <c r="H36" s="40"/>
+      <c r="I36" s="40"/>
+      <c r="J36" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C36:G36)&amp;","</f>
+        <v xml:space="preserve">    92.7792429833984, 92.2402701949049, 90.5523014335592, 77.4468153062754, 54.049481297537,</v>
+      </c>
+      <c r="K36" s="113" t="s">
+        <v>7</v>
+      </c>
+      <c r="L36" s="141"/>
+      <c r="M36" s="125">
+        <v>3.8708284466838099</v>
+      </c>
+      <c r="N36" s="126">
+        <v>4.1159624538095514</v>
+      </c>
+      <c r="O36" s="126">
+        <v>4.0917292690559766</v>
+      </c>
+      <c r="P36" s="126">
+        <v>6.9723184162377478</v>
+      </c>
+      <c r="Q36" s="127">
+        <v>8.876523191689154</v>
+      </c>
+      <c r="R36" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M36:Q36)&amp;","</f>
+        <v xml:space="preserve">    3.87082844668381, 4.11596245380955, 4.09172926905598, 6.97231841623775, 8.87652319168915,</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="106" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" s="104"/>
+      <c r="C37" s="128">
+        <v>91.529115829853595</v>
+      </c>
+      <c r="D37" s="124">
+        <v>91.350643423322225</v>
+      </c>
+      <c r="E37" s="124">
+        <v>89.341760932799787</v>
+      </c>
+      <c r="F37" s="124">
+        <v>79.045051998788765</v>
+      </c>
+      <c r="G37" s="129">
+        <v>52.319711731697872</v>
+      </c>
+      <c r="H37" s="40"/>
+      <c r="I37" s="40"/>
+      <c r="J37" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C37:G37)&amp;","</f>
+        <v xml:space="preserve">    91.5291158298536, 91.3506434233222, 89.3417609327998, 79.0450519987888, 52.3197117316979,</v>
+      </c>
+      <c r="K37" s="101" t="s">
+        <v>8</v>
+      </c>
+      <c r="L37" s="103"/>
+      <c r="M37" s="128">
+        <v>3.326792742141544</v>
+      </c>
+      <c r="N37" s="124">
+        <v>3.370578982220036</v>
+      </c>
+      <c r="O37" s="124">
+        <v>5.5895882093977454</v>
+      </c>
+      <c r="P37" s="124">
+        <v>3.3906236766273481</v>
+      </c>
+      <c r="Q37" s="129">
+        <v>4.5139463885317248</v>
+      </c>
+      <c r="R37" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M37:Q37)&amp;","</f>
+        <v xml:space="preserve">    3.32679274214154, 3.37057898222004, 5.58958820939775, 3.39062367662735, 4.51394638853172,</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="101" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" s="103"/>
+      <c r="C38" s="128">
+        <v>92.904210456970588</v>
+      </c>
+      <c r="D38" s="124">
+        <v>92.1891124359732</v>
+      </c>
+      <c r="E38" s="124">
+        <v>90.496036698942376</v>
+      </c>
+      <c r="F38" s="124">
+        <v>77.336951327754974</v>
+      </c>
+      <c r="G38" s="129">
+        <v>56.222535937160863</v>
+      </c>
+      <c r="H38" s="40"/>
+      <c r="I38" s="40"/>
+      <c r="J38" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C38:G38)&amp;","</f>
+        <v xml:space="preserve">    92.9042104569706, 92.1891124359732, 90.4960366989424, 77.336951327755, 56.2225359371609,</v>
+      </c>
+      <c r="K38" s="101" t="s">
+        <v>21</v>
+      </c>
+      <c r="L38" s="103"/>
+      <c r="M38" s="128">
+        <v>3.6016716439248402</v>
+      </c>
+      <c r="N38" s="124">
+        <v>3.9740552459554821</v>
+      </c>
+      <c r="O38" s="124">
+        <v>4.0466560589706821</v>
+      </c>
+      <c r="P38" s="124">
+        <v>7.6607457787732498</v>
+      </c>
+      <c r="Q38" s="129">
+        <v>9.1988486675501449</v>
+      </c>
+      <c r="R38" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M38:Q38)&amp;","</f>
+        <v xml:space="preserve">    3.60167164392484, 3.97405524595548, 4.04665605897068, 7.66074577877325, 9.19884866755014,</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="101" t="s">
         <v>22</v>
       </c>
-      <c r="L35" s="93"/>
-      <c r="M35" s="41"/>
-      <c r="N35" s="42"/>
-      <c r="O35" s="42"/>
-      <c r="P35" s="42"/>
-      <c r="Q35" s="42"/>
-      <c r="R35" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M35:Q35)&amp;","</f>
-        <v xml:space="preserve">    ,</v>
-      </c>
-    </row>
-    <row r="36" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="J36" s="11"/>
-      <c r="K36" s="11"/>
-      <c r="L36" s="11"/>
-      <c r="M36" s="11"/>
-      <c r="N36" s="11"/>
-      <c r="O36" s="11"/>
-      <c r="P36" s="11"/>
-      <c r="Q36" s="11"/>
-    </row>
-    <row r="37" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="J37" s="11"/>
-      <c r="K37" s="11"/>
-      <c r="L37" s="11"/>
-      <c r="M37" s="11"/>
-      <c r="N37" s="11"/>
-      <c r="O37" s="11"/>
-      <c r="P37" s="11"/>
-      <c r="Q37" s="11"/>
-    </row>
-    <row r="38" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="H38" s="11"/>
-      <c r="I38" s="11"/>
-      <c r="J38" s="11"/>
-      <c r="K38" s="11"/>
-      <c r="L38" s="11"/>
-      <c r="M38" s="11"/>
-      <c r="N38" s="11"/>
-      <c r="O38" s="11"/>
-      <c r="P38" s="11"/>
-      <c r="Q38" s="11"/>
-    </row>
-    <row r="39" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="H39" s="11"/>
-      <c r="I39" s="11"/>
-      <c r="J39" s="11"/>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11"/>
-      <c r="M39" s="11"/>
-      <c r="N39" s="11"/>
-      <c r="O39" s="11"/>
-      <c r="P39" s="11"/>
-      <c r="Q39" s="11"/>
+      <c r="B39" s="103"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="42"/>
+      <c r="E39" s="42"/>
+      <c r="F39" s="42"/>
+      <c r="G39" s="145"/>
+      <c r="H39" s="40"/>
+      <c r="I39" s="40"/>
+      <c r="J39" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C39:G39)&amp;","</f>
+        <v xml:space="preserve">    ,</v>
+      </c>
+      <c r="K39" s="101" t="s">
+        <v>22</v>
+      </c>
+      <c r="L39" s="103"/>
+      <c r="M39" s="41"/>
+      <c r="N39" s="42"/>
+      <c r="O39" s="42"/>
+      <c r="P39" s="42"/>
+      <c r="Q39" s="145"/>
+      <c r="R39" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M39:Q39)&amp;","</f>
+        <v xml:space="preserve">    ,</v>
+      </c>
     </row>
     <row r="40" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="H40" s="11"/>
-      <c r="I40" s="11"/>
       <c r="J40" s="11"/>
       <c r="K40" s="11"/>
       <c r="L40" s="11"/>
@@ -2599,8 +2879,6 @@
       <c r="Q40" s="11"/>
     </row>
     <row r="41" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="H41" s="11"/>
-      <c r="I41" s="11"/>
       <c r="J41" s="11"/>
       <c r="K41" s="11"/>
       <c r="L41" s="11"/>
@@ -2610,67 +2888,115 @@
       <c r="P41" s="11"/>
       <c r="Q41" s="11"/>
     </row>
+    <row r="42" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="H42" s="11"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="11"/>
+      <c r="K42" s="11"/>
+      <c r="L42" s="11"/>
+      <c r="M42" s="11"/>
+      <c r="N42" s="11"/>
+      <c r="O42" s="11"/>
+      <c r="P42" s="11"/>
+      <c r="Q42" s="11"/>
+    </row>
+    <row r="43" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="H43" s="11"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
+      <c r="K43" s="11"/>
+      <c r="L43" s="11"/>
+      <c r="M43" s="11"/>
+      <c r="N43" s="11"/>
+      <c r="O43" s="11"/>
+      <c r="P43" s="11"/>
+      <c r="Q43" s="11"/>
+    </row>
+    <row r="44" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="H44" s="11"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="11"/>
+      <c r="K44" s="11"/>
+      <c r="L44" s="11"/>
+      <c r="M44" s="11"/>
+      <c r="N44" s="11"/>
+      <c r="O44" s="11"/>
+      <c r="P44" s="11"/>
+      <c r="Q44" s="11"/>
+    </row>
+    <row r="45" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="11"/>
+      <c r="K45" s="11"/>
+      <c r="L45" s="11"/>
+      <c r="M45" s="11"/>
+      <c r="N45" s="11"/>
+      <c r="O45" s="11"/>
+      <c r="P45" s="11"/>
+      <c r="Q45" s="11"/>
+    </row>
   </sheetData>
   <mergeCells count="56">
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="K39:L39"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="K38:L38"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="K35:Q35"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="K30:Q30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="K25:Q25"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="K15:Q15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="K5:Q5"/>
+    <mergeCell ref="A10:G10"/>
+    <mergeCell ref="K10:Q10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="K11:L11"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="K5:Q5"/>
-    <mergeCell ref="A8:G8"/>
-    <mergeCell ref="K8:Q8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="K13:Q13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="K23:Q23"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="K26:Q26"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="K31:Q31"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="K34:L34"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C2:G4 C6:G7 C9:G12 C14:G17">
+  <conditionalFormatting sqref="C2:G4 C6:G9 C11:G14 C16:G19">
     <cfRule type="colorScale" priority="294">
       <colorScale>
         <cfvo type="min"/>
@@ -2682,7 +3008,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:G4 H2:I17">
+  <conditionalFormatting sqref="C2:G4 H2:I19">
     <cfRule type="colorScale" priority="277">
       <colorScale>
         <cfvo type="min"/>
@@ -2810,7 +3136,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C7:G7">
+  <conditionalFormatting sqref="C7:G9">
     <cfRule type="colorScale" priority="303">
       <colorScale>
         <cfvo type="min"/>
@@ -2832,7 +3158,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C9:G11 C14:G16">
+  <conditionalFormatting sqref="C11:G13 C16:G18">
     <cfRule type="colorScale" priority="305">
       <colorScale>
         <cfvo type="min"/>
@@ -2844,7 +3170,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C9:G11">
+  <conditionalFormatting sqref="C11:G13">
     <cfRule type="colorScale" priority="307">
       <colorScale>
         <cfvo type="min"/>
@@ -2876,7 +3202,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C9:G12 C14:G17 C6:G7 C2:G4">
+  <conditionalFormatting sqref="C11:G14 C16:G19 C6:G9 C2:G4">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -2888,7 +3214,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C9:G12 C14:G17">
+  <conditionalFormatting sqref="C11:G14 C16:G19">
     <cfRule type="colorScale" priority="310">
       <colorScale>
         <cfvo type="min"/>
@@ -2900,7 +3226,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C14:G16">
+  <conditionalFormatting sqref="C16:G18">
     <cfRule type="colorScale" priority="312">
       <colorScale>
         <cfvo type="min"/>
@@ -2932,7 +3258,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H17">
+  <conditionalFormatting sqref="H2:H19">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -2944,7 +3270,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H31:H35">
+  <conditionalFormatting sqref="H35:H39">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -2976,7 +3302,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I17">
+  <conditionalFormatting sqref="I2:I19">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -2988,7 +3314,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I31:I35">
+  <conditionalFormatting sqref="I35:I39">
     <cfRule type="colorScale" priority="41">
       <colorScale>
         <cfvo type="min"/>
@@ -3113,10 +3439,10 @@
       <c r="V1" s="12"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="99" t="s">
+      <c r="A2" s="94" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="100"/>
+      <c r="B2" s="95"/>
       <c r="C2" s="20"/>
       <c r="D2" s="21"/>
       <c r="E2" s="21"/>
@@ -3136,10 +3462,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:I2)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M2" s="99" t="s">
+      <c r="M2" s="94" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="100"/>
+      <c r="N2" s="95"/>
       <c r="O2" s="31"/>
       <c r="P2" s="32"/>
       <c r="Q2" s="32"/>
@@ -3153,10 +3479,10 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="99" t="s">
+      <c r="A3" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="100"/>
+      <c r="B3" s="95"/>
       <c r="C3" s="31"/>
       <c r="D3" s="32"/>
       <c r="E3" s="32"/>
@@ -3176,10 +3502,10 @@
         <f t="shared" ref="L3:L18" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M3" s="99" t="s">
+      <c r="M3" s="94" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="100"/>
+      <c r="N3" s="95"/>
       <c r="O3" s="31"/>
       <c r="P3" s="32"/>
       <c r="Q3" s="32"/>
@@ -3193,10 +3519,10 @@
       </c>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="99" t="s">
+      <c r="A4" s="94" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="100"/>
+      <c r="B4" s="95"/>
       <c r="C4" s="24"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
@@ -3216,10 +3542,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M4" s="99" t="s">
+      <c r="M4" s="94" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="100"/>
+      <c r="N4" s="95"/>
       <c r="O4" s="43"/>
       <c r="P4" s="26"/>
       <c r="Q4" s="26"/>
@@ -3233,35 +3559,35 @@
       </c>
     </row>
     <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="99" t="s">
+      <c r="A5" s="94" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="101"/>
-      <c r="C5" s="101"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="101"/>
-      <c r="G5" s="101"/>
-      <c r="H5" s="101"/>
-      <c r="I5" s="100"/>
+      <c r="B5" s="96"/>
+      <c r="C5" s="96"/>
+      <c r="D5" s="96"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="96"/>
+      <c r="G5" s="96"/>
+      <c r="H5" s="96"/>
+      <c r="I5" s="95"/>
       <c r="J5" s="34"/>
       <c r="K5" s="34"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="99" t="s">
+      <c r="M5" s="94" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="101"/>
-      <c r="O5" s="101"/>
-      <c r="P5" s="101"/>
-      <c r="Q5" s="101"/>
-      <c r="R5" s="101"/>
-      <c r="S5" s="101"/>
-      <c r="T5" s="101"/>
-      <c r="U5" s="100"/>
+      <c r="N5" s="96"/>
+      <c r="O5" s="96"/>
+      <c r="P5" s="96"/>
+      <c r="Q5" s="96"/>
+      <c r="R5" s="96"/>
+      <c r="S5" s="96"/>
+      <c r="T5" s="96"/>
+      <c r="U5" s="95"/>
       <c r="V5" s="12"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="103" t="s">
+      <c r="A6" s="98" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -3286,7 +3612,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M6" s="103" t="s">
+      <c r="M6" s="98" t="s">
         <v>11</v>
       </c>
       <c r="N6" s="8" t="s">
@@ -3305,7 +3631,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="106"/>
+      <c r="A7" s="110"/>
       <c r="B7" s="8" t="s">
         <v>14</v>
       </c>
@@ -3328,7 +3654,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M7" s="106"/>
+      <c r="M7" s="110"/>
       <c r="N7" s="8" t="s">
         <v>14</v>
       </c>
@@ -3345,7 +3671,7 @@
       </c>
     </row>
     <row r="8" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="106"/>
+      <c r="A8" s="110"/>
       <c r="B8" s="8" t="s">
         <v>17</v>
       </c>
@@ -3368,7 +3694,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M8" s="106"/>
+      <c r="M8" s="110"/>
       <c r="N8" s="8" t="s">
         <v>17</v>
       </c>
@@ -3382,7 +3708,7 @@
       <c r="V8" s="12"/>
     </row>
     <row r="9" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="106"/>
+      <c r="A9" s="110"/>
       <c r="B9" s="8" t="s">
         <v>18</v>
       </c>
@@ -3405,7 +3731,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M9" s="106"/>
+      <c r="M9" s="110"/>
       <c r="N9" s="8" t="s">
         <v>18</v>
       </c>
@@ -3419,7 +3745,7 @@
       <c r="V9" s="12"/>
     </row>
     <row r="10" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="106"/>
+      <c r="A10" s="110"/>
       <c r="B10" s="8" t="s">
         <v>15</v>
       </c>
@@ -3442,7 +3768,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M10" s="106"/>
+      <c r="M10" s="110"/>
       <c r="N10" s="8" t="s">
         <v>15</v>
       </c>
@@ -3456,7 +3782,7 @@
       <c r="V10" s="12"/>
     </row>
     <row r="11" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="106"/>
+      <c r="A11" s="110"/>
       <c r="B11" s="8" t="s">
         <v>25</v>
       </c>
@@ -3479,7 +3805,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M11" s="106"/>
+      <c r="M11" s="110"/>
       <c r="N11" s="8" t="s">
         <v>25</v>
       </c>
@@ -3493,7 +3819,7 @@
       <c r="V11" s="12"/>
     </row>
     <row r="12" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="106"/>
+      <c r="A12" s="110"/>
       <c r="B12" s="8" t="s">
         <v>19</v>
       </c>
@@ -3516,7 +3842,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M12" s="106"/>
+      <c r="M12" s="110"/>
       <c r="N12" s="8" t="s">
         <v>19</v>
       </c>
@@ -3530,7 +3856,7 @@
       <c r="V12" s="12"/>
     </row>
     <row r="13" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="106"/>
+      <c r="A13" s="110"/>
       <c r="B13" s="8" t="s">
         <v>16</v>
       </c>
@@ -3553,7 +3879,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M13" s="106"/>
+      <c r="M13" s="110"/>
       <c r="N13" s="8" t="s">
         <v>16</v>
       </c>
@@ -3567,7 +3893,7 @@
       <c r="V13" s="12"/>
     </row>
     <row r="14" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="107"/>
+      <c r="A14" s="111"/>
       <c r="B14" s="8" t="s">
         <v>26</v>
       </c>
@@ -3590,7 +3916,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M14" s="107"/>
+      <c r="M14" s="111"/>
       <c r="N14" s="8" t="s">
         <v>26</v>
       </c>
@@ -3604,38 +3930,38 @@
       <c r="V14" s="12"/>
     </row>
     <row r="15" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="99" t="s">
+      <c r="A15" s="94" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="101"/>
-      <c r="C15" s="102"/>
-      <c r="D15" s="102"/>
-      <c r="E15" s="102"/>
-      <c r="F15" s="102"/>
-      <c r="G15" s="102"/>
-      <c r="H15" s="102"/>
-      <c r="I15" s="111"/>
+      <c r="B15" s="96"/>
+      <c r="C15" s="100"/>
+      <c r="D15" s="100"/>
+      <c r="E15" s="100"/>
+      <c r="F15" s="100"/>
+      <c r="G15" s="100"/>
+      <c r="H15" s="100"/>
+      <c r="I15" s="108"/>
       <c r="J15" s="34"/>
       <c r="K15" s="34"/>
       <c r="L15" s="12"/>
-      <c r="M15" s="99" t="s">
+      <c r="M15" s="94" t="s">
         <v>20</v>
       </c>
-      <c r="N15" s="101"/>
-      <c r="O15" s="105"/>
-      <c r="P15" s="105"/>
-      <c r="Q15" s="105"/>
-      <c r="R15" s="105"/>
-      <c r="S15" s="105"/>
-      <c r="T15" s="105"/>
-      <c r="U15" s="104"/>
+      <c r="N15" s="96"/>
+      <c r="O15" s="97"/>
+      <c r="P15" s="97"/>
+      <c r="Q15" s="97"/>
+      <c r="R15" s="97"/>
+      <c r="S15" s="97"/>
+      <c r="T15" s="97"/>
+      <c r="U15" s="99"/>
       <c r="V15" s="12"/>
     </row>
     <row r="16" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="99" t="s">
+      <c r="A16" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="100"/>
+      <c r="B16" s="95"/>
       <c r="C16" s="46"/>
       <c r="D16" s="47"/>
       <c r="E16" s="47"/>
@@ -3655,10 +3981,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M16" s="99" t="s">
+      <c r="M16" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="N16" s="100"/>
+      <c r="N16" s="95"/>
       <c r="O16" s="46"/>
       <c r="P16" s="47"/>
       <c r="Q16" s="47"/>
@@ -3672,10 +3998,10 @@
       </c>
     </row>
     <row r="17" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="103" t="s">
+      <c r="A17" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="104"/>
+      <c r="B17" s="99"/>
       <c r="C17" s="49"/>
       <c r="D17" s="12"/>
       <c r="E17" s="12"/>
@@ -3695,10 +4021,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M17" s="99" t="s">
+      <c r="M17" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="N17" s="100"/>
+      <c r="N17" s="95"/>
       <c r="O17" s="49"/>
       <c r="P17" s="12"/>
       <c r="Q17" s="12"/>
@@ -3712,10 +4038,10 @@
       </c>
     </row>
     <row r="18" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="99" t="s">
+      <c r="A18" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="100"/>
+      <c r="B18" s="95"/>
       <c r="C18" s="49"/>
       <c r="D18" s="12"/>
       <c r="E18" s="12"/>
@@ -3735,10 +4061,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M18" s="99" t="s">
+      <c r="M18" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="N18" s="100"/>
+      <c r="N18" s="95"/>
       <c r="O18" s="49"/>
       <c r="P18" s="12"/>
       <c r="Q18" s="12"/>
@@ -3752,10 +4078,10 @@
       </c>
     </row>
     <row r="19" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="99" t="s">
+      <c r="A19" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="100"/>
+      <c r="B19" s="95"/>
       <c r="C19" s="51"/>
       <c r="D19" s="52"/>
       <c r="E19" s="52"/>
@@ -3772,10 +4098,10 @@
         <v>0</v>
       </c>
       <c r="L19" s="12"/>
-      <c r="M19" s="99" t="s">
+      <c r="M19" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="N19" s="100"/>
+      <c r="N19" s="95"/>
       <c r="O19" s="51"/>
       <c r="P19" s="52"/>
       <c r="Q19" s="52"/>
@@ -3786,38 +4112,38 @@
       <c r="V19" s="12"/>
     </row>
     <row r="20" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="99" t="s">
+      <c r="A20" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="101"/>
-      <c r="C20" s="102"/>
-      <c r="D20" s="102"/>
-      <c r="E20" s="102"/>
-      <c r="F20" s="102"/>
-      <c r="G20" s="102"/>
-      <c r="H20" s="102"/>
-      <c r="I20" s="111"/>
+      <c r="B20" s="96"/>
+      <c r="C20" s="100"/>
+      <c r="D20" s="100"/>
+      <c r="E20" s="100"/>
+      <c r="F20" s="100"/>
+      <c r="G20" s="100"/>
+      <c r="H20" s="100"/>
+      <c r="I20" s="108"/>
       <c r="J20" s="34"/>
       <c r="K20" s="34"/>
       <c r="L20" s="12"/>
-      <c r="M20" s="99" t="s">
+      <c r="M20" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="N20" s="101"/>
-      <c r="O20" s="102"/>
-      <c r="P20" s="102"/>
-      <c r="Q20" s="102"/>
-      <c r="R20" s="102"/>
-      <c r="S20" s="102"/>
-      <c r="T20" s="102"/>
-      <c r="U20" s="111"/>
+      <c r="N20" s="96"/>
+      <c r="O20" s="100"/>
+      <c r="P20" s="100"/>
+      <c r="Q20" s="100"/>
+      <c r="R20" s="100"/>
+      <c r="S20" s="100"/>
+      <c r="T20" s="100"/>
+      <c r="U20" s="108"/>
       <c r="V20" s="12"/>
     </row>
     <row r="21" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="99" t="s">
+      <c r="A21" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="100"/>
+      <c r="B21" s="95"/>
       <c r="C21" s="46"/>
       <c r="D21" s="47"/>
       <c r="E21" s="47"/>
@@ -3837,10 +4163,10 @@
         <f t="shared" ref="L21:L23" si="2">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:I21)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M21" s="99" t="s">
+      <c r="M21" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="N21" s="100"/>
+      <c r="N21" s="95"/>
       <c r="O21" s="46"/>
       <c r="P21" s="47"/>
       <c r="Q21" s="47"/>
@@ -3854,10 +4180,10 @@
       </c>
     </row>
     <row r="22" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="103" t="s">
+      <c r="A22" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="104"/>
+      <c r="B22" s="99"/>
       <c r="C22" s="49"/>
       <c r="D22" s="12"/>
       <c r="E22" s="12"/>
@@ -3877,10 +4203,10 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M22" s="99" t="s">
+      <c r="M22" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="N22" s="100"/>
+      <c r="N22" s="95"/>
       <c r="O22" s="49"/>
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
@@ -3894,10 +4220,10 @@
       </c>
     </row>
     <row r="23" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="99" t="s">
+      <c r="A23" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="100"/>
+      <c r="B23" s="95"/>
       <c r="C23" s="49"/>
       <c r="D23" s="12"/>
       <c r="E23" s="12"/>
@@ -3917,10 +4243,10 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M23" s="99" t="s">
+      <c r="M23" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="N23" s="100"/>
+      <c r="N23" s="95"/>
       <c r="O23" s="49"/>
       <c r="P23" s="12"/>
       <c r="Q23" s="12"/>
@@ -3934,10 +4260,10 @@
       </c>
     </row>
     <row r="24" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="99" t="s">
+      <c r="A24" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="100"/>
+      <c r="B24" s="95"/>
       <c r="C24" s="51"/>
       <c r="D24" s="52"/>
       <c r="E24" s="52"/>
@@ -3954,10 +4280,10 @@
         <v>0</v>
       </c>
       <c r="L24" s="12"/>
-      <c r="M24" s="99" t="s">
+      <c r="M24" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="N24" s="100"/>
+      <c r="N24" s="95"/>
       <c r="O24" s="51"/>
       <c r="P24" s="52"/>
       <c r="Q24" s="52"/>
@@ -3968,38 +4294,38 @@
       <c r="V24" s="12"/>
     </row>
     <row r="25" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="99" t="s">
+      <c r="A25" s="94" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="101"/>
-      <c r="C25" s="102"/>
-      <c r="D25" s="102"/>
-      <c r="E25" s="102"/>
-      <c r="F25" s="102"/>
-      <c r="G25" s="102"/>
-      <c r="H25" s="102"/>
-      <c r="I25" s="111"/>
+      <c r="B25" s="96"/>
+      <c r="C25" s="100"/>
+      <c r="D25" s="100"/>
+      <c r="E25" s="100"/>
+      <c r="F25" s="100"/>
+      <c r="G25" s="100"/>
+      <c r="H25" s="100"/>
+      <c r="I25" s="108"/>
       <c r="J25" s="34"/>
       <c r="K25" s="34"/>
       <c r="L25" s="12"/>
-      <c r="M25" s="99" t="s">
+      <c r="M25" s="94" t="s">
         <v>23</v>
       </c>
-      <c r="N25" s="101"/>
-      <c r="O25" s="102"/>
-      <c r="P25" s="102"/>
-      <c r="Q25" s="102"/>
-      <c r="R25" s="102"/>
-      <c r="S25" s="102"/>
-      <c r="T25" s="102"/>
-      <c r="U25" s="111"/>
+      <c r="N25" s="96"/>
+      <c r="O25" s="100"/>
+      <c r="P25" s="100"/>
+      <c r="Q25" s="100"/>
+      <c r="R25" s="100"/>
+      <c r="S25" s="100"/>
+      <c r="T25" s="100"/>
+      <c r="U25" s="108"/>
       <c r="V25" s="12"/>
     </row>
     <row r="26" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="99" t="s">
+      <c r="A26" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="B26" s="100"/>
+      <c r="B26" s="95"/>
       <c r="C26"/>
       <c r="D26"/>
       <c r="E26"/>
@@ -4019,10 +4345,10 @@
         <f t="shared" ref="L26:L28" si="4">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C26:I26)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M26" s="99" t="s">
+      <c r="M26" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="N26" s="100"/>
+      <c r="N26" s="95"/>
       <c r="O26"/>
       <c r="P26"/>
       <c r="Q26"/>
@@ -4036,10 +4362,10 @@
       </c>
     </row>
     <row r="27" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="103" t="s">
+      <c r="A27" s="98" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="104"/>
+      <c r="B27" s="99"/>
       <c r="C27"/>
       <c r="D27"/>
       <c r="E27"/>
@@ -4059,10 +4385,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M27" s="99" t="s">
+      <c r="M27" s="94" t="s">
         <v>8</v>
       </c>
-      <c r="N27" s="100"/>
+      <c r="N27" s="95"/>
       <c r="O27"/>
       <c r="P27"/>
       <c r="Q27"/>
@@ -4076,10 +4402,10 @@
       </c>
     </row>
     <row r="28" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="99" t="s">
+      <c r="A28" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="100"/>
+      <c r="B28" s="95"/>
       <c r="C28"/>
       <c r="D28"/>
       <c r="E28"/>
@@ -4099,10 +4425,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M28" s="99" t="s">
+      <c r="M28" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="N28" s="100"/>
+      <c r="N28" s="95"/>
       <c r="O28"/>
       <c r="P28"/>
       <c r="Q28"/>
@@ -4116,10 +4442,10 @@
       </c>
     </row>
     <row r="29" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="99" t="s">
+      <c r="A29" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="B29" s="100"/>
+      <c r="B29" s="95"/>
       <c r="C29"/>
       <c r="D29"/>
       <c r="E29"/>
@@ -4136,10 +4462,10 @@
         <v>0</v>
       </c>
       <c r="L29" s="12"/>
-      <c r="M29" s="99" t="s">
+      <c r="M29" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="N29" s="100"/>
+      <c r="N29" s="95"/>
       <c r="O29" s="89"/>
       <c r="P29" s="90"/>
       <c r="Q29" s="90"/>
@@ -4232,10 +4558,10 @@
       <c r="V31" s="1"/>
     </row>
     <row r="32" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="92" t="s">
+      <c r="A32" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="B32" s="93"/>
+      <c r="B32" s="102"/>
       <c r="C32" s="38"/>
       <c r="D32" s="38"/>
       <c r="E32" s="38"/>
@@ -4249,10 +4575,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C32:I32)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M32" s="92" t="s">
+      <c r="M32" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="N32" s="93"/>
+      <c r="N32" s="102"/>
       <c r="O32" s="37"/>
       <c r="P32" s="38"/>
       <c r="Q32" s="38"/>
@@ -4266,10 +4592,10 @@
       </c>
     </row>
     <row r="33" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="92" t="s">
+      <c r="A33" s="101" t="s">
         <v>6</v>
       </c>
-      <c r="B33" s="93"/>
+      <c r="B33" s="102"/>
       <c r="C33" s="38"/>
       <c r="D33" s="38"/>
       <c r="E33" s="38"/>
@@ -4283,10 +4609,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C33:I33)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M33" s="92" t="s">
+      <c r="M33" s="101" t="s">
         <v>6</v>
       </c>
-      <c r="N33" s="93"/>
+      <c r="N33" s="102"/>
       <c r="O33" s="38"/>
       <c r="P33" s="38"/>
       <c r="Q33" s="38"/>
@@ -4300,10 +4626,10 @@
       </c>
     </row>
     <row r="34" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="92" t="s">
+      <c r="A34" s="101" t="s">
         <v>10</v>
       </c>
-      <c r="B34" s="93"/>
+      <c r="B34" s="102"/>
       <c r="C34" s="28"/>
       <c r="D34" s="29"/>
       <c r="E34" s="29"/>
@@ -4317,10 +4643,10 @@
         <f t="shared" ref="L34:L43" si="7">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C34:I34)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M34" s="92" t="s">
+      <c r="M34" s="101" t="s">
         <v>10</v>
       </c>
-      <c r="N34" s="93"/>
+      <c r="N34" s="102"/>
       <c r="O34" s="28"/>
       <c r="P34" s="29"/>
       <c r="Q34" s="29"/>
@@ -4334,35 +4660,35 @@
       </c>
     </row>
     <row r="35" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="92" t="s">
+      <c r="A35" s="101" t="s">
         <v>12</v>
       </c>
-      <c r="B35" s="96"/>
-      <c r="C35" s="96"/>
-      <c r="D35" s="96"/>
-      <c r="E35" s="96"/>
-      <c r="F35" s="96"/>
-      <c r="G35" s="96"/>
-      <c r="H35" s="96"/>
-      <c r="I35" s="93"/>
+      <c r="B35" s="103"/>
+      <c r="C35" s="103"/>
+      <c r="D35" s="103"/>
+      <c r="E35" s="103"/>
+      <c r="F35" s="103"/>
+      <c r="G35" s="103"/>
+      <c r="H35" s="103"/>
+      <c r="I35" s="102"/>
       <c r="J35" s="40"/>
       <c r="K35" s="40"/>
       <c r="L35" s="1"/>
-      <c r="M35" s="92" t="s">
+      <c r="M35" s="101" t="s">
         <v>12</v>
       </c>
-      <c r="N35" s="96"/>
-      <c r="O35" s="96"/>
-      <c r="P35" s="96"/>
-      <c r="Q35" s="96"/>
-      <c r="R35" s="96"/>
-      <c r="S35" s="96"/>
-      <c r="T35" s="96"/>
-      <c r="U35" s="93"/>
+      <c r="N35" s="103"/>
+      <c r="O35" s="103"/>
+      <c r="P35" s="103"/>
+      <c r="Q35" s="103"/>
+      <c r="R35" s="103"/>
+      <c r="S35" s="103"/>
+      <c r="T35" s="103"/>
+      <c r="U35" s="102"/>
       <c r="V35" s="1"/>
     </row>
     <row r="36" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="94" t="s">
+      <c r="A36" s="106" t="s">
         <v>11</v>
       </c>
       <c r="B36" s="9" t="s">
@@ -4381,7 +4707,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M36" s="94" t="s">
+      <c r="M36" s="106" t="s">
         <v>11</v>
       </c>
       <c r="N36" s="9" t="s">
@@ -4400,7 +4726,7 @@
       </c>
     </row>
     <row r="37" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="108"/>
+      <c r="A37" s="112"/>
       <c r="B37" s="9" t="s">
         <v>14</v>
       </c>
@@ -4417,7 +4743,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M37" s="108"/>
+      <c r="M37" s="112"/>
       <c r="N37" s="9" t="s">
         <v>14</v>
       </c>
@@ -4434,7 +4760,7 @@
       </c>
     </row>
     <row r="38" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="108"/>
+      <c r="A38" s="112"/>
       <c r="B38" s="9" t="s">
         <v>17</v>
       </c>
@@ -4448,7 +4774,7 @@
       <c r="J38" s="40"/>
       <c r="K38" s="40"/>
       <c r="L38" s="1"/>
-      <c r="M38" s="108"/>
+      <c r="M38" s="112"/>
       <c r="N38" s="9" t="s">
         <v>17</v>
       </c>
@@ -4462,7 +4788,7 @@
       <c r="V38" s="1"/>
     </row>
     <row r="39" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="108"/>
+      <c r="A39" s="112"/>
       <c r="B39" s="9" t="s">
         <v>18</v>
       </c>
@@ -4476,7 +4802,7 @@
       <c r="J39" s="40"/>
       <c r="K39" s="40"/>
       <c r="L39" s="1"/>
-      <c r="M39" s="108"/>
+      <c r="M39" s="112"/>
       <c r="N39" s="9" t="s">
         <v>18</v>
       </c>
@@ -4490,7 +4816,7 @@
       <c r="V39" s="1"/>
     </row>
     <row r="40" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="108"/>
+      <c r="A40" s="112"/>
       <c r="B40" s="9" t="s">
         <v>15</v>
       </c>
@@ -4507,7 +4833,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M40" s="108"/>
+      <c r="M40" s="112"/>
       <c r="N40" s="9" t="s">
         <v>15</v>
       </c>
@@ -4521,7 +4847,7 @@
       <c r="V40" s="1"/>
     </row>
     <row r="41" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="108"/>
+      <c r="A41" s="112"/>
       <c r="B41" s="9" t="s">
         <v>25</v>
       </c>
@@ -4535,7 +4861,7 @@
       <c r="J41" s="40"/>
       <c r="K41" s="40"/>
       <c r="L41" s="1"/>
-      <c r="M41" s="108"/>
+      <c r="M41" s="112"/>
       <c r="N41" s="9" t="s">
         <v>25</v>
       </c>
@@ -4549,7 +4875,7 @@
       <c r="V41" s="1"/>
     </row>
     <row r="42" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="108"/>
+      <c r="A42" s="112"/>
       <c r="B42" s="9" t="s">
         <v>19</v>
       </c>
@@ -4563,7 +4889,7 @@
       <c r="J42" s="40"/>
       <c r="K42" s="40"/>
       <c r="L42" s="1"/>
-      <c r="M42" s="108"/>
+      <c r="M42" s="112"/>
       <c r="N42" s="9" t="s">
         <v>19</v>
       </c>
@@ -4577,7 +4903,7 @@
       <c r="V42" s="1"/>
     </row>
     <row r="43" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="108"/>
+      <c r="A43" s="112"/>
       <c r="B43" s="9" t="s">
         <v>16</v>
       </c>
@@ -4594,7 +4920,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M43" s="108"/>
+      <c r="M43" s="112"/>
       <c r="N43" s="9" t="s">
         <v>16</v>
       </c>
@@ -4608,7 +4934,7 @@
       <c r="V43" s="1"/>
     </row>
     <row r="44" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="109"/>
+      <c r="A44" s="113"/>
       <c r="B44" s="9" t="s">
         <v>26</v>
       </c>
@@ -4622,7 +4948,7 @@
       <c r="J44" s="40"/>
       <c r="K44" s="40"/>
       <c r="L44" s="1"/>
-      <c r="M44" s="109"/>
+      <c r="M44" s="113"/>
       <c r="N44" s="9" t="s">
         <v>26</v>
       </c>
@@ -4636,38 +4962,38 @@
       <c r="V44" s="1"/>
     </row>
     <row r="45" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="92" t="s">
+      <c r="A45" s="101" t="s">
         <v>20</v>
       </c>
-      <c r="B45" s="96"/>
-      <c r="C45" s="97"/>
-      <c r="D45" s="97"/>
-      <c r="E45" s="97"/>
-      <c r="F45" s="97"/>
-      <c r="G45" s="97"/>
-      <c r="H45" s="97"/>
-      <c r="I45" s="110"/>
+      <c r="B45" s="103"/>
+      <c r="C45" s="105"/>
+      <c r="D45" s="105"/>
+      <c r="E45" s="105"/>
+      <c r="F45" s="105"/>
+      <c r="G45" s="105"/>
+      <c r="H45" s="105"/>
+      <c r="I45" s="109"/>
       <c r="J45" s="40"/>
       <c r="K45" s="40"/>
       <c r="L45" s="1"/>
-      <c r="M45" s="92" t="s">
+      <c r="M45" s="101" t="s">
         <v>20</v>
       </c>
-      <c r="N45" s="96"/>
-      <c r="O45" s="97"/>
-      <c r="P45" s="97"/>
-      <c r="Q45" s="97"/>
-      <c r="R45" s="97"/>
-      <c r="S45" s="97"/>
-      <c r="T45" s="97"/>
-      <c r="U45" s="110"/>
+      <c r="N45" s="103"/>
+      <c r="O45" s="105"/>
+      <c r="P45" s="105"/>
+      <c r="Q45" s="105"/>
+      <c r="R45" s="105"/>
+      <c r="S45" s="105"/>
+      <c r="T45" s="105"/>
+      <c r="U45" s="109"/>
       <c r="V45" s="1"/>
     </row>
     <row r="46" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="92" t="s">
+      <c r="A46" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="B46" s="93"/>
+      <c r="B46" s="102"/>
       <c r="C46" s="54"/>
       <c r="D46" s="55"/>
       <c r="E46" s="55"/>
@@ -4681,10 +5007,10 @@
         <f t="shared" ref="L46:L48" si="8">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C46:I46)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M46" s="92" t="s">
+      <c r="M46" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="N46" s="93"/>
+      <c r="N46" s="102"/>
       <c r="O46" s="54"/>
       <c r="P46" s="55"/>
       <c r="Q46" s="55"/>
@@ -4698,10 +5024,10 @@
       </c>
     </row>
     <row r="47" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="92" t="s">
+      <c r="A47" s="101" t="s">
         <v>8</v>
       </c>
-      <c r="B47" s="93"/>
+      <c r="B47" s="102"/>
       <c r="C47" s="57"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -4715,10 +5041,10 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M47" s="92" t="s">
+      <c r="M47" s="101" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="93"/>
+      <c r="N47" s="102"/>
       <c r="O47" s="57"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
@@ -4732,10 +5058,10 @@
       </c>
     </row>
     <row r="48" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="92" t="s">
+      <c r="A48" s="101" t="s">
         <v>21</v>
       </c>
-      <c r="B48" s="93"/>
+      <c r="B48" s="102"/>
       <c r="C48" s="57"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -4749,10 +5075,10 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M48" s="92" t="s">
+      <c r="M48" s="101" t="s">
         <v>21</v>
       </c>
-      <c r="N48" s="93"/>
+      <c r="N48" s="102"/>
       <c r="O48" s="57"/>
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
@@ -4766,10 +5092,10 @@
       </c>
     </row>
     <row r="49" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="92" t="s">
+      <c r="A49" s="101" t="s">
         <v>22</v>
       </c>
-      <c r="B49" s="93"/>
+      <c r="B49" s="102"/>
       <c r="C49" s="59"/>
       <c r="D49" s="60"/>
       <c r="E49" s="60"/>
@@ -4780,10 +5106,10 @@
       <c r="J49" s="45"/>
       <c r="K49" s="45"/>
       <c r="L49" s="44"/>
-      <c r="M49" s="92" t="s">
+      <c r="M49" s="101" t="s">
         <v>22</v>
       </c>
-      <c r="N49" s="93"/>
+      <c r="N49" s="102"/>
       <c r="O49" s="59"/>
       <c r="P49" s="60"/>
       <c r="Q49" s="60"/>
@@ -4794,38 +5120,38 @@
       <c r="V49" s="1"/>
     </row>
     <row r="50" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="92" t="s">
+      <c r="A50" s="101" t="s">
         <v>23</v>
       </c>
-      <c r="B50" s="96"/>
-      <c r="C50" s="97"/>
-      <c r="D50" s="97"/>
-      <c r="E50" s="97"/>
-      <c r="F50" s="97"/>
-      <c r="G50" s="97"/>
-      <c r="H50" s="97"/>
-      <c r="I50" s="110"/>
+      <c r="B50" s="103"/>
+      <c r="C50" s="105"/>
+      <c r="D50" s="105"/>
+      <c r="E50" s="105"/>
+      <c r="F50" s="105"/>
+      <c r="G50" s="105"/>
+      <c r="H50" s="105"/>
+      <c r="I50" s="109"/>
       <c r="J50" s="40"/>
       <c r="K50" s="40"/>
       <c r="L50" s="1"/>
-      <c r="M50" s="92" t="s">
+      <c r="M50" s="101" t="s">
         <v>23</v>
       </c>
-      <c r="N50" s="96"/>
-      <c r="O50" s="97"/>
-      <c r="P50" s="97"/>
-      <c r="Q50" s="97"/>
-      <c r="R50" s="97"/>
-      <c r="S50" s="97"/>
-      <c r="T50" s="97"/>
-      <c r="U50" s="110"/>
+      <c r="N50" s="103"/>
+      <c r="O50" s="105"/>
+      <c r="P50" s="105"/>
+      <c r="Q50" s="105"/>
+      <c r="R50" s="105"/>
+      <c r="S50" s="105"/>
+      <c r="T50" s="105"/>
+      <c r="U50" s="109"/>
       <c r="V50" s="1"/>
     </row>
     <row r="51" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="92" t="s">
+      <c r="A51" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="B51" s="93"/>
+      <c r="B51" s="102"/>
       <c r="C51" s="54"/>
       <c r="D51" s="55"/>
       <c r="E51" s="55"/>
@@ -4839,10 +5165,10 @@
         <f t="shared" ref="L51:L53" si="9">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C51:I51)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M51" s="92" t="s">
+      <c r="M51" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="N51" s="93"/>
+      <c r="N51" s="102"/>
       <c r="O51" s="54"/>
       <c r="P51" s="55"/>
       <c r="Q51" s="55"/>
@@ -4856,10 +5182,10 @@
       </c>
     </row>
     <row r="52" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="94" t="s">
+      <c r="A52" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="B52" s="95"/>
+      <c r="B52" s="107"/>
       <c r="C52" s="57"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -4873,10 +5199,10 @@
         <f t="shared" si="9"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M52" s="92" t="s">
+      <c r="M52" s="101" t="s">
         <v>8</v>
       </c>
-      <c r="N52" s="93"/>
+      <c r="N52" s="102"/>
       <c r="O52" s="57"/>
       <c r="P52" s="1"/>
       <c r="Q52" s="1"/>
@@ -4890,10 +5216,10 @@
       </c>
     </row>
     <row r="53" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="92" t="s">
+      <c r="A53" s="101" t="s">
         <v>21</v>
       </c>
-      <c r="B53" s="93"/>
+      <c r="B53" s="102"/>
       <c r="C53" s="57"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -4907,10 +5233,10 @@
         <f t="shared" si="9"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M53" s="92" t="s">
+      <c r="M53" s="101" t="s">
         <v>21</v>
       </c>
-      <c r="N53" s="93"/>
+      <c r="N53" s="102"/>
       <c r="O53" s="57"/>
       <c r="P53" s="1"/>
       <c r="Q53" s="1"/>
@@ -4924,10 +5250,10 @@
       </c>
     </row>
     <row r="54" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="92" t="s">
+      <c r="A54" s="101" t="s">
         <v>22</v>
       </c>
-      <c r="B54" s="93"/>
+      <c r="B54" s="102"/>
       <c r="C54" s="59"/>
       <c r="D54" s="60"/>
       <c r="E54" s="60"/>
@@ -4938,10 +5264,10 @@
       <c r="J54" s="40"/>
       <c r="K54" s="40"/>
       <c r="L54" s="1"/>
-      <c r="M54" s="92" t="s">
+      <c r="M54" s="101" t="s">
         <v>22</v>
       </c>
-      <c r="N54" s="93"/>
+      <c r="N54" s="102"/>
       <c r="O54" s="59"/>
       <c r="P54" s="60"/>
       <c r="Q54" s="60"/>
@@ -4952,38 +5278,38 @@
       <c r="V54" s="1"/>
     </row>
     <row r="55" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="92" t="s">
+      <c r="A55" s="101" t="s">
         <v>24</v>
       </c>
-      <c r="B55" s="96"/>
-      <c r="C55" s="97"/>
-      <c r="D55" s="97"/>
-      <c r="E55" s="97"/>
-      <c r="F55" s="97"/>
-      <c r="G55" s="97"/>
-      <c r="H55" s="97"/>
-      <c r="I55" s="110"/>
+      <c r="B55" s="103"/>
+      <c r="C55" s="105"/>
+      <c r="D55" s="105"/>
+      <c r="E55" s="105"/>
+      <c r="F55" s="105"/>
+      <c r="G55" s="105"/>
+      <c r="H55" s="105"/>
+      <c r="I55" s="109"/>
       <c r="J55" s="40"/>
       <c r="K55" s="40"/>
       <c r="L55" s="1"/>
-      <c r="M55" s="92" t="s">
+      <c r="M55" s="101" t="s">
         <v>23</v>
       </c>
-      <c r="N55" s="96"/>
-      <c r="O55" s="97"/>
-      <c r="P55" s="97"/>
-      <c r="Q55" s="97"/>
-      <c r="R55" s="97"/>
-      <c r="S55" s="97"/>
-      <c r="T55" s="97"/>
-      <c r="U55" s="110"/>
+      <c r="N55" s="103"/>
+      <c r="O55" s="105"/>
+      <c r="P55" s="105"/>
+      <c r="Q55" s="105"/>
+      <c r="R55" s="105"/>
+      <c r="S55" s="105"/>
+      <c r="T55" s="105"/>
+      <c r="U55" s="109"/>
       <c r="V55" s="1"/>
     </row>
     <row r="56" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="92" t="s">
+      <c r="A56" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="B56" s="93"/>
+      <c r="B56" s="102"/>
       <c r="C56"/>
       <c r="D56"/>
       <c r="E56"/>
@@ -4997,10 +5323,10 @@
         <f t="shared" ref="L56:L58" si="11">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C56:I56)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M56" s="92" t="s">
+      <c r="M56" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="N56" s="93"/>
+      <c r="N56" s="102"/>
       <c r="O56"/>
       <c r="P56"/>
       <c r="Q56"/>
@@ -5014,10 +5340,10 @@
       </c>
     </row>
     <row r="57" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="94" t="s">
+      <c r="A57" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="B57" s="95"/>
+      <c r="B57" s="107"/>
       <c r="C57"/>
       <c r="D57"/>
       <c r="E57"/>
@@ -5031,10 +5357,10 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M57" s="92" t="s">
+      <c r="M57" s="101" t="s">
         <v>8</v>
       </c>
-      <c r="N57" s="93"/>
+      <c r="N57" s="102"/>
       <c r="O57"/>
       <c r="P57"/>
       <c r="Q57"/>
@@ -5048,10 +5374,10 @@
       </c>
     </row>
     <row r="58" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="92" t="s">
+      <c r="A58" s="101" t="s">
         <v>21</v>
       </c>
-      <c r="B58" s="93"/>
+      <c r="B58" s="102"/>
       <c r="C58"/>
       <c r="D58"/>
       <c r="E58"/>
@@ -5065,10 +5391,10 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M58" s="92" t="s">
+      <c r="M58" s="101" t="s">
         <v>21</v>
       </c>
-      <c r="N58" s="93"/>
+      <c r="N58" s="102"/>
       <c r="O58"/>
       <c r="P58"/>
       <c r="Q58"/>
@@ -5082,10 +5408,10 @@
       </c>
     </row>
     <row r="59" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="92" t="s">
+      <c r="A59" s="101" t="s">
         <v>22</v>
       </c>
-      <c r="B59" s="93"/>
+      <c r="B59" s="102"/>
       <c r="C59" s="86"/>
       <c r="D59" s="87"/>
       <c r="E59" s="87"/>
@@ -5096,10 +5422,10 @@
       <c r="J59" s="40"/>
       <c r="K59" s="40"/>
       <c r="L59" s="1"/>
-      <c r="M59" s="92" t="s">
+      <c r="M59" s="101" t="s">
         <v>22</v>
       </c>
-      <c r="N59" s="93"/>
+      <c r="N59" s="102"/>
       <c r="O59" s="86"/>
       <c r="P59" s="87"/>
       <c r="Q59" s="87"/>
@@ -5125,6 +5451,70 @@
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="M59:N59"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="M56:N56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="M57:N57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="M58:N58"/>
+    <mergeCell ref="A6:A14"/>
+    <mergeCell ref="M6:M14"/>
+    <mergeCell ref="A36:A44"/>
+    <mergeCell ref="M36:M44"/>
+    <mergeCell ref="A55:I55"/>
+    <mergeCell ref="M55:U55"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="M25:U25"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="M53:N53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="M54:N54"/>
+    <mergeCell ref="A50:I50"/>
+    <mergeCell ref="M50:U50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="M51:N51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="M52:N52"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="M15:U15"/>
+    <mergeCell ref="M45:U45"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="M35:U35"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="M48:N48"/>
+    <mergeCell ref="M49:N49"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="M46:N46"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="A32:B32"/>
@@ -5141,70 +5531,6 @@
     <mergeCell ref="A15:I15"/>
     <mergeCell ref="A25:I25"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="M48:N48"/>
-    <mergeCell ref="M49:N49"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="M46:N46"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A45:I45"/>
-    <mergeCell ref="M15:U15"/>
-    <mergeCell ref="M45:U45"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="M35:U35"/>
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="M54:N54"/>
-    <mergeCell ref="A50:I50"/>
-    <mergeCell ref="M50:U50"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="M51:N51"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="M52:N52"/>
-    <mergeCell ref="A6:A14"/>
-    <mergeCell ref="M6:M14"/>
-    <mergeCell ref="A36:A44"/>
-    <mergeCell ref="M36:M44"/>
-    <mergeCell ref="A55:I55"/>
-    <mergeCell ref="M55:U55"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="M25:U25"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="M53:N53"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="M59:N59"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="M56:N56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="M57:N57"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="M58:N58"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C2:I4 C6:I14 C16:I19 C21:I24 C26:I29">
@@ -5276,17 +5602,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C9:I9">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="23">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5320,17 +5646,17 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C12:I12">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="25">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -5666,20 +5992,20 @@
   <sheetData>
     <row r="1" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="B2" s="112" t="s">
+      <c r="B2" s="114" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="118"/>
-      <c r="D2" s="115" t="s">
+      <c r="C2" s="120"/>
+      <c r="D2" s="117" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="117"/>
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="119"/>
     </row>
     <row r="3" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="114"/>
-      <c r="C3" s="119"/>
+      <c r="B3" s="116"/>
+      <c r="C3" s="121"/>
       <c r="D3" s="77" t="s">
         <v>27</v>
       </c>
@@ -5732,20 +6058,20 @@
       <c r="G7" s="25"/>
     </row>
     <row r="8" spans="2:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="B8" s="112" t="s">
+      <c r="B8" s="114" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="118"/>
-      <c r="D8" s="115" t="s">
+      <c r="C8" s="120"/>
+      <c r="D8" s="117" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="116"/>
-      <c r="F8" s="116"/>
-      <c r="G8" s="117"/>
+      <c r="E8" s="118"/>
+      <c r="F8" s="118"/>
+      <c r="G8" s="119"/>
     </row>
     <row r="9" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="114"/>
-      <c r="C9" s="119"/>
+      <c r="B9" s="116"/>
+      <c r="C9" s="121"/>
       <c r="D9" s="77" t="s">
         <v>27</v>
       </c>
@@ -5760,7 +6086,7 @@
       </c>
     </row>
     <row r="10" spans="2:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="B10" s="112" t="s">
+      <c r="B10" s="114" t="s">
         <v>30</v>
       </c>
       <c r="C10" s="70" t="s">
@@ -5772,7 +6098,7 @@
       <c r="G10" s="81"/>
     </row>
     <row r="11" spans="2:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="B11" s="113"/>
+      <c r="B11" s="115"/>
       <c r="C11" s="72" t="s">
         <v>28</v>
       </c>
@@ -5782,7 +6108,7 @@
       <c r="G11" s="73"/>
     </row>
     <row r="12" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="114"/>
+      <c r="B12" s="116"/>
       <c r="C12" s="83" t="s">
         <v>29</v>
       </c>

--- a/results_(stress_test)_baselines/summary.xlsx
+++ b/results_(stress_test)_baselines/summary.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RnD_Repo\Research_Engineeirng\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_baselines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0BD73A1-3C2C-41D5-84E5-5EAED4D67950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4162CE8-64BE-4568-A20A-1A9F39FAEBC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="639" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="639" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="partialdata_20260429_unf_idx" sheetId="6" r:id="rId1"/>
+    <sheet name="partialdata_20260618_unf_idx" sheetId="6" r:id="rId1"/>
     <sheet name="figure" sheetId="8" r:id="rId2"/>
     <sheet name="fullldata_20260524_spt_idx" sheetId="5" r:id="rId3"/>
     <sheet name="confusion_mtx" sheetId="7" r:id="rId4"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="41">
   <si>
     <t>Accuracy</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -204,6 +204,31 @@
     <t>AUC</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>Accuracy
+(NRR=0.0625)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy
+(NRR=0.125)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy
+(NRR=0.25)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy
+(NRR=1)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Accuracy
+(NRR=0.5)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -264,7 +289,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -430,11 +455,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -590,9 +626,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -602,18 +635,12 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -624,9 +651,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -647,103 +671,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -758,38 +688,150 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1071,7 +1113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4687D530-62F3-45D6-8CBF-3B0602E24BE5}">
-  <dimension ref="A1:R45"/>
+  <dimension ref="A1:R55"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25" style="10" customWidth="1"/>
@@ -1135,23 +1177,23 @@
       <c r="R1" s="12"/>
     </row>
     <row r="2" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="94" t="s">
+      <c r="A2" s="114" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="95"/>
-      <c r="C2" s="125">
+      <c r="B2" s="115"/>
+      <c r="C2" s="89">
         <v>92.97270449283009</v>
       </c>
-      <c r="D2" s="126">
+      <c r="D2" s="90">
         <v>92.656851126163161</v>
       </c>
-      <c r="E2" s="126">
+      <c r="E2" s="90">
         <v>90.612485113769722</v>
       </c>
-      <c r="F2" s="126">
+      <c r="F2" s="90">
         <v>76.890048068466555</v>
       </c>
-      <c r="G2" s="127">
+      <c r="G2" s="91">
         <v>57.431157132270449</v>
       </c>
       <c r="H2" s="23" cm="1">
@@ -1166,23 +1208,23 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:G2)&amp;","</f>
         <v xml:space="preserve">    92.9727044928301, 92.6568511261632, 90.6124851137697, 76.8900480684666, 57.4311571322704,</v>
       </c>
-      <c r="K2" s="94" t="s">
+      <c r="K2" s="114" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="95"/>
-      <c r="M2" s="125">
+      <c r="L2" s="115"/>
+      <c r="M2" s="89">
         <v>3.6723191410127392</v>
       </c>
-      <c r="N2" s="126">
+      <c r="N2" s="90">
         <v>3.8557140126956959</v>
       </c>
-      <c r="O2" s="126">
+      <c r="O2" s="90">
         <v>4.1717853309388913</v>
       </c>
-      <c r="P2" s="126">
+      <c r="P2" s="90">
         <v>8.1206319222896362</v>
       </c>
-      <c r="Q2" s="127">
+      <c r="Q2" s="91">
         <v>8.7326493747450371</v>
       </c>
       <c r="R2" s="12" t="str">
@@ -1191,23 +1233,23 @@
       </c>
     </row>
     <row r="3" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="94" t="s">
+      <c r="A3" s="114" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="95"/>
-      <c r="C3" s="128">
+      <c r="B3" s="115"/>
+      <c r="C3" s="92">
         <v>93.550650668835075</v>
       </c>
-      <c r="D3" s="124">
+      <c r="D3">
         <v>92.282219857726602</v>
       </c>
-      <c r="E3" s="124">
+      <c r="E3">
         <v>90.501679656975099</v>
       </c>
-      <c r="F3" s="124">
+      <c r="F3">
         <v>72.805808585426078</v>
       </c>
-      <c r="G3" s="129">
+      <c r="G3" s="93">
         <v>54.064066298151367</v>
       </c>
       <c r="H3" s="23" cm="1">
@@ -1222,23 +1264,23 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:G3)&amp;","</f>
         <v xml:space="preserve">    93.5506506688351, 92.2822198577266, 90.5016796569751, 72.8058085854261, 54.0640662981514,</v>
       </c>
-      <c r="K3" s="94" t="s">
+      <c r="K3" s="114" t="s">
         <v>6</v>
       </c>
-      <c r="L3" s="95"/>
-      <c r="M3" s="128">
+      <c r="L3" s="115"/>
+      <c r="M3" s="92">
         <v>3.5444962758226279</v>
       </c>
-      <c r="N3" s="124">
+      <c r="N3">
         <v>3.640571601682856</v>
       </c>
-      <c r="O3" s="124">
+      <c r="O3">
         <v>3.5241233819887818</v>
       </c>
-      <c r="P3" s="124">
+      <c r="P3">
         <v>9.1245390051568016</v>
       </c>
-      <c r="Q3" s="129">
+      <c r="Q3" s="93">
         <v>7.5991148630492704</v>
       </c>
       <c r="R3" s="12" t="str">
@@ -1247,23 +1289,23 @@
       </c>
     </row>
     <row r="4" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="98" t="s">
+      <c r="A4" s="119" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="99"/>
-      <c r="C4" s="128">
+      <c r="B4" s="120"/>
+      <c r="C4" s="92">
         <v>88.646029233240199</v>
       </c>
-      <c r="D4" s="124">
+      <c r="D4">
         <v>87.588003933136662</v>
       </c>
-      <c r="E4" s="124">
+      <c r="E4">
         <v>87.102273087714138</v>
       </c>
-      <c r="F4" s="124">
+      <c r="F4">
         <v>74.826714187262283</v>
       </c>
-      <c r="G4" s="129">
+      <c r="G4" s="93">
         <v>50.055245575942109</v>
       </c>
       <c r="H4" s="34" cm="1">
@@ -1278,23 +1320,23 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C4:G4)&amp;","</f>
         <v xml:space="preserve">    88.6460292332402, 87.5880039331367, 87.1022730877141, 74.8267141872623, 50.0552455759421,</v>
       </c>
-      <c r="K4" s="98" t="s">
+      <c r="K4" s="119" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="99"/>
-      <c r="M4" s="128">
+      <c r="L4" s="120"/>
+      <c r="M4" s="92">
         <v>3.1531095164540388</v>
       </c>
-      <c r="N4" s="124">
+      <c r="N4">
         <v>2.2977524920825498</v>
       </c>
-      <c r="O4" s="124">
+      <c r="O4">
         <v>1.6498123709550609</v>
       </c>
-      <c r="P4" s="124">
+      <c r="P4">
         <v>2.8561346399896621</v>
       </c>
-      <c r="Q4" s="129">
+      <c r="Q4" s="93">
         <v>1.6635727988470741</v>
       </c>
       <c r="R4" s="12" t="str">
@@ -1303,693 +1345,703 @@
       </c>
     </row>
     <row r="5" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="94" t="s">
+      <c r="A5" s="114" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="96"/>
-      <c r="C5" s="96"/>
-      <c r="D5" s="96"/>
-      <c r="E5" s="96"/>
-      <c r="F5" s="96"/>
-      <c r="G5" s="95"/>
+      <c r="B5" s="116"/>
+      <c r="C5" s="116"/>
+      <c r="D5" s="116"/>
+      <c r="E5" s="116"/>
+      <c r="F5" s="116"/>
+      <c r="G5" s="115"/>
       <c r="H5" s="34"/>
       <c r="I5" s="34"/>
       <c r="J5" s="12"/>
-      <c r="K5" s="94" t="s">
+      <c r="K5" s="114" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="96"/>
-      <c r="M5" s="96"/>
-      <c r="N5" s="96"/>
-      <c r="O5" s="96"/>
-      <c r="P5" s="96"/>
-      <c r="Q5" s="95"/>
+      <c r="L5" s="116"/>
+      <c r="M5" s="116"/>
+      <c r="N5" s="116"/>
+      <c r="O5" s="116"/>
+      <c r="P5" s="116"/>
+      <c r="Q5" s="115"/>
       <c r="R5" s="12"/>
     </row>
-    <row r="6" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="92" t="s">
+    <row r="6" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="119" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="144" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="128">
-        <v>93.358985227669237</v>
-      </c>
-      <c r="D6" s="124">
-        <v>92.785690187631374</v>
-      </c>
-      <c r="E6" s="124">
-        <v>91.279001836809442</v>
-      </c>
-      <c r="F6" s="124">
-        <v>77.243569004345488</v>
-      </c>
-      <c r="G6" s="129">
-        <v>56.641689518652129</v>
+      <c r="B6" s="103" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" s="89">
+        <v>93.375631853793436</v>
+      </c>
+      <c r="D6" s="90">
+        <v>92.792878831131745</v>
+      </c>
+      <c r="E6" s="90">
+        <v>91.094066557669166</v>
+      </c>
+      <c r="F6" s="90">
+        <v>74.369665827559075</v>
+      </c>
+      <c r="G6" s="91">
+        <v>56.35401113619784</v>
       </c>
       <c r="H6" s="34" cm="1">
         <f t="array" ref="H6">-SUMPRODUCT((D1:F1-C1:E1)*(C6:E6+D6:F6)/2)</f>
-        <v>80.076916034452438</v>
+        <v>79.869479118908174</v>
       </c>
       <c r="I6" s="34" cm="1">
         <f t="array" ref="I6">-SUMPRODUCT((D1:G1-C1:F1)*(C6:F6+D6:G6)/2)</f>
-        <v>84.260830363296108</v>
-      </c>
-      <c r="J6" s="12" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C6:G6)&amp;","</f>
-        <v xml:space="preserve">    93.3589852276692, 92.7856901876314, 91.2790018368094, 77.2435690043455, 56.6416895186521,</v>
-      </c>
-      <c r="K6" s="92" t="s">
+        <v>83.954594024025582</v>
+      </c>
+      <c r="J6" s="12"/>
+      <c r="K6" s="119" t="s">
         <v>11</v>
       </c>
-      <c r="L6" s="144" t="s">
+      <c r="L6" s="103" t="s">
+        <v>17</v>
+      </c>
+      <c r="M6" s="89">
+        <v>3.4841780245944278</v>
+      </c>
+      <c r="N6" s="90">
+        <v>3.7171339527240979</v>
+      </c>
+      <c r="O6" s="90">
+        <v>3.5950208209222092</v>
+      </c>
+      <c r="P6" s="90">
+        <v>8.5619397568121691</v>
+      </c>
+      <c r="Q6" s="91">
+        <v>8.7436032668579529</v>
+      </c>
+      <c r="R6" s="12"/>
+    </row>
+    <row r="7" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="121"/>
+      <c r="B7" s="103" t="s">
         <v>13</v>
       </c>
-      <c r="M6" s="128">
-        <v>3.5292136776947389</v>
-      </c>
-      <c r="N6" s="124">
-        <v>3.7787197360632829</v>
-      </c>
-      <c r="O6" s="124">
-        <v>3.589155414302748</v>
-      </c>
-      <c r="P6" s="124">
-        <v>7.7490040503559836</v>
-      </c>
-      <c r="Q6" s="129">
-        <v>8.6647795337348459</v>
-      </c>
-      <c r="R6" s="12" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M6:Q6)&amp;","</f>
-        <v xml:space="preserve">    3.52921367769474, 3.77871973606328, 3.58915541430275, 7.74900405035598, 8.66477953373485,</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7" s="128">
-        <v>92.744346116027529</v>
-      </c>
-      <c r="D7" s="124">
-        <v>92.328416912487711</v>
-      </c>
-      <c r="E7" s="124">
-        <v>91.156108616856514</v>
-      </c>
-      <c r="F7" s="124">
-        <v>82.307782362592519</v>
-      </c>
-      <c r="G7" s="129">
-        <v>57.694504277718679</v>
+      <c r="C7" s="92">
+        <v>93.358985227669237</v>
+      </c>
+      <c r="D7" s="141">
+        <v>92.785690187631374</v>
+      </c>
+      <c r="E7" s="141">
+        <v>91.279001836809442</v>
+      </c>
+      <c r="F7" s="141">
+        <v>77.243569004345488</v>
+      </c>
+      <c r="G7" s="93">
+        <v>56.641689518652129</v>
       </c>
       <c r="H7" s="34" cm="1">
         <f t="array" ref="H7">-SUMPRODUCT((D1:F1-C1:E1)*(C7:E7+D7:F7)/2)</f>
-        <v>80.045249634512402</v>
+        <v>80.076916034452438</v>
       </c>
       <c r="I7" s="34" cm="1">
         <f t="array" ref="I7">-SUMPRODUCT((D1:G1-C1:F1)*(C7:F7+D7:G7)/2)</f>
-        <v>84.420321092022121</v>
+        <v>84.260830363296108</v>
       </c>
       <c r="J7" s="12" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C7:G7)&amp;","</f>
-        <v xml:space="preserve">    92.7443461160275, 92.3284169124877, 91.1561086168565, 82.3077823625925, 57.6945042777187,</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M7" s="128">
-        <v>3.3427481085122568</v>
-      </c>
-      <c r="N7" s="124">
-        <v>3.376440347285802</v>
-      </c>
-      <c r="O7" s="124">
-        <v>3.0132050938587081</v>
-      </c>
-      <c r="P7" s="124">
-        <v>4.6775599948055158</v>
-      </c>
-      <c r="Q7" s="129">
-        <v>6.3264357320363649</v>
+        <v xml:space="preserve">    93.3589852276692, 92.7856901876314, 91.2790018368094, 77.2435690043455, 56.6416895186521,</v>
+      </c>
+      <c r="K7" s="121"/>
+      <c r="L7" s="103" t="s">
+        <v>13</v>
+      </c>
+      <c r="M7" s="92">
+        <v>3.5292136776947389</v>
+      </c>
+      <c r="N7" s="141">
+        <v>3.7787197360632829</v>
+      </c>
+      <c r="O7" s="141">
+        <v>3.589155414302748</v>
+      </c>
+      <c r="P7" s="141">
+        <v>7.7490040503559836</v>
+      </c>
+      <c r="Q7" s="93">
+        <v>8.6647795337348459</v>
       </c>
       <c r="R7" s="12" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M7:Q7)&amp;","</f>
-        <v xml:space="preserve">    3.34274810851226, 3.3764403472858, 3.01320509385871, 4.67755999480552, 6.32643573203636,</v>
+        <v xml:space="preserve">    3.52921367769474, 3.77871973606328, 3.58915541430275, 7.74900405035598, 8.66477953373485,</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>11</v>
-      </c>
+      <c r="A8" s="121"/>
       <c r="B8" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="128">
-        <v>93.578171091445412</v>
-      </c>
-      <c r="D8" s="124">
-        <v>92.721736347200235</v>
-      </c>
-      <c r="E8" s="124">
-        <v>90.919630215947663</v>
-      </c>
-      <c r="F8" s="124">
-        <v>73.42964039481312</v>
-      </c>
-      <c r="G8" s="129">
-        <v>56.559615567608724</v>
+        <v>14</v>
+      </c>
+      <c r="C8" s="92">
+        <v>92.744346116027529</v>
+      </c>
+      <c r="D8" s="141">
+        <v>92.328416912487711</v>
+      </c>
+      <c r="E8" s="141">
+        <v>91.156108616856514</v>
+      </c>
+      <c r="F8" s="141">
+        <v>82.307782362592519</v>
+      </c>
+      <c r="G8" s="93">
+        <v>57.694504277718679</v>
       </c>
       <c r="H8" s="34" cm="1">
         <f t="array" ref="H8">-SUMPRODUCT((D1:F1-C1:E1)*(C8:E8+D8:F8)/2)</f>
-        <v>79.80197709322745</v>
+        <v>80.045249634512402</v>
       </c>
       <c r="I8" s="34" cm="1">
         <f t="array" ref="I8">-SUMPRODUCT((D1:G1-C1:F1)*(C8:F8+D8:G8)/2)</f>
-        <v>83.864141342053131</v>
-      </c>
-      <c r="J8" s="12"/>
-      <c r="K8" s="7" t="s">
-        <v>11</v>
-      </c>
+        <v>84.420321092022121</v>
+      </c>
+      <c r="J8" s="12" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C8:G8)&amp;","</f>
+        <v xml:space="preserve">    92.7443461160275, 92.3284169124877, 91.1561086168565, 82.3077823625925, 57.6945042777187,</v>
+      </c>
+      <c r="K8" s="121"/>
       <c r="L8" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="M8" s="128">
-        <v>3.4211604643278899</v>
-      </c>
-      <c r="N8" s="124">
-        <v>3.758697386182225</v>
-      </c>
-      <c r="O8" s="124">
-        <v>3.9384751732193859</v>
-      </c>
-      <c r="P8" s="124">
-        <v>8.9824743171696255</v>
-      </c>
-      <c r="Q8" s="129">
-        <v>8.2082515511175735</v>
+        <v>14</v>
+      </c>
+      <c r="M8" s="92">
+        <v>3.3427481085122568</v>
+      </c>
+      <c r="N8" s="141">
+        <v>3.376440347285802</v>
+      </c>
+      <c r="O8" s="141">
+        <v>3.0132050938587081</v>
+      </c>
+      <c r="P8" s="141">
+        <v>4.6775599948055158</v>
+      </c>
+      <c r="Q8" s="93">
+        <v>6.3264357320363649</v>
       </c>
       <c r="R8" s="12" t="str">
-        <f t="shared" ref="R8:R9" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M8:Q8)&amp;","</f>
-        <v xml:space="preserve">    3.42116046432789, 3.75869738618223, 3.93847517321939, 8.98247431716963, 8.20825155111757,</v>
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M8:Q8)&amp;","</f>
+        <v xml:space="preserve">    3.34274810851226, 3.3764403472858, 3.01320509385871, 4.67755999480552, 6.32643573203636,</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="140" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="128">
-        <v>90.553588987217324</v>
-      </c>
-      <c r="D9" s="124">
-        <v>90.325467059980355</v>
-      </c>
-      <c r="E9" s="124">
-        <v>89.668636118536241</v>
-      </c>
-      <c r="F9" s="124">
-        <v>78.678561233228677</v>
-      </c>
-      <c r="G9" s="129">
-        <v>53.098925307889047</v>
+      <c r="A9" s="121"/>
+      <c r="B9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="92">
+        <v>93.721730580137674</v>
+      </c>
+      <c r="D9" s="141">
+        <v>92.415934970602393</v>
+      </c>
+      <c r="E9" s="141">
+        <v>90.686860036274823</v>
+      </c>
+      <c r="F9" s="141">
+        <v>75.782143444147451</v>
+      </c>
+      <c r="G9" s="93">
+        <v>55.768484156437339</v>
       </c>
       <c r="H9" s="34" cm="1">
         <f t="array" ref="H9">-SUMPRODUCT((D1:F1-C1:E1)*(C9:E9+D9:F9)/2)</f>
-        <v>78.240726743599296</v>
+        <v>79.826578481071053</v>
       </c>
       <c r="I9" s="34" cm="1">
         <f t="array" ref="I9">-SUMPRODUCT((D1:G1-C1:F1)*(C9:F9+D9:G9)/2)</f>
+        <v>83.937535593589331</v>
+      </c>
+      <c r="J9" s="12"/>
+      <c r="K9" s="121"/>
+      <c r="L9" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="M9" s="92">
+        <v>3.5340996284974531</v>
+      </c>
+      <c r="N9" s="141">
+        <v>3.480694084881371</v>
+      </c>
+      <c r="O9" s="141">
+        <v>3.5404972441590532</v>
+      </c>
+      <c r="P9" s="141">
+        <v>8.2748920802292076</v>
+      </c>
+      <c r="Q9" s="93">
+        <v>8.6222095079337446</v>
+      </c>
+      <c r="R9" s="12"/>
+    </row>
+    <row r="10" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="121"/>
+      <c r="B10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="92">
+        <v>93.578171091445412</v>
+      </c>
+      <c r="D10" s="141">
+        <v>92.721736347200235</v>
+      </c>
+      <c r="E10" s="141">
+        <v>90.919630215947663</v>
+      </c>
+      <c r="F10" s="141">
+        <v>73.42964039481312</v>
+      </c>
+      <c r="G10" s="93">
+        <v>56.559615567608724</v>
+      </c>
+      <c r="H10" s="34" cm="1">
+        <f t="array" ref="H10">-SUMPRODUCT((D1:F1-C1:E1)*(C10:E10+D10:F10)/2)</f>
+        <v>79.80197709322745</v>
+      </c>
+      <c r="I10" s="34" cm="1">
+        <f t="array" ref="I10">-SUMPRODUCT((D1:G1-C1:F1)*(C10:F10+D10:G10)/2)</f>
+        <v>83.864141342053131</v>
+      </c>
+      <c r="J10" s="12"/>
+      <c r="K10" s="121"/>
+      <c r="L10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="M10" s="92">
+        <v>3.4211604643278899</v>
+      </c>
+      <c r="N10" s="141">
+        <v>3.758697386182225</v>
+      </c>
+      <c r="O10" s="141">
+        <v>3.9384751732193859</v>
+      </c>
+      <c r="P10" s="141">
+        <v>8.9824743171696255</v>
+      </c>
+      <c r="Q10" s="93">
+        <v>8.2082515511175735</v>
+      </c>
+      <c r="R10" s="12" t="str">
+        <f t="shared" ref="R10:R13" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M10:Q10)&amp;","</f>
+        <v xml:space="preserve">    3.42116046432789, 3.75869738618223, 3.93847517321939, 8.98247431716963, 8.20825155111757,</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="121"/>
+      <c r="B11" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="92">
+        <v>91.299901671583086</v>
+      </c>
+      <c r="D11" s="141">
+        <v>90.822048633638715</v>
+      </c>
+      <c r="E11" s="141">
+        <v>89.932372540708258</v>
+      </c>
+      <c r="F11" s="141">
+        <v>80.986383965259208</v>
+      </c>
+      <c r="G11" s="93">
+        <v>55.071488507686048</v>
+      </c>
+      <c r="H11" s="34" cm="1">
+        <f t="array" ref="H11">-SUMPRODUCT((D1:F1-C1:E1)*(C11:E11+D11:F11)/2)</f>
+        <v>78.807212504721775</v>
+      </c>
+      <c r="I11" s="34" cm="1">
+        <f t="array" ref="I11">-SUMPRODUCT((D1:G1-C1:F1)*(C11:F11+D11:G11)/2)</f>
+        <v>83.059021019501316</v>
+      </c>
+      <c r="J11" s="12"/>
+      <c r="K11" s="121"/>
+      <c r="L11" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" s="92">
+        <v>3.058139598469626</v>
+      </c>
+      <c r="N11" s="141">
+        <v>2.6470632106161909</v>
+      </c>
+      <c r="O11" s="141">
+        <v>2.660097338781473</v>
+      </c>
+      <c r="P11" s="141">
+        <v>4.2324186928534564</v>
+      </c>
+      <c r="Q11" s="93">
+        <v>6.3408360836535147</v>
+      </c>
+      <c r="R11" s="12"/>
+    </row>
+    <row r="12" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="121"/>
+      <c r="B12" s="101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="92">
+        <v>88.345132743362853</v>
+      </c>
+      <c r="D12" s="141">
+        <v>87.267453294001967</v>
+      </c>
+      <c r="E12" s="141">
+        <v>87.102446099591404</v>
+      </c>
+      <c r="F12" s="141">
+        <v>75.414922851120394</v>
+      </c>
+      <c r="G12" s="93">
+        <v>50.409063515543693</v>
+      </c>
+      <c r="H12" s="34" cm="1">
+        <f t="array" ref="H12">-SUMPRODUCT((D1:F1-C1:E1)*(C12:E12+D12:F12)/2)</f>
+        <v>75.856719492959854</v>
+      </c>
+      <c r="I12" s="34" cm="1">
+        <f t="array" ref="I12">-SUMPRODUCT((D1:G1-C1:F1)*(C12:F12+D12:G12)/2)</f>
+        <v>79.788719066918105</v>
+      </c>
+      <c r="J12" s="12"/>
+      <c r="K12" s="121"/>
+      <c r="L12" s="101" t="s">
+        <v>16</v>
+      </c>
+      <c r="M12" s="92">
+        <v>2.983926605181269</v>
+      </c>
+      <c r="N12" s="141">
+        <v>2.3996463413185389</v>
+      </c>
+      <c r="O12" s="141">
+        <v>1.62526252442654</v>
+      </c>
+      <c r="P12" s="141">
+        <v>3.3792106059866658</v>
+      </c>
+      <c r="Q12" s="93">
+        <v>1.3738116379133549</v>
+      </c>
+      <c r="R12" s="12"/>
+    </row>
+    <row r="13" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="121"/>
+      <c r="B13" s="101" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="92">
+        <v>90.553588987217324</v>
+      </c>
+      <c r="D13" s="141">
+        <v>90.325467059980355</v>
+      </c>
+      <c r="E13" s="141">
+        <v>89.668636118536241</v>
+      </c>
+      <c r="F13" s="141">
+        <v>78.678561233228677</v>
+      </c>
+      <c r="G13" s="93">
+        <v>53.098925307889047</v>
+      </c>
+      <c r="H13" s="34" cm="1">
+        <f t="array" ref="H13">-SUMPRODUCT((D1:F1-C1:E1)*(C13:E13+D13:F13)/2)</f>
+        <v>78.240726743599296</v>
+      </c>
+      <c r="I13" s="34" cm="1">
+        <f t="array" ref="I13">-SUMPRODUCT((D1:G1-C1:F1)*(C13:F13+D13:G13)/2)</f>
         <v>82.358773198009231</v>
       </c>
-      <c r="J9" s="12"/>
-      <c r="K9" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="L9" s="140" t="s">
+      <c r="J13" s="12"/>
+      <c r="K13" s="121"/>
+      <c r="L13" s="101" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="128">
+      <c r="M13" s="92">
         <v>2.5990157411770438</v>
       </c>
-      <c r="N9" s="124">
+      <c r="N13" s="141">
         <v>2.3843919339500612</v>
       </c>
-      <c r="O9" s="124">
+      <c r="O13" s="141">
         <v>2.4318730481068318</v>
       </c>
-      <c r="P9" s="124">
+      <c r="P13" s="141">
         <v>3.814135483602267</v>
       </c>
-      <c r="Q9" s="129">
+      <c r="Q13" s="93">
         <v>3.5742222382122981</v>
       </c>
-      <c r="R9" s="12" t="str">
+      <c r="R13" s="12" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">    2.59901574117704, 2.38439193395006, 2.43187304810683, 3.81413548360227, 3.5742222382123,</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="94" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="96"/>
-      <c r="C10" s="96"/>
-      <c r="D10" s="96"/>
-      <c r="E10" s="96"/>
-      <c r="F10" s="96"/>
-      <c r="G10" s="95"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="34"/>
-      <c r="J10" s="12"/>
-      <c r="K10" s="94" t="s">
-        <v>20</v>
-      </c>
-      <c r="L10" s="96"/>
-      <c r="M10" s="96"/>
-      <c r="N10" s="96"/>
-      <c r="O10" s="96"/>
-      <c r="P10" s="96"/>
-      <c r="Q10" s="95"/>
-      <c r="R10" s="12"/>
-    </row>
-    <row r="11" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="111" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="143"/>
-      <c r="C11" s="128">
-        <v>93.207752662220258</v>
-      </c>
-      <c r="D11" s="124">
-        <v>92.783034455315345</v>
-      </c>
-      <c r="E11" s="124">
-        <v>90.565884364628303</v>
-      </c>
-      <c r="F11" s="124">
-        <v>73.076886478256739</v>
-      </c>
-      <c r="G11" s="129">
-        <v>58.556994437668138</v>
-      </c>
-      <c r="H11" s="34" cm="1">
-        <f t="array" ref="H11">-SUMPRODUCT((D1:F1-C1:E1)*(C11:E11+D11:F11)/2)</f>
-        <v>79.643984809557168</v>
-      </c>
-      <c r="I11" s="34" cm="1">
-        <f t="array" ref="I11">-SUMPRODUCT((D1:G1-C1:F1)*(C11:F11+D11:G11)/2)</f>
-        <v>83.757543588179814</v>
-      </c>
-      <c r="J11" s="12" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C11:G11)&amp;","</f>
-        <v xml:space="preserve">    93.2077526622203, 92.7830344553153, 90.5658843646283, 73.0768864782567, 58.5569944376681,</v>
-      </c>
-      <c r="K11" s="111" t="s">
-        <v>7</v>
-      </c>
-      <c r="L11" s="143"/>
-      <c r="M11" s="128">
-        <v>4.081079160307894</v>
-      </c>
-      <c r="N11" s="124">
-        <v>3.9215668791224498</v>
-      </c>
-      <c r="O11" s="124">
-        <v>3.873470124738835</v>
-      </c>
-      <c r="P11" s="124">
-        <v>9.0889689998586825</v>
-      </c>
-      <c r="Q11" s="129">
-        <v>9.0192886420696112</v>
-      </c>
-      <c r="R11" s="12" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M11:Q11)&amp;","</f>
-        <v xml:space="preserve">    4.08107916030789, 3.92156687912245, 3.87347012473884, 9.08896899985868, 9.01928864206961,</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="98" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="99"/>
-      <c r="C12" s="128">
-        <v>93.534975792754821</v>
-      </c>
-      <c r="D12" s="124">
-        <v>92.336467731843129</v>
-      </c>
-      <c r="E12" s="124">
-        <v>88.593520128490155</v>
-      </c>
-      <c r="F12" s="124">
-        <v>71.045294509468079</v>
-      </c>
-      <c r="G12" s="129">
-        <v>53.467062863865607</v>
-      </c>
-      <c r="H12" s="34" cm="1">
-        <f t="array" ref="H12">-SUMPRODUCT((D1:F1-C1:E1)*(C12:E12+D12:F12)/2)</f>
-        <v>79.061535278563539</v>
-      </c>
-      <c r="I12" s="34" cm="1">
-        <f t="array" ref="I12">-SUMPRODUCT((D1:G1-C1:F1)*(C12:F12+D12:G12)/2)</f>
-        <v>82.952546446480213</v>
-      </c>
-      <c r="J12" s="12" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C12:G12)&amp;","</f>
-        <v xml:space="preserve">    93.5349757927548, 92.3364677318431, 88.5935201284902, 71.0452945094681, 53.4670628638656,</v>
-      </c>
-      <c r="K12" s="94" t="s">
-        <v>8</v>
-      </c>
-      <c r="L12" s="95"/>
-      <c r="M12" s="128">
-        <v>3.8494978151380188</v>
-      </c>
-      <c r="N12" s="124">
-        <v>3.7468317792042942</v>
-      </c>
-      <c r="O12" s="124">
-        <v>4.6420078579248552</v>
-      </c>
-      <c r="P12" s="124">
-        <v>10.247976510425289</v>
-      </c>
-      <c r="Q12" s="129">
-        <v>9.5145399413620808</v>
-      </c>
-      <c r="R12" s="12" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M12:Q12)&amp;","</f>
-        <v xml:space="preserve">    3.84949781513802, 3.74683177920429, 4.64200785792486, 10.2479765104253, 9.51453994136208,</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="94" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="95"/>
-      <c r="C13" s="128">
-        <v>93.005297046975599</v>
-      </c>
-      <c r="D13" s="124">
-        <v>91.902444369472647</v>
-      </c>
-      <c r="E13" s="124">
-        <v>89.116278399178753</v>
-      </c>
-      <c r="F13" s="124">
-        <v>72.258814234263852</v>
-      </c>
-      <c r="G13" s="129">
-        <v>53.843628981796257</v>
-      </c>
-      <c r="H13" s="34" cm="1">
-        <f t="array" ref="H13">-SUMPRODUCT((D1:F1-C1:E1)*(C13:E13+D13:F13)/2)</f>
-        <v>78.940218989783645</v>
-      </c>
-      <c r="I13" s="34" cm="1">
-        <f t="array" ref="I13">-SUMPRODUCT((D1:G1-C1:F1)*(C13:F13+D13:G13)/2)</f>
-        <v>82.880920340285527</v>
-      </c>
-      <c r="J13" s="12" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C13:G13)&amp;","</f>
-        <v xml:space="preserve">    93.0052970469756, 91.9024443694726, 89.1162783991788, 72.2588142342639, 53.8436289817963,</v>
-      </c>
-      <c r="K13" s="94" t="s">
-        <v>21</v>
-      </c>
-      <c r="L13" s="95"/>
-      <c r="M13" s="128">
-        <v>3.458803648865628</v>
-      </c>
-      <c r="N13" s="124">
-        <v>4.1139178681351494</v>
-      </c>
-      <c r="O13" s="124">
-        <v>4.3674865362294497</v>
-      </c>
-      <c r="P13" s="124">
-        <v>10.1810612930344</v>
-      </c>
-      <c r="Q13" s="129">
-        <v>8.6745540222164905</v>
-      </c>
-      <c r="R13" s="12" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M13:Q13)&amp;","</f>
-        <v xml:space="preserve">    3.45880364886563, 4.11391786813515, 4.36748653622945, 10.1810612930344, 8.67455402221649,</v>
-      </c>
-    </row>
     <row r="14" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="98" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="99"/>
-      <c r="C14" s="137"/>
-      <c r="D14" s="138"/>
-      <c r="E14" s="138"/>
-      <c r="F14" s="138"/>
-      <c r="G14" s="139"/>
+      <c r="A14" s="117"/>
+      <c r="B14" s="101" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="94">
+        <v>89.149459193706974</v>
+      </c>
+      <c r="D14" s="95">
+        <v>88.338249754178975</v>
+      </c>
+      <c r="E14" s="95">
+        <v>87.909618595316573</v>
+      </c>
+      <c r="F14" s="95">
+        <v>77.044259321735765</v>
+      </c>
+      <c r="G14" s="96">
+        <v>51.470476964910311</v>
+      </c>
       <c r="H14" s="34" cm="1">
         <f t="array" ref="H14">-SUMPRODUCT((D1:F1-C1:E1)*(C14:E14+D14:F14)/2)</f>
-        <v>0</v>
+        <v>76.712528150474199</v>
       </c>
       <c r="I14" s="34" cm="1">
         <f t="array" ref="I14">-SUMPRODUCT((D1:G1-C1:F1)*(C14:F14+D14:G14)/2)</f>
-        <v>0</v>
-      </c>
-      <c r="J14" s="12" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C14:G14)&amp;","</f>
-        <v xml:space="preserve">    ,</v>
-      </c>
-      <c r="K14" s="98" t="s">
-        <v>22</v>
-      </c>
-      <c r="L14" s="99"/>
-      <c r="M14" s="137"/>
-      <c r="N14" s="138"/>
-      <c r="O14" s="138"/>
-      <c r="P14" s="138"/>
-      <c r="Q14" s="139"/>
-      <c r="R14" s="12" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M14:Q14)&amp;","</f>
-        <v xml:space="preserve">    ,</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="94" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="96"/>
-      <c r="C15" s="96"/>
-      <c r="D15" s="96"/>
-      <c r="E15" s="96"/>
-      <c r="F15" s="96"/>
-      <c r="G15" s="95"/>
+        <v>80.728613659431886</v>
+      </c>
+      <c r="J14" s="12"/>
+      <c r="K14" s="117"/>
+      <c r="L14" s="101" t="s">
+        <v>26</v>
+      </c>
+      <c r="M14" s="94">
+        <v>2.7752984471319091</v>
+      </c>
+      <c r="N14" s="95">
+        <v>2.3015697910981339</v>
+      </c>
+      <c r="O14" s="95">
+        <v>2.0162357843530452</v>
+      </c>
+      <c r="P14" s="95">
+        <v>3.0539531580418511</v>
+      </c>
+      <c r="Q14" s="96">
+        <v>1.6877124305890641</v>
+      </c>
+      <c r="R14" s="12"/>
+    </row>
+    <row r="15" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="114" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" s="116"/>
+      <c r="C15" s="116"/>
+      <c r="D15" s="116"/>
+      <c r="E15" s="116"/>
+      <c r="F15" s="116"/>
+      <c r="G15" s="115"/>
       <c r="H15" s="34"/>
       <c r="I15" s="34"/>
       <c r="J15" s="12"/>
-      <c r="K15" s="94" t="s">
-        <v>23</v>
-      </c>
-      <c r="L15" s="96"/>
-      <c r="M15" s="96"/>
-      <c r="N15" s="96"/>
-      <c r="O15" s="96"/>
-      <c r="P15" s="96"/>
-      <c r="Q15" s="95"/>
+      <c r="K15" s="114" t="s">
+        <v>20</v>
+      </c>
+      <c r="L15" s="116"/>
+      <c r="M15" s="116"/>
+      <c r="N15" s="116"/>
+      <c r="O15" s="116"/>
+      <c r="P15" s="116"/>
+      <c r="Q15" s="115"/>
       <c r="R15" s="12"/>
     </row>
     <row r="16" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="111" t="s">
+      <c r="A16" s="117" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="143"/>
-      <c r="C16" s="128">
-        <v>93.204569243678591</v>
-      </c>
-      <c r="D16" s="124">
-        <v>92.71893643831983</v>
-      </c>
-      <c r="E16" s="124">
-        <v>91.010196166633492</v>
-      </c>
-      <c r="F16" s="124">
-        <v>77.775612245780678</v>
-      </c>
-      <c r="G16" s="129">
-        <v>55.921856302101808</v>
+      <c r="B16" s="118"/>
+      <c r="C16" s="92">
+        <v>93.207752662220258</v>
+      </c>
+      <c r="D16">
+        <v>92.783034455315345</v>
+      </c>
+      <c r="E16">
+        <v>90.565884364628303</v>
+      </c>
+      <c r="F16">
+        <v>73.076886478256739</v>
+      </c>
+      <c r="G16" s="93">
+        <v>58.556994437668138</v>
       </c>
       <c r="H16" s="34" cm="1">
         <f t="array" ref="H16">-SUMPRODUCT((D1:F1-C1:E1)*(C16:E16+D16:F16)/2)</f>
-        <v>79.996131021894655</v>
+        <v>79.643984809557168</v>
       </c>
       <c r="I16" s="34" cm="1">
         <f t="array" ref="I16">-SUMPRODUCT((D1:G1-C1:F1)*(C16:F16+D16:G16)/2)</f>
-        <v>84.174176914015987</v>
+        <v>83.757543588179814</v>
       </c>
       <c r="J16" s="12" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C16:G16)&amp;","</f>
-        <v xml:space="preserve">    93.2045692436786, 92.7189364383198, 91.0101961666335, 77.7756122457807, 55.9218563021018,</v>
-      </c>
-      <c r="K16" s="111" t="s">
+        <v xml:space="preserve">    93.2077526622203, 92.7830344553153, 90.5658843646283, 73.0768864782567, 58.5569944376681,</v>
+      </c>
+      <c r="K16" s="117" t="s">
         <v>7</v>
       </c>
-      <c r="L16" s="143"/>
-      <c r="M16" s="128">
-        <v>3.5338969773137729</v>
-      </c>
-      <c r="N16" s="124">
-        <v>3.7216965755259852</v>
-      </c>
-      <c r="O16" s="124">
-        <v>3.7478593835578962</v>
-      </c>
-      <c r="P16" s="124">
-        <v>6.7863547394302319</v>
-      </c>
-      <c r="Q16" s="129">
-        <v>8.2097242202983072</v>
+      <c r="L16" s="118"/>
+      <c r="M16" s="92">
+        <v>4.081079160307894</v>
+      </c>
+      <c r="N16">
+        <v>3.9215668791224498</v>
+      </c>
+      <c r="O16">
+        <v>3.873470124738835</v>
+      </c>
+      <c r="P16">
+        <v>9.0889689998586825</v>
+      </c>
+      <c r="Q16" s="93">
+        <v>9.0192886420696112</v>
       </c>
       <c r="R16" s="12" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M16:Q16)&amp;","</f>
-        <v xml:space="preserve">    3.53389697731377, 3.72169657552599, 3.7478593835579, 6.78635473943023, 8.20972422029831,</v>
+        <v xml:space="preserve">    4.08107916030789, 3.92156687912245, 3.87347012473884, 9.08896899985868, 9.01928864206961,</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="98" t="s">
+      <c r="A17" s="119" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="99"/>
-      <c r="C17" s="128">
-        <v>91.935155148400952</v>
-      </c>
-      <c r="D17" s="124">
-        <v>91.692255123314226</v>
-      </c>
-      <c r="E17" s="124">
-        <v>89.847648624411406</v>
-      </c>
-      <c r="F17" s="124">
-        <v>79.400747411309794</v>
-      </c>
-      <c r="G17" s="129">
-        <v>53.25364406266489</v>
+      <c r="B17" s="120"/>
+      <c r="C17" s="92">
+        <v>93.534975792754821</v>
+      </c>
+      <c r="D17">
+        <v>92.336467731843129</v>
+      </c>
+      <c r="E17">
+        <v>88.593520128490155</v>
+      </c>
+      <c r="F17">
+        <v>71.045294509468079</v>
+      </c>
+      <c r="G17" s="93">
+        <v>53.467062863865607</v>
       </c>
       <c r="H17" s="34" cm="1">
         <f t="array" ref="H17">-SUMPRODUCT((D1:F1-C1:E1)*(C17:E17+D17:F17)/2)</f>
-        <v>79.177365288627072</v>
+        <v>79.061535278563539</v>
       </c>
       <c r="I17" s="34" cm="1">
         <f t="array" ref="I17">-SUMPRODUCT((D1:G1-C1:F1)*(C17:F17+D17:G17)/2)</f>
-        <v>83.322815022188777</v>
+        <v>82.952546446480213</v>
       </c>
       <c r="J17" s="12" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C17:G17)&amp;","</f>
-        <v xml:space="preserve">    91.935155148401, 91.6922551233142, 89.8476486244114, 79.4007474113098, 53.2536440626649,</v>
-      </c>
-      <c r="K17" s="94" t="s">
+        <v xml:space="preserve">    93.5349757927548, 92.3364677318431, 88.5935201284902, 71.0452945094681, 53.4670628638656,</v>
+      </c>
+      <c r="K17" s="114" t="s">
         <v>8</v>
       </c>
-      <c r="L17" s="95"/>
-      <c r="M17" s="128">
-        <v>3.0404967647063641</v>
-      </c>
-      <c r="N17" s="124">
-        <v>3.2195663824364602</v>
-      </c>
-      <c r="O17" s="124">
-        <v>5.1059080333021827</v>
-      </c>
-      <c r="P17" s="124">
-        <v>3.323723681934811</v>
-      </c>
-      <c r="Q17" s="129">
-        <v>4.2607284397566696</v>
+      <c r="L17" s="115"/>
+      <c r="M17" s="92">
+        <v>3.8494978151380188</v>
+      </c>
+      <c r="N17">
+        <v>3.7468317792042942</v>
+      </c>
+      <c r="O17">
+        <v>4.6420078579248552</v>
+      </c>
+      <c r="P17">
+        <v>10.247976510425289</v>
+      </c>
+      <c r="Q17" s="93">
+        <v>9.5145399413620808</v>
       </c>
       <c r="R17" s="12" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M17:Q17)&amp;","</f>
-        <v xml:space="preserve">    3.04049676470636, 3.21956638243646, 5.10590803330218, 3.32372368193481, 4.26072843975667,</v>
+        <v xml:space="preserve">    3.84949781513802, 3.74683177920429, 4.64200785792486, 10.2479765104253, 9.51453994136208,</v>
       </c>
     </row>
     <row r="18" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="94" t="s">
+      <c r="A18" s="114" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="95"/>
-      <c r="C18" s="128">
-        <v>93.32960781090955</v>
-      </c>
-      <c r="D18" s="124">
-        <v>92.627433339965464</v>
-      </c>
-      <c r="E18" s="124">
-        <v>90.919543710009009</v>
-      </c>
-      <c r="F18" s="124">
-        <v>77.743400317765136</v>
-      </c>
-      <c r="G18" s="129">
-        <v>58.391070280308071</v>
+      <c r="B18" s="115"/>
+      <c r="C18" s="92">
+        <v>93.005297046975599</v>
+      </c>
+      <c r="D18">
+        <v>91.902444369472647</v>
+      </c>
+      <c r="E18">
+        <v>89.116278399178753</v>
+      </c>
+      <c r="F18">
+        <v>72.258814234263852</v>
+      </c>
+      <c r="G18" s="93">
+        <v>53.843628981796257</v>
       </c>
       <c r="H18" s="34" cm="1">
         <f t="array" ref="H18">-SUMPRODUCT((D1:F1-C1:E1)*(C18:E18+D18:F18)/2)</f>
-        <v>79.974066420701448</v>
+        <v>78.940218989783645</v>
       </c>
       <c r="I18" s="34" cm="1">
         <f t="array" ref="I18">-SUMPRODUCT((D1:G1-C1:F1)*(C18:F18+D18:G18)/2)</f>
-        <v>84.228268626891236</v>
+        <v>82.880920340285527</v>
       </c>
       <c r="J18" s="12" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C18:G18)&amp;","</f>
-        <v xml:space="preserve">    93.3296078109096, 92.6274333399655, 90.919543710009, 77.7434003177651, 58.3910702803081,</v>
-      </c>
-      <c r="K18" s="94" t="s">
+        <v xml:space="preserve">    93.0052970469756, 91.9024443694726, 89.1162783991788, 72.2588142342639, 53.8436289817963,</v>
+      </c>
+      <c r="K18" s="114" t="s">
         <v>21</v>
       </c>
-      <c r="L18" s="95"/>
-      <c r="M18" s="128">
-        <v>3.3471189071482028</v>
-      </c>
-      <c r="N18" s="124">
-        <v>3.632082464261972</v>
-      </c>
-      <c r="O18" s="124">
-        <v>3.8019445786359811</v>
-      </c>
-      <c r="P18" s="124">
-        <v>7.5417080235248886</v>
-      </c>
-      <c r="Q18" s="129">
-        <v>8.4137702230121008</v>
+      <c r="L18" s="115"/>
+      <c r="M18" s="92">
+        <v>3.458803648865628</v>
+      </c>
+      <c r="N18">
+        <v>4.1139178681351494</v>
+      </c>
+      <c r="O18">
+        <v>4.3674865362294497</v>
+      </c>
+      <c r="P18">
+        <v>10.1810612930344</v>
+      </c>
+      <c r="Q18" s="93">
+        <v>8.6745540222164905</v>
       </c>
       <c r="R18" s="12" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M18:Q18)&amp;","</f>
-        <v xml:space="preserve">    3.3471189071482, 3.63208246426197, 3.80194457863598, 7.54170802352489, 8.4137702230121,</v>
+        <v xml:space="preserve">    3.45880364886563, 4.11391786813515, 4.36748653622945, 10.1810612930344, 8.67455402221649,</v>
       </c>
     </row>
     <row r="19" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="94" t="s">
+      <c r="A19" s="119" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="95"/>
-      <c r="C19" s="35"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="133"/>
+      <c r="B19" s="120"/>
+      <c r="C19" s="99"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="100"/>
       <c r="H19" s="34" cm="1">
         <f t="array" ref="H19">-SUMPRODUCT((D1:F1-C1:E1)*(C19:E19+D19:F19)/2)</f>
         <v>0</v>
@@ -2002,1014 +2054,1454 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C19:G19)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="K19" s="94" t="s">
+      <c r="K19" s="119" t="s">
         <v>22</v>
       </c>
-      <c r="L19" s="95"/>
-      <c r="M19" s="35"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="36"/>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="133"/>
+      <c r="L19" s="120"/>
+      <c r="M19" s="99"/>
+      <c r="N19" s="34"/>
+      <c r="O19" s="34"/>
+      <c r="P19" s="34"/>
+      <c r="Q19" s="100"/>
       <c r="R19" s="12" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M19:Q19)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="25"/>
-      <c r="B20" s="25"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="25"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="25"/>
-      <c r="H20" s="25"/>
-      <c r="I20" s="25"/>
-      <c r="K20" s="25"/>
-      <c r="L20" s="25"/>
-      <c r="M20" s="25"/>
-      <c r="N20" s="25"/>
-      <c r="O20" s="25"/>
-      <c r="P20" s="25"/>
-      <c r="Q20" s="25"/>
-    </row>
-    <row r="21" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
+    <row r="20" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="114" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="116"/>
+      <c r="C20" s="116"/>
+      <c r="D20" s="116"/>
+      <c r="E20" s="116"/>
+      <c r="F20" s="116"/>
+      <c r="G20" s="115"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="114" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" s="116"/>
+      <c r="M20" s="116"/>
+      <c r="N20" s="116"/>
+      <c r="O20" s="116"/>
+      <c r="P20" s="116"/>
+      <c r="Q20" s="115"/>
+      <c r="R20" s="12"/>
+    </row>
+    <row r="21" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="117" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="118"/>
+      <c r="C21" s="92">
+        <v>93.204569243678591</v>
+      </c>
+      <c r="D21">
+        <v>92.71893643831983</v>
+      </c>
+      <c r="E21">
+        <v>91.010196166633492</v>
+      </c>
+      <c r="F21">
+        <v>77.775612245780678</v>
+      </c>
+      <c r="G21" s="93">
+        <v>55.921856302101808</v>
+      </c>
+      <c r="H21" s="34" cm="1">
+        <f t="array" ref="H21">-SUMPRODUCT((D1:F1-C1:E1)*(C21:E21+D21:F21)/2)</f>
+        <v>79.996131021894655</v>
+      </c>
+      <c r="I21" s="34" cm="1">
+        <f t="array" ref="I21">-SUMPRODUCT((D1:G1-C1:F1)*(C21:F21+D21:G21)/2)</f>
+        <v>84.174176914015987</v>
+      </c>
+      <c r="J21" s="12" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:G21)&amp;","</f>
+        <v xml:space="preserve">    93.2045692436786, 92.7189364383198, 91.0101961666335, 77.7756122457807, 55.9218563021018,</v>
+      </c>
+      <c r="K21" s="117" t="s">
+        <v>7</v>
+      </c>
+      <c r="L21" s="118"/>
+      <c r="M21" s="92">
+        <v>3.5338969773137729</v>
+      </c>
+      <c r="N21">
+        <v>3.7216965755259852</v>
+      </c>
+      <c r="O21">
+        <v>3.7478593835578962</v>
+      </c>
+      <c r="P21">
+        <v>6.7863547394302319</v>
+      </c>
+      <c r="Q21" s="93">
+        <v>8.2097242202983072</v>
+      </c>
+      <c r="R21" s="12" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M21:Q21)&amp;","</f>
+        <v xml:space="preserve">    3.53389697731377, 3.72169657552599, 3.7478593835579, 6.78635473943023, 8.20972422029831,</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="119" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="120"/>
+      <c r="C22" s="92">
+        <v>91.935155148400952</v>
+      </c>
+      <c r="D22">
+        <v>91.692255123314226</v>
+      </c>
+      <c r="E22">
+        <v>89.847648624411406</v>
+      </c>
+      <c r="F22">
+        <v>79.400747411309794</v>
+      </c>
+      <c r="G22" s="93">
+        <v>53.25364406266489</v>
+      </c>
+      <c r="H22" s="34" cm="1">
+        <f t="array" ref="H22">-SUMPRODUCT((D1:F1-C1:E1)*(C22:E22+D22:F22)/2)</f>
+        <v>79.177365288627072</v>
+      </c>
+      <c r="I22" s="34" cm="1">
+        <f t="array" ref="I22">-SUMPRODUCT((D1:G1-C1:F1)*(C22:F22+D22:G22)/2)</f>
+        <v>83.322815022188777</v>
+      </c>
+      <c r="J22" s="12" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C22:G22)&amp;","</f>
+        <v xml:space="preserve">    91.935155148401, 91.6922551233142, 89.8476486244114, 79.4007474113098, 53.2536440626649,</v>
+      </c>
+      <c r="K22" s="114" t="s">
+        <v>8</v>
+      </c>
+      <c r="L22" s="115"/>
+      <c r="M22" s="92">
+        <v>3.0404967647063641</v>
+      </c>
+      <c r="N22">
+        <v>3.2195663824364602</v>
+      </c>
+      <c r="O22">
+        <v>5.1059080333021827</v>
+      </c>
+      <c r="P22">
+        <v>3.323723681934811</v>
+      </c>
+      <c r="Q22" s="93">
+        <v>4.2607284397566696</v>
+      </c>
+      <c r="R22" s="12" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M22:Q22)&amp;","</f>
+        <v xml:space="preserve">    3.04049676470636, 3.21956638243646, 5.10590803330218, 3.32372368193481, 4.26072843975667,</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="114" t="s">
+        <v>21</v>
+      </c>
+      <c r="B23" s="115"/>
+      <c r="C23" s="92">
+        <v>93.32960781090955</v>
+      </c>
+      <c r="D23">
+        <v>92.627433339965464</v>
+      </c>
+      <c r="E23">
+        <v>90.919543710009009</v>
+      </c>
+      <c r="F23">
+        <v>77.743400317765136</v>
+      </c>
+      <c r="G23" s="93">
+        <v>58.391070280308071</v>
+      </c>
+      <c r="H23" s="34" cm="1">
+        <f t="array" ref="H23">-SUMPRODUCT((D1:F1-C1:E1)*(C23:E23+D23:F23)/2)</f>
+        <v>79.974066420701448</v>
+      </c>
+      <c r="I23" s="34" cm="1">
+        <f t="array" ref="I23">-SUMPRODUCT((D1:G1-C1:F1)*(C23:F23+D23:G23)/2)</f>
+        <v>84.228268626891236</v>
+      </c>
+      <c r="J23" s="12" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C23:G23)&amp;","</f>
+        <v xml:space="preserve">    93.3296078109096, 92.6274333399655, 90.919543710009, 77.7434003177651, 58.3910702803081,</v>
+      </c>
+      <c r="K23" s="114" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" s="115"/>
+      <c r="M23" s="92">
+        <v>3.3471189071482028</v>
+      </c>
+      <c r="N23">
+        <v>3.632082464261972</v>
+      </c>
+      <c r="O23">
+        <v>3.8019445786359811</v>
+      </c>
+      <c r="P23">
+        <v>7.5417080235248886</v>
+      </c>
+      <c r="Q23" s="93">
+        <v>8.4137702230121008</v>
+      </c>
+      <c r="R23" s="12" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M23:Q23)&amp;","</f>
+        <v xml:space="preserve">    3.3471189071482, 3.63208246426197, 3.80194457863598, 7.54170802352489, 8.4137702230121,</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="114" t="s">
+        <v>22</v>
+      </c>
+      <c r="B24" s="115"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="97"/>
+      <c r="H24" s="34" cm="1">
+        <f t="array" ref="H24">-SUMPRODUCT((D1:F1-C1:E1)*(C24:E24+D24:F24)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="34" cm="1">
+        <f t="array" ref="I24">-SUMPRODUCT((D1:G1-C1:F1)*(C24:F24+D24:G24)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="J24" s="12" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C24:G24)&amp;","</f>
+        <v xml:space="preserve">    ,</v>
+      </c>
+      <c r="K24" s="114" t="s">
+        <v>22</v>
+      </c>
+      <c r="L24" s="115"/>
+      <c r="M24" s="35"/>
+      <c r="N24" s="36"/>
+      <c r="O24" s="36"/>
+      <c r="P24" s="36"/>
+      <c r="Q24" s="97"/>
+      <c r="R24" s="12" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M24:Q24)&amp;","</f>
+        <v xml:space="preserve">    ,</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="25"/>
+      <c r="B25" s="25"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="25"/>
+      <c r="M25" s="25"/>
+      <c r="N25" s="25"/>
+      <c r="O25" s="25"/>
+      <c r="P25" s="25"/>
+      <c r="Q25" s="25"/>
+    </row>
+    <row r="26" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B26" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C21" s="14">
+      <c r="C26" s="14">
         <v>1</v>
       </c>
-      <c r="D21" s="16">
+      <c r="D26" s="16">
         <v>0.5</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E26" s="16">
         <v>0.25</v>
       </c>
-      <c r="F21" s="16">
+      <c r="F26" s="16">
         <v>0.125</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G26" s="2">
         <v>6.25E-2</v>
       </c>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="4" t="s">
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L21" s="5" t="s">
+      <c r="L26" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="M21" s="14">
+      <c r="M26" s="14">
         <v>1</v>
       </c>
-      <c r="N21" s="16">
+      <c r="N26" s="16">
         <v>0.5</v>
       </c>
-      <c r="O21" s="16">
+      <c r="O26" s="16">
         <v>0.25</v>
       </c>
-      <c r="P21" s="16">
+      <c r="P26" s="16">
         <v>0.125</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="Q26" s="2">
         <v>6.25E-2</v>
       </c>
-      <c r="R21" s="1"/>
-    </row>
-    <row r="22" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="101" t="s">
+      <c r="R26" s="1"/>
+    </row>
+    <row r="27" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="105" t="s">
         <v>5</v>
       </c>
-      <c r="B22" s="103"/>
-      <c r="C22" s="125">
+      <c r="B27" s="106"/>
+      <c r="C27" s="89">
         <v>92.485449200300948</v>
       </c>
-      <c r="D22" s="126">
+      <c r="D27" s="90">
         <v>92.185357970009463</v>
       </c>
-      <c r="E22" s="126">
+      <c r="E27" s="90">
         <v>90.049361274020285</v>
       </c>
-      <c r="F22" s="126">
+      <c r="F27" s="90">
         <v>76.424179894802663</v>
       </c>
-      <c r="G22" s="127">
+      <c r="G27" s="91">
         <v>55.817166373785298</v>
-      </c>
-      <c r="H22" s="40"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C22:G22)&amp;","</f>
-        <v xml:space="preserve">    92.4854492003009, 92.1853579700095, 90.0493612740203, 76.4241798948027, 55.8171663737853,</v>
-      </c>
-      <c r="K22" s="101" t="s">
-        <v>5</v>
-      </c>
-      <c r="L22" s="103"/>
-      <c r="M22" s="125">
-        <v>4.0542209595909764</v>
-      </c>
-      <c r="N22" s="126">
-        <v>4.1862833242412467</v>
-      </c>
-      <c r="O22" s="126">
-        <v>4.5232246954320994</v>
-      </c>
-      <c r="P22" s="126">
-        <v>8.3692490038067824</v>
-      </c>
-      <c r="Q22" s="127">
-        <v>9.4522568492704835</v>
-      </c>
-      <c r="R22" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M22:Q22)&amp;","</f>
-        <v xml:space="preserve">    4.05422095959098, 4.18628332424125, 4.5232246954321, 8.36924900380678, 9.45225684927048,</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="101" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="103"/>
-      <c r="C23" s="128">
-        <v>93.221737995090834</v>
-      </c>
-      <c r="D23" s="124">
-        <v>91.888033005684576</v>
-      </c>
-      <c r="E23" s="124">
-        <v>90.02393898401543</v>
-      </c>
-      <c r="F23" s="124">
-        <v>72.290420081448175</v>
-      </c>
-      <c r="G23" s="129">
-        <v>51.841305264174281</v>
-      </c>
-      <c r="H23" s="40"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C23:G23)&amp;","</f>
-        <v xml:space="preserve">    93.2217379950908, 91.8880330056846, 90.0239389840154, 72.2904200814482, 51.8413052641743,</v>
-      </c>
-      <c r="K23" s="101" t="s">
-        <v>6</v>
-      </c>
-      <c r="L23" s="103"/>
-      <c r="M23" s="128">
-        <v>3.877808098377264</v>
-      </c>
-      <c r="N23" s="124">
-        <v>3.9588226549458381</v>
-      </c>
-      <c r="O23" s="124">
-        <v>3.8583306594917439</v>
-      </c>
-      <c r="P23" s="124">
-        <v>9.3469718907111154</v>
-      </c>
-      <c r="Q23" s="129">
-        <v>8.4900588367667034</v>
-      </c>
-      <c r="R23" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M23:Q23)&amp;","</f>
-        <v xml:space="preserve">    3.87780809837726, 3.95882265494584, 3.85833065949174, 9.34697189071112, 8.4900588367667,</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="106" t="s">
-        <v>10</v>
-      </c>
-      <c r="B24" s="104"/>
-      <c r="C24" s="130">
-        <v>88.242190127710941</v>
-      </c>
-      <c r="D24" s="131">
-        <v>87.235659245723795</v>
-      </c>
-      <c r="E24" s="131">
-        <v>86.840356363138071</v>
-      </c>
-      <c r="F24" s="131">
-        <v>74.54100008231579</v>
-      </c>
-      <c r="G24" s="132">
-        <v>48.979529992306112</v>
-      </c>
-      <c r="H24" s="40"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C24:G24)&amp;","</f>
-        <v xml:space="preserve">    88.2421901277109, 87.2356592457238, 86.8403563631381, 74.5410000823158, 48.9795299923061,</v>
-      </c>
-      <c r="K24" s="106" t="s">
-        <v>10</v>
-      </c>
-      <c r="L24" s="104"/>
-      <c r="M24" s="130">
-        <v>3.345739818904093</v>
-      </c>
-      <c r="N24" s="131">
-        <v>2.427737239251389</v>
-      </c>
-      <c r="O24" s="131">
-        <v>1.707344435820553</v>
-      </c>
-      <c r="P24" s="131">
-        <v>2.910710341880129</v>
-      </c>
-      <c r="Q24" s="132">
-        <v>2.034771708486713</v>
-      </c>
-      <c r="R24" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M24:Q24)&amp;","</f>
-        <v xml:space="preserve">    3.34573981890409, 2.42773723925139, 1.70734443582055, 2.91071034188013, 2.03477170848671,</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="101" t="s">
-        <v>12</v>
-      </c>
-      <c r="B25" s="103"/>
-      <c r="C25" s="103"/>
-      <c r="D25" s="103"/>
-      <c r="E25" s="103"/>
-      <c r="F25" s="103"/>
-      <c r="G25" s="102"/>
-      <c r="H25" s="40"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="101" t="s">
-        <v>12</v>
-      </c>
-      <c r="L25" s="103"/>
-      <c r="M25" s="103"/>
-      <c r="N25" s="103"/>
-      <c r="O25" s="103"/>
-      <c r="P25" s="103"/>
-      <c r="Q25" s="102"/>
-      <c r="R25" s="1"/>
-    </row>
-    <row r="26" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="93" t="s">
-        <v>11</v>
-      </c>
-      <c r="B26" s="142" t="s">
-        <v>13</v>
-      </c>
-      <c r="C26" s="125">
-        <v>92.884757186814937</v>
-      </c>
-      <c r="D26" s="126">
-        <v>92.335436215459112</v>
-      </c>
-      <c r="E26" s="126">
-        <v>90.9231205519105</v>
-      </c>
-      <c r="F26" s="126">
-        <v>76.864790806262661</v>
-      </c>
-      <c r="G26" s="127">
-        <v>54.700390036572337</v>
-      </c>
-      <c r="H26" s="40"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C26:G26)&amp;","</f>
-        <v xml:space="preserve">    92.8847571868149, 92.3354362154591, 90.9231205519105, 76.8647908062627, 54.7003900365723,</v>
-      </c>
-      <c r="K26" s="93" t="s">
-        <v>11</v>
-      </c>
-      <c r="L26" s="142" t="s">
-        <v>13</v>
-      </c>
-      <c r="M26" s="125">
-        <v>3.9275095693540201</v>
-      </c>
-      <c r="N26" s="126">
-        <v>4.1004926648702904</v>
-      </c>
-      <c r="O26" s="126">
-        <v>3.731232057084795</v>
-      </c>
-      <c r="P26" s="126">
-        <v>7.9334375921235116</v>
-      </c>
-      <c r="Q26" s="127">
-        <v>9.3194201516218254</v>
-      </c>
-      <c r="R26" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M26:Q26)&amp;","</f>
-        <v xml:space="preserve">    3.92750956935402, 4.10049266487029, 3.73123205708479, 7.93343759212351, 9.31942015162183,</v>
-      </c>
-    </row>
-    <row r="27" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B27" s="122" t="s">
-        <v>14</v>
-      </c>
-      <c r="C27" s="128">
-        <v>92.328683900261311</v>
-      </c>
-      <c r="D27" s="124">
-        <v>92.052039116791605</v>
-      </c>
-      <c r="E27" s="124">
-        <v>90.722946775710213</v>
-      </c>
-      <c r="F27" s="124">
-        <v>81.998727124399025</v>
-      </c>
-      <c r="G27" s="129">
-        <v>56.932651064742558</v>
       </c>
       <c r="H27" s="40"/>
       <c r="I27" s="40"/>
       <c r="J27" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C27:G27)&amp;","</f>
-        <v xml:space="preserve">    92.3286839002613, 92.0520391167916, 90.7229467757102, 81.998727124399, 56.9326510647426,</v>
-      </c>
-      <c r="K27" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="L27" s="122" t="s">
-        <v>14</v>
-      </c>
-      <c r="M27" s="128">
-        <v>3.6425445085490389</v>
-      </c>
-      <c r="N27" s="124">
-        <v>3.5031960343483388</v>
-      </c>
-      <c r="O27" s="124">
-        <v>3.28867394504752</v>
-      </c>
-      <c r="P27" s="124">
-        <v>4.6860855472410874</v>
-      </c>
-      <c r="Q27" s="129">
-        <v>6.5118967468904154</v>
+        <v xml:space="preserve">    92.4854492003009, 92.1853579700095, 90.0493612740203, 76.4241798948027, 55.8171663737853,</v>
+      </c>
+      <c r="K27" s="105" t="s">
+        <v>5</v>
+      </c>
+      <c r="L27" s="106"/>
+      <c r="M27" s="89">
+        <v>4.0542209595909764</v>
+      </c>
+      <c r="N27" s="90">
+        <v>4.1862833242412467</v>
+      </c>
+      <c r="O27" s="90">
+        <v>4.5232246954320994</v>
+      </c>
+      <c r="P27" s="90">
+        <v>8.3692490038067824</v>
+      </c>
+      <c r="Q27" s="91">
+        <v>9.4522568492704835</v>
       </c>
       <c r="R27" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M27:Q27)&amp;","</f>
-        <v xml:space="preserve">    3.64254450854904, 3.50319603434834, 3.28867394504752, 4.68608554724109, 6.51189674689042,</v>
+        <v xml:space="preserve">    4.05422095959098, 4.18628332424125, 4.5232246954321, 8.36924900380678, 9.45225684927048,</v>
       </c>
     </row>
     <row r="28" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B28" s="122" t="s">
-        <v>18</v>
-      </c>
-      <c r="C28" s="128">
-        <v>93.17956577363725</v>
-      </c>
-      <c r="D28" s="124">
-        <v>92.311564351892216</v>
-      </c>
-      <c r="E28" s="124">
-        <v>90.442696954145944</v>
-      </c>
-      <c r="F28" s="124">
-        <v>73.029683164461161</v>
-      </c>
-      <c r="G28" s="129">
-        <v>54.393186167944343</v>
+      <c r="A28" s="105" t="s">
+        <v>6</v>
+      </c>
+      <c r="B28" s="106"/>
+      <c r="C28" s="92">
+        <v>93.221737995090834</v>
+      </c>
+      <c r="D28">
+        <v>91.888033005684576</v>
+      </c>
+      <c r="E28">
+        <v>90.02393898401543</v>
+      </c>
+      <c r="F28">
+        <v>72.290420081448175</v>
+      </c>
+      <c r="G28" s="93">
+        <v>51.841305264174281</v>
       </c>
       <c r="H28" s="40"/>
       <c r="I28" s="40"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="L28" s="122" t="s">
-        <v>18</v>
-      </c>
-      <c r="M28" s="128">
-        <v>3.743131605295734</v>
-      </c>
-      <c r="N28" s="124">
-        <v>4.0679999153192643</v>
-      </c>
-      <c r="O28" s="124">
-        <v>4.2835813429220631</v>
-      </c>
-      <c r="P28" s="124">
-        <v>9.1240722898599991</v>
-      </c>
-      <c r="Q28" s="129">
-        <v>8.7084512165137298</v>
-      </c>
-      <c r="R28" s="1"/>
+      <c r="J28" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C28:G28)&amp;","</f>
+        <v xml:space="preserve">    93.2217379950908, 91.8880330056846, 90.0239389840154, 72.2904200814482, 51.8413052641743,</v>
+      </c>
+      <c r="K28" s="105" t="s">
+        <v>6</v>
+      </c>
+      <c r="L28" s="106"/>
+      <c r="M28" s="92">
+        <v>3.877808098377264</v>
+      </c>
+      <c r="N28">
+        <v>3.9588226549458381</v>
+      </c>
+      <c r="O28">
+        <v>3.8583306594917439</v>
+      </c>
+      <c r="P28">
+        <v>9.3469718907111154</v>
+      </c>
+      <c r="Q28" s="93">
+        <v>8.4900588367667034</v>
+      </c>
+      <c r="R28" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M28:Q28)&amp;","</f>
+        <v xml:space="preserve">    3.87780809837726, 3.95882265494584, 3.85833065949174, 9.34697189071112, 8.4900588367667,</v>
+      </c>
     </row>
     <row r="29" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="B29" s="122" t="s">
-        <v>19</v>
-      </c>
-      <c r="C29" s="130">
-        <v>90.264167794210408</v>
-      </c>
-      <c r="D29" s="131">
-        <v>89.992256751037203</v>
-      </c>
-      <c r="E29" s="131">
-        <v>89.343495694119156</v>
-      </c>
-      <c r="F29" s="131">
-        <v>78.329165755951735</v>
-      </c>
-      <c r="G29" s="132">
-        <v>52.215737786802968</v>
+      <c r="A29" s="109" t="s">
+        <v>10</v>
+      </c>
+      <c r="B29" s="110"/>
+      <c r="C29" s="94">
+        <v>88.242190127710941</v>
+      </c>
+      <c r="D29" s="95">
+        <v>87.235659245723795</v>
+      </c>
+      <c r="E29" s="95">
+        <v>86.840356363138071</v>
+      </c>
+      <c r="F29" s="95">
+        <v>74.54100008231579</v>
+      </c>
+      <c r="G29" s="96">
+        <v>48.979529992306112</v>
       </c>
       <c r="H29" s="40"/>
       <c r="I29" s="40"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="14" t="s">
-        <v>11</v>
-      </c>
-      <c r="L29" s="136" t="s">
-        <v>19</v>
-      </c>
-      <c r="M29" s="130">
-        <v>2.813777787794177</v>
-      </c>
-      <c r="N29" s="131">
-        <v>2.515073286885404</v>
-      </c>
-      <c r="O29" s="131">
-        <v>2.61246052058309</v>
-      </c>
-      <c r="P29" s="131">
-        <v>3.988565827203912</v>
-      </c>
-      <c r="Q29" s="132">
-        <v>3.7859616126423878</v>
-      </c>
-      <c r="R29" s="1"/>
+      <c r="J29" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C29:G29)&amp;","</f>
+        <v xml:space="preserve">    88.2421901277109, 87.2356592457238, 86.8403563631381, 74.5410000823158, 48.9795299923061,</v>
+      </c>
+      <c r="K29" s="109" t="s">
+        <v>10</v>
+      </c>
+      <c r="L29" s="110"/>
+      <c r="M29" s="94">
+        <v>3.345739818904093</v>
+      </c>
+      <c r="N29" s="95">
+        <v>2.427737239251389</v>
+      </c>
+      <c r="O29" s="95">
+        <v>1.707344435820553</v>
+      </c>
+      <c r="P29" s="95">
+        <v>2.910710341880129</v>
+      </c>
+      <c r="Q29" s="96">
+        <v>2.034771708486713</v>
+      </c>
+      <c r="R29" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M29:Q29)&amp;","</f>
+        <v xml:space="preserve">    3.34573981890409, 2.42773723925139, 1.70734443582055, 2.91071034188013, 2.03477170848671,</v>
+      </c>
     </row>
     <row r="30" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="101" t="s">
-        <v>20</v>
-      </c>
-      <c r="B30" s="103"/>
-      <c r="C30" s="123"/>
-      <c r="D30" s="123"/>
-      <c r="E30" s="123"/>
-      <c r="F30" s="123"/>
-      <c r="G30" s="123"/>
+      <c r="A30" s="105" t="s">
+        <v>12</v>
+      </c>
+      <c r="B30" s="106"/>
+      <c r="C30" s="110"/>
+      <c r="D30" s="110"/>
+      <c r="E30" s="110"/>
+      <c r="F30" s="110"/>
+      <c r="G30" s="111"/>
       <c r="H30" s="40"/>
       <c r="I30" s="40"/>
       <c r="J30" s="1"/>
-      <c r="K30" s="101" t="s">
-        <v>20</v>
-      </c>
-      <c r="L30" s="103"/>
-      <c r="M30" s="103"/>
-      <c r="N30" s="103"/>
-      <c r="O30" s="103"/>
-      <c r="P30" s="103"/>
-      <c r="Q30" s="102"/>
+      <c r="K30" s="105" t="s">
+        <v>12</v>
+      </c>
+      <c r="L30" s="106"/>
+      <c r="M30" s="110"/>
+      <c r="N30" s="110"/>
+      <c r="O30" s="110"/>
+      <c r="P30" s="110"/>
+      <c r="Q30" s="111"/>
       <c r="R30" s="1"/>
     </row>
-    <row r="31" spans="1:18" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="101" t="s">
-        <v>7</v>
-      </c>
-      <c r="B31" s="103"/>
-      <c r="C31" s="125">
-        <v>92.781043798288394</v>
-      </c>
-      <c r="D31" s="126">
-        <v>92.393805655393209</v>
-      </c>
-      <c r="E31" s="126">
-        <v>90.00908396624763</v>
-      </c>
-      <c r="F31" s="126">
-        <v>72.498171965203667</v>
-      </c>
-      <c r="G31" s="127">
-        <v>56.674852997991948</v>
+    <row r="31" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="142" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" s="88" t="s">
+        <v>17</v>
+      </c>
+      <c r="C31" s="89">
+        <v>92.96850376823356</v>
+      </c>
+      <c r="D31" s="90">
+        <v>92.40153506683653</v>
+      </c>
+      <c r="E31" s="90">
+        <v>90.677668832287424</v>
+      </c>
+      <c r="F31" s="90">
+        <v>74.017532689742268</v>
+      </c>
+      <c r="G31" s="91">
+        <v>53.92352732591884</v>
       </c>
       <c r="H31" s="40"/>
       <c r="I31" s="40"/>
-      <c r="J31" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C31:G31)&amp;","</f>
-        <v xml:space="preserve">    92.7810437982884, 92.3938056553932, 90.0090839662476, 72.4981719652037, 56.6748529979919,</v>
-      </c>
-      <c r="K31" s="113" t="s">
-        <v>7</v>
-      </c>
-      <c r="L31" s="141"/>
-      <c r="M31" s="125">
-        <v>4.5014366094349993</v>
-      </c>
-      <c r="N31" s="126">
-        <v>4.2660991290099446</v>
-      </c>
-      <c r="O31" s="126">
-        <v>4.2894182874628113</v>
-      </c>
-      <c r="P31" s="126">
-        <v>9.3344724861133059</v>
-      </c>
-      <c r="Q31" s="127">
-        <v>9.7546209717543917</v>
-      </c>
-      <c r="R31" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M31:Q31)&amp;","</f>
-        <v xml:space="preserve">    4.501436609435, 4.26609912900994, 4.28941828746281, 9.33447248611331, 9.75462097175439,</v>
-      </c>
+      <c r="J31" s="1"/>
+      <c r="K31" s="142" t="s">
+        <v>11</v>
+      </c>
+      <c r="L31" s="88" t="s">
+        <v>17</v>
+      </c>
+      <c r="M31" s="89">
+        <v>3.8454600924080049</v>
+      </c>
+      <c r="N31" s="90">
+        <v>4.0669297112418992</v>
+      </c>
+      <c r="O31" s="90">
+        <v>3.8537049252854398</v>
+      </c>
+      <c r="P31" s="90">
+        <v>8.7041298457857419</v>
+      </c>
+      <c r="Q31" s="91">
+        <v>9.6394684933662074</v>
+      </c>
+      <c r="R31" s="1"/>
     </row>
     <row r="32" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="101" t="s">
-        <v>8</v>
-      </c>
-      <c r="B32" s="103"/>
-      <c r="C32" s="128">
-        <v>93.113144022293241</v>
-      </c>
-      <c r="D32" s="124">
-        <v>91.949604112069864</v>
-      </c>
-      <c r="E32" s="124">
-        <v>88.043149271791009</v>
-      </c>
-      <c r="F32" s="124">
-        <v>70.437814383158539</v>
-      </c>
-      <c r="G32" s="129">
-        <v>50.027165788274679</v>
+      <c r="A32" s="143"/>
+      <c r="B32" s="102" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" s="92">
+        <v>92.884757186814937</v>
+      </c>
+      <c r="D32" s="141">
+        <v>92.335436215459112</v>
+      </c>
+      <c r="E32" s="141">
+        <v>90.9231205519105</v>
+      </c>
+      <c r="F32" s="141">
+        <v>76.864790806262661</v>
+      </c>
+      <c r="G32" s="93">
+        <v>54.700390036572337</v>
       </c>
       <c r="H32" s="40"/>
       <c r="I32" s="40"/>
       <c r="J32" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C32:G32)&amp;","</f>
-        <v xml:space="preserve">    93.1131440222932, 91.9496041120699, 88.043149271791, 70.4378143831585, 50.0271657882747,</v>
-      </c>
-      <c r="K32" s="101" t="s">
-        <v>8</v>
-      </c>
-      <c r="L32" s="103"/>
-      <c r="M32" s="128">
-        <v>4.249709534316878</v>
-      </c>
-      <c r="N32" s="124">
-        <v>4.0308606644498308</v>
-      </c>
-      <c r="O32" s="124">
-        <v>4.9865974054077986</v>
-      </c>
-      <c r="P32" s="124">
-        <v>10.497443911766959</v>
-      </c>
-      <c r="Q32" s="129">
-        <v>10.803449952087821</v>
+        <v xml:space="preserve">    92.8847571868149, 92.3354362154591, 90.9231205519105, 76.8647908062627, 54.7003900365723,</v>
+      </c>
+      <c r="K32" s="143"/>
+      <c r="L32" s="102" t="s">
+        <v>13</v>
+      </c>
+      <c r="M32" s="92">
+        <v>3.9275095693540201</v>
+      </c>
+      <c r="N32" s="141">
+        <v>4.1004926648702904</v>
+      </c>
+      <c r="O32" s="141">
+        <v>3.731232057084795</v>
+      </c>
+      <c r="P32" s="141">
+        <v>7.9334375921235116</v>
+      </c>
+      <c r="Q32" s="93">
+        <v>9.3194201516218254</v>
       </c>
       <c r="R32" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M32:Q32)&amp;","</f>
-        <v xml:space="preserve">    4.24970953431688, 4.03086066444983, 4.9865974054078, 10.497443911767, 10.8034499520878,</v>
+        <v xml:space="preserve">    3.92750956935402, 4.10049266487029, 3.73123205708479, 7.93343759212351, 9.31942015162183,</v>
       </c>
     </row>
     <row r="33" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="101" t="s">
-        <v>21</v>
-      </c>
-      <c r="B33" s="103"/>
-      <c r="C33" s="130">
-        <v>92.587964837227005</v>
-      </c>
-      <c r="D33" s="131">
-        <v>91.423582441600061</v>
-      </c>
-      <c r="E33" s="131">
-        <v>88.545464929422721</v>
-      </c>
-      <c r="F33" s="131">
-        <v>71.659800595038618</v>
-      </c>
-      <c r="G33" s="132">
-        <v>50.266469026560699</v>
+      <c r="A33" s="143"/>
+      <c r="B33" s="88" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="92">
+        <v>92.328683900261311</v>
+      </c>
+      <c r="D33" s="141">
+        <v>92.052039116791605</v>
+      </c>
+      <c r="E33" s="141">
+        <v>90.722946775710213</v>
+      </c>
+      <c r="F33" s="141">
+        <v>81.998727124399025</v>
+      </c>
+      <c r="G33" s="93">
+        <v>56.932651064742558</v>
       </c>
       <c r="H33" s="40"/>
       <c r="I33" s="40"/>
       <c r="J33" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C33:G33)&amp;","</f>
-        <v xml:space="preserve">    92.587964837227, 91.4235824416001, 88.5454649294227, 71.6598005950386, 50.2664690265607,</v>
-      </c>
-      <c r="K33" s="101" t="s">
-        <v>21</v>
-      </c>
-      <c r="L33" s="103"/>
-      <c r="M33" s="128">
-        <v>3.7645606938355249</v>
-      </c>
-      <c r="N33" s="124">
-        <v>4.4885904163036674</v>
-      </c>
-      <c r="O33" s="124">
-        <v>4.6842035667864703</v>
-      </c>
-      <c r="P33" s="124">
-        <v>10.46873255591585</v>
-      </c>
-      <c r="Q33" s="129">
-        <v>9.9892548989807413</v>
+        <v xml:space="preserve">    92.3286839002613, 92.0520391167916, 90.7229467757102, 81.998727124399, 56.9326510647426,</v>
+      </c>
+      <c r="K33" s="143"/>
+      <c r="L33" s="88" t="s">
+        <v>14</v>
+      </c>
+      <c r="M33" s="92">
+        <v>3.6425445085490389</v>
+      </c>
+      <c r="N33" s="141">
+        <v>3.5031960343483388</v>
+      </c>
+      <c r="O33" s="141">
+        <v>3.28867394504752</v>
+      </c>
+      <c r="P33" s="141">
+        <v>4.6860855472410874</v>
+      </c>
+      <c r="Q33" s="93">
+        <v>6.5118967468904154</v>
       </c>
       <c r="R33" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M33:Q33)&amp;","</f>
-        <v xml:space="preserve">    3.76456069383552, 4.48859041630367, 4.68420356678647, 10.4687325559158, 9.98925489898074,</v>
+        <v xml:space="preserve">    3.64254450854904, 3.50319603434834, 3.28867394504752, 4.68608554724109, 6.51189674689042,</v>
       </c>
     </row>
     <row r="34" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="106" t="s">
-        <v>22</v>
-      </c>
-      <c r="B34" s="107"/>
-      <c r="C34" s="134"/>
-      <c r="D34" s="135"/>
-      <c r="E34" s="135"/>
-      <c r="F34" s="135"/>
-      <c r="G34" s="135"/>
-      <c r="H34" s="45"/>
-      <c r="I34" s="45"/>
-      <c r="J34" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C34:G34)&amp;","</f>
-        <v xml:space="preserve">    ,</v>
-      </c>
-      <c r="K34" s="106" t="s">
-        <v>22</v>
-      </c>
-      <c r="L34" s="104"/>
-      <c r="M34" s="41"/>
-      <c r="N34" s="42"/>
-      <c r="O34" s="42"/>
-      <c r="P34" s="42"/>
-      <c r="Q34" s="145"/>
-      <c r="R34" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M34:Q34)&amp;","</f>
-        <v xml:space="preserve">    ,</v>
-      </c>
-    </row>
-    <row r="35" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="101" t="s">
-        <v>23</v>
-      </c>
-      <c r="B35" s="103"/>
-      <c r="C35" s="103"/>
-      <c r="D35" s="103"/>
-      <c r="E35" s="103"/>
-      <c r="F35" s="103"/>
-      <c r="G35" s="102"/>
+      <c r="A34" s="143"/>
+      <c r="B34" s="88" t="s">
+        <v>15</v>
+      </c>
+      <c r="C34" s="92">
+        <v>93.343840114066111</v>
+      </c>
+      <c r="D34" s="141">
+        <v>91.954404928715931</v>
+      </c>
+      <c r="E34" s="141">
+        <v>90.224796797452356</v>
+      </c>
+      <c r="F34" s="141">
+        <v>75.418279728826036</v>
+      </c>
+      <c r="G34" s="93">
+        <v>54.024842451700351</v>
+      </c>
+      <c r="H34" s="40"/>
+      <c r="I34" s="40"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="143"/>
+      <c r="L34" s="88" t="s">
+        <v>15</v>
+      </c>
+      <c r="M34" s="92">
+        <v>3.867155660480134</v>
+      </c>
+      <c r="N34" s="141">
+        <v>3.8459340780537419</v>
+      </c>
+      <c r="O34" s="141">
+        <v>3.7451559754967332</v>
+      </c>
+      <c r="P34" s="141">
+        <v>8.3745003498256878</v>
+      </c>
+      <c r="Q34" s="93">
+        <v>9.3705924310602366</v>
+      </c>
+      <c r="R34" s="1"/>
+    </row>
+    <row r="35" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="143"/>
+      <c r="B35" s="88" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="92">
+        <v>93.17956577363725</v>
+      </c>
+      <c r="D35" s="141">
+        <v>92.311564351892216</v>
+      </c>
+      <c r="E35" s="141">
+        <v>90.442696954145944</v>
+      </c>
+      <c r="F35" s="141">
+        <v>73.029683164461161</v>
+      </c>
+      <c r="G35" s="93">
+        <v>54.393186167944343</v>
+      </c>
       <c r="H35" s="40"/>
       <c r="I35" s="40"/>
       <c r="J35" s="1"/>
-      <c r="K35" s="101" t="s">
-        <v>23</v>
-      </c>
-      <c r="L35" s="103"/>
-      <c r="M35" s="103"/>
-      <c r="N35" s="103"/>
-      <c r="O35" s="103"/>
-      <c r="P35" s="103"/>
-      <c r="Q35" s="102"/>
+      <c r="K35" s="143"/>
+      <c r="L35" s="88" t="s">
+        <v>18</v>
+      </c>
+      <c r="M35" s="92">
+        <v>3.743131605295734</v>
+      </c>
+      <c r="N35" s="141">
+        <v>4.0679999153192643</v>
+      </c>
+      <c r="O35" s="141">
+        <v>4.2835813429220631</v>
+      </c>
+      <c r="P35" s="141">
+        <v>9.1240722898599991</v>
+      </c>
+      <c r="Q35" s="93">
+        <v>8.7084512165137298</v>
+      </c>
       <c r="R35" s="1"/>
     </row>
-    <row r="36" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="113" t="s">
-        <v>7</v>
-      </c>
-      <c r="B36" s="141"/>
-      <c r="C36" s="125">
-        <v>92.779242983398433</v>
-      </c>
-      <c r="D36" s="126">
-        <v>92.240270194904923</v>
-      </c>
-      <c r="E36" s="126">
-        <v>90.552301433559194</v>
-      </c>
-      <c r="F36" s="126">
-        <v>77.44681530627544</v>
-      </c>
-      <c r="G36" s="127">
-        <v>54.049481297537007</v>
+    <row r="36" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="143"/>
+      <c r="B36" s="88" t="s">
+        <v>25</v>
+      </c>
+      <c r="C36" s="92">
+        <v>90.924141700367642</v>
+      </c>
+      <c r="D36" s="141">
+        <v>90.531815219430456</v>
+      </c>
+      <c r="E36" s="141">
+        <v>89.551513659244264</v>
+      </c>
+      <c r="F36" s="141">
+        <v>80.742066180975286</v>
+      </c>
+      <c r="G36" s="93">
+        <v>54.139653004991288</v>
       </c>
       <c r="H36" s="40"/>
       <c r="I36" s="40"/>
-      <c r="J36" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C36:G36)&amp;","</f>
-        <v xml:space="preserve">    92.7792429833984, 92.2402701949049, 90.5523014335592, 77.4468153062754, 54.049481297537,</v>
-      </c>
-      <c r="K36" s="113" t="s">
-        <v>7</v>
-      </c>
-      <c r="L36" s="141"/>
-      <c r="M36" s="125">
-        <v>3.8708284466838099</v>
-      </c>
-      <c r="N36" s="126">
-        <v>4.1159624538095514</v>
-      </c>
-      <c r="O36" s="126">
-        <v>4.0917292690559766</v>
-      </c>
-      <c r="P36" s="126">
-        <v>6.9723184162377478</v>
-      </c>
-      <c r="Q36" s="127">
-        <v>8.876523191689154</v>
-      </c>
-      <c r="R36" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M36:Q36)&amp;","</f>
-        <v xml:space="preserve">    3.87082844668381, 4.11596245380955, 4.09172926905598, 6.97231841623775, 8.87652319168915,</v>
-      </c>
-    </row>
-    <row r="37" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="106" t="s">
-        <v>8</v>
-      </c>
-      <c r="B37" s="104"/>
-      <c r="C37" s="128">
-        <v>91.529115829853595</v>
-      </c>
-      <c r="D37" s="124">
-        <v>91.350643423322225</v>
-      </c>
-      <c r="E37" s="124">
-        <v>89.341760932799787</v>
-      </c>
-      <c r="F37" s="124">
-        <v>79.045051998788765</v>
-      </c>
-      <c r="G37" s="129">
-        <v>52.319711731697872</v>
+      <c r="J36" s="1"/>
+      <c r="K36" s="143"/>
+      <c r="L36" s="88" t="s">
+        <v>25</v>
+      </c>
+      <c r="M36" s="92">
+        <v>3.2766682411196539</v>
+      </c>
+      <c r="N36" s="141">
+        <v>2.78458571585282</v>
+      </c>
+      <c r="O36" s="141">
+        <v>2.9252385560800671</v>
+      </c>
+      <c r="P36" s="141">
+        <v>4.2888241274046361</v>
+      </c>
+      <c r="Q36" s="93">
+        <v>6.6722118847395508</v>
+      </c>
+      <c r="R36" s="1"/>
+    </row>
+    <row r="37" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="143"/>
+      <c r="B37" s="88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" s="92">
+        <v>88.022061049133967</v>
+      </c>
+      <c r="D37" s="141">
+        <v>86.687391232306652</v>
+      </c>
+      <c r="E37" s="141">
+        <v>86.899490010131302</v>
+      </c>
+      <c r="F37" s="141">
+        <v>75.166534149020336</v>
+      </c>
+      <c r="G37" s="93">
+        <v>49.417617539398499</v>
       </c>
       <c r="H37" s="40"/>
       <c r="I37" s="40"/>
-      <c r="J37" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C37:G37)&amp;","</f>
-        <v xml:space="preserve">    91.5291158298536, 91.3506434233222, 89.3417609327998, 79.0450519987888, 52.3197117316979,</v>
-      </c>
-      <c r="K37" s="101" t="s">
-        <v>8</v>
-      </c>
-      <c r="L37" s="103"/>
-      <c r="M37" s="128">
-        <v>3.326792742141544</v>
-      </c>
-      <c r="N37" s="124">
-        <v>3.370578982220036</v>
-      </c>
-      <c r="O37" s="124">
-        <v>5.5895882093977454</v>
-      </c>
-      <c r="P37" s="124">
-        <v>3.3906236766273481</v>
-      </c>
-      <c r="Q37" s="129">
-        <v>4.5139463885317248</v>
-      </c>
-      <c r="R37" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M37:Q37)&amp;","</f>
-        <v xml:space="preserve">    3.32679274214154, 3.37057898222004, 5.58958820939775, 3.39062367662735, 4.51394638853172,</v>
-      </c>
-    </row>
-    <row r="38" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="101" t="s">
-        <v>21</v>
-      </c>
-      <c r="B38" s="103"/>
-      <c r="C38" s="128">
-        <v>92.904210456970588</v>
-      </c>
-      <c r="D38" s="124">
-        <v>92.1891124359732</v>
-      </c>
-      <c r="E38" s="124">
-        <v>90.496036698942376</v>
-      </c>
-      <c r="F38" s="124">
-        <v>77.336951327754974</v>
-      </c>
-      <c r="G38" s="129">
-        <v>56.222535937160863</v>
+      <c r="J37" s="1"/>
+      <c r="K37" s="143"/>
+      <c r="L37" s="88" t="s">
+        <v>16</v>
+      </c>
+      <c r="M37" s="92">
+        <v>3.1059564342295989</v>
+      </c>
+      <c r="N37" s="141">
+        <v>2.606378506216009</v>
+      </c>
+      <c r="O37" s="141">
+        <v>1.672205327538536</v>
+      </c>
+      <c r="P37" s="141">
+        <v>3.4989537204184411</v>
+      </c>
+      <c r="Q37" s="93">
+        <v>1.5086756884059249</v>
+      </c>
+      <c r="R37" s="1"/>
+    </row>
+    <row r="38" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="143"/>
+      <c r="B38" s="88" t="s">
+        <v>19</v>
+      </c>
+      <c r="C38" s="92">
+        <v>90.264167794210408</v>
+      </c>
+      <c r="D38" s="141">
+        <v>89.992256751037203</v>
+      </c>
+      <c r="E38" s="141">
+        <v>89.343495694119156</v>
+      </c>
+      <c r="F38" s="141">
+        <v>78.329165755951735</v>
+      </c>
+      <c r="G38" s="93">
+        <v>52.215737786802968</v>
       </c>
       <c r="H38" s="40"/>
       <c r="I38" s="40"/>
-      <c r="J38" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C38:G38)&amp;","</f>
-        <v xml:space="preserve">    92.9042104569706, 92.1891124359732, 90.4960366989424, 77.336951327755, 56.2225359371609,</v>
-      </c>
-      <c r="K38" s="101" t="s">
-        <v>21</v>
-      </c>
-      <c r="L38" s="103"/>
-      <c r="M38" s="128">
-        <v>3.6016716439248402</v>
-      </c>
-      <c r="N38" s="124">
-        <v>3.9740552459554821</v>
-      </c>
-      <c r="O38" s="124">
-        <v>4.0466560589706821</v>
-      </c>
-      <c r="P38" s="124">
-        <v>7.6607457787732498</v>
-      </c>
-      <c r="Q38" s="129">
-        <v>9.1988486675501449</v>
-      </c>
-      <c r="R38" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M38:Q38)&amp;","</f>
-        <v xml:space="preserve">    3.60167164392484, 3.97405524595548, 4.04665605897068, 7.66074577877325, 9.19884866755014,</v>
-      </c>
-    </row>
-    <row r="39" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="101" t="s">
-        <v>22</v>
-      </c>
-      <c r="B39" s="103"/>
-      <c r="C39" s="41"/>
-      <c r="D39" s="42"/>
-      <c r="E39" s="42"/>
-      <c r="F39" s="42"/>
-      <c r="G39" s="145"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="143"/>
+      <c r="L38" s="88" t="s">
+        <v>19</v>
+      </c>
+      <c r="M38" s="92">
+        <v>2.813777787794177</v>
+      </c>
+      <c r="N38" s="141">
+        <v>2.515073286885404</v>
+      </c>
+      <c r="O38" s="141">
+        <v>2.61246052058309</v>
+      </c>
+      <c r="P38" s="141">
+        <v>3.988565827203912</v>
+      </c>
+      <c r="Q38" s="93">
+        <v>3.7859616126423878</v>
+      </c>
+      <c r="R38" s="1"/>
+    </row>
+    <row r="39" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="144"/>
+      <c r="B39" s="88" t="s">
+        <v>26</v>
+      </c>
+      <c r="C39" s="94">
+        <v>88.816569678290051</v>
+      </c>
+      <c r="D39" s="95">
+        <v>88.13924460400689</v>
+      </c>
+      <c r="E39" s="95">
+        <v>87.754122925075478</v>
+      </c>
+      <c r="F39" s="95">
+        <v>76.74804506712546</v>
+      </c>
+      <c r="G39" s="96">
+        <v>50.462449044076237</v>
+      </c>
       <c r="H39" s="40"/>
       <c r="I39" s="40"/>
-      <c r="J39" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C39:G39)&amp;","</f>
+      <c r="J39" s="1"/>
+      <c r="K39" s="144"/>
+      <c r="L39" s="88" t="s">
+        <v>26</v>
+      </c>
+      <c r="M39" s="94">
+        <v>2.8080857507745329</v>
+      </c>
+      <c r="N39" s="95">
+        <v>2.4101693608449022</v>
+      </c>
+      <c r="O39" s="95">
+        <v>2.0261358563845731</v>
+      </c>
+      <c r="P39" s="95">
+        <v>3.1965959386571878</v>
+      </c>
+      <c r="Q39" s="96">
+        <v>1.998032998184734</v>
+      </c>
+      <c r="R39" s="1"/>
+    </row>
+    <row r="40" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="105" t="s">
+        <v>20</v>
+      </c>
+      <c r="B40" s="106"/>
+      <c r="C40" s="113"/>
+      <c r="D40" s="113"/>
+      <c r="E40" s="113"/>
+      <c r="F40" s="113"/>
+      <c r="G40" s="113"/>
+      <c r="H40" s="40"/>
+      <c r="I40" s="40"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="105" t="s">
+        <v>20</v>
+      </c>
+      <c r="L40" s="106"/>
+      <c r="M40" s="108"/>
+      <c r="N40" s="108"/>
+      <c r="O40" s="108"/>
+      <c r="P40" s="108"/>
+      <c r="Q40" s="145"/>
+      <c r="R40" s="1"/>
+    </row>
+    <row r="41" spans="1:18" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="105" t="s">
+        <v>7</v>
+      </c>
+      <c r="B41" s="106"/>
+      <c r="C41" s="89">
+        <v>92.781043798288394</v>
+      </c>
+      <c r="D41" s="90">
+        <v>92.393805655393209</v>
+      </c>
+      <c r="E41" s="90">
+        <v>90.00908396624763</v>
+      </c>
+      <c r="F41" s="90">
+        <v>72.498171965203667</v>
+      </c>
+      <c r="G41" s="91">
+        <v>56.674852997991948</v>
+      </c>
+      <c r="H41" s="40"/>
+      <c r="I41" s="40"/>
+      <c r="J41" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C41:G41)&amp;","</f>
+        <v xml:space="preserve">    92.7810437982884, 92.3938056553932, 90.0090839662476, 72.4981719652037, 56.6748529979919,</v>
+      </c>
+      <c r="K41" s="107" t="s">
+        <v>7</v>
+      </c>
+      <c r="L41" s="108"/>
+      <c r="M41" s="89">
+        <v>4.5014366094349993</v>
+      </c>
+      <c r="N41" s="90">
+        <v>4.2660991290099446</v>
+      </c>
+      <c r="O41" s="90">
+        <v>4.2894182874628113</v>
+      </c>
+      <c r="P41" s="90">
+        <v>9.3344724861133059</v>
+      </c>
+      <c r="Q41" s="91">
+        <v>9.7546209717543917</v>
+      </c>
+      <c r="R41" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M41:Q41)&amp;","</f>
+        <v xml:space="preserve">    4.501436609435, 4.26609912900994, 4.28941828746281, 9.33447248611331, 9.75462097175439,</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="105" t="s">
+        <v>8</v>
+      </c>
+      <c r="B42" s="106"/>
+      <c r="C42" s="92">
+        <v>93.113144022293241</v>
+      </c>
+      <c r="D42">
+        <v>91.949604112069864</v>
+      </c>
+      <c r="E42">
+        <v>88.043149271791009</v>
+      </c>
+      <c r="F42">
+        <v>70.437814383158539</v>
+      </c>
+      <c r="G42" s="93">
+        <v>50.027165788274679</v>
+      </c>
+      <c r="H42" s="40"/>
+      <c r="I42" s="40"/>
+      <c r="J42" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C42:G42)&amp;","</f>
+        <v xml:space="preserve">    93.1131440222932, 91.9496041120699, 88.043149271791, 70.4378143831585, 50.0271657882747,</v>
+      </c>
+      <c r="K42" s="105" t="s">
+        <v>8</v>
+      </c>
+      <c r="L42" s="106"/>
+      <c r="M42" s="92">
+        <v>4.249709534316878</v>
+      </c>
+      <c r="N42">
+        <v>4.0308606644498308</v>
+      </c>
+      <c r="O42">
+        <v>4.9865974054077986</v>
+      </c>
+      <c r="P42">
+        <v>10.497443911766959</v>
+      </c>
+      <c r="Q42" s="93">
+        <v>10.803449952087821</v>
+      </c>
+      <c r="R42" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M42:Q42)&amp;","</f>
+        <v xml:space="preserve">    4.24970953431688, 4.03086066444983, 4.9865974054078, 10.497443911767, 10.8034499520878,</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="105" t="s">
+        <v>21</v>
+      </c>
+      <c r="B43" s="106"/>
+      <c r="C43" s="94">
+        <v>92.587964837227005</v>
+      </c>
+      <c r="D43" s="95">
+        <v>91.423582441600061</v>
+      </c>
+      <c r="E43" s="95">
+        <v>88.545464929422721</v>
+      </c>
+      <c r="F43" s="95">
+        <v>71.659800595038618</v>
+      </c>
+      <c r="G43" s="96">
+        <v>50.266469026560699</v>
+      </c>
+      <c r="H43" s="40"/>
+      <c r="I43" s="40"/>
+      <c r="J43" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C43:G43)&amp;","</f>
+        <v xml:space="preserve">    92.587964837227, 91.4235824416001, 88.5454649294227, 71.6598005950386, 50.2664690265607,</v>
+      </c>
+      <c r="K43" s="105" t="s">
+        <v>21</v>
+      </c>
+      <c r="L43" s="106"/>
+      <c r="M43" s="92">
+        <v>3.7645606938355249</v>
+      </c>
+      <c r="N43">
+        <v>4.4885904163036674</v>
+      </c>
+      <c r="O43">
+        <v>4.6842035667864703</v>
+      </c>
+      <c r="P43">
+        <v>10.46873255591585</v>
+      </c>
+      <c r="Q43" s="93">
+        <v>9.9892548989807413</v>
+      </c>
+      <c r="R43" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M43:Q43)&amp;","</f>
+        <v xml:space="preserve">    3.76456069383552, 4.48859041630367, 4.68420356678647, 10.4687325559158, 9.98925489898074,</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="109" t="s">
+        <v>22</v>
+      </c>
+      <c r="B44" s="111"/>
+      <c r="C44" s="98"/>
+      <c r="D44" s="40"/>
+      <c r="E44" s="40"/>
+      <c r="F44" s="40"/>
+      <c r="G44" s="40"/>
+      <c r="H44" s="45"/>
+      <c r="I44" s="45"/>
+      <c r="J44" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C44:G44)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="K39" s="101" t="s">
+      <c r="K44" s="109" t="s">
         <v>22</v>
       </c>
-      <c r="L39" s="103"/>
-      <c r="M39" s="41"/>
-      <c r="N39" s="42"/>
-      <c r="O39" s="42"/>
-      <c r="P39" s="42"/>
-      <c r="Q39" s="145"/>
-      <c r="R39" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M39:Q39)&amp;","</f>
+      <c r="L44" s="110"/>
+      <c r="M44" s="41"/>
+      <c r="N44" s="42"/>
+      <c r="O44" s="42"/>
+      <c r="P44" s="42"/>
+      <c r="Q44" s="104"/>
+      <c r="R44" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M44:Q44)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="J40" s="11"/>
-      <c r="K40" s="11"/>
-      <c r="L40" s="11"/>
-      <c r="M40" s="11"/>
-      <c r="N40" s="11"/>
-      <c r="O40" s="11"/>
-      <c r="P40" s="11"/>
-      <c r="Q40" s="11"/>
-    </row>
-    <row r="41" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="J41" s="11"/>
-      <c r="K41" s="11"/>
-      <c r="L41" s="11"/>
-      <c r="M41" s="11"/>
-      <c r="N41" s="11"/>
-      <c r="O41" s="11"/>
-      <c r="P41" s="11"/>
-      <c r="Q41" s="11"/>
-    </row>
-    <row r="42" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="H42" s="11"/>
-      <c r="I42" s="11"/>
-      <c r="J42" s="11"/>
-      <c r="K42" s="11"/>
-      <c r="L42" s="11"/>
-      <c r="M42" s="11"/>
-      <c r="N42" s="11"/>
-      <c r="O42" s="11"/>
-      <c r="P42" s="11"/>
-      <c r="Q42" s="11"/>
-    </row>
-    <row r="43" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="H43" s="11"/>
-      <c r="I43" s="11"/>
-      <c r="J43" s="11"/>
-      <c r="K43" s="11"/>
-      <c r="L43" s="11"/>
-      <c r="M43" s="11"/>
-      <c r="N43" s="11"/>
-      <c r="O43" s="11"/>
-      <c r="P43" s="11"/>
-      <c r="Q43" s="11"/>
-    </row>
-    <row r="44" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="H44" s="11"/>
-      <c r="I44" s="11"/>
-      <c r="J44" s="11"/>
-      <c r="K44" s="11"/>
-      <c r="L44" s="11"/>
-      <c r="M44" s="11"/>
-      <c r="N44" s="11"/>
-      <c r="O44" s="11"/>
-      <c r="P44" s="11"/>
-      <c r="Q44" s="11"/>
-    </row>
-    <row r="45" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="H45" s="11"/>
-      <c r="I45" s="11"/>
-      <c r="J45" s="11"/>
-      <c r="K45" s="11"/>
-      <c r="L45" s="11"/>
-      <c r="M45" s="11"/>
-      <c r="N45" s="11"/>
-      <c r="O45" s="11"/>
-      <c r="P45" s="11"/>
-      <c r="Q45" s="11"/>
+    <row r="45" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="105" t="s">
+        <v>23</v>
+      </c>
+      <c r="B45" s="106"/>
+      <c r="C45" s="106"/>
+      <c r="D45" s="106"/>
+      <c r="E45" s="106"/>
+      <c r="F45" s="106"/>
+      <c r="G45" s="112"/>
+      <c r="H45" s="40"/>
+      <c r="I45" s="40"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="105" t="s">
+        <v>23</v>
+      </c>
+      <c r="L45" s="106"/>
+      <c r="M45" s="106"/>
+      <c r="N45" s="106"/>
+      <c r="O45" s="106"/>
+      <c r="P45" s="106"/>
+      <c r="Q45" s="112"/>
+      <c r="R45" s="1"/>
+    </row>
+    <row r="46" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="107" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" s="108"/>
+      <c r="C46" s="89">
+        <v>92.779242983398433</v>
+      </c>
+      <c r="D46" s="90">
+        <v>92.240270194904923</v>
+      </c>
+      <c r="E46" s="90">
+        <v>90.552301433559194</v>
+      </c>
+      <c r="F46" s="90">
+        <v>77.44681530627544</v>
+      </c>
+      <c r="G46" s="91">
+        <v>54.049481297537007</v>
+      </c>
+      <c r="H46" s="40"/>
+      <c r="I46" s="40"/>
+      <c r="J46" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C46:G46)&amp;","</f>
+        <v xml:space="preserve">    92.7792429833984, 92.2402701949049, 90.5523014335592, 77.4468153062754, 54.049481297537,</v>
+      </c>
+      <c r="K46" s="107" t="s">
+        <v>7</v>
+      </c>
+      <c r="L46" s="108"/>
+      <c r="M46" s="89">
+        <v>3.8708284466838099</v>
+      </c>
+      <c r="N46" s="90">
+        <v>4.1159624538095514</v>
+      </c>
+      <c r="O46" s="90">
+        <v>4.0917292690559766</v>
+      </c>
+      <c r="P46" s="90">
+        <v>6.9723184162377478</v>
+      </c>
+      <c r="Q46" s="91">
+        <v>8.876523191689154</v>
+      </c>
+      <c r="R46" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M46:Q46)&amp;","</f>
+        <v xml:space="preserve">    3.87082844668381, 4.11596245380955, 4.09172926905598, 6.97231841623775, 8.87652319168915,</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="109" t="s">
+        <v>8</v>
+      </c>
+      <c r="B47" s="110"/>
+      <c r="C47" s="92">
+        <v>91.529115829853595</v>
+      </c>
+      <c r="D47">
+        <v>91.350643423322225</v>
+      </c>
+      <c r="E47">
+        <v>89.341760932799787</v>
+      </c>
+      <c r="F47">
+        <v>79.045051998788765</v>
+      </c>
+      <c r="G47" s="93">
+        <v>52.319711731697872</v>
+      </c>
+      <c r="H47" s="40"/>
+      <c r="I47" s="40"/>
+      <c r="J47" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C47:G47)&amp;","</f>
+        <v xml:space="preserve">    91.5291158298536, 91.3506434233222, 89.3417609327998, 79.0450519987888, 52.3197117316979,</v>
+      </c>
+      <c r="K47" s="105" t="s">
+        <v>8</v>
+      </c>
+      <c r="L47" s="106"/>
+      <c r="M47" s="92">
+        <v>3.326792742141544</v>
+      </c>
+      <c r="N47">
+        <v>3.370578982220036</v>
+      </c>
+      <c r="O47">
+        <v>5.5895882093977454</v>
+      </c>
+      <c r="P47">
+        <v>3.3906236766273481</v>
+      </c>
+      <c r="Q47" s="93">
+        <v>4.5139463885317248</v>
+      </c>
+      <c r="R47" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M47:Q47)&amp;","</f>
+        <v xml:space="preserve">    3.32679274214154, 3.37057898222004, 5.58958820939775, 3.39062367662735, 4.51394638853172,</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="105" t="s">
+        <v>21</v>
+      </c>
+      <c r="B48" s="106"/>
+      <c r="C48" s="92">
+        <v>92.904210456970588</v>
+      </c>
+      <c r="D48">
+        <v>92.1891124359732</v>
+      </c>
+      <c r="E48">
+        <v>90.496036698942376</v>
+      </c>
+      <c r="F48">
+        <v>77.336951327754974</v>
+      </c>
+      <c r="G48" s="93">
+        <v>56.222535937160863</v>
+      </c>
+      <c r="H48" s="40"/>
+      <c r="I48" s="40"/>
+      <c r="J48" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C48:G48)&amp;","</f>
+        <v xml:space="preserve">    92.9042104569706, 92.1891124359732, 90.4960366989424, 77.336951327755, 56.2225359371609,</v>
+      </c>
+      <c r="K48" s="105" t="s">
+        <v>21</v>
+      </c>
+      <c r="L48" s="106"/>
+      <c r="M48" s="92">
+        <v>3.6016716439248402</v>
+      </c>
+      <c r="N48">
+        <v>3.9740552459554821</v>
+      </c>
+      <c r="O48">
+        <v>4.0466560589706821</v>
+      </c>
+      <c r="P48">
+        <v>7.6607457787732498</v>
+      </c>
+      <c r="Q48" s="93">
+        <v>9.1988486675501449</v>
+      </c>
+      <c r="R48" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M48:Q48)&amp;","</f>
+        <v xml:space="preserve">    3.60167164392484, 3.97405524595548, 4.04665605897068, 7.66074577877325, 9.19884866755014,</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="105" t="s">
+        <v>22</v>
+      </c>
+      <c r="B49" s="106"/>
+      <c r="C49" s="41"/>
+      <c r="D49" s="42"/>
+      <c r="E49" s="42"/>
+      <c r="F49" s="42"/>
+      <c r="G49" s="104"/>
+      <c r="H49" s="40"/>
+      <c r="I49" s="40"/>
+      <c r="J49" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C49:G49)&amp;","</f>
+        <v xml:space="preserve">    ,</v>
+      </c>
+      <c r="K49" s="105" t="s">
+        <v>22</v>
+      </c>
+      <c r="L49" s="106"/>
+      <c r="M49" s="41"/>
+      <c r="N49" s="42"/>
+      <c r="O49" s="42"/>
+      <c r="P49" s="42"/>
+      <c r="Q49" s="104"/>
+      <c r="R49" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M49:Q49)&amp;","</f>
+        <v xml:space="preserve">    ,</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="J50" s="11"/>
+      <c r="K50" s="11"/>
+      <c r="L50" s="11"/>
+      <c r="M50" s="11"/>
+      <c r="N50" s="11"/>
+      <c r="O50" s="11"/>
+      <c r="P50" s="11"/>
+      <c r="Q50" s="11"/>
+    </row>
+    <row r="51" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="J51" s="11"/>
+      <c r="K51" s="11"/>
+      <c r="L51" s="11"/>
+      <c r="M51" s="11"/>
+      <c r="N51" s="11"/>
+      <c r="O51" s="11"/>
+      <c r="P51" s="11"/>
+      <c r="Q51" s="11"/>
+    </row>
+    <row r="52" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="H52" s="11"/>
+      <c r="I52" s="11"/>
+      <c r="J52" s="11"/>
+      <c r="K52" s="11"/>
+      <c r="L52" s="11"/>
+      <c r="M52" s="11"/>
+      <c r="N52" s="11"/>
+      <c r="O52" s="11"/>
+      <c r="P52" s="11"/>
+      <c r="Q52" s="11"/>
+    </row>
+    <row r="53" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="H53" s="11"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="11"/>
+      <c r="K53" s="11"/>
+      <c r="L53" s="11"/>
+      <c r="M53" s="11"/>
+      <c r="N53" s="11"/>
+      <c r="O53" s="11"/>
+      <c r="P53" s="11"/>
+      <c r="Q53" s="11"/>
+    </row>
+    <row r="54" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="H54" s="11"/>
+      <c r="I54" s="11"/>
+      <c r="J54" s="11"/>
+      <c r="K54" s="11"/>
+      <c r="L54" s="11"/>
+      <c r="M54" s="11"/>
+      <c r="N54" s="11"/>
+      <c r="O54" s="11"/>
+      <c r="P54" s="11"/>
+      <c r="Q54" s="11"/>
+    </row>
+    <row r="55" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="H55" s="11"/>
+      <c r="I55" s="11"/>
+      <c r="J55" s="11"/>
+      <c r="K55" s="11"/>
+      <c r="L55" s="11"/>
+      <c r="M55" s="11"/>
+      <c r="N55" s="11"/>
+      <c r="O55" s="11"/>
+      <c r="P55" s="11"/>
+      <c r="Q55" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="56">
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="K39:L39"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="K38:L38"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="A35:G35"/>
-    <mergeCell ref="K35:Q35"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="K30:Q30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="K25:Q25"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="A15:G15"/>
-    <mergeCell ref="K15:Q15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="K5:Q5"/>
-    <mergeCell ref="A10:G10"/>
-    <mergeCell ref="K10:Q10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="K11:L11"/>
+  <mergeCells count="60">
+    <mergeCell ref="A31:A39"/>
+    <mergeCell ref="K31:K39"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="K4:L4"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="K5:Q5"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="K15:Q15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="A6:A14"/>
+    <mergeCell ref="K6:K14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="K20:Q20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="K30:Q30"/>
+    <mergeCell ref="A40:G40"/>
+    <mergeCell ref="K40:Q40"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="A42:B42"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="K45:Q45"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="K48:L48"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C2:G4 C6:G9 C11:G14 C16:G19">
-    <cfRule type="colorScale" priority="294">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:G4 H2:I19">
-    <cfRule type="colorScale" priority="277">
+  <conditionalFormatting sqref="C2:G4 C7:G14 C16:G19 C21:G24">
+    <cfRule type="colorScale" priority="302">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:G4 H2:I24">
+    <cfRule type="colorScale" priority="285">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3021,17 +3513,301 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:G4">
-    <cfRule type="colorScale" priority="298">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="299">
+    <cfRule type="colorScale" priority="306">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="307">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="308">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3:G4 H3:I6">
+    <cfRule type="colorScale" priority="288">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="289">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="290">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="291">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="292">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="293">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C7:G7">
+    <cfRule type="colorScale" priority="309">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="310">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8:G14">
+    <cfRule type="colorScale" priority="311">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="312">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:G18 C21:G23">
+    <cfRule type="colorScale" priority="313">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:G18">
+    <cfRule type="colorScale" priority="315">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="316">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="317">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:G19 C21:G24 C7:G14 C2:G4">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:G19 C21:G24">
+    <cfRule type="colorScale" priority="318">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C21:G23">
+    <cfRule type="colorScale" priority="320">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="321">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="322">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H24">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H45:H49">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I24">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I45:I49">
+    <cfRule type="colorScale" priority="49">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3051,70 +3827,6 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C3:G4 H3:I5">
-    <cfRule type="colorScale" priority="280">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="281">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="282">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="283">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="284">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="285">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C6:G6">
     <cfRule type="colorScale" priority="301">
       <colorScale>
         <cfvo type="min"/>
@@ -3125,84 +3837,8 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="302">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C7:G9">
-    <cfRule type="colorScale" priority="303">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="304">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C11:G13 C16:G18">
-    <cfRule type="colorScale" priority="305">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C11:G13">
-    <cfRule type="colorScale" priority="307">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="308">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="309">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C11:G14 C16:G19 C6:G9 C2:G4">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C6:G14 C2:G4 C16:G19 C21:G24">
     <cfRule type="colorScale" priority="8">
       <colorScale>
         <cfvo type="min"/>
@@ -3214,128 +3850,56 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C11:G14 C16:G19">
-    <cfRule type="colorScale" priority="310">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G18">
-    <cfRule type="colorScale" priority="312">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="313">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="314">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H19">
+  <conditionalFormatting sqref="C2:C4 C6:C14">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D4 D6:D14">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E4 E6:E14">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F4 F6:F14">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G4 G6:G14">
     <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H35:H39">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I19">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I35:I39">
-    <cfRule type="colorScale" priority="41">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="292">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="293">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3439,10 +4003,10 @@
       <c r="V1" s="12"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="94" t="s">
+      <c r="A2" s="114" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="95"/>
+      <c r="B2" s="115"/>
       <c r="C2" s="20"/>
       <c r="D2" s="21"/>
       <c r="E2" s="21"/>
@@ -3462,10 +4026,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:I2)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M2" s="94" t="s">
+      <c r="M2" s="114" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="95"/>
+      <c r="N2" s="115"/>
       <c r="O2" s="31"/>
       <c r="P2" s="32"/>
       <c r="Q2" s="32"/>
@@ -3479,10 +4043,10 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="94" t="s">
+      <c r="A3" s="114" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="95"/>
+      <c r="B3" s="115"/>
       <c r="C3" s="31"/>
       <c r="D3" s="32"/>
       <c r="E3" s="32"/>
@@ -3502,10 +4066,10 @@
         <f t="shared" ref="L3:L18" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M3" s="94" t="s">
+      <c r="M3" s="114" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="95"/>
+      <c r="N3" s="115"/>
       <c r="O3" s="31"/>
       <c r="P3" s="32"/>
       <c r="Q3" s="32"/>
@@ -3519,10 +4083,10 @@
       </c>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="94" t="s">
+      <c r="A4" s="114" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="95"/>
+      <c r="B4" s="115"/>
       <c r="C4" s="24"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
@@ -3542,10 +4106,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M4" s="94" t="s">
+      <c r="M4" s="114" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="95"/>
+      <c r="N4" s="115"/>
       <c r="O4" s="43"/>
       <c r="P4" s="26"/>
       <c r="Q4" s="26"/>
@@ -3559,35 +4123,35 @@
       </c>
     </row>
     <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="94" t="s">
+      <c r="A5" s="114" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="96"/>
-      <c r="C5" s="96"/>
-      <c r="D5" s="96"/>
-      <c r="E5" s="96"/>
-      <c r="F5" s="96"/>
-      <c r="G5" s="96"/>
-      <c r="H5" s="96"/>
-      <c r="I5" s="95"/>
+      <c r="B5" s="116"/>
+      <c r="C5" s="116"/>
+      <c r="D5" s="116"/>
+      <c r="E5" s="116"/>
+      <c r="F5" s="116"/>
+      <c r="G5" s="116"/>
+      <c r="H5" s="116"/>
+      <c r="I5" s="115"/>
       <c r="J5" s="34"/>
       <c r="K5" s="34"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="94" t="s">
+      <c r="M5" s="114" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="96"/>
-      <c r="O5" s="96"/>
-      <c r="P5" s="96"/>
-      <c r="Q5" s="96"/>
-      <c r="R5" s="96"/>
-      <c r="S5" s="96"/>
-      <c r="T5" s="96"/>
-      <c r="U5" s="95"/>
+      <c r="N5" s="116"/>
+      <c r="O5" s="116"/>
+      <c r="P5" s="116"/>
+      <c r="Q5" s="116"/>
+      <c r="R5" s="116"/>
+      <c r="S5" s="116"/>
+      <c r="T5" s="116"/>
+      <c r="U5" s="115"/>
       <c r="V5" s="12"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="98" t="s">
+      <c r="A6" s="119" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -3612,7 +4176,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M6" s="98" t="s">
+      <c r="M6" s="119" t="s">
         <v>11</v>
       </c>
       <c r="N6" s="8" t="s">
@@ -3631,7 +4195,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="110"/>
+      <c r="A7" s="121"/>
       <c r="B7" s="8" t="s">
         <v>14</v>
       </c>
@@ -3654,7 +4218,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M7" s="110"/>
+      <c r="M7" s="121"/>
       <c r="N7" s="8" t="s">
         <v>14</v>
       </c>
@@ -3671,7 +4235,7 @@
       </c>
     </row>
     <row r="8" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="110"/>
+      <c r="A8" s="121"/>
       <c r="B8" s="8" t="s">
         <v>17</v>
       </c>
@@ -3694,7 +4258,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M8" s="110"/>
+      <c r="M8" s="121"/>
       <c r="N8" s="8" t="s">
         <v>17</v>
       </c>
@@ -3708,7 +4272,7 @@
       <c r="V8" s="12"/>
     </row>
     <row r="9" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="110"/>
+      <c r="A9" s="121"/>
       <c r="B9" s="8" t="s">
         <v>18</v>
       </c>
@@ -3731,7 +4295,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M9" s="110"/>
+      <c r="M9" s="121"/>
       <c r="N9" s="8" t="s">
         <v>18</v>
       </c>
@@ -3745,7 +4309,7 @@
       <c r="V9" s="12"/>
     </row>
     <row r="10" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="110"/>
+      <c r="A10" s="121"/>
       <c r="B10" s="8" t="s">
         <v>15</v>
       </c>
@@ -3768,7 +4332,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M10" s="110"/>
+      <c r="M10" s="121"/>
       <c r="N10" s="8" t="s">
         <v>15</v>
       </c>
@@ -3782,7 +4346,7 @@
       <c r="V10" s="12"/>
     </row>
     <row r="11" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="110"/>
+      <c r="A11" s="121"/>
       <c r="B11" s="8" t="s">
         <v>25</v>
       </c>
@@ -3805,7 +4369,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M11" s="110"/>
+      <c r="M11" s="121"/>
       <c r="N11" s="8" t="s">
         <v>25</v>
       </c>
@@ -3819,7 +4383,7 @@
       <c r="V11" s="12"/>
     </row>
     <row r="12" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="110"/>
+      <c r="A12" s="121"/>
       <c r="B12" s="8" t="s">
         <v>19</v>
       </c>
@@ -3842,7 +4406,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M12" s="110"/>
+      <c r="M12" s="121"/>
       <c r="N12" s="8" t="s">
         <v>19</v>
       </c>
@@ -3856,7 +4420,7 @@
       <c r="V12" s="12"/>
     </row>
     <row r="13" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="110"/>
+      <c r="A13" s="121"/>
       <c r="B13" s="8" t="s">
         <v>16</v>
       </c>
@@ -3879,7 +4443,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M13" s="110"/>
+      <c r="M13" s="121"/>
       <c r="N13" s="8" t="s">
         <v>16</v>
       </c>
@@ -3893,7 +4457,7 @@
       <c r="V13" s="12"/>
     </row>
     <row r="14" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="111"/>
+      <c r="A14" s="117"/>
       <c r="B14" s="8" t="s">
         <v>26</v>
       </c>
@@ -3916,7 +4480,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M14" s="111"/>
+      <c r="M14" s="117"/>
       <c r="N14" s="8" t="s">
         <v>26</v>
       </c>
@@ -3930,38 +4494,38 @@
       <c r="V14" s="12"/>
     </row>
     <row r="15" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="94" t="s">
+      <c r="A15" s="114" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="96"/>
-      <c r="C15" s="100"/>
-      <c r="D15" s="100"/>
-      <c r="E15" s="100"/>
-      <c r="F15" s="100"/>
-      <c r="G15" s="100"/>
-      <c r="H15" s="100"/>
-      <c r="I15" s="108"/>
+      <c r="B15" s="116"/>
+      <c r="C15" s="124"/>
+      <c r="D15" s="124"/>
+      <c r="E15" s="124"/>
+      <c r="F15" s="124"/>
+      <c r="G15" s="124"/>
+      <c r="H15" s="124"/>
+      <c r="I15" s="125"/>
       <c r="J15" s="34"/>
       <c r="K15" s="34"/>
       <c r="L15" s="12"/>
-      <c r="M15" s="94" t="s">
+      <c r="M15" s="114" t="s">
         <v>20</v>
       </c>
-      <c r="N15" s="96"/>
-      <c r="O15" s="97"/>
-      <c r="P15" s="97"/>
-      <c r="Q15" s="97"/>
-      <c r="R15" s="97"/>
-      <c r="S15" s="97"/>
-      <c r="T15" s="97"/>
-      <c r="U15" s="99"/>
+      <c r="N15" s="116"/>
+      <c r="O15" s="126"/>
+      <c r="P15" s="126"/>
+      <c r="Q15" s="126"/>
+      <c r="R15" s="126"/>
+      <c r="S15" s="126"/>
+      <c r="T15" s="126"/>
+      <c r="U15" s="120"/>
       <c r="V15" s="12"/>
     </row>
     <row r="16" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="94" t="s">
+      <c r="A16" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="95"/>
+      <c r="B16" s="115"/>
       <c r="C16" s="46"/>
       <c r="D16" s="47"/>
       <c r="E16" s="47"/>
@@ -3981,10 +4545,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M16" s="94" t="s">
+      <c r="M16" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="N16" s="95"/>
+      <c r="N16" s="115"/>
       <c r="O16" s="46"/>
       <c r="P16" s="47"/>
       <c r="Q16" s="47"/>
@@ -3998,10 +4562,10 @@
       </c>
     </row>
     <row r="17" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="98" t="s">
+      <c r="A17" s="119" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="99"/>
+      <c r="B17" s="120"/>
       <c r="C17" s="49"/>
       <c r="D17" s="12"/>
       <c r="E17" s="12"/>
@@ -4021,10 +4585,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M17" s="94" t="s">
+      <c r="M17" s="114" t="s">
         <v>8</v>
       </c>
-      <c r="N17" s="95"/>
+      <c r="N17" s="115"/>
       <c r="O17" s="49"/>
       <c r="P17" s="12"/>
       <c r="Q17" s="12"/>
@@ -4038,10 +4602,10 @@
       </c>
     </row>
     <row r="18" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="94" t="s">
+      <c r="A18" s="114" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="95"/>
+      <c r="B18" s="115"/>
       <c r="C18" s="49"/>
       <c r="D18" s="12"/>
       <c r="E18" s="12"/>
@@ -4061,10 +4625,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M18" s="94" t="s">
+      <c r="M18" s="114" t="s">
         <v>21</v>
       </c>
-      <c r="N18" s="95"/>
+      <c r="N18" s="115"/>
       <c r="O18" s="49"/>
       <c r="P18" s="12"/>
       <c r="Q18" s="12"/>
@@ -4078,10 +4642,10 @@
       </c>
     </row>
     <row r="19" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="94" t="s">
+      <c r="A19" s="114" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="95"/>
+      <c r="B19" s="115"/>
       <c r="C19" s="51"/>
       <c r="D19" s="52"/>
       <c r="E19" s="52"/>
@@ -4098,10 +4662,10 @@
         <v>0</v>
       </c>
       <c r="L19" s="12"/>
-      <c r="M19" s="94" t="s">
+      <c r="M19" s="114" t="s">
         <v>22</v>
       </c>
-      <c r="N19" s="95"/>
+      <c r="N19" s="115"/>
       <c r="O19" s="51"/>
       <c r="P19" s="52"/>
       <c r="Q19" s="52"/>
@@ -4112,38 +4676,38 @@
       <c r="V19" s="12"/>
     </row>
     <row r="20" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="94" t="s">
+      <c r="A20" s="114" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="96"/>
-      <c r="C20" s="100"/>
-      <c r="D20" s="100"/>
-      <c r="E20" s="100"/>
-      <c r="F20" s="100"/>
-      <c r="G20" s="100"/>
-      <c r="H20" s="100"/>
-      <c r="I20" s="108"/>
+      <c r="B20" s="116"/>
+      <c r="C20" s="124"/>
+      <c r="D20" s="124"/>
+      <c r="E20" s="124"/>
+      <c r="F20" s="124"/>
+      <c r="G20" s="124"/>
+      <c r="H20" s="124"/>
+      <c r="I20" s="125"/>
       <c r="J20" s="34"/>
       <c r="K20" s="34"/>
       <c r="L20" s="12"/>
-      <c r="M20" s="94" t="s">
+      <c r="M20" s="114" t="s">
         <v>23</v>
       </c>
-      <c r="N20" s="96"/>
-      <c r="O20" s="100"/>
-      <c r="P20" s="100"/>
-      <c r="Q20" s="100"/>
-      <c r="R20" s="100"/>
-      <c r="S20" s="100"/>
-      <c r="T20" s="100"/>
-      <c r="U20" s="108"/>
+      <c r="N20" s="116"/>
+      <c r="O20" s="124"/>
+      <c r="P20" s="124"/>
+      <c r="Q20" s="124"/>
+      <c r="R20" s="124"/>
+      <c r="S20" s="124"/>
+      <c r="T20" s="124"/>
+      <c r="U20" s="125"/>
       <c r="V20" s="12"/>
     </row>
     <row r="21" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="94" t="s">
+      <c r="A21" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="95"/>
+      <c r="B21" s="115"/>
       <c r="C21" s="46"/>
       <c r="D21" s="47"/>
       <c r="E21" s="47"/>
@@ -4163,10 +4727,10 @@
         <f t="shared" ref="L21:L23" si="2">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:I21)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M21" s="94" t="s">
+      <c r="M21" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="N21" s="95"/>
+      <c r="N21" s="115"/>
       <c r="O21" s="46"/>
       <c r="P21" s="47"/>
       <c r="Q21" s="47"/>
@@ -4180,10 +4744,10 @@
       </c>
     </row>
     <row r="22" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="98" t="s">
+      <c r="A22" s="119" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="99"/>
+      <c r="B22" s="120"/>
       <c r="C22" s="49"/>
       <c r="D22" s="12"/>
       <c r="E22" s="12"/>
@@ -4203,10 +4767,10 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M22" s="94" t="s">
+      <c r="M22" s="114" t="s">
         <v>8</v>
       </c>
-      <c r="N22" s="95"/>
+      <c r="N22" s="115"/>
       <c r="O22" s="49"/>
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
@@ -4220,10 +4784,10 @@
       </c>
     </row>
     <row r="23" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="94" t="s">
+      <c r="A23" s="114" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="95"/>
+      <c r="B23" s="115"/>
       <c r="C23" s="49"/>
       <c r="D23" s="12"/>
       <c r="E23" s="12"/>
@@ -4243,10 +4807,10 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M23" s="94" t="s">
+      <c r="M23" s="114" t="s">
         <v>21</v>
       </c>
-      <c r="N23" s="95"/>
+      <c r="N23" s="115"/>
       <c r="O23" s="49"/>
       <c r="P23" s="12"/>
       <c r="Q23" s="12"/>
@@ -4260,10 +4824,10 @@
       </c>
     </row>
     <row r="24" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="94" t="s">
+      <c r="A24" s="114" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="95"/>
+      <c r="B24" s="115"/>
       <c r="C24" s="51"/>
       <c r="D24" s="52"/>
       <c r="E24" s="52"/>
@@ -4280,10 +4844,10 @@
         <v>0</v>
       </c>
       <c r="L24" s="12"/>
-      <c r="M24" s="94" t="s">
+      <c r="M24" s="114" t="s">
         <v>22</v>
       </c>
-      <c r="N24" s="95"/>
+      <c r="N24" s="115"/>
       <c r="O24" s="51"/>
       <c r="P24" s="52"/>
       <c r="Q24" s="52"/>
@@ -4294,38 +4858,38 @@
       <c r="V24" s="12"/>
     </row>
     <row r="25" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="94" t="s">
+      <c r="A25" s="114" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="96"/>
-      <c r="C25" s="100"/>
-      <c r="D25" s="100"/>
-      <c r="E25" s="100"/>
-      <c r="F25" s="100"/>
-      <c r="G25" s="100"/>
-      <c r="H25" s="100"/>
-      <c r="I25" s="108"/>
+      <c r="B25" s="116"/>
+      <c r="C25" s="124"/>
+      <c r="D25" s="124"/>
+      <c r="E25" s="124"/>
+      <c r="F25" s="124"/>
+      <c r="G25" s="124"/>
+      <c r="H25" s="124"/>
+      <c r="I25" s="125"/>
       <c r="J25" s="34"/>
       <c r="K25" s="34"/>
       <c r="L25" s="12"/>
-      <c r="M25" s="94" t="s">
+      <c r="M25" s="114" t="s">
         <v>23</v>
       </c>
-      <c r="N25" s="96"/>
-      <c r="O25" s="100"/>
-      <c r="P25" s="100"/>
-      <c r="Q25" s="100"/>
-      <c r="R25" s="100"/>
-      <c r="S25" s="100"/>
-      <c r="T25" s="100"/>
-      <c r="U25" s="108"/>
+      <c r="N25" s="116"/>
+      <c r="O25" s="124"/>
+      <c r="P25" s="124"/>
+      <c r="Q25" s="124"/>
+      <c r="R25" s="124"/>
+      <c r="S25" s="124"/>
+      <c r="T25" s="124"/>
+      <c r="U25" s="125"/>
       <c r="V25" s="12"/>
     </row>
     <row r="26" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="94" t="s">
+      <c r="A26" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="B26" s="95"/>
+      <c r="B26" s="115"/>
       <c r="C26"/>
       <c r="D26"/>
       <c r="E26"/>
@@ -4345,10 +4909,10 @@
         <f t="shared" ref="L26:L28" si="4">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C26:I26)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M26" s="94" t="s">
+      <c r="M26" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="N26" s="95"/>
+      <c r="N26" s="115"/>
       <c r="O26"/>
       <c r="P26"/>
       <c r="Q26"/>
@@ -4362,10 +4926,10 @@
       </c>
     </row>
     <row r="27" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="98" t="s">
+      <c r="A27" s="119" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="99"/>
+      <c r="B27" s="120"/>
       <c r="C27"/>
       <c r="D27"/>
       <c r="E27"/>
@@ -4385,10 +4949,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M27" s="94" t="s">
+      <c r="M27" s="114" t="s">
         <v>8</v>
       </c>
-      <c r="N27" s="95"/>
+      <c r="N27" s="115"/>
       <c r="O27"/>
       <c r="P27"/>
       <c r="Q27"/>
@@ -4402,10 +4966,10 @@
       </c>
     </row>
     <row r="28" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="94" t="s">
+      <c r="A28" s="114" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="95"/>
+      <c r="B28" s="115"/>
       <c r="C28"/>
       <c r="D28"/>
       <c r="E28"/>
@@ -4425,10 +4989,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M28" s="94" t="s">
+      <c r="M28" s="114" t="s">
         <v>21</v>
       </c>
-      <c r="N28" s="95"/>
+      <c r="N28" s="115"/>
       <c r="O28"/>
       <c r="P28"/>
       <c r="Q28"/>
@@ -4442,10 +5006,10 @@
       </c>
     </row>
     <row r="29" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="94" t="s">
+      <c r="A29" s="114" t="s">
         <v>22</v>
       </c>
-      <c r="B29" s="95"/>
+      <c r="B29" s="115"/>
       <c r="C29"/>
       <c r="D29"/>
       <c r="E29"/>
@@ -4462,17 +5026,17 @@
         <v>0</v>
       </c>
       <c r="L29" s="12"/>
-      <c r="M29" s="94" t="s">
+      <c r="M29" s="114" t="s">
         <v>22</v>
       </c>
-      <c r="N29" s="95"/>
-      <c r="O29" s="89"/>
-      <c r="P29" s="90"/>
-      <c r="Q29" s="90"/>
-      <c r="R29" s="90"/>
-      <c r="S29" s="90"/>
-      <c r="T29" s="90"/>
-      <c r="U29" s="91"/>
+      <c r="N29" s="115"/>
+      <c r="O29" s="85"/>
+      <c r="P29" s="86"/>
+      <c r="Q29" s="86"/>
+      <c r="R29" s="86"/>
+      <c r="S29" s="86"/>
+      <c r="T29" s="86"/>
+      <c r="U29" s="87"/>
       <c r="V29" s="12"/>
     </row>
     <row r="30" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.25">
@@ -4558,10 +5122,10 @@
       <c r="V31" s="1"/>
     </row>
     <row r="32" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="101" t="s">
+      <c r="A32" s="105" t="s">
         <v>5</v>
       </c>
-      <c r="B32" s="102"/>
+      <c r="B32" s="112"/>
       <c r="C32" s="38"/>
       <c r="D32" s="38"/>
       <c r="E32" s="38"/>
@@ -4575,10 +5139,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C32:I32)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M32" s="101" t="s">
+      <c r="M32" s="105" t="s">
         <v>5</v>
       </c>
-      <c r="N32" s="102"/>
+      <c r="N32" s="112"/>
       <c r="O32" s="37"/>
       <c r="P32" s="38"/>
       <c r="Q32" s="38"/>
@@ -4592,10 +5156,10 @@
       </c>
     </row>
     <row r="33" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="101" t="s">
+      <c r="A33" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="B33" s="102"/>
+      <c r="B33" s="112"/>
       <c r="C33" s="38"/>
       <c r="D33" s="38"/>
       <c r="E33" s="38"/>
@@ -4609,10 +5173,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C33:I33)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M33" s="101" t="s">
+      <c r="M33" s="105" t="s">
         <v>6</v>
       </c>
-      <c r="N33" s="102"/>
+      <c r="N33" s="112"/>
       <c r="O33" s="38"/>
       <c r="P33" s="38"/>
       <c r="Q33" s="38"/>
@@ -4626,10 +5190,10 @@
       </c>
     </row>
     <row r="34" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="101" t="s">
+      <c r="A34" s="105" t="s">
         <v>10</v>
       </c>
-      <c r="B34" s="102"/>
+      <c r="B34" s="112"/>
       <c r="C34" s="28"/>
       <c r="D34" s="29"/>
       <c r="E34" s="29"/>
@@ -4643,10 +5207,10 @@
         <f t="shared" ref="L34:L43" si="7">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C34:I34)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M34" s="101" t="s">
+      <c r="M34" s="105" t="s">
         <v>10</v>
       </c>
-      <c r="N34" s="102"/>
+      <c r="N34" s="112"/>
       <c r="O34" s="28"/>
       <c r="P34" s="29"/>
       <c r="Q34" s="29"/>
@@ -4660,35 +5224,35 @@
       </c>
     </row>
     <row r="35" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="101" t="s">
+      <c r="A35" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="B35" s="103"/>
-      <c r="C35" s="103"/>
-      <c r="D35" s="103"/>
-      <c r="E35" s="103"/>
-      <c r="F35" s="103"/>
-      <c r="G35" s="103"/>
-      <c r="H35" s="103"/>
-      <c r="I35" s="102"/>
+      <c r="B35" s="106"/>
+      <c r="C35" s="106"/>
+      <c r="D35" s="106"/>
+      <c r="E35" s="106"/>
+      <c r="F35" s="106"/>
+      <c r="G35" s="106"/>
+      <c r="H35" s="106"/>
+      <c r="I35" s="112"/>
       <c r="J35" s="40"/>
       <c r="K35" s="40"/>
       <c r="L35" s="1"/>
-      <c r="M35" s="101" t="s">
+      <c r="M35" s="105" t="s">
         <v>12</v>
       </c>
-      <c r="N35" s="103"/>
-      <c r="O35" s="103"/>
-      <c r="P35" s="103"/>
-      <c r="Q35" s="103"/>
-      <c r="R35" s="103"/>
-      <c r="S35" s="103"/>
-      <c r="T35" s="103"/>
-      <c r="U35" s="102"/>
+      <c r="N35" s="106"/>
+      <c r="O35" s="106"/>
+      <c r="P35" s="106"/>
+      <c r="Q35" s="106"/>
+      <c r="R35" s="106"/>
+      <c r="S35" s="106"/>
+      <c r="T35" s="106"/>
+      <c r="U35" s="112"/>
       <c r="V35" s="1"/>
     </row>
     <row r="36" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="106" t="s">
+      <c r="A36" s="109" t="s">
         <v>11</v>
       </c>
       <c r="B36" s="9" t="s">
@@ -4707,7 +5271,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M36" s="106" t="s">
+      <c r="M36" s="109" t="s">
         <v>11</v>
       </c>
       <c r="N36" s="9" t="s">
@@ -4726,7 +5290,7 @@
       </c>
     </row>
     <row r="37" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="112"/>
+      <c r="A37" s="122"/>
       <c r="B37" s="9" t="s">
         <v>14</v>
       </c>
@@ -4743,7 +5307,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M37" s="112"/>
+      <c r="M37" s="122"/>
       <c r="N37" s="9" t="s">
         <v>14</v>
       </c>
@@ -4760,7 +5324,7 @@
       </c>
     </row>
     <row r="38" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="112"/>
+      <c r="A38" s="122"/>
       <c r="B38" s="9" t="s">
         <v>17</v>
       </c>
@@ -4774,7 +5338,7 @@
       <c r="J38" s="40"/>
       <c r="K38" s="40"/>
       <c r="L38" s="1"/>
-      <c r="M38" s="112"/>
+      <c r="M38" s="122"/>
       <c r="N38" s="9" t="s">
         <v>17</v>
       </c>
@@ -4788,7 +5352,7 @@
       <c r="V38" s="1"/>
     </row>
     <row r="39" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="112"/>
+      <c r="A39" s="122"/>
       <c r="B39" s="9" t="s">
         <v>18</v>
       </c>
@@ -4802,7 +5366,7 @@
       <c r="J39" s="40"/>
       <c r="K39" s="40"/>
       <c r="L39" s="1"/>
-      <c r="M39" s="112"/>
+      <c r="M39" s="122"/>
       <c r="N39" s="9" t="s">
         <v>18</v>
       </c>
@@ -4816,7 +5380,7 @@
       <c r="V39" s="1"/>
     </row>
     <row r="40" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="112"/>
+      <c r="A40" s="122"/>
       <c r="B40" s="9" t="s">
         <v>15</v>
       </c>
@@ -4833,7 +5397,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M40" s="112"/>
+      <c r="M40" s="122"/>
       <c r="N40" s="9" t="s">
         <v>15</v>
       </c>
@@ -4847,7 +5411,7 @@
       <c r="V40" s="1"/>
     </row>
     <row r="41" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="112"/>
+      <c r="A41" s="122"/>
       <c r="B41" s="9" t="s">
         <v>25</v>
       </c>
@@ -4861,7 +5425,7 @@
       <c r="J41" s="40"/>
       <c r="K41" s="40"/>
       <c r="L41" s="1"/>
-      <c r="M41" s="112"/>
+      <c r="M41" s="122"/>
       <c r="N41" s="9" t="s">
         <v>25</v>
       </c>
@@ -4875,7 +5439,7 @@
       <c r="V41" s="1"/>
     </row>
     <row r="42" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="112"/>
+      <c r="A42" s="122"/>
       <c r="B42" s="9" t="s">
         <v>19</v>
       </c>
@@ -4889,7 +5453,7 @@
       <c r="J42" s="40"/>
       <c r="K42" s="40"/>
       <c r="L42" s="1"/>
-      <c r="M42" s="112"/>
+      <c r="M42" s="122"/>
       <c r="N42" s="9" t="s">
         <v>19</v>
       </c>
@@ -4903,7 +5467,7 @@
       <c r="V42" s="1"/>
     </row>
     <row r="43" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="112"/>
+      <c r="A43" s="122"/>
       <c r="B43" s="9" t="s">
         <v>16</v>
       </c>
@@ -4920,7 +5484,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M43" s="112"/>
+      <c r="M43" s="122"/>
       <c r="N43" s="9" t="s">
         <v>16</v>
       </c>
@@ -4934,7 +5498,7 @@
       <c r="V43" s="1"/>
     </row>
     <row r="44" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="113"/>
+      <c r="A44" s="107"/>
       <c r="B44" s="9" t="s">
         <v>26</v>
       </c>
@@ -4948,7 +5512,7 @@
       <c r="J44" s="40"/>
       <c r="K44" s="40"/>
       <c r="L44" s="1"/>
-      <c r="M44" s="113"/>
+      <c r="M44" s="107"/>
       <c r="N44" s="9" t="s">
         <v>26</v>
       </c>
@@ -4962,38 +5526,38 @@
       <c r="V44" s="1"/>
     </row>
     <row r="45" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="101" t="s">
+      <c r="A45" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="B45" s="103"/>
-      <c r="C45" s="105"/>
-      <c r="D45" s="105"/>
-      <c r="E45" s="105"/>
-      <c r="F45" s="105"/>
-      <c r="G45" s="105"/>
-      <c r="H45" s="105"/>
-      <c r="I45" s="109"/>
+      <c r="B45" s="106"/>
+      <c r="C45" s="113"/>
+      <c r="D45" s="113"/>
+      <c r="E45" s="113"/>
+      <c r="F45" s="113"/>
+      <c r="G45" s="113"/>
+      <c r="H45" s="113"/>
+      <c r="I45" s="123"/>
       <c r="J45" s="40"/>
       <c r="K45" s="40"/>
       <c r="L45" s="1"/>
-      <c r="M45" s="101" t="s">
+      <c r="M45" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="N45" s="103"/>
-      <c r="O45" s="105"/>
-      <c r="P45" s="105"/>
-      <c r="Q45" s="105"/>
-      <c r="R45" s="105"/>
-      <c r="S45" s="105"/>
-      <c r="T45" s="105"/>
-      <c r="U45" s="109"/>
+      <c r="N45" s="106"/>
+      <c r="O45" s="113"/>
+      <c r="P45" s="113"/>
+      <c r="Q45" s="113"/>
+      <c r="R45" s="113"/>
+      <c r="S45" s="113"/>
+      <c r="T45" s="113"/>
+      <c r="U45" s="123"/>
       <c r="V45" s="1"/>
     </row>
     <row r="46" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="101" t="s">
+      <c r="A46" s="105" t="s">
         <v>7</v>
       </c>
-      <c r="B46" s="102"/>
+      <c r="B46" s="112"/>
       <c r="C46" s="54"/>
       <c r="D46" s="55"/>
       <c r="E46" s="55"/>
@@ -5007,10 +5571,10 @@
         <f t="shared" ref="L46:L48" si="8">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C46:I46)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M46" s="101" t="s">
+      <c r="M46" s="105" t="s">
         <v>7</v>
       </c>
-      <c r="N46" s="102"/>
+      <c r="N46" s="112"/>
       <c r="O46" s="54"/>
       <c r="P46" s="55"/>
       <c r="Q46" s="55"/>
@@ -5024,10 +5588,10 @@
       </c>
     </row>
     <row r="47" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="101" t="s">
+      <c r="A47" s="105" t="s">
         <v>8</v>
       </c>
-      <c r="B47" s="102"/>
+      <c r="B47" s="112"/>
       <c r="C47" s="57"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -5041,10 +5605,10 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M47" s="101" t="s">
+      <c r="M47" s="105" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="102"/>
+      <c r="N47" s="112"/>
       <c r="O47" s="57"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
@@ -5058,10 +5622,10 @@
       </c>
     </row>
     <row r="48" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="101" t="s">
+      <c r="A48" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="B48" s="102"/>
+      <c r="B48" s="112"/>
       <c r="C48" s="57"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -5075,10 +5639,10 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M48" s="101" t="s">
+      <c r="M48" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="N48" s="102"/>
+      <c r="N48" s="112"/>
       <c r="O48" s="57"/>
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
@@ -5092,10 +5656,10 @@
       </c>
     </row>
     <row r="49" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="101" t="s">
+      <c r="A49" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="B49" s="102"/>
+      <c r="B49" s="112"/>
       <c r="C49" s="59"/>
       <c r="D49" s="60"/>
       <c r="E49" s="60"/>
@@ -5106,10 +5670,10 @@
       <c r="J49" s="45"/>
       <c r="K49" s="45"/>
       <c r="L49" s="44"/>
-      <c r="M49" s="101" t="s">
+      <c r="M49" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="N49" s="102"/>
+      <c r="N49" s="112"/>
       <c r="O49" s="59"/>
       <c r="P49" s="60"/>
       <c r="Q49" s="60"/>
@@ -5120,38 +5684,38 @@
       <c r="V49" s="1"/>
     </row>
     <row r="50" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="101" t="s">
+      <c r="A50" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="B50" s="103"/>
-      <c r="C50" s="105"/>
-      <c r="D50" s="105"/>
-      <c r="E50" s="105"/>
-      <c r="F50" s="105"/>
-      <c r="G50" s="105"/>
-      <c r="H50" s="105"/>
-      <c r="I50" s="109"/>
+      <c r="B50" s="106"/>
+      <c r="C50" s="113"/>
+      <c r="D50" s="113"/>
+      <c r="E50" s="113"/>
+      <c r="F50" s="113"/>
+      <c r="G50" s="113"/>
+      <c r="H50" s="113"/>
+      <c r="I50" s="123"/>
       <c r="J50" s="40"/>
       <c r="K50" s="40"/>
       <c r="L50" s="1"/>
-      <c r="M50" s="101" t="s">
+      <c r="M50" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="N50" s="103"/>
-      <c r="O50" s="105"/>
-      <c r="P50" s="105"/>
-      <c r="Q50" s="105"/>
-      <c r="R50" s="105"/>
-      <c r="S50" s="105"/>
-      <c r="T50" s="105"/>
-      <c r="U50" s="109"/>
+      <c r="N50" s="106"/>
+      <c r="O50" s="113"/>
+      <c r="P50" s="113"/>
+      <c r="Q50" s="113"/>
+      <c r="R50" s="113"/>
+      <c r="S50" s="113"/>
+      <c r="T50" s="113"/>
+      <c r="U50" s="123"/>
       <c r="V50" s="1"/>
     </row>
     <row r="51" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="101" t="s">
+      <c r="A51" s="105" t="s">
         <v>7</v>
       </c>
-      <c r="B51" s="102"/>
+      <c r="B51" s="112"/>
       <c r="C51" s="54"/>
       <c r="D51" s="55"/>
       <c r="E51" s="55"/>
@@ -5165,10 +5729,10 @@
         <f t="shared" ref="L51:L53" si="9">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C51:I51)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M51" s="101" t="s">
+      <c r="M51" s="105" t="s">
         <v>7</v>
       </c>
-      <c r="N51" s="102"/>
+      <c r="N51" s="112"/>
       <c r="O51" s="54"/>
       <c r="P51" s="55"/>
       <c r="Q51" s="55"/>
@@ -5182,10 +5746,10 @@
       </c>
     </row>
     <row r="52" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="106" t="s">
+      <c r="A52" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="B52" s="107"/>
+      <c r="B52" s="111"/>
       <c r="C52" s="57"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -5199,10 +5763,10 @@
         <f t="shared" si="9"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M52" s="101" t="s">
+      <c r="M52" s="105" t="s">
         <v>8</v>
       </c>
-      <c r="N52" s="102"/>
+      <c r="N52" s="112"/>
       <c r="O52" s="57"/>
       <c r="P52" s="1"/>
       <c r="Q52" s="1"/>
@@ -5216,10 +5780,10 @@
       </c>
     </row>
     <row r="53" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="101" t="s">
+      <c r="A53" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="B53" s="102"/>
+      <c r="B53" s="112"/>
       <c r="C53" s="57"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -5233,10 +5797,10 @@
         <f t="shared" si="9"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M53" s="101" t="s">
+      <c r="M53" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="N53" s="102"/>
+      <c r="N53" s="112"/>
       <c r="O53" s="57"/>
       <c r="P53" s="1"/>
       <c r="Q53" s="1"/>
@@ -5250,10 +5814,10 @@
       </c>
     </row>
     <row r="54" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="101" t="s">
+      <c r="A54" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="B54" s="102"/>
+      <c r="B54" s="112"/>
       <c r="C54" s="59"/>
       <c r="D54" s="60"/>
       <c r="E54" s="60"/>
@@ -5264,10 +5828,10 @@
       <c r="J54" s="40"/>
       <c r="K54" s="40"/>
       <c r="L54" s="1"/>
-      <c r="M54" s="101" t="s">
+      <c r="M54" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="N54" s="102"/>
+      <c r="N54" s="112"/>
       <c r="O54" s="59"/>
       <c r="P54" s="60"/>
       <c r="Q54" s="60"/>
@@ -5278,38 +5842,38 @@
       <c r="V54" s="1"/>
     </row>
     <row r="55" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="101" t="s">
+      <c r="A55" s="105" t="s">
         <v>24</v>
       </c>
-      <c r="B55" s="103"/>
-      <c r="C55" s="105"/>
-      <c r="D55" s="105"/>
-      <c r="E55" s="105"/>
-      <c r="F55" s="105"/>
-      <c r="G55" s="105"/>
-      <c r="H55" s="105"/>
-      <c r="I55" s="109"/>
+      <c r="B55" s="106"/>
+      <c r="C55" s="113"/>
+      <c r="D55" s="113"/>
+      <c r="E55" s="113"/>
+      <c r="F55" s="113"/>
+      <c r="G55" s="113"/>
+      <c r="H55" s="113"/>
+      <c r="I55" s="123"/>
       <c r="J55" s="40"/>
       <c r="K55" s="40"/>
       <c r="L55" s="1"/>
-      <c r="M55" s="101" t="s">
+      <c r="M55" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="N55" s="103"/>
-      <c r="O55" s="105"/>
-      <c r="P55" s="105"/>
-      <c r="Q55" s="105"/>
-      <c r="R55" s="105"/>
-      <c r="S55" s="105"/>
-      <c r="T55" s="105"/>
-      <c r="U55" s="109"/>
+      <c r="N55" s="106"/>
+      <c r="O55" s="113"/>
+      <c r="P55" s="113"/>
+      <c r="Q55" s="113"/>
+      <c r="R55" s="113"/>
+      <c r="S55" s="113"/>
+      <c r="T55" s="113"/>
+      <c r="U55" s="123"/>
       <c r="V55" s="1"/>
     </row>
     <row r="56" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="101" t="s">
+      <c r="A56" s="105" t="s">
         <v>7</v>
       </c>
-      <c r="B56" s="102"/>
+      <c r="B56" s="112"/>
       <c r="C56"/>
       <c r="D56"/>
       <c r="E56"/>
@@ -5323,10 +5887,10 @@
         <f t="shared" ref="L56:L58" si="11">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C56:I56)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M56" s="101" t="s">
+      <c r="M56" s="105" t="s">
         <v>7</v>
       </c>
-      <c r="N56" s="102"/>
+      <c r="N56" s="112"/>
       <c r="O56"/>
       <c r="P56"/>
       <c r="Q56"/>
@@ -5340,10 +5904,10 @@
       </c>
     </row>
     <row r="57" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="106" t="s">
+      <c r="A57" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="B57" s="107"/>
+      <c r="B57" s="111"/>
       <c r="C57"/>
       <c r="D57"/>
       <c r="E57"/>
@@ -5357,10 +5921,10 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M57" s="101" t="s">
+      <c r="M57" s="105" t="s">
         <v>8</v>
       </c>
-      <c r="N57" s="102"/>
+      <c r="N57" s="112"/>
       <c r="O57"/>
       <c r="P57"/>
       <c r="Q57"/>
@@ -5374,10 +5938,10 @@
       </c>
     </row>
     <row r="58" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="101" t="s">
+      <c r="A58" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="B58" s="102"/>
+      <c r="B58" s="112"/>
       <c r="C58"/>
       <c r="D58"/>
       <c r="E58"/>
@@ -5391,10 +5955,10 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M58" s="101" t="s">
+      <c r="M58" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="N58" s="102"/>
+      <c r="N58" s="112"/>
       <c r="O58"/>
       <c r="P58"/>
       <c r="Q58"/>
@@ -5408,31 +5972,31 @@
       </c>
     </row>
     <row r="59" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="101" t="s">
+      <c r="A59" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="B59" s="102"/>
-      <c r="C59" s="86"/>
-      <c r="D59" s="87"/>
-      <c r="E59" s="87"/>
-      <c r="F59" s="87"/>
-      <c r="G59" s="87"/>
-      <c r="H59" s="87"/>
-      <c r="I59" s="88"/>
+      <c r="B59" s="112"/>
+      <c r="C59" s="82"/>
+      <c r="D59" s="83"/>
+      <c r="E59" s="83"/>
+      <c r="F59" s="83"/>
+      <c r="G59" s="83"/>
+      <c r="H59" s="83"/>
+      <c r="I59" s="84"/>
       <c r="J59" s="40"/>
       <c r="K59" s="40"/>
       <c r="L59" s="1"/>
-      <c r="M59" s="101" t="s">
+      <c r="M59" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="N59" s="102"/>
-      <c r="O59" s="86"/>
-      <c r="P59" s="87"/>
-      <c r="Q59" s="87"/>
-      <c r="R59" s="87"/>
-      <c r="S59" s="87"/>
-      <c r="T59" s="87"/>
-      <c r="U59" s="88"/>
+      <c r="N59" s="112"/>
+      <c r="O59" s="82"/>
+      <c r="P59" s="83"/>
+      <c r="Q59" s="83"/>
+      <c r="R59" s="83"/>
+      <c r="S59" s="83"/>
+      <c r="T59" s="83"/>
+      <c r="U59" s="84"/>
       <c r="V59" s="1"/>
     </row>
     <row r="60" spans="1:22" ht="15" x14ac:dyDescent="0.2">
@@ -5451,14 +6015,62 @@
     </row>
   </sheetData>
   <mergeCells count="80">
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="M59:N59"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="M56:N56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="M57:N57"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="M58:N58"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="M5:U5"/>
+    <mergeCell ref="M20:U20"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="M48:N48"/>
+    <mergeCell ref="M49:N49"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="M46:N46"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="M15:U15"/>
+    <mergeCell ref="M45:U45"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="M35:U35"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="M54:N54"/>
+    <mergeCell ref="A50:I50"/>
+    <mergeCell ref="M50:U50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="M51:N51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="M52:N52"/>
     <mergeCell ref="A6:A14"/>
     <mergeCell ref="M6:M14"/>
     <mergeCell ref="A36:A44"/>
@@ -5475,62 +6087,14 @@
     <mergeCell ref="M29:N29"/>
     <mergeCell ref="A53:B53"/>
     <mergeCell ref="M53:N53"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="M54:N54"/>
-    <mergeCell ref="A50:I50"/>
-    <mergeCell ref="M50:U50"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="M51:N51"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="M52:N52"/>
-    <mergeCell ref="A45:I45"/>
-    <mergeCell ref="M15:U15"/>
-    <mergeCell ref="M45:U45"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="M35:U35"/>
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="M48:N48"/>
-    <mergeCell ref="M49:N49"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="M46:N46"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A5:I5"/>
-    <mergeCell ref="M5:U5"/>
-    <mergeCell ref="M20:U20"/>
-    <mergeCell ref="A15:I15"/>
-    <mergeCell ref="A25:I25"/>
-    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="M59:N59"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="M56:N56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="M57:N57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="M58:N58"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C2:I4 C6:I14 C16:I19 C21:I24 C26:I29">
@@ -5984,162 +6548,992 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A38A25A9-7BAB-4662-AC2A-B7F2DABCCE29}">
-  <dimension ref="B1:G12"/>
+  <dimension ref="B2:U25"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="7" max="7" width="17.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="B2" s="114" t="s">
+    <row r="2" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="2:14" ht="15" x14ac:dyDescent="0.25">
+      <c r="B3" s="127" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="120"/>
-      <c r="D2" s="117" t="s">
+      <c r="C3" s="133"/>
+      <c r="D3" s="130" t="s">
         <v>31</v>
       </c>
-      <c r="E2" s="118"/>
-      <c r="F2" s="118"/>
-      <c r="G2" s="119"/>
-    </row>
-    <row r="3" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="116"/>
-      <c r="C3" s="121"/>
-      <c r="D3" s="77" t="s">
+      <c r="E3" s="131"/>
+      <c r="F3" s="131"/>
+      <c r="G3" s="132"/>
+    </row>
+    <row r="4" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="129"/>
+      <c r="C4" s="134"/>
+      <c r="D4" s="137" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="74" t="s">
+      <c r="E4" s="136" t="s">
         <v>28</v>
       </c>
-      <c r="F3" s="74" t="s">
+      <c r="F4" s="136" t="s">
         <v>29</v>
       </c>
-      <c r="G3" s="83" t="s">
+      <c r="G4" s="71" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="84" t="s">
+    <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="80" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="85" t="s">
+      <c r="C5" s="81" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="78"/>
-      <c r="E4" s="79"/>
-      <c r="F4" s="79"/>
-      <c r="G4" s="80"/>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="D5" s="75"/>
+      <c r="E5" s="76">
+        <v>84.26</v>
+      </c>
+      <c r="F5" s="76">
+        <v>84.42</v>
+      </c>
+      <c r="G5" s="77"/>
+    </row>
+    <row r="6" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="25"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
       <c r="E6" s="25"/>
-      <c r="F6" s="25"/>
+      <c r="F6" s="25" t="s">
+        <v>32</v>
+      </c>
       <c r="G6" s="25"/>
     </row>
-    <row r="7" spans="2:7" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="25"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25" t="s">
-        <v>32</v>
-      </c>
-      <c r="G7" s="25"/>
-    </row>
-    <row r="8" spans="2:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="B8" s="114" t="s">
+    <row r="7" spans="2:14" ht="15" x14ac:dyDescent="0.25">
+      <c r="B7" s="127" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="120"/>
-      <c r="D8" s="117" t="s">
+      <c r="C7" s="133"/>
+      <c r="D7" s="130" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="118"/>
-      <c r="F8" s="118"/>
-      <c r="G8" s="119"/>
-    </row>
-    <row r="9" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="116"/>
-      <c r="C9" s="121"/>
-      <c r="D9" s="77" t="s">
+      <c r="E7" s="131"/>
+      <c r="F7" s="131"/>
+      <c r="G7" s="132"/>
+    </row>
+    <row r="8" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="129"/>
+      <c r="C8" s="134"/>
+      <c r="D8" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="74" t="s">
+      <c r="E8" s="72" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="74" t="s">
+      <c r="F8" s="72" t="s">
         <v>29</v>
       </c>
-      <c r="G9" s="83" t="s">
+      <c r="G8" s="71" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="10" spans="2:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="B10" s="114" t="s">
+      <c r="K8" s="135"/>
+      <c r="L8" s="135"/>
+    </row>
+    <row r="9" spans="2:14" ht="15" x14ac:dyDescent="0.25">
+      <c r="B9" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="70" t="s">
+      <c r="C9" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="68"/>
-      <c r="E10" s="69"/>
-      <c r="F10" s="69"/>
-      <c r="G10" s="81"/>
-    </row>
-    <row r="11" spans="2:7" ht="15" x14ac:dyDescent="0.25">
-      <c r="B11" s="115"/>
-      <c r="C11" s="72" t="s">
+      <c r="D9" s="68">
+        <v>83.95</v>
+      </c>
+      <c r="E9" s="135">
+        <v>84.26</v>
+      </c>
+      <c r="F9" s="135">
+        <v>84.42</v>
+      </c>
+      <c r="G9" s="138">
+        <v>83.98</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" ht="15" x14ac:dyDescent="0.25">
+      <c r="B10" s="128"/>
+      <c r="C10" s="71" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="71"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="73"/>
-    </row>
-    <row r="12" spans="2:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="116"/>
-      <c r="C12" s="83" t="s">
+      <c r="D10" s="70">
+        <v>83.86</v>
+      </c>
+      <c r="E10" s="25">
+        <v>83.93</v>
+      </c>
+      <c r="F10" s="25"/>
+      <c r="G10" s="139">
+        <v>83.47</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="129"/>
+      <c r="C11" s="79" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="82"/>
-      <c r="E12" s="75"/>
-      <c r="F12" s="75"/>
-      <c r="G12" s="76"/>
+      <c r="D11" s="78">
+        <v>82.35</v>
+      </c>
+      <c r="E11" s="73"/>
+      <c r="F11" s="73">
+        <v>82.35</v>
+      </c>
+      <c r="G11" s="140">
+        <v>79.91</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" ht="15" x14ac:dyDescent="0.25">
+      <c r="B12" s="147"/>
+      <c r="C12" s="136"/>
+      <c r="D12" s="135"/>
+      <c r="E12" s="135"/>
+      <c r="F12" s="135"/>
+      <c r="G12" s="135"/>
+    </row>
+    <row r="13" spans="2:14" ht="15" x14ac:dyDescent="0.25">
+      <c r="B13" s="147"/>
+      <c r="C13" s="136"/>
+      <c r="D13" s="135"/>
+      <c r="E13" s="135"/>
+      <c r="F13" s="135"/>
+      <c r="G13" s="135"/>
+    </row>
+    <row r="14" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="147"/>
+      <c r="C14" s="136"/>
+      <c r="D14" s="135"/>
+      <c r="E14" s="135"/>
+      <c r="F14" s="135"/>
+      <c r="G14" s="135"/>
+    </row>
+    <row r="15" spans="2:14" ht="15" x14ac:dyDescent="0.25">
+      <c r="B15" s="146" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" s="133"/>
+      <c r="D15" s="130" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" s="131"/>
+      <c r="F15" s="131"/>
+      <c r="G15" s="132"/>
+      <c r="I15" s="146" t="s">
+        <v>40</v>
+      </c>
+      <c r="J15" s="133"/>
+      <c r="K15" s="130" t="s">
+        <v>31</v>
+      </c>
+      <c r="L15" s="131"/>
+      <c r="M15" s="131"/>
+      <c r="N15" s="132"/>
+    </row>
+    <row r="16" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="129"/>
+      <c r="C16" s="134"/>
+      <c r="D16" s="74" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="72" t="s">
+        <v>28</v>
+      </c>
+      <c r="F16" s="72" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="71" t="s">
+        <v>33</v>
+      </c>
+      <c r="I16" s="129"/>
+      <c r="J16" s="134"/>
+      <c r="K16" s="74" t="s">
+        <v>27</v>
+      </c>
+      <c r="L16" s="72" t="s">
+        <v>28</v>
+      </c>
+      <c r="M16" s="72" t="s">
+        <v>29</v>
+      </c>
+      <c r="N16" s="71" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="2:21" ht="15" x14ac:dyDescent="0.25">
+      <c r="B17" s="127" t="s">
+        <v>30</v>
+      </c>
+      <c r="C17" s="69" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="68"/>
+      <c r="E17" s="135"/>
+      <c r="F17" s="135"/>
+      <c r="G17" s="138">
+        <v>92.97</v>
+      </c>
+      <c r="I17" s="127" t="s">
+        <v>30</v>
+      </c>
+      <c r="J17" s="69" t="s">
+        <v>27</v>
+      </c>
+      <c r="K17" s="68"/>
+      <c r="L17" s="135"/>
+      <c r="M17" s="135"/>
+      <c r="N17" s="138"/>
+    </row>
+    <row r="18" spans="2:21" ht="15" x14ac:dyDescent="0.25">
+      <c r="B18" s="128"/>
+      <c r="C18" s="71" t="s">
+        <v>28</v>
+      </c>
+      <c r="D18" s="70"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="139">
+        <v>93.55</v>
+      </c>
+      <c r="I18" s="128"/>
+      <c r="J18" s="71" t="s">
+        <v>28</v>
+      </c>
+      <c r="K18" s="70"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="25"/>
+      <c r="N18" s="139"/>
+    </row>
+    <row r="19" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="129"/>
+      <c r="C19" s="79" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="78"/>
+      <c r="E19" s="73"/>
+      <c r="F19" s="73"/>
+      <c r="G19" s="140">
+        <v>88.64</v>
+      </c>
+      <c r="I19" s="129"/>
+      <c r="J19" s="79" t="s">
+        <v>29</v>
+      </c>
+      <c r="K19" s="78"/>
+      <c r="L19" s="73"/>
+      <c r="M19" s="73"/>
+      <c r="N19" s="140"/>
+    </row>
+    <row r="20" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="2:21" ht="15" x14ac:dyDescent="0.25">
+      <c r="B21" s="146" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="133"/>
+      <c r="D21" s="130" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21" s="131"/>
+      <c r="F21" s="131"/>
+      <c r="G21" s="132"/>
+      <c r="I21" s="146" t="s">
+        <v>37</v>
+      </c>
+      <c r="J21" s="133"/>
+      <c r="K21" s="130" t="s">
+        <v>31</v>
+      </c>
+      <c r="L21" s="131"/>
+      <c r="M21" s="131"/>
+      <c r="N21" s="132"/>
+      <c r="P21" s="146" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q21" s="133"/>
+      <c r="R21" s="130" t="s">
+        <v>31</v>
+      </c>
+      <c r="S21" s="131"/>
+      <c r="T21" s="131"/>
+      <c r="U21" s="132"/>
+    </row>
+    <row r="22" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="129"/>
+      <c r="C22" s="134"/>
+      <c r="D22" s="74" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="72" t="s">
+        <v>28</v>
+      </c>
+      <c r="F22" s="72" t="s">
+        <v>29</v>
+      </c>
+      <c r="G22" s="71" t="s">
+        <v>33</v>
+      </c>
+      <c r="I22" s="129"/>
+      <c r="J22" s="134"/>
+      <c r="K22" s="74" t="s">
+        <v>27</v>
+      </c>
+      <c r="L22" s="72" t="s">
+        <v>28</v>
+      </c>
+      <c r="M22" s="72" t="s">
+        <v>29</v>
+      </c>
+      <c r="N22" s="71" t="s">
+        <v>33</v>
+      </c>
+      <c r="P22" s="129"/>
+      <c r="Q22" s="134"/>
+      <c r="R22" s="74" t="s">
+        <v>27</v>
+      </c>
+      <c r="S22" s="72" t="s">
+        <v>28</v>
+      </c>
+      <c r="T22" s="72" t="s">
+        <v>29</v>
+      </c>
+      <c r="U22" s="71" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="2:21" ht="15" x14ac:dyDescent="0.25">
+      <c r="B23" s="127" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" s="69" t="s">
+        <v>27</v>
+      </c>
+      <c r="D23" s="68">
+        <v>91.1</v>
+      </c>
+      <c r="E23" s="135">
+        <v>91.28</v>
+      </c>
+      <c r="F23" s="135">
+        <v>91.16</v>
+      </c>
+      <c r="G23" s="138">
+        <v>90.61</v>
+      </c>
+      <c r="I23" s="127" t="s">
+        <v>30</v>
+      </c>
+      <c r="J23" s="69" t="s">
+        <v>27</v>
+      </c>
+      <c r="K23" s="68">
+        <v>74.37</v>
+      </c>
+      <c r="L23" s="135">
+        <v>77.239999999999995</v>
+      </c>
+      <c r="M23" s="135">
+        <v>82.31</v>
+      </c>
+      <c r="N23" s="138">
+        <v>76.89</v>
+      </c>
+      <c r="P23" s="127" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q23" s="69" t="s">
+        <v>27</v>
+      </c>
+      <c r="R23" s="68">
+        <v>56.35</v>
+      </c>
+      <c r="S23" s="135">
+        <v>56.64</v>
+      </c>
+      <c r="T23" s="135">
+        <v>57.69</v>
+      </c>
+      <c r="U23" s="138">
+        <v>57.43</v>
+      </c>
+    </row>
+    <row r="24" spans="2:21" ht="15" x14ac:dyDescent="0.25">
+      <c r="B24" s="128"/>
+      <c r="C24" s="71" t="s">
+        <v>28</v>
+      </c>
+      <c r="D24" s="70">
+        <v>90.92</v>
+      </c>
+      <c r="E24" s="25">
+        <v>90.69</v>
+      </c>
+      <c r="F24" s="25">
+        <v>89.93</v>
+      </c>
+      <c r="G24" s="139">
+        <v>90.5</v>
+      </c>
+      <c r="I24" s="128"/>
+      <c r="J24" s="71" t="s">
+        <v>28</v>
+      </c>
+      <c r="K24" s="70">
+        <v>73.430000000000007</v>
+      </c>
+      <c r="L24" s="25">
+        <v>75.78</v>
+      </c>
+      <c r="M24" s="25">
+        <v>80.989999999999995</v>
+      </c>
+      <c r="N24" s="139">
+        <v>72.8</v>
+      </c>
+      <c r="P24" s="128"/>
+      <c r="Q24" s="71" t="s">
+        <v>28</v>
+      </c>
+      <c r="R24" s="70">
+        <v>56.56</v>
+      </c>
+      <c r="S24" s="25">
+        <v>55.76</v>
+      </c>
+      <c r="T24" s="25">
+        <v>55.07</v>
+      </c>
+      <c r="U24" s="139">
+        <v>54.06</v>
+      </c>
+    </row>
+    <row r="25" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="129"/>
+      <c r="C25" s="79" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="78">
+        <v>89.67</v>
+      </c>
+      <c r="E25" s="73">
+        <v>87.91</v>
+      </c>
+      <c r="F25" s="73">
+        <v>87.1</v>
+      </c>
+      <c r="G25" s="140">
+        <v>87.1</v>
+      </c>
+      <c r="I25" s="129"/>
+      <c r="J25" s="79" t="s">
+        <v>29</v>
+      </c>
+      <c r="K25" s="78">
+        <v>78.680000000000007</v>
+      </c>
+      <c r="L25" s="73">
+        <v>77.040000000000006</v>
+      </c>
+      <c r="M25" s="73">
+        <v>75.41</v>
+      </c>
+      <c r="N25" s="140">
+        <v>74.819999999999993</v>
+      </c>
+      <c r="P25" s="129"/>
+      <c r="Q25" s="79" t="s">
+        <v>29</v>
+      </c>
+      <c r="R25" s="78">
+        <v>53.09</v>
+      </c>
+      <c r="S25" s="73">
+        <v>51.47</v>
+      </c>
+      <c r="T25" s="73">
+        <v>50.41</v>
+      </c>
+      <c r="U25" s="140">
+        <v>50.06</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="D8:G8"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="B2:C3"/>
-    <mergeCell ref="B8:C9"/>
+  <mergeCells count="20">
+    <mergeCell ref="P23:P25"/>
+    <mergeCell ref="I21:J22"/>
+    <mergeCell ref="K21:N21"/>
+    <mergeCell ref="I23:I25"/>
+    <mergeCell ref="B21:C22"/>
+    <mergeCell ref="D21:G21"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="P21:Q22"/>
+    <mergeCell ref="R21:U21"/>
+    <mergeCell ref="B15:C16"/>
+    <mergeCell ref="D15:G15"/>
+    <mergeCell ref="I15:J16"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="I17:I19"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="D7:G7"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="B3:C4"/>
+    <mergeCell ref="B7:C8"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="D4:G4">
+  <conditionalFormatting sqref="D5:G5">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF5A8AC6"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D10:F14 D9">
+    <cfRule type="colorScale" priority="41">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K8:L8">
+    <cfRule type="colorScale" priority="37">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E9:F9">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G9">
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G10">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G11:G14">
+    <cfRule type="colorScale" priority="33">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D9:G14">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R24:T25 R23">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S23:T23">
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U23">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U24">
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U25">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R23:U25">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K24:M25 K23">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L23:M23">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N23">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N24">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N25">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K23:N25">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D24:F25 D23">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E23:F23">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G23">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G24">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G25">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D23:G25">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K18:M19 K17">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L17:M17">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N17">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N18">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N19">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K17:N19">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D18:F19 D17">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17:F17">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G17">
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G18">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D17:G19">
     <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D10:G12">
-    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>

--- a/results_(stress_test)_baselines/summary.xlsx
+++ b/results_(stress_test)_baselines/summary.xlsx
@@ -5,18 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RnD_Repo\Research_Engineeirng\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_baselines\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\RnD_Repo\Research_Engineering\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_baselines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4162CE8-64BE-4568-A20A-1A9F39FAEBC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCD0E556-7A82-4991-BDE7-C1F21762A7A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="639" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-210" windowWidth="29040" windowHeight="16440" tabRatio="639" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="partialdata_20260618_unf_idx" sheetId="6" r:id="rId1"/>
     <sheet name="figure" sheetId="8" r:id="rId2"/>
     <sheet name="fullldata_20260524_spt_idx" sheetId="5" r:id="rId3"/>
     <sheet name="confusion_mtx" sheetId="7" r:id="rId4"/>
+    <sheet name="confusion_mtx (2)" sheetId="9" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -59,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="39">
   <si>
     <t>Accuracy</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -189,15 +190,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0 (no threshold)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Basis</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -269,7 +262,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -285,6 +278,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,7 +469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -626,9 +625,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -641,28 +637,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
@@ -706,136 +681,232 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1113,7 +1184,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4687D530-62F3-45D6-8CBF-3B0602E24BE5}">
-  <dimension ref="A1:R55"/>
+  <dimension ref="A1:R60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25" style="10" customWidth="1"/>
@@ -1177,23 +1248,23 @@
       <c r="R1" s="12"/>
     </row>
     <row r="2" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="114" t="s">
+      <c r="A2" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="115"/>
-      <c r="C2" s="89">
+      <c r="B2" s="114"/>
+      <c r="C2" s="170">
         <v>92.97270449283009</v>
       </c>
-      <c r="D2" s="90">
+      <c r="D2" s="171">
         <v>92.656851126163161</v>
       </c>
-      <c r="E2" s="90">
+      <c r="E2" s="171">
         <v>90.612485113769722</v>
       </c>
-      <c r="F2" s="90">
+      <c r="F2" s="171">
         <v>76.890048068466555</v>
       </c>
-      <c r="G2" s="91">
+      <c r="G2" s="172">
         <v>57.431157132270449</v>
       </c>
       <c r="H2" s="23" cm="1">
@@ -1208,23 +1279,23 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:G2)&amp;","</f>
         <v xml:space="preserve">    92.9727044928301, 92.6568511261632, 90.6124851137697, 76.8900480684666, 57.4311571322704,</v>
       </c>
-      <c r="K2" s="114" t="s">
+      <c r="K2" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="115"/>
-      <c r="M2" s="89">
+      <c r="L2" s="114"/>
+      <c r="M2" s="81">
         <v>3.6723191410127392</v>
       </c>
-      <c r="N2" s="90">
+      <c r="N2" s="82">
         <v>3.8557140126956959</v>
       </c>
-      <c r="O2" s="90">
+      <c r="O2" s="82">
         <v>4.1717853309388913</v>
       </c>
-      <c r="P2" s="90">
+      <c r="P2" s="82">
         <v>8.1206319222896362</v>
       </c>
-      <c r="Q2" s="91">
+      <c r="Q2" s="83">
         <v>8.7326493747450371</v>
       </c>
       <c r="R2" s="12" t="str">
@@ -1233,23 +1304,23 @@
       </c>
     </row>
     <row r="3" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="114" t="s">
+      <c r="A3" s="113" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="115"/>
-      <c r="C3" s="92">
+      <c r="B3" s="114"/>
+      <c r="C3" s="173">
         <v>93.550650668835075</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="174">
         <v>92.282219857726602</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="174">
         <v>90.501679656975099</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="174">
         <v>72.805808585426078</v>
       </c>
-      <c r="G3" s="93">
+      <c r="G3" s="175">
         <v>54.064066298151367</v>
       </c>
       <c r="H3" s="23" cm="1">
@@ -1264,11 +1335,11 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:G3)&amp;","</f>
         <v xml:space="preserve">    93.5506506688351, 92.2822198577266, 90.5016796569751, 72.8058085854261, 54.0640662981514,</v>
       </c>
-      <c r="K3" s="114" t="s">
+      <c r="K3" s="113" t="s">
         <v>6</v>
       </c>
-      <c r="L3" s="115"/>
-      <c r="M3" s="92">
+      <c r="L3" s="114"/>
+      <c r="M3" s="84">
         <v>3.5444962758226279</v>
       </c>
       <c r="N3">
@@ -1280,7 +1351,7 @@
       <c r="P3">
         <v>9.1245390051568016</v>
       </c>
-      <c r="Q3" s="93">
+      <c r="Q3" s="85">
         <v>7.5991148630492704</v>
       </c>
       <c r="R3" s="12" t="str">
@@ -1289,23 +1360,23 @@
       </c>
     </row>
     <row r="4" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="119" t="s">
+      <c r="A4" s="115" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="120"/>
-      <c r="C4" s="92">
+      <c r="B4" s="116"/>
+      <c r="C4" s="173">
         <v>88.646029233240199</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="174">
         <v>87.588003933136662</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="174">
         <v>87.102273087714138</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="174">
         <v>74.826714187262283</v>
       </c>
-      <c r="G4" s="93">
+      <c r="G4" s="175">
         <v>50.055245575942109</v>
       </c>
       <c r="H4" s="34" cm="1">
@@ -1320,11 +1391,11 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C4:G4)&amp;","</f>
         <v xml:space="preserve">    88.6460292332402, 87.5880039331367, 87.1022730877141, 74.8267141872623, 50.0552455759421,</v>
       </c>
-      <c r="K4" s="119" t="s">
+      <c r="K4" s="115" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="120"/>
-      <c r="M4" s="92">
+      <c r="L4" s="116"/>
+      <c r="M4" s="84">
         <v>3.1531095164540388</v>
       </c>
       <c r="N4">
@@ -1336,7 +1407,7 @@
       <c r="P4">
         <v>2.8561346399896621</v>
       </c>
-      <c r="Q4" s="93">
+      <c r="Q4" s="85">
         <v>1.6635727988470741</v>
       </c>
       <c r="R4" s="12" t="str">
@@ -1345,49 +1416,49 @@
       </c>
     </row>
     <row r="5" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="114" t="s">
+      <c r="A5" s="113" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="116"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="115"/>
+      <c r="B5" s="117"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="114"/>
       <c r="H5" s="34"/>
       <c r="I5" s="34"/>
       <c r="J5" s="12"/>
-      <c r="K5" s="114" t="s">
+      <c r="K5" s="113" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="116"/>
-      <c r="M5" s="116"/>
-      <c r="N5" s="116"/>
-      <c r="O5" s="116"/>
-      <c r="P5" s="116"/>
-      <c r="Q5" s="115"/>
+      <c r="L5" s="117"/>
+      <c r="M5" s="117"/>
+      <c r="N5" s="117"/>
+      <c r="O5" s="117"/>
+      <c r="P5" s="117"/>
+      <c r="Q5" s="114"/>
       <c r="R5" s="12"/>
     </row>
     <row r="6" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="119" t="s">
+      <c r="A6" s="115" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="103" t="s">
+      <c r="B6" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="89">
+      <c r="C6" s="170">
         <v>93.375631853793436</v>
       </c>
-      <c r="D6" s="90">
+      <c r="D6" s="171">
         <v>92.792878831131745</v>
       </c>
-      <c r="E6" s="90">
+      <c r="E6" s="171">
         <v>91.094066557669166</v>
       </c>
-      <c r="F6" s="90">
+      <c r="F6" s="171">
         <v>74.369665827559075</v>
       </c>
-      <c r="G6" s="91">
+      <c r="G6" s="172">
         <v>56.35401113619784</v>
       </c>
       <c r="H6" s="34" cm="1">
@@ -1399,47 +1470,47 @@
         <v>83.954594024025582</v>
       </c>
       <c r="J6" s="12"/>
-      <c r="K6" s="119" t="s">
+      <c r="K6" s="115" t="s">
         <v>11</v>
       </c>
-      <c r="L6" s="103" t="s">
+      <c r="L6" s="95" t="s">
         <v>17</v>
       </c>
-      <c r="M6" s="89">
+      <c r="M6" s="81">
         <v>3.4841780245944278</v>
       </c>
-      <c r="N6" s="90">
+      <c r="N6" s="82">
         <v>3.7171339527240979</v>
       </c>
-      <c r="O6" s="90">
+      <c r="O6" s="82">
         <v>3.5950208209222092</v>
       </c>
-      <c r="P6" s="90">
+      <c r="P6" s="82">
         <v>8.5619397568121691</v>
       </c>
-      <c r="Q6" s="91">
+      <c r="Q6" s="83">
         <v>8.7436032668579529</v>
       </c>
       <c r="R6" s="12"/>
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="121"/>
-      <c r="B7" s="103" t="s">
+      <c r="A7" s="120"/>
+      <c r="B7" s="95" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="92">
+      <c r="C7" s="173">
         <v>93.358985227669237</v>
       </c>
-      <c r="D7" s="141">
+      <c r="D7" s="174">
         <v>92.785690187631374</v>
       </c>
-      <c r="E7" s="141">
+      <c r="E7" s="174">
         <v>91.279001836809442</v>
       </c>
-      <c r="F7" s="141">
+      <c r="F7" s="174">
         <v>77.243569004345488</v>
       </c>
-      <c r="G7" s="93">
+      <c r="G7" s="175">
         <v>56.641689518652129</v>
       </c>
       <c r="H7" s="34" cm="1">
@@ -1454,23 +1525,23 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C7:G7)&amp;","</f>
         <v xml:space="preserve">    93.3589852276692, 92.7856901876314, 91.2790018368094, 77.2435690043455, 56.6416895186521,</v>
       </c>
-      <c r="K7" s="121"/>
-      <c r="L7" s="103" t="s">
+      <c r="K7" s="120"/>
+      <c r="L7" s="95" t="s">
         <v>13</v>
       </c>
-      <c r="M7" s="92">
+      <c r="M7" s="84">
         <v>3.5292136776947389</v>
       </c>
-      <c r="N7" s="141">
+      <c r="N7">
         <v>3.7787197360632829</v>
       </c>
-      <c r="O7" s="141">
+      <c r="O7">
         <v>3.589155414302748</v>
       </c>
-      <c r="P7" s="141">
+      <c r="P7">
         <v>7.7490040503559836</v>
       </c>
-      <c r="Q7" s="93">
+      <c r="Q7" s="85">
         <v>8.6647795337348459</v>
       </c>
       <c r="R7" s="12" t="str">
@@ -1479,23 +1550,23 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="121"/>
+      <c r="A8" s="120"/>
       <c r="B8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="92">
+      <c r="C8" s="173">
         <v>92.744346116027529</v>
       </c>
-      <c r="D8" s="141">
+      <c r="D8" s="174">
         <v>92.328416912487711</v>
       </c>
-      <c r="E8" s="141">
+      <c r="E8" s="174">
         <v>91.156108616856514</v>
       </c>
-      <c r="F8" s="141">
+      <c r="F8" s="174">
         <v>82.307782362592519</v>
       </c>
-      <c r="G8" s="93">
+      <c r="G8" s="175">
         <v>57.694504277718679</v>
       </c>
       <c r="H8" s="34" cm="1">
@@ -1510,23 +1581,23 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C8:G8)&amp;","</f>
         <v xml:space="preserve">    92.7443461160275, 92.3284169124877, 91.1561086168565, 82.3077823625925, 57.6945042777187,</v>
       </c>
-      <c r="K8" s="121"/>
+      <c r="K8" s="120"/>
       <c r="L8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="M8" s="92">
+      <c r="M8" s="84">
         <v>3.3427481085122568</v>
       </c>
-      <c r="N8" s="141">
+      <c r="N8">
         <v>3.376440347285802</v>
       </c>
-      <c r="O8" s="141">
+      <c r="O8">
         <v>3.0132050938587081</v>
       </c>
-      <c r="P8" s="141">
+      <c r="P8">
         <v>4.6775599948055158</v>
       </c>
-      <c r="Q8" s="93">
+      <c r="Q8" s="85">
         <v>6.3264357320363649</v>
       </c>
       <c r="R8" s="12" t="str">
@@ -1535,23 +1606,23 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="121"/>
+      <c r="A9" s="120"/>
       <c r="B9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="92">
+      <c r="C9" s="173">
         <v>93.721730580137674</v>
       </c>
-      <c r="D9" s="141">
+      <c r="D9" s="174">
         <v>92.415934970602393</v>
       </c>
-      <c r="E9" s="141">
+      <c r="E9" s="174">
         <v>90.686860036274823</v>
       </c>
-      <c r="F9" s="141">
+      <c r="F9" s="174">
         <v>75.782143444147451</v>
       </c>
-      <c r="G9" s="93">
+      <c r="G9" s="175">
         <v>55.768484156437339</v>
       </c>
       <c r="H9" s="34" cm="1">
@@ -1563,45 +1634,45 @@
         <v>83.937535593589331</v>
       </c>
       <c r="J9" s="12"/>
-      <c r="K9" s="121"/>
+      <c r="K9" s="120"/>
       <c r="L9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="M9" s="92">
+      <c r="M9" s="84">
         <v>3.5340996284974531</v>
       </c>
-      <c r="N9" s="141">
+      <c r="N9">
         <v>3.480694084881371</v>
       </c>
-      <c r="O9" s="141">
+      <c r="O9">
         <v>3.5404972441590532</v>
       </c>
-      <c r="P9" s="141">
+      <c r="P9">
         <v>8.2748920802292076</v>
       </c>
-      <c r="Q9" s="93">
+      <c r="Q9" s="85">
         <v>8.6222095079337446</v>
       </c>
       <c r="R9" s="12"/>
     </row>
     <row r="10" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="121"/>
+      <c r="A10" s="120"/>
       <c r="B10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="92">
+      <c r="C10" s="173">
         <v>93.578171091445412</v>
       </c>
-      <c r="D10" s="141">
+      <c r="D10" s="174">
         <v>92.721736347200235</v>
       </c>
-      <c r="E10" s="141">
+      <c r="E10" s="174">
         <v>90.919630215947663</v>
       </c>
-      <c r="F10" s="141">
+      <c r="F10" s="174">
         <v>73.42964039481312</v>
       </c>
-      <c r="G10" s="93">
+      <c r="G10" s="175">
         <v>56.559615567608724</v>
       </c>
       <c r="H10" s="34" cm="1">
@@ -1613,23 +1684,23 @@
         <v>83.864141342053131</v>
       </c>
       <c r="J10" s="12"/>
-      <c r="K10" s="121"/>
+      <c r="K10" s="120"/>
       <c r="L10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="M10" s="92">
+      <c r="M10" s="84">
         <v>3.4211604643278899</v>
       </c>
-      <c r="N10" s="141">
+      <c r="N10">
         <v>3.758697386182225</v>
       </c>
-      <c r="O10" s="141">
+      <c r="O10">
         <v>3.9384751732193859</v>
       </c>
-      <c r="P10" s="141">
+      <c r="P10">
         <v>8.9824743171696255</v>
       </c>
-      <c r="Q10" s="93">
+      <c r="Q10" s="85">
         <v>8.2082515511175735</v>
       </c>
       <c r="R10" s="12" t="str">
@@ -1638,23 +1709,23 @@
       </c>
     </row>
     <row r="11" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="121"/>
+      <c r="A11" s="120"/>
       <c r="B11" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="92">
+      <c r="C11" s="173">
         <v>91.299901671583086</v>
       </c>
-      <c r="D11" s="141">
+      <c r="D11" s="174">
         <v>90.822048633638715</v>
       </c>
-      <c r="E11" s="141">
+      <c r="E11" s="174">
         <v>89.932372540708258</v>
       </c>
-      <c r="F11" s="141">
+      <c r="F11" s="174">
         <v>80.986383965259208</v>
       </c>
-      <c r="G11" s="93">
+      <c r="G11" s="175">
         <v>55.071488507686048</v>
       </c>
       <c r="H11" s="34" cm="1">
@@ -1666,45 +1737,45 @@
         <v>83.059021019501316</v>
       </c>
       <c r="J11" s="12"/>
-      <c r="K11" s="121"/>
+      <c r="K11" s="120"/>
       <c r="L11" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="M11" s="92">
+      <c r="M11" s="84">
         <v>3.058139598469626</v>
       </c>
-      <c r="N11" s="141">
+      <c r="N11">
         <v>2.6470632106161909</v>
       </c>
-      <c r="O11" s="141">
+      <c r="O11">
         <v>2.660097338781473</v>
       </c>
-      <c r="P11" s="141">
+      <c r="P11">
         <v>4.2324186928534564</v>
       </c>
-      <c r="Q11" s="93">
+      <c r="Q11" s="85">
         <v>6.3408360836535147</v>
       </c>
       <c r="R11" s="12"/>
     </row>
     <row r="12" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="121"/>
-      <c r="B12" s="101" t="s">
+      <c r="A12" s="120"/>
+      <c r="B12" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="92">
+      <c r="C12" s="173">
         <v>88.345132743362853</v>
       </c>
-      <c r="D12" s="141">
+      <c r="D12" s="174">
         <v>87.267453294001967</v>
       </c>
-      <c r="E12" s="141">
+      <c r="E12" s="174">
         <v>87.102446099591404</v>
       </c>
-      <c r="F12" s="141">
+      <c r="F12" s="174">
         <v>75.414922851120394</v>
       </c>
-      <c r="G12" s="93">
+      <c r="G12" s="175">
         <v>50.409063515543693</v>
       </c>
       <c r="H12" s="34" cm="1">
@@ -1716,45 +1787,45 @@
         <v>79.788719066918105</v>
       </c>
       <c r="J12" s="12"/>
-      <c r="K12" s="121"/>
-      <c r="L12" s="101" t="s">
+      <c r="K12" s="120"/>
+      <c r="L12" s="93" t="s">
         <v>16</v>
       </c>
-      <c r="M12" s="92">
+      <c r="M12" s="84">
         <v>2.983926605181269</v>
       </c>
-      <c r="N12" s="141">
+      <c r="N12">
         <v>2.3996463413185389</v>
       </c>
-      <c r="O12" s="141">
+      <c r="O12">
         <v>1.62526252442654</v>
       </c>
-      <c r="P12" s="141">
+      <c r="P12">
         <v>3.3792106059866658</v>
       </c>
-      <c r="Q12" s="93">
+      <c r="Q12" s="85">
         <v>1.3738116379133549</v>
       </c>
       <c r="R12" s="12"/>
     </row>
     <row r="13" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="121"/>
-      <c r="B13" s="101" t="s">
+      <c r="A13" s="120"/>
+      <c r="B13" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="92">
+      <c r="C13" s="173">
         <v>90.553588987217324</v>
       </c>
-      <c r="D13" s="141">
+      <c r="D13" s="174">
         <v>90.325467059980355</v>
       </c>
-      <c r="E13" s="141">
+      <c r="E13" s="174">
         <v>89.668636118536241</v>
       </c>
-      <c r="F13" s="141">
+      <c r="F13" s="174">
         <v>78.678561233228677</v>
       </c>
-      <c r="G13" s="93">
+      <c r="G13" s="175">
         <v>53.098925307889047</v>
       </c>
       <c r="H13" s="34" cm="1">
@@ -1766,23 +1837,23 @@
         <v>82.358773198009231</v>
       </c>
       <c r="J13" s="12"/>
-      <c r="K13" s="121"/>
-      <c r="L13" s="101" t="s">
+      <c r="K13" s="120"/>
+      <c r="L13" s="93" t="s">
         <v>19</v>
       </c>
-      <c r="M13" s="92">
+      <c r="M13" s="84">
         <v>2.5990157411770438</v>
       </c>
-      <c r="N13" s="141">
+      <c r="N13">
         <v>2.3843919339500612</v>
       </c>
-      <c r="O13" s="141">
+      <c r="O13">
         <v>2.4318730481068318</v>
       </c>
-      <c r="P13" s="141">
+      <c r="P13">
         <v>3.814135483602267</v>
       </c>
-      <c r="Q13" s="93">
+      <c r="Q13" s="85">
         <v>3.5742222382122981</v>
       </c>
       <c r="R13" s="12" t="str">
@@ -1791,23 +1862,23 @@
       </c>
     </row>
     <row r="14" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="117"/>
-      <c r="B14" s="101" t="s">
+      <c r="A14" s="118"/>
+      <c r="B14" s="93" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="94">
+      <c r="C14" s="77">
         <v>89.149459193706974</v>
       </c>
-      <c r="D14" s="95">
+      <c r="D14" s="78">
         <v>88.338249754178975</v>
       </c>
-      <c r="E14" s="95">
+      <c r="E14" s="78">
         <v>87.909618595316573</v>
       </c>
-      <c r="F14" s="95">
+      <c r="F14" s="78">
         <v>77.044259321735765</v>
       </c>
-      <c r="G14" s="96">
+      <c r="G14" s="79">
         <v>51.470476964910311</v>
       </c>
       <c r="H14" s="34" cm="1">
@@ -1819,69 +1890,69 @@
         <v>80.728613659431886</v>
       </c>
       <c r="J14" s="12"/>
-      <c r="K14" s="117"/>
-      <c r="L14" s="101" t="s">
+      <c r="K14" s="118"/>
+      <c r="L14" s="93" t="s">
         <v>26</v>
       </c>
-      <c r="M14" s="94">
+      <c r="M14" s="86">
         <v>2.7752984471319091</v>
       </c>
-      <c r="N14" s="95">
+      <c r="N14" s="87">
         <v>2.3015697910981339</v>
       </c>
-      <c r="O14" s="95">
+      <c r="O14" s="87">
         <v>2.0162357843530452</v>
       </c>
-      <c r="P14" s="95">
+      <c r="P14" s="87">
         <v>3.0539531580418511</v>
       </c>
-      <c r="Q14" s="96">
+      <c r="Q14" s="88">
         <v>1.6877124305890641</v>
       </c>
       <c r="R14" s="12"/>
     </row>
     <row r="15" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="114" t="s">
+      <c r="A15" s="113" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="116"/>
-      <c r="C15" s="116"/>
-      <c r="D15" s="116"/>
-      <c r="E15" s="116"/>
-      <c r="F15" s="116"/>
-      <c r="G15" s="115"/>
+      <c r="B15" s="117"/>
+      <c r="C15" s="117"/>
+      <c r="D15" s="117"/>
+      <c r="E15" s="117"/>
+      <c r="F15" s="117"/>
+      <c r="G15" s="114"/>
       <c r="H15" s="34"/>
       <c r="I15" s="34"/>
       <c r="J15" s="12"/>
-      <c r="K15" s="114" t="s">
+      <c r="K15" s="113" t="s">
         <v>20</v>
       </c>
-      <c r="L15" s="116"/>
-      <c r="M15" s="116"/>
-      <c r="N15" s="116"/>
-      <c r="O15" s="116"/>
-      <c r="P15" s="116"/>
-      <c r="Q15" s="115"/>
+      <c r="L15" s="117"/>
+      <c r="M15" s="117"/>
+      <c r="N15" s="117"/>
+      <c r="O15" s="117"/>
+      <c r="P15" s="117"/>
+      <c r="Q15" s="114"/>
       <c r="R15" s="12"/>
     </row>
     <row r="16" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="117" t="s">
+      <c r="A16" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="118"/>
-      <c r="C16" s="92">
+      <c r="B16" s="119"/>
+      <c r="C16" s="173">
         <v>93.207752662220258</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="174">
         <v>92.783034455315345</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="174">
         <v>90.565884364628303</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="174">
         <v>73.076886478256739</v>
       </c>
-      <c r="G16" s="93">
+      <c r="G16" s="175">
         <v>58.556994437668138</v>
       </c>
       <c r="H16" s="34" cm="1">
@@ -1896,11 +1967,11 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C16:G16)&amp;","</f>
         <v xml:space="preserve">    93.2077526622203, 92.7830344553153, 90.5658843646283, 73.0768864782567, 58.5569944376681,</v>
       </c>
-      <c r="K16" s="117" t="s">
+      <c r="K16" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="L16" s="118"/>
-      <c r="M16" s="92">
+      <c r="L16" s="119"/>
+      <c r="M16" s="84">
         <v>4.081079160307894</v>
       </c>
       <c r="N16">
@@ -1912,7 +1983,7 @@
       <c r="P16">
         <v>9.0889689998586825</v>
       </c>
-      <c r="Q16" s="93">
+      <c r="Q16" s="85">
         <v>9.0192886420696112</v>
       </c>
       <c r="R16" s="12" t="str">
@@ -1921,23 +1992,23 @@
       </c>
     </row>
     <row r="17" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="119" t="s">
+      <c r="A17" s="115" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="120"/>
-      <c r="C17" s="92">
+      <c r="B17" s="116"/>
+      <c r="C17" s="173">
         <v>93.534975792754821</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="174">
         <v>92.336467731843129</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="174">
         <v>88.593520128490155</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="174">
         <v>71.045294509468079</v>
       </c>
-      <c r="G17" s="93">
+      <c r="G17" s="175">
         <v>53.467062863865607</v>
       </c>
       <c r="H17" s="34" cm="1">
@@ -1952,11 +2023,11 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C17:G17)&amp;","</f>
         <v xml:space="preserve">    93.5349757927548, 92.3364677318431, 88.5935201284902, 71.0452945094681, 53.4670628638656,</v>
       </c>
-      <c r="K17" s="114" t="s">
+      <c r="K17" s="113" t="s">
         <v>8</v>
       </c>
-      <c r="L17" s="115"/>
-      <c r="M17" s="92">
+      <c r="L17" s="114"/>
+      <c r="M17" s="84">
         <v>3.8494978151380188</v>
       </c>
       <c r="N17">
@@ -1968,7 +2039,7 @@
       <c r="P17">
         <v>10.247976510425289</v>
       </c>
-      <c r="Q17" s="93">
+      <c r="Q17" s="85">
         <v>9.5145399413620808</v>
       </c>
       <c r="R17" s="12" t="str">
@@ -1977,23 +2048,23 @@
       </c>
     </row>
     <row r="18" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="114" t="s">
+      <c r="A18" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="115"/>
-      <c r="C18" s="92">
+      <c r="B18" s="114"/>
+      <c r="C18" s="173">
         <v>93.005297046975599</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="174">
         <v>91.902444369472647</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="174">
         <v>89.116278399178753</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="174">
         <v>72.258814234263852</v>
       </c>
-      <c r="G18" s="93">
+      <c r="G18" s="175">
         <v>53.843628981796257</v>
       </c>
       <c r="H18" s="34" cm="1">
@@ -2008,11 +2079,11 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C18:G18)&amp;","</f>
         <v xml:space="preserve">    93.0052970469756, 91.9024443694726, 89.1162783991788, 72.2588142342639, 53.8436289817963,</v>
       </c>
-      <c r="K18" s="114" t="s">
+      <c r="K18" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="L18" s="115"/>
-      <c r="M18" s="92">
+      <c r="L18" s="114"/>
+      <c r="M18" s="84">
         <v>3.458803648865628</v>
       </c>
       <c r="N18">
@@ -2024,7 +2095,7 @@
       <c r="P18">
         <v>10.1810612930344</v>
       </c>
-      <c r="Q18" s="93">
+      <c r="Q18" s="85">
         <v>8.6745540222164905</v>
       </c>
       <c r="R18" s="12" t="str">
@@ -2033,15 +2104,15 @@
       </c>
     </row>
     <row r="19" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="119" t="s">
+      <c r="A19" s="115" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="120"/>
-      <c r="C19" s="99"/>
+      <c r="B19" s="116"/>
+      <c r="C19" s="91"/>
       <c r="D19" s="34"/>
       <c r="E19" s="34"/>
       <c r="F19" s="34"/>
-      <c r="G19" s="100"/>
+      <c r="G19" s="92"/>
       <c r="H19" s="34" cm="1">
         <f t="array" ref="H19">-SUMPRODUCT((D1:F1-C1:E1)*(C19:E19+D19:F19)/2)</f>
         <v>0</v>
@@ -2054,62 +2125,62 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C19:G19)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="K19" s="119" t="s">
+      <c r="K19" s="115" t="s">
         <v>22</v>
       </c>
-      <c r="L19" s="120"/>
-      <c r="M19" s="99"/>
+      <c r="L19" s="116"/>
+      <c r="M19" s="91"/>
       <c r="N19" s="34"/>
       <c r="O19" s="34"/>
       <c r="P19" s="34"/>
-      <c r="Q19" s="100"/>
+      <c r="Q19" s="92"/>
       <c r="R19" s="12" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M19:Q19)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
     </row>
     <row r="20" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="114" t="s">
+      <c r="A20" s="113" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="116"/>
-      <c r="C20" s="116"/>
-      <c r="D20" s="116"/>
-      <c r="E20" s="116"/>
-      <c r="F20" s="116"/>
-      <c r="G20" s="115"/>
+      <c r="B20" s="117"/>
+      <c r="C20" s="117"/>
+      <c r="D20" s="117"/>
+      <c r="E20" s="117"/>
+      <c r="F20" s="117"/>
+      <c r="G20" s="114"/>
       <c r="H20" s="34"/>
       <c r="I20" s="34"/>
       <c r="J20" s="12"/>
-      <c r="K20" s="114" t="s">
+      <c r="K20" s="113" t="s">
         <v>23</v>
       </c>
-      <c r="L20" s="116"/>
-      <c r="M20" s="116"/>
-      <c r="N20" s="116"/>
-      <c r="O20" s="116"/>
-      <c r="P20" s="116"/>
-      <c r="Q20" s="115"/>
+      <c r="L20" s="117"/>
+      <c r="M20" s="117"/>
+      <c r="N20" s="117"/>
+      <c r="O20" s="117"/>
+      <c r="P20" s="117"/>
+      <c r="Q20" s="114"/>
       <c r="R20" s="12"/>
     </row>
     <row r="21" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="117" t="s">
+      <c r="A21" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="118"/>
-      <c r="C21" s="92">
+      <c r="B21" s="119"/>
+      <c r="C21" s="173">
         <v>93.204569243678591</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="174">
         <v>92.71893643831983</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="174">
         <v>91.010196166633492</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="174">
         <v>77.775612245780678</v>
       </c>
-      <c r="G21" s="93">
+      <c r="G21" s="175">
         <v>55.921856302101808</v>
       </c>
       <c r="H21" s="34" cm="1">
@@ -2124,11 +2195,11 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:G21)&amp;","</f>
         <v xml:space="preserve">    93.2045692436786, 92.7189364383198, 91.0101961666335, 77.7756122457807, 55.9218563021018,</v>
       </c>
-      <c r="K21" s="117" t="s">
+      <c r="K21" s="118" t="s">
         <v>7</v>
       </c>
-      <c r="L21" s="118"/>
-      <c r="M21" s="92">
+      <c r="L21" s="119"/>
+      <c r="M21" s="84">
         <v>3.5338969773137729</v>
       </c>
       <c r="N21">
@@ -2140,7 +2211,7 @@
       <c r="P21">
         <v>6.7863547394302319</v>
       </c>
-      <c r="Q21" s="93">
+      <c r="Q21" s="85">
         <v>8.2097242202983072</v>
       </c>
       <c r="R21" s="12" t="str">
@@ -2149,23 +2220,23 @@
       </c>
     </row>
     <row r="22" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="119" t="s">
+      <c r="A22" s="115" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="120"/>
-      <c r="C22" s="92">
+      <c r="B22" s="116"/>
+      <c r="C22" s="173">
         <v>91.935155148400952</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="174">
         <v>91.692255123314226</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="174">
         <v>89.847648624411406</v>
       </c>
-      <c r="F22">
+      <c r="F22" s="174">
         <v>79.400747411309794</v>
       </c>
-      <c r="G22" s="93">
+      <c r="G22" s="175">
         <v>53.25364406266489</v>
       </c>
       <c r="H22" s="34" cm="1">
@@ -2180,11 +2251,11 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C22:G22)&amp;","</f>
         <v xml:space="preserve">    91.935155148401, 91.6922551233142, 89.8476486244114, 79.4007474113098, 53.2536440626649,</v>
       </c>
-      <c r="K22" s="114" t="s">
+      <c r="K22" s="113" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="115"/>
-      <c r="M22" s="92">
+      <c r="L22" s="114"/>
+      <c r="M22" s="84">
         <v>3.0404967647063641</v>
       </c>
       <c r="N22">
@@ -2196,7 +2267,7 @@
       <c r="P22">
         <v>3.323723681934811</v>
       </c>
-      <c r="Q22" s="93">
+      <c r="Q22" s="85">
         <v>4.2607284397566696</v>
       </c>
       <c r="R22" s="12" t="str">
@@ -2205,23 +2276,23 @@
       </c>
     </row>
     <row r="23" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="114" t="s">
+      <c r="A23" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="115"/>
-      <c r="C23" s="92">
+      <c r="B23" s="114"/>
+      <c r="C23" s="173">
         <v>93.32960781090955</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="174">
         <v>92.627433339965464</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="174">
         <v>90.919543710009009</v>
       </c>
-      <c r="F23">
+      <c r="F23" s="174">
         <v>77.743400317765136</v>
       </c>
-      <c r="G23" s="93">
+      <c r="G23" s="175">
         <v>58.391070280308071</v>
       </c>
       <c r="H23" s="34" cm="1">
@@ -2236,11 +2307,11 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C23:G23)&amp;","</f>
         <v xml:space="preserve">    93.3296078109096, 92.6274333399655, 90.919543710009, 77.7434003177651, 58.3910702803081,</v>
       </c>
-      <c r="K23" s="114" t="s">
+      <c r="K23" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="L23" s="115"/>
-      <c r="M23" s="92">
+      <c r="L23" s="114"/>
+      <c r="M23" s="84">
         <v>3.3471189071482028</v>
       </c>
       <c r="N23">
@@ -2252,7 +2323,7 @@
       <c r="P23">
         <v>7.5417080235248886</v>
       </c>
-      <c r="Q23" s="93">
+      <c r="Q23" s="85">
         <v>8.4137702230121008</v>
       </c>
       <c r="R23" s="12" t="str">
@@ -2261,15 +2332,15 @@
       </c>
     </row>
     <row r="24" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="114" t="s">
+      <c r="A24" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="115"/>
+      <c r="B24" s="114"/>
       <c r="C24" s="35"/>
       <c r="D24" s="36"/>
       <c r="E24" s="36"/>
       <c r="F24" s="36"/>
-      <c r="G24" s="97"/>
+      <c r="G24" s="89"/>
       <c r="H24" s="34" cm="1">
         <f t="array" ref="H24">-SUMPRODUCT((D1:F1-C1:E1)*(C24:E24+D24:F24)/2)</f>
         <v>0</v>
@@ -2282,1139 +2353,1279 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C24:G24)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="K24" s="114" t="s">
+      <c r="K24" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="L24" s="115"/>
+      <c r="L24" s="114"/>
       <c r="M24" s="35"/>
       <c r="N24" s="36"/>
       <c r="O24" s="36"/>
       <c r="P24" s="36"/>
-      <c r="Q24" s="97"/>
+      <c r="Q24" s="89"/>
       <c r="R24" s="12" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M24:Q24)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="25"/>
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
-      <c r="G25" s="25"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="25"/>
-      <c r="K25" s="25"/>
-      <c r="L25" s="25"/>
-      <c r="M25" s="25"/>
-      <c r="N25" s="25"/>
-      <c r="O25" s="25"/>
-      <c r="P25" s="25"/>
-      <c r="Q25" s="25"/>
-    </row>
-    <row r="26" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+    <row r="25" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="113" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="117"/>
+      <c r="C25" s="117"/>
+      <c r="D25" s="117"/>
+      <c r="E25" s="117"/>
+      <c r="F25" s="117"/>
+      <c r="G25" s="114"/>
+      <c r="H25" s="34"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="113" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" s="117"/>
+      <c r="M25" s="117"/>
+      <c r="N25" s="117"/>
+      <c r="O25" s="117"/>
+      <c r="P25" s="117"/>
+      <c r="Q25" s="114"/>
+      <c r="R25" s="12"/>
+    </row>
+    <row r="26" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="118" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="119"/>
+      <c r="C26" s="173"/>
+      <c r="D26" s="174"/>
+      <c r="E26" s="174"/>
+      <c r="F26" s="174"/>
+      <c r="G26" s="175"/>
+      <c r="H26" s="34" cm="1">
+        <f t="array" ref="H26">-SUMPRODUCT((D6:F6-C6:E6)*(C26:E26+D26:F26)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="34" cm="1">
+        <f t="array" ref="I26">-SUMPRODUCT((D6:G6-C6:F6)*(C26:F26+D26:G26)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="12" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C26:G26)&amp;","</f>
+        <v xml:space="preserve">    ,</v>
+      </c>
+      <c r="K26" s="118" t="s">
+        <v>7</v>
+      </c>
+      <c r="L26" s="119"/>
+      <c r="M26" s="84">
+        <v>3.5338969773137729</v>
+      </c>
+      <c r="N26">
+        <v>3.7216965755259852</v>
+      </c>
+      <c r="O26">
+        <v>3.7478593835578962</v>
+      </c>
+      <c r="P26">
+        <v>6.7863547394302319</v>
+      </c>
+      <c r="Q26" s="85">
+        <v>8.2097242202983072</v>
+      </c>
+      <c r="R26" s="12" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M26:Q26)&amp;","</f>
+        <v xml:space="preserve">    3.53389697731377, 3.72169657552599, 3.7478593835579, 6.78635473943023, 8.20972422029831,</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="115" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="116"/>
+      <c r="C27" s="173"/>
+      <c r="D27" s="174"/>
+      <c r="E27" s="174"/>
+      <c r="F27" s="174"/>
+      <c r="G27" s="175"/>
+      <c r="H27" s="34" cm="1">
+        <f t="array" ref="H27">-SUMPRODUCT((D6:F6-C6:E6)*(C27:E27+D27:F27)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="34" cm="1">
+        <f t="array" ref="I27">-SUMPRODUCT((D6:G6-C6:F6)*(C27:F27+D27:G27)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="J27" s="12" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C27:G27)&amp;","</f>
+        <v xml:space="preserve">    ,</v>
+      </c>
+      <c r="K27" s="113" t="s">
+        <v>8</v>
+      </c>
+      <c r="L27" s="114"/>
+      <c r="M27" s="84">
+        <v>3.0404967647063641</v>
+      </c>
+      <c r="N27">
+        <v>3.2195663824364602</v>
+      </c>
+      <c r="O27">
+        <v>5.1059080333021827</v>
+      </c>
+      <c r="P27">
+        <v>3.323723681934811</v>
+      </c>
+      <c r="Q27" s="85">
+        <v>4.2607284397566696</v>
+      </c>
+      <c r="R27" s="12" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M27:Q27)&amp;","</f>
+        <v xml:space="preserve">    3.04049676470636, 3.21956638243646, 5.10590803330218, 3.32372368193481, 4.26072843975667,</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="113" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="114"/>
+      <c r="C28" s="173"/>
+      <c r="D28" s="174"/>
+      <c r="E28" s="174"/>
+      <c r="F28" s="174"/>
+      <c r="G28" s="175"/>
+      <c r="H28" s="34" cm="1">
+        <f t="array" ref="H28">-SUMPRODUCT((D6:F6-C6:E6)*(C28:E28+D28:F28)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="34" cm="1">
+        <f t="array" ref="I28">-SUMPRODUCT((D6:G6-C6:F6)*(C28:F28+D28:G28)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="J28" s="12" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C28:G28)&amp;","</f>
+        <v xml:space="preserve">    ,</v>
+      </c>
+      <c r="K28" s="113" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="114"/>
+      <c r="M28" s="84">
+        <v>3.3471189071482028</v>
+      </c>
+      <c r="N28">
+        <v>3.632082464261972</v>
+      </c>
+      <c r="O28">
+        <v>3.8019445786359811</v>
+      </c>
+      <c r="P28">
+        <v>7.5417080235248886</v>
+      </c>
+      <c r="Q28" s="85">
+        <v>8.4137702230121008</v>
+      </c>
+      <c r="R28" s="12" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M28:Q28)&amp;","</f>
+        <v xml:space="preserve">    3.3471189071482, 3.63208246426197, 3.80194457863598, 7.54170802352489, 8.4137702230121,</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="113" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29" s="114"/>
+      <c r="C29" s="35"/>
+      <c r="D29" s="36"/>
+      <c r="E29" s="36"/>
+      <c r="F29" s="36"/>
+      <c r="G29" s="89"/>
+      <c r="H29" s="34" cm="1">
+        <f t="array" ref="H29">-SUMPRODUCT((D6:F6-C6:E6)*(C29:E29+D29:F29)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="I29" s="34" cm="1">
+        <f t="array" ref="I29">-SUMPRODUCT((D6:G6-C6:F6)*(C29:F29+D29:G29)/2)</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="12" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C29:G29)&amp;","</f>
+        <v xml:space="preserve">    ,</v>
+      </c>
+      <c r="K29" s="113" t="s">
+        <v>22</v>
+      </c>
+      <c r="L29" s="114"/>
+      <c r="M29" s="35"/>
+      <c r="N29" s="36"/>
+      <c r="O29" s="36"/>
+      <c r="P29" s="36"/>
+      <c r="Q29" s="89"/>
+      <c r="R29" s="12" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M29:Q29)&amp;","</f>
+        <v xml:space="preserve">    ,</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="25"/>
+      <c r="B30" s="25"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="25"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
+      <c r="G30" s="25"/>
+      <c r="H30" s="25"/>
+      <c r="I30" s="25"/>
+      <c r="K30" s="25"/>
+      <c r="L30" s="25"/>
+      <c r="M30" s="25"/>
+      <c r="N30" s="25"/>
+      <c r="O30" s="25"/>
+      <c r="P30" s="25"/>
+      <c r="Q30" s="25"/>
+    </row>
+    <row r="31" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B31" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C26" s="14">
+      <c r="C31" s="14">
         <v>1</v>
       </c>
-      <c r="D26" s="16">
+      <c r="D31" s="16">
         <v>0.5</v>
       </c>
-      <c r="E26" s="16">
+      <c r="E31" s="16">
         <v>0.25</v>
       </c>
-      <c r="F26" s="16">
+      <c r="F31" s="16">
         <v>0.125</v>
       </c>
-      <c r="G26" s="2">
+      <c r="G31" s="2">
         <v>6.25E-2</v>
       </c>
-      <c r="H26" s="19"/>
-      <c r="I26" s="19"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="4" t="s">
+      <c r="H31" s="19"/>
+      <c r="I31" s="19"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="L26" s="5" t="s">
+      <c r="L31" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="M26" s="14">
+      <c r="M31" s="14">
         <v>1</v>
       </c>
-      <c r="N26" s="16">
+      <c r="N31" s="16">
         <v>0.5</v>
       </c>
-      <c r="O26" s="16">
+      <c r="O31" s="16">
         <v>0.25</v>
       </c>
-      <c r="P26" s="16">
+      <c r="P31" s="16">
         <v>0.125</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="Q31" s="2">
         <v>6.25E-2</v>
       </c>
-      <c r="R26" s="1"/>
-    </row>
-    <row r="27" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="105" t="s">
+      <c r="R31" s="1"/>
+    </row>
+    <row r="32" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="121" t="s">
         <v>5</v>
       </c>
-      <c r="B27" s="106"/>
-      <c r="C27" s="89">
+      <c r="B32" s="122"/>
+      <c r="C32" s="81">
         <v>92.485449200300948</v>
       </c>
-      <c r="D27" s="90">
+      <c r="D32" s="82">
         <v>92.185357970009463</v>
       </c>
-      <c r="E27" s="90">
+      <c r="E32" s="82">
         <v>90.049361274020285</v>
       </c>
-      <c r="F27" s="90">
+      <c r="F32" s="82">
         <v>76.424179894802663</v>
       </c>
-      <c r="G27" s="91">
+      <c r="G32" s="83">
         <v>55.817166373785298</v>
-      </c>
-      <c r="H27" s="40"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C27:G27)&amp;","</f>
-        <v xml:space="preserve">    92.4854492003009, 92.1853579700095, 90.0493612740203, 76.4241798948027, 55.8171663737853,</v>
-      </c>
-      <c r="K27" s="105" t="s">
-        <v>5</v>
-      </c>
-      <c r="L27" s="106"/>
-      <c r="M27" s="89">
-        <v>4.0542209595909764</v>
-      </c>
-      <c r="N27" s="90">
-        <v>4.1862833242412467</v>
-      </c>
-      <c r="O27" s="90">
-        <v>4.5232246954320994</v>
-      </c>
-      <c r="P27" s="90">
-        <v>8.3692490038067824</v>
-      </c>
-      <c r="Q27" s="91">
-        <v>9.4522568492704835</v>
-      </c>
-      <c r="R27" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M27:Q27)&amp;","</f>
-        <v xml:space="preserve">    4.05422095959098, 4.18628332424125, 4.5232246954321, 8.36924900380678, 9.45225684927048,</v>
-      </c>
-    </row>
-    <row r="28" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="105" t="s">
-        <v>6</v>
-      </c>
-      <c r="B28" s="106"/>
-      <c r="C28" s="92">
-        <v>93.221737995090834</v>
-      </c>
-      <c r="D28">
-        <v>91.888033005684576</v>
-      </c>
-      <c r="E28">
-        <v>90.02393898401543</v>
-      </c>
-      <c r="F28">
-        <v>72.290420081448175</v>
-      </c>
-      <c r="G28" s="93">
-        <v>51.841305264174281</v>
-      </c>
-      <c r="H28" s="40"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C28:G28)&amp;","</f>
-        <v xml:space="preserve">    93.2217379950908, 91.8880330056846, 90.0239389840154, 72.2904200814482, 51.8413052641743,</v>
-      </c>
-      <c r="K28" s="105" t="s">
-        <v>6</v>
-      </c>
-      <c r="L28" s="106"/>
-      <c r="M28" s="92">
-        <v>3.877808098377264</v>
-      </c>
-      <c r="N28">
-        <v>3.9588226549458381</v>
-      </c>
-      <c r="O28">
-        <v>3.8583306594917439</v>
-      </c>
-      <c r="P28">
-        <v>9.3469718907111154</v>
-      </c>
-      <c r="Q28" s="93">
-        <v>8.4900588367667034</v>
-      </c>
-      <c r="R28" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M28:Q28)&amp;","</f>
-        <v xml:space="preserve">    3.87780809837726, 3.95882265494584, 3.85833065949174, 9.34697189071112, 8.4900588367667,</v>
-      </c>
-    </row>
-    <row r="29" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="109" t="s">
-        <v>10</v>
-      </c>
-      <c r="B29" s="110"/>
-      <c r="C29" s="94">
-        <v>88.242190127710941</v>
-      </c>
-      <c r="D29" s="95">
-        <v>87.235659245723795</v>
-      </c>
-      <c r="E29" s="95">
-        <v>86.840356363138071</v>
-      </c>
-      <c r="F29" s="95">
-        <v>74.54100008231579</v>
-      </c>
-      <c r="G29" s="96">
-        <v>48.979529992306112</v>
-      </c>
-      <c r="H29" s="40"/>
-      <c r="I29" s="40"/>
-      <c r="J29" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C29:G29)&amp;","</f>
-        <v xml:space="preserve">    88.2421901277109, 87.2356592457238, 86.8403563631381, 74.5410000823158, 48.9795299923061,</v>
-      </c>
-      <c r="K29" s="109" t="s">
-        <v>10</v>
-      </c>
-      <c r="L29" s="110"/>
-      <c r="M29" s="94">
-        <v>3.345739818904093</v>
-      </c>
-      <c r="N29" s="95">
-        <v>2.427737239251389</v>
-      </c>
-      <c r="O29" s="95">
-        <v>1.707344435820553</v>
-      </c>
-      <c r="P29" s="95">
-        <v>2.910710341880129</v>
-      </c>
-      <c r="Q29" s="96">
-        <v>2.034771708486713</v>
-      </c>
-      <c r="R29" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M29:Q29)&amp;","</f>
-        <v xml:space="preserve">    3.34573981890409, 2.42773723925139, 1.70734443582055, 2.91071034188013, 2.03477170848671,</v>
-      </c>
-    </row>
-    <row r="30" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="105" t="s">
-        <v>12</v>
-      </c>
-      <c r="B30" s="106"/>
-      <c r="C30" s="110"/>
-      <c r="D30" s="110"/>
-      <c r="E30" s="110"/>
-      <c r="F30" s="110"/>
-      <c r="G30" s="111"/>
-      <c r="H30" s="40"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="105" t="s">
-        <v>12</v>
-      </c>
-      <c r="L30" s="106"/>
-      <c r="M30" s="110"/>
-      <c r="N30" s="110"/>
-      <c r="O30" s="110"/>
-      <c r="P30" s="110"/>
-      <c r="Q30" s="111"/>
-      <c r="R30" s="1"/>
-    </row>
-    <row r="31" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="142" t="s">
-        <v>11</v>
-      </c>
-      <c r="B31" s="88" t="s">
-        <v>17</v>
-      </c>
-      <c r="C31" s="89">
-        <v>92.96850376823356</v>
-      </c>
-      <c r="D31" s="90">
-        <v>92.40153506683653</v>
-      </c>
-      <c r="E31" s="90">
-        <v>90.677668832287424</v>
-      </c>
-      <c r="F31" s="90">
-        <v>74.017532689742268</v>
-      </c>
-      <c r="G31" s="91">
-        <v>53.92352732591884</v>
-      </c>
-      <c r="H31" s="40"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="142" t="s">
-        <v>11</v>
-      </c>
-      <c r="L31" s="88" t="s">
-        <v>17</v>
-      </c>
-      <c r="M31" s="89">
-        <v>3.8454600924080049</v>
-      </c>
-      <c r="N31" s="90">
-        <v>4.0669297112418992</v>
-      </c>
-      <c r="O31" s="90">
-        <v>3.8537049252854398</v>
-      </c>
-      <c r="P31" s="90">
-        <v>8.7041298457857419</v>
-      </c>
-      <c r="Q31" s="91">
-        <v>9.6394684933662074</v>
-      </c>
-      <c r="R31" s="1"/>
-    </row>
-    <row r="32" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="143"/>
-      <c r="B32" s="102" t="s">
-        <v>13</v>
-      </c>
-      <c r="C32" s="92">
-        <v>92.884757186814937</v>
-      </c>
-      <c r="D32" s="141">
-        <v>92.335436215459112</v>
-      </c>
-      <c r="E32" s="141">
-        <v>90.9231205519105</v>
-      </c>
-      <c r="F32" s="141">
-        <v>76.864790806262661</v>
-      </c>
-      <c r="G32" s="93">
-        <v>54.700390036572337</v>
       </c>
       <c r="H32" s="40"/>
       <c r="I32" s="40"/>
       <c r="J32" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C32:G32)&amp;","</f>
-        <v xml:space="preserve">    92.8847571868149, 92.3354362154591, 90.9231205519105, 76.8647908062627, 54.7003900365723,</v>
-      </c>
-      <c r="K32" s="143"/>
-      <c r="L32" s="102" t="s">
-        <v>13</v>
-      </c>
-      <c r="M32" s="92">
-        <v>3.9275095693540201</v>
-      </c>
-      <c r="N32" s="141">
-        <v>4.1004926648702904</v>
-      </c>
-      <c r="O32" s="141">
-        <v>3.731232057084795</v>
-      </c>
-      <c r="P32" s="141">
-        <v>7.9334375921235116</v>
-      </c>
-      <c r="Q32" s="93">
-        <v>9.3194201516218254</v>
+        <v xml:space="preserve">    92.4854492003009, 92.1853579700095, 90.0493612740203, 76.4241798948027, 55.8171663737853,</v>
+      </c>
+      <c r="K32" s="121" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="122"/>
+      <c r="M32" s="81">
+        <v>4.0542209595909764</v>
+      </c>
+      <c r="N32" s="82">
+        <v>4.1862833242412467</v>
+      </c>
+      <c r="O32" s="82">
+        <v>4.5232246954320994</v>
+      </c>
+      <c r="P32" s="82">
+        <v>8.3692490038067824</v>
+      </c>
+      <c r="Q32" s="83">
+        <v>9.4522568492704835</v>
       </c>
       <c r="R32" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M32:Q32)&amp;","</f>
-        <v xml:space="preserve">    3.92750956935402, 4.10049266487029, 3.73123205708479, 7.93343759212351, 9.31942015162183,</v>
+        <v xml:space="preserve">    4.05422095959098, 4.18628332424125, 4.5232246954321, 8.36924900380678, 9.45225684927048,</v>
       </c>
     </row>
     <row r="33" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="143"/>
-      <c r="B33" s="88" t="s">
-        <v>14</v>
-      </c>
-      <c r="C33" s="92">
-        <v>92.328683900261311</v>
-      </c>
-      <c r="D33" s="141">
-        <v>92.052039116791605</v>
-      </c>
-      <c r="E33" s="141">
-        <v>90.722946775710213</v>
-      </c>
-      <c r="F33" s="141">
-        <v>81.998727124399025</v>
-      </c>
-      <c r="G33" s="93">
-        <v>56.932651064742558</v>
+      <c r="A33" s="121" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33" s="122"/>
+      <c r="C33" s="84">
+        <v>93.221737995090834</v>
+      </c>
+      <c r="D33">
+        <v>91.888033005684576</v>
+      </c>
+      <c r="E33">
+        <v>90.02393898401543</v>
+      </c>
+      <c r="F33">
+        <v>72.290420081448175</v>
+      </c>
+      <c r="G33" s="85">
+        <v>51.841305264174281</v>
       </c>
       <c r="H33" s="40"/>
       <c r="I33" s="40"/>
       <c r="J33" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C33:G33)&amp;","</f>
-        <v xml:space="preserve">    92.3286839002613, 92.0520391167916, 90.7229467757102, 81.998727124399, 56.9326510647426,</v>
-      </c>
-      <c r="K33" s="143"/>
-      <c r="L33" s="88" t="s">
-        <v>14</v>
-      </c>
-      <c r="M33" s="92">
-        <v>3.6425445085490389</v>
-      </c>
-      <c r="N33" s="141">
-        <v>3.5031960343483388</v>
-      </c>
-      <c r="O33" s="141">
-        <v>3.28867394504752</v>
-      </c>
-      <c r="P33" s="141">
-        <v>4.6860855472410874</v>
-      </c>
-      <c r="Q33" s="93">
-        <v>6.5118967468904154</v>
+        <v xml:space="preserve">    93.2217379950908, 91.8880330056846, 90.0239389840154, 72.2904200814482, 51.8413052641743,</v>
+      </c>
+      <c r="K33" s="121" t="s">
+        <v>6</v>
+      </c>
+      <c r="L33" s="122"/>
+      <c r="M33" s="84">
+        <v>3.877808098377264</v>
+      </c>
+      <c r="N33">
+        <v>3.9588226549458381</v>
+      </c>
+      <c r="O33">
+        <v>3.8583306594917439</v>
+      </c>
+      <c r="P33">
+        <v>9.3469718907111154</v>
+      </c>
+      <c r="Q33" s="85">
+        <v>8.4900588367667034</v>
       </c>
       <c r="R33" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M33:Q33)&amp;","</f>
-        <v xml:space="preserve">    3.64254450854904, 3.50319603434834, 3.28867394504752, 4.68608554724109, 6.51189674689042,</v>
+        <v xml:space="preserve">    3.87780809837726, 3.95882265494584, 3.85833065949174, 9.34697189071112, 8.4900588367667,</v>
       </c>
     </row>
     <row r="34" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="143"/>
-      <c r="B34" s="88" t="s">
-        <v>15</v>
-      </c>
-      <c r="C34" s="92">
-        <v>93.343840114066111</v>
-      </c>
-      <c r="D34" s="141">
-        <v>91.954404928715931</v>
-      </c>
-      <c r="E34" s="141">
-        <v>90.224796797452356</v>
-      </c>
-      <c r="F34" s="141">
-        <v>75.418279728826036</v>
-      </c>
-      <c r="G34" s="93">
-        <v>54.024842451700351</v>
+      <c r="A34" s="123" t="s">
+        <v>10</v>
+      </c>
+      <c r="B34" s="124"/>
+      <c r="C34" s="86">
+        <v>88.242190127710941</v>
+      </c>
+      <c r="D34" s="87">
+        <v>87.235659245723795</v>
+      </c>
+      <c r="E34" s="87">
+        <v>86.840356363138071</v>
+      </c>
+      <c r="F34" s="87">
+        <v>74.54100008231579</v>
+      </c>
+      <c r="G34" s="88">
+        <v>48.979529992306112</v>
       </c>
       <c r="H34" s="40"/>
       <c r="I34" s="40"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="143"/>
-      <c r="L34" s="88" t="s">
-        <v>15</v>
-      </c>
-      <c r="M34" s="92">
-        <v>3.867155660480134</v>
-      </c>
-      <c r="N34" s="141">
-        <v>3.8459340780537419</v>
-      </c>
-      <c r="O34" s="141">
-        <v>3.7451559754967332</v>
-      </c>
-      <c r="P34" s="141">
-        <v>8.3745003498256878</v>
-      </c>
-      <c r="Q34" s="93">
-        <v>9.3705924310602366</v>
-      </c>
-      <c r="R34" s="1"/>
+      <c r="J34" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C34:G34)&amp;","</f>
+        <v xml:space="preserve">    88.2421901277109, 87.2356592457238, 86.8403563631381, 74.5410000823158, 48.9795299923061,</v>
+      </c>
+      <c r="K34" s="123" t="s">
+        <v>10</v>
+      </c>
+      <c r="L34" s="124"/>
+      <c r="M34" s="86">
+        <v>3.345739818904093</v>
+      </c>
+      <c r="N34" s="87">
+        <v>2.427737239251389</v>
+      </c>
+      <c r="O34" s="87">
+        <v>1.707344435820553</v>
+      </c>
+      <c r="P34" s="87">
+        <v>2.910710341880129</v>
+      </c>
+      <c r="Q34" s="88">
+        <v>2.034771708486713</v>
+      </c>
+      <c r="R34" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M34:Q34)&amp;","</f>
+        <v xml:space="preserve">    3.34573981890409, 2.42773723925139, 1.70734443582055, 2.91071034188013, 2.03477170848671,</v>
+      </c>
     </row>
     <row r="35" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="143"/>
-      <c r="B35" s="88" t="s">
-        <v>18</v>
-      </c>
-      <c r="C35" s="92">
-        <v>93.17956577363725</v>
-      </c>
-      <c r="D35" s="141">
-        <v>92.311564351892216</v>
-      </c>
-      <c r="E35" s="141">
-        <v>90.442696954145944</v>
-      </c>
-      <c r="F35" s="141">
-        <v>73.029683164461161</v>
-      </c>
-      <c r="G35" s="93">
-        <v>54.393186167944343</v>
-      </c>
+      <c r="A35" s="121" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="122"/>
+      <c r="C35" s="124"/>
+      <c r="D35" s="124"/>
+      <c r="E35" s="124"/>
+      <c r="F35" s="124"/>
+      <c r="G35" s="125"/>
       <c r="H35" s="40"/>
       <c r="I35" s="40"/>
       <c r="J35" s="1"/>
-      <c r="K35" s="143"/>
-      <c r="L35" s="88" t="s">
-        <v>18</v>
-      </c>
-      <c r="M35" s="92">
-        <v>3.743131605295734</v>
-      </c>
-      <c r="N35" s="141">
-        <v>4.0679999153192643</v>
-      </c>
-      <c r="O35" s="141">
-        <v>4.2835813429220631</v>
-      </c>
-      <c r="P35" s="141">
-        <v>9.1240722898599991</v>
-      </c>
-      <c r="Q35" s="93">
-        <v>8.7084512165137298</v>
-      </c>
+      <c r="K35" s="121" t="s">
+        <v>12</v>
+      </c>
+      <c r="L35" s="122"/>
+      <c r="M35" s="124"/>
+      <c r="N35" s="124"/>
+      <c r="O35" s="124"/>
+      <c r="P35" s="124"/>
+      <c r="Q35" s="125"/>
       <c r="R35" s="1"/>
     </row>
     <row r="36" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="143"/>
-      <c r="B36" s="88" t="s">
-        <v>25</v>
-      </c>
-      <c r="C36" s="92">
-        <v>90.924141700367642</v>
-      </c>
-      <c r="D36" s="141">
-        <v>90.531815219430456</v>
-      </c>
-      <c r="E36" s="141">
-        <v>89.551513659244264</v>
-      </c>
-      <c r="F36" s="141">
-        <v>80.742066180975286</v>
-      </c>
-      <c r="G36" s="93">
-        <v>54.139653004991288</v>
+      <c r="A36" s="110" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" s="80" t="s">
+        <v>17</v>
+      </c>
+      <c r="C36" s="81">
+        <v>92.96850376823356</v>
+      </c>
+      <c r="D36" s="82">
+        <v>92.40153506683653</v>
+      </c>
+      <c r="E36" s="82">
+        <v>90.677668832287424</v>
+      </c>
+      <c r="F36" s="82">
+        <v>74.017532689742268</v>
+      </c>
+      <c r="G36" s="83">
+        <v>53.92352732591884</v>
       </c>
       <c r="H36" s="40"/>
       <c r="I36" s="40"/>
       <c r="J36" s="1"/>
-      <c r="K36" s="143"/>
-      <c r="L36" s="88" t="s">
-        <v>25</v>
-      </c>
-      <c r="M36" s="92">
-        <v>3.2766682411196539</v>
-      </c>
-      <c r="N36" s="141">
-        <v>2.78458571585282</v>
-      </c>
-      <c r="O36" s="141">
-        <v>2.9252385560800671</v>
-      </c>
-      <c r="P36" s="141">
-        <v>4.2888241274046361</v>
-      </c>
-      <c r="Q36" s="93">
-        <v>6.6722118847395508</v>
+      <c r="K36" s="110" t="s">
+        <v>11</v>
+      </c>
+      <c r="L36" s="80" t="s">
+        <v>17</v>
+      </c>
+      <c r="M36" s="81">
+        <v>3.8454600924080049</v>
+      </c>
+      <c r="N36" s="82">
+        <v>4.0669297112418992</v>
+      </c>
+      <c r="O36" s="82">
+        <v>3.8537049252854398</v>
+      </c>
+      <c r="P36" s="82">
+        <v>8.7041298457857419</v>
+      </c>
+      <c r="Q36" s="83">
+        <v>9.6394684933662074</v>
       </c>
       <c r="R36" s="1"/>
     </row>
     <row r="37" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="143"/>
-      <c r="B37" s="88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" s="92">
-        <v>88.022061049133967</v>
-      </c>
-      <c r="D37" s="141">
-        <v>86.687391232306652</v>
-      </c>
-      <c r="E37" s="141">
-        <v>86.899490010131302</v>
-      </c>
-      <c r="F37" s="141">
-        <v>75.166534149020336</v>
-      </c>
-      <c r="G37" s="93">
-        <v>49.417617539398499</v>
+      <c r="A37" s="111"/>
+      <c r="B37" s="94" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="84">
+        <v>92.884757186814937</v>
+      </c>
+      <c r="D37">
+        <v>92.335436215459112</v>
+      </c>
+      <c r="E37">
+        <v>90.9231205519105</v>
+      </c>
+      <c r="F37">
+        <v>76.864790806262661</v>
+      </c>
+      <c r="G37" s="85">
+        <v>54.700390036572337</v>
       </c>
       <c r="H37" s="40"/>
       <c r="I37" s="40"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="143"/>
-      <c r="L37" s="88" t="s">
-        <v>16</v>
-      </c>
-      <c r="M37" s="92">
-        <v>3.1059564342295989</v>
-      </c>
-      <c r="N37" s="141">
-        <v>2.606378506216009</v>
-      </c>
-      <c r="O37" s="141">
-        <v>1.672205327538536</v>
-      </c>
-      <c r="P37" s="141">
-        <v>3.4989537204184411</v>
-      </c>
-      <c r="Q37" s="93">
-        <v>1.5086756884059249</v>
-      </c>
-      <c r="R37" s="1"/>
+      <c r="J37" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C37:G37)&amp;","</f>
+        <v xml:space="preserve">    92.8847571868149, 92.3354362154591, 90.9231205519105, 76.8647908062627, 54.7003900365723,</v>
+      </c>
+      <c r="K37" s="111"/>
+      <c r="L37" s="94" t="s">
+        <v>13</v>
+      </c>
+      <c r="M37" s="84">
+        <v>3.9275095693540201</v>
+      </c>
+      <c r="N37">
+        <v>4.1004926648702904</v>
+      </c>
+      <c r="O37">
+        <v>3.731232057084795</v>
+      </c>
+      <c r="P37">
+        <v>7.9334375921235116</v>
+      </c>
+      <c r="Q37" s="85">
+        <v>9.3194201516218254</v>
+      </c>
+      <c r="R37" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M37:Q37)&amp;","</f>
+        <v xml:space="preserve">    3.92750956935402, 4.10049266487029, 3.73123205708479, 7.93343759212351, 9.31942015162183,</v>
+      </c>
     </row>
     <row r="38" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="143"/>
-      <c r="B38" s="88" t="s">
-        <v>19</v>
-      </c>
-      <c r="C38" s="92">
-        <v>90.264167794210408</v>
-      </c>
-      <c r="D38" s="141">
-        <v>89.992256751037203</v>
-      </c>
-      <c r="E38" s="141">
-        <v>89.343495694119156</v>
-      </c>
-      <c r="F38" s="141">
-        <v>78.329165755951735</v>
-      </c>
-      <c r="G38" s="93">
-        <v>52.215737786802968</v>
+      <c r="A38" s="111"/>
+      <c r="B38" s="80" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" s="84">
+        <v>92.328683900261311</v>
+      </c>
+      <c r="D38">
+        <v>92.052039116791605</v>
+      </c>
+      <c r="E38">
+        <v>90.722946775710213</v>
+      </c>
+      <c r="F38">
+        <v>81.998727124399025</v>
+      </c>
+      <c r="G38" s="85">
+        <v>56.932651064742558</v>
       </c>
       <c r="H38" s="40"/>
       <c r="I38" s="40"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="143"/>
-      <c r="L38" s="88" t="s">
-        <v>19</v>
-      </c>
-      <c r="M38" s="92">
-        <v>2.813777787794177</v>
-      </c>
-      <c r="N38" s="141">
-        <v>2.515073286885404</v>
-      </c>
-      <c r="O38" s="141">
-        <v>2.61246052058309</v>
-      </c>
-      <c r="P38" s="141">
-        <v>3.988565827203912</v>
-      </c>
-      <c r="Q38" s="93">
-        <v>3.7859616126423878</v>
-      </c>
-      <c r="R38" s="1"/>
+      <c r="J38" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C38:G38)&amp;","</f>
+        <v xml:space="preserve">    92.3286839002613, 92.0520391167916, 90.7229467757102, 81.998727124399, 56.9326510647426,</v>
+      </c>
+      <c r="K38" s="111"/>
+      <c r="L38" s="80" t="s">
+        <v>14</v>
+      </c>
+      <c r="M38" s="84">
+        <v>3.6425445085490389</v>
+      </c>
+      <c r="N38">
+        <v>3.5031960343483388</v>
+      </c>
+      <c r="O38">
+        <v>3.28867394504752</v>
+      </c>
+      <c r="P38">
+        <v>4.6860855472410874</v>
+      </c>
+      <c r="Q38" s="85">
+        <v>6.5118967468904154</v>
+      </c>
+      <c r="R38" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M38:Q38)&amp;","</f>
+        <v xml:space="preserve">    3.64254450854904, 3.50319603434834, 3.28867394504752, 4.68608554724109, 6.51189674689042,</v>
+      </c>
     </row>
     <row r="39" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="144"/>
-      <c r="B39" s="88" t="s">
-        <v>26</v>
-      </c>
-      <c r="C39" s="94">
-        <v>88.816569678290051</v>
-      </c>
-      <c r="D39" s="95">
-        <v>88.13924460400689</v>
-      </c>
-      <c r="E39" s="95">
-        <v>87.754122925075478</v>
-      </c>
-      <c r="F39" s="95">
-        <v>76.74804506712546</v>
-      </c>
-      <c r="G39" s="96">
-        <v>50.462449044076237</v>
+      <c r="A39" s="111"/>
+      <c r="B39" s="80" t="s">
+        <v>15</v>
+      </c>
+      <c r="C39" s="84">
+        <v>93.343840114066111</v>
+      </c>
+      <c r="D39">
+        <v>91.954404928715931</v>
+      </c>
+      <c r="E39">
+        <v>90.224796797452356</v>
+      </c>
+      <c r="F39">
+        <v>75.418279728826036</v>
+      </c>
+      <c r="G39" s="85">
+        <v>54.024842451700351</v>
       </c>
       <c r="H39" s="40"/>
       <c r="I39" s="40"/>
       <c r="J39" s="1"/>
-      <c r="K39" s="144"/>
-      <c r="L39" s="88" t="s">
-        <v>26</v>
-      </c>
-      <c r="M39" s="94">
-        <v>2.8080857507745329</v>
-      </c>
-      <c r="N39" s="95">
-        <v>2.4101693608449022</v>
-      </c>
-      <c r="O39" s="95">
-        <v>2.0261358563845731</v>
-      </c>
-      <c r="P39" s="95">
-        <v>3.1965959386571878</v>
-      </c>
-      <c r="Q39" s="96">
-        <v>1.998032998184734</v>
+      <c r="K39" s="111"/>
+      <c r="L39" s="80" t="s">
+        <v>15</v>
+      </c>
+      <c r="M39" s="84">
+        <v>3.867155660480134</v>
+      </c>
+      <c r="N39">
+        <v>3.8459340780537419</v>
+      </c>
+      <c r="O39">
+        <v>3.7451559754967332</v>
+      </c>
+      <c r="P39">
+        <v>8.3745003498256878</v>
+      </c>
+      <c r="Q39" s="85">
+        <v>9.3705924310602366</v>
       </c>
       <c r="R39" s="1"/>
     </row>
     <row r="40" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="105" t="s">
-        <v>20</v>
-      </c>
-      <c r="B40" s="106"/>
-      <c r="C40" s="113"/>
-      <c r="D40" s="113"/>
-      <c r="E40" s="113"/>
-      <c r="F40" s="113"/>
-      <c r="G40" s="113"/>
+      <c r="A40" s="111"/>
+      <c r="B40" s="80" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="84">
+        <v>93.17956577363725</v>
+      </c>
+      <c r="D40">
+        <v>92.311564351892216</v>
+      </c>
+      <c r="E40">
+        <v>90.442696954145944</v>
+      </c>
+      <c r="F40">
+        <v>73.029683164461161</v>
+      </c>
+      <c r="G40" s="85">
+        <v>54.393186167944343</v>
+      </c>
       <c r="H40" s="40"/>
       <c r="I40" s="40"/>
       <c r="J40" s="1"/>
-      <c r="K40" s="105" t="s">
-        <v>20</v>
-      </c>
-      <c r="L40" s="106"/>
-      <c r="M40" s="108"/>
-      <c r="N40" s="108"/>
-      <c r="O40" s="108"/>
-      <c r="P40" s="108"/>
-      <c r="Q40" s="145"/>
+      <c r="K40" s="111"/>
+      <c r="L40" s="80" t="s">
+        <v>18</v>
+      </c>
+      <c r="M40" s="84">
+        <v>3.743131605295734</v>
+      </c>
+      <c r="N40">
+        <v>4.0679999153192643</v>
+      </c>
+      <c r="O40">
+        <v>4.2835813429220631</v>
+      </c>
+      <c r="P40">
+        <v>9.1240722898599991</v>
+      </c>
+      <c r="Q40" s="85">
+        <v>8.7084512165137298</v>
+      </c>
       <c r="R40" s="1"/>
     </row>
-    <row r="41" spans="1:18" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="105" t="s">
-        <v>7</v>
-      </c>
-      <c r="B41" s="106"/>
-      <c r="C41" s="89">
-        <v>92.781043798288394</v>
-      </c>
-      <c r="D41" s="90">
-        <v>92.393805655393209</v>
-      </c>
-      <c r="E41" s="90">
-        <v>90.00908396624763</v>
-      </c>
-      <c r="F41" s="90">
-        <v>72.498171965203667</v>
-      </c>
-      <c r="G41" s="91">
-        <v>56.674852997991948</v>
+    <row r="41" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="111"/>
+      <c r="B41" s="80" t="s">
+        <v>25</v>
+      </c>
+      <c r="C41" s="84">
+        <v>90.924141700367642</v>
+      </c>
+      <c r="D41">
+        <v>90.531815219430456</v>
+      </c>
+      <c r="E41">
+        <v>89.551513659244264</v>
+      </c>
+      <c r="F41">
+        <v>80.742066180975286</v>
+      </c>
+      <c r="G41" s="85">
+        <v>54.139653004991288</v>
       </c>
       <c r="H41" s="40"/>
       <c r="I41" s="40"/>
-      <c r="J41" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C41:G41)&amp;","</f>
-        <v xml:space="preserve">    92.7810437982884, 92.3938056553932, 90.0090839662476, 72.4981719652037, 56.6748529979919,</v>
-      </c>
-      <c r="K41" s="107" t="s">
-        <v>7</v>
-      </c>
-      <c r="L41" s="108"/>
-      <c r="M41" s="89">
-        <v>4.5014366094349993</v>
-      </c>
-      <c r="N41" s="90">
-        <v>4.2660991290099446</v>
-      </c>
-      <c r="O41" s="90">
-        <v>4.2894182874628113</v>
-      </c>
-      <c r="P41" s="90">
-        <v>9.3344724861133059</v>
-      </c>
-      <c r="Q41" s="91">
-        <v>9.7546209717543917</v>
-      </c>
-      <c r="R41" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M41:Q41)&amp;","</f>
-        <v xml:space="preserve">    4.501436609435, 4.26609912900994, 4.28941828746281, 9.33447248611331, 9.75462097175439,</v>
-      </c>
+      <c r="J41" s="1"/>
+      <c r="K41" s="111"/>
+      <c r="L41" s="80" t="s">
+        <v>25</v>
+      </c>
+      <c r="M41" s="84">
+        <v>3.2766682411196539</v>
+      </c>
+      <c r="N41">
+        <v>2.78458571585282</v>
+      </c>
+      <c r="O41">
+        <v>2.9252385560800671</v>
+      </c>
+      <c r="P41">
+        <v>4.2888241274046361</v>
+      </c>
+      <c r="Q41" s="85">
+        <v>6.6722118847395508</v>
+      </c>
+      <c r="R41" s="1"/>
     </row>
     <row r="42" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="105" t="s">
-        <v>8</v>
-      </c>
-      <c r="B42" s="106"/>
-      <c r="C42" s="92">
-        <v>93.113144022293241</v>
+      <c r="A42" s="111"/>
+      <c r="B42" s="80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" s="84">
+        <v>88.022061049133967</v>
       </c>
       <c r="D42">
-        <v>91.949604112069864</v>
+        <v>86.687391232306652</v>
       </c>
       <c r="E42">
-        <v>88.043149271791009</v>
+        <v>86.899490010131302</v>
       </c>
       <c r="F42">
-        <v>70.437814383158539</v>
-      </c>
-      <c r="G42" s="93">
-        <v>50.027165788274679</v>
+        <v>75.166534149020336</v>
+      </c>
+      <c r="G42" s="85">
+        <v>49.417617539398499</v>
       </c>
       <c r="H42" s="40"/>
       <c r="I42" s="40"/>
-      <c r="J42" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C42:G42)&amp;","</f>
-        <v xml:space="preserve">    93.1131440222932, 91.9496041120699, 88.043149271791, 70.4378143831585, 50.0271657882747,</v>
-      </c>
-      <c r="K42" s="105" t="s">
-        <v>8</v>
-      </c>
-      <c r="L42" s="106"/>
-      <c r="M42" s="92">
-        <v>4.249709534316878</v>
+      <c r="J42" s="1"/>
+      <c r="K42" s="111"/>
+      <c r="L42" s="80" t="s">
+        <v>16</v>
+      </c>
+      <c r="M42" s="84">
+        <v>3.1059564342295989</v>
       </c>
       <c r="N42">
-        <v>4.0308606644498308</v>
+        <v>2.606378506216009</v>
       </c>
       <c r="O42">
-        <v>4.9865974054077986</v>
+        <v>1.672205327538536</v>
       </c>
       <c r="P42">
-        <v>10.497443911766959</v>
-      </c>
-      <c r="Q42" s="93">
-        <v>10.803449952087821</v>
-      </c>
-      <c r="R42" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M42:Q42)&amp;","</f>
-        <v xml:space="preserve">    4.24970953431688, 4.03086066444983, 4.9865974054078, 10.497443911767, 10.8034499520878,</v>
-      </c>
+        <v>3.4989537204184411</v>
+      </c>
+      <c r="Q42" s="85">
+        <v>1.5086756884059249</v>
+      </c>
+      <c r="R42" s="1"/>
     </row>
     <row r="43" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="105" t="s">
-        <v>21</v>
-      </c>
-      <c r="B43" s="106"/>
-      <c r="C43" s="94">
-        <v>92.587964837227005</v>
-      </c>
-      <c r="D43" s="95">
-        <v>91.423582441600061</v>
-      </c>
-      <c r="E43" s="95">
-        <v>88.545464929422721</v>
-      </c>
-      <c r="F43" s="95">
-        <v>71.659800595038618</v>
-      </c>
-      <c r="G43" s="96">
-        <v>50.266469026560699</v>
+      <c r="A43" s="111"/>
+      <c r="B43" s="80" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="84">
+        <v>90.264167794210408</v>
+      </c>
+      <c r="D43">
+        <v>89.992256751037203</v>
+      </c>
+      <c r="E43">
+        <v>89.343495694119156</v>
+      </c>
+      <c r="F43">
+        <v>78.329165755951735</v>
+      </c>
+      <c r="G43" s="85">
+        <v>52.215737786802968</v>
       </c>
       <c r="H43" s="40"/>
       <c r="I43" s="40"/>
-      <c r="J43" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C43:G43)&amp;","</f>
-        <v xml:space="preserve">    92.587964837227, 91.4235824416001, 88.5454649294227, 71.6598005950386, 50.2664690265607,</v>
-      </c>
-      <c r="K43" s="105" t="s">
-        <v>21</v>
-      </c>
-      <c r="L43" s="106"/>
-      <c r="M43" s="92">
-        <v>3.7645606938355249</v>
+      <c r="J43" s="1"/>
+      <c r="K43" s="111"/>
+      <c r="L43" s="80" t="s">
+        <v>19</v>
+      </c>
+      <c r="M43" s="84">
+        <v>2.813777787794177</v>
       </c>
       <c r="N43">
-        <v>4.4885904163036674</v>
+        <v>2.515073286885404</v>
       </c>
       <c r="O43">
-        <v>4.6842035667864703</v>
+        <v>2.61246052058309</v>
       </c>
       <c r="P43">
-        <v>10.46873255591585</v>
-      </c>
-      <c r="Q43" s="93">
-        <v>9.9892548989807413</v>
-      </c>
-      <c r="R43" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M43:Q43)&amp;","</f>
-        <v xml:space="preserve">    3.76456069383552, 4.48859041630367, 4.68420356678647, 10.4687325559158, 9.98925489898074,</v>
-      </c>
+        <v>3.988565827203912</v>
+      </c>
+      <c r="Q43" s="85">
+        <v>3.7859616126423878</v>
+      </c>
+      <c r="R43" s="1"/>
     </row>
     <row r="44" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="109" t="s">
-        <v>22</v>
-      </c>
-      <c r="B44" s="111"/>
-      <c r="C44" s="98"/>
-      <c r="D44" s="40"/>
-      <c r="E44" s="40"/>
-      <c r="F44" s="40"/>
-      <c r="G44" s="40"/>
-      <c r="H44" s="45"/>
-      <c r="I44" s="45"/>
-      <c r="J44" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C44:G44)&amp;","</f>
-        <v xml:space="preserve">    ,</v>
-      </c>
-      <c r="K44" s="109" t="s">
-        <v>22</v>
-      </c>
-      <c r="L44" s="110"/>
-      <c r="M44" s="41"/>
-      <c r="N44" s="42"/>
-      <c r="O44" s="42"/>
-      <c r="P44" s="42"/>
-      <c r="Q44" s="104"/>
-      <c r="R44" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M44:Q44)&amp;","</f>
-        <v xml:space="preserve">    ,</v>
-      </c>
-    </row>
-    <row r="45" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="105" t="s">
-        <v>23</v>
-      </c>
-      <c r="B45" s="106"/>
-      <c r="C45" s="106"/>
-      <c r="D45" s="106"/>
-      <c r="E45" s="106"/>
-      <c r="F45" s="106"/>
-      <c r="G45" s="112"/>
+      <c r="A44" s="112"/>
+      <c r="B44" s="80" t="s">
+        <v>26</v>
+      </c>
+      <c r="C44" s="86">
+        <v>88.816569678290051</v>
+      </c>
+      <c r="D44" s="87">
+        <v>88.13924460400689</v>
+      </c>
+      <c r="E44" s="87">
+        <v>87.754122925075478</v>
+      </c>
+      <c r="F44" s="87">
+        <v>76.74804506712546</v>
+      </c>
+      <c r="G44" s="88">
+        <v>50.462449044076237</v>
+      </c>
+      <c r="H44" s="40"/>
+      <c r="I44" s="40"/>
+      <c r="J44" s="1"/>
+      <c r="K44" s="112"/>
+      <c r="L44" s="80" t="s">
+        <v>26</v>
+      </c>
+      <c r="M44" s="86">
+        <v>2.8080857507745329</v>
+      </c>
+      <c r="N44" s="87">
+        <v>2.4101693608449022</v>
+      </c>
+      <c r="O44" s="87">
+        <v>2.0261358563845731</v>
+      </c>
+      <c r="P44" s="87">
+        <v>3.1965959386571878</v>
+      </c>
+      <c r="Q44" s="88">
+        <v>1.998032998184734</v>
+      </c>
+      <c r="R44" s="1"/>
+    </row>
+    <row r="45" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="B45" s="122"/>
+      <c r="C45" s="126"/>
+      <c r="D45" s="126"/>
+      <c r="E45" s="126"/>
+      <c r="F45" s="126"/>
+      <c r="G45" s="126"/>
       <c r="H45" s="40"/>
       <c r="I45" s="40"/>
       <c r="J45" s="1"/>
-      <c r="K45" s="105" t="s">
-        <v>23</v>
-      </c>
-      <c r="L45" s="106"/>
-      <c r="M45" s="106"/>
-      <c r="N45" s="106"/>
-      <c r="O45" s="106"/>
-      <c r="P45" s="106"/>
-      <c r="Q45" s="112"/>
+      <c r="K45" s="121" t="s">
+        <v>20</v>
+      </c>
+      <c r="L45" s="122"/>
+      <c r="M45" s="127"/>
+      <c r="N45" s="127"/>
+      <c r="O45" s="127"/>
+      <c r="P45" s="127"/>
+      <c r="Q45" s="128"/>
       <c r="R45" s="1"/>
     </row>
-    <row r="46" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="107" t="s">
+    <row r="46" spans="1:18" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="121" t="s">
         <v>7</v>
       </c>
-      <c r="B46" s="108"/>
-      <c r="C46" s="89">
-        <v>92.779242983398433</v>
-      </c>
-      <c r="D46" s="90">
-        <v>92.240270194904923</v>
-      </c>
-      <c r="E46" s="90">
-        <v>90.552301433559194</v>
-      </c>
-      <c r="F46" s="90">
-        <v>77.44681530627544</v>
-      </c>
-      <c r="G46" s="91">
-        <v>54.049481297537007</v>
+      <c r="B46" s="122"/>
+      <c r="C46" s="81">
+        <v>92.781043798288394</v>
+      </c>
+      <c r="D46" s="82">
+        <v>92.393805655393209</v>
+      </c>
+      <c r="E46" s="82">
+        <v>90.00908396624763</v>
+      </c>
+      <c r="F46" s="82">
+        <v>72.498171965203667</v>
+      </c>
+      <c r="G46" s="83">
+        <v>56.674852997991948</v>
       </c>
       <c r="H46" s="40"/>
       <c r="I46" s="40"/>
       <c r="J46" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C46:G46)&amp;","</f>
-        <v xml:space="preserve">    92.7792429833984, 92.2402701949049, 90.5523014335592, 77.4468153062754, 54.049481297537,</v>
-      </c>
-      <c r="K46" s="107" t="s">
+        <v xml:space="preserve">    92.7810437982884, 92.3938056553932, 90.0090839662476, 72.4981719652037, 56.6748529979919,</v>
+      </c>
+      <c r="K46" s="129" t="s">
         <v>7</v>
       </c>
-      <c r="L46" s="108"/>
-      <c r="M46" s="89">
-        <v>3.8708284466838099</v>
-      </c>
-      <c r="N46" s="90">
-        <v>4.1159624538095514</v>
-      </c>
-      <c r="O46" s="90">
-        <v>4.0917292690559766</v>
-      </c>
-      <c r="P46" s="90">
-        <v>6.9723184162377478</v>
-      </c>
-      <c r="Q46" s="91">
-        <v>8.876523191689154</v>
+      <c r="L46" s="127"/>
+      <c r="M46" s="81">
+        <v>4.5014366094349993</v>
+      </c>
+      <c r="N46" s="82">
+        <v>4.2660991290099446</v>
+      </c>
+      <c r="O46" s="82">
+        <v>4.2894182874628113</v>
+      </c>
+      <c r="P46" s="82">
+        <v>9.3344724861133059</v>
+      </c>
+      <c r="Q46" s="83">
+        <v>9.7546209717543917</v>
       </c>
       <c r="R46" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M46:Q46)&amp;","</f>
-        <v xml:space="preserve">    3.87082844668381, 4.11596245380955, 4.09172926905598, 6.97231841623775, 8.87652319168915,</v>
-      </c>
-    </row>
-    <row r="47" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="109" t="s">
+        <v xml:space="preserve">    4.501436609435, 4.26609912900994, 4.28941828746281, 9.33447248611331, 9.75462097175439,</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="121" t="s">
         <v>8</v>
       </c>
-      <c r="B47" s="110"/>
-      <c r="C47" s="92">
-        <v>91.529115829853595</v>
+      <c r="B47" s="122"/>
+      <c r="C47" s="84">
+        <v>93.113144022293241</v>
       </c>
       <c r="D47">
-        <v>91.350643423322225</v>
+        <v>91.949604112069864</v>
       </c>
       <c r="E47">
-        <v>89.341760932799787</v>
+        <v>88.043149271791009</v>
       </c>
       <c r="F47">
-        <v>79.045051998788765</v>
-      </c>
-      <c r="G47" s="93">
-        <v>52.319711731697872</v>
+        <v>70.437814383158539</v>
+      </c>
+      <c r="G47" s="85">
+        <v>50.027165788274679</v>
       </c>
       <c r="H47" s="40"/>
       <c r="I47" s="40"/>
       <c r="J47" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C47:G47)&amp;","</f>
-        <v xml:space="preserve">    91.5291158298536, 91.3506434233222, 89.3417609327998, 79.0450519987888, 52.3197117316979,</v>
-      </c>
-      <c r="K47" s="105" t="s">
+        <v xml:space="preserve">    93.1131440222932, 91.9496041120699, 88.043149271791, 70.4378143831585, 50.0271657882747,</v>
+      </c>
+      <c r="K47" s="121" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="106"/>
-      <c r="M47" s="92">
-        <v>3.326792742141544</v>
+      <c r="L47" s="122"/>
+      <c r="M47" s="84">
+        <v>4.249709534316878</v>
       </c>
       <c r="N47">
-        <v>3.370578982220036</v>
+        <v>4.0308606644498308</v>
       </c>
       <c r="O47">
-        <v>5.5895882093977454</v>
+        <v>4.9865974054077986</v>
       </c>
       <c r="P47">
-        <v>3.3906236766273481</v>
-      </c>
-      <c r="Q47" s="93">
-        <v>4.5139463885317248</v>
+        <v>10.497443911766959</v>
+      </c>
+      <c r="Q47" s="85">
+        <v>10.803449952087821</v>
       </c>
       <c r="R47" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M47:Q47)&amp;","</f>
-        <v xml:space="preserve">    3.32679274214154, 3.37057898222004, 5.58958820939775, 3.39062367662735, 4.51394638853172,</v>
-      </c>
-    </row>
-    <row r="48" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="105" t="s">
+        <v xml:space="preserve">    4.24970953431688, 4.03086066444983, 4.9865974054078, 10.497443911767, 10.8034499520878,</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="121" t="s">
         <v>21</v>
       </c>
-      <c r="B48" s="106"/>
-      <c r="C48" s="92">
-        <v>92.904210456970588</v>
-      </c>
-      <c r="D48">
-        <v>92.1891124359732</v>
-      </c>
-      <c r="E48">
-        <v>90.496036698942376</v>
-      </c>
-      <c r="F48">
-        <v>77.336951327754974</v>
-      </c>
-      <c r="G48" s="93">
-        <v>56.222535937160863</v>
+      <c r="B48" s="122"/>
+      <c r="C48" s="86">
+        <v>92.587964837227005</v>
+      </c>
+      <c r="D48" s="87">
+        <v>91.423582441600061</v>
+      </c>
+      <c r="E48" s="87">
+        <v>88.545464929422721</v>
+      </c>
+      <c r="F48" s="87">
+        <v>71.659800595038618</v>
+      </c>
+      <c r="G48" s="88">
+        <v>50.266469026560699</v>
       </c>
       <c r="H48" s="40"/>
       <c r="I48" s="40"/>
       <c r="J48" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C48:G48)&amp;","</f>
-        <v xml:space="preserve">    92.9042104569706, 92.1891124359732, 90.4960366989424, 77.336951327755, 56.2225359371609,</v>
-      </c>
-      <c r="K48" s="105" t="s">
+        <v xml:space="preserve">    92.587964837227, 91.4235824416001, 88.5454649294227, 71.6598005950386, 50.2664690265607,</v>
+      </c>
+      <c r="K48" s="121" t="s">
         <v>21</v>
       </c>
-      <c r="L48" s="106"/>
-      <c r="M48" s="92">
-        <v>3.6016716439248402</v>
+      <c r="L48" s="122"/>
+      <c r="M48" s="84">
+        <v>3.7645606938355249</v>
       </c>
       <c r="N48">
-        <v>3.9740552459554821</v>
+        <v>4.4885904163036674</v>
       </c>
       <c r="O48">
-        <v>4.0466560589706821</v>
+        <v>4.6842035667864703</v>
       </c>
       <c r="P48">
-        <v>7.6607457787732498</v>
-      </c>
-      <c r="Q48" s="93">
-        <v>9.1988486675501449</v>
+        <v>10.46873255591585</v>
+      </c>
+      <c r="Q48" s="85">
+        <v>9.9892548989807413</v>
       </c>
       <c r="R48" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M48:Q48)&amp;","</f>
-        <v xml:space="preserve">    3.60167164392484, 3.97405524595548, 4.04665605897068, 7.66074577877325, 9.19884866755014,</v>
-      </c>
-    </row>
-    <row r="49" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="105" t="s">
+        <v xml:space="preserve">    3.76456069383552, 4.48859041630367, 4.68420356678647, 10.4687325559158, 9.98925489898074,</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="123" t="s">
         <v>22</v>
       </c>
-      <c r="B49" s="106"/>
-      <c r="C49" s="41"/>
-      <c r="D49" s="42"/>
-      <c r="E49" s="42"/>
-      <c r="F49" s="42"/>
-      <c r="G49" s="104"/>
-      <c r="H49" s="40"/>
-      <c r="I49" s="40"/>
+      <c r="B49" s="125"/>
+      <c r="C49" s="90"/>
+      <c r="D49" s="40"/>
+      <c r="E49" s="40"/>
+      <c r="F49" s="40"/>
+      <c r="G49" s="40"/>
+      <c r="H49" s="45"/>
+      <c r="I49" s="45"/>
       <c r="J49" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C49:G49)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="K49" s="105" t="s">
+      <c r="K49" s="123" t="s">
         <v>22</v>
       </c>
-      <c r="L49" s="106"/>
+      <c r="L49" s="124"/>
       <c r="M49" s="41"/>
       <c r="N49" s="42"/>
       <c r="O49" s="42"/>
       <c r="P49" s="42"/>
-      <c r="Q49" s="104"/>
+      <c r="Q49" s="96"/>
       <c r="R49" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M49:Q49)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="J50" s="11"/>
-      <c r="K50" s="11"/>
-      <c r="L50" s="11"/>
-      <c r="M50" s="11"/>
-      <c r="N50" s="11"/>
-      <c r="O50" s="11"/>
-      <c r="P50" s="11"/>
-      <c r="Q50" s="11"/>
-    </row>
-    <row r="51" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="J51" s="11"/>
-      <c r="K51" s="11"/>
-      <c r="L51" s="11"/>
-      <c r="M51" s="11"/>
-      <c r="N51" s="11"/>
-      <c r="O51" s="11"/>
-      <c r="P51" s="11"/>
-      <c r="Q51" s="11"/>
-    </row>
-    <row r="52" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="H52" s="11"/>
-      <c r="I52" s="11"/>
-      <c r="J52" s="11"/>
-      <c r="K52" s="11"/>
-      <c r="L52" s="11"/>
-      <c r="M52" s="11"/>
-      <c r="N52" s="11"/>
-      <c r="O52" s="11"/>
-      <c r="P52" s="11"/>
-      <c r="Q52" s="11"/>
-    </row>
-    <row r="53" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="H53" s="11"/>
-      <c r="I53" s="11"/>
-      <c r="J53" s="11"/>
-      <c r="K53" s="11"/>
-      <c r="L53" s="11"/>
-      <c r="M53" s="11"/>
-      <c r="N53" s="11"/>
-      <c r="O53" s="11"/>
-      <c r="P53" s="11"/>
-      <c r="Q53" s="11"/>
-    </row>
-    <row r="54" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="H54" s="11"/>
-      <c r="I54" s="11"/>
-      <c r="J54" s="11"/>
-      <c r="K54" s="11"/>
-      <c r="L54" s="11"/>
-      <c r="M54" s="11"/>
-      <c r="N54" s="11"/>
-      <c r="O54" s="11"/>
-      <c r="P54" s="11"/>
-      <c r="Q54" s="11"/>
+    <row r="50" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="121" t="s">
+        <v>23</v>
+      </c>
+      <c r="B50" s="122"/>
+      <c r="C50" s="122"/>
+      <c r="D50" s="122"/>
+      <c r="E50" s="122"/>
+      <c r="F50" s="122"/>
+      <c r="G50" s="130"/>
+      <c r="H50" s="40"/>
+      <c r="I50" s="40"/>
+      <c r="J50" s="1"/>
+      <c r="K50" s="121" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" s="122"/>
+      <c r="M50" s="122"/>
+      <c r="N50" s="122"/>
+      <c r="O50" s="122"/>
+      <c r="P50" s="122"/>
+      <c r="Q50" s="130"/>
+      <c r="R50" s="1"/>
+    </row>
+    <row r="51" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="129" t="s">
+        <v>7</v>
+      </c>
+      <c r="B51" s="127"/>
+      <c r="C51" s="81">
+        <v>92.779242983398433</v>
+      </c>
+      <c r="D51" s="82">
+        <v>92.240270194904923</v>
+      </c>
+      <c r="E51" s="82">
+        <v>90.552301433559194</v>
+      </c>
+      <c r="F51" s="82">
+        <v>77.44681530627544</v>
+      </c>
+      <c r="G51" s="83">
+        <v>54.049481297537007</v>
+      </c>
+      <c r="H51" s="40"/>
+      <c r="I51" s="40"/>
+      <c r="J51" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C51:G51)&amp;","</f>
+        <v xml:space="preserve">    92.7792429833984, 92.2402701949049, 90.5523014335592, 77.4468153062754, 54.049481297537,</v>
+      </c>
+      <c r="K51" s="129" t="s">
+        <v>7</v>
+      </c>
+      <c r="L51" s="127"/>
+      <c r="M51" s="81">
+        <v>3.8708284466838099</v>
+      </c>
+      <c r="N51" s="82">
+        <v>4.1159624538095514</v>
+      </c>
+      <c r="O51" s="82">
+        <v>4.0917292690559766</v>
+      </c>
+      <c r="P51" s="82">
+        <v>6.9723184162377478</v>
+      </c>
+      <c r="Q51" s="83">
+        <v>8.876523191689154</v>
+      </c>
+      <c r="R51" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M51:Q51)&amp;","</f>
+        <v xml:space="preserve">    3.87082844668381, 4.11596245380955, 4.09172926905598, 6.97231841623775, 8.87652319168915,</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="123" t="s">
+        <v>8</v>
+      </c>
+      <c r="B52" s="124"/>
+      <c r="C52" s="84">
+        <v>91.529115829853595</v>
+      </c>
+      <c r="D52">
+        <v>91.350643423322225</v>
+      </c>
+      <c r="E52">
+        <v>89.341760932799787</v>
+      </c>
+      <c r="F52">
+        <v>79.045051998788765</v>
+      </c>
+      <c r="G52" s="85">
+        <v>52.319711731697872</v>
+      </c>
+      <c r="H52" s="40"/>
+      <c r="I52" s="40"/>
+      <c r="J52" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C52:G52)&amp;","</f>
+        <v xml:space="preserve">    91.5291158298536, 91.3506434233222, 89.3417609327998, 79.0450519987888, 52.3197117316979,</v>
+      </c>
+      <c r="K52" s="121" t="s">
+        <v>8</v>
+      </c>
+      <c r="L52" s="122"/>
+      <c r="M52" s="84">
+        <v>3.326792742141544</v>
+      </c>
+      <c r="N52">
+        <v>3.370578982220036</v>
+      </c>
+      <c r="O52">
+        <v>5.5895882093977454</v>
+      </c>
+      <c r="P52">
+        <v>3.3906236766273481</v>
+      </c>
+      <c r="Q52" s="85">
+        <v>4.5139463885317248</v>
+      </c>
+      <c r="R52" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M52:Q52)&amp;","</f>
+        <v xml:space="preserve">    3.32679274214154, 3.37057898222004, 5.58958820939775, 3.39062367662735, 4.51394638853172,</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="121" t="s">
+        <v>21</v>
+      </c>
+      <c r="B53" s="122"/>
+      <c r="C53" s="84">
+        <v>92.904210456970588</v>
+      </c>
+      <c r="D53">
+        <v>92.1891124359732</v>
+      </c>
+      <c r="E53">
+        <v>90.496036698942376</v>
+      </c>
+      <c r="F53">
+        <v>77.336951327754974</v>
+      </c>
+      <c r="G53" s="85">
+        <v>56.222535937160863</v>
+      </c>
+      <c r="H53" s="40"/>
+      <c r="I53" s="40"/>
+      <c r="J53" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C53:G53)&amp;","</f>
+        <v xml:space="preserve">    92.9042104569706, 92.1891124359732, 90.4960366989424, 77.336951327755, 56.2225359371609,</v>
+      </c>
+      <c r="K53" s="121" t="s">
+        <v>21</v>
+      </c>
+      <c r="L53" s="122"/>
+      <c r="M53" s="84">
+        <v>3.6016716439248402</v>
+      </c>
+      <c r="N53">
+        <v>3.9740552459554821</v>
+      </c>
+      <c r="O53">
+        <v>4.0466560589706821</v>
+      </c>
+      <c r="P53">
+        <v>7.6607457787732498</v>
+      </c>
+      <c r="Q53" s="85">
+        <v>9.1988486675501449</v>
+      </c>
+      <c r="R53" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M53:Q53)&amp;","</f>
+        <v xml:space="preserve">    3.60167164392484, 3.97405524595548, 4.04665605897068, 7.66074577877325, 9.19884866755014,</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="121" t="s">
+        <v>22</v>
+      </c>
+      <c r="B54" s="122"/>
+      <c r="C54" s="41"/>
+      <c r="D54" s="42"/>
+      <c r="E54" s="42"/>
+      <c r="F54" s="42"/>
+      <c r="G54" s="96"/>
+      <c r="H54" s="40"/>
+      <c r="I54" s="40"/>
+      <c r="J54" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C54:G54)&amp;","</f>
+        <v xml:space="preserve">    ,</v>
+      </c>
+      <c r="K54" s="121" t="s">
+        <v>22</v>
+      </c>
+      <c r="L54" s="122"/>
+      <c r="M54" s="41"/>
+      <c r="N54" s="42"/>
+      <c r="O54" s="42"/>
+      <c r="P54" s="42"/>
+      <c r="Q54" s="96"/>
+      <c r="R54" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M54:Q54)&amp;","</f>
+        <v xml:space="preserve">    ,</v>
+      </c>
     </row>
     <row r="55" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="H55" s="11"/>
-      <c r="I55" s="11"/>
       <c r="J55" s="11"/>
       <c r="K55" s="11"/>
       <c r="L55" s="11"/>
@@ -3424,10 +3635,122 @@
       <c r="P55" s="11"/>
       <c r="Q55" s="11"/>
     </row>
+    <row r="56" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="J56" s="11"/>
+      <c r="K56" s="11"/>
+      <c r="L56" s="11"/>
+      <c r="M56" s="11"/>
+      <c r="N56" s="11"/>
+      <c r="O56" s="11"/>
+      <c r="P56" s="11"/>
+      <c r="Q56" s="11"/>
+    </row>
+    <row r="57" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="H57" s="11"/>
+      <c r="I57" s="11"/>
+      <c r="J57" s="11"/>
+      <c r="K57" s="11"/>
+      <c r="L57" s="11"/>
+      <c r="M57" s="11"/>
+      <c r="N57" s="11"/>
+      <c r="O57" s="11"/>
+      <c r="P57" s="11"/>
+      <c r="Q57" s="11"/>
+    </row>
+    <row r="58" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="H58" s="11"/>
+      <c r="I58" s="11"/>
+      <c r="J58" s="11"/>
+      <c r="K58" s="11"/>
+      <c r="L58" s="11"/>
+      <c r="M58" s="11"/>
+      <c r="N58" s="11"/>
+      <c r="O58" s="11"/>
+      <c r="P58" s="11"/>
+      <c r="Q58" s="11"/>
+    </row>
+    <row r="59" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="H59" s="11"/>
+      <c r="I59" s="11"/>
+      <c r="J59" s="11"/>
+      <c r="K59" s="11"/>
+      <c r="L59" s="11"/>
+      <c r="M59" s="11"/>
+      <c r="N59" s="11"/>
+      <c r="O59" s="11"/>
+      <c r="P59" s="11"/>
+      <c r="Q59" s="11"/>
+    </row>
+    <row r="60" spans="1:18" ht="15" x14ac:dyDescent="0.2">
+      <c r="H60" s="11"/>
+      <c r="I60" s="11"/>
+      <c r="J60" s="11"/>
+      <c r="K60" s="11"/>
+      <c r="L60" s="11"/>
+      <c r="M60" s="11"/>
+      <c r="N60" s="11"/>
+      <c r="O60" s="11"/>
+      <c r="P60" s="11"/>
+      <c r="Q60" s="11"/>
+    </row>
   </sheetData>
-  <mergeCells count="60">
-    <mergeCell ref="A31:A39"/>
-    <mergeCell ref="K31:K39"/>
+  <mergeCells count="70">
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="K54:L54"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="K51:L51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="K52:L52"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="K53:L53"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="K48:L48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="K50:Q50"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="K45:Q45"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="K35:Q35"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="K25:Q25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="K20:Q20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="A36:A44"/>
+    <mergeCell ref="K36:K44"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="A3:B3"/>
@@ -3442,66 +3765,34 @@
     <mergeCell ref="K16:L16"/>
     <mergeCell ref="A6:A14"/>
     <mergeCell ref="K6:K14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="K20:Q20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="A30:G30"/>
-    <mergeCell ref="K30:Q30"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="K40:Q40"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="K41:L41"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="K42:L42"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="K44:L44"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="K45:Q45"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="K46:L46"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="K47:L47"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="K48:L48"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="C2:G4 C7:G14 C16:G19 C21:G24">
-    <cfRule type="colorScale" priority="302">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:G4 H2:I24">
-    <cfRule type="colorScale" priority="285">
+  <conditionalFormatting sqref="C2:C4 C6:C14">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:G4 C7:G14 C16:G19 C21:G24 C26:G29">
+    <cfRule type="colorScale" priority="307">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:G4 H2:I29">
+    <cfRule type="colorScale" priority="290">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -3513,6 +3804,380 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:G4">
+    <cfRule type="colorScale" priority="311">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="312">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="313">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3:G4 H3:I6">
+    <cfRule type="colorScale" priority="293">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="294">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="295">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="296">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="297">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="298">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C6:G14 C2:G4 C16:G19 C21:G24 C26:G29">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C7:G7">
+    <cfRule type="colorScale" priority="314">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="315">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8:G14">
+    <cfRule type="colorScale" priority="316">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="317">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:G18 C21:G23">
+    <cfRule type="colorScale" priority="318">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:G18">
+    <cfRule type="colorScale" priority="320">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="321">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="322">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:G19 C21:G24 C7:G14 C2:G4 C26:G29">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:G19 C21:G24 C26:G29">
+    <cfRule type="colorScale" priority="323">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C21:G23">
+    <cfRule type="colorScale" priority="325">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="326">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="327">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D4 D6:D14">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E4 E6:E14">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F4 F6:F14">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:G4 G6:G14">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H2:H29">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H50:H54">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I2:I29">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I50:I54">
+    <cfRule type="colorScale" priority="54">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="305">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="306">
       <colorScale>
         <cfvo type="min"/>
@@ -3523,334 +4188,8 @@
         <color rgb="FFF8696B"/>
       </colorScale>
     </cfRule>
-    <cfRule type="colorScale" priority="307">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="308">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C3:G4 H3:I6">
-    <cfRule type="colorScale" priority="288">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="289">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="290">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="291">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="292">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="293">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C7:G7">
-    <cfRule type="colorScale" priority="309">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="310">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C8:G14">
-    <cfRule type="colorScale" priority="311">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="312">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G18 C21:G23">
-    <cfRule type="colorScale" priority="313">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G18">
-    <cfRule type="colorScale" priority="315">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="316">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="317">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G19 C21:G24 C7:G14 C2:G4">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G19 C21:G24">
-    <cfRule type="colorScale" priority="318">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C21:G23">
-    <cfRule type="colorScale" priority="320">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="321">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="322">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H24">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H45:H49">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I24">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I45:I49">
-    <cfRule type="colorScale" priority="49">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="300">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="301">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C6:G14 C2:G4 C16:G19 C21:G24">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C4 C6:C14">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:G4 C6:G14">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -3862,44 +4201,40 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D4 D6:D14">
+  <conditionalFormatting sqref="C26:G28">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C26:G28">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
     <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E4 E6:E14">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F4 F6:F14">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G4 G6:G14">
-    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4003,10 +4338,10 @@
       <c r="V1" s="12"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="114" t="s">
+      <c r="A2" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="115"/>
+      <c r="B2" s="114"/>
       <c r="C2" s="20"/>
       <c r="D2" s="21"/>
       <c r="E2" s="21"/>
@@ -4026,10 +4361,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:I2)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M2" s="114" t="s">
+      <c r="M2" s="113" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="115"/>
+      <c r="N2" s="114"/>
       <c r="O2" s="31"/>
       <c r="P2" s="32"/>
       <c r="Q2" s="32"/>
@@ -4043,10 +4378,10 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="114" t="s">
+      <c r="A3" s="113" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="115"/>
+      <c r="B3" s="114"/>
       <c r="C3" s="31"/>
       <c r="D3" s="32"/>
       <c r="E3" s="32"/>
@@ -4066,10 +4401,10 @@
         <f t="shared" ref="L3:L18" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M3" s="114" t="s">
+      <c r="M3" s="113" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="115"/>
+      <c r="N3" s="114"/>
       <c r="O3" s="31"/>
       <c r="P3" s="32"/>
       <c r="Q3" s="32"/>
@@ -4083,10 +4418,10 @@
       </c>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="114" t="s">
+      <c r="A4" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="115"/>
+      <c r="B4" s="114"/>
       <c r="C4" s="24"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
@@ -4106,10 +4441,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M4" s="114" t="s">
+      <c r="M4" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="115"/>
+      <c r="N4" s="114"/>
       <c r="O4" s="43"/>
       <c r="P4" s="26"/>
       <c r="Q4" s="26"/>
@@ -4123,35 +4458,35 @@
       </c>
     </row>
     <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="114" t="s">
+      <c r="A5" s="113" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="116"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
-      <c r="H5" s="116"/>
-      <c r="I5" s="115"/>
+      <c r="B5" s="117"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="117"/>
+      <c r="I5" s="114"/>
       <c r="J5" s="34"/>
       <c r="K5" s="34"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="114" t="s">
+      <c r="M5" s="113" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="116"/>
-      <c r="O5" s="116"/>
-      <c r="P5" s="116"/>
-      <c r="Q5" s="116"/>
-      <c r="R5" s="116"/>
-      <c r="S5" s="116"/>
-      <c r="T5" s="116"/>
-      <c r="U5" s="115"/>
+      <c r="N5" s="117"/>
+      <c r="O5" s="117"/>
+      <c r="P5" s="117"/>
+      <c r="Q5" s="117"/>
+      <c r="R5" s="117"/>
+      <c r="S5" s="117"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="114"/>
       <c r="V5" s="12"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="119" t="s">
+      <c r="A6" s="115" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -4176,7 +4511,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M6" s="119" t="s">
+      <c r="M6" s="115" t="s">
         <v>11</v>
       </c>
       <c r="N6" s="8" t="s">
@@ -4195,7 +4530,7 @@
       </c>
     </row>
     <row r="7" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="121"/>
+      <c r="A7" s="120"/>
       <c r="B7" s="8" t="s">
         <v>14</v>
       </c>
@@ -4218,7 +4553,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M7" s="121"/>
+      <c r="M7" s="120"/>
       <c r="N7" s="8" t="s">
         <v>14</v>
       </c>
@@ -4235,7 +4570,7 @@
       </c>
     </row>
     <row r="8" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="121"/>
+      <c r="A8" s="120"/>
       <c r="B8" s="8" t="s">
         <v>17</v>
       </c>
@@ -4258,7 +4593,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M8" s="121"/>
+      <c r="M8" s="120"/>
       <c r="N8" s="8" t="s">
         <v>17</v>
       </c>
@@ -4272,7 +4607,7 @@
       <c r="V8" s="12"/>
     </row>
     <row r="9" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="121"/>
+      <c r="A9" s="120"/>
       <c r="B9" s="8" t="s">
         <v>18</v>
       </c>
@@ -4295,7 +4630,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M9" s="121"/>
+      <c r="M9" s="120"/>
       <c r="N9" s="8" t="s">
         <v>18</v>
       </c>
@@ -4309,7 +4644,7 @@
       <c r="V9" s="12"/>
     </row>
     <row r="10" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="121"/>
+      <c r="A10" s="120"/>
       <c r="B10" s="8" t="s">
         <v>15</v>
       </c>
@@ -4332,7 +4667,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M10" s="121"/>
+      <c r="M10" s="120"/>
       <c r="N10" s="8" t="s">
         <v>15</v>
       </c>
@@ -4346,7 +4681,7 @@
       <c r="V10" s="12"/>
     </row>
     <row r="11" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="121"/>
+      <c r="A11" s="120"/>
       <c r="B11" s="8" t="s">
         <v>25</v>
       </c>
@@ -4369,7 +4704,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M11" s="121"/>
+      <c r="M11" s="120"/>
       <c r="N11" s="8" t="s">
         <v>25</v>
       </c>
@@ -4383,7 +4718,7 @@
       <c r="V11" s="12"/>
     </row>
     <row r="12" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="121"/>
+      <c r="A12" s="120"/>
       <c r="B12" s="8" t="s">
         <v>19</v>
       </c>
@@ -4406,7 +4741,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M12" s="121"/>
+      <c r="M12" s="120"/>
       <c r="N12" s="8" t="s">
         <v>19</v>
       </c>
@@ -4420,7 +4755,7 @@
       <c r="V12" s="12"/>
     </row>
     <row r="13" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="121"/>
+      <c r="A13" s="120"/>
       <c r="B13" s="8" t="s">
         <v>16</v>
       </c>
@@ -4443,7 +4778,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M13" s="121"/>
+      <c r="M13" s="120"/>
       <c r="N13" s="8" t="s">
         <v>16</v>
       </c>
@@ -4457,7 +4792,7 @@
       <c r="V13" s="12"/>
     </row>
     <row r="14" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="117"/>
+      <c r="A14" s="118"/>
       <c r="B14" s="8" t="s">
         <v>26</v>
       </c>
@@ -4480,7 +4815,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M14" s="117"/>
+      <c r="M14" s="118"/>
       <c r="N14" s="8" t="s">
         <v>26</v>
       </c>
@@ -4494,38 +4829,38 @@
       <c r="V14" s="12"/>
     </row>
     <row r="15" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="114" t="s">
+      <c r="A15" s="113" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="116"/>
-      <c r="C15" s="124"/>
-      <c r="D15" s="124"/>
-      <c r="E15" s="124"/>
-      <c r="F15" s="124"/>
-      <c r="G15" s="124"/>
-      <c r="H15" s="124"/>
-      <c r="I15" s="125"/>
+      <c r="B15" s="117"/>
+      <c r="C15" s="131"/>
+      <c r="D15" s="131"/>
+      <c r="E15" s="131"/>
+      <c r="F15" s="131"/>
+      <c r="G15" s="131"/>
+      <c r="H15" s="131"/>
+      <c r="I15" s="132"/>
       <c r="J15" s="34"/>
       <c r="K15" s="34"/>
       <c r="L15" s="12"/>
-      <c r="M15" s="114" t="s">
+      <c r="M15" s="113" t="s">
         <v>20</v>
       </c>
-      <c r="N15" s="116"/>
-      <c r="O15" s="126"/>
-      <c r="P15" s="126"/>
-      <c r="Q15" s="126"/>
-      <c r="R15" s="126"/>
-      <c r="S15" s="126"/>
-      <c r="T15" s="126"/>
-      <c r="U15" s="120"/>
+      <c r="N15" s="117"/>
+      <c r="O15" s="134"/>
+      <c r="P15" s="134"/>
+      <c r="Q15" s="134"/>
+      <c r="R15" s="134"/>
+      <c r="S15" s="134"/>
+      <c r="T15" s="134"/>
+      <c r="U15" s="116"/>
       <c r="V15" s="12"/>
     </row>
     <row r="16" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="114" t="s">
+      <c r="A16" s="113" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="115"/>
+      <c r="B16" s="114"/>
       <c r="C16" s="46"/>
       <c r="D16" s="47"/>
       <c r="E16" s="47"/>
@@ -4545,10 +4880,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M16" s="114" t="s">
+      <c r="M16" s="113" t="s">
         <v>7</v>
       </c>
-      <c r="N16" s="115"/>
+      <c r="N16" s="114"/>
       <c r="O16" s="46"/>
       <c r="P16" s="47"/>
       <c r="Q16" s="47"/>
@@ -4562,10 +4897,10 @@
       </c>
     </row>
     <row r="17" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="119" t="s">
+      <c r="A17" s="115" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="120"/>
+      <c r="B17" s="116"/>
       <c r="C17" s="49"/>
       <c r="D17" s="12"/>
       <c r="E17" s="12"/>
@@ -4585,10 +4920,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M17" s="114" t="s">
+      <c r="M17" s="113" t="s">
         <v>8</v>
       </c>
-      <c r="N17" s="115"/>
+      <c r="N17" s="114"/>
       <c r="O17" s="49"/>
       <c r="P17" s="12"/>
       <c r="Q17" s="12"/>
@@ -4602,10 +4937,10 @@
       </c>
     </row>
     <row r="18" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="114" t="s">
+      <c r="A18" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="115"/>
+      <c r="B18" s="114"/>
       <c r="C18" s="49"/>
       <c r="D18" s="12"/>
       <c r="E18" s="12"/>
@@ -4625,10 +4960,10 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M18" s="114" t="s">
+      <c r="M18" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="N18" s="115"/>
+      <c r="N18" s="114"/>
       <c r="O18" s="49"/>
       <c r="P18" s="12"/>
       <c r="Q18" s="12"/>
@@ -4642,10 +4977,10 @@
       </c>
     </row>
     <row r="19" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="114" t="s">
+      <c r="A19" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="115"/>
+      <c r="B19" s="114"/>
       <c r="C19" s="51"/>
       <c r="D19" s="52"/>
       <c r="E19" s="52"/>
@@ -4662,10 +4997,10 @@
         <v>0</v>
       </c>
       <c r="L19" s="12"/>
-      <c r="M19" s="114" t="s">
+      <c r="M19" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="N19" s="115"/>
+      <c r="N19" s="114"/>
       <c r="O19" s="51"/>
       <c r="P19" s="52"/>
       <c r="Q19" s="52"/>
@@ -4676,38 +5011,38 @@
       <c r="V19" s="12"/>
     </row>
     <row r="20" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="114" t="s">
+      <c r="A20" s="113" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="116"/>
-      <c r="C20" s="124"/>
-      <c r="D20" s="124"/>
-      <c r="E20" s="124"/>
-      <c r="F20" s="124"/>
-      <c r="G20" s="124"/>
-      <c r="H20" s="124"/>
-      <c r="I20" s="125"/>
+      <c r="B20" s="117"/>
+      <c r="C20" s="131"/>
+      <c r="D20" s="131"/>
+      <c r="E20" s="131"/>
+      <c r="F20" s="131"/>
+      <c r="G20" s="131"/>
+      <c r="H20" s="131"/>
+      <c r="I20" s="132"/>
       <c r="J20" s="34"/>
       <c r="K20" s="34"/>
       <c r="L20" s="12"/>
-      <c r="M20" s="114" t="s">
+      <c r="M20" s="113" t="s">
         <v>23</v>
       </c>
-      <c r="N20" s="116"/>
-      <c r="O20" s="124"/>
-      <c r="P20" s="124"/>
-      <c r="Q20" s="124"/>
-      <c r="R20" s="124"/>
-      <c r="S20" s="124"/>
-      <c r="T20" s="124"/>
-      <c r="U20" s="125"/>
+      <c r="N20" s="117"/>
+      <c r="O20" s="131"/>
+      <c r="P20" s="131"/>
+      <c r="Q20" s="131"/>
+      <c r="R20" s="131"/>
+      <c r="S20" s="131"/>
+      <c r="T20" s="131"/>
+      <c r="U20" s="132"/>
       <c r="V20" s="12"/>
     </row>
     <row r="21" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="114" t="s">
+      <c r="A21" s="113" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="115"/>
+      <c r="B21" s="114"/>
       <c r="C21" s="46"/>
       <c r="D21" s="47"/>
       <c r="E21" s="47"/>
@@ -4727,10 +5062,10 @@
         <f t="shared" ref="L21:L23" si="2">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:I21)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M21" s="114" t="s">
+      <c r="M21" s="113" t="s">
         <v>7</v>
       </c>
-      <c r="N21" s="115"/>
+      <c r="N21" s="114"/>
       <c r="O21" s="46"/>
       <c r="P21" s="47"/>
       <c r="Q21" s="47"/>
@@ -4744,10 +5079,10 @@
       </c>
     </row>
     <row r="22" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="119" t="s">
+      <c r="A22" s="115" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="120"/>
+      <c r="B22" s="116"/>
       <c r="C22" s="49"/>
       <c r="D22" s="12"/>
       <c r="E22" s="12"/>
@@ -4767,10 +5102,10 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M22" s="114" t="s">
+      <c r="M22" s="113" t="s">
         <v>8</v>
       </c>
-      <c r="N22" s="115"/>
+      <c r="N22" s="114"/>
       <c r="O22" s="49"/>
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
@@ -4784,10 +5119,10 @@
       </c>
     </row>
     <row r="23" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="114" t="s">
+      <c r="A23" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="115"/>
+      <c r="B23" s="114"/>
       <c r="C23" s="49"/>
       <c r="D23" s="12"/>
       <c r="E23" s="12"/>
@@ -4807,10 +5142,10 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M23" s="114" t="s">
+      <c r="M23" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="N23" s="115"/>
+      <c r="N23" s="114"/>
       <c r="O23" s="49"/>
       <c r="P23" s="12"/>
       <c r="Q23" s="12"/>
@@ -4824,10 +5159,10 @@
       </c>
     </row>
     <row r="24" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="114" t="s">
+      <c r="A24" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="115"/>
+      <c r="B24" s="114"/>
       <c r="C24" s="51"/>
       <c r="D24" s="52"/>
       <c r="E24" s="52"/>
@@ -4844,10 +5179,10 @@
         <v>0</v>
       </c>
       <c r="L24" s="12"/>
-      <c r="M24" s="114" t="s">
+      <c r="M24" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="N24" s="115"/>
+      <c r="N24" s="114"/>
       <c r="O24" s="51"/>
       <c r="P24" s="52"/>
       <c r="Q24" s="52"/>
@@ -4858,38 +5193,38 @@
       <c r="V24" s="12"/>
     </row>
     <row r="25" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="114" t="s">
+      <c r="A25" s="113" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="116"/>
-      <c r="C25" s="124"/>
-      <c r="D25" s="124"/>
-      <c r="E25" s="124"/>
-      <c r="F25" s="124"/>
-      <c r="G25" s="124"/>
-      <c r="H25" s="124"/>
-      <c r="I25" s="125"/>
+      <c r="B25" s="117"/>
+      <c r="C25" s="131"/>
+      <c r="D25" s="131"/>
+      <c r="E25" s="131"/>
+      <c r="F25" s="131"/>
+      <c r="G25" s="131"/>
+      <c r="H25" s="131"/>
+      <c r="I25" s="132"/>
       <c r="J25" s="34"/>
       <c r="K25" s="34"/>
       <c r="L25" s="12"/>
-      <c r="M25" s="114" t="s">
+      <c r="M25" s="113" t="s">
         <v>23</v>
       </c>
-      <c r="N25" s="116"/>
-      <c r="O25" s="124"/>
-      <c r="P25" s="124"/>
-      <c r="Q25" s="124"/>
-      <c r="R25" s="124"/>
-      <c r="S25" s="124"/>
-      <c r="T25" s="124"/>
-      <c r="U25" s="125"/>
+      <c r="N25" s="117"/>
+      <c r="O25" s="131"/>
+      <c r="P25" s="131"/>
+      <c r="Q25" s="131"/>
+      <c r="R25" s="131"/>
+      <c r="S25" s="131"/>
+      <c r="T25" s="131"/>
+      <c r="U25" s="132"/>
       <c r="V25" s="12"/>
     </row>
     <row r="26" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="114" t="s">
+      <c r="A26" s="113" t="s">
         <v>7</v>
       </c>
-      <c r="B26" s="115"/>
+      <c r="B26" s="114"/>
       <c r="C26"/>
       <c r="D26"/>
       <c r="E26"/>
@@ -4909,10 +5244,10 @@
         <f t="shared" ref="L26:L28" si="4">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C26:I26)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M26" s="114" t="s">
+      <c r="M26" s="113" t="s">
         <v>7</v>
       </c>
-      <c r="N26" s="115"/>
+      <c r="N26" s="114"/>
       <c r="O26"/>
       <c r="P26"/>
       <c r="Q26"/>
@@ -4926,10 +5261,10 @@
       </c>
     </row>
     <row r="27" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="119" t="s">
+      <c r="A27" s="115" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="120"/>
+      <c r="B27" s="116"/>
       <c r="C27"/>
       <c r="D27"/>
       <c r="E27"/>
@@ -4949,10 +5284,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M27" s="114" t="s">
+      <c r="M27" s="113" t="s">
         <v>8</v>
       </c>
-      <c r="N27" s="115"/>
+      <c r="N27" s="114"/>
       <c r="O27"/>
       <c r="P27"/>
       <c r="Q27"/>
@@ -4966,10 +5301,10 @@
       </c>
     </row>
     <row r="28" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="114" t="s">
+      <c r="A28" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="115"/>
+      <c r="B28" s="114"/>
       <c r="C28"/>
       <c r="D28"/>
       <c r="E28"/>
@@ -4989,10 +5324,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M28" s="114" t="s">
+      <c r="M28" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="N28" s="115"/>
+      <c r="N28" s="114"/>
       <c r="O28"/>
       <c r="P28"/>
       <c r="Q28"/>
@@ -5006,10 +5341,10 @@
       </c>
     </row>
     <row r="29" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="114" t="s">
+      <c r="A29" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="B29" s="115"/>
+      <c r="B29" s="114"/>
       <c r="C29"/>
       <c r="D29"/>
       <c r="E29"/>
@@ -5026,17 +5361,17 @@
         <v>0</v>
       </c>
       <c r="L29" s="12"/>
-      <c r="M29" s="114" t="s">
+      <c r="M29" s="113" t="s">
         <v>22</v>
       </c>
-      <c r="N29" s="115"/>
-      <c r="O29" s="85"/>
-      <c r="P29" s="86"/>
-      <c r="Q29" s="86"/>
-      <c r="R29" s="86"/>
-      <c r="S29" s="86"/>
-      <c r="T29" s="86"/>
-      <c r="U29" s="87"/>
+      <c r="N29" s="114"/>
+      <c r="O29" s="77"/>
+      <c r="P29" s="78"/>
+      <c r="Q29" s="78"/>
+      <c r="R29" s="78"/>
+      <c r="S29" s="78"/>
+      <c r="T29" s="78"/>
+      <c r="U29" s="79"/>
       <c r="V29" s="12"/>
     </row>
     <row r="30" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.25">
@@ -5122,10 +5457,10 @@
       <c r="V31" s="1"/>
     </row>
     <row r="32" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="105" t="s">
+      <c r="A32" s="121" t="s">
         <v>5</v>
       </c>
-      <c r="B32" s="112"/>
+      <c r="B32" s="130"/>
       <c r="C32" s="38"/>
       <c r="D32" s="38"/>
       <c r="E32" s="38"/>
@@ -5139,10 +5474,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C32:I32)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M32" s="105" t="s">
+      <c r="M32" s="121" t="s">
         <v>5</v>
       </c>
-      <c r="N32" s="112"/>
+      <c r="N32" s="130"/>
       <c r="O32" s="37"/>
       <c r="P32" s="38"/>
       <c r="Q32" s="38"/>
@@ -5156,10 +5491,10 @@
       </c>
     </row>
     <row r="33" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="105" t="s">
+      <c r="A33" s="121" t="s">
         <v>6</v>
       </c>
-      <c r="B33" s="112"/>
+      <c r="B33" s="130"/>
       <c r="C33" s="38"/>
       <c r="D33" s="38"/>
       <c r="E33" s="38"/>
@@ -5173,10 +5508,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C33:I33)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M33" s="105" t="s">
+      <c r="M33" s="121" t="s">
         <v>6</v>
       </c>
-      <c r="N33" s="112"/>
+      <c r="N33" s="130"/>
       <c r="O33" s="38"/>
       <c r="P33" s="38"/>
       <c r="Q33" s="38"/>
@@ -5190,10 +5525,10 @@
       </c>
     </row>
     <row r="34" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="105" t="s">
+      <c r="A34" s="121" t="s">
         <v>10</v>
       </c>
-      <c r="B34" s="112"/>
+      <c r="B34" s="130"/>
       <c r="C34" s="28"/>
       <c r="D34" s="29"/>
       <c r="E34" s="29"/>
@@ -5207,10 +5542,10 @@
         <f t="shared" ref="L34:L43" si="7">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C34:I34)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M34" s="105" t="s">
+      <c r="M34" s="121" t="s">
         <v>10</v>
       </c>
-      <c r="N34" s="112"/>
+      <c r="N34" s="130"/>
       <c r="O34" s="28"/>
       <c r="P34" s="29"/>
       <c r="Q34" s="29"/>
@@ -5224,35 +5559,35 @@
       </c>
     </row>
     <row r="35" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="105" t="s">
+      <c r="A35" s="121" t="s">
         <v>12</v>
       </c>
-      <c r="B35" s="106"/>
-      <c r="C35" s="106"/>
-      <c r="D35" s="106"/>
-      <c r="E35" s="106"/>
-      <c r="F35" s="106"/>
-      <c r="G35" s="106"/>
-      <c r="H35" s="106"/>
-      <c r="I35" s="112"/>
+      <c r="B35" s="122"/>
+      <c r="C35" s="122"/>
+      <c r="D35" s="122"/>
+      <c r="E35" s="122"/>
+      <c r="F35" s="122"/>
+      <c r="G35" s="122"/>
+      <c r="H35" s="122"/>
+      <c r="I35" s="130"/>
       <c r="J35" s="40"/>
       <c r="K35" s="40"/>
       <c r="L35" s="1"/>
-      <c r="M35" s="105" t="s">
+      <c r="M35" s="121" t="s">
         <v>12</v>
       </c>
-      <c r="N35" s="106"/>
-      <c r="O35" s="106"/>
-      <c r="P35" s="106"/>
-      <c r="Q35" s="106"/>
-      <c r="R35" s="106"/>
-      <c r="S35" s="106"/>
-      <c r="T35" s="106"/>
-      <c r="U35" s="112"/>
+      <c r="N35" s="122"/>
+      <c r="O35" s="122"/>
+      <c r="P35" s="122"/>
+      <c r="Q35" s="122"/>
+      <c r="R35" s="122"/>
+      <c r="S35" s="122"/>
+      <c r="T35" s="122"/>
+      <c r="U35" s="130"/>
       <c r="V35" s="1"/>
     </row>
     <row r="36" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="109" t="s">
+      <c r="A36" s="123" t="s">
         <v>11</v>
       </c>
       <c r="B36" s="9" t="s">
@@ -5271,7 +5606,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M36" s="109" t="s">
+      <c r="M36" s="123" t="s">
         <v>11</v>
       </c>
       <c r="N36" s="9" t="s">
@@ -5290,7 +5625,7 @@
       </c>
     </row>
     <row r="37" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="122"/>
+      <c r="A37" s="135"/>
       <c r="B37" s="9" t="s">
         <v>14</v>
       </c>
@@ -5307,7 +5642,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M37" s="122"/>
+      <c r="M37" s="135"/>
       <c r="N37" s="9" t="s">
         <v>14</v>
       </c>
@@ -5324,7 +5659,7 @@
       </c>
     </row>
     <row r="38" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="122"/>
+      <c r="A38" s="135"/>
       <c r="B38" s="9" t="s">
         <v>17</v>
       </c>
@@ -5338,7 +5673,7 @@
       <c r="J38" s="40"/>
       <c r="K38" s="40"/>
       <c r="L38" s="1"/>
-      <c r="M38" s="122"/>
+      <c r="M38" s="135"/>
       <c r="N38" s="9" t="s">
         <v>17</v>
       </c>
@@ -5352,7 +5687,7 @@
       <c r="V38" s="1"/>
     </row>
     <row r="39" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="122"/>
+      <c r="A39" s="135"/>
       <c r="B39" s="9" t="s">
         <v>18</v>
       </c>
@@ -5366,7 +5701,7 @@
       <c r="J39" s="40"/>
       <c r="K39" s="40"/>
       <c r="L39" s="1"/>
-      <c r="M39" s="122"/>
+      <c r="M39" s="135"/>
       <c r="N39" s="9" t="s">
         <v>18</v>
       </c>
@@ -5380,7 +5715,7 @@
       <c r="V39" s="1"/>
     </row>
     <row r="40" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="122"/>
+      <c r="A40" s="135"/>
       <c r="B40" s="9" t="s">
         <v>15</v>
       </c>
@@ -5397,7 +5732,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M40" s="122"/>
+      <c r="M40" s="135"/>
       <c r="N40" s="9" t="s">
         <v>15</v>
       </c>
@@ -5411,7 +5746,7 @@
       <c r="V40" s="1"/>
     </row>
     <row r="41" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="122"/>
+      <c r="A41" s="135"/>
       <c r="B41" s="9" t="s">
         <v>25</v>
       </c>
@@ -5425,7 +5760,7 @@
       <c r="J41" s="40"/>
       <c r="K41" s="40"/>
       <c r="L41" s="1"/>
-      <c r="M41" s="122"/>
+      <c r="M41" s="135"/>
       <c r="N41" s="9" t="s">
         <v>25</v>
       </c>
@@ -5439,7 +5774,7 @@
       <c r="V41" s="1"/>
     </row>
     <row r="42" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="122"/>
+      <c r="A42" s="135"/>
       <c r="B42" s="9" t="s">
         <v>19</v>
       </c>
@@ -5453,7 +5788,7 @@
       <c r="J42" s="40"/>
       <c r="K42" s="40"/>
       <c r="L42" s="1"/>
-      <c r="M42" s="122"/>
+      <c r="M42" s="135"/>
       <c r="N42" s="9" t="s">
         <v>19</v>
       </c>
@@ -5467,7 +5802,7 @@
       <c r="V42" s="1"/>
     </row>
     <row r="43" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="122"/>
+      <c r="A43" s="135"/>
       <c r="B43" s="9" t="s">
         <v>16</v>
       </c>
@@ -5484,7 +5819,7 @@
         <f t="shared" si="7"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M43" s="122"/>
+      <c r="M43" s="135"/>
       <c r="N43" s="9" t="s">
         <v>16</v>
       </c>
@@ -5498,7 +5833,7 @@
       <c r="V43" s="1"/>
     </row>
     <row r="44" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="107"/>
+      <c r="A44" s="129"/>
       <c r="B44" s="9" t="s">
         <v>26</v>
       </c>
@@ -5512,7 +5847,7 @@
       <c r="J44" s="40"/>
       <c r="K44" s="40"/>
       <c r="L44" s="1"/>
-      <c r="M44" s="107"/>
+      <c r="M44" s="129"/>
       <c r="N44" s="9" t="s">
         <v>26</v>
       </c>
@@ -5526,38 +5861,38 @@
       <c r="V44" s="1"/>
     </row>
     <row r="45" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="105" t="s">
+      <c r="A45" s="121" t="s">
         <v>20</v>
       </c>
-      <c r="B45" s="106"/>
-      <c r="C45" s="113"/>
-      <c r="D45" s="113"/>
-      <c r="E45" s="113"/>
-      <c r="F45" s="113"/>
-      <c r="G45" s="113"/>
-      <c r="H45" s="113"/>
-      <c r="I45" s="123"/>
+      <c r="B45" s="122"/>
+      <c r="C45" s="126"/>
+      <c r="D45" s="126"/>
+      <c r="E45" s="126"/>
+      <c r="F45" s="126"/>
+      <c r="G45" s="126"/>
+      <c r="H45" s="126"/>
+      <c r="I45" s="133"/>
       <c r="J45" s="40"/>
       <c r="K45" s="40"/>
       <c r="L45" s="1"/>
-      <c r="M45" s="105" t="s">
+      <c r="M45" s="121" t="s">
         <v>20</v>
       </c>
-      <c r="N45" s="106"/>
-      <c r="O45" s="113"/>
-      <c r="P45" s="113"/>
-      <c r="Q45" s="113"/>
-      <c r="R45" s="113"/>
-      <c r="S45" s="113"/>
-      <c r="T45" s="113"/>
-      <c r="U45" s="123"/>
+      <c r="N45" s="122"/>
+      <c r="O45" s="126"/>
+      <c r="P45" s="126"/>
+      <c r="Q45" s="126"/>
+      <c r="R45" s="126"/>
+      <c r="S45" s="126"/>
+      <c r="T45" s="126"/>
+      <c r="U45" s="133"/>
       <c r="V45" s="1"/>
     </row>
     <row r="46" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="105" t="s">
+      <c r="A46" s="121" t="s">
         <v>7</v>
       </c>
-      <c r="B46" s="112"/>
+      <c r="B46" s="130"/>
       <c r="C46" s="54"/>
       <c r="D46" s="55"/>
       <c r="E46" s="55"/>
@@ -5571,10 +5906,10 @@
         <f t="shared" ref="L46:L48" si="8">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C46:I46)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M46" s="105" t="s">
+      <c r="M46" s="121" t="s">
         <v>7</v>
       </c>
-      <c r="N46" s="112"/>
+      <c r="N46" s="130"/>
       <c r="O46" s="54"/>
       <c r="P46" s="55"/>
       <c r="Q46" s="55"/>
@@ -5588,10 +5923,10 @@
       </c>
     </row>
     <row r="47" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="105" t="s">
+      <c r="A47" s="121" t="s">
         <v>8</v>
       </c>
-      <c r="B47" s="112"/>
+      <c r="B47" s="130"/>
       <c r="C47" s="57"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -5605,10 +5940,10 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M47" s="105" t="s">
+      <c r="M47" s="121" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="112"/>
+      <c r="N47" s="130"/>
       <c r="O47" s="57"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
@@ -5622,10 +5957,10 @@
       </c>
     </row>
     <row r="48" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="105" t="s">
+      <c r="A48" s="121" t="s">
         <v>21</v>
       </c>
-      <c r="B48" s="112"/>
+      <c r="B48" s="130"/>
       <c r="C48" s="57"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -5639,10 +5974,10 @@
         <f t="shared" si="8"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M48" s="105" t="s">
+      <c r="M48" s="121" t="s">
         <v>21</v>
       </c>
-      <c r="N48" s="112"/>
+      <c r="N48" s="130"/>
       <c r="O48" s="57"/>
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
@@ -5656,10 +5991,10 @@
       </c>
     </row>
     <row r="49" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="105" t="s">
+      <c r="A49" s="121" t="s">
         <v>22</v>
       </c>
-      <c r="B49" s="112"/>
+      <c r="B49" s="130"/>
       <c r="C49" s="59"/>
       <c r="D49" s="60"/>
       <c r="E49" s="60"/>
@@ -5670,10 +6005,10 @@
       <c r="J49" s="45"/>
       <c r="K49" s="45"/>
       <c r="L49" s="44"/>
-      <c r="M49" s="105" t="s">
+      <c r="M49" s="121" t="s">
         <v>22</v>
       </c>
-      <c r="N49" s="112"/>
+      <c r="N49" s="130"/>
       <c r="O49" s="59"/>
       <c r="P49" s="60"/>
       <c r="Q49" s="60"/>
@@ -5684,38 +6019,38 @@
       <c r="V49" s="1"/>
     </row>
     <row r="50" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="105" t="s">
+      <c r="A50" s="121" t="s">
         <v>23</v>
       </c>
-      <c r="B50" s="106"/>
-      <c r="C50" s="113"/>
-      <c r="D50" s="113"/>
-      <c r="E50" s="113"/>
-      <c r="F50" s="113"/>
-      <c r="G50" s="113"/>
-      <c r="H50" s="113"/>
-      <c r="I50" s="123"/>
+      <c r="B50" s="122"/>
+      <c r="C50" s="126"/>
+      <c r="D50" s="126"/>
+      <c r="E50" s="126"/>
+      <c r="F50" s="126"/>
+      <c r="G50" s="126"/>
+      <c r="H50" s="126"/>
+      <c r="I50" s="133"/>
       <c r="J50" s="40"/>
       <c r="K50" s="40"/>
       <c r="L50" s="1"/>
-      <c r="M50" s="105" t="s">
+      <c r="M50" s="121" t="s">
         <v>23</v>
       </c>
-      <c r="N50" s="106"/>
-      <c r="O50" s="113"/>
-      <c r="P50" s="113"/>
-      <c r="Q50" s="113"/>
-      <c r="R50" s="113"/>
-      <c r="S50" s="113"/>
-      <c r="T50" s="113"/>
-      <c r="U50" s="123"/>
+      <c r="N50" s="122"/>
+      <c r="O50" s="126"/>
+      <c r="P50" s="126"/>
+      <c r="Q50" s="126"/>
+      <c r="R50" s="126"/>
+      <c r="S50" s="126"/>
+      <c r="T50" s="126"/>
+      <c r="U50" s="133"/>
       <c r="V50" s="1"/>
     </row>
     <row r="51" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="105" t="s">
+      <c r="A51" s="121" t="s">
         <v>7</v>
       </c>
-      <c r="B51" s="112"/>
+      <c r="B51" s="130"/>
       <c r="C51" s="54"/>
       <c r="D51" s="55"/>
       <c r="E51" s="55"/>
@@ -5729,10 +6064,10 @@
         <f t="shared" ref="L51:L53" si="9">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C51:I51)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M51" s="105" t="s">
+      <c r="M51" s="121" t="s">
         <v>7</v>
       </c>
-      <c r="N51" s="112"/>
+      <c r="N51" s="130"/>
       <c r="O51" s="54"/>
       <c r="P51" s="55"/>
       <c r="Q51" s="55"/>
@@ -5746,10 +6081,10 @@
       </c>
     </row>
     <row r="52" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="109" t="s">
+      <c r="A52" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="B52" s="111"/>
+      <c r="B52" s="125"/>
       <c r="C52" s="57"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -5763,10 +6098,10 @@
         <f t="shared" si="9"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M52" s="105" t="s">
+      <c r="M52" s="121" t="s">
         <v>8</v>
       </c>
-      <c r="N52" s="112"/>
+      <c r="N52" s="130"/>
       <c r="O52" s="57"/>
       <c r="P52" s="1"/>
       <c r="Q52" s="1"/>
@@ -5780,10 +6115,10 @@
       </c>
     </row>
     <row r="53" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="105" t="s">
+      <c r="A53" s="121" t="s">
         <v>21</v>
       </c>
-      <c r="B53" s="112"/>
+      <c r="B53" s="130"/>
       <c r="C53" s="57"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -5797,10 +6132,10 @@
         <f t="shared" si="9"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M53" s="105" t="s">
+      <c r="M53" s="121" t="s">
         <v>21</v>
       </c>
-      <c r="N53" s="112"/>
+      <c r="N53" s="130"/>
       <c r="O53" s="57"/>
       <c r="P53" s="1"/>
       <c r="Q53" s="1"/>
@@ -5814,10 +6149,10 @@
       </c>
     </row>
     <row r="54" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="105" t="s">
+      <c r="A54" s="121" t="s">
         <v>22</v>
       </c>
-      <c r="B54" s="112"/>
+      <c r="B54" s="130"/>
       <c r="C54" s="59"/>
       <c r="D54" s="60"/>
       <c r="E54" s="60"/>
@@ -5828,10 +6163,10 @@
       <c r="J54" s="40"/>
       <c r="K54" s="40"/>
       <c r="L54" s="1"/>
-      <c r="M54" s="105" t="s">
+      <c r="M54" s="121" t="s">
         <v>22</v>
       </c>
-      <c r="N54" s="112"/>
+      <c r="N54" s="130"/>
       <c r="O54" s="59"/>
       <c r="P54" s="60"/>
       <c r="Q54" s="60"/>
@@ -5842,38 +6177,38 @@
       <c r="V54" s="1"/>
     </row>
     <row r="55" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="105" t="s">
+      <c r="A55" s="121" t="s">
         <v>24</v>
       </c>
-      <c r="B55" s="106"/>
-      <c r="C55" s="113"/>
-      <c r="D55" s="113"/>
-      <c r="E55" s="113"/>
-      <c r="F55" s="113"/>
-      <c r="G55" s="113"/>
-      <c r="H55" s="113"/>
-      <c r="I55" s="123"/>
+      <c r="B55" s="122"/>
+      <c r="C55" s="126"/>
+      <c r="D55" s="126"/>
+      <c r="E55" s="126"/>
+      <c r="F55" s="126"/>
+      <c r="G55" s="126"/>
+      <c r="H55" s="126"/>
+      <c r="I55" s="133"/>
       <c r="J55" s="40"/>
       <c r="K55" s="40"/>
       <c r="L55" s="1"/>
-      <c r="M55" s="105" t="s">
+      <c r="M55" s="121" t="s">
         <v>23</v>
       </c>
-      <c r="N55" s="106"/>
-      <c r="O55" s="113"/>
-      <c r="P55" s="113"/>
-      <c r="Q55" s="113"/>
-      <c r="R55" s="113"/>
-      <c r="S55" s="113"/>
-      <c r="T55" s="113"/>
-      <c r="U55" s="123"/>
+      <c r="N55" s="122"/>
+      <c r="O55" s="126"/>
+      <c r="P55" s="126"/>
+      <c r="Q55" s="126"/>
+      <c r="R55" s="126"/>
+      <c r="S55" s="126"/>
+      <c r="T55" s="126"/>
+      <c r="U55" s="133"/>
       <c r="V55" s="1"/>
     </row>
     <row r="56" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="105" t="s">
+      <c r="A56" s="121" t="s">
         <v>7</v>
       </c>
-      <c r="B56" s="112"/>
+      <c r="B56" s="130"/>
       <c r="C56"/>
       <c r="D56"/>
       <c r="E56"/>
@@ -5887,10 +6222,10 @@
         <f t="shared" ref="L56:L58" si="11">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C56:I56)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M56" s="105" t="s">
+      <c r="M56" s="121" t="s">
         <v>7</v>
       </c>
-      <c r="N56" s="112"/>
+      <c r="N56" s="130"/>
       <c r="O56"/>
       <c r="P56"/>
       <c r="Q56"/>
@@ -5904,10 +6239,10 @@
       </c>
     </row>
     <row r="57" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="109" t="s">
+      <c r="A57" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="B57" s="111"/>
+      <c r="B57" s="125"/>
       <c r="C57"/>
       <c r="D57"/>
       <c r="E57"/>
@@ -5921,10 +6256,10 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M57" s="105" t="s">
+      <c r="M57" s="121" t="s">
         <v>8</v>
       </c>
-      <c r="N57" s="112"/>
+      <c r="N57" s="130"/>
       <c r="O57"/>
       <c r="P57"/>
       <c r="Q57"/>
@@ -5938,10 +6273,10 @@
       </c>
     </row>
     <row r="58" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="105" t="s">
+      <c r="A58" s="121" t="s">
         <v>21</v>
       </c>
-      <c r="B58" s="112"/>
+      <c r="B58" s="130"/>
       <c r="C58"/>
       <c r="D58"/>
       <c r="E58"/>
@@ -5955,10 +6290,10 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M58" s="105" t="s">
+      <c r="M58" s="121" t="s">
         <v>21</v>
       </c>
-      <c r="N58" s="112"/>
+      <c r="N58" s="130"/>
       <c r="O58"/>
       <c r="P58"/>
       <c r="Q58"/>
@@ -5972,31 +6307,31 @@
       </c>
     </row>
     <row r="59" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="105" t="s">
+      <c r="A59" s="121" t="s">
         <v>22</v>
       </c>
-      <c r="B59" s="112"/>
-      <c r="C59" s="82"/>
-      <c r="D59" s="83"/>
-      <c r="E59" s="83"/>
-      <c r="F59" s="83"/>
-      <c r="G59" s="83"/>
-      <c r="H59" s="83"/>
-      <c r="I59" s="84"/>
+      <c r="B59" s="130"/>
+      <c r="C59" s="74"/>
+      <c r="D59" s="75"/>
+      <c r="E59" s="75"/>
+      <c r="F59" s="75"/>
+      <c r="G59" s="75"/>
+      <c r="H59" s="75"/>
+      <c r="I59" s="76"/>
       <c r="J59" s="40"/>
       <c r="K59" s="40"/>
       <c r="L59" s="1"/>
-      <c r="M59" s="105" t="s">
+      <c r="M59" s="121" t="s">
         <v>22</v>
       </c>
-      <c r="N59" s="112"/>
-      <c r="O59" s="82"/>
-      <c r="P59" s="83"/>
-      <c r="Q59" s="83"/>
-      <c r="R59" s="83"/>
-      <c r="S59" s="83"/>
-      <c r="T59" s="83"/>
-      <c r="U59" s="84"/>
+      <c r="N59" s="130"/>
+      <c r="O59" s="74"/>
+      <c r="P59" s="75"/>
+      <c r="Q59" s="75"/>
+      <c r="R59" s="75"/>
+      <c r="S59" s="75"/>
+      <c r="T59" s="75"/>
+      <c r="U59" s="76"/>
       <c r="V59" s="1"/>
     </row>
     <row r="60" spans="1:22" ht="15" x14ac:dyDescent="0.2">
@@ -6015,6 +6350,70 @@
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="M59:N59"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="M56:N56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="M57:N57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="M58:N58"/>
+    <mergeCell ref="A6:A14"/>
+    <mergeCell ref="M6:M14"/>
+    <mergeCell ref="A36:A44"/>
+    <mergeCell ref="M36:M44"/>
+    <mergeCell ref="A55:I55"/>
+    <mergeCell ref="M55:U55"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="M25:U25"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="M53:N53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="M54:N54"/>
+    <mergeCell ref="A50:I50"/>
+    <mergeCell ref="M50:U50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="M51:N51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="M52:N52"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="M15:U15"/>
+    <mergeCell ref="M45:U45"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="M35:U35"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="M48:N48"/>
+    <mergeCell ref="M49:N49"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="M46:N46"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="A32:B32"/>
@@ -6031,70 +6430,6 @@
     <mergeCell ref="A15:I15"/>
     <mergeCell ref="A25:I25"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="M48:N48"/>
-    <mergeCell ref="M49:N49"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="M46:N46"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A45:I45"/>
-    <mergeCell ref="M15:U15"/>
-    <mergeCell ref="M45:U45"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="M35:U35"/>
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="M54:N54"/>
-    <mergeCell ref="A50:I50"/>
-    <mergeCell ref="M50:U50"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="M51:N51"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="M52:N52"/>
-    <mergeCell ref="A6:A14"/>
-    <mergeCell ref="M6:M14"/>
-    <mergeCell ref="A36:A44"/>
-    <mergeCell ref="M36:M44"/>
-    <mergeCell ref="A55:I55"/>
-    <mergeCell ref="M55:U55"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="M25:U25"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="M53:N53"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="M59:N59"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="M56:N56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="M57:N57"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="M58:N58"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C2:I4 C6:I14 C16:I19 C21:I24 C26:I29">
@@ -6548,29 +6883,31 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A38A25A9-7BAB-4662-AC2A-B7F2DABCCE29}">
-  <dimension ref="B2:U25"/>
+  <dimension ref="B2:U21"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="7" max="7" width="17.5" customWidth="1"/>
+    <col min="14" max="14" width="17.5" customWidth="1"/>
+    <col min="21" max="21" width="17.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="B3" s="127" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="133"/>
-      <c r="D3" s="130" t="s">
+      <c r="B3" s="101" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="105"/>
+      <c r="D3" s="107" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="131"/>
-      <c r="F3" s="131"/>
-      <c r="G3" s="132"/>
+      <c r="E3" s="108"/>
+      <c r="F3" s="108"/>
+      <c r="G3" s="109"/>
     </row>
     <row r="4" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="129"/>
-      <c r="C4" s="134"/>
-      <c r="D4" s="137" t="s">
+      <c r="B4" s="103"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="99" t="s">
         <v>27</v>
       </c>
       <c r="E4" s="136" t="s">
@@ -6579,612 +6916,914 @@
       <c r="F4" s="136" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="71" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="80" t="s">
+      <c r="G4" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="25"/>
+      <c r="L4" s="25"/>
+    </row>
+    <row r="5" spans="2:14" ht="15" x14ac:dyDescent="0.25">
+      <c r="B5" s="101" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="97" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="68">
+        <v>83.95</v>
+      </c>
+      <c r="E5" s="168">
+        <v>84.26</v>
+      </c>
+      <c r="F5" s="168">
+        <v>84.42</v>
+      </c>
+      <c r="G5" s="169">
+        <v>83.98</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14" ht="15" x14ac:dyDescent="0.25">
+      <c r="B6" s="102"/>
+      <c r="C6" s="136" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="69">
+        <v>83.86</v>
+      </c>
+      <c r="E6" s="137">
+        <v>83.93</v>
+      </c>
+      <c r="F6" s="137">
+        <v>83.06</v>
+      </c>
+      <c r="G6" s="138">
+        <v>83.47</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="103"/>
+      <c r="C7" s="71" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="73">
+        <v>82.35</v>
+      </c>
+      <c r="E7" s="72">
+        <v>80.72</v>
+      </c>
+      <c r="F7" s="72">
+        <v>82.35</v>
+      </c>
+      <c r="G7" s="139">
+        <v>79.91</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" ht="15" x14ac:dyDescent="0.25">
+      <c r="B8" s="100"/>
+      <c r="C8" s="98"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+    </row>
+    <row r="9" spans="2:14" ht="15" x14ac:dyDescent="0.25">
+      <c r="B9" s="100"/>
+      <c r="C9" s="98"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+    </row>
+    <row r="10" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="100"/>
+      <c r="C10" s="98"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+    </row>
+    <row r="11" spans="2:14" ht="15" x14ac:dyDescent="0.25">
+      <c r="B11" s="104" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="105"/>
+      <c r="D11" s="107" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="108"/>
+      <c r="F11" s="108"/>
+      <c r="G11" s="109"/>
+      <c r="I11" s="104" t="s">
+        <v>38</v>
+      </c>
+      <c r="J11" s="105"/>
+      <c r="K11" s="107" t="s">
+        <v>31</v>
+      </c>
+      <c r="L11" s="108"/>
+      <c r="M11" s="108"/>
+      <c r="N11" s="109"/>
+    </row>
+    <row r="12" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="103"/>
+      <c r="C12" s="106"/>
+      <c r="D12" s="99" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="136" t="s">
+        <v>28</v>
+      </c>
+      <c r="F12" s="136" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="I12" s="103"/>
+      <c r="J12" s="106"/>
+      <c r="K12" s="99" t="s">
+        <v>27</v>
+      </c>
+      <c r="L12" s="136" t="s">
+        <v>28</v>
+      </c>
+      <c r="M12" s="136" t="s">
+        <v>29</v>
+      </c>
+      <c r="N12" s="70" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" ht="15" x14ac:dyDescent="0.25">
+      <c r="B13" s="101" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="97" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="68">
+        <v>93.38</v>
+      </c>
+      <c r="E13" s="168">
+        <v>93.36</v>
+      </c>
+      <c r="F13" s="168">
+        <v>92.74</v>
+      </c>
+      <c r="G13" s="169">
+        <v>92.97</v>
+      </c>
+      <c r="I13" s="101" t="s">
+        <v>30</v>
+      </c>
+      <c r="J13" s="97" t="s">
+        <v>27</v>
+      </c>
+      <c r="K13" s="68">
+        <v>92.79</v>
+      </c>
+      <c r="L13" s="168">
+        <v>92.79</v>
+      </c>
+      <c r="M13" s="168">
+        <v>92.33</v>
+      </c>
+      <c r="N13" s="169">
+        <v>92.66</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" ht="15" x14ac:dyDescent="0.25">
+      <c r="B14" s="102"/>
+      <c r="C14" s="136" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="69">
+        <v>93.58</v>
+      </c>
+      <c r="E14" s="137">
+        <v>93.72</v>
+      </c>
+      <c r="F14" s="137">
+        <v>91.3</v>
+      </c>
+      <c r="G14" s="138">
+        <v>93.55</v>
+      </c>
+      <c r="I14" s="102"/>
+      <c r="J14" s="136" t="s">
+        <v>28</v>
+      </c>
+      <c r="K14" s="69">
+        <v>92.72</v>
+      </c>
+      <c r="L14" s="137">
+        <v>92.42</v>
+      </c>
+      <c r="M14" s="137">
+        <v>90.82</v>
+      </c>
+      <c r="N14" s="138">
+        <v>92.28</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="103"/>
+      <c r="C15" s="71" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="73">
+        <v>92.55</v>
+      </c>
+      <c r="E15" s="72">
+        <v>89.15</v>
+      </c>
+      <c r="F15" s="72">
+        <v>88.35</v>
+      </c>
+      <c r="G15" s="139">
+        <v>88.64</v>
+      </c>
+      <c r="I15" s="103"/>
+      <c r="J15" s="71" t="s">
+        <v>29</v>
+      </c>
+      <c r="K15" s="73">
+        <v>90.33</v>
+      </c>
+      <c r="L15" s="72">
+        <v>88.34</v>
+      </c>
+      <c r="M15" s="72">
+        <v>87.26</v>
+      </c>
+      <c r="N15" s="139">
+        <v>87.59</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="17" spans="2:21" ht="15" x14ac:dyDescent="0.25">
+      <c r="B17" s="104" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="105"/>
+      <c r="D17" s="107" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="108"/>
+      <c r="F17" s="108"/>
+      <c r="G17" s="109"/>
+      <c r="I17" s="104" t="s">
+        <v>35</v>
+      </c>
+      <c r="J17" s="105"/>
+      <c r="K17" s="107" t="s">
+        <v>31</v>
+      </c>
+      <c r="L17" s="108"/>
+      <c r="M17" s="108"/>
+      <c r="N17" s="109"/>
+      <c r="P17" s="104" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="81" t="s">
+      <c r="Q17" s="105"/>
+      <c r="R17" s="107" t="s">
+        <v>31</v>
+      </c>
+      <c r="S17" s="108"/>
+      <c r="T17" s="108"/>
+      <c r="U17" s="109"/>
+    </row>
+    <row r="18" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="103"/>
+      <c r="C18" s="106"/>
+      <c r="D18" s="99" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="75"/>
-      <c r="E5" s="76">
-        <v>84.26</v>
-      </c>
-      <c r="F5" s="76">
-        <v>84.42</v>
-      </c>
-      <c r="G5" s="77"/>
-    </row>
-    <row r="6" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="25"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="25" t="s">
+      <c r="E18" s="136" t="s">
+        <v>28</v>
+      </c>
+      <c r="F18" s="136" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18" s="70" t="s">
         <v>32</v>
       </c>
-      <c r="G6" s="25"/>
-    </row>
-    <row r="7" spans="2:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="B7" s="127" t="s">
-        <v>35</v>
-      </c>
-      <c r="C7" s="133"/>
-      <c r="D7" s="130" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="131"/>
-      <c r="F7" s="131"/>
-      <c r="G7" s="132"/>
-    </row>
-    <row r="8" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="129"/>
-      <c r="C8" s="134"/>
-      <c r="D8" s="74" t="s">
+      <c r="I18" s="103"/>
+      <c r="J18" s="106"/>
+      <c r="K18" s="99" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="72" t="s">
+      <c r="L18" s="136" t="s">
         <v>28</v>
       </c>
-      <c r="F8" s="72" t="s">
+      <c r="M18" s="136" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="71" t="s">
-        <v>33</v>
-      </c>
-      <c r="K8" s="135"/>
-      <c r="L8" s="135"/>
-    </row>
-    <row r="9" spans="2:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="B9" s="127" t="s">
+      <c r="N18" s="70" t="s">
+        <v>32</v>
+      </c>
+      <c r="P18" s="103"/>
+      <c r="Q18" s="106"/>
+      <c r="R18" s="99" t="s">
+        <v>27</v>
+      </c>
+      <c r="S18" s="136" t="s">
+        <v>28</v>
+      </c>
+      <c r="T18" s="136" t="s">
+        <v>29</v>
+      </c>
+      <c r="U18" s="70" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19" spans="2:21" ht="15" x14ac:dyDescent="0.25">
+      <c r="B19" s="101" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="69" t="s">
+      <c r="C19" s="97" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="68">
-        <v>83.95</v>
-      </c>
-      <c r="E9" s="135">
-        <v>84.26</v>
-      </c>
-      <c r="F9" s="135">
-        <v>84.42</v>
-      </c>
-      <c r="G9" s="138">
-        <v>83.98</v>
-      </c>
-    </row>
-    <row r="10" spans="2:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="B10" s="128"/>
-      <c r="C10" s="71" t="s">
+      <c r="D19" s="68">
+        <v>91.1</v>
+      </c>
+      <c r="E19" s="168">
+        <v>91.28</v>
+      </c>
+      <c r="F19" s="168">
+        <v>91.16</v>
+      </c>
+      <c r="G19" s="169">
+        <v>90.61</v>
+      </c>
+      <c r="I19" s="101" t="s">
+        <v>30</v>
+      </c>
+      <c r="J19" s="97" t="s">
+        <v>27</v>
+      </c>
+      <c r="K19" s="68">
+        <v>74.37</v>
+      </c>
+      <c r="L19" s="168">
+        <v>77.239999999999995</v>
+      </c>
+      <c r="M19" s="168">
+        <v>82.31</v>
+      </c>
+      <c r="N19" s="169">
+        <v>76.89</v>
+      </c>
+      <c r="P19" s="101" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q19" s="97" t="s">
+        <v>27</v>
+      </c>
+      <c r="R19" s="68">
+        <v>56.35</v>
+      </c>
+      <c r="S19" s="168">
+        <v>56.64</v>
+      </c>
+      <c r="T19" s="168">
+        <v>57.69</v>
+      </c>
+      <c r="U19" s="169">
+        <v>57.43</v>
+      </c>
+    </row>
+    <row r="20" spans="2:21" ht="15" x14ac:dyDescent="0.25">
+      <c r="B20" s="102"/>
+      <c r="C20" s="136" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="70">
-        <v>83.86</v>
-      </c>
-      <c r="E10" s="25">
-        <v>83.93</v>
-      </c>
-      <c r="F10" s="25"/>
-      <c r="G10" s="139">
-        <v>83.47</v>
-      </c>
-    </row>
-    <row r="11" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="129"/>
-      <c r="C11" s="79" t="s">
+      <c r="D20" s="69">
+        <v>90.92</v>
+      </c>
+      <c r="E20" s="137">
+        <v>90.69</v>
+      </c>
+      <c r="F20" s="137">
+        <v>89.93</v>
+      </c>
+      <c r="G20" s="138">
+        <v>90.5</v>
+      </c>
+      <c r="I20" s="102"/>
+      <c r="J20" s="136" t="s">
+        <v>28</v>
+      </c>
+      <c r="K20" s="69">
+        <v>73.430000000000007</v>
+      </c>
+      <c r="L20" s="137">
+        <v>75.78</v>
+      </c>
+      <c r="M20" s="137">
+        <v>80.989999999999995</v>
+      </c>
+      <c r="N20" s="138">
+        <v>72.8</v>
+      </c>
+      <c r="P20" s="102"/>
+      <c r="Q20" s="136" t="s">
+        <v>28</v>
+      </c>
+      <c r="R20" s="69">
+        <v>56.56</v>
+      </c>
+      <c r="S20" s="137">
+        <v>55.76</v>
+      </c>
+      <c r="T20" s="137">
+        <v>55.07</v>
+      </c>
+      <c r="U20" s="138">
+        <v>54.06</v>
+      </c>
+    </row>
+    <row r="21" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="103"/>
+      <c r="C21" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="78">
-        <v>82.35</v>
-      </c>
-      <c r="E11" s="73"/>
-      <c r="F11" s="73">
-        <v>82.35</v>
-      </c>
-      <c r="G11" s="140">
-        <v>79.91</v>
-      </c>
-    </row>
-    <row r="12" spans="2:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="B12" s="147"/>
-      <c r="C12" s="136"/>
-      <c r="D12" s="135"/>
-      <c r="E12" s="135"/>
-      <c r="F12" s="135"/>
-      <c r="G12" s="135"/>
-    </row>
-    <row r="13" spans="2:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="B13" s="147"/>
-      <c r="C13" s="136"/>
-      <c r="D13" s="135"/>
-      <c r="E13" s="135"/>
-      <c r="F13" s="135"/>
-      <c r="G13" s="135"/>
-    </row>
-    <row r="14" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="147"/>
-      <c r="C14" s="136"/>
-      <c r="D14" s="135"/>
-      <c r="E14" s="135"/>
-      <c r="F14" s="135"/>
-      <c r="G14" s="135"/>
-    </row>
-    <row r="15" spans="2:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="B15" s="146" t="s">
-        <v>39</v>
-      </c>
-      <c r="C15" s="133"/>
-      <c r="D15" s="130" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="131"/>
-      <c r="F15" s="131"/>
-      <c r="G15" s="132"/>
-      <c r="I15" s="146" t="s">
-        <v>40</v>
-      </c>
-      <c r="J15" s="133"/>
-      <c r="K15" s="130" t="s">
-        <v>31</v>
-      </c>
-      <c r="L15" s="131"/>
-      <c r="M15" s="131"/>
-      <c r="N15" s="132"/>
-    </row>
-    <row r="16" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="129"/>
-      <c r="C16" s="134"/>
-      <c r="D16" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" s="72" t="s">
-        <v>28</v>
-      </c>
-      <c r="F16" s="72" t="s">
+      <c r="D21" s="73">
+        <v>89.67</v>
+      </c>
+      <c r="E21" s="72">
+        <v>87.91</v>
+      </c>
+      <c r="F21" s="72">
+        <v>87.1</v>
+      </c>
+      <c r="G21" s="139">
+        <v>87.1</v>
+      </c>
+      <c r="I21" s="103"/>
+      <c r="J21" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="71" t="s">
-        <v>33</v>
-      </c>
-      <c r="I16" s="129"/>
-      <c r="J16" s="134"/>
-      <c r="K16" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="L16" s="72" t="s">
-        <v>28</v>
-      </c>
-      <c r="M16" s="72" t="s">
+      <c r="K21" s="73">
+        <v>78.680000000000007</v>
+      </c>
+      <c r="L21" s="72">
+        <v>77.040000000000006</v>
+      </c>
+      <c r="M21" s="72">
+        <v>75.41</v>
+      </c>
+      <c r="N21" s="139">
+        <v>74.819999999999993</v>
+      </c>
+      <c r="P21" s="103"/>
+      <c r="Q21" s="71" t="s">
         <v>29</v>
       </c>
-      <c r="N16" s="71" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="2:21" ht="15" x14ac:dyDescent="0.25">
-      <c r="B17" s="127" t="s">
-        <v>30</v>
-      </c>
-      <c r="C17" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" s="68"/>
-      <c r="E17" s="135"/>
-      <c r="F17" s="135"/>
-      <c r="G17" s="138">
-        <v>92.97</v>
-      </c>
-      <c r="I17" s="127" t="s">
-        <v>30</v>
-      </c>
-      <c r="J17" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="K17" s="68"/>
-      <c r="L17" s="135"/>
-      <c r="M17" s="135"/>
-      <c r="N17" s="138"/>
-    </row>
-    <row r="18" spans="2:21" ht="15" x14ac:dyDescent="0.25">
-      <c r="B18" s="128"/>
-      <c r="C18" s="71" t="s">
-        <v>28</v>
-      </c>
-      <c r="D18" s="70"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="25"/>
-      <c r="G18" s="139">
-        <v>93.55</v>
-      </c>
-      <c r="I18" s="128"/>
-      <c r="J18" s="71" t="s">
-        <v>28</v>
-      </c>
-      <c r="K18" s="70"/>
-      <c r="L18" s="25"/>
-      <c r="M18" s="25"/>
-      <c r="N18" s="139"/>
-    </row>
-    <row r="19" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="129"/>
-      <c r="C19" s="79" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" s="78"/>
-      <c r="E19" s="73"/>
-      <c r="F19" s="73"/>
-      <c r="G19" s="140">
-        <v>88.64</v>
-      </c>
-      <c r="I19" s="129"/>
-      <c r="J19" s="79" t="s">
-        <v>29</v>
-      </c>
-      <c r="K19" s="78"/>
-      <c r="L19" s="73"/>
-      <c r="M19" s="73"/>
-      <c r="N19" s="140"/>
-    </row>
-    <row r="20" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="21" spans="2:21" ht="15" x14ac:dyDescent="0.25">
-      <c r="B21" s="146" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" s="133"/>
-      <c r="D21" s="130" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="131"/>
-      <c r="F21" s="131"/>
-      <c r="G21" s="132"/>
-      <c r="I21" s="146" t="s">
-        <v>37</v>
-      </c>
-      <c r="J21" s="133"/>
-      <c r="K21" s="130" t="s">
-        <v>31</v>
-      </c>
-      <c r="L21" s="131"/>
-      <c r="M21" s="131"/>
-      <c r="N21" s="132"/>
-      <c r="P21" s="146" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q21" s="133"/>
-      <c r="R21" s="130" t="s">
-        <v>31</v>
-      </c>
-      <c r="S21" s="131"/>
-      <c r="T21" s="131"/>
-      <c r="U21" s="132"/>
-    </row>
-    <row r="22" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="129"/>
-      <c r="C22" s="134"/>
-      <c r="D22" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" s="72" t="s">
-        <v>28</v>
-      </c>
-      <c r="F22" s="72" t="s">
-        <v>29</v>
-      </c>
-      <c r="G22" s="71" t="s">
-        <v>33</v>
-      </c>
-      <c r="I22" s="129"/>
-      <c r="J22" s="134"/>
-      <c r="K22" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="L22" s="72" t="s">
-        <v>28</v>
-      </c>
-      <c r="M22" s="72" t="s">
-        <v>29</v>
-      </c>
-      <c r="N22" s="71" t="s">
-        <v>33</v>
-      </c>
-      <c r="P22" s="129"/>
-      <c r="Q22" s="134"/>
-      <c r="R22" s="74" t="s">
-        <v>27</v>
-      </c>
-      <c r="S22" s="72" t="s">
-        <v>28</v>
-      </c>
-      <c r="T22" s="72" t="s">
-        <v>29</v>
-      </c>
-      <c r="U22" s="71" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="2:21" ht="15" x14ac:dyDescent="0.25">
-      <c r="B23" s="127" t="s">
-        <v>30</v>
-      </c>
-      <c r="C23" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" s="68">
-        <v>91.1</v>
-      </c>
-      <c r="E23" s="135">
-        <v>91.28</v>
-      </c>
-      <c r="F23" s="135">
-        <v>91.16</v>
-      </c>
-      <c r="G23" s="138">
-        <v>90.61</v>
-      </c>
-      <c r="I23" s="127" t="s">
-        <v>30</v>
-      </c>
-      <c r="J23" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="K23" s="68">
-        <v>74.37</v>
-      </c>
-      <c r="L23" s="135">
-        <v>77.239999999999995</v>
-      </c>
-      <c r="M23" s="135">
-        <v>82.31</v>
-      </c>
-      <c r="N23" s="138">
-        <v>76.89</v>
-      </c>
-      <c r="P23" s="127" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q23" s="69" t="s">
-        <v>27</v>
-      </c>
-      <c r="R23" s="68">
-        <v>56.35</v>
-      </c>
-      <c r="S23" s="135">
-        <v>56.64</v>
-      </c>
-      <c r="T23" s="135">
-        <v>57.69</v>
-      </c>
-      <c r="U23" s="138">
-        <v>57.43</v>
-      </c>
-    </row>
-    <row r="24" spans="2:21" ht="15" x14ac:dyDescent="0.25">
-      <c r="B24" s="128"/>
-      <c r="C24" s="71" t="s">
-        <v>28</v>
-      </c>
-      <c r="D24" s="70">
-        <v>90.92</v>
-      </c>
-      <c r="E24" s="25">
-        <v>90.69</v>
-      </c>
-      <c r="F24" s="25">
-        <v>89.93</v>
-      </c>
-      <c r="G24" s="139">
-        <v>90.5</v>
-      </c>
-      <c r="I24" s="128"/>
-      <c r="J24" s="71" t="s">
-        <v>28</v>
-      </c>
-      <c r="K24" s="70">
-        <v>73.430000000000007</v>
-      </c>
-      <c r="L24" s="25">
-        <v>75.78</v>
-      </c>
-      <c r="M24" s="25">
-        <v>80.989999999999995</v>
-      </c>
-      <c r="N24" s="139">
-        <v>72.8</v>
-      </c>
-      <c r="P24" s="128"/>
-      <c r="Q24" s="71" t="s">
-        <v>28</v>
-      </c>
-      <c r="R24" s="70">
-        <v>56.56</v>
-      </c>
-      <c r="S24" s="25">
-        <v>55.76</v>
-      </c>
-      <c r="T24" s="25">
-        <v>55.07</v>
-      </c>
-      <c r="U24" s="139">
-        <v>54.06</v>
-      </c>
-    </row>
-    <row r="25" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="129"/>
-      <c r="C25" s="79" t="s">
-        <v>29</v>
-      </c>
-      <c r="D25" s="78">
-        <v>89.67</v>
-      </c>
-      <c r="E25" s="73">
-        <v>87.91</v>
-      </c>
-      <c r="F25" s="73">
-        <v>87.1</v>
-      </c>
-      <c r="G25" s="140">
-        <v>87.1</v>
-      </c>
-      <c r="I25" s="129"/>
-      <c r="J25" s="79" t="s">
-        <v>29</v>
-      </c>
-      <c r="K25" s="78">
-        <v>78.680000000000007</v>
-      </c>
-      <c r="L25" s="73">
-        <v>77.040000000000006</v>
-      </c>
-      <c r="M25" s="73">
-        <v>75.41</v>
-      </c>
-      <c r="N25" s="140">
-        <v>74.819999999999993</v>
-      </c>
-      <c r="P25" s="129"/>
-      <c r="Q25" s="79" t="s">
-        <v>29</v>
-      </c>
-      <c r="R25" s="78">
+      <c r="R21" s="73">
         <v>53.09</v>
       </c>
-      <c r="S25" s="73">
+      <c r="S21" s="72">
         <v>51.47</v>
       </c>
-      <c r="T25" s="73">
+      <c r="T21" s="72">
         <v>50.41</v>
       </c>
-      <c r="U25" s="140">
+      <c r="U21" s="139">
         <v>50.06</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="20">
-    <mergeCell ref="P23:P25"/>
-    <mergeCell ref="I21:J22"/>
-    <mergeCell ref="K21:N21"/>
-    <mergeCell ref="I23:I25"/>
-    <mergeCell ref="B21:C22"/>
-    <mergeCell ref="D21:G21"/>
-    <mergeCell ref="B23:B25"/>
-    <mergeCell ref="P21:Q22"/>
-    <mergeCell ref="R21:U21"/>
-    <mergeCell ref="B15:C16"/>
-    <mergeCell ref="D15:G15"/>
-    <mergeCell ref="I15:J16"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="I17:I19"/>
-    <mergeCell ref="B9:B11"/>
-    <mergeCell ref="D7:G7"/>
+  <mergeCells count="18">
+    <mergeCell ref="B5:B7"/>
     <mergeCell ref="D3:G3"/>
     <mergeCell ref="B3:C4"/>
-    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="R17:U17"/>
+    <mergeCell ref="B11:C12"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="I11:J12"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="I13:I15"/>
+    <mergeCell ref="P19:P21"/>
+    <mergeCell ref="I17:J18"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="I19:I21"/>
+    <mergeCell ref="B17:C18"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="P17:Q18"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="D5:G5">
+  <conditionalFormatting sqref="D6:F10 D5">
+    <cfRule type="colorScale" priority="45">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D14:F15 D13">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D20:F21 D19">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8:G10 D5:F7">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13:G15">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D19:G21">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:F5">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13:F13">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E19:F19">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G8:G10">
+    <cfRule type="colorScale" priority="37">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G13">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G14">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G15">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G19">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G20">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G21">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K4:L4">
+    <cfRule type="colorScale" priority="41">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K14:M15 K13">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K20:M21 K19">
+    <cfRule type="colorScale" priority="28">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K13:N15">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K19:N21">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L13:M13">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L19:M19">
+    <cfRule type="colorScale" priority="27">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N13">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N14">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N15">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N19">
+    <cfRule type="colorScale" priority="26">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N20">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N21">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R20:T21 R19">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R19:U21">
+    <cfRule type="colorScale" priority="29">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S19:T19">
+    <cfRule type="colorScale" priority="33">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U19">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U20">
     <cfRule type="colorScale" priority="31">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
         <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FF5A8AC6"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D10:F14 D9">
-    <cfRule type="colorScale" priority="41">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K8:L8">
-    <cfRule type="colorScale" priority="37">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9:F9">
-    <cfRule type="colorScale" priority="36">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G9">
-    <cfRule type="colorScale" priority="35">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G10">
-    <cfRule type="colorScale" priority="34">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G11:G14">
-    <cfRule type="colorScale" priority="33">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D9:G14">
-    <cfRule type="colorScale" priority="32">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R24:T25 R23">
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U21">
     <cfRule type="colorScale" priority="30">
       <colorScale>
         <cfvo type="min"/>
@@ -7196,319 +7835,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S23:T23">
-    <cfRule type="colorScale" priority="29">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U23">
-    <cfRule type="colorScale" priority="28">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U24">
-    <cfRule type="colorScale" priority="27">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U25">
-    <cfRule type="colorScale" priority="26">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R23:U25">
-    <cfRule type="colorScale" priority="25">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K24:M25 K23">
-    <cfRule type="colorScale" priority="24">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L23:M23">
-    <cfRule type="colorScale" priority="23">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N23">
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N24">
-    <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N25">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K23:N25">
-    <cfRule type="colorScale" priority="19">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D24:F25 D23">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E23:F23">
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G23">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G24">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G25">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D23:G25">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K18:M19 K17">
-    <cfRule type="colorScale" priority="12">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L17:M17">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N17">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N18">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N19">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K17:N19">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D18:F19 D17">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E17:F17">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G17">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G18">
+  <conditionalFormatting sqref="D5:F7">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -7520,7 +7847,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G19">
+  <conditionalFormatting sqref="D13:G15 D19:G21 K13:N15 K19:N21 R19:U21">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -7532,7 +7859,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D17:G19">
+  <conditionalFormatting sqref="D5:G7">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -7546,4 +7873,1336 @@
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA1D8921-C075-4AB7-9807-2BEBE054D729}">
+  <dimension ref="A2:V22"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
+    <col min="8" max="8" width="3.75" customWidth="1"/>
+    <col min="14" max="14" width="17.5" customWidth="1"/>
+    <col min="15" max="15" width="3.75" customWidth="1"/>
+    <col min="21" max="21" width="17.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="140"/>
+      <c r="B2" s="140"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="140"/>
+      <c r="E2" s="140"/>
+      <c r="F2" s="140"/>
+      <c r="G2" s="140"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="140"/>
+      <c r="J2" s="140"/>
+      <c r="K2" s="140"/>
+      <c r="L2" s="140"/>
+      <c r="M2" s="140"/>
+      <c r="N2" s="140"/>
+      <c r="O2" s="140"/>
+      <c r="P2" s="140"/>
+      <c r="Q2" s="140"/>
+      <c r="R2" s="140"/>
+      <c r="S2" s="140"/>
+      <c r="T2" s="140"/>
+      <c r="U2" s="140"/>
+      <c r="V2" s="140"/>
+    </row>
+    <row r="3" spans="1:22" ht="15" x14ac:dyDescent="0.25">
+      <c r="A3" s="140"/>
+      <c r="B3" s="141" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="142"/>
+      <c r="D3" s="143" t="s">
+        <v>31</v>
+      </c>
+      <c r="E3" s="144"/>
+      <c r="F3" s="144"/>
+      <c r="G3" s="145"/>
+      <c r="H3" s="140"/>
+      <c r="I3" s="140"/>
+      <c r="J3" s="140"/>
+      <c r="K3" s="140"/>
+      <c r="L3" s="140"/>
+      <c r="M3" s="140"/>
+      <c r="N3" s="140"/>
+      <c r="O3" s="140"/>
+      <c r="P3" s="140"/>
+      <c r="Q3" s="140"/>
+      <c r="R3" s="140"/>
+      <c r="S3" s="140"/>
+      <c r="T3" s="140"/>
+      <c r="U3" s="140"/>
+      <c r="V3" s="140"/>
+    </row>
+    <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="140"/>
+      <c r="B4" s="146"/>
+      <c r="C4" s="147"/>
+      <c r="D4" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="149" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="150" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="151" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="140"/>
+      <c r="I4" s="140"/>
+      <c r="J4" s="140"/>
+      <c r="K4" s="152"/>
+      <c r="L4" s="152"/>
+      <c r="M4" s="140"/>
+      <c r="N4" s="140"/>
+      <c r="O4" s="140"/>
+      <c r="P4" s="140"/>
+      <c r="Q4" s="140"/>
+      <c r="R4" s="140"/>
+      <c r="S4" s="140"/>
+      <c r="T4" s="140"/>
+      <c r="U4" s="140"/>
+      <c r="V4" s="140"/>
+    </row>
+    <row r="5" spans="1:22" ht="15" x14ac:dyDescent="0.25">
+      <c r="A5" s="140"/>
+      <c r="B5" s="141" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="154">
+        <v>83.98</v>
+      </c>
+      <c r="E5" s="155">
+        <v>83.95</v>
+      </c>
+      <c r="F5" s="156">
+        <v>84.26</v>
+      </c>
+      <c r="G5" s="157">
+        <v>84.42</v>
+      </c>
+      <c r="H5" s="140"/>
+      <c r="I5" s="140"/>
+      <c r="J5" s="140"/>
+      <c r="K5" s="140"/>
+      <c r="L5" s="140"/>
+      <c r="M5" s="140"/>
+      <c r="N5" s="140"/>
+      <c r="O5" s="140"/>
+      <c r="P5" s="140"/>
+      <c r="Q5" s="140"/>
+      <c r="R5" s="140"/>
+      <c r="S5" s="140"/>
+      <c r="T5" s="140"/>
+      <c r="U5" s="140"/>
+      <c r="V5" s="140"/>
+    </row>
+    <row r="6" spans="1:22" ht="15" x14ac:dyDescent="0.25">
+      <c r="A6" s="140"/>
+      <c r="B6" s="158"/>
+      <c r="C6" s="148" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="159">
+        <v>83.47</v>
+      </c>
+      <c r="E6" s="160">
+        <v>83.86</v>
+      </c>
+      <c r="F6" s="156">
+        <v>83.93</v>
+      </c>
+      <c r="G6" s="157">
+        <v>83.06</v>
+      </c>
+      <c r="H6" s="140"/>
+      <c r="I6" s="140"/>
+      <c r="J6" s="140"/>
+      <c r="K6" s="140"/>
+      <c r="L6" s="140"/>
+      <c r="M6" s="140"/>
+      <c r="N6" s="140"/>
+      <c r="O6" s="140"/>
+      <c r="P6" s="140"/>
+      <c r="Q6" s="140"/>
+      <c r="R6" s="140"/>
+      <c r="S6" s="140"/>
+      <c r="T6" s="140"/>
+      <c r="U6" s="140"/>
+      <c r="V6" s="140"/>
+    </row>
+    <row r="7" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="140"/>
+      <c r="B7" s="146"/>
+      <c r="C7" s="151" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="161">
+        <v>79.91</v>
+      </c>
+      <c r="E7" s="162">
+        <v>82.35</v>
+      </c>
+      <c r="F7" s="163">
+        <v>80.72</v>
+      </c>
+      <c r="G7" s="164">
+        <v>82.35</v>
+      </c>
+      <c r="H7" s="140"/>
+      <c r="I7" s="140"/>
+      <c r="J7" s="140"/>
+      <c r="K7" s="140"/>
+      <c r="L7" s="140"/>
+      <c r="M7" s="140"/>
+      <c r="N7" s="140"/>
+      <c r="O7" s="140"/>
+      <c r="P7" s="140"/>
+      <c r="Q7" s="140"/>
+      <c r="R7" s="140"/>
+      <c r="S7" s="140"/>
+      <c r="T7" s="140"/>
+      <c r="U7" s="140"/>
+      <c r="V7" s="140"/>
+    </row>
+    <row r="8" spans="1:22" ht="15" x14ac:dyDescent="0.25">
+      <c r="A8" s="140"/>
+      <c r="B8" s="165"/>
+      <c r="C8" s="166"/>
+      <c r="D8" s="152"/>
+      <c r="E8" s="152"/>
+      <c r="F8" s="152"/>
+      <c r="G8" s="152"/>
+      <c r="H8" s="140"/>
+      <c r="I8" s="140"/>
+      <c r="J8" s="140"/>
+      <c r="K8" s="140"/>
+      <c r="L8" s="140"/>
+      <c r="M8" s="140"/>
+      <c r="N8" s="140"/>
+      <c r="O8" s="140"/>
+      <c r="P8" s="140"/>
+      <c r="Q8" s="140"/>
+      <c r="R8" s="140"/>
+      <c r="S8" s="140"/>
+      <c r="T8" s="140"/>
+      <c r="U8" s="140"/>
+      <c r="V8" s="140"/>
+    </row>
+    <row r="9" spans="1:22" ht="15" x14ac:dyDescent="0.25">
+      <c r="A9" s="140"/>
+      <c r="B9" s="165"/>
+      <c r="C9" s="166"/>
+      <c r="D9" s="152"/>
+      <c r="E9" s="152"/>
+      <c r="F9" s="152"/>
+      <c r="G9" s="152"/>
+      <c r="H9" s="140"/>
+      <c r="I9" s="140"/>
+      <c r="J9" s="140"/>
+      <c r="K9" s="140"/>
+      <c r="L9" s="140"/>
+      <c r="M9" s="140"/>
+      <c r="N9" s="140"/>
+      <c r="O9" s="140"/>
+      <c r="P9" s="140"/>
+      <c r="Q9" s="140"/>
+      <c r="R9" s="140"/>
+      <c r="S9" s="140"/>
+      <c r="T9" s="140"/>
+      <c r="U9" s="140"/>
+      <c r="V9" s="140"/>
+    </row>
+    <row r="10" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="140"/>
+      <c r="B10" s="165"/>
+      <c r="C10" s="166"/>
+      <c r="D10" s="152"/>
+      <c r="E10" s="152"/>
+      <c r="F10" s="152"/>
+      <c r="G10" s="152"/>
+      <c r="H10" s="140"/>
+      <c r="I10" s="140"/>
+      <c r="J10" s="140"/>
+      <c r="K10" s="140"/>
+      <c r="L10" s="140"/>
+      <c r="M10" s="140"/>
+      <c r="N10" s="140"/>
+      <c r="O10" s="140"/>
+      <c r="P10" s="140"/>
+      <c r="Q10" s="140"/>
+      <c r="R10" s="140"/>
+      <c r="S10" s="140"/>
+      <c r="T10" s="140"/>
+      <c r="U10" s="140"/>
+      <c r="V10" s="140"/>
+    </row>
+    <row r="11" spans="1:22" ht="15" x14ac:dyDescent="0.25">
+      <c r="A11" s="140"/>
+      <c r="B11" s="167" t="s">
+        <v>37</v>
+      </c>
+      <c r="C11" s="142"/>
+      <c r="D11" s="143" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11" s="144"/>
+      <c r="F11" s="144"/>
+      <c r="G11" s="145"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="167" t="s">
+        <v>38</v>
+      </c>
+      <c r="J11" s="142"/>
+      <c r="K11" s="143" t="s">
+        <v>31</v>
+      </c>
+      <c r="L11" s="144"/>
+      <c r="M11" s="144"/>
+      <c r="N11" s="145"/>
+      <c r="O11" s="140"/>
+      <c r="P11" s="140"/>
+      <c r="Q11" s="140"/>
+      <c r="R11" s="140"/>
+      <c r="S11" s="140"/>
+      <c r="T11" s="140"/>
+      <c r="U11" s="140"/>
+      <c r="V11" s="140"/>
+    </row>
+    <row r="12" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="140"/>
+      <c r="B12" s="146"/>
+      <c r="C12" s="147"/>
+      <c r="D12" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="149" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="150" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="151" t="s">
+        <v>29</v>
+      </c>
+      <c r="H12" s="140"/>
+      <c r="I12" s="146"/>
+      <c r="J12" s="147"/>
+      <c r="K12" s="149" t="s">
+        <v>27</v>
+      </c>
+      <c r="L12" s="150" t="s">
+        <v>28</v>
+      </c>
+      <c r="M12" s="150" t="s">
+        <v>29</v>
+      </c>
+      <c r="N12" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="O12" s="140"/>
+      <c r="P12" s="140"/>
+      <c r="Q12" s="140"/>
+      <c r="R12" s="140"/>
+      <c r="S12" s="140"/>
+      <c r="T12" s="140"/>
+      <c r="U12" s="140"/>
+      <c r="V12" s="140"/>
+    </row>
+    <row r="13" spans="1:22" ht="15" x14ac:dyDescent="0.25">
+      <c r="A13" s="140"/>
+      <c r="B13" s="141" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="154">
+        <v>92.97</v>
+      </c>
+      <c r="E13" s="155">
+        <v>93.38</v>
+      </c>
+      <c r="F13" s="156">
+        <v>93.36</v>
+      </c>
+      <c r="G13" s="157">
+        <v>92.74</v>
+      </c>
+      <c r="H13" s="140"/>
+      <c r="I13" s="141" t="s">
+        <v>30</v>
+      </c>
+      <c r="J13" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="K13" s="155">
+        <v>92.79</v>
+      </c>
+      <c r="L13" s="152">
+        <v>92.79</v>
+      </c>
+      <c r="M13" s="152">
+        <v>92.33</v>
+      </c>
+      <c r="N13" s="154">
+        <v>92.66</v>
+      </c>
+      <c r="O13" s="140"/>
+      <c r="P13" s="140"/>
+      <c r="Q13" s="140"/>
+      <c r="R13" s="140"/>
+      <c r="S13" s="140"/>
+      <c r="T13" s="140"/>
+      <c r="U13" s="140"/>
+      <c r="V13" s="140"/>
+    </row>
+    <row r="14" spans="1:22" ht="15" x14ac:dyDescent="0.25">
+      <c r="A14" s="140"/>
+      <c r="B14" s="158"/>
+      <c r="C14" s="148" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="159">
+        <v>93.55</v>
+      </c>
+      <c r="E14" s="160">
+        <v>93.58</v>
+      </c>
+      <c r="F14" s="156">
+        <v>93.72</v>
+      </c>
+      <c r="G14" s="157">
+        <v>91.3</v>
+      </c>
+      <c r="H14" s="140"/>
+      <c r="I14" s="158"/>
+      <c r="J14" s="148" t="s">
+        <v>28</v>
+      </c>
+      <c r="K14" s="160">
+        <v>92.72</v>
+      </c>
+      <c r="L14" s="152">
+        <v>92.42</v>
+      </c>
+      <c r="M14" s="152">
+        <v>90.82</v>
+      </c>
+      <c r="N14" s="159">
+        <v>92.28</v>
+      </c>
+      <c r="O14" s="140"/>
+      <c r="P14" s="140"/>
+      <c r="Q14" s="140"/>
+      <c r="R14" s="140"/>
+      <c r="S14" s="140"/>
+      <c r="T14" s="140"/>
+      <c r="U14" s="140"/>
+      <c r="V14" s="140"/>
+    </row>
+    <row r="15" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="140"/>
+      <c r="B15" s="146"/>
+      <c r="C15" s="151" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="161">
+        <v>88.64</v>
+      </c>
+      <c r="E15" s="162">
+        <v>92.55</v>
+      </c>
+      <c r="F15" s="163">
+        <v>89.15</v>
+      </c>
+      <c r="G15" s="164">
+        <v>88.35</v>
+      </c>
+      <c r="H15" s="140"/>
+      <c r="I15" s="146"/>
+      <c r="J15" s="151" t="s">
+        <v>29</v>
+      </c>
+      <c r="K15" s="162">
+        <v>90.33</v>
+      </c>
+      <c r="L15" s="163">
+        <v>88.34</v>
+      </c>
+      <c r="M15" s="163">
+        <v>87.26</v>
+      </c>
+      <c r="N15" s="161">
+        <v>87.59</v>
+      </c>
+      <c r="O15" s="140"/>
+      <c r="P15" s="140"/>
+      <c r="Q15" s="140"/>
+      <c r="R15" s="140"/>
+      <c r="S15" s="140"/>
+      <c r="T15" s="140"/>
+      <c r="U15" s="140"/>
+      <c r="V15" s="140"/>
+    </row>
+    <row r="16" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="140"/>
+      <c r="B16" s="140"/>
+      <c r="C16" s="140"/>
+      <c r="D16" s="140"/>
+      <c r="E16" s="140"/>
+      <c r="F16" s="140"/>
+      <c r="G16" s="140"/>
+      <c r="H16" s="140"/>
+      <c r="I16" s="140"/>
+      <c r="J16" s="140"/>
+      <c r="K16" s="140"/>
+      <c r="L16" s="140"/>
+      <c r="M16" s="140"/>
+      <c r="N16" s="140"/>
+      <c r="O16" s="140"/>
+      <c r="P16" s="140"/>
+      <c r="Q16" s="140"/>
+      <c r="R16" s="140"/>
+      <c r="S16" s="140"/>
+      <c r="T16" s="140"/>
+      <c r="U16" s="140"/>
+      <c r="V16" s="140"/>
+    </row>
+    <row r="17" spans="1:22" ht="15" x14ac:dyDescent="0.25">
+      <c r="A17" s="140"/>
+      <c r="B17" s="167" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="142"/>
+      <c r="D17" s="143" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17" s="144"/>
+      <c r="F17" s="144"/>
+      <c r="G17" s="145"/>
+      <c r="H17" s="140"/>
+      <c r="I17" s="167" t="s">
+        <v>35</v>
+      </c>
+      <c r="J17" s="142"/>
+      <c r="K17" s="143" t="s">
+        <v>31</v>
+      </c>
+      <c r="L17" s="144"/>
+      <c r="M17" s="144"/>
+      <c r="N17" s="145"/>
+      <c r="O17" s="140"/>
+      <c r="P17" s="167" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q17" s="142"/>
+      <c r="R17" s="143" t="s">
+        <v>31</v>
+      </c>
+      <c r="S17" s="144"/>
+      <c r="T17" s="144"/>
+      <c r="U17" s="145"/>
+      <c r="V17" s="140"/>
+    </row>
+    <row r="18" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="140"/>
+      <c r="B18" s="146"/>
+      <c r="C18" s="147"/>
+      <c r="D18" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="149" t="s">
+        <v>27</v>
+      </c>
+      <c r="F18" s="150" t="s">
+        <v>28</v>
+      </c>
+      <c r="G18" s="151" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="140"/>
+      <c r="I18" s="146"/>
+      <c r="J18" s="147"/>
+      <c r="K18" s="149" t="s">
+        <v>27</v>
+      </c>
+      <c r="L18" s="150" t="s">
+        <v>28</v>
+      </c>
+      <c r="M18" s="150" t="s">
+        <v>29</v>
+      </c>
+      <c r="N18" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="O18" s="140"/>
+      <c r="P18" s="146"/>
+      <c r="Q18" s="147"/>
+      <c r="R18" s="149" t="s">
+        <v>27</v>
+      </c>
+      <c r="S18" s="150" t="s">
+        <v>28</v>
+      </c>
+      <c r="T18" s="150" t="s">
+        <v>29</v>
+      </c>
+      <c r="U18" s="148" t="s">
+        <v>32</v>
+      </c>
+      <c r="V18" s="140"/>
+    </row>
+    <row r="19" spans="1:22" ht="15" x14ac:dyDescent="0.25">
+      <c r="A19" s="140"/>
+      <c r="B19" s="141" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="154">
+        <v>90.61</v>
+      </c>
+      <c r="E19" s="155">
+        <v>91.1</v>
+      </c>
+      <c r="F19" s="156">
+        <v>91.28</v>
+      </c>
+      <c r="G19" s="157">
+        <v>91.16</v>
+      </c>
+      <c r="H19" s="140"/>
+      <c r="I19" s="141" t="s">
+        <v>30</v>
+      </c>
+      <c r="J19" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="K19" s="155">
+        <v>74.37</v>
+      </c>
+      <c r="L19" s="152">
+        <v>77.239999999999995</v>
+      </c>
+      <c r="M19" s="152">
+        <v>82.31</v>
+      </c>
+      <c r="N19" s="154">
+        <v>76.89</v>
+      </c>
+      <c r="O19" s="140"/>
+      <c r="P19" s="141" t="s">
+        <v>30</v>
+      </c>
+      <c r="Q19" s="153" t="s">
+        <v>27</v>
+      </c>
+      <c r="R19" s="155">
+        <v>56.35</v>
+      </c>
+      <c r="S19" s="152">
+        <v>56.64</v>
+      </c>
+      <c r="T19" s="152">
+        <v>57.69</v>
+      </c>
+      <c r="U19" s="154">
+        <v>57.43</v>
+      </c>
+      <c r="V19" s="140"/>
+    </row>
+    <row r="20" spans="1:22" ht="15" x14ac:dyDescent="0.25">
+      <c r="A20" s="140"/>
+      <c r="B20" s="158"/>
+      <c r="C20" s="148" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" s="159">
+        <v>90.5</v>
+      </c>
+      <c r="E20" s="160">
+        <v>90.92</v>
+      </c>
+      <c r="F20" s="156">
+        <v>90.69</v>
+      </c>
+      <c r="G20" s="157">
+        <v>89.93</v>
+      </c>
+      <c r="H20" s="140"/>
+      <c r="I20" s="158"/>
+      <c r="J20" s="148" t="s">
+        <v>28</v>
+      </c>
+      <c r="K20" s="160">
+        <v>73.430000000000007</v>
+      </c>
+      <c r="L20" s="152">
+        <v>75.78</v>
+      </c>
+      <c r="M20" s="152">
+        <v>80.989999999999995</v>
+      </c>
+      <c r="N20" s="159">
+        <v>72.8</v>
+      </c>
+      <c r="O20" s="140"/>
+      <c r="P20" s="158"/>
+      <c r="Q20" s="148" t="s">
+        <v>28</v>
+      </c>
+      <c r="R20" s="160">
+        <v>56.56</v>
+      </c>
+      <c r="S20" s="152">
+        <v>55.76</v>
+      </c>
+      <c r="T20" s="152">
+        <v>55.07</v>
+      </c>
+      <c r="U20" s="159">
+        <v>54.06</v>
+      </c>
+      <c r="V20" s="140"/>
+    </row>
+    <row r="21" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="140"/>
+      <c r="B21" s="146"/>
+      <c r="C21" s="151" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="161">
+        <v>87.1</v>
+      </c>
+      <c r="E21" s="162">
+        <v>89.67</v>
+      </c>
+      <c r="F21" s="163">
+        <v>87.91</v>
+      </c>
+      <c r="G21" s="164">
+        <v>87.1</v>
+      </c>
+      <c r="H21" s="140"/>
+      <c r="I21" s="146"/>
+      <c r="J21" s="151" t="s">
+        <v>29</v>
+      </c>
+      <c r="K21" s="162">
+        <v>78.680000000000007</v>
+      </c>
+      <c r="L21" s="163">
+        <v>77.040000000000006</v>
+      </c>
+      <c r="M21" s="163">
+        <v>75.41</v>
+      </c>
+      <c r="N21" s="161">
+        <v>74.819999999999993</v>
+      </c>
+      <c r="O21" s="140"/>
+      <c r="P21" s="146"/>
+      <c r="Q21" s="151" t="s">
+        <v>29</v>
+      </c>
+      <c r="R21" s="162">
+        <v>53.09</v>
+      </c>
+      <c r="S21" s="163">
+        <v>51.47</v>
+      </c>
+      <c r="T21" s="163">
+        <v>50.41</v>
+      </c>
+      <c r="U21" s="161">
+        <v>50.06</v>
+      </c>
+      <c r="V21" s="140"/>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="A22" s="140"/>
+      <c r="B22" s="140"/>
+      <c r="C22" s="140"/>
+      <c r="D22" s="140"/>
+      <c r="E22" s="140"/>
+      <c r="F22" s="140"/>
+      <c r="G22" s="140"/>
+      <c r="H22" s="140"/>
+      <c r="I22" s="140"/>
+      <c r="J22" s="140"/>
+      <c r="K22" s="140"/>
+      <c r="L22" s="140"/>
+      <c r="M22" s="140"/>
+      <c r="N22" s="140"/>
+      <c r="O22" s="140"/>
+      <c r="P22" s="140"/>
+      <c r="Q22" s="140"/>
+      <c r="R22" s="140"/>
+      <c r="S22" s="140"/>
+      <c r="T22" s="140"/>
+      <c r="U22" s="140"/>
+      <c r="V22" s="140"/>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="P17:Q18"/>
+    <mergeCell ref="R17:U17"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="I19:I21"/>
+    <mergeCell ref="P19:P21"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="K11:N11"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="I13:I15"/>
+    <mergeCell ref="B17:C18"/>
+    <mergeCell ref="I17:J18"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="B3:C4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="B11:C12"/>
+    <mergeCell ref="I11:J12"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="E6:G10 E5">
+    <cfRule type="colorScale" priority="60">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E14:G15 E13">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E20:G21 E19">
+    <cfRule type="colorScale" priority="43">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F5:G5">
+    <cfRule type="colorScale" priority="58">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F13:G13">
+    <cfRule type="colorScale" priority="30">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19:G19">
+    <cfRule type="colorScale" priority="42">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K4:L4">
+    <cfRule type="colorScale" priority="59">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K14:M15 K13">
+    <cfRule type="colorScale" priority="37">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K20:M21 K19">
+    <cfRule type="colorScale" priority="49">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K13:N15">
+    <cfRule type="colorScale" priority="32">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K19:N21">
+    <cfRule type="colorScale" priority="44">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L13:M13">
+    <cfRule type="colorScale" priority="36">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L19:M19">
+    <cfRule type="colorScale" priority="48">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N13">
+    <cfRule type="colorScale" priority="35">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N14">
+    <cfRule type="colorScale" priority="34">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N15">
+    <cfRule type="colorScale" priority="33">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N19">
+    <cfRule type="colorScale" priority="47">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N20">
+    <cfRule type="colorScale" priority="46">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N21">
+    <cfRule type="colorScale" priority="45">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R20:T21 R19">
+    <cfRule type="colorScale" priority="55">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R19:U21">
+    <cfRule type="colorScale" priority="50">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S19:T19">
+    <cfRule type="colorScale" priority="54">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U19">
+    <cfRule type="colorScale" priority="53">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U20">
+    <cfRule type="colorScale" priority="52">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U21">
+    <cfRule type="colorScale" priority="51">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:G7">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K13:N15 E13:G15 E19:G21 K19:N21 R19:U21">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8:D10">
+    <cfRule type="colorScale" priority="21">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13:D15">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D19:D21">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D8:D10">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D14">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D15">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D19">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D20">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D21">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D13:D15 D19:D21">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D5:D7">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E5:G10">
+    <cfRule type="colorScale" priority="333">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E13:G15">
+    <cfRule type="colorScale" priority="335">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E19:G21">
+    <cfRule type="colorScale" priority="336">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="5" id="{9626EE22-E465-41AD-B042-1C387315CF57}">
+            <x14:iconSet iconSet="3Triangles">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>33</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>67</xm:f>
+              </x14:cfvo>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>K19:N21</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
 </file>
--- a/results_(stress_test)_baselines/summary.xlsx
+++ b/results_(stress_test)_baselines/summary.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RnD_Repo\Research_Engineeirng\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_baselines\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\RnD_Repo\Research_Engineering\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_baselines\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD5127AD-39D0-4F11-B658-9D6136FAA285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B2D0DC-A473-480E-9EE7-404C7EC5E523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="639" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-210" windowWidth="29040" windowHeight="16440" tabRatio="639" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="partialdata_20260618_unf_idx" sheetId="6" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="40">
   <si>
     <t>Accuracy</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -231,7 +231,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -262,6 +262,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -473,7 +480,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="168">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -581,12 +588,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -655,9 +656,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -666,9 +664,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -752,84 +747,84 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -840,6 +835,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -848,14 +852,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -863,30 +876,15 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1164,7 +1162,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4687D530-62F3-45D6-8CBF-3B0602E24BE5}">
-  <dimension ref="A1:R57"/>
+  <dimension ref="A1:R55"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25" style="10" customWidth="1"/>
@@ -1228,23 +1226,23 @@
       <c r="R1" s="12"/>
     </row>
     <row r="2" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="134" t="s">
+      <c r="A2" s="123" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="135"/>
-      <c r="C2" s="118">
+      <c r="B2" s="124"/>
+      <c r="C2" s="114">
         <v>92.97270449283009</v>
       </c>
-      <c r="D2" s="119">
+      <c r="D2" s="115">
         <v>92.656851126163161</v>
       </c>
-      <c r="E2" s="119">
+      <c r="E2" s="115">
         <v>90.612485113769722</v>
       </c>
-      <c r="F2" s="119">
+      <c r="F2" s="115">
         <v>76.890048068466555</v>
       </c>
-      <c r="G2" s="120">
+      <c r="G2" s="116">
         <v>57.431157132270449</v>
       </c>
       <c r="H2" s="23" cm="1">
@@ -1259,23 +1257,23 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:G2)&amp;","</f>
         <v xml:space="preserve">    92.9727044928301, 92.6568511261632, 90.6124851137697, 76.8900480684666, 57.4311571322704,</v>
       </c>
-      <c r="K2" s="134" t="s">
+      <c r="K2" s="123" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="135"/>
-      <c r="M2" s="79">
+      <c r="L2" s="124"/>
+      <c r="M2" s="77">
         <v>3.6723191410127392</v>
       </c>
-      <c r="N2" s="80">
+      <c r="N2" s="78">
         <v>3.8557140126956959</v>
       </c>
-      <c r="O2" s="80">
+      <c r="O2" s="78">
         <v>4.1717853309388913</v>
       </c>
-      <c r="P2" s="80">
+      <c r="P2" s="78">
         <v>8.1206319222896362</v>
       </c>
-      <c r="Q2" s="81">
+      <c r="Q2" s="79">
         <v>8.7326493747450371</v>
       </c>
       <c r="R2" s="12" t="str">
@@ -1284,23 +1282,23 @@
       </c>
     </row>
     <row r="3" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="134" t="s">
+      <c r="A3" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="135"/>
-      <c r="C3" s="121">
+      <c r="B3" s="124"/>
+      <c r="C3" s="117">
         <v>93.550650668835075</v>
       </c>
-      <c r="D3" s="122">
+      <c r="D3" s="118">
         <v>92.282219857726602</v>
       </c>
-      <c r="E3" s="122">
+      <c r="E3" s="118">
         <v>90.501679656975099</v>
       </c>
-      <c r="F3" s="122">
+      <c r="F3" s="118">
         <v>72.805808585426078</v>
       </c>
-      <c r="G3" s="123">
+      <c r="G3" s="119">
         <v>54.064066298151367</v>
       </c>
       <c r="H3" s="23" cm="1">
@@ -1315,11 +1313,11 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:G3)&amp;","</f>
         <v xml:space="preserve">    93.5506506688351, 92.2822198577266, 90.5016796569751, 72.8058085854261, 54.0640662981514,</v>
       </c>
-      <c r="K3" s="134" t="s">
+      <c r="K3" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="L3" s="135"/>
-      <c r="M3" s="82">
+      <c r="L3" s="124"/>
+      <c r="M3" s="80">
         <v>3.5444962758226279</v>
       </c>
       <c r="N3">
@@ -1331,7 +1329,7 @@
       <c r="P3">
         <v>9.1245390051568016</v>
       </c>
-      <c r="Q3" s="83">
+      <c r="Q3" s="81">
         <v>7.5991148630492704</v>
       </c>
       <c r="R3" s="12" t="str">
@@ -1340,23 +1338,23 @@
       </c>
     </row>
     <row r="4" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="139" t="s">
+      <c r="A4" s="125" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="140"/>
-      <c r="C4" s="121">
+      <c r="B4" s="126"/>
+      <c r="C4" s="117">
         <v>88.646029233240199</v>
       </c>
-      <c r="D4" s="122">
+      <c r="D4" s="118">
         <v>87.588003933136662</v>
       </c>
-      <c r="E4" s="122">
+      <c r="E4" s="118">
         <v>87.102273087714138</v>
       </c>
-      <c r="F4" s="122">
+      <c r="F4" s="118">
         <v>74.826714187262283</v>
       </c>
-      <c r="G4" s="123">
+      <c r="G4" s="119">
         <v>50.055245575942109</v>
       </c>
       <c r="H4" s="34" cm="1">
@@ -1371,11 +1369,11 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C4:G4)&amp;","</f>
         <v xml:space="preserve">    88.6460292332402, 87.5880039331367, 87.1022730877141, 74.8267141872623, 50.0552455759421,</v>
       </c>
-      <c r="K4" s="139" t="s">
+      <c r="K4" s="125" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="140"/>
-      <c r="M4" s="82">
+      <c r="L4" s="126"/>
+      <c r="M4" s="80">
         <v>3.1531095164540388</v>
       </c>
       <c r="N4">
@@ -1387,7 +1385,7 @@
       <c r="P4">
         <v>2.8561346399896621</v>
       </c>
-      <c r="Q4" s="83">
+      <c r="Q4" s="81">
         <v>1.6635727988470741</v>
       </c>
       <c r="R4" s="12" t="str">
@@ -1396,49 +1394,49 @@
       </c>
     </row>
     <row r="5" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="123" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="136"/>
-      <c r="C5" s="136"/>
-      <c r="D5" s="136"/>
-      <c r="E5" s="136"/>
-      <c r="F5" s="136"/>
-      <c r="G5" s="135"/>
+      <c r="B5" s="127"/>
+      <c r="C5" s="127"/>
+      <c r="D5" s="127"/>
+      <c r="E5" s="127"/>
+      <c r="F5" s="127"/>
+      <c r="G5" s="124"/>
       <c r="H5" s="34"/>
       <c r="I5" s="34"/>
       <c r="J5" s="12"/>
-      <c r="K5" s="134" t="s">
+      <c r="K5" s="123" t="s">
         <v>12</v>
       </c>
-      <c r="L5" s="136"/>
-      <c r="M5" s="136"/>
-      <c r="N5" s="136"/>
-      <c r="O5" s="136"/>
-      <c r="P5" s="136"/>
-      <c r="Q5" s="135"/>
+      <c r="L5" s="127"/>
+      <c r="M5" s="127"/>
+      <c r="N5" s="127"/>
+      <c r="O5" s="127"/>
+      <c r="P5" s="127"/>
+      <c r="Q5" s="124"/>
       <c r="R5" s="12"/>
     </row>
     <row r="6" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="139" t="s">
+      <c r="A6" s="125" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="90" t="s">
+      <c r="B6" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="118">
+      <c r="C6" s="114">
         <v>93.375631853793436</v>
       </c>
-      <c r="D6" s="119">
+      <c r="D6" s="115">
         <v>92.792878831131745</v>
       </c>
-      <c r="E6" s="119">
+      <c r="E6" s="115">
         <v>91.094066557669166</v>
       </c>
-      <c r="F6" s="119">
+      <c r="F6" s="115">
         <v>74.369665827559075</v>
       </c>
-      <c r="G6" s="120">
+      <c r="G6" s="116">
         <v>56.35401113619784</v>
       </c>
       <c r="H6" s="34" cm="1">
@@ -1450,47 +1448,47 @@
         <v>83.954594024025582</v>
       </c>
       <c r="J6" s="12"/>
-      <c r="K6" s="139" t="s">
+      <c r="K6" s="125" t="s">
         <v>11</v>
       </c>
-      <c r="L6" s="90" t="s">
+      <c r="L6" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="M6" s="79">
+      <c r="M6" s="77">
         <v>3.4841780245944278</v>
       </c>
-      <c r="N6" s="80">
+      <c r="N6" s="78">
         <v>3.7171339527240979</v>
       </c>
-      <c r="O6" s="80">
+      <c r="O6" s="78">
         <v>3.5950208209222092</v>
       </c>
-      <c r="P6" s="80">
+      <c r="P6" s="78">
         <v>8.5619397568121691</v>
       </c>
-      <c r="Q6" s="81">
+      <c r="Q6" s="79">
         <v>8.7436032668579529</v>
       </c>
       <c r="R6" s="12"/>
     </row>
     <row r="7" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="144"/>
-      <c r="B7" s="90" t="s">
+      <c r="A7" s="130"/>
+      <c r="B7" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="121">
+      <c r="C7" s="117">
         <v>93.358985227669237</v>
       </c>
-      <c r="D7" s="122">
+      <c r="D7" s="118">
         <v>92.785690187631374</v>
       </c>
-      <c r="E7" s="122">
+      <c r="E7" s="118">
         <v>91.279001836809442</v>
       </c>
-      <c r="F7" s="122">
+      <c r="F7" s="118">
         <v>77.243569004345488</v>
       </c>
-      <c r="G7" s="123">
+      <c r="G7" s="119">
         <v>56.641689518652129</v>
       </c>
       <c r="H7" s="34" cm="1">
@@ -1505,11 +1503,11 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C7:G7)&amp;","</f>
         <v xml:space="preserve">    93.3589852276692, 92.7856901876314, 91.2790018368094, 77.2435690043455, 56.6416895186521,</v>
       </c>
-      <c r="K7" s="144"/>
-      <c r="L7" s="90" t="s">
+      <c r="K7" s="130"/>
+      <c r="L7" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="M7" s="82">
+      <c r="M7" s="80">
         <v>3.5292136776947389</v>
       </c>
       <c r="N7">
@@ -1521,7 +1519,7 @@
       <c r="P7">
         <v>7.7490040503559836</v>
       </c>
-      <c r="Q7" s="83">
+      <c r="Q7" s="81">
         <v>8.6647795337348459</v>
       </c>
       <c r="R7" s="12" t="str">
@@ -1530,23 +1528,23 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="144"/>
-      <c r="B8" s="8" t="s">
+      <c r="A8" s="130"/>
+      <c r="B8" s="164" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="121">
+      <c r="C8" s="117">
         <v>92.744346116027529</v>
       </c>
-      <c r="D8" s="122">
+      <c r="D8" s="118">
         <v>92.328416912487711</v>
       </c>
-      <c r="E8" s="122">
+      <c r="E8" s="118">
         <v>91.156108616856514</v>
       </c>
-      <c r="F8" s="122">
+      <c r="F8" s="118">
         <v>82.307782362592519</v>
       </c>
-      <c r="G8" s="123">
+      <c r="G8" s="119">
         <v>57.694504277718679</v>
       </c>
       <c r="H8" s="34" cm="1">
@@ -1561,11 +1559,11 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C8:G8)&amp;","</f>
         <v xml:space="preserve">    92.7443461160275, 92.3284169124877, 91.1561086168565, 82.3077823625925, 57.6945042777187,</v>
       </c>
-      <c r="K8" s="144"/>
+      <c r="K8" s="130"/>
       <c r="L8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="M8" s="82">
+      <c r="M8" s="80">
         <v>3.3427481085122568</v>
       </c>
       <c r="N8">
@@ -1577,7 +1575,7 @@
       <c r="P8">
         <v>4.6775599948055158</v>
       </c>
-      <c r="Q8" s="83">
+      <c r="Q8" s="81">
         <v>6.3264357320363649</v>
       </c>
       <c r="R8" s="12" t="str">
@@ -1586,23 +1584,23 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="144"/>
+      <c r="A9" s="130"/>
       <c r="B9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="121">
+      <c r="C9" s="117">
         <v>93.721730580137674</v>
       </c>
-      <c r="D9" s="122">
+      <c r="D9" s="118">
         <v>92.415934970602393</v>
       </c>
-      <c r="E9" s="122">
+      <c r="E9" s="118">
         <v>90.686860036274823</v>
       </c>
-      <c r="F9" s="122">
+      <c r="F9" s="118">
         <v>75.782143444147451</v>
       </c>
-      <c r="G9" s="123">
+      <c r="G9" s="119">
         <v>55.768484156437339</v>
       </c>
       <c r="H9" s="34" cm="1">
@@ -1614,11 +1612,11 @@
         <v>83.937535593589331</v>
       </c>
       <c r="J9" s="12"/>
-      <c r="K9" s="144"/>
+      <c r="K9" s="130"/>
       <c r="L9" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="M9" s="82">
+      <c r="M9" s="80">
         <v>3.5340996284974531</v>
       </c>
       <c r="N9">
@@ -1630,29 +1628,29 @@
       <c r="P9">
         <v>8.2748920802292076</v>
       </c>
-      <c r="Q9" s="83">
+      <c r="Q9" s="81">
         <v>8.6222095079337446</v>
       </c>
       <c r="R9" s="12"/>
     </row>
     <row r="10" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="144"/>
+      <c r="A10" s="130"/>
       <c r="B10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="121">
+      <c r="C10" s="117">
         <v>93.578171091445412</v>
       </c>
-      <c r="D10" s="122">
+      <c r="D10" s="118">
         <v>92.721736347200235</v>
       </c>
-      <c r="E10" s="122">
+      <c r="E10" s="118">
         <v>90.919630215947663</v>
       </c>
-      <c r="F10" s="122">
+      <c r="F10" s="118">
         <v>73.42964039481312</v>
       </c>
-      <c r="G10" s="123">
+      <c r="G10" s="119">
         <v>56.559615567608724</v>
       </c>
       <c r="H10" s="34" cm="1">
@@ -1664,11 +1662,11 @@
         <v>83.864141342053131</v>
       </c>
       <c r="J10" s="12"/>
-      <c r="K10" s="144"/>
+      <c r="K10" s="130"/>
       <c r="L10" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="M10" s="82">
+      <c r="M10" s="80">
         <v>3.4211604643278899</v>
       </c>
       <c r="N10">
@@ -1680,7 +1678,7 @@
       <c r="P10">
         <v>8.9824743171696255</v>
       </c>
-      <c r="Q10" s="83">
+      <c r="Q10" s="81">
         <v>8.2082515511175735</v>
       </c>
       <c r="R10" s="12" t="str">
@@ -1689,23 +1687,23 @@
       </c>
     </row>
     <row r="11" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="144"/>
-      <c r="B11" s="8" t="s">
+      <c r="A11" s="130"/>
+      <c r="B11" s="164" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="121">
+      <c r="C11" s="117">
         <v>91.299901671583086</v>
       </c>
-      <c r="D11" s="122">
+      <c r="D11" s="118">
         <v>90.822048633638715</v>
       </c>
-      <c r="E11" s="122">
+      <c r="E11" s="118">
         <v>89.932372540708258</v>
       </c>
-      <c r="F11" s="122">
+      <c r="F11" s="118">
         <v>80.986383965259208</v>
       </c>
-      <c r="G11" s="123">
+      <c r="G11" s="119">
         <v>55.071488507686048</v>
       </c>
       <c r="H11" s="34" cm="1">
@@ -1717,11 +1715,11 @@
         <v>83.059021019501316</v>
       </c>
       <c r="J11" s="12"/>
-      <c r="K11" s="144"/>
+      <c r="K11" s="130"/>
       <c r="L11" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="M11" s="82">
+      <c r="M11" s="80">
         <v>3.058139598469626</v>
       </c>
       <c r="N11">
@@ -1733,29 +1731,29 @@
       <c r="P11">
         <v>4.2324186928534564</v>
       </c>
-      <c r="Q11" s="83">
+      <c r="Q11" s="81">
         <v>6.3408360836535147</v>
       </c>
       <c r="R11" s="12"/>
     </row>
     <row r="12" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="144"/>
-      <c r="B12" s="88" t="s">
+      <c r="A12" s="130"/>
+      <c r="B12" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="121">
+      <c r="C12" s="117">
         <v>88.345132743362853</v>
       </c>
-      <c r="D12" s="122">
+      <c r="D12" s="118">
         <v>87.267453294001967</v>
       </c>
-      <c r="E12" s="122">
+      <c r="E12" s="118">
         <v>87.102446099591404</v>
       </c>
-      <c r="F12" s="122">
+      <c r="F12" s="118">
         <v>75.414922851120394</v>
       </c>
-      <c r="G12" s="123">
+      <c r="G12" s="119">
         <v>50.409063515543693</v>
       </c>
       <c r="H12" s="34" cm="1">
@@ -1767,11 +1765,11 @@
         <v>79.788719066918105</v>
       </c>
       <c r="J12" s="12"/>
-      <c r="K12" s="144"/>
-      <c r="L12" s="88" t="s">
+      <c r="K12" s="130"/>
+      <c r="L12" s="85" t="s">
         <v>16</v>
       </c>
-      <c r="M12" s="82">
+      <c r="M12" s="80">
         <v>2.983926605181269</v>
       </c>
       <c r="N12">
@@ -1783,29 +1781,29 @@
       <c r="P12">
         <v>3.3792106059866658</v>
       </c>
-      <c r="Q12" s="83">
+      <c r="Q12" s="81">
         <v>1.3738116379133549</v>
       </c>
       <c r="R12" s="12"/>
     </row>
     <row r="13" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="144"/>
-      <c r="B13" s="88" t="s">
+      <c r="A13" s="130"/>
+      <c r="B13" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="121">
+      <c r="C13" s="117">
         <v>90.553588987217324</v>
       </c>
-      <c r="D13" s="122">
+      <c r="D13" s="118">
         <v>90.325467059980355</v>
       </c>
-      <c r="E13" s="122">
+      <c r="E13" s="118">
         <v>89.668636118536241</v>
       </c>
-      <c r="F13" s="122">
+      <c r="F13" s="118">
         <v>78.678561233228677</v>
       </c>
-      <c r="G13" s="123">
+      <c r="G13" s="119">
         <v>53.098925307889047</v>
       </c>
       <c r="H13" s="34" cm="1">
@@ -1817,11 +1815,11 @@
         <v>82.358773198009231</v>
       </c>
       <c r="J13" s="12"/>
-      <c r="K13" s="144"/>
-      <c r="L13" s="88" t="s">
+      <c r="K13" s="130"/>
+      <c r="L13" s="85" t="s">
         <v>19</v>
       </c>
-      <c r="M13" s="82">
+      <c r="M13" s="80">
         <v>2.5990157411770438</v>
       </c>
       <c r="N13">
@@ -1833,7 +1831,7 @@
       <c r="P13">
         <v>3.814135483602267</v>
       </c>
-      <c r="Q13" s="83">
+      <c r="Q13" s="81">
         <v>3.5742222382122981</v>
       </c>
       <c r="R13" s="12" t="str">
@@ -1842,23 +1840,23 @@
       </c>
     </row>
     <row r="14" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="137"/>
-      <c r="B14" s="88" t="s">
+      <c r="A14" s="128"/>
+      <c r="B14" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="75">
+      <c r="C14" s="73">
         <v>89.149459193706974</v>
       </c>
-      <c r="D14" s="76">
+      <c r="D14" s="74">
         <v>88.338249754178975</v>
       </c>
-      <c r="E14" s="76">
+      <c r="E14" s="74">
         <v>87.909618595316573</v>
       </c>
-      <c r="F14" s="76">
+      <c r="F14" s="74">
         <v>77.044259321735765</v>
       </c>
-      <c r="G14" s="77">
+      <c r="G14" s="75">
         <v>51.470476964910311</v>
       </c>
       <c r="H14" s="34" cm="1">
@@ -1870,69 +1868,69 @@
         <v>80.728613659431886</v>
       </c>
       <c r="J14" s="12"/>
-      <c r="K14" s="137"/>
-      <c r="L14" s="88" t="s">
+      <c r="K14" s="128"/>
+      <c r="L14" s="85" t="s">
         <v>26</v>
       </c>
-      <c r="M14" s="84">
+      <c r="M14" s="82">
         <v>2.7752984471319091</v>
       </c>
-      <c r="N14" s="85">
+      <c r="N14" s="83">
         <v>2.3015697910981339</v>
       </c>
-      <c r="O14" s="85">
+      <c r="O14" s="83">
         <v>2.0162357843530452</v>
       </c>
-      <c r="P14" s="85">
+      <c r="P14" s="83">
         <v>3.0539531580418511</v>
       </c>
-      <c r="Q14" s="86">
+      <c r="Q14" s="84">
         <v>1.6877124305890641</v>
       </c>
       <c r="R14" s="12"/>
     </row>
     <row r="15" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="134" t="s">
+      <c r="A15" s="123" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="136"/>
-      <c r="C15" s="136"/>
-      <c r="D15" s="136"/>
-      <c r="E15" s="136"/>
-      <c r="F15" s="136"/>
-      <c r="G15" s="135"/>
+      <c r="B15" s="127"/>
+      <c r="C15" s="127"/>
+      <c r="D15" s="127"/>
+      <c r="E15" s="127"/>
+      <c r="F15" s="127"/>
+      <c r="G15" s="124"/>
       <c r="H15" s="34"/>
       <c r="I15" s="34"/>
       <c r="J15" s="12"/>
-      <c r="K15" s="134" t="s">
+      <c r="K15" s="123" t="s">
         <v>20</v>
       </c>
-      <c r="L15" s="136"/>
-      <c r="M15" s="136"/>
-      <c r="N15" s="136"/>
-      <c r="O15" s="136"/>
-      <c r="P15" s="136"/>
-      <c r="Q15" s="135"/>
+      <c r="L15" s="127"/>
+      <c r="M15" s="127"/>
+      <c r="N15" s="127"/>
+      <c r="O15" s="127"/>
+      <c r="P15" s="127"/>
+      <c r="Q15" s="124"/>
       <c r="R15" s="12"/>
     </row>
     <row r="16" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="137" t="s">
+      <c r="A16" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="138"/>
-      <c r="C16" s="121">
+      <c r="B16" s="129"/>
+      <c r="C16" s="117">
         <v>93.207752662220258</v>
       </c>
-      <c r="D16" s="122">
+      <c r="D16" s="118">
         <v>92.783034455315345</v>
       </c>
-      <c r="E16" s="122">
+      <c r="E16" s="118">
         <v>90.565884364628303</v>
       </c>
-      <c r="F16" s="122">
+      <c r="F16" s="118">
         <v>73.076886478256739</v>
       </c>
-      <c r="G16" s="123">
+      <c r="G16" s="119">
         <v>58.556994437668138</v>
       </c>
       <c r="H16" s="34" cm="1">
@@ -1947,11 +1945,11 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C16:G16)&amp;","</f>
         <v xml:space="preserve">    93.2077526622203, 92.7830344553153, 90.5658843646283, 73.0768864782567, 58.5569944376681,</v>
       </c>
-      <c r="K16" s="137" t="s">
+      <c r="K16" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="L16" s="138"/>
-      <c r="M16" s="82">
+      <c r="L16" s="129"/>
+      <c r="M16" s="80">
         <v>4.081079160307894</v>
       </c>
       <c r="N16">
@@ -1963,7 +1961,7 @@
       <c r="P16">
         <v>9.0889689998586825</v>
       </c>
-      <c r="Q16" s="83">
+      <c r="Q16" s="81">
         <v>9.0192886420696112</v>
       </c>
       <c r="R16" s="12" t="str">
@@ -1972,23 +1970,23 @@
       </c>
     </row>
     <row r="17" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="139" t="s">
+      <c r="A17" s="125" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="140"/>
-      <c r="C17" s="121">
+      <c r="B17" s="126"/>
+      <c r="C17" s="117">
         <v>93.534975792754821</v>
       </c>
-      <c r="D17" s="122">
+      <c r="D17" s="118">
         <v>92.336467731843129</v>
       </c>
-      <c r="E17" s="122">
+      <c r="E17" s="118">
         <v>88.593520128490155</v>
       </c>
-      <c r="F17" s="122">
+      <c r="F17" s="118">
         <v>71.045294509468079</v>
       </c>
-      <c r="G17" s="123">
+      <c r="G17" s="119">
         <v>53.467062863865607</v>
       </c>
       <c r="H17" s="34" cm="1">
@@ -2003,11 +2001,11 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C17:G17)&amp;","</f>
         <v xml:space="preserve">    93.5349757927548, 92.3364677318431, 88.5935201284902, 71.0452945094681, 53.4670628638656,</v>
       </c>
-      <c r="K17" s="134" t="s">
+      <c r="K17" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="L17" s="135"/>
-      <c r="M17" s="82">
+      <c r="L17" s="124"/>
+      <c r="M17" s="80">
         <v>3.8494978151380188</v>
       </c>
       <c r="N17">
@@ -2019,7 +2017,7 @@
       <c r="P17">
         <v>10.247976510425289</v>
       </c>
-      <c r="Q17" s="83">
+      <c r="Q17" s="81">
         <v>9.5145399413620808</v>
       </c>
       <c r="R17" s="12" t="str">
@@ -2028,23 +2026,23 @@
       </c>
     </row>
     <row r="18" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="134" t="s">
+      <c r="A18" s="123" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="135"/>
-      <c r="C18" s="121">
+      <c r="B18" s="124"/>
+      <c r="C18" s="117">
         <v>93.005297046975599</v>
       </c>
-      <c r="D18" s="122">
+      <c r="D18" s="118">
         <v>91.902444369472647</v>
       </c>
-      <c r="E18" s="122">
+      <c r="E18" s="118">
         <v>89.116278399178753</v>
       </c>
-      <c r="F18" s="122">
+      <c r="F18" s="118">
         <v>72.258814234263852</v>
       </c>
-      <c r="G18" s="123">
+      <c r="G18" s="119">
         <v>53.843628981796257</v>
       </c>
       <c r="H18" s="34" cm="1">
@@ -2059,11 +2057,11 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C18:G18)&amp;","</f>
         <v xml:space="preserve">    93.0052970469756, 91.9024443694726, 89.1162783991788, 72.2588142342639, 53.8436289817963,</v>
       </c>
-      <c r="K18" s="134" t="s">
+      <c r="K18" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="L18" s="135"/>
-      <c r="M18" s="82">
+      <c r="L18" s="124"/>
+      <c r="M18" s="80">
         <v>3.458803648865628</v>
       </c>
       <c r="N18">
@@ -2075,7 +2073,7 @@
       <c r="P18">
         <v>10.1810612930344</v>
       </c>
-      <c r="Q18" s="83">
+      <c r="Q18" s="81">
         <v>8.6745540222164905</v>
       </c>
       <c r="R18" s="12" t="str">
@@ -2084,47 +2082,47 @@
       </c>
     </row>
     <row r="19" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="134" t="s">
+      <c r="A19" s="123" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="136"/>
-      <c r="C19" s="136"/>
-      <c r="D19" s="136"/>
-      <c r="E19" s="136"/>
-      <c r="F19" s="136"/>
-      <c r="G19" s="135"/>
+      <c r="B19" s="127"/>
+      <c r="C19" s="127"/>
+      <c r="D19" s="127"/>
+      <c r="E19" s="127"/>
+      <c r="F19" s="127"/>
+      <c r="G19" s="124"/>
       <c r="H19" s="34"/>
       <c r="I19" s="34"/>
       <c r="J19" s="12"/>
-      <c r="K19" s="134" t="s">
+      <c r="K19" s="123" t="s">
         <v>23</v>
       </c>
-      <c r="L19" s="136"/>
-      <c r="M19" s="136"/>
-      <c r="N19" s="136"/>
-      <c r="O19" s="136"/>
-      <c r="P19" s="136"/>
-      <c r="Q19" s="135"/>
+      <c r="L19" s="127"/>
+      <c r="M19" s="127"/>
+      <c r="N19" s="127"/>
+      <c r="O19" s="127"/>
+      <c r="P19" s="127"/>
+      <c r="Q19" s="124"/>
       <c r="R19" s="12"/>
     </row>
     <row r="20" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="137" t="s">
+      <c r="A20" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="B20" s="138"/>
-      <c r="C20" s="121">
+      <c r="B20" s="129"/>
+      <c r="C20" s="117">
         <v>93.204569243678591</v>
       </c>
-      <c r="D20" s="122">
+      <c r="D20" s="118">
         <v>92.71893643831983</v>
       </c>
-      <c r="E20" s="122">
+      <c r="E20" s="118">
         <v>91.010196166633492</v>
       </c>
-      <c r="F20" s="122">
+      <c r="F20" s="118">
         <v>77.775612245780678</v>
       </c>
-      <c r="G20" s="123">
+      <c r="G20" s="119">
         <v>55.921856302101808</v>
       </c>
       <c r="H20" s="34" cm="1">
@@ -2139,11 +2137,11 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C20:G20)&amp;","</f>
         <v xml:space="preserve">    93.2045692436786, 92.7189364383198, 91.0101961666335, 77.7756122457807, 55.9218563021018,</v>
       </c>
-      <c r="K20" s="137" t="s">
+      <c r="K20" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="L20" s="138"/>
-      <c r="M20" s="82">
+      <c r="L20" s="129"/>
+      <c r="M20" s="80">
         <v>3.5338969773137729</v>
       </c>
       <c r="N20">
@@ -2155,7 +2153,7 @@
       <c r="P20">
         <v>6.7863547394302319</v>
       </c>
-      <c r="Q20" s="83">
+      <c r="Q20" s="81">
         <v>8.2097242202983072</v>
       </c>
       <c r="R20" s="12" t="str">
@@ -2164,23 +2162,23 @@
       </c>
     </row>
     <row r="21" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="139" t="s">
+      <c r="A21" s="125" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="140"/>
-      <c r="C21" s="121">
+      <c r="B21" s="126"/>
+      <c r="C21" s="117">
         <v>91.935155148400952</v>
       </c>
-      <c r="D21" s="122">
+      <c r="D21" s="118">
         <v>91.692255123314226</v>
       </c>
-      <c r="E21" s="122">
+      <c r="E21" s="118">
         <v>89.847648624411406</v>
       </c>
-      <c r="F21" s="122">
+      <c r="F21" s="118">
         <v>79.400747411309794</v>
       </c>
-      <c r="G21" s="123">
+      <c r="G21" s="119">
         <v>53.25364406266489</v>
       </c>
       <c r="H21" s="34" cm="1">
@@ -2195,11 +2193,11 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:G21)&amp;","</f>
         <v xml:space="preserve">    91.935155148401, 91.6922551233142, 89.8476486244114, 79.4007474113098, 53.2536440626649,</v>
       </c>
-      <c r="K21" s="134" t="s">
+      <c r="K21" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="L21" s="135"/>
-      <c r="M21" s="82">
+      <c r="L21" s="124"/>
+      <c r="M21" s="80">
         <v>3.0404967647063641</v>
       </c>
       <c r="N21">
@@ -2211,7 +2209,7 @@
       <c r="P21">
         <v>3.323723681934811</v>
       </c>
-      <c r="Q21" s="83">
+      <c r="Q21" s="81">
         <v>4.2607284397566696</v>
       </c>
       <c r="R21" s="12" t="str">
@@ -2220,23 +2218,23 @@
       </c>
     </row>
     <row r="22" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="134" t="s">
+      <c r="A22" s="123" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="135"/>
-      <c r="C22" s="121">
+      <c r="B22" s="124"/>
+      <c r="C22" s="117">
         <v>93.32960781090955</v>
       </c>
-      <c r="D22" s="122">
+      <c r="D22" s="118">
         <v>92.627433339965464</v>
       </c>
-      <c r="E22" s="122">
+      <c r="E22" s="118">
         <v>90.919543710009009</v>
       </c>
-      <c r="F22" s="122">
+      <c r="F22" s="118">
         <v>77.743400317765136</v>
       </c>
-      <c r="G22" s="123">
+      <c r="G22" s="119">
         <v>58.391070280308071</v>
       </c>
       <c r="H22" s="34" cm="1">
@@ -2251,11 +2249,11 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C22:G22)&amp;","</f>
         <v xml:space="preserve">    93.3296078109096, 92.6274333399655, 90.919543710009, 77.7434003177651, 58.3910702803081,</v>
       </c>
-      <c r="K22" s="134" t="s">
+      <c r="K22" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="L22" s="135"/>
-      <c r="M22" s="82">
+      <c r="L22" s="124"/>
+      <c r="M22" s="80">
         <v>3.3471189071482028</v>
       </c>
       <c r="N22">
@@ -2267,7 +2265,7 @@
       <c r="P22">
         <v>7.5417080235248886</v>
       </c>
-      <c r="Q22" s="83">
+      <c r="Q22" s="81">
         <v>8.4137702230121008</v>
       </c>
       <c r="R22" s="12" t="str">
@@ -2276,165 +2274,195 @@
       </c>
     </row>
     <row r="23" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="134" t="s">
+      <c r="A23" s="123" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="136"/>
-      <c r="C23" s="136"/>
-      <c r="D23" s="136"/>
-      <c r="E23" s="136"/>
-      <c r="F23" s="136"/>
-      <c r="G23" s="135"/>
+      <c r="B23" s="127"/>
+      <c r="C23" s="127"/>
+      <c r="D23" s="127"/>
+      <c r="E23" s="127"/>
+      <c r="F23" s="127"/>
+      <c r="G23" s="124"/>
       <c r="H23" s="34"/>
       <c r="I23" s="34"/>
       <c r="J23" s="12"/>
-      <c r="K23" s="134" t="s">
+      <c r="K23" s="123" t="s">
         <v>23</v>
       </c>
-      <c r="L23" s="136"/>
-      <c r="M23" s="136"/>
-      <c r="N23" s="136"/>
-      <c r="O23" s="136"/>
-      <c r="P23" s="136"/>
-      <c r="Q23" s="135"/>
+      <c r="L23" s="127"/>
+      <c r="M23" s="127"/>
+      <c r="N23" s="127"/>
+      <c r="O23" s="127"/>
+      <c r="P23" s="127"/>
+      <c r="Q23" s="124"/>
       <c r="R23" s="12"/>
     </row>
     <row r="24" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="137" t="s">
+      <c r="A24" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="B24" s="138"/>
-      <c r="C24" s="121"/>
-      <c r="D24" s="122"/>
-      <c r="E24" s="122"/>
-      <c r="F24" s="122"/>
-      <c r="G24" s="123"/>
+      <c r="B24" s="129"/>
+      <c r="C24">
+        <v>92.975423662834444</v>
+      </c>
+      <c r="D24">
+        <v>92.044247787610615</v>
+      </c>
+      <c r="E24">
+        <v>90.162250538499464</v>
+      </c>
+      <c r="F24">
+        <v>76.396687399256635</v>
+      </c>
+      <c r="G24">
+        <v>53.479289036525692</v>
+      </c>
       <c r="H24" s="34" cm="1">
-        <f t="array" ref="H24">-SUMPRODUCT((D6:F6-C6:E6)*(C24:E24+D24:F24)/2)</f>
-        <v>0</v>
+        <f t="array" ref="H24">-SUMPRODUCT((D1:F1-C1:E1)*(C24:E24+D24:F24)/2)</f>
+        <v>79.44066377448479</v>
       </c>
       <c r="I24" s="34" cm="1">
-        <f t="array" ref="I24">-SUMPRODUCT((D6:G6-C6:F6)*(C24:F24+D24:G24)/2)</f>
-        <v>0</v>
+        <f t="array" ref="I24">-SUMPRODUCT((D1:F1-C1:E1)*(C24:E24+D24:F24)/2)</f>
+        <v>79.44066377448479</v>
       </c>
       <c r="J24" s="12" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C24:G24)&amp;","</f>
-        <v xml:space="preserve">    ,</v>
-      </c>
-      <c r="K24" s="137" t="s">
+        <v xml:space="preserve">    92.9754236628344, 92.0442477876106, 90.1622505384995, 76.3966873992566, 53.4792890365257,</v>
+      </c>
+      <c r="K24" s="128" t="s">
         <v>7</v>
       </c>
-      <c r="L24" s="138"/>
-      <c r="M24" s="82">
-        <v>3.5338969773137729</v>
+      <c r="L24" s="129"/>
+      <c r="M24">
+        <v>3.5495358905530332</v>
       </c>
       <c r="N24">
-        <v>3.7216965755259852</v>
+        <v>3.3447316885202891</v>
       </c>
       <c r="O24">
-        <v>3.7478593835578962</v>
+        <v>3.709370743803551</v>
       </c>
       <c r="P24">
-        <v>6.7863547394302319</v>
-      </c>
-      <c r="Q24" s="83">
-        <v>8.2097242202983072</v>
+        <v>6.7029737079824372</v>
+      </c>
+      <c r="Q24">
+        <v>7.0274491383815452</v>
       </c>
       <c r="R24" s="12" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M24:Q24)&amp;","</f>
-        <v xml:space="preserve">    3.53389697731377, 3.72169657552599, 3.7478593835579, 6.78635473943023, 8.20972422029831,</v>
+        <v xml:space="preserve">    3.54953589055303, 3.34473168852029, 3.70937074380355, 6.70297370798244, 7.02744913838155,</v>
       </c>
     </row>
     <row r="25" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="139" t="s">
+      <c r="A25" s="125" t="s">
         <v>8</v>
       </c>
-      <c r="B25" s="140"/>
-      <c r="C25" s="121"/>
-      <c r="D25" s="122"/>
-      <c r="E25" s="122"/>
-      <c r="F25" s="122"/>
-      <c r="G25" s="123"/>
+      <c r="B25" s="126"/>
+      <c r="C25">
+        <v>89.994106062047834</v>
+      </c>
+      <c r="D25">
+        <v>88.872173058013772</v>
+      </c>
+      <c r="E25">
+        <v>88.072967759236676</v>
+      </c>
+      <c r="F25">
+        <v>74.378786437022228</v>
+      </c>
+      <c r="G25">
+        <v>49.976311790471087</v>
+      </c>
       <c r="H25" s="34" cm="1">
-        <f t="array" ref="H25">-SUMPRODUCT((D6:F6-C6:E6)*(C25:E25+D25:F25)/2)</f>
-        <v>0</v>
+        <f t="array" ref="H25">-SUMPRODUCT((D1:F1-C1:E1)*(C25:E25+D25:F25)/2)</f>
+        <v>76.987947019437897</v>
       </c>
       <c r="I25" s="34" cm="1">
-        <f t="array" ref="I25">-SUMPRODUCT((D6:G6-C6:F6)*(C25:F25+D25:G25)/2)</f>
-        <v>0</v>
+        <f t="array" ref="I25">-SUMPRODUCT((D1:F1-C1:E1)*(C25:E25+D25:F25)/2)</f>
+        <v>76.987947019437897</v>
       </c>
       <c r="J25" s="12" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C25:G25)&amp;","</f>
-        <v xml:space="preserve">    ,</v>
-      </c>
-      <c r="K25" s="134" t="s">
+        <v xml:space="preserve">    89.9941060620478, 88.8721730580138, 88.0729677592367, 74.3787864370222, 49.9763117904711,</v>
+      </c>
+      <c r="K25" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="L25" s="135"/>
-      <c r="M25" s="82">
-        <v>3.0404967647063641</v>
+      <c r="L25" s="124"/>
+      <c r="M25">
+        <v>2.7058137956739952</v>
       </c>
       <c r="N25">
-        <v>3.2195663824364602</v>
+        <v>2.5936421489117918</v>
       </c>
       <c r="O25">
-        <v>5.1059080333021827</v>
+        <v>2.42672800519615</v>
       </c>
       <c r="P25">
-        <v>3.323723681934811</v>
-      </c>
-      <c r="Q25" s="83">
-        <v>4.2607284397566696</v>
+        <v>3.729228486529601</v>
+      </c>
+      <c r="Q25">
+        <v>2.7682145351675702</v>
       </c>
       <c r="R25" s="12" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M25:Q25)&amp;","</f>
-        <v xml:space="preserve">    3.04049676470636, 3.21956638243646, 5.10590803330218, 3.32372368193481, 4.26072843975667,</v>
+        <v xml:space="preserve">    2.705813795674, 2.59364214891179, 2.42672800519615, 3.7292284865296, 2.76821453516757,</v>
       </c>
     </row>
     <row r="26" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="134" t="s">
+      <c r="A26" s="123" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="135"/>
-      <c r="C26" s="121"/>
-      <c r="D26" s="122"/>
-      <c r="E26" s="122"/>
-      <c r="F26" s="122"/>
-      <c r="G26" s="123"/>
+      <c r="B26" s="124"/>
+      <c r="C26">
+        <v>93.745335167259228</v>
+      </c>
+      <c r="D26">
+        <v>92.527080684088972</v>
+      </c>
+      <c r="E26">
+        <v>90.728625103446703</v>
+      </c>
+      <c r="F26">
+        <v>73.396918081759623</v>
+      </c>
+      <c r="G26">
+        <v>55.869494257447442</v>
+      </c>
       <c r="H26" s="34" cm="1">
-        <f t="array" ref="H26">-SUMPRODUCT((D6:F6-C6:E6)*(C26:E26+D26:F26)/2)</f>
-        <v>0</v>
+        <f t="array" ref="H26">-SUMPRODUCT((D1:F1-C1:E1)*(C26:E26+D26:F26)/2)</f>
+        <v>79.732913635354407</v>
       </c>
       <c r="I26" s="34" cm="1">
-        <f t="array" ref="I26">-SUMPRODUCT((D6:G6-C6:F6)*(C26:F26+D26:G26)/2)</f>
-        <v>0</v>
+        <f t="array" ref="I26">-SUMPRODUCT((D1:F1-C1:E1)*(C26:E26+D26:F26)/2)</f>
+        <v>79.732913635354407</v>
       </c>
       <c r="J26" s="12" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C26:G26)&amp;","</f>
-        <v xml:space="preserve">    ,</v>
-      </c>
-      <c r="K26" s="134" t="s">
+        <v xml:space="preserve">    93.7453351672592, 92.527080684089, 90.7286251034467, 73.3969180817596, 55.8694942574474,</v>
+      </c>
+      <c r="K26" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="L26" s="135"/>
-      <c r="M26" s="82">
-        <v>3.3471189071482028</v>
+      <c r="L26" s="124"/>
+      <c r="M26">
+        <v>3.2813687789549171</v>
       </c>
       <c r="N26">
-        <v>3.632082464261972</v>
+        <v>3.1827251453906529</v>
       </c>
       <c r="O26">
-        <v>3.8019445786359811</v>
+        <v>3.706870006136624</v>
       </c>
       <c r="P26">
-        <v>7.5417080235248886</v>
-      </c>
-      <c r="Q26" s="83">
-        <v>8.4137702230121008</v>
+        <v>8.2308689720279524</v>
+      </c>
+      <c r="Q26">
+        <v>7.757674526307957</v>
       </c>
       <c r="R26" s="12" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M26:Q26)&amp;","</f>
-        <v xml:space="preserve">    3.3471189071482, 3.63208246426197, 3.80194457863598, 7.54170802352489, 8.4137702230121,</v>
+        <v xml:space="preserve">    3.28136877895492, 3.18272514539065, 3.70687000613662, 8.23086897202795, 7.75767452630796,</v>
       </c>
     </row>
     <row r="27" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.25">
@@ -2504,23 +2532,23 @@
       <c r="R28" s="1"/>
     </row>
     <row r="29" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="124" t="s">
+      <c r="A29" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="125"/>
-      <c r="C29" s="79">
+      <c r="B29" s="132"/>
+      <c r="C29" s="77">
         <v>92.485449200300948</v>
       </c>
-      <c r="D29" s="80">
+      <c r="D29" s="78">
         <v>92.185357970009463</v>
       </c>
-      <c r="E29" s="80">
+      <c r="E29" s="78">
         <v>90.049361274020285</v>
       </c>
-      <c r="F29" s="80">
+      <c r="F29" s="78">
         <v>76.424179894802663</v>
       </c>
-      <c r="G29" s="81">
+      <c r="G29" s="79">
         <v>55.817166373785298</v>
       </c>
       <c r="H29" s="38"/>
@@ -2529,23 +2557,23 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C29:G29)&amp;","</f>
         <v xml:space="preserve">    92.4854492003009, 92.1853579700095, 90.0493612740203, 76.4241798948027, 55.8171663737853,</v>
       </c>
-      <c r="K29" s="124" t="s">
+      <c r="K29" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="L29" s="125"/>
-      <c r="M29" s="79">
+      <c r="L29" s="132"/>
+      <c r="M29" s="77">
         <v>4.0542209595909764</v>
       </c>
-      <c r="N29" s="80">
+      <c r="N29" s="78">
         <v>4.1862833242412467</v>
       </c>
-      <c r="O29" s="80">
+      <c r="O29" s="78">
         <v>4.5232246954320994</v>
       </c>
-      <c r="P29" s="80">
+      <c r="P29" s="78">
         <v>8.3692490038067824</v>
       </c>
-      <c r="Q29" s="81">
+      <c r="Q29" s="79">
         <v>9.4522568492704835</v>
       </c>
       <c r="R29" s="1" t="str">
@@ -2554,11 +2582,11 @@
       </c>
     </row>
     <row r="30" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="124" t="s">
+      <c r="A30" s="131" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="125"/>
-      <c r="C30" s="82">
+      <c r="B30" s="132"/>
+      <c r="C30" s="80">
         <v>93.221737995090834</v>
       </c>
       <c r="D30">
@@ -2570,7 +2598,7 @@
       <c r="F30">
         <v>72.290420081448175</v>
       </c>
-      <c r="G30" s="83">
+      <c r="G30" s="81">
         <v>51.841305264174281</v>
       </c>
       <c r="H30" s="38"/>
@@ -2579,11 +2607,11 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C30:G30)&amp;","</f>
         <v xml:space="preserve">    93.2217379950908, 91.8880330056846, 90.0239389840154, 72.2904200814482, 51.8413052641743,</v>
       </c>
-      <c r="K30" s="124" t="s">
+      <c r="K30" s="131" t="s">
         <v>6</v>
       </c>
-      <c r="L30" s="125"/>
-      <c r="M30" s="82">
+      <c r="L30" s="132"/>
+      <c r="M30" s="80">
         <v>3.877808098377264</v>
       </c>
       <c r="N30">
@@ -2595,7 +2623,7 @@
       <c r="P30">
         <v>9.3469718907111154</v>
       </c>
-      <c r="Q30" s="83">
+      <c r="Q30" s="81">
         <v>8.4900588367667034</v>
       </c>
       <c r="R30" s="1" t="str">
@@ -2604,23 +2632,23 @@
       </c>
     </row>
     <row r="31" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="128" t="s">
+      <c r="A31" s="133" t="s">
         <v>10</v>
       </c>
-      <c r="B31" s="129"/>
-      <c r="C31" s="84">
+      <c r="B31" s="134"/>
+      <c r="C31" s="82">
         <v>88.242190127710941</v>
       </c>
-      <c r="D31" s="85">
+      <c r="D31" s="83">
         <v>87.235659245723795</v>
       </c>
-      <c r="E31" s="85">
+      <c r="E31" s="83">
         <v>86.840356363138071</v>
       </c>
-      <c r="F31" s="85">
+      <c r="F31" s="83">
         <v>74.54100008231579</v>
       </c>
-      <c r="G31" s="86">
+      <c r="G31" s="84">
         <v>48.979529992306112</v>
       </c>
       <c r="H31" s="38"/>
@@ -2629,23 +2657,23 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C31:G31)&amp;","</f>
         <v xml:space="preserve">    88.2421901277109, 87.2356592457238, 86.8403563631381, 74.5410000823158, 48.9795299923061,</v>
       </c>
-      <c r="K31" s="128" t="s">
+      <c r="K31" s="133" t="s">
         <v>10</v>
       </c>
-      <c r="L31" s="129"/>
-      <c r="M31" s="84">
+      <c r="L31" s="134"/>
+      <c r="M31" s="82">
         <v>3.345739818904093</v>
       </c>
-      <c r="N31" s="85">
+      <c r="N31" s="83">
         <v>2.427737239251389</v>
       </c>
-      <c r="O31" s="85">
+      <c r="O31" s="83">
         <v>1.707344435820553</v>
       </c>
-      <c r="P31" s="85">
+      <c r="P31" s="83">
         <v>2.910710341880129</v>
       </c>
-      <c r="Q31" s="86">
+      <c r="Q31" s="84">
         <v>2.034771708486713</v>
       </c>
       <c r="R31" s="1" t="str">
@@ -2654,83 +2682,83 @@
       </c>
     </row>
     <row r="32" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="124" t="s">
+      <c r="A32" s="131" t="s">
         <v>12</v>
       </c>
-      <c r="B32" s="125"/>
-      <c r="C32" s="129"/>
-      <c r="D32" s="129"/>
-      <c r="E32" s="129"/>
-      <c r="F32" s="129"/>
-      <c r="G32" s="130"/>
+      <c r="B32" s="132"/>
+      <c r="C32" s="134"/>
+      <c r="D32" s="134"/>
+      <c r="E32" s="134"/>
+      <c r="F32" s="134"/>
+      <c r="G32" s="135"/>
       <c r="H32" s="38"/>
       <c r="I32" s="38"/>
       <c r="J32" s="1"/>
-      <c r="K32" s="124" t="s">
+      <c r="K32" s="131" t="s">
         <v>12</v>
       </c>
-      <c r="L32" s="125"/>
-      <c r="M32" s="129"/>
-      <c r="N32" s="129"/>
-      <c r="O32" s="129"/>
-      <c r="P32" s="129"/>
-      <c r="Q32" s="130"/>
+      <c r="L32" s="132"/>
+      <c r="M32" s="134"/>
+      <c r="N32" s="134"/>
+      <c r="O32" s="134"/>
+      <c r="P32" s="134"/>
+      <c r="Q32" s="135"/>
       <c r="R32" s="1"/>
     </row>
     <row r="33" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="141" t="s">
+      <c r="A33" s="120" t="s">
         <v>11</v>
       </c>
-      <c r="B33" s="78" t="s">
+      <c r="B33" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="C33" s="79">
+      <c r="C33" s="77">
         <v>92.96850376823356</v>
       </c>
-      <c r="D33" s="80">
+      <c r="D33" s="78">
         <v>92.40153506683653</v>
       </c>
-      <c r="E33" s="80">
+      <c r="E33" s="78">
         <v>90.677668832287424</v>
       </c>
-      <c r="F33" s="80">
+      <c r="F33" s="78">
         <v>74.017532689742268</v>
       </c>
-      <c r="G33" s="81">
+      <c r="G33" s="79">
         <v>53.92352732591884</v>
       </c>
       <c r="H33" s="38"/>
       <c r="I33" s="38"/>
       <c r="J33" s="1"/>
-      <c r="K33" s="141" t="s">
+      <c r="K33" s="120" t="s">
         <v>11</v>
       </c>
-      <c r="L33" s="78" t="s">
+      <c r="L33" s="76" t="s">
         <v>17</v>
       </c>
-      <c r="M33" s="79">
+      <c r="M33" s="77">
         <v>3.8454600924080049</v>
       </c>
-      <c r="N33" s="80">
+      <c r="N33" s="78">
         <v>4.0669297112418992</v>
       </c>
-      <c r="O33" s="80">
+      <c r="O33" s="78">
         <v>3.8537049252854398</v>
       </c>
-      <c r="P33" s="80">
+      <c r="P33" s="78">
         <v>8.7041298457857419</v>
       </c>
-      <c r="Q33" s="81">
+      <c r="Q33" s="79">
         <v>9.6394684933662074</v>
       </c>
       <c r="R33" s="1"/>
     </row>
     <row r="34" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="142"/>
-      <c r="B34" s="89" t="s">
+      <c r="A34" s="121"/>
+      <c r="B34" s="86" t="s">
         <v>13</v>
       </c>
-      <c r="C34" s="82">
+      <c r="C34" s="80">
         <v>92.884757186814937</v>
       </c>
       <c r="D34">
@@ -2742,7 +2770,7 @@
       <c r="F34">
         <v>76.864790806262661</v>
       </c>
-      <c r="G34" s="83">
+      <c r="G34" s="81">
         <v>54.700390036572337</v>
       </c>
       <c r="H34" s="38"/>
@@ -2751,11 +2779,11 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C34:G34)&amp;","</f>
         <v xml:space="preserve">    92.8847571868149, 92.3354362154591, 90.9231205519105, 76.8647908062627, 54.7003900365723,</v>
       </c>
-      <c r="K34" s="142"/>
-      <c r="L34" s="89" t="s">
+      <c r="K34" s="121"/>
+      <c r="L34" s="86" t="s">
         <v>13</v>
       </c>
-      <c r="M34" s="82">
+      <c r="M34" s="80">
         <v>3.9275095693540201</v>
       </c>
       <c r="N34">
@@ -2767,7 +2795,7 @@
       <c r="P34">
         <v>7.9334375921235116</v>
       </c>
-      <c r="Q34" s="83">
+      <c r="Q34" s="81">
         <v>9.3194201516218254</v>
       </c>
       <c r="R34" s="1" t="str">
@@ -2776,11 +2804,11 @@
       </c>
     </row>
     <row r="35" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="142"/>
-      <c r="B35" s="78" t="s">
+      <c r="A35" s="121"/>
+      <c r="B35" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="C35" s="82">
+      <c r="C35" s="80">
         <v>92.328683900261311</v>
       </c>
       <c r="D35">
@@ -2792,7 +2820,7 @@
       <c r="F35">
         <v>81.998727124399025</v>
       </c>
-      <c r="G35" s="83">
+      <c r="G35" s="81">
         <v>56.932651064742558</v>
       </c>
       <c r="H35" s="38"/>
@@ -2801,11 +2829,11 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C35:G35)&amp;","</f>
         <v xml:space="preserve">    92.3286839002613, 92.0520391167916, 90.7229467757102, 81.998727124399, 56.9326510647426,</v>
       </c>
-      <c r="K35" s="142"/>
-      <c r="L35" s="78" t="s">
+      <c r="K35" s="121"/>
+      <c r="L35" s="76" t="s">
         <v>14</v>
       </c>
-      <c r="M35" s="82">
+      <c r="M35" s="80">
         <v>3.6425445085490389</v>
       </c>
       <c r="N35">
@@ -2817,7 +2845,7 @@
       <c r="P35">
         <v>4.6860855472410874</v>
       </c>
-      <c r="Q35" s="83">
+      <c r="Q35" s="81">
         <v>6.5118967468904154</v>
       </c>
       <c r="R35" s="1" t="str">
@@ -2826,11 +2854,11 @@
       </c>
     </row>
     <row r="36" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="142"/>
-      <c r="B36" s="78" t="s">
+      <c r="A36" s="121"/>
+      <c r="B36" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="C36" s="82">
+      <c r="C36" s="80">
         <v>93.343840114066111</v>
       </c>
       <c r="D36">
@@ -2842,17 +2870,17 @@
       <c r="F36">
         <v>75.418279728826036</v>
       </c>
-      <c r="G36" s="83">
+      <c r="G36" s="81">
         <v>54.024842451700351</v>
       </c>
       <c r="H36" s="38"/>
       <c r="I36" s="38"/>
       <c r="J36" s="1"/>
-      <c r="K36" s="142"/>
-      <c r="L36" s="78" t="s">
+      <c r="K36" s="121"/>
+      <c r="L36" s="76" t="s">
         <v>15</v>
       </c>
-      <c r="M36" s="82">
+      <c r="M36" s="80">
         <v>3.867155660480134</v>
       </c>
       <c r="N36">
@@ -2864,17 +2892,17 @@
       <c r="P36">
         <v>8.3745003498256878</v>
       </c>
-      <c r="Q36" s="83">
+      <c r="Q36" s="81">
         <v>9.3705924310602366</v>
       </c>
       <c r="R36" s="1"/>
     </row>
     <row r="37" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="142"/>
-      <c r="B37" s="78" t="s">
+      <c r="A37" s="121"/>
+      <c r="B37" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="C37" s="82">
+      <c r="C37" s="80">
         <v>93.17956577363725</v>
       </c>
       <c r="D37">
@@ -2886,17 +2914,17 @@
       <c r="F37">
         <v>73.029683164461161</v>
       </c>
-      <c r="G37" s="83">
+      <c r="G37" s="81">
         <v>54.393186167944343</v>
       </c>
       <c r="H37" s="38"/>
       <c r="I37" s="38"/>
       <c r="J37" s="1"/>
-      <c r="K37" s="142"/>
-      <c r="L37" s="78" t="s">
+      <c r="K37" s="121"/>
+      <c r="L37" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="M37" s="82">
+      <c r="M37" s="80">
         <v>3.743131605295734</v>
       </c>
       <c r="N37">
@@ -2908,17 +2936,17 @@
       <c r="P37">
         <v>9.1240722898599991</v>
       </c>
-      <c r="Q37" s="83">
+      <c r="Q37" s="81">
         <v>8.7084512165137298</v>
       </c>
       <c r="R37" s="1"/>
     </row>
     <row r="38" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="142"/>
-      <c r="B38" s="78" t="s">
+      <c r="A38" s="121"/>
+      <c r="B38" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="C38" s="82">
+      <c r="C38" s="80">
         <v>90.924141700367642</v>
       </c>
       <c r="D38">
@@ -2930,17 +2958,17 @@
       <c r="F38">
         <v>80.742066180975286</v>
       </c>
-      <c r="G38" s="83">
+      <c r="G38" s="81">
         <v>54.139653004991288</v>
       </c>
       <c r="H38" s="38"/>
       <c r="I38" s="38"/>
       <c r="J38" s="1"/>
-      <c r="K38" s="142"/>
-      <c r="L38" s="78" t="s">
+      <c r="K38" s="121"/>
+      <c r="L38" s="76" t="s">
         <v>25</v>
       </c>
-      <c r="M38" s="82">
+      <c r="M38" s="80">
         <v>3.2766682411196539</v>
       </c>
       <c r="N38">
@@ -2952,17 +2980,17 @@
       <c r="P38">
         <v>4.2888241274046361</v>
       </c>
-      <c r="Q38" s="83">
+      <c r="Q38" s="81">
         <v>6.6722118847395508</v>
       </c>
       <c r="R38" s="1"/>
     </row>
     <row r="39" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="142"/>
-      <c r="B39" s="78" t="s">
+      <c r="A39" s="121"/>
+      <c r="B39" s="76" t="s">
         <v>16</v>
       </c>
-      <c r="C39" s="82">
+      <c r="C39" s="80">
         <v>88.022061049133967</v>
       </c>
       <c r="D39">
@@ -2974,17 +3002,17 @@
       <c r="F39">
         <v>75.166534149020336</v>
       </c>
-      <c r="G39" s="83">
+      <c r="G39" s="81">
         <v>49.417617539398499</v>
       </c>
       <c r="H39" s="38"/>
       <c r="I39" s="38"/>
       <c r="J39" s="1"/>
-      <c r="K39" s="142"/>
-      <c r="L39" s="78" t="s">
+      <c r="K39" s="121"/>
+      <c r="L39" s="76" t="s">
         <v>16</v>
       </c>
-      <c r="M39" s="82">
+      <c r="M39" s="80">
         <v>3.1059564342295989</v>
       </c>
       <c r="N39">
@@ -2996,17 +3024,17 @@
       <c r="P39">
         <v>3.4989537204184411</v>
       </c>
-      <c r="Q39" s="83">
+      <c r="Q39" s="81">
         <v>1.5086756884059249</v>
       </c>
       <c r="R39" s="1"/>
     </row>
     <row r="40" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="142"/>
-      <c r="B40" s="78" t="s">
+      <c r="A40" s="121"/>
+      <c r="B40" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="C40" s="82">
+      <c r="C40" s="80">
         <v>90.264167794210408</v>
       </c>
       <c r="D40">
@@ -3018,17 +3046,17 @@
       <c r="F40">
         <v>78.329165755951735</v>
       </c>
-      <c r="G40" s="83">
+      <c r="G40" s="81">
         <v>52.215737786802968</v>
       </c>
       <c r="H40" s="38"/>
       <c r="I40" s="38"/>
       <c r="J40" s="1"/>
-      <c r="K40" s="142"/>
-      <c r="L40" s="78" t="s">
+      <c r="K40" s="121"/>
+      <c r="L40" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="M40" s="82">
+      <c r="M40" s="80">
         <v>2.813777787794177</v>
       </c>
       <c r="N40">
@@ -3040,97 +3068,97 @@
       <c r="P40">
         <v>3.988565827203912</v>
       </c>
-      <c r="Q40" s="83">
+      <c r="Q40" s="81">
         <v>3.7859616126423878</v>
       </c>
       <c r="R40" s="1"/>
     </row>
     <row r="41" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="143"/>
-      <c r="B41" s="78" t="s">
+      <c r="A41" s="122"/>
+      <c r="B41" s="76" t="s">
         <v>26</v>
       </c>
-      <c r="C41" s="84">
+      <c r="C41" s="82">
         <v>88.816569678290051</v>
       </c>
-      <c r="D41" s="85">
+      <c r="D41" s="83">
         <v>88.13924460400689</v>
       </c>
-      <c r="E41" s="85">
+      <c r="E41" s="83">
         <v>87.754122925075478</v>
       </c>
-      <c r="F41" s="85">
+      <c r="F41" s="83">
         <v>76.74804506712546</v>
       </c>
-      <c r="G41" s="86">
+      <c r="G41" s="84">
         <v>50.462449044076237</v>
       </c>
       <c r="H41" s="38"/>
       <c r="I41" s="38"/>
       <c r="J41" s="1"/>
-      <c r="K41" s="143"/>
-      <c r="L41" s="78" t="s">
+      <c r="K41" s="122"/>
+      <c r="L41" s="76" t="s">
         <v>26</v>
       </c>
-      <c r="M41" s="84">
+      <c r="M41" s="82">
         <v>2.8080857507745329</v>
       </c>
-      <c r="N41" s="85">
+      <c r="N41" s="83">
         <v>2.4101693608449022</v>
       </c>
-      <c r="O41" s="85">
+      <c r="O41" s="83">
         <v>2.0261358563845731</v>
       </c>
-      <c r="P41" s="85">
+      <c r="P41" s="83">
         <v>3.1965959386571878</v>
       </c>
-      <c r="Q41" s="86">
+      <c r="Q41" s="84">
         <v>1.998032998184734</v>
       </c>
       <c r="R41" s="1"/>
     </row>
     <row r="42" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="124" t="s">
+      <c r="A42" s="131" t="s">
         <v>20</v>
       </c>
-      <c r="B42" s="125"/>
-      <c r="C42" s="132"/>
-      <c r="D42" s="132"/>
-      <c r="E42" s="132"/>
-      <c r="F42" s="132"/>
-      <c r="G42" s="132"/>
+      <c r="B42" s="132"/>
+      <c r="C42" s="136"/>
+      <c r="D42" s="136"/>
+      <c r="E42" s="136"/>
+      <c r="F42" s="136"/>
+      <c r="G42" s="136"/>
       <c r="H42" s="38"/>
       <c r="I42" s="38"/>
       <c r="J42" s="1"/>
-      <c r="K42" s="124" t="s">
+      <c r="K42" s="131" t="s">
         <v>20</v>
       </c>
-      <c r="L42" s="125"/>
-      <c r="M42" s="127"/>
-      <c r="N42" s="127"/>
-      <c r="O42" s="127"/>
-      <c r="P42" s="127"/>
-      <c r="Q42" s="133"/>
+      <c r="L42" s="132"/>
+      <c r="M42" s="137"/>
+      <c r="N42" s="137"/>
+      <c r="O42" s="137"/>
+      <c r="P42" s="137"/>
+      <c r="Q42" s="138"/>
       <c r="R42" s="1"/>
     </row>
     <row r="43" spans="1:18" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="124" t="s">
+      <c r="A43" s="131" t="s">
         <v>7</v>
       </c>
-      <c r="B43" s="125"/>
-      <c r="C43" s="79">
+      <c r="B43" s="132"/>
+      <c r="C43" s="77">
         <v>92.781043798288394</v>
       </c>
-      <c r="D43" s="80">
+      <c r="D43" s="78">
         <v>92.393805655393209</v>
       </c>
-      <c r="E43" s="80">
+      <c r="E43" s="78">
         <v>90.00908396624763</v>
       </c>
-      <c r="F43" s="80">
+      <c r="F43" s="78">
         <v>72.498171965203667</v>
       </c>
-      <c r="G43" s="81">
+      <c r="G43" s="79">
         <v>56.674852997991948</v>
       </c>
       <c r="H43" s="38"/>
@@ -3139,23 +3167,23 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C43:G43)&amp;","</f>
         <v xml:space="preserve">    92.7810437982884, 92.3938056553932, 90.0090839662476, 72.4981719652037, 56.6748529979919,</v>
       </c>
-      <c r="K43" s="126" t="s">
+      <c r="K43" s="139" t="s">
         <v>7</v>
       </c>
-      <c r="L43" s="127"/>
-      <c r="M43" s="79">
+      <c r="L43" s="137"/>
+      <c r="M43" s="77">
         <v>4.5014366094349993</v>
       </c>
-      <c r="N43" s="80">
+      <c r="N43" s="78">
         <v>4.2660991290099446</v>
       </c>
-      <c r="O43" s="80">
+      <c r="O43" s="78">
         <v>4.2894182874628113</v>
       </c>
-      <c r="P43" s="80">
+      <c r="P43" s="78">
         <v>9.3344724861133059</v>
       </c>
-      <c r="Q43" s="81">
+      <c r="Q43" s="79">
         <v>9.7546209717543917</v>
       </c>
       <c r="R43" s="1" t="str">
@@ -3164,11 +3192,11 @@
       </c>
     </row>
     <row r="44" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="124" t="s">
+      <c r="A44" s="131" t="s">
         <v>8</v>
       </c>
-      <c r="B44" s="125"/>
-      <c r="C44" s="82">
+      <c r="B44" s="132"/>
+      <c r="C44" s="80">
         <v>93.113144022293241</v>
       </c>
       <c r="D44">
@@ -3180,7 +3208,7 @@
       <c r="F44">
         <v>70.437814383158539</v>
       </c>
-      <c r="G44" s="83">
+      <c r="G44" s="81">
         <v>50.027165788274679</v>
       </c>
       <c r="H44" s="38"/>
@@ -3189,11 +3217,11 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C44:G44)&amp;","</f>
         <v xml:space="preserve">    93.1131440222932, 91.9496041120699, 88.043149271791, 70.4378143831585, 50.0271657882747,</v>
       </c>
-      <c r="K44" s="124" t="s">
+      <c r="K44" s="131" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="125"/>
-      <c r="M44" s="82">
+      <c r="L44" s="132"/>
+      <c r="M44" s="80">
         <v>4.249709534316878</v>
       </c>
       <c r="N44">
@@ -3205,7 +3233,7 @@
       <c r="P44">
         <v>10.497443911766959</v>
       </c>
-      <c r="Q44" s="83">
+      <c r="Q44" s="81">
         <v>10.803449952087821</v>
       </c>
       <c r="R44" s="1" t="str">
@@ -3214,23 +3242,23 @@
       </c>
     </row>
     <row r="45" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="124" t="s">
+      <c r="A45" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="B45" s="125"/>
-      <c r="C45" s="84">
+      <c r="B45" s="132"/>
+      <c r="C45" s="82">
         <v>92.587964837227005</v>
       </c>
-      <c r="D45" s="85">
+      <c r="D45" s="83">
         <v>91.423582441600061</v>
       </c>
-      <c r="E45" s="85">
+      <c r="E45" s="83">
         <v>88.545464929422721</v>
       </c>
-      <c r="F45" s="85">
+      <c r="F45" s="83">
         <v>71.659800595038618</v>
       </c>
-      <c r="G45" s="86">
+      <c r="G45" s="84">
         <v>50.266469026560699</v>
       </c>
       <c r="H45" s="38"/>
@@ -3239,11 +3267,11 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C45:G45)&amp;","</f>
         <v xml:space="preserve">    92.587964837227, 91.4235824416001, 88.5454649294227, 71.6598005950386, 50.2664690265607,</v>
       </c>
-      <c r="K45" s="124" t="s">
+      <c r="K45" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="L45" s="125"/>
-      <c r="M45" s="82">
+      <c r="L45" s="132"/>
+      <c r="M45" s="80">
         <v>3.7645606938355249</v>
       </c>
       <c r="N45">
@@ -3255,7 +3283,7 @@
       <c r="P45">
         <v>10.46873255591585</v>
       </c>
-      <c r="Q45" s="83">
+      <c r="Q45" s="81">
         <v>9.9892548989807413</v>
       </c>
       <c r="R45" s="1" t="str">
@@ -3263,259 +3291,353 @@
         <v xml:space="preserve">    3.76456069383552, 4.48859041630367, 4.68420356678647, 10.4687325559158, 9.98925489898074,</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="128" t="s">
-        <v>22</v>
-      </c>
-      <c r="B46" s="130"/>
-      <c r="C46" s="87"/>
-      <c r="D46" s="38"/>
-      <c r="E46" s="38"/>
-      <c r="F46" s="38"/>
-      <c r="G46" s="38"/>
-      <c r="H46" s="43"/>
-      <c r="I46" s="43"/>
-      <c r="J46" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C46:G46)&amp;","</f>
-        <v xml:space="preserve">    ,</v>
-      </c>
-      <c r="K46" s="128" t="s">
-        <v>22</v>
-      </c>
-      <c r="L46" s="129"/>
-      <c r="M46" s="39"/>
-      <c r="N46" s="40"/>
-      <c r="O46" s="40"/>
-      <c r="P46" s="40"/>
-      <c r="Q46" s="91"/>
-      <c r="R46" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M46:Q46)&amp;","</f>
-        <v xml:space="preserve">    ,</v>
-      </c>
+    <row r="46" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="131" t="s">
+        <v>23</v>
+      </c>
+      <c r="B46" s="132"/>
+      <c r="C46" s="132"/>
+      <c r="D46" s="132"/>
+      <c r="E46" s="132"/>
+      <c r="F46" s="132"/>
+      <c r="G46" s="140"/>
+      <c r="H46" s="38"/>
+      <c r="I46" s="38"/>
+      <c r="J46" s="1"/>
+      <c r="K46" s="131" t="s">
+        <v>23</v>
+      </c>
+      <c r="L46" s="132"/>
+      <c r="M46" s="132"/>
+      <c r="N46" s="132"/>
+      <c r="O46" s="132"/>
+      <c r="P46" s="132"/>
+      <c r="Q46" s="140"/>
+      <c r="R46" s="1"/>
     </row>
     <row r="47" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="124" t="s">
-        <v>23</v>
-      </c>
-      <c r="B47" s="125"/>
-      <c r="C47" s="125"/>
-      <c r="D47" s="125"/>
-      <c r="E47" s="125"/>
-      <c r="F47" s="125"/>
-      <c r="G47" s="131"/>
+      <c r="A47" s="139" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" s="137"/>
+      <c r="C47" s="77">
+        <v>92.779242983398433</v>
+      </c>
+      <c r="D47" s="78">
+        <v>92.240270194904923</v>
+      </c>
+      <c r="E47" s="78">
+        <v>90.552301433559194</v>
+      </c>
+      <c r="F47" s="78">
+        <v>77.44681530627544</v>
+      </c>
+      <c r="G47" s="79">
+        <v>54.049481297537007</v>
+      </c>
       <c r="H47" s="38"/>
       <c r="I47" s="38"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="124" t="s">
-        <v>23</v>
-      </c>
-      <c r="L47" s="125"/>
-      <c r="M47" s="125"/>
-      <c r="N47" s="125"/>
-      <c r="O47" s="125"/>
-      <c r="P47" s="125"/>
-      <c r="Q47" s="131"/>
-      <c r="R47" s="1"/>
+      <c r="J47" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C47:G47)&amp;","</f>
+        <v xml:space="preserve">    92.7792429833984, 92.2402701949049, 90.5523014335592, 77.4468153062754, 54.049481297537,</v>
+      </c>
+      <c r="K47" s="139" t="s">
+        <v>7</v>
+      </c>
+      <c r="L47" s="137"/>
+      <c r="M47" s="77">
+        <v>3.8708284466838099</v>
+      </c>
+      <c r="N47" s="78">
+        <v>4.1159624538095514</v>
+      </c>
+      <c r="O47" s="78">
+        <v>4.0917292690559766</v>
+      </c>
+      <c r="P47" s="78">
+        <v>6.9723184162377478</v>
+      </c>
+      <c r="Q47" s="79">
+        <v>8.876523191689154</v>
+      </c>
+      <c r="R47" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M47:Q47)&amp;","</f>
+        <v xml:space="preserve">    3.87082844668381, 4.11596245380955, 4.09172926905598, 6.97231841623775, 8.87652319168915,</v>
+      </c>
     </row>
     <row r="48" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="126" t="s">
-        <v>7</v>
-      </c>
-      <c r="B48" s="127"/>
-      <c r="C48" s="79">
-        <v>92.779242983398433</v>
-      </c>
-      <c r="D48" s="80">
-        <v>92.240270194904923</v>
-      </c>
-      <c r="E48" s="80">
-        <v>90.552301433559194</v>
-      </c>
-      <c r="F48" s="80">
-        <v>77.44681530627544</v>
+      <c r="A48" s="133" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" s="134"/>
+      <c r="C48" s="80">
+        <v>91.529115829853595</v>
+      </c>
+      <c r="D48">
+        <v>91.350643423322225</v>
+      </c>
+      <c r="E48">
+        <v>89.341760932799787</v>
+      </c>
+      <c r="F48">
+        <v>79.045051998788765</v>
       </c>
       <c r="G48" s="81">
-        <v>54.049481297537007</v>
+        <v>52.319711731697872</v>
       </c>
       <c r="H48" s="38"/>
       <c r="I48" s="38"/>
       <c r="J48" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C48:G48)&amp;","</f>
-        <v xml:space="preserve">    92.7792429833984, 92.2402701949049, 90.5523014335592, 77.4468153062754, 54.049481297537,</v>
-      </c>
-      <c r="K48" s="126" t="s">
-        <v>7</v>
-      </c>
-      <c r="L48" s="127"/>
-      <c r="M48" s="79">
-        <v>3.8708284466838099</v>
-      </c>
-      <c r="N48" s="80">
-        <v>4.1159624538095514</v>
-      </c>
-      <c r="O48" s="80">
-        <v>4.0917292690559766</v>
-      </c>
-      <c r="P48" s="80">
-        <v>6.9723184162377478</v>
+        <v xml:space="preserve">    91.5291158298536, 91.3506434233222, 89.3417609327998, 79.0450519987888, 52.3197117316979,</v>
+      </c>
+      <c r="K48" s="131" t="s">
+        <v>8</v>
+      </c>
+      <c r="L48" s="132"/>
+      <c r="M48" s="80">
+        <v>3.326792742141544</v>
+      </c>
+      <c r="N48">
+        <v>3.370578982220036</v>
+      </c>
+      <c r="O48">
+        <v>5.5895882093977454</v>
+      </c>
+      <c r="P48">
+        <v>3.3906236766273481</v>
       </c>
       <c r="Q48" s="81">
-        <v>8.876523191689154</v>
+        <v>4.5139463885317248</v>
       </c>
       <c r="R48" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M48:Q48)&amp;","</f>
-        <v xml:space="preserve">    3.87082844668381, 4.11596245380955, 4.09172926905598, 6.97231841623775, 8.87652319168915,</v>
+        <v xml:space="preserve">    3.32679274214154, 3.37057898222004, 5.58958820939775, 3.39062367662735, 4.51394638853172,</v>
       </c>
     </row>
     <row r="49" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="128" t="s">
-        <v>8</v>
-      </c>
-      <c r="B49" s="129"/>
-      <c r="C49" s="82">
-        <v>91.529115829853595</v>
+      <c r="A49" s="131" t="s">
+        <v>21</v>
+      </c>
+      <c r="B49" s="132"/>
+      <c r="C49" s="80">
+        <v>92.904210456970588</v>
       </c>
       <c r="D49">
-        <v>91.350643423322225</v>
+        <v>92.1891124359732</v>
       </c>
       <c r="E49">
-        <v>89.341760932799787</v>
+        <v>90.496036698942376</v>
       </c>
       <c r="F49">
-        <v>79.045051998788765</v>
-      </c>
-      <c r="G49" s="83">
-        <v>52.319711731697872</v>
+        <v>77.336951327754974</v>
+      </c>
+      <c r="G49" s="81">
+        <v>56.222535937160863</v>
       </c>
       <c r="H49" s="38"/>
       <c r="I49" s="38"/>
       <c r="J49" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C49:G49)&amp;","</f>
-        <v xml:space="preserve">    91.5291158298536, 91.3506434233222, 89.3417609327998, 79.0450519987888, 52.3197117316979,</v>
-      </c>
-      <c r="K49" s="124" t="s">
-        <v>8</v>
-      </c>
-      <c r="L49" s="125"/>
-      <c r="M49" s="82">
-        <v>3.326792742141544</v>
+        <v xml:space="preserve">    92.9042104569706, 92.1891124359732, 90.4960366989424, 77.336951327755, 56.2225359371609,</v>
+      </c>
+      <c r="K49" s="131" t="s">
+        <v>21</v>
+      </c>
+      <c r="L49" s="132"/>
+      <c r="M49" s="80">
+        <v>3.6016716439248402</v>
       </c>
       <c r="N49">
-        <v>3.370578982220036</v>
+        <v>3.9740552459554821</v>
       </c>
       <c r="O49">
-        <v>5.5895882093977454</v>
+        <v>4.0466560589706821</v>
       </c>
       <c r="P49">
-        <v>3.3906236766273481</v>
-      </c>
-      <c r="Q49" s="83">
-        <v>4.5139463885317248</v>
+        <v>7.6607457787732498</v>
+      </c>
+      <c r="Q49" s="81">
+        <v>9.1988486675501449</v>
       </c>
       <c r="R49" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M49:Q49)&amp;","</f>
-        <v xml:space="preserve">    3.32679274214154, 3.37057898222004, 5.58958820939775, 3.39062367662735, 4.51394638853172,</v>
+        <v xml:space="preserve">    3.60167164392484, 3.97405524595548, 4.04665605897068, 7.66074577877325, 9.19884866755014,</v>
       </c>
     </row>
     <row r="50" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="124" t="s">
-        <v>21</v>
-      </c>
-      <c r="B50" s="125"/>
-      <c r="C50" s="82">
-        <v>92.904210456970588</v>
-      </c>
-      <c r="D50">
-        <v>92.1891124359732</v>
-      </c>
-      <c r="E50">
-        <v>90.496036698942376</v>
-      </c>
-      <c r="F50">
-        <v>77.336951327754974</v>
-      </c>
-      <c r="G50" s="83">
-        <v>56.222535937160863</v>
-      </c>
+      <c r="A50" s="131" t="s">
+        <v>24</v>
+      </c>
+      <c r="B50" s="132"/>
+      <c r="C50" s="132"/>
+      <c r="D50" s="132"/>
+      <c r="E50" s="132"/>
+      <c r="F50" s="132"/>
+      <c r="G50" s="140"/>
       <c r="H50" s="38"/>
       <c r="I50" s="38"/>
-      <c r="J50" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C50:G50)&amp;","</f>
-        <v xml:space="preserve">    92.9042104569706, 92.1891124359732, 90.4960366989424, 77.336951327755, 56.2225359371609,</v>
-      </c>
-      <c r="K50" s="124" t="s">
-        <v>21</v>
-      </c>
-      <c r="L50" s="125"/>
-      <c r="M50" s="82">
-        <v>3.6016716439248402</v>
-      </c>
-      <c r="N50">
-        <v>3.9740552459554821</v>
-      </c>
-      <c r="O50">
-        <v>4.0466560589706821</v>
-      </c>
-      <c r="P50">
-        <v>7.6607457787732498</v>
-      </c>
-      <c r="Q50" s="83">
-        <v>9.1988486675501449</v>
-      </c>
-      <c r="R50" s="1" t="str">
-        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M50:Q50)&amp;","</f>
-        <v xml:space="preserve">    3.60167164392484, 3.97405524595548, 4.04665605897068, 7.66074577877325, 9.19884866755014,</v>
-      </c>
+      <c r="J50" s="1"/>
+      <c r="K50" s="131" t="s">
+        <v>24</v>
+      </c>
+      <c r="L50" s="132"/>
+      <c r="M50" s="132"/>
+      <c r="N50" s="132"/>
+      <c r="O50" s="132"/>
+      <c r="P50" s="132"/>
+      <c r="Q50" s="140"/>
+      <c r="R50" s="1"/>
     </row>
     <row r="51" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="124" t="s">
-        <v>22</v>
-      </c>
-      <c r="B51" s="125"/>
-      <c r="C51" s="39"/>
-      <c r="D51" s="40"/>
-      <c r="E51" s="40"/>
-      <c r="F51" s="40"/>
-      <c r="G51" s="91"/>
+      <c r="A51" s="139" t="s">
+        <v>7</v>
+      </c>
+      <c r="B51" s="137"/>
+      <c r="C51">
+        <v>92.570848555845046</v>
+      </c>
+      <c r="D51">
+        <v>91.630054097616338</v>
+      </c>
+      <c r="E51">
+        <v>89.79275707341418</v>
+      </c>
+      <c r="F51">
+        <v>76.17214136905659</v>
+      </c>
+      <c r="G51">
+        <v>51.926306580162297</v>
+      </c>
       <c r="H51" s="38"/>
       <c r="I51" s="38"/>
       <c r="J51" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C51:G51)&amp;","</f>
-        <v xml:space="preserve">    ,</v>
-      </c>
-      <c r="K51" s="124" t="s">
-        <v>22</v>
-      </c>
-      <c r="L51" s="125"/>
-      <c r="M51" s="39"/>
-      <c r="N51" s="40"/>
-      <c r="O51" s="40"/>
-      <c r="P51" s="40"/>
-      <c r="Q51" s="91"/>
+        <v xml:space="preserve">    92.570848555845, 91.6300540976163, 89.7927570734142, 76.1721413690566, 51.9263065801623,</v>
+      </c>
+      <c r="K51" s="139" t="s">
+        <v>7</v>
+      </c>
+      <c r="L51" s="137"/>
+      <c r="M51">
+        <v>3.9499959320021021</v>
+      </c>
+      <c r="N51">
+        <v>3.687046549937286</v>
+      </c>
+      <c r="O51">
+        <v>3.9869395814007311</v>
+      </c>
+      <c r="P51">
+        <v>6.7230943957633427</v>
+      </c>
+      <c r="Q51">
+        <v>7.5980511109918547</v>
+      </c>
       <c r="R51" s="1" t="str">
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M51:Q51)&amp;","</f>
-        <v xml:space="preserve">    ,</v>
-      </c>
-    </row>
-    <row r="52" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="J52" s="11"/>
-      <c r="K52" s="11"/>
-      <c r="L52" s="11"/>
-      <c r="M52" s="11"/>
-      <c r="N52" s="11"/>
-      <c r="O52" s="11"/>
-      <c r="P52" s="11"/>
-      <c r="Q52" s="11"/>
-    </row>
-    <row r="53" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="J53" s="11"/>
-      <c r="K53" s="11"/>
-      <c r="L53" s="11"/>
-      <c r="M53" s="11"/>
-      <c r="N53" s="11"/>
-      <c r="O53" s="11"/>
-      <c r="P53" s="11"/>
-      <c r="Q53" s="11"/>
+        <v xml:space="preserve">    3.9499959320021, 3.68704654993729, 3.98693958140073, 6.72309439576334, 7.59805111099185,</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="133" t="s">
+        <v>8</v>
+      </c>
+      <c r="B52" s="134"/>
+      <c r="C52">
+        <v>89.680415246872897</v>
+      </c>
+      <c r="D52">
+        <v>88.422345528560356</v>
+      </c>
+      <c r="E52">
+        <v>87.839629305658192</v>
+      </c>
+      <c r="F52">
+        <v>74.072340833145091</v>
+      </c>
+      <c r="G52">
+        <v>48.786962024816582</v>
+      </c>
+      <c r="H52" s="38"/>
+      <c r="I52" s="38"/>
+      <c r="J52" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C52:G52)&amp;","</f>
+        <v xml:space="preserve">    89.6804152468729, 88.4223455285604, 87.8396293056582, 74.0723408331451, 48.7869620248166,</v>
+      </c>
+      <c r="K52" s="131" t="s">
+        <v>8</v>
+      </c>
+      <c r="L52" s="132"/>
+      <c r="M52">
+        <v>2.856200195635104</v>
+      </c>
+      <c r="N52">
+        <v>2.8101495747388969</v>
+      </c>
+      <c r="O52">
+        <v>2.5286856802679329</v>
+      </c>
+      <c r="P52">
+        <v>3.7511269974144361</v>
+      </c>
+      <c r="Q52">
+        <v>3.0728993155431739</v>
+      </c>
+      <c r="R52" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M52:Q52)&amp;","</f>
+        <v xml:space="preserve">    2.8562001956351, 2.8101495747389, 2.52868568026793, 3.75112699741444, 3.07289931554317,</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="131" t="s">
+        <v>21</v>
+      </c>
+      <c r="B53" s="132"/>
+      <c r="C53">
+        <v>93.356158779022067</v>
+      </c>
+      <c r="D53">
+        <v>92.090334953499195</v>
+      </c>
+      <c r="E53">
+        <v>90.283061574905688</v>
+      </c>
+      <c r="F53">
+        <v>73.007047896512162</v>
+      </c>
+      <c r="G53">
+        <v>53.767089209072303</v>
+      </c>
+      <c r="H53" s="38"/>
+      <c r="I53" s="38"/>
+      <c r="J53" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C53:G53)&amp;","</f>
+        <v xml:space="preserve">    93.3561587790221, 92.0903349534992, 90.2830615749057, 73.0070478965122, 53.7670892090723,</v>
+      </c>
+      <c r="K53" s="131" t="s">
+        <v>21</v>
+      </c>
+      <c r="L53" s="132"/>
+      <c r="M53">
+        <v>3.7078351435189272</v>
+      </c>
+      <c r="N53">
+        <v>3.5332042497139939</v>
+      </c>
+      <c r="O53">
+        <v>3.9393537211774352</v>
+      </c>
+      <c r="P53">
+        <v>8.314275724981675</v>
+      </c>
+      <c r="Q53">
+        <v>8.4462932852283163</v>
+      </c>
+      <c r="R53" s="1" t="str">
+        <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,M53:Q53)&amp;","</f>
+        <v xml:space="preserve">    3.70783514351893, 3.53320424971399, 3.93935372117744, 8.31427572498167, 8.44629328522832,</v>
+      </c>
     </row>
     <row r="54" spans="1:18" ht="15" x14ac:dyDescent="0.2">
       <c r="H54" s="11"/>
@@ -3541,32 +3663,60 @@
       <c r="P55" s="11"/>
       <c r="Q55" s="11"/>
     </row>
-    <row r="56" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="H56" s="11"/>
-      <c r="I56" s="11"/>
-      <c r="J56" s="11"/>
-      <c r="K56" s="11"/>
-      <c r="L56" s="11"/>
-      <c r="M56" s="11"/>
-      <c r="N56" s="11"/>
-      <c r="O56" s="11"/>
-      <c r="P56" s="11"/>
-      <c r="Q56" s="11"/>
-    </row>
-    <row r="57" spans="1:18" ht="15" x14ac:dyDescent="0.2">
-      <c r="H57" s="11"/>
-      <c r="I57" s="11"/>
-      <c r="J57" s="11"/>
-      <c r="K57" s="11"/>
-      <c r="L57" s="11"/>
-      <c r="M57" s="11"/>
-      <c r="N57" s="11"/>
-      <c r="O57" s="11"/>
-      <c r="P57" s="11"/>
-      <c r="Q57" s="11"/>
-    </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="68">
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="K51:L51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="K52:L52"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="K53:L53"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="K47:L47"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="K48:L48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="K49:L49"/>
+    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="K50:Q50"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="K45:L45"/>
+    <mergeCell ref="A46:G46"/>
+    <mergeCell ref="K46:Q46"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="K42:Q42"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="A32:G32"/>
+    <mergeCell ref="K32:Q32"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K29:L29"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="K23:Q23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="K19:Q19"/>
     <mergeCell ref="A33:A41"/>
     <mergeCell ref="K33:K41"/>
     <mergeCell ref="A2:B2"/>
@@ -3583,57 +3733,361 @@
     <mergeCell ref="K16:L16"/>
     <mergeCell ref="A6:A14"/>
     <mergeCell ref="K6:K14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="K19:Q19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="K29:L29"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="K23:Q23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="K32:Q32"/>
-    <mergeCell ref="A42:G42"/>
-    <mergeCell ref="K42:Q42"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="A44:B44"/>
-    <mergeCell ref="K44:L44"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="K45:L45"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="K46:L46"/>
-    <mergeCell ref="A47:G47"/>
-    <mergeCell ref="K47:Q47"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="K51:L51"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="K48:L48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="K49:L49"/>
-    <mergeCell ref="A50:B50"/>
-    <mergeCell ref="K50:L50"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C2:C4 C6:C14">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:G4 C6:G14">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:G4 H2:I26">
+    <cfRule type="colorScale" priority="400">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:G4">
+    <cfRule type="colorScale" priority="315">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="316">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="317">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C3:G4 H3:I6">
+    <cfRule type="colorScale" priority="297">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="298">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="299">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="300">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="301">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="302">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C7:G7">
+    <cfRule type="colorScale" priority="318">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="319">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C8:G14">
+    <cfRule type="colorScale" priority="320">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="321">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C16:G18">
+    <cfRule type="colorScale" priority="324">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="325">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="326">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C20:G22 C16:G18">
+    <cfRule type="colorScale" priority="322">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C20:G22">
+    <cfRule type="colorScale" priority="329">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="330">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="331">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C24:G26 C20:G22 C2:G4 C7:G14 C16:G18">
+    <cfRule type="colorScale" priority="382">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C24:G26 C20:G22 C6:G14 C2:G4 C16:G18">
+    <cfRule type="colorScale" priority="387">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C24:G26 C20:G22 C16:G18 C7:G14 C2:G4">
+    <cfRule type="colorScale" priority="392">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C24:G26 C20:G22 C16:G18">
+    <cfRule type="colorScale" priority="397">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C24:G26">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D4 D6:D14">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E4 E6:E14">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
@@ -3645,275 +4099,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:G4 C6:G14">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:G4">
-    <cfRule type="colorScale" priority="313">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="314">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="315">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C3:G4 H3:I6">
-    <cfRule type="colorScale" priority="295">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="296">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="297">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="298">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="299">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="300">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C7:G7">
-    <cfRule type="colorScale" priority="316">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="317">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C8:G14">
-    <cfRule type="colorScale" priority="318">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="319">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G22 C16:G18">
-    <cfRule type="colorScale" priority="320">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G18">
-    <cfRule type="colorScale" priority="322">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="323">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="324">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G22">
-    <cfRule type="colorScale" priority="327">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="328">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="329">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C24:G26">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D4 D6:D14">
+  <conditionalFormatting sqref="F2:F4 F6:F14">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="min"/>
@@ -3925,156 +4111,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E4 E6:E14">
+  <conditionalFormatting sqref="G2:G4 G6:G14">
     <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F4 F6:F14">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G4 G6:G14">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H47:H51">
-    <cfRule type="colorScale" priority="20">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="21">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="22">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I47:I51">
-    <cfRule type="colorScale" priority="56">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="307">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-    <cfRule type="colorScale" priority="308">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C24:G26 C20:G22 C2:G4 C7:G14 C16:G18">
-    <cfRule type="colorScale" priority="380">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C24:G26 C20:G22 C6:G14 C2:G4 C16:G18">
-    <cfRule type="colorScale" priority="385">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C24:G26 C20:G22 C16:G18 C7:G14 C2:G4">
-    <cfRule type="colorScale" priority="390">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C24:G26 C20:G22 C16:G18">
-    <cfRule type="colorScale" priority="395">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF5A8AC6"/>
-        <color rgb="FFFCFCFF"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C2:G4 H2:I26">
-    <cfRule type="colorScale" priority="398">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4099,6 +4137,70 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I26">
     <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H46:H53">
+    <cfRule type="colorScale" priority="401">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="402">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="403">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I46:I53">
+    <cfRule type="colorScale" priority="404">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="405">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF5A8AC6"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
+    </cfRule>
+    <cfRule type="colorScale" priority="406">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -4202,10 +4304,10 @@
       <c r="V1" s="12"/>
     </row>
     <row r="2" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="134" t="s">
+      <c r="A2" s="123" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="135"/>
+      <c r="B2" s="124"/>
       <c r="C2" s="20"/>
       <c r="D2" s="21"/>
       <c r="E2" s="21"/>
@@ -4225,10 +4327,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C2:I2)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M2" s="134" t="s">
+      <c r="M2" s="123" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="135"/>
+      <c r="N2" s="124"/>
       <c r="O2" s="31"/>
       <c r="P2" s="32"/>
       <c r="Q2" s="32"/>
@@ -4242,10 +4344,10 @@
       </c>
     </row>
     <row r="3" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="134" t="s">
+      <c r="A3" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="135"/>
+      <c r="B3" s="124"/>
       <c r="C3" s="31"/>
       <c r="D3" s="32"/>
       <c r="E3" s="32"/>
@@ -4265,10 +4367,10 @@
         <f t="shared" ref="L3:L18" si="0">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C3:I3)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M3" s="134" t="s">
+      <c r="M3" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="N3" s="135"/>
+      <c r="N3" s="124"/>
       <c r="O3" s="31"/>
       <c r="P3" s="32"/>
       <c r="Q3" s="32"/>
@@ -4282,10 +4384,10 @@
       </c>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="134" t="s">
+      <c r="A4" s="123" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="135"/>
+      <c r="B4" s="124"/>
       <c r="C4" s="24"/>
       <c r="D4" s="26"/>
       <c r="E4" s="26"/>
@@ -4305,11 +4407,11 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M4" s="134" t="s">
+      <c r="M4" s="123" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="135"/>
-      <c r="O4" s="41"/>
+      <c r="N4" s="124"/>
+      <c r="O4" s="39"/>
       <c r="P4" s="26"/>
       <c r="Q4" s="26"/>
       <c r="R4" s="26"/>
@@ -4322,47 +4424,47 @@
       </c>
     </row>
     <row r="5" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="123" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="136"/>
-      <c r="C5" s="136"/>
-      <c r="D5" s="136"/>
-      <c r="E5" s="136"/>
-      <c r="F5" s="136"/>
-      <c r="G5" s="136"/>
-      <c r="H5" s="136"/>
-      <c r="I5" s="135"/>
+      <c r="B5" s="127"/>
+      <c r="C5" s="127"/>
+      <c r="D5" s="127"/>
+      <c r="E5" s="127"/>
+      <c r="F5" s="127"/>
+      <c r="G5" s="127"/>
+      <c r="H5" s="127"/>
+      <c r="I5" s="124"/>
       <c r="J5" s="34"/>
       <c r="K5" s="34"/>
       <c r="L5" s="12"/>
-      <c r="M5" s="134" t="s">
+      <c r="M5" s="123" t="s">
         <v>12</v>
       </c>
-      <c r="N5" s="136"/>
-      <c r="O5" s="136"/>
-      <c r="P5" s="136"/>
-      <c r="Q5" s="136"/>
-      <c r="R5" s="136"/>
-      <c r="S5" s="136"/>
-      <c r="T5" s="136"/>
-      <c r="U5" s="135"/>
+      <c r="N5" s="127"/>
+      <c r="O5" s="127"/>
+      <c r="P5" s="127"/>
+      <c r="Q5" s="127"/>
+      <c r="R5" s="127"/>
+      <c r="S5" s="127"/>
+      <c r="T5" s="127"/>
+      <c r="U5" s="124"/>
       <c r="V5" s="12"/>
     </row>
     <row r="6" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="139" t="s">
+      <c r="A6" s="125" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="49"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="51"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="49"/>
       <c r="J6" s="34" cm="1">
         <f t="array" ref="J6">-SUMPRODUCT((D1:H1-C1:G1)*(C6:G6+D6:H6)/2)</f>
         <v>0</v>
@@ -4375,36 +4477,36 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M6" s="139" t="s">
+      <c r="M6" s="125" t="s">
         <v>11</v>
       </c>
       <c r="N6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="O6" s="49"/>
-      <c r="P6" s="50"/>
-      <c r="Q6" s="50"/>
-      <c r="R6" s="50"/>
-      <c r="S6" s="50"/>
-      <c r="T6" s="50"/>
-      <c r="U6" s="51"/>
+      <c r="O6" s="47"/>
+      <c r="P6" s="48"/>
+      <c r="Q6" s="48"/>
+      <c r="R6" s="48"/>
+      <c r="S6" s="48"/>
+      <c r="T6" s="48"/>
+      <c r="U6" s="49"/>
       <c r="V6" s="12" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">    ,</v>
       </c>
     </row>
     <row r="7" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="144"/>
+      <c r="A7" s="130"/>
       <c r="B7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="49"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="50"/>
-      <c r="I7" s="51"/>
+      <c r="C7" s="47"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="49"/>
       <c r="J7" s="34" cm="1">
         <f t="array" ref="J7">-SUMPRODUCT((D1:H1-C1:G1)*(C7:G7+D7:H7)/2)</f>
         <v>0</v>
@@ -4417,34 +4519,34 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M7" s="144"/>
+      <c r="M7" s="130"/>
       <c r="N7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="O7" s="49"/>
-      <c r="P7" s="50"/>
-      <c r="Q7" s="50"/>
-      <c r="R7" s="50"/>
-      <c r="S7" s="50"/>
-      <c r="T7" s="50"/>
-      <c r="U7" s="51"/>
+      <c r="O7" s="47"/>
+      <c r="P7" s="48"/>
+      <c r="Q7" s="48"/>
+      <c r="R7" s="48"/>
+      <c r="S7" s="48"/>
+      <c r="T7" s="48"/>
+      <c r="U7" s="49"/>
       <c r="V7" s="12" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">    ,</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="144"/>
+      <c r="A8" s="130"/>
       <c r="B8" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="49"/>
-      <c r="D8" s="50"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="51"/>
+      <c r="C8" s="47"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="49"/>
       <c r="J8" s="34" cm="1">
         <f t="array" ref="J8">-SUMPRODUCT((D1:H1-C1:G1)*(C8:G8+D8:H8)/2)</f>
         <v>0</v>
@@ -4457,31 +4559,31 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M8" s="144"/>
+      <c r="M8" s="130"/>
       <c r="N8" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="O8" s="49"/>
-      <c r="P8" s="50"/>
-      <c r="Q8" s="50"/>
-      <c r="R8" s="50"/>
-      <c r="S8" s="50"/>
-      <c r="T8" s="50"/>
-      <c r="U8" s="51"/>
+      <c r="O8" s="47"/>
+      <c r="P8" s="48"/>
+      <c r="Q8" s="48"/>
+      <c r="R8" s="48"/>
+      <c r="S8" s="48"/>
+      <c r="T8" s="48"/>
+      <c r="U8" s="49"/>
       <c r="V8" s="12"/>
     </row>
     <row r="9" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="144"/>
+      <c r="A9" s="130"/>
       <c r="B9" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="49"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="50"/>
-      <c r="F9" s="50"/>
-      <c r="G9" s="50"/>
-      <c r="H9" s="50"/>
-      <c r="I9" s="51"/>
+      <c r="C9" s="47"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="49"/>
       <c r="J9" s="34" cm="1">
         <f t="array" ref="J9">-SUMPRODUCT((D1:H1-C1:G1)*(C9:G9+D9:H9)/2)</f>
         <v>0</v>
@@ -4494,31 +4596,31 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M9" s="144"/>
+      <c r="M9" s="130"/>
       <c r="N9" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="O9" s="49"/>
-      <c r="P9" s="50"/>
-      <c r="Q9" s="50"/>
-      <c r="R9" s="50"/>
-      <c r="S9" s="50"/>
-      <c r="T9" s="50"/>
-      <c r="U9" s="51"/>
+      <c r="O9" s="47"/>
+      <c r="P9" s="48"/>
+      <c r="Q9" s="48"/>
+      <c r="R9" s="48"/>
+      <c r="S9" s="48"/>
+      <c r="T9" s="48"/>
+      <c r="U9" s="49"/>
       <c r="V9" s="12"/>
     </row>
     <row r="10" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="144"/>
+      <c r="A10" s="130"/>
       <c r="B10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="49"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="51"/>
+      <c r="C10" s="47"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="49"/>
       <c r="J10" s="34" cm="1">
         <f t="array" ref="J10">-SUMPRODUCT((D1:H1-C1:G1)*(C10:G10+D10:H10)/2)</f>
         <v>0</v>
@@ -4531,31 +4633,31 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M10" s="144"/>
+      <c r="M10" s="130"/>
       <c r="N10" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="O10" s="49"/>
-      <c r="P10" s="50"/>
-      <c r="Q10" s="50"/>
-      <c r="R10" s="50"/>
-      <c r="S10" s="50"/>
-      <c r="T10" s="50"/>
-      <c r="U10" s="51"/>
+      <c r="O10" s="47"/>
+      <c r="P10" s="48"/>
+      <c r="Q10" s="48"/>
+      <c r="R10" s="48"/>
+      <c r="S10" s="48"/>
+      <c r="T10" s="48"/>
+      <c r="U10" s="49"/>
       <c r="V10" s="12"/>
     </row>
     <row r="11" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="144"/>
+      <c r="A11" s="130"/>
       <c r="B11" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="60"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="61"/>
-      <c r="H11" s="61"/>
-      <c r="I11" s="62"/>
+      <c r="C11" s="58"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="60"/>
       <c r="J11" s="34" cm="1">
         <f t="array" ref="J11">-SUMPRODUCT((D1:H1-C1:G1)*(C11:G11+D11:H11)/2)</f>
         <v>0</v>
@@ -4568,31 +4670,31 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M11" s="144"/>
+      <c r="M11" s="130"/>
       <c r="N11" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="O11" s="60"/>
-      <c r="P11" s="61"/>
-      <c r="Q11" s="61"/>
-      <c r="R11" s="61"/>
-      <c r="S11" s="61"/>
-      <c r="T11" s="61"/>
-      <c r="U11" s="62"/>
+      <c r="O11" s="58"/>
+      <c r="P11" s="59"/>
+      <c r="Q11" s="59"/>
+      <c r="R11" s="59"/>
+      <c r="S11" s="59"/>
+      <c r="T11" s="59"/>
+      <c r="U11" s="60"/>
       <c r="V11" s="12"/>
     </row>
     <row r="12" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="144"/>
+      <c r="A12" s="130"/>
       <c r="B12" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="49"/>
-      <c r="D12" s="50"/>
-      <c r="E12" s="50"/>
-      <c r="F12" s="50"/>
-      <c r="G12" s="50"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="51"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="48"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="48"/>
+      <c r="G12" s="48"/>
+      <c r="H12" s="48"/>
+      <c r="I12" s="49"/>
       <c r="J12" s="34" cm="1">
         <f t="array" ref="J12">-SUMPRODUCT((D1:H1-C1:G1)*(C12:G12+D12:H12)/2)</f>
         <v>0</v>
@@ -4605,31 +4707,31 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M12" s="144"/>
+      <c r="M12" s="130"/>
       <c r="N12" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="O12" s="49"/>
-      <c r="P12" s="50"/>
-      <c r="Q12" s="50"/>
-      <c r="R12" s="50"/>
-      <c r="S12" s="50"/>
-      <c r="T12" s="50"/>
-      <c r="U12" s="51"/>
+      <c r="O12" s="47"/>
+      <c r="P12" s="48"/>
+      <c r="Q12" s="48"/>
+      <c r="R12" s="48"/>
+      <c r="S12" s="48"/>
+      <c r="T12" s="48"/>
+      <c r="U12" s="49"/>
       <c r="V12" s="12"/>
     </row>
     <row r="13" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="144"/>
+      <c r="A13" s="130"/>
       <c r="B13" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="49"/>
-      <c r="D13" s="50"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="51"/>
+      <c r="C13" s="47"/>
+      <c r="D13" s="48"/>
+      <c r="E13" s="48"/>
+      <c r="F13" s="48"/>
+      <c r="G13" s="48"/>
+      <c r="H13" s="48"/>
+      <c r="I13" s="49"/>
       <c r="J13" s="34" cm="1">
         <f t="array" ref="J13">-SUMPRODUCT((D1:H1-C1:G1)*(C13:G13+D13:H13)/2)</f>
         <v>0</v>
@@ -4642,31 +4744,31 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M13" s="144"/>
+      <c r="M13" s="130"/>
       <c r="N13" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="O13" s="49"/>
-      <c r="P13" s="50"/>
-      <c r="Q13" s="50"/>
-      <c r="R13" s="50"/>
-      <c r="S13" s="50"/>
-      <c r="T13" s="50"/>
-      <c r="U13" s="51"/>
+      <c r="O13" s="47"/>
+      <c r="P13" s="48"/>
+      <c r="Q13" s="48"/>
+      <c r="R13" s="48"/>
+      <c r="S13" s="48"/>
+      <c r="T13" s="48"/>
+      <c r="U13" s="49"/>
       <c r="V13" s="12"/>
     </row>
     <row r="14" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="137"/>
+      <c r="A14" s="128"/>
       <c r="B14" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C14" s="60"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="61"/>
-      <c r="G14" s="61"/>
-      <c r="H14" s="61"/>
-      <c r="I14" s="62"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="60"/>
       <c r="J14" s="34" cm="1">
         <f t="array" ref="J14">-SUMPRODUCT((D1:H1-C1:G1)*(C14:G14+D14:H14)/2)</f>
         <v>0</v>
@@ -4679,7 +4781,7 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M14" s="137"/>
+      <c r="M14" s="128"/>
       <c r="N14" s="8" t="s">
         <v>26</v>
       </c>
@@ -4693,45 +4795,45 @@
       <c r="V14" s="12"/>
     </row>
     <row r="15" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="134" t="s">
+      <c r="A15" s="123" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="136"/>
-      <c r="C15" s="147"/>
-      <c r="D15" s="147"/>
-      <c r="E15" s="147"/>
-      <c r="F15" s="147"/>
-      <c r="G15" s="147"/>
-      <c r="H15" s="147"/>
-      <c r="I15" s="148"/>
+      <c r="B15" s="127"/>
+      <c r="C15" s="141"/>
+      <c r="D15" s="141"/>
+      <c r="E15" s="141"/>
+      <c r="F15" s="141"/>
+      <c r="G15" s="141"/>
+      <c r="H15" s="141"/>
+      <c r="I15" s="142"/>
       <c r="J15" s="34"/>
       <c r="K15" s="34"/>
       <c r="L15" s="12"/>
-      <c r="M15" s="134" t="s">
+      <c r="M15" s="123" t="s">
         <v>20</v>
       </c>
-      <c r="N15" s="136"/>
-      <c r="O15" s="149"/>
-      <c r="P15" s="149"/>
-      <c r="Q15" s="149"/>
-      <c r="R15" s="149"/>
-      <c r="S15" s="149"/>
-      <c r="T15" s="149"/>
-      <c r="U15" s="140"/>
+      <c r="N15" s="127"/>
+      <c r="O15" s="144"/>
+      <c r="P15" s="144"/>
+      <c r="Q15" s="144"/>
+      <c r="R15" s="144"/>
+      <c r="S15" s="144"/>
+      <c r="T15" s="144"/>
+      <c r="U15" s="126"/>
       <c r="V15" s="12"/>
     </row>
     <row r="16" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="134" t="s">
+      <c r="A16" s="123" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="135"/>
-      <c r="C16" s="44"/>
-      <c r="D16" s="45"/>
-      <c r="E16" s="45"/>
-      <c r="F16" s="45"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="45"/>
-      <c r="I16" s="46"/>
+      <c r="B16" s="124"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="43"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="44"/>
       <c r="J16" s="34" cm="1">
         <f t="array" ref="J16">-SUMPRODUCT((D1:H1-C1:G1)*(C16:G16+D16:H16)/2)</f>
         <v>0</v>
@@ -4744,34 +4846,34 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M16" s="134" t="s">
+      <c r="M16" s="123" t="s">
         <v>7</v>
       </c>
-      <c r="N16" s="135"/>
-      <c r="O16" s="44"/>
-      <c r="P16" s="45"/>
-      <c r="Q16" s="45"/>
-      <c r="R16" s="45"/>
-      <c r="S16" s="45"/>
-      <c r="T16" s="45"/>
-      <c r="U16" s="46"/>
+      <c r="N16" s="124"/>
+      <c r="O16" s="42"/>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="43"/>
+      <c r="R16" s="43"/>
+      <c r="S16" s="43"/>
+      <c r="T16" s="43"/>
+      <c r="U16" s="44"/>
       <c r="V16" s="12" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">    ,</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="139" t="s">
+      <c r="A17" s="125" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="140"/>
-      <c r="C17" s="47"/>
+      <c r="B17" s="126"/>
+      <c r="C17" s="45"/>
       <c r="D17" s="12"/>
       <c r="E17" s="12"/>
       <c r="F17" s="12"/>
       <c r="G17" s="12"/>
       <c r="H17" s="12"/>
-      <c r="I17" s="48"/>
+      <c r="I17" s="46"/>
       <c r="J17" s="34" cm="1">
         <f t="array" ref="J17">-SUMPRODUCT((D1:H1-C1:G1)*(C17:G17+D17:H17)/2)</f>
         <v>0</v>
@@ -4784,34 +4886,34 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M17" s="134" t="s">
+      <c r="M17" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="N17" s="135"/>
-      <c r="O17" s="47"/>
+      <c r="N17" s="124"/>
+      <c r="O17" s="45"/>
       <c r="P17" s="12"/>
       <c r="Q17" s="12"/>
       <c r="R17" s="12"/>
       <c r="S17" s="12"/>
       <c r="T17" s="12"/>
-      <c r="U17" s="48"/>
+      <c r="U17" s="46"/>
       <c r="V17" s="12" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">    ,</v>
       </c>
     </row>
     <row r="18" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="134" t="s">
+      <c r="A18" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="135"/>
-      <c r="C18" s="47"/>
+      <c r="B18" s="124"/>
+      <c r="C18" s="45"/>
       <c r="D18" s="12"/>
       <c r="E18" s="12"/>
       <c r="F18" s="12"/>
       <c r="G18" s="12"/>
       <c r="H18" s="12"/>
-      <c r="I18" s="48"/>
+      <c r="I18" s="46"/>
       <c r="J18" s="34" cm="1">
         <f t="array" ref="J18">-SUMPRODUCT((D1:H1-C1:G1)*(C18:G18+D18:H18)/2)</f>
         <v>0</v>
@@ -4824,34 +4926,34 @@
         <f t="shared" si="0"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M18" s="134" t="s">
+      <c r="M18" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="N18" s="135"/>
-      <c r="O18" s="47"/>
+      <c r="N18" s="124"/>
+      <c r="O18" s="45"/>
       <c r="P18" s="12"/>
       <c r="Q18" s="12"/>
       <c r="R18" s="12"/>
       <c r="S18" s="12"/>
       <c r="T18" s="12"/>
-      <c r="U18" s="48"/>
+      <c r="U18" s="46"/>
       <c r="V18" s="12" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">    ,</v>
       </c>
     </row>
     <row r="19" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="134" t="s">
+      <c r="A19" s="123" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="135"/>
-      <c r="C19" s="49"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="51"/>
+      <c r="B19" s="124"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="48"/>
+      <c r="E19" s="48"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="48"/>
+      <c r="H19" s="48"/>
+      <c r="I19" s="49"/>
       <c r="J19" s="34" cm="1">
         <f t="array" ref="J19">-SUMPRODUCT((D1:H1-C1:G1)*(C19:G19+D19:H19)/2)</f>
         <v>0</v>
@@ -4861,59 +4963,59 @@
         <v>0</v>
       </c>
       <c r="L19" s="12"/>
-      <c r="M19" s="134" t="s">
+      <c r="M19" s="123" t="s">
         <v>22</v>
       </c>
-      <c r="N19" s="135"/>
-      <c r="O19" s="49"/>
-      <c r="P19" s="50"/>
-      <c r="Q19" s="50"/>
-      <c r="R19" s="50"/>
-      <c r="S19" s="50"/>
-      <c r="T19" s="50"/>
-      <c r="U19" s="51"/>
+      <c r="N19" s="124"/>
+      <c r="O19" s="47"/>
+      <c r="P19" s="48"/>
+      <c r="Q19" s="48"/>
+      <c r="R19" s="48"/>
+      <c r="S19" s="48"/>
+      <c r="T19" s="48"/>
+      <c r="U19" s="49"/>
       <c r="V19" s="12"/>
     </row>
     <row r="20" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="134" t="s">
+      <c r="A20" s="123" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="136"/>
-      <c r="C20" s="147"/>
-      <c r="D20" s="147"/>
-      <c r="E20" s="147"/>
-      <c r="F20" s="147"/>
-      <c r="G20" s="147"/>
-      <c r="H20" s="147"/>
-      <c r="I20" s="148"/>
+      <c r="B20" s="127"/>
+      <c r="C20" s="141"/>
+      <c r="D20" s="141"/>
+      <c r="E20" s="141"/>
+      <c r="F20" s="141"/>
+      <c r="G20" s="141"/>
+      <c r="H20" s="141"/>
+      <c r="I20" s="142"/>
       <c r="J20" s="34"/>
       <c r="K20" s="34"/>
       <c r="L20" s="12"/>
-      <c r="M20" s="134" t="s">
+      <c r="M20" s="123" t="s">
         <v>23</v>
       </c>
-      <c r="N20" s="136"/>
-      <c r="O20" s="147"/>
-      <c r="P20" s="147"/>
-      <c r="Q20" s="147"/>
-      <c r="R20" s="147"/>
-      <c r="S20" s="147"/>
-      <c r="T20" s="147"/>
-      <c r="U20" s="148"/>
+      <c r="N20" s="127"/>
+      <c r="O20" s="141"/>
+      <c r="P20" s="141"/>
+      <c r="Q20" s="141"/>
+      <c r="R20" s="141"/>
+      <c r="S20" s="141"/>
+      <c r="T20" s="141"/>
+      <c r="U20" s="142"/>
       <c r="V20" s="12"/>
     </row>
     <row r="21" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="134" t="s">
+      <c r="A21" s="123" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="135"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="45"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="46"/>
+      <c r="B21" s="124"/>
+      <c r="C21" s="42"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="44"/>
       <c r="J21" s="34" cm="1">
         <f t="array" ref="J21">-SUMPRODUCT((D1:H1-C1:G1)*(C21:G21+D21:H21)/2)</f>
         <v>0</v>
@@ -4926,34 +5028,34 @@
         <f t="shared" ref="L21:L23" si="2">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C21:I21)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M21" s="134" t="s">
+      <c r="M21" s="123" t="s">
         <v>7</v>
       </c>
-      <c r="N21" s="135"/>
-      <c r="O21" s="44"/>
-      <c r="P21" s="45"/>
-      <c r="Q21" s="45"/>
-      <c r="R21" s="45"/>
-      <c r="S21" s="45"/>
-      <c r="T21" s="45"/>
-      <c r="U21" s="46"/>
+      <c r="N21" s="124"/>
+      <c r="O21" s="42"/>
+      <c r="P21" s="43"/>
+      <c r="Q21" s="43"/>
+      <c r="R21" s="43"/>
+      <c r="S21" s="43"/>
+      <c r="T21" s="43"/>
+      <c r="U21" s="44"/>
       <c r="V21" s="12" t="str">
         <f t="shared" ref="V21:V23" si="3">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O21:U21)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="139" t="s">
+      <c r="A22" s="125" t="s">
         <v>8</v>
       </c>
-      <c r="B22" s="140"/>
-      <c r="C22" s="47"/>
+      <c r="B22" s="126"/>
+      <c r="C22" s="45"/>
       <c r="D22" s="12"/>
       <c r="E22" s="12"/>
       <c r="F22" s="12"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
-      <c r="I22" s="48"/>
+      <c r="I22" s="46"/>
       <c r="J22" s="34" cm="1">
         <f t="array" ref="J22">-SUMPRODUCT((D1:H1-C1:G1)*(C22:G22+D22:H22)/2)</f>
         <v>0</v>
@@ -4966,34 +5068,34 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M22" s="134" t="s">
+      <c r="M22" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="N22" s="135"/>
-      <c r="O22" s="47"/>
+      <c r="N22" s="124"/>
+      <c r="O22" s="45"/>
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
       <c r="R22" s="12"/>
       <c r="S22" s="12"/>
       <c r="T22" s="12"/>
-      <c r="U22" s="48"/>
+      <c r="U22" s="46"/>
       <c r="V22" s="12" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">    ,</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="134" t="s">
+      <c r="A23" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="135"/>
-      <c r="C23" s="47"/>
+      <c r="B23" s="124"/>
+      <c r="C23" s="45"/>
       <c r="D23" s="12"/>
       <c r="E23" s="12"/>
       <c r="F23" s="12"/>
       <c r="G23" s="12"/>
       <c r="H23" s="12"/>
-      <c r="I23" s="48"/>
+      <c r="I23" s="46"/>
       <c r="J23" s="34" cm="1">
         <f t="array" ref="J23">-SUMPRODUCT((D1:H1-C1:G1)*(C23:G23+D23:H23)/2)</f>
         <v>0</v>
@@ -5006,34 +5108,34 @@
         <f t="shared" si="2"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M23" s="134" t="s">
+      <c r="M23" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="N23" s="135"/>
-      <c r="O23" s="47"/>
+      <c r="N23" s="124"/>
+      <c r="O23" s="45"/>
       <c r="P23" s="12"/>
       <c r="Q23" s="12"/>
       <c r="R23" s="12"/>
       <c r="S23" s="12"/>
       <c r="T23" s="12"/>
-      <c r="U23" s="48"/>
+      <c r="U23" s="46"/>
       <c r="V23" s="12" t="str">
         <f t="shared" si="3"/>
         <v xml:space="preserve">    ,</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="134" t="s">
+      <c r="A24" s="123" t="s">
         <v>22</v>
       </c>
-      <c r="B24" s="135"/>
-      <c r="C24" s="49"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="50"/>
-      <c r="I24" s="51"/>
+      <c r="B24" s="124"/>
+      <c r="C24" s="47"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="48"/>
+      <c r="I24" s="49"/>
       <c r="J24" s="34" cm="1">
         <f t="array" ref="J24">-SUMPRODUCT((D1:H1-C1:G1)*(C24:G24+D24:H24)/2)</f>
         <v>0</v>
@@ -5043,52 +5145,52 @@
         <v>0</v>
       </c>
       <c r="L24" s="12"/>
-      <c r="M24" s="134" t="s">
+      <c r="M24" s="123" t="s">
         <v>22</v>
       </c>
-      <c r="N24" s="135"/>
-      <c r="O24" s="49"/>
-      <c r="P24" s="50"/>
-      <c r="Q24" s="50"/>
-      <c r="R24" s="50"/>
-      <c r="S24" s="50"/>
-      <c r="T24" s="50"/>
-      <c r="U24" s="51"/>
+      <c r="N24" s="124"/>
+      <c r="O24" s="47"/>
+      <c r="P24" s="48"/>
+      <c r="Q24" s="48"/>
+      <c r="R24" s="48"/>
+      <c r="S24" s="48"/>
+      <c r="T24" s="48"/>
+      <c r="U24" s="49"/>
       <c r="V24" s="12"/>
     </row>
     <row r="25" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="134" t="s">
+      <c r="A25" s="123" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="136"/>
-      <c r="C25" s="147"/>
-      <c r="D25" s="147"/>
-      <c r="E25" s="147"/>
-      <c r="F25" s="147"/>
-      <c r="G25" s="147"/>
-      <c r="H25" s="147"/>
-      <c r="I25" s="148"/>
+      <c r="B25" s="127"/>
+      <c r="C25" s="141"/>
+      <c r="D25" s="141"/>
+      <c r="E25" s="141"/>
+      <c r="F25" s="141"/>
+      <c r="G25" s="141"/>
+      <c r="H25" s="141"/>
+      <c r="I25" s="142"/>
       <c r="J25" s="34"/>
       <c r="K25" s="34"/>
       <c r="L25" s="12"/>
-      <c r="M25" s="134" t="s">
+      <c r="M25" s="123" t="s">
         <v>23</v>
       </c>
-      <c r="N25" s="136"/>
-      <c r="O25" s="147"/>
-      <c r="P25" s="147"/>
-      <c r="Q25" s="147"/>
-      <c r="R25" s="147"/>
-      <c r="S25" s="147"/>
-      <c r="T25" s="147"/>
-      <c r="U25" s="148"/>
+      <c r="N25" s="127"/>
+      <c r="O25" s="141"/>
+      <c r="P25" s="141"/>
+      <c r="Q25" s="141"/>
+      <c r="R25" s="141"/>
+      <c r="S25" s="141"/>
+      <c r="T25" s="141"/>
+      <c r="U25" s="142"/>
       <c r="V25" s="12"/>
     </row>
     <row r="26" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="134" t="s">
+      <c r="A26" s="123" t="s">
         <v>7</v>
       </c>
-      <c r="B26" s="135"/>
+      <c r="B26" s="124"/>
       <c r="C26"/>
       <c r="D26"/>
       <c r="E26"/>
@@ -5108,10 +5210,10 @@
         <f t="shared" ref="L26:L28" si="4">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C26:I26)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M26" s="134" t="s">
+      <c r="M26" s="123" t="s">
         <v>7</v>
       </c>
-      <c r="N26" s="135"/>
+      <c r="N26" s="124"/>
       <c r="O26"/>
       <c r="P26"/>
       <c r="Q26"/>
@@ -5125,10 +5227,10 @@
       </c>
     </row>
     <row r="27" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="139" t="s">
+      <c r="A27" s="125" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="140"/>
+      <c r="B27" s="126"/>
       <c r="C27"/>
       <c r="D27"/>
       <c r="E27"/>
@@ -5148,10 +5250,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M27" s="134" t="s">
+      <c r="M27" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="N27" s="135"/>
+      <c r="N27" s="124"/>
       <c r="O27"/>
       <c r="P27"/>
       <c r="Q27"/>
@@ -5165,10 +5267,10 @@
       </c>
     </row>
     <row r="28" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="134" t="s">
+      <c r="A28" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="B28" s="135"/>
+      <c r="B28" s="124"/>
       <c r="C28"/>
       <c r="D28"/>
       <c r="E28"/>
@@ -5188,10 +5290,10 @@
         <f t="shared" si="4"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M28" s="134" t="s">
+      <c r="M28" s="123" t="s">
         <v>21</v>
       </c>
-      <c r="N28" s="135"/>
+      <c r="N28" s="124"/>
       <c r="O28"/>
       <c r="P28"/>
       <c r="Q28"/>
@@ -5205,10 +5307,10 @@
       </c>
     </row>
     <row r="29" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="134" t="s">
+      <c r="A29" s="123" t="s">
         <v>22</v>
       </c>
-      <c r="B29" s="135"/>
+      <c r="B29" s="124"/>
       <c r="C29"/>
       <c r="D29"/>
       <c r="E29"/>
@@ -5225,17 +5327,17 @@
         <v>0</v>
       </c>
       <c r="L29" s="12"/>
-      <c r="M29" s="134" t="s">
+      <c r="M29" s="123" t="s">
         <v>22</v>
       </c>
-      <c r="N29" s="135"/>
-      <c r="O29" s="75"/>
-      <c r="P29" s="76"/>
-      <c r="Q29" s="76"/>
-      <c r="R29" s="76"/>
-      <c r="S29" s="76"/>
-      <c r="T29" s="76"/>
-      <c r="U29" s="77"/>
+      <c r="N29" s="124"/>
+      <c r="O29" s="73"/>
+      <c r="P29" s="74"/>
+      <c r="Q29" s="74"/>
+      <c r="R29" s="74"/>
+      <c r="S29" s="74"/>
+      <c r="T29" s="74"/>
+      <c r="U29" s="75"/>
       <c r="V29" s="12"/>
     </row>
     <row r="30" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.25">
@@ -5321,10 +5423,10 @@
       <c r="V31" s="1"/>
     </row>
     <row r="32" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="124" t="s">
+      <c r="A32" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="B32" s="131"/>
+      <c r="B32" s="140"/>
       <c r="C32" s="36"/>
       <c r="D32" s="36"/>
       <c r="E32" s="36"/>
@@ -5338,10 +5440,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C32:I32)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M32" s="124" t="s">
+      <c r="M32" s="131" t="s">
         <v>5</v>
       </c>
-      <c r="N32" s="131"/>
+      <c r="N32" s="140"/>
       <c r="O32" s="35"/>
       <c r="P32" s="36"/>
       <c r="Q32" s="36"/>
@@ -5355,10 +5457,10 @@
       </c>
     </row>
     <row r="33" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="124" t="s">
+      <c r="A33" s="131" t="s">
         <v>6</v>
       </c>
-      <c r="B33" s="131"/>
+      <c r="B33" s="140"/>
       <c r="C33" s="36"/>
       <c r="D33" s="36"/>
       <c r="E33" s="36"/>
@@ -5372,10 +5474,10 @@
         <f>"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C33:I33)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M33" s="124" t="s">
+      <c r="M33" s="131" t="s">
         <v>6</v>
       </c>
-      <c r="N33" s="131"/>
+      <c r="N33" s="140"/>
       <c r="O33" s="36"/>
       <c r="P33" s="36"/>
       <c r="Q33" s="36"/>
@@ -5389,10 +5491,10 @@
       </c>
     </row>
     <row r="34" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="124" t="s">
+      <c r="A34" s="131" t="s">
         <v>10</v>
       </c>
-      <c r="B34" s="131"/>
+      <c r="B34" s="140"/>
       <c r="C34" s="28"/>
       <c r="D34" s="29"/>
       <c r="E34" s="29"/>
@@ -5406,10 +5508,10 @@
         <f t="shared" ref="L34:L43" si="7">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C34:I34)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M34" s="124" t="s">
+      <c r="M34" s="131" t="s">
         <v>10</v>
       </c>
-      <c r="N34" s="131"/>
+      <c r="N34" s="140"/>
       <c r="O34" s="28"/>
       <c r="P34" s="29"/>
       <c r="Q34" s="29"/>
@@ -5423,66 +5525,66 @@
       </c>
     </row>
     <row r="35" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="124" t="s">
+      <c r="A35" s="131" t="s">
         <v>12</v>
       </c>
-      <c r="B35" s="125"/>
-      <c r="C35" s="125"/>
-      <c r="D35" s="125"/>
-      <c r="E35" s="125"/>
-      <c r="F35" s="125"/>
-      <c r="G35" s="125"/>
-      <c r="H35" s="125"/>
-      <c r="I35" s="131"/>
+      <c r="B35" s="132"/>
+      <c r="C35" s="132"/>
+      <c r="D35" s="132"/>
+      <c r="E35" s="132"/>
+      <c r="F35" s="132"/>
+      <c r="G35" s="132"/>
+      <c r="H35" s="132"/>
+      <c r="I35" s="140"/>
       <c r="J35" s="38"/>
       <c r="K35" s="38"/>
       <c r="L35" s="1"/>
-      <c r="M35" s="124" t="s">
+      <c r="M35" s="131" t="s">
         <v>12</v>
       </c>
-      <c r="N35" s="125"/>
-      <c r="O35" s="125"/>
-      <c r="P35" s="125"/>
-      <c r="Q35" s="125"/>
-      <c r="R35" s="125"/>
-      <c r="S35" s="125"/>
-      <c r="T35" s="125"/>
-      <c r="U35" s="131"/>
+      <c r="N35" s="132"/>
+      <c r="O35" s="132"/>
+      <c r="P35" s="132"/>
+      <c r="Q35" s="132"/>
+      <c r="R35" s="132"/>
+      <c r="S35" s="132"/>
+      <c r="T35" s="132"/>
+      <c r="U35" s="140"/>
       <c r="V35" s="1"/>
     </row>
     <row r="36" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="128" t="s">
+      <c r="A36" s="133" t="s">
         <v>11</v>
       </c>
       <c r="B36" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="C36" s="57"/>
-      <c r="D36" s="58"/>
-      <c r="E36" s="58"/>
-      <c r="F36" s="58"/>
-      <c r="G36" s="58"/>
-      <c r="H36" s="58"/>
-      <c r="I36" s="59"/>
+      <c r="C36" s="55"/>
+      <c r="D36" s="56"/>
+      <c r="E36" s="56"/>
+      <c r="F36" s="56"/>
+      <c r="G36" s="56"/>
+      <c r="H36" s="56"/>
+      <c r="I36" s="57"/>
       <c r="J36" s="38"/>
       <c r="K36" s="38"/>
       <c r="L36" s="1" t="str">
         <f t="shared" si="7"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M36" s="128" t="s">
+      <c r="M36" s="133" t="s">
         <v>11</v>
       </c>
       <c r="N36" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="O36" s="57"/>
-      <c r="P36" s="58"/>
-      <c r="Q36" s="58"/>
-      <c r="R36" s="58"/>
-      <c r="S36" s="58"/>
-      <c r="T36" s="58"/>
-      <c r="U36" s="59"/>
+      <c r="O36" s="55"/>
+      <c r="P36" s="56"/>
+      <c r="Q36" s="56"/>
+      <c r="R36" s="56"/>
+      <c r="S36" s="56"/>
+      <c r="T36" s="56"/>
+      <c r="U36" s="57"/>
       <c r="V36" s="1" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve">    ,</v>
@@ -5493,13 +5595,13 @@
       <c r="B37" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C37" s="57"/>
-      <c r="D37" s="58"/>
-      <c r="E37" s="58"/>
-      <c r="F37" s="58"/>
-      <c r="G37" s="58"/>
-      <c r="H37" s="58"/>
-      <c r="I37" s="59"/>
+      <c r="C37" s="55"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="56"/>
+      <c r="F37" s="56"/>
+      <c r="G37" s="56"/>
+      <c r="H37" s="56"/>
+      <c r="I37" s="57"/>
       <c r="J37" s="38"/>
       <c r="K37" s="38"/>
       <c r="L37" s="1" t="str">
@@ -5510,13 +5612,13 @@
       <c r="N37" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="O37" s="57"/>
-      <c r="P37" s="58"/>
-      <c r="Q37" s="58"/>
-      <c r="R37" s="58"/>
-      <c r="S37" s="58"/>
-      <c r="T37" s="58"/>
-      <c r="U37" s="59"/>
+      <c r="O37" s="55"/>
+      <c r="P37" s="56"/>
+      <c r="Q37" s="56"/>
+      <c r="R37" s="56"/>
+      <c r="S37" s="56"/>
+      <c r="T37" s="56"/>
+      <c r="U37" s="57"/>
       <c r="V37" s="1" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve">    ,</v>
@@ -5527,13 +5629,13 @@
       <c r="B38" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C38" s="57"/>
-      <c r="D38" s="58"/>
-      <c r="E38" s="58"/>
-      <c r="F38" s="58"/>
-      <c r="G38" s="58"/>
-      <c r="H38" s="58"/>
-      <c r="I38" s="59"/>
+      <c r="C38" s="55"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56"/>
+      <c r="F38" s="56"/>
+      <c r="G38" s="56"/>
+      <c r="H38" s="56"/>
+      <c r="I38" s="57"/>
       <c r="J38" s="38"/>
       <c r="K38" s="38"/>
       <c r="L38" s="1"/>
@@ -5541,13 +5643,13 @@
       <c r="N38" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O38" s="57"/>
-      <c r="P38" s="58"/>
-      <c r="Q38" s="58"/>
-      <c r="R38" s="58"/>
-      <c r="S38" s="58"/>
-      <c r="T38" s="58"/>
-      <c r="U38" s="59"/>
+      <c r="O38" s="55"/>
+      <c r="P38" s="56"/>
+      <c r="Q38" s="56"/>
+      <c r="R38" s="56"/>
+      <c r="S38" s="56"/>
+      <c r="T38" s="56"/>
+      <c r="U38" s="57"/>
       <c r="V38" s="1"/>
     </row>
     <row r="39" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -5555,13 +5657,13 @@
       <c r="B39" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C39" s="57"/>
-      <c r="D39" s="58"/>
-      <c r="E39" s="58"/>
-      <c r="F39" s="58"/>
-      <c r="G39" s="58"/>
-      <c r="H39" s="58"/>
-      <c r="I39" s="59"/>
+      <c r="C39" s="55"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="56"/>
+      <c r="F39" s="56"/>
+      <c r="G39" s="56"/>
+      <c r="H39" s="56"/>
+      <c r="I39" s="57"/>
       <c r="J39" s="38"/>
       <c r="K39" s="38"/>
       <c r="L39" s="1"/>
@@ -5569,13 +5671,13 @@
       <c r="N39" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="O39" s="57"/>
-      <c r="P39" s="58"/>
-      <c r="Q39" s="58"/>
-      <c r="R39" s="58"/>
-      <c r="S39" s="58"/>
-      <c r="T39" s="58"/>
-      <c r="U39" s="59"/>
+      <c r="O39" s="55"/>
+      <c r="P39" s="56"/>
+      <c r="Q39" s="56"/>
+      <c r="R39" s="56"/>
+      <c r="S39" s="56"/>
+      <c r="T39" s="56"/>
+      <c r="U39" s="57"/>
       <c r="V39" s="1"/>
     </row>
     <row r="40" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -5583,13 +5685,13 @@
       <c r="B40" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C40" s="57"/>
-      <c r="D40" s="58"/>
-      <c r="E40" s="58"/>
-      <c r="F40" s="58"/>
-      <c r="G40" s="58"/>
-      <c r="H40" s="58"/>
-      <c r="I40" s="59"/>
+      <c r="C40" s="55"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="56"/>
+      <c r="F40" s="56"/>
+      <c r="G40" s="56"/>
+      <c r="H40" s="56"/>
+      <c r="I40" s="57"/>
       <c r="J40" s="38"/>
       <c r="K40" s="38"/>
       <c r="L40" s="1" t="str">
@@ -5600,13 +5702,13 @@
       <c r="N40" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="O40" s="57"/>
-      <c r="P40" s="58"/>
-      <c r="Q40" s="58"/>
-      <c r="R40" s="58"/>
-      <c r="S40" s="58"/>
-      <c r="T40" s="58"/>
-      <c r="U40" s="59"/>
+      <c r="O40" s="55"/>
+      <c r="P40" s="56"/>
+      <c r="Q40" s="56"/>
+      <c r="R40" s="56"/>
+      <c r="S40" s="56"/>
+      <c r="T40" s="56"/>
+      <c r="U40" s="57"/>
       <c r="V40" s="1"/>
     </row>
     <row r="41" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -5614,13 +5716,13 @@
       <c r="B41" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C41" s="63"/>
-      <c r="D41" s="64"/>
-      <c r="E41" s="64"/>
-      <c r="F41" s="64"/>
-      <c r="G41" s="64"/>
-      <c r="H41" s="64"/>
-      <c r="I41" s="65"/>
+      <c r="C41" s="61"/>
+      <c r="D41" s="62"/>
+      <c r="E41" s="62"/>
+      <c r="F41" s="62"/>
+      <c r="G41" s="62"/>
+      <c r="H41" s="62"/>
+      <c r="I41" s="63"/>
       <c r="J41" s="38"/>
       <c r="K41" s="38"/>
       <c r="L41" s="1"/>
@@ -5628,13 +5730,13 @@
       <c r="N41" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="O41" s="63"/>
-      <c r="P41" s="64"/>
-      <c r="Q41" s="64"/>
-      <c r="R41" s="64"/>
-      <c r="S41" s="64"/>
-      <c r="T41" s="64"/>
-      <c r="U41" s="65"/>
+      <c r="O41" s="61"/>
+      <c r="P41" s="62"/>
+      <c r="Q41" s="62"/>
+      <c r="R41" s="62"/>
+      <c r="S41" s="62"/>
+      <c r="T41" s="62"/>
+      <c r="U41" s="63"/>
       <c r="V41" s="1"/>
     </row>
     <row r="42" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -5642,13 +5744,13 @@
       <c r="B42" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C42" s="57"/>
-      <c r="D42" s="58"/>
-      <c r="E42" s="58"/>
-      <c r="F42" s="58"/>
-      <c r="G42" s="58"/>
-      <c r="H42" s="58"/>
-      <c r="I42" s="59"/>
+      <c r="C42" s="55"/>
+      <c r="D42" s="56"/>
+      <c r="E42" s="56"/>
+      <c r="F42" s="56"/>
+      <c r="G42" s="56"/>
+      <c r="H42" s="56"/>
+      <c r="I42" s="57"/>
       <c r="J42" s="38"/>
       <c r="K42" s="38"/>
       <c r="L42" s="1"/>
@@ -5656,13 +5758,13 @@
       <c r="N42" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="O42" s="57"/>
-      <c r="P42" s="58"/>
-      <c r="Q42" s="58"/>
-      <c r="R42" s="58"/>
-      <c r="S42" s="58"/>
-      <c r="T42" s="58"/>
-      <c r="U42" s="59"/>
+      <c r="O42" s="55"/>
+      <c r="P42" s="56"/>
+      <c r="Q42" s="56"/>
+      <c r="R42" s="56"/>
+      <c r="S42" s="56"/>
+      <c r="T42" s="56"/>
+      <c r="U42" s="57"/>
       <c r="V42" s="1"/>
     </row>
     <row r="43" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -5670,13 +5772,13 @@
       <c r="B43" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C43" s="57"/>
-      <c r="D43" s="58"/>
-      <c r="E43" s="58"/>
-      <c r="F43" s="58"/>
-      <c r="G43" s="58"/>
-      <c r="H43" s="58"/>
-      <c r="I43" s="59"/>
+      <c r="C43" s="55"/>
+      <c r="D43" s="56"/>
+      <c r="E43" s="56"/>
+      <c r="F43" s="56"/>
+      <c r="G43" s="56"/>
+      <c r="H43" s="56"/>
+      <c r="I43" s="57"/>
       <c r="J43" s="38"/>
       <c r="K43" s="38"/>
       <c r="L43" s="1" t="str">
@@ -5687,392 +5789,392 @@
       <c r="N43" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="O43" s="57"/>
-      <c r="P43" s="58"/>
-      <c r="Q43" s="58"/>
-      <c r="R43" s="58"/>
-      <c r="S43" s="58"/>
-      <c r="T43" s="58"/>
-      <c r="U43" s="59"/>
+      <c r="O43" s="55"/>
+      <c r="P43" s="56"/>
+      <c r="Q43" s="56"/>
+      <c r="R43" s="56"/>
+      <c r="S43" s="56"/>
+      <c r="T43" s="56"/>
+      <c r="U43" s="57"/>
       <c r="V43" s="1"/>
     </row>
     <row r="44" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="126"/>
+      <c r="A44" s="139"/>
       <c r="B44" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="63"/>
-      <c r="D44" s="64"/>
-      <c r="E44" s="64"/>
-      <c r="F44" s="64"/>
-      <c r="G44" s="64"/>
-      <c r="H44" s="64"/>
-      <c r="I44" s="65"/>
+      <c r="C44" s="61"/>
+      <c r="D44" s="62"/>
+      <c r="E44" s="62"/>
+      <c r="F44" s="62"/>
+      <c r="G44" s="62"/>
+      <c r="H44" s="62"/>
+      <c r="I44" s="63"/>
       <c r="J44" s="38"/>
       <c r="K44" s="38"/>
       <c r="L44" s="1"/>
-      <c r="M44" s="126"/>
+      <c r="M44" s="139"/>
       <c r="N44" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="O44" s="63"/>
-      <c r="P44" s="64"/>
-      <c r="Q44" s="64"/>
-      <c r="R44" s="64"/>
-      <c r="S44" s="64"/>
-      <c r="T44" s="64"/>
-      <c r="U44" s="65"/>
+      <c r="O44" s="61"/>
+      <c r="P44" s="62"/>
+      <c r="Q44" s="62"/>
+      <c r="R44" s="62"/>
+      <c r="S44" s="62"/>
+      <c r="T44" s="62"/>
+      <c r="U44" s="63"/>
       <c r="V44" s="1"/>
     </row>
     <row r="45" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="124" t="s">
+      <c r="A45" s="131" t="s">
         <v>20</v>
       </c>
-      <c r="B45" s="125"/>
-      <c r="C45" s="132"/>
-      <c r="D45" s="132"/>
-      <c r="E45" s="132"/>
-      <c r="F45" s="132"/>
-      <c r="G45" s="132"/>
-      <c r="H45" s="132"/>
-      <c r="I45" s="146"/>
+      <c r="B45" s="132"/>
+      <c r="C45" s="136"/>
+      <c r="D45" s="136"/>
+      <c r="E45" s="136"/>
+      <c r="F45" s="136"/>
+      <c r="G45" s="136"/>
+      <c r="H45" s="136"/>
+      <c r="I45" s="143"/>
       <c r="J45" s="38"/>
       <c r="K45" s="38"/>
       <c r="L45" s="1"/>
-      <c r="M45" s="124" t="s">
+      <c r="M45" s="131" t="s">
         <v>20</v>
       </c>
-      <c r="N45" s="125"/>
-      <c r="O45" s="132"/>
-      <c r="P45" s="132"/>
-      <c r="Q45" s="132"/>
-      <c r="R45" s="132"/>
-      <c r="S45" s="132"/>
-      <c r="T45" s="132"/>
-      <c r="U45" s="146"/>
+      <c r="N45" s="132"/>
+      <c r="O45" s="136"/>
+      <c r="P45" s="136"/>
+      <c r="Q45" s="136"/>
+      <c r="R45" s="136"/>
+      <c r="S45" s="136"/>
+      <c r="T45" s="136"/>
+      <c r="U45" s="143"/>
       <c r="V45" s="1"/>
     </row>
     <row r="46" spans="1:22" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="124" t="s">
+      <c r="A46" s="131" t="s">
         <v>7</v>
       </c>
-      <c r="B46" s="131"/>
-      <c r="C46" s="52"/>
-      <c r="D46" s="53"/>
-      <c r="E46" s="53"/>
-      <c r="F46" s="53"/>
-      <c r="G46" s="53"/>
-      <c r="H46" s="53"/>
-      <c r="I46" s="54"/>
+      <c r="B46" s="140"/>
+      <c r="C46" s="50"/>
+      <c r="D46" s="51"/>
+      <c r="E46" s="51"/>
+      <c r="F46" s="51"/>
+      <c r="G46" s="51"/>
+      <c r="H46" s="51"/>
+      <c r="I46" s="52"/>
       <c r="J46" s="38"/>
       <c r="K46" s="38"/>
       <c r="L46" s="1" t="str">
         <f t="shared" ref="L46:L48" si="8">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C46:I46)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M46" s="124" t="s">
+      <c r="M46" s="131" t="s">
         <v>7</v>
       </c>
-      <c r="N46" s="131"/>
-      <c r="O46" s="52"/>
-      <c r="P46" s="53"/>
-      <c r="Q46" s="53"/>
-      <c r="R46" s="53"/>
-      <c r="S46" s="53"/>
-      <c r="T46" s="53"/>
-      <c r="U46" s="54"/>
+      <c r="N46" s="140"/>
+      <c r="O46" s="50"/>
+      <c r="P46" s="51"/>
+      <c r="Q46" s="51"/>
+      <c r="R46" s="51"/>
+      <c r="S46" s="51"/>
+      <c r="T46" s="51"/>
+      <c r="U46" s="52"/>
       <c r="V46" s="1" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve">    ,</v>
       </c>
     </row>
     <row r="47" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="124" t="s">
+      <c r="A47" s="131" t="s">
         <v>8</v>
       </c>
-      <c r="B47" s="131"/>
-      <c r="C47" s="55"/>
+      <c r="B47" s="140"/>
+      <c r="C47" s="53"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="1"/>
       <c r="G47" s="1"/>
       <c r="H47" s="1"/>
-      <c r="I47" s="56"/>
+      <c r="I47" s="54"/>
       <c r="J47" s="38"/>
       <c r="K47" s="38"/>
       <c r="L47" s="1" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M47" s="124" t="s">
+      <c r="M47" s="131" t="s">
         <v>8</v>
       </c>
-      <c r="N47" s="131"/>
-      <c r="O47" s="55"/>
+      <c r="N47" s="140"/>
+      <c r="O47" s="53"/>
       <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
       <c r="R47" s="1"/>
       <c r="S47" s="1"/>
       <c r="T47" s="1"/>
-      <c r="U47" s="56"/>
+      <c r="U47" s="54"/>
       <c r="V47" s="1" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve">    ,</v>
       </c>
     </row>
     <row r="48" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="124" t="s">
+      <c r="A48" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="B48" s="131"/>
-      <c r="C48" s="55"/>
+      <c r="B48" s="140"/>
+      <c r="C48" s="53"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
-      <c r="I48" s="56"/>
+      <c r="I48" s="54"/>
       <c r="J48" s="38"/>
       <c r="K48" s="38"/>
       <c r="L48" s="1" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M48" s="124" t="s">
+      <c r="M48" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="N48" s="131"/>
-      <c r="O48" s="55"/>
+      <c r="N48" s="140"/>
+      <c r="O48" s="53"/>
       <c r="P48" s="1"/>
       <c r="Q48" s="1"/>
       <c r="R48" s="1"/>
       <c r="S48" s="1"/>
       <c r="T48" s="1"/>
-      <c r="U48" s="56"/>
+      <c r="U48" s="54"/>
       <c r="V48" s="1" t="str">
         <f t="shared" si="6"/>
         <v xml:space="preserve">    ,</v>
       </c>
     </row>
     <row r="49" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="124" t="s">
+      <c r="A49" s="131" t="s">
         <v>22</v>
       </c>
-      <c r="B49" s="131"/>
-      <c r="C49" s="57"/>
-      <c r="D49" s="58"/>
-      <c r="E49" s="58"/>
-      <c r="F49" s="58"/>
-      <c r="G49" s="58"/>
-      <c r="H49" s="58"/>
-      <c r="I49" s="59"/>
-      <c r="J49" s="43"/>
-      <c r="K49" s="43"/>
-      <c r="L49" s="42"/>
-      <c r="M49" s="124" t="s">
+      <c r="B49" s="140"/>
+      <c r="C49" s="55"/>
+      <c r="D49" s="56"/>
+      <c r="E49" s="56"/>
+      <c r="F49" s="56"/>
+      <c r="G49" s="56"/>
+      <c r="H49" s="56"/>
+      <c r="I49" s="57"/>
+      <c r="J49" s="41"/>
+      <c r="K49" s="41"/>
+      <c r="L49" s="40"/>
+      <c r="M49" s="131" t="s">
         <v>22</v>
       </c>
-      <c r="N49" s="131"/>
-      <c r="O49" s="57"/>
-      <c r="P49" s="58"/>
-      <c r="Q49" s="58"/>
-      <c r="R49" s="58"/>
-      <c r="S49" s="58"/>
-      <c r="T49" s="58"/>
-      <c r="U49" s="59"/>
+      <c r="N49" s="140"/>
+      <c r="O49" s="55"/>
+      <c r="P49" s="56"/>
+      <c r="Q49" s="56"/>
+      <c r="R49" s="56"/>
+      <c r="S49" s="56"/>
+      <c r="T49" s="56"/>
+      <c r="U49" s="57"/>
       <c r="V49" s="1"/>
     </row>
     <row r="50" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="124" t="s">
+      <c r="A50" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="B50" s="125"/>
-      <c r="C50" s="132"/>
-      <c r="D50" s="132"/>
-      <c r="E50" s="132"/>
-      <c r="F50" s="132"/>
-      <c r="G50" s="132"/>
-      <c r="H50" s="132"/>
-      <c r="I50" s="146"/>
+      <c r="B50" s="132"/>
+      <c r="C50" s="136"/>
+      <c r="D50" s="136"/>
+      <c r="E50" s="136"/>
+      <c r="F50" s="136"/>
+      <c r="G50" s="136"/>
+      <c r="H50" s="136"/>
+      <c r="I50" s="143"/>
       <c r="J50" s="38"/>
       <c r="K50" s="38"/>
       <c r="L50" s="1"/>
-      <c r="M50" s="124" t="s">
+      <c r="M50" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="N50" s="125"/>
-      <c r="O50" s="132"/>
-      <c r="P50" s="132"/>
-      <c r="Q50" s="132"/>
-      <c r="R50" s="132"/>
-      <c r="S50" s="132"/>
-      <c r="T50" s="132"/>
-      <c r="U50" s="146"/>
+      <c r="N50" s="132"/>
+      <c r="O50" s="136"/>
+      <c r="P50" s="136"/>
+      <c r="Q50" s="136"/>
+      <c r="R50" s="136"/>
+      <c r="S50" s="136"/>
+      <c r="T50" s="136"/>
+      <c r="U50" s="143"/>
       <c r="V50" s="1"/>
     </row>
     <row r="51" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="124" t="s">
+      <c r="A51" s="131" t="s">
         <v>7</v>
       </c>
-      <c r="B51" s="131"/>
-      <c r="C51" s="52"/>
-      <c r="D51" s="53"/>
-      <c r="E51" s="53"/>
-      <c r="F51" s="53"/>
-      <c r="G51" s="53"/>
-      <c r="H51" s="53"/>
-      <c r="I51" s="54"/>
+      <c r="B51" s="140"/>
+      <c r="C51" s="50"/>
+      <c r="D51" s="51"/>
+      <c r="E51" s="51"/>
+      <c r="F51" s="51"/>
+      <c r="G51" s="51"/>
+      <c r="H51" s="51"/>
+      <c r="I51" s="52"/>
       <c r="J51" s="38"/>
       <c r="K51" s="38"/>
       <c r="L51" s="1" t="str">
         <f t="shared" ref="L51:L53" si="9">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C51:I51)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M51" s="124" t="s">
+      <c r="M51" s="131" t="s">
         <v>7</v>
       </c>
-      <c r="N51" s="131"/>
-      <c r="O51" s="52"/>
-      <c r="P51" s="53"/>
-      <c r="Q51" s="53"/>
-      <c r="R51" s="53"/>
-      <c r="S51" s="53"/>
-      <c r="T51" s="53"/>
-      <c r="U51" s="54"/>
+      <c r="N51" s="140"/>
+      <c r="O51" s="50"/>
+      <c r="P51" s="51"/>
+      <c r="Q51" s="51"/>
+      <c r="R51" s="51"/>
+      <c r="S51" s="51"/>
+      <c r="T51" s="51"/>
+      <c r="U51" s="52"/>
       <c r="V51" s="1" t="str">
         <f t="shared" ref="V51:V53" si="10">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,O51:U51)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
     </row>
     <row r="52" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="128" t="s">
+      <c r="A52" s="133" t="s">
         <v>8</v>
       </c>
-      <c r="B52" s="130"/>
-      <c r="C52" s="55"/>
+      <c r="B52" s="135"/>
+      <c r="C52" s="53"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
-      <c r="I52" s="56"/>
+      <c r="I52" s="54"/>
       <c r="J52" s="38"/>
       <c r="K52" s="38"/>
       <c r="L52" s="1" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M52" s="124" t="s">
+      <c r="M52" s="131" t="s">
         <v>8</v>
       </c>
-      <c r="N52" s="131"/>
-      <c r="O52" s="55"/>
+      <c r="N52" s="140"/>
+      <c r="O52" s="53"/>
       <c r="P52" s="1"/>
       <c r="Q52" s="1"/>
       <c r="R52" s="1"/>
       <c r="S52" s="1"/>
       <c r="T52" s="1"/>
-      <c r="U52" s="56"/>
+      <c r="U52" s="54"/>
       <c r="V52" s="1" t="str">
         <f t="shared" si="10"/>
         <v xml:space="preserve">    ,</v>
       </c>
     </row>
     <row r="53" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="124" t="s">
+      <c r="A53" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="B53" s="131"/>
-      <c r="C53" s="55"/>
+      <c r="B53" s="140"/>
+      <c r="C53" s="53"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
-      <c r="I53" s="56"/>
+      <c r="I53" s="54"/>
       <c r="J53" s="38"/>
       <c r="K53" s="38"/>
       <c r="L53" s="1" t="str">
         <f t="shared" si="9"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M53" s="124" t="s">
+      <c r="M53" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="N53" s="131"/>
-      <c r="O53" s="55"/>
+      <c r="N53" s="140"/>
+      <c r="O53" s="53"/>
       <c r="P53" s="1"/>
       <c r="Q53" s="1"/>
       <c r="R53" s="1"/>
       <c r="S53" s="1"/>
       <c r="T53" s="1"/>
-      <c r="U53" s="56"/>
+      <c r="U53" s="54"/>
       <c r="V53" s="1" t="str">
         <f t="shared" si="10"/>
         <v xml:space="preserve">    ,</v>
       </c>
     </row>
     <row r="54" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="124" t="s">
+      <c r="A54" s="131" t="s">
         <v>22</v>
       </c>
-      <c r="B54" s="131"/>
-      <c r="C54" s="57"/>
-      <c r="D54" s="58"/>
-      <c r="E54" s="58"/>
-      <c r="F54" s="58"/>
-      <c r="G54" s="58"/>
-      <c r="H54" s="58"/>
-      <c r="I54" s="59"/>
+      <c r="B54" s="140"/>
+      <c r="C54" s="55"/>
+      <c r="D54" s="56"/>
+      <c r="E54" s="56"/>
+      <c r="F54" s="56"/>
+      <c r="G54" s="56"/>
+      <c r="H54" s="56"/>
+      <c r="I54" s="57"/>
       <c r="J54" s="38"/>
       <c r="K54" s="38"/>
       <c r="L54" s="1"/>
-      <c r="M54" s="124" t="s">
+      <c r="M54" s="131" t="s">
         <v>22</v>
       </c>
-      <c r="N54" s="131"/>
-      <c r="O54" s="57"/>
-      <c r="P54" s="58"/>
-      <c r="Q54" s="58"/>
-      <c r="R54" s="58"/>
-      <c r="S54" s="58"/>
-      <c r="T54" s="58"/>
-      <c r="U54" s="59"/>
+      <c r="N54" s="140"/>
+      <c r="O54" s="55"/>
+      <c r="P54" s="56"/>
+      <c r="Q54" s="56"/>
+      <c r="R54" s="56"/>
+      <c r="S54" s="56"/>
+      <c r="T54" s="56"/>
+      <c r="U54" s="57"/>
       <c r="V54" s="1"/>
     </row>
     <row r="55" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="124" t="s">
+      <c r="A55" s="131" t="s">
         <v>24</v>
       </c>
-      <c r="B55" s="125"/>
-      <c r="C55" s="132"/>
-      <c r="D55" s="132"/>
-      <c r="E55" s="132"/>
-      <c r="F55" s="132"/>
-      <c r="G55" s="132"/>
-      <c r="H55" s="132"/>
-      <c r="I55" s="146"/>
+      <c r="B55" s="132"/>
+      <c r="C55" s="136"/>
+      <c r="D55" s="136"/>
+      <c r="E55" s="136"/>
+      <c r="F55" s="136"/>
+      <c r="G55" s="136"/>
+      <c r="H55" s="136"/>
+      <c r="I55" s="143"/>
       <c r="J55" s="38"/>
       <c r="K55" s="38"/>
       <c r="L55" s="1"/>
-      <c r="M55" s="124" t="s">
+      <c r="M55" s="131" t="s">
         <v>23</v>
       </c>
-      <c r="N55" s="125"/>
-      <c r="O55" s="132"/>
-      <c r="P55" s="132"/>
-      <c r="Q55" s="132"/>
-      <c r="R55" s="132"/>
-      <c r="S55" s="132"/>
-      <c r="T55" s="132"/>
-      <c r="U55" s="146"/>
+      <c r="N55" s="132"/>
+      <c r="O55" s="136"/>
+      <c r="P55" s="136"/>
+      <c r="Q55" s="136"/>
+      <c r="R55" s="136"/>
+      <c r="S55" s="136"/>
+      <c r="T55" s="136"/>
+      <c r="U55" s="143"/>
       <c r="V55" s="1"/>
     </row>
     <row r="56" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="124" t="s">
+      <c r="A56" s="131" t="s">
         <v>7</v>
       </c>
-      <c r="B56" s="131"/>
+      <c r="B56" s="140"/>
       <c r="C56"/>
       <c r="D56"/>
       <c r="E56"/>
@@ -6086,10 +6188,10 @@
         <f t="shared" ref="L56:L58" si="11">"    "&amp;_xlfn.TEXTJOIN(", ",TRUE,C56:I56)&amp;","</f>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M56" s="124" t="s">
+      <c r="M56" s="131" t="s">
         <v>7</v>
       </c>
-      <c r="N56" s="131"/>
+      <c r="N56" s="140"/>
       <c r="O56"/>
       <c r="P56"/>
       <c r="Q56"/>
@@ -6103,10 +6205,10 @@
       </c>
     </row>
     <row r="57" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="128" t="s">
+      <c r="A57" s="133" t="s">
         <v>8</v>
       </c>
-      <c r="B57" s="130"/>
+      <c r="B57" s="135"/>
       <c r="C57"/>
       <c r="D57"/>
       <c r="E57"/>
@@ -6120,10 +6222,10 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M57" s="124" t="s">
+      <c r="M57" s="131" t="s">
         <v>8</v>
       </c>
-      <c r="N57" s="131"/>
+      <c r="N57" s="140"/>
       <c r="O57"/>
       <c r="P57"/>
       <c r="Q57"/>
@@ -6137,10 +6239,10 @@
       </c>
     </row>
     <row r="58" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="124" t="s">
+      <c r="A58" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="B58" s="131"/>
+      <c r="B58" s="140"/>
       <c r="C58"/>
       <c r="D58"/>
       <c r="E58"/>
@@ -6154,10 +6256,10 @@
         <f t="shared" si="11"/>
         <v xml:space="preserve">    ,</v>
       </c>
-      <c r="M58" s="124" t="s">
+      <c r="M58" s="131" t="s">
         <v>21</v>
       </c>
-      <c r="N58" s="131"/>
+      <c r="N58" s="140"/>
       <c r="O58"/>
       <c r="P58"/>
       <c r="Q58"/>
@@ -6171,31 +6273,31 @@
       </c>
     </row>
     <row r="59" spans="1:22" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="124" t="s">
+      <c r="A59" s="131" t="s">
         <v>22</v>
       </c>
-      <c r="B59" s="131"/>
-      <c r="C59" s="72"/>
-      <c r="D59" s="73"/>
-      <c r="E59" s="73"/>
-      <c r="F59" s="73"/>
-      <c r="G59" s="73"/>
-      <c r="H59" s="73"/>
-      <c r="I59" s="74"/>
+      <c r="B59" s="140"/>
+      <c r="C59" s="70"/>
+      <c r="D59" s="71"/>
+      <c r="E59" s="71"/>
+      <c r="F59" s="71"/>
+      <c r="G59" s="71"/>
+      <c r="H59" s="71"/>
+      <c r="I59" s="72"/>
       <c r="J59" s="38"/>
       <c r="K59" s="38"/>
       <c r="L59" s="1"/>
-      <c r="M59" s="124" t="s">
+      <c r="M59" s="131" t="s">
         <v>22</v>
       </c>
-      <c r="N59" s="131"/>
-      <c r="O59" s="72"/>
-      <c r="P59" s="73"/>
-      <c r="Q59" s="73"/>
-      <c r="R59" s="73"/>
-      <c r="S59" s="73"/>
-      <c r="T59" s="73"/>
-      <c r="U59" s="74"/>
+      <c r="N59" s="140"/>
+      <c r="O59" s="70"/>
+      <c r="P59" s="71"/>
+      <c r="Q59" s="71"/>
+      <c r="R59" s="71"/>
+      <c r="S59" s="71"/>
+      <c r="T59" s="71"/>
+      <c r="U59" s="72"/>
       <c r="V59" s="1"/>
     </row>
     <row r="60" spans="1:22" ht="15" x14ac:dyDescent="0.2">
@@ -6214,6 +6316,70 @@
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="M59:N59"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="M56:N56"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="M57:N57"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="M58:N58"/>
+    <mergeCell ref="A6:A14"/>
+    <mergeCell ref="M6:M14"/>
+    <mergeCell ref="A36:A44"/>
+    <mergeCell ref="M36:M44"/>
+    <mergeCell ref="A55:I55"/>
+    <mergeCell ref="M55:U55"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="M25:U25"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="M53:N53"/>
+    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="M54:N54"/>
+    <mergeCell ref="A50:I50"/>
+    <mergeCell ref="M50:U50"/>
+    <mergeCell ref="A51:B51"/>
+    <mergeCell ref="M51:N51"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="M52:N52"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="M15:U15"/>
+    <mergeCell ref="M45:U45"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="M35:U35"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="A48:B48"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="M48:N48"/>
+    <mergeCell ref="M49:N49"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="A46:B46"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="M46:N46"/>
+    <mergeCell ref="M47:N47"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="M34:N34"/>
+    <mergeCell ref="A35:I35"/>
+    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="M2:N2"/>
     <mergeCell ref="A32:B32"/>
@@ -6230,70 +6396,6 @@
     <mergeCell ref="A15:I15"/>
     <mergeCell ref="A25:I25"/>
     <mergeCell ref="A26:B26"/>
-    <mergeCell ref="A48:B48"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="M48:N48"/>
-    <mergeCell ref="M49:N49"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="A46:B46"/>
-    <mergeCell ref="A47:B47"/>
-    <mergeCell ref="M46:N46"/>
-    <mergeCell ref="M47:N47"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="M34:N34"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A45:I45"/>
-    <mergeCell ref="M15:U15"/>
-    <mergeCell ref="M45:U45"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="M35:U35"/>
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="A54:B54"/>
-    <mergeCell ref="M54:N54"/>
-    <mergeCell ref="A50:I50"/>
-    <mergeCell ref="M50:U50"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="M51:N51"/>
-    <mergeCell ref="A52:B52"/>
-    <mergeCell ref="M52:N52"/>
-    <mergeCell ref="A6:A14"/>
-    <mergeCell ref="M6:M14"/>
-    <mergeCell ref="A36:A44"/>
-    <mergeCell ref="M36:M44"/>
-    <mergeCell ref="A55:I55"/>
-    <mergeCell ref="M55:U55"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="M25:U25"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="A53:B53"/>
-    <mergeCell ref="M53:N53"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="M59:N59"/>
-    <mergeCell ref="A56:B56"/>
-    <mergeCell ref="M56:N56"/>
-    <mergeCell ref="A57:B57"/>
-    <mergeCell ref="M57:N57"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="M58:N58"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="C2:I4 C6:I14 C16:I19 C21:I24 C26:I29">
@@ -6757,61 +6859,61 @@
   <sheetData>
     <row r="2" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="2:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="B3" s="150" t="s">
+      <c r="B3" s="146" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="156"/>
-      <c r="D3" s="153" t="s">
+      <c r="C3" s="150"/>
+      <c r="D3" s="152" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="154"/>
-      <c r="F3" s="154"/>
-      <c r="G3" s="155"/>
+      <c r="E3" s="153"/>
+      <c r="F3" s="153"/>
+      <c r="G3" s="154"/>
     </row>
     <row r="4" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="152"/>
-      <c r="C4" s="157"/>
-      <c r="D4" s="94" t="s">
+      <c r="B4" s="148"/>
+      <c r="C4" s="151"/>
+      <c r="D4" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="93" t="s">
+      <c r="E4" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="93" t="s">
+      <c r="F4" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="68" t="s">
+      <c r="G4" s="66" t="s">
         <v>32</v>
       </c>
       <c r="K4" s="25"/>
       <c r="L4" s="25"/>
     </row>
     <row r="5" spans="2:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="B5" s="150" t="s">
+      <c r="B5" s="146" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="92" t="s">
+      <c r="C5" s="88" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="66">
+      <c r="D5" s="64">
         <v>83.95</v>
       </c>
-      <c r="E5" s="116">
+      <c r="E5" s="112">
         <v>84.26</v>
       </c>
-      <c r="F5" s="116">
+      <c r="F5" s="112">
         <v>84.42</v>
       </c>
-      <c r="G5" s="117">
+      <c r="G5" s="113">
         <v>83.98</v>
       </c>
     </row>
     <row r="6" spans="2:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="B6" s="151"/>
-      <c r="C6" s="93" t="s">
+      <c r="B6" s="147"/>
+      <c r="C6" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="67">
+      <c r="D6" s="65">
         <v>83.86</v>
       </c>
       <c r="E6" s="25">
@@ -6820,148 +6922,148 @@
       <c r="F6" s="25">
         <v>83.06</v>
       </c>
-      <c r="G6" s="96">
+      <c r="G6" s="92">
         <v>83.47</v>
       </c>
     </row>
     <row r="7" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="152"/>
-      <c r="C7" s="69" t="s">
+      <c r="B7" s="148"/>
+      <c r="C7" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="71">
+      <c r="D7" s="69">
         <v>82.35</v>
       </c>
-      <c r="E7" s="70">
+      <c r="E7" s="68">
         <v>80.72</v>
       </c>
-      <c r="F7" s="70">
+      <c r="F7" s="68">
         <v>82.35</v>
       </c>
-      <c r="G7" s="97">
+      <c r="G7" s="93">
         <v>79.91</v>
       </c>
     </row>
     <row r="8" spans="2:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="B8" s="95"/>
-      <c r="C8" s="93"/>
+      <c r="B8" s="91"/>
+      <c r="C8" s="89"/>
       <c r="D8" s="25"/>
       <c r="E8" s="25"/>
       <c r="F8" s="25"/>
       <c r="G8" s="25"/>
     </row>
     <row r="9" spans="2:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="B9" s="95"/>
-      <c r="C9" s="93"/>
+      <c r="B9" s="91"/>
+      <c r="C9" s="89"/>
       <c r="D9" s="25"/>
       <c r="E9" s="25"/>
       <c r="F9" s="25"/>
       <c r="G9" s="25"/>
     </row>
     <row r="10" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="95"/>
-      <c r="C10" s="93"/>
+      <c r="B10" s="91"/>
+      <c r="C10" s="89"/>
       <c r="D10" s="25"/>
       <c r="E10" s="25"/>
       <c r="F10" s="25"/>
       <c r="G10" s="25"/>
     </row>
     <row r="11" spans="2:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="B11" s="158" t="s">
+      <c r="B11" s="149" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="156"/>
-      <c r="D11" s="153" t="s">
+      <c r="C11" s="150"/>
+      <c r="D11" s="152" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="154"/>
-      <c r="F11" s="154"/>
-      <c r="G11" s="155"/>
-      <c r="I11" s="158" t="s">
+      <c r="E11" s="153"/>
+      <c r="F11" s="153"/>
+      <c r="G11" s="154"/>
+      <c r="I11" s="149" t="s">
         <v>38</v>
       </c>
-      <c r="J11" s="156"/>
-      <c r="K11" s="153" t="s">
+      <c r="J11" s="150"/>
+      <c r="K11" s="152" t="s">
         <v>31</v>
       </c>
-      <c r="L11" s="154"/>
-      <c r="M11" s="154"/>
-      <c r="N11" s="155"/>
+      <c r="L11" s="153"/>
+      <c r="M11" s="153"/>
+      <c r="N11" s="154"/>
     </row>
     <row r="12" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="152"/>
-      <c r="C12" s="157"/>
-      <c r="D12" s="94" t="s">
+      <c r="B12" s="148"/>
+      <c r="C12" s="151"/>
+      <c r="D12" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="93" t="s">
+      <c r="E12" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="93" t="s">
+      <c r="F12" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="68" t="s">
+      <c r="G12" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="152"/>
-      <c r="J12" s="157"/>
-      <c r="K12" s="94" t="s">
+      <c r="I12" s="148"/>
+      <c r="J12" s="151"/>
+      <c r="K12" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="L12" s="93" t="s">
+      <c r="L12" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="M12" s="93" t="s">
+      <c r="M12" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="N12" s="68" t="s">
+      <c r="N12" s="66" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="13" spans="2:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="B13" s="150" t="s">
+      <c r="B13" s="146" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="92" t="s">
+      <c r="C13" s="88" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="66">
+      <c r="D13" s="64">
         <v>93.38</v>
       </c>
-      <c r="E13" s="116">
+      <c r="E13" s="112">
         <v>93.36</v>
       </c>
-      <c r="F13" s="116">
+      <c r="F13" s="112">
         <v>92.74</v>
       </c>
-      <c r="G13" s="117">
+      <c r="G13" s="113">
         <v>92.97</v>
       </c>
-      <c r="I13" s="150" t="s">
+      <c r="I13" s="146" t="s">
         <v>30</v>
       </c>
-      <c r="J13" s="92" t="s">
+      <c r="J13" s="88" t="s">
         <v>27</v>
       </c>
-      <c r="K13" s="66">
+      <c r="K13" s="64">
         <v>92.79</v>
       </c>
-      <c r="L13" s="116">
+      <c r="L13" s="112">
         <v>92.79</v>
       </c>
-      <c r="M13" s="116">
+      <c r="M13" s="112">
         <v>92.33</v>
       </c>
-      <c r="N13" s="117">
+      <c r="N13" s="113">
         <v>92.66</v>
       </c>
     </row>
     <row r="14" spans="2:14" ht="15" x14ac:dyDescent="0.25">
-      <c r="B14" s="151"/>
-      <c r="C14" s="93" t="s">
+      <c r="B14" s="147"/>
+      <c r="C14" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="67">
+      <c r="D14" s="65">
         <v>93.58</v>
       </c>
       <c r="E14" s="25">
@@ -6970,14 +7072,14 @@
       <c r="F14" s="25">
         <v>91.3</v>
       </c>
-      <c r="G14" s="96">
+      <c r="G14" s="92">
         <v>93.55</v>
       </c>
-      <c r="I14" s="151"/>
-      <c r="J14" s="93" t="s">
+      <c r="I14" s="147"/>
+      <c r="J14" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="K14" s="67">
+      <c r="K14" s="65">
         <v>92.72</v>
       </c>
       <c r="L14" s="25">
@@ -6986,183 +7088,183 @@
       <c r="M14" s="25">
         <v>90.82</v>
       </c>
-      <c r="N14" s="96">
+      <c r="N14" s="92">
         <v>92.28</v>
       </c>
     </row>
     <row r="15" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="152"/>
-      <c r="C15" s="69" t="s">
+      <c r="B15" s="148"/>
+      <c r="C15" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="71">
+      <c r="D15" s="69">
         <v>92.55</v>
       </c>
-      <c r="E15" s="70">
+      <c r="E15" s="68">
         <v>89.15</v>
       </c>
-      <c r="F15" s="70">
+      <c r="F15" s="68">
         <v>88.35</v>
       </c>
-      <c r="G15" s="97">
+      <c r="G15" s="93">
         <v>88.64</v>
       </c>
-      <c r="I15" s="152"/>
-      <c r="J15" s="69" t="s">
+      <c r="I15" s="148"/>
+      <c r="J15" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="K15" s="71">
+      <c r="K15" s="69">
         <v>90.33</v>
       </c>
-      <c r="L15" s="70">
+      <c r="L15" s="68">
         <v>88.34</v>
       </c>
-      <c r="M15" s="70">
+      <c r="M15" s="68">
         <v>87.26</v>
       </c>
-      <c r="N15" s="97">
+      <c r="N15" s="93">
         <v>87.59</v>
       </c>
     </row>
     <row r="16" spans="2:14" ht="15" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="17" spans="2:21" ht="15" x14ac:dyDescent="0.25">
-      <c r="B17" s="158" t="s">
+      <c r="B17" s="149" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="156"/>
-      <c r="D17" s="153" t="s">
+      <c r="C17" s="150"/>
+      <c r="D17" s="152" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="154"/>
-      <c r="F17" s="154"/>
-      <c r="G17" s="155"/>
-      <c r="I17" s="158" t="s">
+      <c r="E17" s="153"/>
+      <c r="F17" s="153"/>
+      <c r="G17" s="154"/>
+      <c r="I17" s="149" t="s">
         <v>35</v>
       </c>
-      <c r="J17" s="156"/>
-      <c r="K17" s="153" t="s">
+      <c r="J17" s="150"/>
+      <c r="K17" s="152" t="s">
         <v>31</v>
       </c>
-      <c r="L17" s="154"/>
-      <c r="M17" s="154"/>
-      <c r="N17" s="155"/>
-      <c r="P17" s="158" t="s">
+      <c r="L17" s="153"/>
+      <c r="M17" s="153"/>
+      <c r="N17" s="154"/>
+      <c r="P17" s="149" t="s">
         <v>34</v>
       </c>
-      <c r="Q17" s="156"/>
-      <c r="R17" s="153" t="s">
+      <c r="Q17" s="150"/>
+      <c r="R17" s="152" t="s">
         <v>31</v>
       </c>
-      <c r="S17" s="154"/>
-      <c r="T17" s="154"/>
-      <c r="U17" s="155"/>
+      <c r="S17" s="153"/>
+      <c r="T17" s="153"/>
+      <c r="U17" s="154"/>
     </row>
     <row r="18" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="152"/>
-      <c r="C18" s="157"/>
-      <c r="D18" s="94" t="s">
+      <c r="B18" s="148"/>
+      <c r="C18" s="151"/>
+      <c r="D18" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="93" t="s">
+      <c r="E18" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="93" t="s">
+      <c r="F18" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="G18" s="68" t="s">
+      <c r="G18" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="I18" s="152"/>
-      <c r="J18" s="157"/>
-      <c r="K18" s="94" t="s">
+      <c r="I18" s="148"/>
+      <c r="J18" s="151"/>
+      <c r="K18" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="L18" s="93" t="s">
+      <c r="L18" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="M18" s="93" t="s">
+      <c r="M18" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="N18" s="68" t="s">
+      <c r="N18" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="P18" s="152"/>
-      <c r="Q18" s="157"/>
-      <c r="R18" s="94" t="s">
+      <c r="P18" s="148"/>
+      <c r="Q18" s="151"/>
+      <c r="R18" s="90" t="s">
         <v>27</v>
       </c>
-      <c r="S18" s="93" t="s">
+      <c r="S18" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="T18" s="93" t="s">
+      <c r="T18" s="89" t="s">
         <v>29</v>
       </c>
-      <c r="U18" s="68" t="s">
+      <c r="U18" s="66" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="19" spans="2:21" ht="15" x14ac:dyDescent="0.25">
-      <c r="B19" s="150" t="s">
+      <c r="B19" s="146" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="92" t="s">
+      <c r="C19" s="88" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="66">
+      <c r="D19" s="64">
         <v>91.1</v>
       </c>
-      <c r="E19" s="116">
+      <c r="E19" s="112">
         <v>91.28</v>
       </c>
-      <c r="F19" s="116">
+      <c r="F19" s="112">
         <v>91.16</v>
       </c>
-      <c r="G19" s="117">
+      <c r="G19" s="113">
         <v>90.61</v>
       </c>
-      <c r="I19" s="150" t="s">
+      <c r="I19" s="146" t="s">
         <v>30</v>
       </c>
-      <c r="J19" s="92" t="s">
+      <c r="J19" s="88" t="s">
         <v>27</v>
       </c>
-      <c r="K19" s="66">
+      <c r="K19" s="64">
         <v>74.37</v>
       </c>
-      <c r="L19" s="116">
+      <c r="L19" s="112">
         <v>77.239999999999995</v>
       </c>
-      <c r="M19" s="116">
+      <c r="M19" s="112">
         <v>82.31</v>
       </c>
-      <c r="N19" s="117">
+      <c r="N19" s="113">
         <v>76.89</v>
       </c>
-      <c r="P19" s="150" t="s">
+      <c r="P19" s="146" t="s">
         <v>30</v>
       </c>
-      <c r="Q19" s="92" t="s">
+      <c r="Q19" s="88" t="s">
         <v>27</v>
       </c>
-      <c r="R19" s="66">
+      <c r="R19" s="64">
         <v>56.35</v>
       </c>
-      <c r="S19" s="116">
+      <c r="S19" s="112">
         <v>56.64</v>
       </c>
-      <c r="T19" s="116">
+      <c r="T19" s="112">
         <v>57.69</v>
       </c>
-      <c r="U19" s="117">
+      <c r="U19" s="113">
         <v>57.43</v>
       </c>
     </row>
     <row r="20" spans="2:21" ht="15" x14ac:dyDescent="0.25">
-      <c r="B20" s="151"/>
-      <c r="C20" s="93" t="s">
+      <c r="B20" s="147"/>
+      <c r="C20" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="67">
+      <c r="D20" s="65">
         <v>90.92</v>
       </c>
       <c r="E20" s="25">
@@ -7171,14 +7273,14 @@
       <c r="F20" s="25">
         <v>89.93</v>
       </c>
-      <c r="G20" s="96">
+      <c r="G20" s="92">
         <v>90.5</v>
       </c>
-      <c r="I20" s="151"/>
-      <c r="J20" s="93" t="s">
+      <c r="I20" s="147"/>
+      <c r="J20" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="K20" s="67">
+      <c r="K20" s="65">
         <v>73.430000000000007</v>
       </c>
       <c r="L20" s="25">
@@ -7187,14 +7289,14 @@
       <c r="M20" s="25">
         <v>80.989999999999995</v>
       </c>
-      <c r="N20" s="96">
+      <c r="N20" s="92">
         <v>72.8</v>
       </c>
-      <c r="P20" s="151"/>
-      <c r="Q20" s="93" t="s">
+      <c r="P20" s="147"/>
+      <c r="Q20" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="R20" s="67">
+      <c r="R20" s="65">
         <v>56.56</v>
       </c>
       <c r="S20" s="25">
@@ -7203,70 +7305,62 @@
       <c r="T20" s="25">
         <v>55.07</v>
       </c>
-      <c r="U20" s="96">
+      <c r="U20" s="92">
         <v>54.06</v>
       </c>
     </row>
     <row r="21" spans="2:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B21" s="152"/>
-      <c r="C21" s="69" t="s">
+      <c r="B21" s="148"/>
+      <c r="C21" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="71">
+      <c r="D21" s="69">
         <v>89.67</v>
       </c>
-      <c r="E21" s="70">
+      <c r="E21" s="68">
         <v>87.91</v>
       </c>
-      <c r="F21" s="70">
+      <c r="F21" s="68">
         <v>87.1</v>
       </c>
-      <c r="G21" s="97">
+      <c r="G21" s="93">
         <v>87.1</v>
       </c>
-      <c r="I21" s="152"/>
-      <c r="J21" s="69" t="s">
+      <c r="I21" s="148"/>
+      <c r="J21" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="K21" s="71">
+      <c r="K21" s="69">
         <v>78.680000000000007</v>
       </c>
-      <c r="L21" s="70">
+      <c r="L21" s="68">
         <v>77.040000000000006</v>
       </c>
-      <c r="M21" s="70">
+      <c r="M21" s="68">
         <v>75.41</v>
       </c>
-      <c r="N21" s="97">
+      <c r="N21" s="93">
         <v>74.819999999999993</v>
       </c>
-      <c r="P21" s="152"/>
-      <c r="Q21" s="69" t="s">
+      <c r="P21" s="148"/>
+      <c r="Q21" s="67" t="s">
         <v>29</v>
       </c>
-      <c r="R21" s="71">
+      <c r="R21" s="69">
         <v>53.09</v>
       </c>
-      <c r="S21" s="70">
+      <c r="S21" s="68">
         <v>51.47</v>
       </c>
-      <c r="T21" s="70">
+      <c r="T21" s="68">
         <v>50.41</v>
       </c>
-      <c r="U21" s="97">
+      <c r="U21" s="93">
         <v>50.06</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="P19:P21"/>
-    <mergeCell ref="I17:J18"/>
-    <mergeCell ref="K17:N17"/>
-    <mergeCell ref="I19:I21"/>
-    <mergeCell ref="B17:C18"/>
-    <mergeCell ref="D17:G17"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="P17:Q18"/>
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="D3:G3"/>
     <mergeCell ref="B3:C4"/>
@@ -7277,6 +7371,14 @@
     <mergeCell ref="K11:N11"/>
     <mergeCell ref="B13:B15"/>
     <mergeCell ref="I13:I15"/>
+    <mergeCell ref="P19:P21"/>
+    <mergeCell ref="I17:J18"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="I19:I21"/>
+    <mergeCell ref="B17:C18"/>
+    <mergeCell ref="D17:G17"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="P17:Q18"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="D5:F7">
@@ -7752,775 +7854,780 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="98"/>
-      <c r="B2" s="98"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="98"/>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="98"/>
-      <c r="J2" s="98"/>
-      <c r="K2" s="98"/>
-      <c r="L2" s="98"/>
-      <c r="M2" s="98"/>
-      <c r="N2" s="98"/>
-      <c r="O2" s="98"/>
-      <c r="P2" s="98"/>
-      <c r="Q2" s="98"/>
-      <c r="R2" s="98"/>
-      <c r="S2" s="98"/>
-      <c r="T2" s="98"/>
-      <c r="U2" s="98"/>
-      <c r="V2" s="98"/>
+      <c r="A2" s="94"/>
+      <c r="B2" s="94"/>
+      <c r="C2" s="94"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
+      <c r="H2" s="94"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="94"/>
+      <c r="K2" s="94"/>
+      <c r="L2" s="94"/>
+      <c r="M2" s="94"/>
+      <c r="N2" s="94"/>
+      <c r="O2" s="94"/>
+      <c r="P2" s="94"/>
+      <c r="Q2" s="94"/>
+      <c r="R2" s="94"/>
+      <c r="S2" s="94"/>
+      <c r="T2" s="94"/>
+      <c r="U2" s="94"/>
+      <c r="V2" s="94"/>
     </row>
     <row r="3" spans="1:22" ht="15" x14ac:dyDescent="0.25">
-      <c r="A3" s="98"/>
-      <c r="B3" s="166" t="s">
+      <c r="A3" s="94"/>
+      <c r="B3" s="158" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="160"/>
-      <c r="D3" s="163" t="s">
+      <c r="C3" s="162"/>
+      <c r="D3" s="155" t="s">
         <v>31</v>
       </c>
-      <c r="E3" s="164"/>
-      <c r="F3" s="164"/>
-      <c r="G3" s="165"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="98"/>
-      <c r="J3" s="98"/>
-      <c r="K3" s="98"/>
-      <c r="L3" s="98"/>
-      <c r="M3" s="98"/>
-      <c r="N3" s="98"/>
-      <c r="O3" s="98"/>
-      <c r="P3" s="98"/>
-      <c r="Q3" s="98"/>
-      <c r="R3" s="98"/>
-      <c r="S3" s="98"/>
-      <c r="T3" s="98"/>
-      <c r="U3" s="98"/>
-      <c r="V3" s="98"/>
+      <c r="E3" s="156"/>
+      <c r="F3" s="156"/>
+      <c r="G3" s="157"/>
+      <c r="H3" s="94"/>
+      <c r="I3" s="94"/>
+      <c r="J3" s="94"/>
+      <c r="K3" s="94"/>
+      <c r="L3" s="94"/>
+      <c r="M3" s="94"/>
+      <c r="N3" s="94"/>
+      <c r="O3" s="94"/>
+      <c r="P3" s="94"/>
+      <c r="Q3" s="94"/>
+      <c r="R3" s="94"/>
+      <c r="S3" s="94"/>
+      <c r="T3" s="94"/>
+      <c r="U3" s="94"/>
+      <c r="V3" s="94"/>
     </row>
     <row r="4" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="98"/>
-      <c r="B4" s="161"/>
-      <c r="C4" s="162"/>
-      <c r="D4" s="100" t="s">
+      <c r="A4" s="94"/>
+      <c r="B4" s="160"/>
+      <c r="C4" s="163"/>
+      <c r="D4" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="E4" s="101" t="s">
+      <c r="E4" s="97" t="s">
         <v>27</v>
       </c>
-      <c r="F4" s="102" t="s">
+      <c r="F4" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="G4" s="103" t="s">
+      <c r="G4" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="98"/>
-      <c r="I4" s="98"/>
-      <c r="J4" s="98"/>
-      <c r="K4" s="104"/>
-      <c r="L4" s="104"/>
-      <c r="M4" s="98"/>
-      <c r="N4" s="98"/>
-      <c r="O4" s="98"/>
-      <c r="P4" s="98"/>
-      <c r="Q4" s="98"/>
-      <c r="R4" s="98"/>
-      <c r="S4" s="98"/>
-      <c r="T4" s="98"/>
-      <c r="U4" s="98"/>
-      <c r="V4" s="98"/>
+      <c r="H4" s="94"/>
+      <c r="I4" s="94"/>
+      <c r="J4" s="94"/>
+      <c r="K4" s="100"/>
+      <c r="L4" s="100"/>
+      <c r="M4" s="94"/>
+      <c r="N4" s="94"/>
+      <c r="O4" s="94"/>
+      <c r="P4" s="94"/>
+      <c r="Q4" s="94"/>
+      <c r="R4" s="94"/>
+      <c r="S4" s="94"/>
+      <c r="T4" s="94"/>
+      <c r="U4" s="94"/>
+      <c r="V4" s="94"/>
     </row>
     <row r="5" spans="1:22" ht="15" x14ac:dyDescent="0.25">
-      <c r="A5" s="98"/>
-      <c r="B5" s="166" t="s">
+      <c r="A5" s="94"/>
+      <c r="B5" s="158" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="99" t="s">
+      <c r="C5" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="105">
+      <c r="D5" s="101">
         <v>83.98</v>
       </c>
-      <c r="E5" s="106">
+      <c r="E5" s="102">
         <v>83.95</v>
       </c>
-      <c r="F5" s="104">
+      <c r="F5" s="100">
         <v>84.26</v>
       </c>
-      <c r="G5" s="107">
+      <c r="G5" s="103">
         <v>84.42</v>
       </c>
-      <c r="H5" s="98"/>
-      <c r="I5" s="98"/>
-      <c r="J5" s="98"/>
-      <c r="K5" s="98"/>
-      <c r="L5" s="98"/>
-      <c r="M5" s="98"/>
-      <c r="N5" s="98"/>
-      <c r="O5" s="98"/>
-      <c r="P5" s="98"/>
-      <c r="Q5" s="98"/>
-      <c r="R5" s="98"/>
-      <c r="S5" s="98"/>
-      <c r="T5" s="98"/>
-      <c r="U5" s="98"/>
-      <c r="V5" s="98"/>
+      <c r="H5" s="94"/>
+      <c r="I5" s="94"/>
+      <c r="J5" s="94"/>
+      <c r="K5" s="94"/>
+      <c r="L5" s="94"/>
+      <c r="M5" s="94"/>
+      <c r="N5" s="94"/>
+      <c r="O5" s="94"/>
+      <c r="P5" s="94"/>
+      <c r="Q5" s="94"/>
+      <c r="R5" s="94"/>
+      <c r="S5" s="94"/>
+      <c r="T5" s="94"/>
+      <c r="U5" s="94"/>
+      <c r="V5" s="94"/>
     </row>
     <row r="6" spans="1:22" ht="15" x14ac:dyDescent="0.25">
-      <c r="A6" s="98"/>
-      <c r="B6" s="167"/>
-      <c r="C6" s="100" t="s">
+      <c r="A6" s="94"/>
+      <c r="B6" s="159"/>
+      <c r="C6" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="108">
+      <c r="D6" s="104">
         <v>83.47</v>
       </c>
-      <c r="E6" s="109">
+      <c r="E6" s="105">
         <v>83.86</v>
       </c>
-      <c r="F6" s="104">
+      <c r="F6" s="100">
         <v>83.93</v>
       </c>
-      <c r="G6" s="107">
+      <c r="G6" s="103">
         <v>83.06</v>
       </c>
-      <c r="H6" s="98"/>
-      <c r="I6" s="98"/>
-      <c r="J6" s="98"/>
-      <c r="K6" s="98"/>
-      <c r="L6" s="98"/>
-      <c r="M6" s="98"/>
-      <c r="N6" s="98"/>
-      <c r="O6" s="98"/>
-      <c r="P6" s="98"/>
-      <c r="Q6" s="98"/>
-      <c r="R6" s="98"/>
-      <c r="S6" s="98"/>
-      <c r="T6" s="98"/>
-      <c r="U6" s="98"/>
-      <c r="V6" s="98"/>
+      <c r="H6" s="94"/>
+      <c r="I6" s="94"/>
+      <c r="J6" s="94"/>
+      <c r="K6" s="94"/>
+      <c r="L6" s="94"/>
+      <c r="M6" s="94"/>
+      <c r="N6" s="94"/>
+      <c r="O6" s="94"/>
+      <c r="P6" s="94"/>
+      <c r="Q6" s="94"/>
+      <c r="R6" s="94"/>
+      <c r="S6" s="94"/>
+      <c r="T6" s="94"/>
+      <c r="U6" s="94"/>
+      <c r="V6" s="94"/>
     </row>
     <row r="7" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="98"/>
-      <c r="B7" s="161"/>
-      <c r="C7" s="103" t="s">
+      <c r="A7" s="94"/>
+      <c r="B7" s="160"/>
+      <c r="C7" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="110">
+      <c r="D7" s="106">
         <v>79.91</v>
       </c>
-      <c r="E7" s="111">
+      <c r="E7" s="107">
         <v>82.35</v>
       </c>
-      <c r="F7" s="112">
+      <c r="F7" s="108">
         <v>80.72</v>
       </c>
-      <c r="G7" s="113">
+      <c r="G7" s="109">
         <v>82.35</v>
       </c>
-      <c r="H7" s="98"/>
-      <c r="I7" s="98"/>
-      <c r="J7" s="98"/>
-      <c r="K7" s="98"/>
-      <c r="L7" s="98"/>
-      <c r="M7" s="98"/>
-      <c r="N7" s="98"/>
-      <c r="O7" s="98"/>
-      <c r="P7" s="98"/>
-      <c r="Q7" s="98"/>
-      <c r="R7" s="98"/>
-      <c r="S7" s="98"/>
-      <c r="T7" s="98"/>
-      <c r="U7" s="98"/>
-      <c r="V7" s="98"/>
+      <c r="H7" s="94"/>
+      <c r="I7" s="94"/>
+      <c r="J7" s="94"/>
+      <c r="K7" s="94"/>
+      <c r="L7" s="94"/>
+      <c r="M7" s="94"/>
+      <c r="N7" s="94"/>
+      <c r="O7" s="94"/>
+      <c r="P7" s="94"/>
+      <c r="Q7" s="94"/>
+      <c r="R7" s="94"/>
+      <c r="S7" s="94"/>
+      <c r="T7" s="94"/>
+      <c r="U7" s="94"/>
+      <c r="V7" s="94"/>
     </row>
     <row r="8" spans="1:22" ht="15" x14ac:dyDescent="0.25">
-      <c r="A8" s="98"/>
-      <c r="B8" s="114"/>
-      <c r="C8" s="115"/>
-      <c r="D8" s="104"/>
-      <c r="E8" s="104"/>
-      <c r="F8" s="104"/>
-      <c r="G8" s="104"/>
-      <c r="H8" s="98"/>
-      <c r="I8" s="98"/>
-      <c r="J8" s="98"/>
-      <c r="K8" s="98"/>
-      <c r="L8" s="98"/>
-      <c r="M8" s="98"/>
-      <c r="N8" s="98"/>
-      <c r="O8" s="98"/>
-      <c r="P8" s="98"/>
-      <c r="Q8" s="98"/>
-      <c r="R8" s="98"/>
-      <c r="S8" s="98"/>
-      <c r="T8" s="98"/>
-      <c r="U8" s="98"/>
-      <c r="V8" s="98"/>
+      <c r="A8" s="94"/>
+      <c r="B8" s="110"/>
+      <c r="C8" s="111"/>
+      <c r="D8" s="100"/>
+      <c r="E8" s="100"/>
+      <c r="F8" s="100"/>
+      <c r="G8" s="100"/>
+      <c r="H8" s="94"/>
+      <c r="I8" s="94"/>
+      <c r="J8" s="94"/>
+      <c r="K8" s="94"/>
+      <c r="L8" s="94"/>
+      <c r="M8" s="94"/>
+      <c r="N8" s="94"/>
+      <c r="O8" s="94"/>
+      <c r="P8" s="94"/>
+      <c r="Q8" s="94"/>
+      <c r="R8" s="94"/>
+      <c r="S8" s="94"/>
+      <c r="T8" s="94"/>
+      <c r="U8" s="94"/>
+      <c r="V8" s="94"/>
     </row>
     <row r="9" spans="1:22" ht="15" x14ac:dyDescent="0.25">
-      <c r="A9" s="98"/>
-      <c r="B9" s="114"/>
-      <c r="C9" s="115"/>
-      <c r="D9" s="104"/>
-      <c r="E9" s="104"/>
-      <c r="F9" s="104"/>
-      <c r="G9" s="104"/>
-      <c r="H9" s="98"/>
-      <c r="I9" s="98"/>
-      <c r="J9" s="98"/>
-      <c r="K9" s="98"/>
-      <c r="L9" s="98"/>
-      <c r="M9" s="98"/>
-      <c r="N9" s="98"/>
-      <c r="O9" s="98"/>
-      <c r="P9" s="98"/>
-      <c r="Q9" s="98"/>
-      <c r="R9" s="98"/>
-      <c r="S9" s="98"/>
-      <c r="T9" s="98"/>
-      <c r="U9" s="98"/>
-      <c r="V9" s="98"/>
+      <c r="A9" s="94"/>
+      <c r="B9" s="110"/>
+      <c r="C9" s="111"/>
+      <c r="D9" s="100"/>
+      <c r="E9" s="100"/>
+      <c r="F9" s="100"/>
+      <c r="G9" s="100"/>
+      <c r="H9" s="94"/>
+      <c r="I9" s="94"/>
+      <c r="J9" s="94"/>
+      <c r="K9" s="94"/>
+      <c r="L9" s="94"/>
+      <c r="M9" s="94"/>
+      <c r="N9" s="94"/>
+      <c r="O9" s="94"/>
+      <c r="P9" s="94"/>
+      <c r="Q9" s="94"/>
+      <c r="R9" s="94"/>
+      <c r="S9" s="94"/>
+      <c r="T9" s="94"/>
+      <c r="U9" s="94"/>
+      <c r="V9" s="94"/>
     </row>
     <row r="10" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="98"/>
-      <c r="B10" s="114"/>
-      <c r="C10" s="115"/>
-      <c r="D10" s="104"/>
-      <c r="E10" s="104"/>
-      <c r="F10" s="104"/>
-      <c r="G10" s="104"/>
-      <c r="H10" s="98"/>
-      <c r="I10" s="98"/>
-      <c r="J10" s="98"/>
-      <c r="K10" s="98"/>
-      <c r="L10" s="98"/>
-      <c r="M10" s="98"/>
-      <c r="N10" s="98"/>
-      <c r="O10" s="98"/>
-      <c r="P10" s="98"/>
-      <c r="Q10" s="98"/>
-      <c r="R10" s="98"/>
-      <c r="S10" s="98"/>
-      <c r="T10" s="98"/>
-      <c r="U10" s="98"/>
-      <c r="V10" s="98"/>
+      <c r="A10" s="94"/>
+      <c r="B10" s="110"/>
+      <c r="C10" s="111"/>
+      <c r="D10" s="100"/>
+      <c r="E10" s="100"/>
+      <c r="F10" s="100"/>
+      <c r="G10" s="100"/>
+      <c r="H10" s="94"/>
+      <c r="I10" s="94"/>
+      <c r="J10" s="94"/>
+      <c r="K10" s="94"/>
+      <c r="L10" s="94"/>
+      <c r="M10" s="94"/>
+      <c r="N10" s="94"/>
+      <c r="O10" s="94"/>
+      <c r="P10" s="94"/>
+      <c r="Q10" s="94"/>
+      <c r="R10" s="94"/>
+      <c r="S10" s="94"/>
+      <c r="T10" s="94"/>
+      <c r="U10" s="94"/>
+      <c r="V10" s="94"/>
     </row>
     <row r="11" spans="1:22" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="98"/>
-      <c r="B11" s="159" t="s">
+      <c r="A11" s="94"/>
+      <c r="B11" s="161" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="160"/>
-      <c r="D11" s="163" t="s">
+      <c r="C11" s="162"/>
+      <c r="D11" s="155" t="s">
         <v>31</v>
       </c>
-      <c r="E11" s="164"/>
-      <c r="F11" s="164"/>
-      <c r="G11" s="165"/>
-      <c r="H11" s="98"/>
-      <c r="I11" s="159" t="s">
+      <c r="E11" s="156"/>
+      <c r="F11" s="156"/>
+      <c r="G11" s="157"/>
+      <c r="H11" s="94"/>
+      <c r="I11" s="161" t="s">
         <v>38</v>
       </c>
-      <c r="J11" s="160"/>
-      <c r="K11" s="163" t="s">
+      <c r="J11" s="162"/>
+      <c r="K11" s="155" t="s">
         <v>31</v>
       </c>
-      <c r="L11" s="164"/>
-      <c r="M11" s="164"/>
-      <c r="N11" s="165"/>
-      <c r="O11" s="98"/>
-      <c r="P11" s="98"/>
-      <c r="Q11" s="98"/>
-      <c r="R11" s="98"/>
-      <c r="S11" s="98"/>
-      <c r="T11" s="98"/>
-      <c r="U11" s="98"/>
-      <c r="V11" s="98"/>
+      <c r="L11" s="156"/>
+      <c r="M11" s="156"/>
+      <c r="N11" s="157"/>
+      <c r="O11" s="94"/>
+      <c r="P11" s="94"/>
+      <c r="Q11" s="94"/>
+      <c r="R11" s="94"/>
+      <c r="S11" s="94"/>
+      <c r="T11" s="94"/>
+      <c r="U11" s="94"/>
+      <c r="V11" s="94"/>
     </row>
     <row r="12" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="98"/>
-      <c r="B12" s="161"/>
-      <c r="C12" s="162"/>
-      <c r="D12" s="100" t="s">
+      <c r="A12" s="94"/>
+      <c r="B12" s="160"/>
+      <c r="C12" s="163"/>
+      <c r="D12" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="E12" s="101" t="s">
+      <c r="E12" s="97" t="s">
         <v>27</v>
       </c>
-      <c r="F12" s="102" t="s">
+      <c r="F12" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="G12" s="103" t="s">
+      <c r="G12" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="H12" s="98"/>
-      <c r="I12" s="161"/>
-      <c r="J12" s="162"/>
-      <c r="K12" s="101" t="s">
+      <c r="H12" s="94"/>
+      <c r="I12" s="160"/>
+      <c r="J12" s="163"/>
+      <c r="K12" s="97" t="s">
         <v>27</v>
       </c>
-      <c r="L12" s="102" t="s">
+      <c r="L12" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="M12" s="102" t="s">
+      <c r="M12" s="98" t="s">
         <v>29</v>
       </c>
-      <c r="N12" s="100" t="s">
+      <c r="N12" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="O12" s="98"/>
-      <c r="P12" s="98"/>
-      <c r="Q12" s="98"/>
-      <c r="R12" s="98"/>
-      <c r="S12" s="98"/>
-      <c r="T12" s="98"/>
-      <c r="U12" s="98"/>
-      <c r="V12" s="98"/>
+      <c r="O12" s="94"/>
+      <c r="P12" s="94"/>
+      <c r="Q12" s="94"/>
+      <c r="R12" s="94"/>
+      <c r="S12" s="94"/>
+      <c r="T12" s="94"/>
+      <c r="U12" s="94"/>
+      <c r="V12" s="94"/>
     </row>
     <row r="13" spans="1:22" ht="15" x14ac:dyDescent="0.25">
-      <c r="A13" s="98"/>
-      <c r="B13" s="166" t="s">
+      <c r="A13" s="94"/>
+      <c r="B13" s="158" t="s">
         <v>30</v>
       </c>
-      <c r="C13" s="99" t="s">
+      <c r="C13" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="105">
+      <c r="D13" s="101">
         <v>92.97</v>
       </c>
-      <c r="E13" s="106">
+      <c r="E13" s="102">
         <v>93.38</v>
       </c>
-      <c r="F13" s="104">
+      <c r="F13" s="100">
         <v>93.36</v>
       </c>
-      <c r="G13" s="107">
+      <c r="G13" s="103">
         <v>92.74</v>
       </c>
-      <c r="H13" s="98"/>
-      <c r="I13" s="166" t="s">
+      <c r="H13" s="94"/>
+      <c r="I13" s="158" t="s">
         <v>30</v>
       </c>
-      <c r="J13" s="99" t="s">
+      <c r="J13" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="K13" s="106">
+      <c r="K13" s="102">
         <v>92.79</v>
       </c>
-      <c r="L13" s="104">
+      <c r="L13" s="100">
         <v>92.79</v>
       </c>
-      <c r="M13" s="104">
+      <c r="M13" s="100">
         <v>92.33</v>
       </c>
-      <c r="N13" s="105">
+      <c r="N13" s="101">
         <v>92.66</v>
       </c>
-      <c r="O13" s="98"/>
-      <c r="P13" s="98"/>
-      <c r="Q13" s="98"/>
-      <c r="R13" s="98"/>
-      <c r="S13" s="98"/>
-      <c r="T13" s="98"/>
-      <c r="U13" s="98"/>
-      <c r="V13" s="98"/>
+      <c r="O13" s="94"/>
+      <c r="P13" s="94"/>
+      <c r="Q13" s="94"/>
+      <c r="R13" s="94"/>
+      <c r="S13" s="94"/>
+      <c r="T13" s="94"/>
+      <c r="U13" s="94"/>
+      <c r="V13" s="94"/>
     </row>
     <row r="14" spans="1:22" ht="15" x14ac:dyDescent="0.25">
-      <c r="A14" s="98"/>
-      <c r="B14" s="167"/>
-      <c r="C14" s="100" t="s">
+      <c r="A14" s="94"/>
+      <c r="B14" s="159"/>
+      <c r="C14" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="108">
+      <c r="D14" s="104">
         <v>93.55</v>
       </c>
-      <c r="E14" s="109">
+      <c r="E14" s="105">
         <v>93.58</v>
       </c>
-      <c r="F14" s="104">
+      <c r="F14" s="100">
         <v>93.72</v>
       </c>
-      <c r="G14" s="107">
+      <c r="G14" s="103">
         <v>91.3</v>
       </c>
-      <c r="H14" s="98"/>
-      <c r="I14" s="167"/>
-      <c r="J14" s="100" t="s">
+      <c r="H14" s="94"/>
+      <c r="I14" s="159"/>
+      <c r="J14" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="K14" s="109">
+      <c r="K14" s="105">
         <v>92.72</v>
       </c>
-      <c r="L14" s="104">
+      <c r="L14" s="100">
         <v>92.42</v>
       </c>
-      <c r="M14" s="104">
+      <c r="M14" s="100">
         <v>90.82</v>
       </c>
-      <c r="N14" s="108">
+      <c r="N14" s="104">
         <v>92.28</v>
       </c>
-      <c r="O14" s="98"/>
-      <c r="P14" s="98"/>
-      <c r="Q14" s="98"/>
-      <c r="R14" s="98"/>
-      <c r="S14" s="98"/>
-      <c r="T14" s="98"/>
-      <c r="U14" s="98"/>
-      <c r="V14" s="98"/>
+      <c r="O14" s="94"/>
+      <c r="P14" s="94"/>
+      <c r="Q14" s="94"/>
+      <c r="R14" s="94"/>
+      <c r="S14" s="94"/>
+      <c r="T14" s="94"/>
+      <c r="U14" s="94"/>
+      <c r="V14" s="94"/>
     </row>
     <row r="15" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="98"/>
-      <c r="B15" s="161"/>
-      <c r="C15" s="103" t="s">
+      <c r="A15" s="94"/>
+      <c r="B15" s="160"/>
+      <c r="C15" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="110">
+      <c r="D15" s="106">
         <v>88.64</v>
       </c>
-      <c r="E15" s="111">
+      <c r="E15" s="107">
         <v>92.55</v>
       </c>
-      <c r="F15" s="112">
+      <c r="F15" s="108">
         <v>89.15</v>
       </c>
-      <c r="G15" s="113">
+      <c r="G15" s="109">
         <v>88.35</v>
       </c>
-      <c r="H15" s="98"/>
-      <c r="I15" s="161"/>
-      <c r="J15" s="103" t="s">
+      <c r="H15" s="94"/>
+      <c r="I15" s="160"/>
+      <c r="J15" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="K15" s="111">
+      <c r="K15" s="107">
         <v>90.33</v>
       </c>
-      <c r="L15" s="112">
+      <c r="L15" s="108">
         <v>88.34</v>
       </c>
-      <c r="M15" s="112">
+      <c r="M15" s="108">
         <v>87.26</v>
       </c>
-      <c r="N15" s="110">
+      <c r="N15" s="106">
         <v>87.59</v>
       </c>
-      <c r="O15" s="98"/>
-      <c r="P15" s="98"/>
-      <c r="Q15" s="98"/>
-      <c r="R15" s="98"/>
-      <c r="S15" s="98"/>
-      <c r="T15" s="98"/>
-      <c r="U15" s="98"/>
-      <c r="V15" s="98"/>
+      <c r="O15" s="94"/>
+      <c r="P15" s="94"/>
+      <c r="Q15" s="94"/>
+      <c r="R15" s="94"/>
+      <c r="S15" s="94"/>
+      <c r="T15" s="94"/>
+      <c r="U15" s="94"/>
+      <c r="V15" s="94"/>
     </row>
     <row r="16" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="98"/>
-      <c r="B16" s="98"/>
-      <c r="C16" s="98"/>
-      <c r="D16" s="98"/>
-      <c r="E16" s="98"/>
-      <c r="F16" s="98"/>
-      <c r="G16" s="98"/>
-      <c r="H16" s="98"/>
-      <c r="I16" s="98"/>
-      <c r="J16" s="98"/>
-      <c r="K16" s="98"/>
-      <c r="L16" s="98"/>
-      <c r="M16" s="98"/>
-      <c r="N16" s="98"/>
-      <c r="O16" s="98"/>
-      <c r="P16" s="98"/>
-      <c r="Q16" s="98"/>
-      <c r="R16" s="98"/>
-      <c r="S16" s="98"/>
-      <c r="T16" s="98"/>
-      <c r="U16" s="98"/>
-      <c r="V16" s="98"/>
+      <c r="A16" s="94"/>
+      <c r="B16" s="94"/>
+      <c r="C16" s="94"/>
+      <c r="D16" s="94"/>
+      <c r="E16" s="94"/>
+      <c r="F16" s="94"/>
+      <c r="G16" s="94"/>
+      <c r="H16" s="94"/>
+      <c r="I16" s="94"/>
+      <c r="J16" s="94"/>
+      <c r="K16" s="94"/>
+      <c r="L16" s="94"/>
+      <c r="M16" s="94"/>
+      <c r="N16" s="94"/>
+      <c r="O16" s="94"/>
+      <c r="P16" s="94"/>
+      <c r="Q16" s="94"/>
+      <c r="R16" s="94"/>
+      <c r="S16" s="94"/>
+      <c r="T16" s="94"/>
+      <c r="U16" s="94"/>
+      <c r="V16" s="94"/>
     </row>
     <row r="17" spans="1:22" ht="15" x14ac:dyDescent="0.25">
-      <c r="A17" s="98"/>
-      <c r="B17" s="159" t="s">
+      <c r="A17" s="94"/>
+      <c r="B17" s="161" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="160"/>
-      <c r="D17" s="163" t="s">
+      <c r="C17" s="162"/>
+      <c r="D17" s="155" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="164"/>
-      <c r="F17" s="164"/>
-      <c r="G17" s="165"/>
-      <c r="H17" s="98"/>
-      <c r="I17" s="159" t="s">
+      <c r="E17" s="156"/>
+      <c r="F17" s="156"/>
+      <c r="G17" s="157"/>
+      <c r="H17" s="94"/>
+      <c r="I17" s="161" t="s">
         <v>35</v>
       </c>
-      <c r="J17" s="160"/>
-      <c r="K17" s="163" t="s">
+      <c r="J17" s="162"/>
+      <c r="K17" s="155" t="s">
         <v>31</v>
       </c>
-      <c r="L17" s="164"/>
-      <c r="M17" s="164"/>
-      <c r="N17" s="165"/>
-      <c r="O17" s="98"/>
-      <c r="P17" s="159" t="s">
+      <c r="L17" s="156"/>
+      <c r="M17" s="156"/>
+      <c r="N17" s="157"/>
+      <c r="O17" s="94"/>
+      <c r="P17" s="161" t="s">
         <v>34</v>
       </c>
-      <c r="Q17" s="160"/>
-      <c r="R17" s="163" t="s">
+      <c r="Q17" s="162"/>
+      <c r="R17" s="155" t="s">
         <v>31</v>
       </c>
-      <c r="S17" s="164"/>
-      <c r="T17" s="164"/>
-      <c r="U17" s="165"/>
-      <c r="V17" s="98"/>
+      <c r="S17" s="156"/>
+      <c r="T17" s="156"/>
+      <c r="U17" s="157"/>
+      <c r="V17" s="94"/>
     </row>
     <row r="18" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="98"/>
-      <c r="B18" s="161"/>
-      <c r="C18" s="162"/>
-      <c r="D18" s="100" t="s">
+      <c r="A18" s="94"/>
+      <c r="B18" s="160"/>
+      <c r="C18" s="163"/>
+      <c r="D18" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="E18" s="101" t="s">
+      <c r="E18" s="97" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="102" t="s">
+      <c r="F18" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="G18" s="103" t="s">
+      <c r="G18" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="H18" s="98"/>
-      <c r="I18" s="161"/>
-      <c r="J18" s="162"/>
-      <c r="K18" s="101" t="s">
+      <c r="H18" s="94"/>
+      <c r="I18" s="160"/>
+      <c r="J18" s="163"/>
+      <c r="K18" s="97" t="s">
         <v>27</v>
       </c>
-      <c r="L18" s="102" t="s">
+      <c r="L18" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="M18" s="102" t="s">
+      <c r="M18" s="98" t="s">
         <v>29</v>
       </c>
-      <c r="N18" s="100" t="s">
+      <c r="N18" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="O18" s="98"/>
-      <c r="P18" s="161"/>
-      <c r="Q18" s="162"/>
-      <c r="R18" s="101" t="s">
+      <c r="O18" s="94"/>
+      <c r="P18" s="160"/>
+      <c r="Q18" s="163"/>
+      <c r="R18" s="97" t="s">
         <v>27</v>
       </c>
-      <c r="S18" s="102" t="s">
+      <c r="S18" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="T18" s="102" t="s">
+      <c r="T18" s="98" t="s">
         <v>29</v>
       </c>
-      <c r="U18" s="100" t="s">
+      <c r="U18" s="96" t="s">
         <v>32</v>
       </c>
-      <c r="V18" s="98"/>
+      <c r="V18" s="94"/>
     </row>
     <row r="19" spans="1:22" ht="15" x14ac:dyDescent="0.25">
-      <c r="A19" s="98"/>
-      <c r="B19" s="166" t="s">
+      <c r="A19" s="94"/>
+      <c r="B19" s="158" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="99" t="s">
+      <c r="C19" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="D19" s="105">
+      <c r="D19" s="101">
         <v>90.61</v>
       </c>
-      <c r="E19" s="106">
+      <c r="E19" s="102">
         <v>91.1</v>
       </c>
-      <c r="F19" s="104">
+      <c r="F19" s="100">
         <v>91.28</v>
       </c>
-      <c r="G19" s="107">
+      <c r="G19" s="103">
         <v>91.16</v>
       </c>
-      <c r="H19" s="98"/>
-      <c r="I19" s="166" t="s">
+      <c r="H19" s="94"/>
+      <c r="I19" s="158" t="s">
         <v>30</v>
       </c>
-      <c r="J19" s="99" t="s">
+      <c r="J19" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="K19" s="106">
+      <c r="K19" s="102">
         <v>74.37</v>
       </c>
-      <c r="L19" s="104">
+      <c r="L19" s="100">
         <v>77.239999999999995</v>
       </c>
-      <c r="M19" s="104">
+      <c r="M19" s="100">
         <v>82.31</v>
       </c>
-      <c r="N19" s="105">
+      <c r="N19" s="101">
         <v>76.89</v>
       </c>
-      <c r="O19" s="98"/>
-      <c r="P19" s="166" t="s">
+      <c r="O19" s="94"/>
+      <c r="P19" s="158" t="s">
         <v>30</v>
       </c>
-      <c r="Q19" s="99" t="s">
+      <c r="Q19" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="R19" s="106">
+      <c r="R19" s="102">
         <v>56.35</v>
       </c>
-      <c r="S19" s="104">
+      <c r="S19" s="100">
         <v>56.64</v>
       </c>
-      <c r="T19" s="104">
+      <c r="T19" s="100">
         <v>57.69</v>
       </c>
-      <c r="U19" s="105">
+      <c r="U19" s="101">
         <v>57.43</v>
       </c>
-      <c r="V19" s="98"/>
+      <c r="V19" s="94"/>
     </row>
     <row r="20" spans="1:22" ht="15" x14ac:dyDescent="0.25">
-      <c r="A20" s="98"/>
-      <c r="B20" s="167"/>
-      <c r="C20" s="100" t="s">
+      <c r="A20" s="94"/>
+      <c r="B20" s="159"/>
+      <c r="C20" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="D20" s="108">
+      <c r="D20" s="104">
         <v>90.5</v>
       </c>
-      <c r="E20" s="109">
+      <c r="E20" s="105">
         <v>90.92</v>
       </c>
-      <c r="F20" s="104">
+      <c r="F20" s="100">
         <v>90.69</v>
       </c>
-      <c r="G20" s="107">
+      <c r="G20" s="103">
         <v>89.93</v>
       </c>
-      <c r="H20" s="98"/>
-      <c r="I20" s="167"/>
-      <c r="J20" s="100" t="s">
+      <c r="H20" s="94"/>
+      <c r="I20" s="159"/>
+      <c r="J20" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="K20" s="109">
+      <c r="K20" s="105">
         <v>73.430000000000007</v>
       </c>
-      <c r="L20" s="104">
+      <c r="L20" s="100">
         <v>75.78</v>
       </c>
-      <c r="M20" s="104">
+      <c r="M20" s="100">
         <v>80.989999999999995</v>
       </c>
-      <c r="N20" s="108">
+      <c r="N20" s="104">
         <v>72.8</v>
       </c>
-      <c r="O20" s="98"/>
-      <c r="P20" s="167"/>
-      <c r="Q20" s="100" t="s">
+      <c r="O20" s="94"/>
+      <c r="P20" s="159"/>
+      <c r="Q20" s="96" t="s">
         <v>28</v>
       </c>
-      <c r="R20" s="109">
+      <c r="R20" s="105">
         <v>56.56</v>
       </c>
-      <c r="S20" s="104">
+      <c r="S20" s="100">
         <v>55.76</v>
       </c>
-      <c r="T20" s="104">
+      <c r="T20" s="100">
         <v>55.07</v>
       </c>
-      <c r="U20" s="108">
+      <c r="U20" s="104">
         <v>54.06</v>
       </c>
-      <c r="V20" s="98"/>
+      <c r="V20" s="94"/>
     </row>
     <row r="21" spans="1:22" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="98"/>
-      <c r="B21" s="161"/>
-      <c r="C21" s="103" t="s">
+      <c r="A21" s="94"/>
+      <c r="B21" s="160"/>
+      <c r="C21" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="110">
+      <c r="D21" s="106">
         <v>87.1</v>
       </c>
-      <c r="E21" s="111">
+      <c r="E21" s="107">
         <v>89.67</v>
       </c>
-      <c r="F21" s="112">
+      <c r="F21" s="108">
         <v>87.91</v>
       </c>
-      <c r="G21" s="113">
+      <c r="G21" s="109">
         <v>87.1</v>
       </c>
-      <c r="H21" s="98"/>
-      <c r="I21" s="161"/>
-      <c r="J21" s="103" t="s">
+      <c r="H21" s="94"/>
+      <c r="I21" s="160"/>
+      <c r="J21" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="K21" s="111">
+      <c r="K21" s="107">
         <v>78.680000000000007</v>
       </c>
-      <c r="L21" s="112">
+      <c r="L21" s="108">
         <v>77.040000000000006</v>
       </c>
-      <c r="M21" s="112">
+      <c r="M21" s="108">
         <v>75.41</v>
       </c>
-      <c r="N21" s="110">
+      <c r="N21" s="106">
         <v>74.819999999999993</v>
       </c>
-      <c r="O21" s="98"/>
-      <c r="P21" s="161"/>
-      <c r="Q21" s="103" t="s">
+      <c r="O21" s="94"/>
+      <c r="P21" s="160"/>
+      <c r="Q21" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="R21" s="111">
+      <c r="R21" s="107">
         <v>53.09</v>
       </c>
-      <c r="S21" s="112">
+      <c r="S21" s="108">
         <v>51.47</v>
       </c>
-      <c r="T21" s="112">
+      <c r="T21" s="108">
         <v>50.41</v>
       </c>
-      <c r="U21" s="110">
+      <c r="U21" s="106">
         <v>50.06</v>
       </c>
-      <c r="V21" s="98"/>
+      <c r="V21" s="94"/>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A22" s="98"/>
-      <c r="B22" s="98"/>
-      <c r="C22" s="98"/>
-      <c r="D22" s="98"/>
-      <c r="E22" s="98"/>
-      <c r="F22" s="98"/>
-      <c r="G22" s="98"/>
-      <c r="H22" s="98"/>
-      <c r="I22" s="98"/>
-      <c r="J22" s="98"/>
-      <c r="K22" s="98"/>
-      <c r="L22" s="98"/>
-      <c r="M22" s="98"/>
-      <c r="N22" s="98"/>
-      <c r="O22" s="98"/>
-      <c r="P22" s="98"/>
-      <c r="Q22" s="98"/>
-      <c r="R22" s="98"/>
-      <c r="S22" s="98"/>
-      <c r="T22" s="98"/>
-      <c r="U22" s="98"/>
-      <c r="V22" s="98"/>
+      <c r="A22" s="94"/>
+      <c r="B22" s="94"/>
+      <c r="C22" s="94"/>
+      <c r="D22" s="94"/>
+      <c r="E22" s="94"/>
+      <c r="F22" s="94"/>
+      <c r="G22" s="94"/>
+      <c r="H22" s="94"/>
+      <c r="I22" s="94"/>
+      <c r="J22" s="94"/>
+      <c r="K22" s="94"/>
+      <c r="L22" s="94"/>
+      <c r="M22" s="94"/>
+      <c r="N22" s="94"/>
+      <c r="O22" s="94"/>
+      <c r="P22" s="94"/>
+      <c r="Q22" s="94"/>
+      <c r="R22" s="94"/>
+      <c r="S22" s="94"/>
+      <c r="T22" s="94"/>
+      <c r="U22" s="94"/>
+      <c r="V22" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="P17:Q18"/>
+    <mergeCell ref="R17:U17"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="I19:I21"/>
+    <mergeCell ref="P19:P21"/>
     <mergeCell ref="D3:G3"/>
     <mergeCell ref="D11:G11"/>
     <mergeCell ref="D17:G17"/>
@@ -8534,11 +8641,6 @@
     <mergeCell ref="B5:B7"/>
     <mergeCell ref="B11:C12"/>
     <mergeCell ref="I11:J12"/>
-    <mergeCell ref="P17:Q18"/>
-    <mergeCell ref="R17:U17"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="I19:I21"/>
-    <mergeCell ref="P19:P21"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="D5:D7">

--- a/results_(stress_test)_baselines/summary.xlsx
+++ b/results_(stress_test)_baselines/summary.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B2D0DC-A473-480E-9EE7-404C7EC5E523}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-210" windowWidth="29040" windowHeight="16440" tabRatio="639" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-210" windowWidth="29040" windowHeight="16440" tabRatio="639" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="partialdata_20260618_unf_idx" sheetId="6" r:id="rId1"/>
